--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="71">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -209,10 +209,16 @@
     <t>Pedido para villacicencio</t>
   </si>
   <si>
-    <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS</t>
+    <t>Se envía huevo más fresco a Sincelejo</t>
+  </si>
+  <si>
+    <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
   </si>
   <si>
     <t>ALKA2</t>
+  </si>
+  <si>
+    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
   </si>
   <si>
     <t>LANZA</t>
@@ -282,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -332,6 +338,9 @@
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -2166,7 +2175,9 @@
       <c r="B49" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="14"/>
+      <c r="C49" s="14" t="s">
+        <v>15</v>
+      </c>
       <c r="D49" s="7">
         <v>2110402.0</v>
       </c>
@@ -2182,8 +2193,12 @@
       <c r="H49" s="7">
         <v>287235.0</v>
       </c>
-      <c r="I49" s="10"/>
-      <c r="J49" s="12"/>
+      <c r="I49" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="9">
@@ -2214,7 +2229,7 @@
         <v>26</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51">
@@ -5163,7 +5178,7 @@
         <v>46224.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="7">
@@ -5181,22 +5196,26 @@
       <c r="H2" s="7">
         <v>3712.0</v>
       </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="11"/>
+      <c r="I2" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="9">
         <v>46224.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="7">
         <v>2114158.0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F3" s="7">
         <v>60.0</v>
@@ -5207,7 +5226,7 @@
       <c r="H3" s="7">
         <v>60.0</v>
       </c>
-      <c r="I3" s="17"/>
+      <c r="I3" s="18"/>
       <c r="J3" s="11"/>
     </row>
     <row r="4">

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="85">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -215,6 +215,12 @@
     <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
   </si>
   <si>
+    <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
+  </si>
+  <si>
+    <t>SalIO en sugeridos de hoy 22/07/2026</t>
+  </si>
+  <si>
     <t>ALKA2</t>
   </si>
   <si>
@@ -225,6 +231,42 @@
   </si>
   <si>
     <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
+  </si>
+  <si>
+    <t>Pendiente Transformar Roto GT Por manipulación</t>
+  </si>
+  <si>
+    <t>HUEVO B X30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>se equivocaron al cargar una estiba</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+  </si>
+  <si>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+  </si>
+  <si>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
+  </si>
+  <si>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
   </si>
 </sst>
 </file>
@@ -341,8 +383,8 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,7 +475,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J50" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J53" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -451,7 +493,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J3" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J9" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -2232,14 +2274,99 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51">
-      <c r="I51" s="16"/>
-    </row>
-    <row r="52">
-      <c r="I52" s="16"/>
-    </row>
-    <row r="53">
-      <c r="I53" s="16"/>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D51" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" s="7">
+        <v>130560.0</v>
+      </c>
+      <c r="G51" s="7">
+        <v>52658.0</v>
+      </c>
+      <c r="H51" s="7">
+        <v>153840.0</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="7">
+        <v>87447.0</v>
+      </c>
+      <c r="G52" s="7">
+        <v>59056.0</v>
+      </c>
+      <c r="H52" s="7">
+        <v>104365.0</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="12"/>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="7">
+        <v>25200.0</v>
+      </c>
+      <c r="G53" s="7">
+        <v>2085.0</v>
+      </c>
+      <c r="H53" s="7">
+        <v>25920.0</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="54">
       <c r="I54" s="16"/>
@@ -5105,13 +5232,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I50">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I53">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I51:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I54:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A50">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A53">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -5178,7 +5305,7 @@
         <v>46224.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="7">
@@ -5200,7 +5327,7 @@
         <v>26</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -5208,14 +5335,14 @@
         <v>46224.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="7">
         <v>2114158.0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F3" s="7">
         <v>60.0</v>
@@ -5226,26 +5353,192 @@
       <c r="H3" s="7">
         <v>60.0</v>
       </c>
-      <c r="I3" s="18"/>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4">
-      <c r="I4" s="16"/>
-    </row>
-    <row r="5">
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6">
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7">
-      <c r="I7" s="16"/>
-    </row>
-    <row r="8">
-      <c r="I8" s="16"/>
-    </row>
-    <row r="9">
-      <c r="I9" s="16"/>
+      <c r="I3" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="7">
+        <v>10501.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="7">
+        <v>415093.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>115920.0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>543038.0</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>29400.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>12300.0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="7">
+        <v>132357.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1560.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1560.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>4560.0</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>11160.0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>5940.0</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="7">
+        <v>3712.0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>46723.0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>213.0</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="10">
       <c r="I10" s="16"/>
@@ -8102,13 +8395,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I3">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I9">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I10:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A3">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A9">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="88">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -221,6 +221,12 @@
     <t>SalIO en sugeridos de hoy 22/07/2026</t>
   </si>
   <si>
+    <t>Yovanis Arevalo</t>
+  </si>
+  <si>
+    <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
+  </si>
+  <si>
     <t>ALKA2</t>
   </si>
   <si>
@@ -267,6 +273,9 @@
   </si>
   <si>
     <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+  </si>
+  <si>
+    <t>HUEVO PICADO ROJO</t>
   </si>
 </sst>
 </file>
@@ -475,7 +484,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J53" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J55" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -493,7 +502,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J9" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J13" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -2368,11 +2377,67 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54">
-      <c r="I54" s="16"/>
-    </row>
-    <row r="55">
-      <c r="I55" s="16"/>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" s="7">
+        <v>285405.0</v>
+      </c>
+      <c r="G54" s="7">
+        <v>203180.0</v>
+      </c>
+      <c r="H54" s="7">
+        <v>226069.0</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D55" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="7">
+        <v>692280.0</v>
+      </c>
+      <c r="G55" s="7">
+        <v>118381.0</v>
+      </c>
+      <c r="H55" s="7">
+        <v>700200.0</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J55" s="12"/>
     </row>
     <row r="56">
       <c r="I56" s="16"/>
@@ -5232,13 +5297,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I53">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I55">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I54:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I56:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A53">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A55">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -5305,7 +5370,7 @@
         <v>46224.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="7">
@@ -5327,7 +5392,7 @@
         <v>26</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
@@ -5335,14 +5400,14 @@
         <v>46224.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="7">
         <v>2114158.0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="7">
         <v>60.0</v>
@@ -5357,7 +5422,7 @@
         <v>37</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
@@ -5365,14 +5430,14 @@
         <v>46225.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="7">
         <v>10501.0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" s="7">
         <v>415093.0</v>
@@ -5387,7 +5452,7 @@
         <v>17</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
@@ -5395,14 +5460,14 @@
         <v>46225.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="7">
         <v>112379.0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F5" s="7">
         <v>3000.0</v>
@@ -5417,7 +5482,7 @@
         <v>26</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
@@ -5425,14 +5490,14 @@
         <v>46225.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="7">
         <v>112268.0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F6" s="7">
         <v>3000.0</v>
@@ -5447,7 +5512,7 @@
         <v>26</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
@@ -5455,14 +5520,14 @@
         <v>46225.0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="7">
         <v>132357.0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F7" s="7">
         <v>1560.0</v>
@@ -5477,7 +5542,7 @@
         <v>26</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
@@ -5485,7 +5550,7 @@
         <v>46225.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="7">
@@ -5507,7 +5572,7 @@
         <v>26</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
@@ -5515,7 +5580,7 @@
         <v>46225.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="7">
@@ -5537,20 +5602,112 @@
         <v>26</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="I10" s="16"/>
-    </row>
-    <row r="11">
-      <c r="I11" s="16"/>
-    </row>
-    <row r="12">
-      <c r="I12" s="16"/>
-    </row>
-    <row r="13">
-      <c r="I13" s="16"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="7">
+        <v>73001.0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="7">
+        <v>73787.0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>72000.0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>109487.0</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>1800.0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="12"/>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="7">
+        <v>4200.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>7500.0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>3900.0</v>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="12"/>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="7">
+        <v>379471.0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>392580.0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>357186.0</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="12"/>
     </row>
     <row r="14">
       <c r="I14" s="16"/>
@@ -8395,13 +8552,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I9">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I13">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I10:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I14:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A9">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A13">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="93">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -44,96 +44,159 @@
     <t xml:space="preserve">Otro </t>
   </si>
   <si>
+    <t>ALKA2</t>
+  </si>
+  <si>
     <t>TAT BOGOTA MONTEVIDEO</t>
   </si>
   <si>
     <t>Daniel Castro</t>
   </si>
   <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t>7. Otro</t>
+  </si>
+  <si>
+    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
+  </si>
+  <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
     <t>TAT MONTERIA</t>
   </si>
   <si>
+    <t>LANZA</t>
+  </si>
+  <si>
     <t>LUIS LOPEZ</t>
   </si>
   <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
     <t>3. Falla De Rotación</t>
   </si>
   <si>
+    <t>6. Transformación De Referencias</t>
+  </si>
+  <si>
+    <t>Pendiente Transformar Roto GT Por manipulación</t>
+  </si>
+  <si>
     <t>TAT MEDELLIN</t>
   </si>
   <si>
     <t>FABIO GOMEZ</t>
   </si>
   <si>
+    <t>HUEVO B X30 CARTON GRIS</t>
+  </si>
+  <si>
     <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
   </si>
   <si>
+    <t>se equivocaron al cargar una estiba</t>
+  </si>
+  <si>
     <t>TAT CARTAGENA</t>
   </si>
   <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
     <t>Dilan Barraza</t>
   </si>
   <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
     <t>4. Exigencia Del Cliente (Edad)</t>
   </si>
   <si>
     <t>Venta FS</t>
   </si>
   <si>
-    <t>7. Otro</t>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+  </si>
+  <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
+  </si>
+  <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+  </si>
+  <si>
     <t>TAT CALI</t>
   </si>
   <si>
     <t>DIEGO ROJAS</t>
   </si>
   <si>
+    <t>HUEVO PICADO ROJO</t>
+  </si>
+  <si>
+    <t>No se carga todod por capacidad de Vehiculo</t>
+  </si>
+  <si>
     <t>TAT CUCUTA</t>
   </si>
   <si>
     <t>ALEXANDER PEÑA</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
-    <t>6. Transformación De Referencias</t>
-  </si>
-  <si>
     <t>Clientes FS</t>
   </si>
   <si>
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
+    <t>HUEVO SUCIO DE JAULA</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
+    <t>Esta para despacho hoy</t>
+  </si>
+  <si>
     <t>Transformación de PET</t>
   </si>
   <si>
@@ -149,6 +212,9 @@
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
+    <t>Cola de programación</t>
+  </si>
+  <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
@@ -225,57 +291,6 @@
   </si>
   <si>
     <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
-  </si>
-  <si>
-    <t>ALKA2</t>
-  </si>
-  <si>
-    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
-  </si>
-  <si>
-    <t>LANZA</t>
-  </si>
-  <si>
-    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
-  </si>
-  <si>
-    <t>Pendiente Transformar Roto GT Por manipulación</t>
-  </si>
-  <si>
-    <t>HUEVO B X30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>se equivocaron al cargar una estiba</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
-  </si>
-  <si>
-    <t>PALMAS</t>
-  </si>
-  <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
-  </si>
-  <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
-  </si>
-  <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
-  </si>
-  <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
-  </si>
-  <si>
-    <t>HUEVO PICADO ROJO</t>
   </si>
 </sst>
 </file>
@@ -315,14 +330,14 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -339,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -353,44 +368,47 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -484,7 +502,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J55" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J59" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -502,7 +520,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J13" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J18" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -765,1691 +783,1791 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>46204.0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="7">
+      <c r="C2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="9">
+        <v>359100.0</v>
+      </c>
+      <c r="G2" s="9">
+        <v>83486.0</v>
+      </c>
+      <c r="H2" s="9">
+        <v>206140.0</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" hidden="1" customHeight="1">
+      <c r="A3" s="4">
+        <v>46205.0</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="9">
+        <v>298282.0</v>
+      </c>
+      <c r="G3" s="9">
+        <v>42201.0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>260675.0</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
+      <c r="A4" s="4">
+        <v>46205.0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2110217.0</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="9">
+        <v>21120.0</v>
+      </c>
+      <c r="G4" s="9">
+        <v>11039.0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>16920.0</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="7"/>
+    </row>
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
+      <c r="A5" s="4">
+        <v>46205.0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="9">
+        <v>75680.0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>5640.0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>3134.0</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="9">
+        <v>189540.0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>161685.0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>144720.0</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="9">
+        <v>20640.0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>3761.0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>13920.0</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="9">
+        <v>14700.0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>6435.0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>9600.0</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="11"/>
+    </row>
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
+      <c r="A9" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="9">
+        <v>228240.0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>77306.0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>124260.0</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
+      <c r="A10" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="9">
+        <v>7830.0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>1980.0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>6030.0</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="9">
+        <v>31680.0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>5526.0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>23040.0</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
+      <c r="A12" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="9">
+        <v>51387.0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>10827.0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>12170.0</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
+      <c r="A13" s="4">
+        <v>46209.0</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="9">
+        <v>195810.0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>93809.0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>133410.0</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
+      <c r="A14" s="4">
+        <v>46209.0</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="9">
+        <v>526002.0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>301965.0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>424588.0</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="4">
+        <v>46209.0</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="9">
+        <v>14160.0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>6692.0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>12360.0</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
+      <c r="A16" s="4">
+        <v>46210.0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="9">
+        <v>149040.0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>119573.0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>289680.0</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" ht="22.5" hidden="1" customHeight="1">
+      <c r="A17" s="4">
+        <v>46210.0</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="9">
+        <v>2110217.0</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="9">
+        <v>22770.0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>3926.0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>19770.0</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" ht="22.5" hidden="1" customHeight="1">
+      <c r="A18" s="4">
+        <v>46210.0</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="9">
+        <v>222021.0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>61385.0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>162125.0</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="11"/>
+    </row>
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
+      <c r="A19" s="4">
+        <v>46211.0</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="9">
+        <v>495833.0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>148815.0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>401280.0</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
+      <c r="A20" s="4">
+        <v>46211.0</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="9">
+        <v>139920.0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>54384.0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>74040.0</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="11"/>
+    </row>
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
+      <c r="A21" s="4">
+        <v>46211.0</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="9">
+        <v>162125.0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>60138.0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>100687.0</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" hidden="1" customHeight="1">
+      <c r="A22" s="4">
+        <v>46211.0</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="7">
-        <v>359100.0</v>
-      </c>
-      <c r="G2" s="7">
-        <v>83486.0</v>
-      </c>
-      <c r="H2" s="7">
-        <v>206140.0</v>
-      </c>
-      <c r="I2" s="8" t="s">
+      <c r="D22" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="9">
+        <v>32850.0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>7065.0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>32700.0</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" ht="22.5" hidden="1" customHeight="1">
+      <c r="A23" s="4">
+        <v>46211.0</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="9">
+        <v>112271.0</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="9">
+        <v>16500.0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>5310.0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>18000.0</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J23" s="11"/>
+    </row>
+    <row r="24" ht="22.5" hidden="1" customHeight="1">
+      <c r="A24" s="4">
+        <v>46212.0</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="9">
+        <v>190047.0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>59822.0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>248481.0</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" s="11"/>
+    </row>
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
+      <c r="A25" s="4">
+        <v>46212.0</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="9">
+        <v>178080.0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>47784.0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>203520.0</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J25" s="11"/>
+    </row>
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
+      <c r="A26" s="4">
+        <v>46212.0</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="9">
-        <v>46205.0</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="F26" s="9">
+        <v>10320.0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>5869.0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>13200.0</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
+      <c r="A27" s="4">
+        <v>46212.0</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="9">
+        <v>112271.0</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" s="9">
+        <v>18000.0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>4485.0</v>
+      </c>
+      <c r="H27" s="9">
+        <v>13500.0</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="11"/>
+    </row>
+    <row r="28" ht="22.5" hidden="1" customHeight="1">
+      <c r="A28" s="4">
+        <v>46213.0</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="9">
+        <v>208440.0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>85608.0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>150833.0</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" hidden="1" customHeight="1">
+      <c r="A29" s="4">
+        <v>46213.0</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="F29" s="9">
+        <v>962820.0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>80644.0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>922140.0</v>
+      </c>
+      <c r="I29" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="7">
+      <c r="J29" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
+      <c r="A30" s="4">
+        <v>46213.0</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="9">
+        <v>335340.0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>111433.0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>381600.0</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="4">
+        <v>46213.0</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="9">
+        <v>316800.0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>99546.0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>229680.0</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" s="11"/>
+    </row>
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
+      <c r="A32" s="4">
+        <v>46213.0</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="9">
+        <v>176850.0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>47499.0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>128971.0</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
+      <c r="A33" s="4">
+        <v>46213.0</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="7">
-        <v>298282.0</v>
-      </c>
-      <c r="G3" s="7">
-        <v>42201.0</v>
-      </c>
-      <c r="H3" s="7">
-        <v>260675.0</v>
-      </c>
-      <c r="I3" s="10" t="s">
+      <c r="E33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="9">
+        <v>58080.0</v>
+      </c>
+      <c r="G33" s="9">
+        <v>20865.0</v>
+      </c>
+      <c r="H33" s="9">
+        <v>25440.0</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="11"/>
+    </row>
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
+      <c r="A34" s="4">
+        <v>46217.0</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="9">
+        <v>481440.0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>464517.0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>151435.0</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" ht="22.5" hidden="1" customHeight="1">
+      <c r="A35" s="4">
+        <v>46217.0</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="9">
+        <v>355720.0</v>
+      </c>
+      <c r="G35" s="9">
+        <v>342811.0</v>
+      </c>
+      <c r="H35" s="9">
+        <v>302760.0</v>
+      </c>
+      <c r="I35" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="9">
-        <v>46205.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="J35" s="11"/>
+    </row>
+    <row r="36" ht="22.5" hidden="1" customHeight="1">
+      <c r="A36" s="4">
+        <v>46217.0</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" s="9">
+        <v>35280.0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>16988.0</v>
+      </c>
+      <c r="H36" s="9">
+        <v>37926.0</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" hidden="1" customHeight="1">
+      <c r="A37" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="9">
+        <v>272073.0</v>
+      </c>
+      <c r="G37" s="9">
+        <v>76546.0</v>
+      </c>
+      <c r="H37" s="9">
+        <v>275205.0</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" ht="22.5" hidden="1" customHeight="1">
+      <c r="A38" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="9">
+        <v>37926.0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>5633.0</v>
+      </c>
+      <c r="H38" s="9">
+        <v>25746.0</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" ht="22.5" hidden="1" customHeight="1">
+      <c r="A39" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9">
+        <v>20640.0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>4951.0</v>
+      </c>
+      <c r="H39" s="9">
+        <v>16320.0</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" ht="22.5" hidden="1" customHeight="1">
+      <c r="A40" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" s="9">
+        <v>10980.0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>2379.0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>13500.0</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" ht="22.5" hidden="1" customHeight="1">
+      <c r="A41" s="4">
+        <v>46219.0</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F41" s="9">
+        <v>130320.0</v>
+      </c>
+      <c r="G41" s="9">
+        <v>47410.0</v>
+      </c>
+      <c r="H41" s="9">
+        <v>90480.0</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" ht="22.5" hidden="1" customHeight="1">
+      <c r="A42" s="4">
+        <v>46219.0</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F42" s="9">
+        <v>36225.0</v>
+      </c>
+      <c r="G42" s="9">
+        <v>11746.0</v>
+      </c>
+      <c r="H42" s="9">
+        <v>27570.0</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" ht="22.5" hidden="1" customHeight="1">
+      <c r="A43" s="4">
+        <v>46219.0</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="9">
+        <v>152833.0</v>
+      </c>
+      <c r="G43" s="9">
+        <v>50641.0</v>
+      </c>
+      <c r="H43" s="9">
+        <v>96472.0</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" hidden="1" customHeight="1">
+      <c r="A44" s="4">
+        <v>46219.0</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="9">
+        <v>237828.0</v>
+      </c>
+      <c r="G44" s="9">
+        <v>173585.0</v>
+      </c>
+      <c r="H44" s="9">
+        <v>71560.0</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" ht="22.5" hidden="1" customHeight="1">
+      <c r="A45" s="4">
+        <v>46219.0</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F45" s="9">
+        <v>31125.0</v>
+      </c>
+      <c r="G45" s="9">
+        <v>7815.0</v>
+      </c>
+      <c r="H45" s="9">
+        <v>31845.0</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" hidden="1" customHeight="1">
+      <c r="A46" s="4">
+        <v>46219.0</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F46" s="9">
+        <v>25746.0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>6168.0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>28683.0</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" ht="22.5" hidden="1" customHeight="1">
+      <c r="A47" s="4">
+        <v>46220.0</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="9">
+        <v>261166.0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>74573.0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>221549.0</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" ht="22.5" hidden="1" customHeight="1">
+      <c r="A48" s="4">
+        <v>46220.0</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="9">
+        <v>2110217.0</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" s="9">
+        <v>115289.0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>26931.0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>119584.0</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" s="11"/>
+    </row>
+    <row r="49" ht="22.5" hidden="1" customHeight="1">
+      <c r="A49" s="4">
+        <v>46224.0</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7">
-        <v>2110217.0</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="C49" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="7">
-        <v>21120.0</v>
-      </c>
-      <c r="G4" s="7">
-        <v>11039.0</v>
-      </c>
-      <c r="H4" s="7">
-        <v>16920.0</v>
-      </c>
-      <c r="I4" s="10" t="s">
+      <c r="D49" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="11"/>
-    </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="9">
-        <v>46205.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="F49" s="9">
+        <v>398570.0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>288226.0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>287235.0</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" ht="22.5" hidden="1" customHeight="1">
+      <c r="A50" s="4">
+        <v>46224.0</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="9">
+        <v>745107.0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>378927.0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>551645.0</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" s="9">
+        <v>130560.0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>52658.0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>153840.0</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="9">
+        <v>87447.0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>59056.0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>104365.0</v>
+      </c>
+      <c r="I52" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="7">
-        <v>75680.0</v>
-      </c>
-      <c r="G5" s="7">
-        <v>5640.0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>3134.0</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="12" t="s">
+      <c r="J52" s="11"/>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D53" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9">
+        <v>25200.0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>2085.0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>25920.0</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="9">
+        <v>285405.0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>203180.0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>226069.0</v>
+      </c>
+      <c r="I54" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="C55" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="7">
-        <v>189540.0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>161685.0</v>
-      </c>
-      <c r="H6" s="7">
-        <v>144720.0</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="7">
-        <v>2010102.0</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="7">
-        <v>20640.0</v>
-      </c>
-      <c r="G7" s="7">
-        <v>3761.0</v>
-      </c>
-      <c r="H7" s="7">
-        <v>13920.0</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="7">
-        <v>152384.0</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="E55" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="9">
+        <v>692280.0</v>
+      </c>
+      <c r="G55" s="9">
+        <v>118381.0</v>
+      </c>
+      <c r="H55" s="9">
+        <v>700200.0</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J55" s="11"/>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="A56" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" s="9">
+        <v>700200.0</v>
+      </c>
+      <c r="G56" s="9">
+        <v>112628.0</v>
+      </c>
+      <c r="H56" s="9">
+        <v>668440.0</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" s="11"/>
+    </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="7">
-        <v>14700.0</v>
-      </c>
-      <c r="G8" s="7">
-        <v>6435.0</v>
-      </c>
-      <c r="H8" s="7">
-        <v>9600.0</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C57" s="19"/>
+      <c r="D57" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="9">
+        <v>226069.0</v>
+      </c>
+      <c r="G57" s="9">
+        <v>193130.0</v>
+      </c>
+      <c r="H57" s="9">
+        <v>326391.0</v>
+      </c>
+      <c r="I57" s="13"/>
+      <c r="J57" s="11"/>
+    </row>
+    <row r="58" ht="22.5" customHeight="1">
+      <c r="A58" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="7">
-        <v>228240.0</v>
-      </c>
-      <c r="G9" s="7">
-        <v>77306.0</v>
-      </c>
-      <c r="H9" s="7">
-        <v>124260.0</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="7">
-        <v>2152388.0</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="7">
-        <v>7830.0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>1980.0</v>
-      </c>
-      <c r="H10" s="7">
-        <v>6030.0</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="13"/>
-    </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="E58" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="9">
+        <v>144637.0</v>
+      </c>
+      <c r="G58" s="9">
+        <v>64227.0</v>
+      </c>
+      <c r="H58" s="9">
+        <v>128160.0</v>
+      </c>
+      <c r="I58" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="J58" s="11"/>
+    </row>
+    <row r="59" ht="22.5" customHeight="1">
+      <c r="A59" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" s="19"/>
+      <c r="D59" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="7">
-        <v>31680.0</v>
-      </c>
-      <c r="G11" s="7">
-        <v>5526.0</v>
-      </c>
-      <c r="H11" s="7">
-        <v>23040.0</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="7">
-        <v>51387.0</v>
-      </c>
-      <c r="G12" s="7">
-        <v>10827.0</v>
-      </c>
-      <c r="H12" s="7">
-        <v>12170.0</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="9">
-        <v>46209.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="7">
-        <v>195810.0</v>
-      </c>
-      <c r="G13" s="7">
-        <v>93809.0</v>
-      </c>
-      <c r="H13" s="7">
-        <v>133410.0</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="9">
-        <v>46209.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="7">
-        <v>526002.0</v>
-      </c>
-      <c r="G14" s="7">
-        <v>301965.0</v>
-      </c>
-      <c r="H14" s="7">
-        <v>424588.0</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="9">
-        <v>46209.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="7">
-        <v>2010102.0</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="7">
-        <v>14160.0</v>
-      </c>
-      <c r="G15" s="7">
-        <v>6692.0</v>
-      </c>
-      <c r="H15" s="7">
-        <v>12360.0</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="9">
-        <v>46210.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="7">
-        <v>149040.0</v>
-      </c>
-      <c r="G16" s="7">
-        <v>119573.0</v>
-      </c>
-      <c r="H16" s="7">
-        <v>289680.0</v>
-      </c>
-      <c r="I16" s="10" t="s">
+      <c r="E59" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="9">
-        <v>46210.0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="7">
-        <v>2110217.0</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="7">
-        <v>22770.0</v>
-      </c>
-      <c r="G17" s="7">
-        <v>3926.0</v>
-      </c>
-      <c r="H17" s="7">
-        <v>19770.0</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="12"/>
-    </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="9">
-        <v>46210.0</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="7">
-        <v>222021.0</v>
-      </c>
-      <c r="G18" s="7">
-        <v>61385.0</v>
-      </c>
-      <c r="H18" s="7">
-        <v>162125.0</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="12"/>
-    </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="9">
-        <v>46211.0</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="7">
-        <v>495833.0</v>
-      </c>
-      <c r="G19" s="7">
-        <v>148815.0</v>
-      </c>
-      <c r="H19" s="7">
-        <v>401280.0</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="9">
-        <v>46211.0</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="7">
-        <v>139920.0</v>
-      </c>
-      <c r="G20" s="7">
-        <v>54384.0</v>
-      </c>
-      <c r="H20" s="7">
-        <v>74040.0</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="12"/>
-    </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="9">
-        <v>46211.0</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="7">
-        <v>162125.0</v>
-      </c>
-      <c r="G21" s="7">
-        <v>60138.0</v>
-      </c>
-      <c r="H21" s="7">
-        <v>100687.0</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="9">
-        <v>46211.0</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="7">
-        <v>152384.0</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="7">
-        <v>32850.0</v>
-      </c>
-      <c r="G22" s="7">
-        <v>7065.0</v>
-      </c>
-      <c r="H22" s="7">
-        <v>32700.0</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="12"/>
-    </row>
-    <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="9">
-        <v>46211.0</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="7">
-        <v>112271.0</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="7">
-        <v>16500.0</v>
-      </c>
-      <c r="G23" s="7">
-        <v>5310.0</v>
-      </c>
-      <c r="H23" s="7">
-        <v>18000.0</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="12"/>
-    </row>
-    <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="9">
-        <v>46212.0</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="7">
-        <v>190047.0</v>
-      </c>
-      <c r="G24" s="7">
-        <v>59822.0</v>
-      </c>
-      <c r="H24" s="7">
-        <v>248481.0</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" s="12"/>
-    </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="9">
-        <v>46212.0</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="7">
-        <v>178080.0</v>
-      </c>
-      <c r="G25" s="7">
-        <v>47784.0</v>
-      </c>
-      <c r="H25" s="7">
-        <v>203520.0</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J25" s="12"/>
-    </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="9">
-        <v>46212.0</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" s="7">
-        <v>10320.0</v>
-      </c>
-      <c r="G26" s="7">
-        <v>5869.0</v>
-      </c>
-      <c r="H26" s="7">
-        <v>13200.0</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="9">
-        <v>46212.0</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="7">
-        <v>112271.0</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F27" s="7">
-        <v>18000.0</v>
-      </c>
-      <c r="G27" s="7">
-        <v>4485.0</v>
-      </c>
-      <c r="H27" s="7">
-        <v>13500.0</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="12"/>
-    </row>
-    <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="9">
-        <v>46213.0</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="7">
-        <v>208440.0</v>
-      </c>
-      <c r="G28" s="7">
-        <v>85608.0</v>
-      </c>
-      <c r="H28" s="7">
-        <v>150833.0</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="9">
-        <v>46213.0</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="7">
-        <v>962820.0</v>
-      </c>
-      <c r="G29" s="7">
-        <v>80644.0</v>
-      </c>
-      <c r="H29" s="7">
-        <v>922140.0</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J29" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="9">
-        <v>46213.0</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="7">
-        <v>335340.0</v>
-      </c>
-      <c r="G30" s="7">
-        <v>111433.0</v>
-      </c>
-      <c r="H30" s="7">
-        <v>381600.0</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="9">
-        <v>46213.0</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="7">
-        <v>316800.0</v>
-      </c>
-      <c r="G31" s="7">
-        <v>99546.0</v>
-      </c>
-      <c r="H31" s="7">
-        <v>229680.0</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="12"/>
-    </row>
-    <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="9">
-        <v>46213.0</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="7">
-        <v>176850.0</v>
-      </c>
-      <c r="G32" s="7">
-        <v>47499.0</v>
-      </c>
-      <c r="H32" s="7">
-        <v>128971.0</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="12"/>
-    </row>
-    <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="9">
-        <v>46213.0</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="7">
-        <v>58080.0</v>
-      </c>
-      <c r="G33" s="7">
-        <v>20865.0</v>
-      </c>
-      <c r="H33" s="7">
-        <v>25440.0</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="12"/>
-    </row>
-    <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="9">
-        <v>46217.0</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="7">
-        <v>481440.0</v>
-      </c>
-      <c r="G34" s="7">
-        <v>464517.0</v>
-      </c>
-      <c r="H34" s="7">
-        <v>151435.0</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="12"/>
-    </row>
-    <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="9">
-        <v>46217.0</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="7">
-        <v>355720.0</v>
-      </c>
-      <c r="G35" s="7">
-        <v>342811.0</v>
-      </c>
-      <c r="H35" s="7">
-        <v>302760.0</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="12"/>
-    </row>
-    <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="9">
-        <v>46217.0</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="7">
-        <v>2010102.0</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="7">
-        <v>35280.0</v>
-      </c>
-      <c r="G36" s="7">
-        <v>16988.0</v>
-      </c>
-      <c r="H36" s="7">
-        <v>37926.0</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" ht="22.5" hidden="1" customHeight="1">
-      <c r="A37" s="15">
-        <v>46218.0</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F37" s="7">
-        <v>272073.0</v>
-      </c>
-      <c r="G37" s="7">
-        <v>76546.0</v>
-      </c>
-      <c r="H37" s="7">
-        <v>275205.0</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" ht="22.5" hidden="1" customHeight="1">
-      <c r="A38" s="15">
-        <v>46218.0</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="7">
-        <v>2010102.0</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="7">
-        <v>37926.0</v>
-      </c>
-      <c r="G38" s="7">
-        <v>5633.0</v>
-      </c>
-      <c r="H38" s="7">
-        <v>25746.0</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" ht="22.5" hidden="1" customHeight="1">
-      <c r="A39" s="15">
-        <v>46218.0</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F39" s="7">
-        <v>20640.0</v>
-      </c>
-      <c r="G39" s="7">
-        <v>4951.0</v>
-      </c>
-      <c r="H39" s="7">
-        <v>16320.0</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" ht="22.5" hidden="1" customHeight="1">
-      <c r="A40" s="15">
-        <v>46218.0</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="7">
-        <v>2110317.0</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F40" s="7">
-        <v>10980.0</v>
-      </c>
-      <c r="G40" s="7">
-        <v>2379.0</v>
-      </c>
-      <c r="H40" s="7">
-        <v>13500.0</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="12"/>
-    </row>
-    <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="9">
-        <v>46219.0</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F41" s="7">
-        <v>130320.0</v>
-      </c>
-      <c r="G41" s="7">
-        <v>47410.0</v>
-      </c>
-      <c r="H41" s="7">
-        <v>90480.0</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="9">
-        <v>46219.0</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D42" s="7">
-        <v>2152388.0</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42" s="7">
-        <v>36225.0</v>
-      </c>
-      <c r="G42" s="7">
-        <v>11746.0</v>
-      </c>
-      <c r="H42" s="7">
-        <v>27570.0</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="12"/>
-    </row>
-    <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="9">
-        <v>46219.0</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F43" s="7">
-        <v>152833.0</v>
-      </c>
-      <c r="G43" s="7">
-        <v>50641.0</v>
-      </c>
-      <c r="H43" s="7">
-        <v>96472.0</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="9">
-        <v>46219.0</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F44" s="7">
-        <v>237828.0</v>
-      </c>
-      <c r="G44" s="7">
-        <v>173585.0</v>
-      </c>
-      <c r="H44" s="7">
-        <v>71560.0</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="12"/>
-    </row>
-    <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="9">
-        <v>46219.0</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="7">
-        <v>152384.0</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F45" s="7">
-        <v>31125.0</v>
-      </c>
-      <c r="G45" s="7">
-        <v>7815.0</v>
-      </c>
-      <c r="H45" s="7">
-        <v>31845.0</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="9">
-        <v>46219.0</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="7">
-        <v>2010102.0</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" s="7">
-        <v>25746.0</v>
-      </c>
-      <c r="G46" s="7">
-        <v>6168.0</v>
-      </c>
-      <c r="H46" s="7">
-        <v>28683.0</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="9">
-        <v>46220.0</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F47" s="7">
-        <v>261166.0</v>
-      </c>
-      <c r="G47" s="7">
-        <v>74573.0</v>
-      </c>
-      <c r="H47" s="7">
-        <v>221549.0</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="9">
-        <v>46220.0</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" s="7">
-        <v>2110217.0</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F48" s="7">
-        <v>115289.0</v>
-      </c>
-      <c r="G48" s="7">
-        <v>26931.0</v>
-      </c>
-      <c r="H48" s="7">
-        <v>119584.0</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="12"/>
-    </row>
-    <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="9">
-        <v>46224.0</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F49" s="7">
-        <v>398570.0</v>
-      </c>
-      <c r="G49" s="7">
-        <v>288226.0</v>
-      </c>
-      <c r="H49" s="7">
-        <v>287235.0</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="9">
-        <v>46224.0</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D50" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" s="7">
-        <v>745107.0</v>
-      </c>
-      <c r="G50" s="7">
-        <v>378927.0</v>
-      </c>
-      <c r="H50" s="7">
-        <v>551645.0</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D51" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F51" s="7">
-        <v>130560.0</v>
-      </c>
-      <c r="G51" s="7">
-        <v>52658.0</v>
-      </c>
-      <c r="H51" s="7">
-        <v>153840.0</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D52" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F52" s="7">
-        <v>87447.0</v>
-      </c>
-      <c r="G52" s="7">
-        <v>59056.0</v>
-      </c>
-      <c r="H52" s="7">
-        <v>104365.0</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="12"/>
-    </row>
-    <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D53" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F53" s="7">
-        <v>25200.0</v>
-      </c>
-      <c r="G53" s="7">
-        <v>2085.0</v>
-      </c>
-      <c r="H53" s="7">
-        <v>25920.0</v>
-      </c>
-      <c r="I53" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" s="7">
-        <v>285405.0</v>
-      </c>
-      <c r="G54" s="7">
-        <v>203180.0</v>
-      </c>
-      <c r="H54" s="7">
-        <v>226069.0</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D55" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" s="7">
-        <v>692280.0</v>
-      </c>
-      <c r="G55" s="7">
-        <v>118381.0</v>
-      </c>
-      <c r="H55" s="7">
-        <v>700200.0</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J55" s="12"/>
-    </row>
-    <row r="56">
-      <c r="I56" s="16"/>
-    </row>
-    <row r="57">
-      <c r="I57" s="16"/>
-    </row>
-    <row r="58">
-      <c r="I58" s="16"/>
-    </row>
-    <row r="59">
-      <c r="I59" s="16"/>
+      <c r="F59" s="9">
+        <v>295359.0</v>
+      </c>
+      <c r="G59" s="9">
+        <v>126369.0</v>
+      </c>
+      <c r="H59" s="9">
+        <v>166642.0</v>
+      </c>
+      <c r="I59" s="13"/>
+      <c r="J59" s="11"/>
     </row>
     <row r="60">
       <c r="I60" s="16"/>
@@ -5297,13 +5415,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I55">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I59">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I56:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I60:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A55">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A59">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -5323,7 +5441,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="18.38"/>
     <col customWidth="1" min="2" max="2" width="26.5"/>
-    <col customWidth="1" min="3" max="3" width="20.0"/>
+    <col customWidth="1" min="3" max="3" width="6.13"/>
     <col customWidth="1" min="4" max="4" width="9.25"/>
     <col customWidth="1" min="5" max="5" width="64.0"/>
     <col customWidth="1" min="6" max="6" width="12.25"/>
@@ -5366,363 +5484,506 @@
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="9">
+      <c r="A2" s="4">
         <v>46224.0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="7">
+      <c r="B2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="9">
+        <v>333.0</v>
+      </c>
+      <c r="G2" s="9">
+        <v>6480.0</v>
+      </c>
+      <c r="H2" s="9">
+        <v>3712.0</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7">
-        <v>333.0</v>
-      </c>
-      <c r="G2" s="7">
-        <v>6480.0</v>
-      </c>
-      <c r="H2" s="7">
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="4">
+        <v>46224.0</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="9">
+        <v>2114158.0</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G3" s="9">
+        <v>1000.0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="9">
+        <v>10501.0</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="9">
+        <v>415093.0</v>
+      </c>
+      <c r="G4" s="9">
+        <v>115920.0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>543038.0</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="9">
+        <v>112379.0</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="9">
+        <v>3000.0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>29400.0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>3000.0</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="9">
+        <v>3000.0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>12300.0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>3300.0</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="9">
+        <v>132357.0</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="9">
+        <v>1560.0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>1560.0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>4560.0</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="9">
+        <v>720.0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>11160.0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>5940.0</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="9">
         <v>3712.0</v>
       </c>
-      <c r="I2" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="9">
-        <v>46224.0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="7">
-        <v>2114158.0</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="7">
-        <v>60.0</v>
-      </c>
-      <c r="G3" s="7">
-        <v>1000.0</v>
-      </c>
-      <c r="H3" s="7">
-        <v>60.0</v>
-      </c>
-      <c r="I3" s="17" t="s">
+      <c r="G9" s="9">
+        <v>46723.0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>213.0</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="9">
+        <v>73001.0</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="9">
+        <v>73787.0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>72000.0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>109487.0</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="7">
-        <v>10501.0</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="7">
-        <v>415093.0</v>
-      </c>
-      <c r="G4" s="7">
-        <v>115920.0</v>
-      </c>
-      <c r="H4" s="7">
-        <v>543038.0</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="7">
+      <c r="F11" s="9">
+        <v>3300.0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>1800.0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>3300.0</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="9">
         <v>112379.0</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="7">
-        <v>3000.0</v>
-      </c>
-      <c r="G5" s="7">
-        <v>29400.0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>3000.0</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="7">
+      <c r="E12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="9">
+        <v>4200.0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>7500.0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>3900.0</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="9">
+        <v>379471.0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>392580.0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>357186.0</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="9">
+        <v>72001.0</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="9">
+        <v>21905.0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>47670.0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>38000.0</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="9">
+        <v>2110327.0</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="9">
+        <v>69120.0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>57600.0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>40320.0</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="9">
+        <v>112379.0</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="9">
+        <v>3900.0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>102600.0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>1500.0</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="9">
+        <v>720.0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>9720.0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>2580.0</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="9">
         <v>112268.0</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="7">
-        <v>3000.0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>12300.0</v>
-      </c>
-      <c r="H6" s="7">
+      <c r="E18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="9">
         <v>3300.0</v>
       </c>
-      <c r="I6" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="7">
-        <v>132357.0</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1560.0</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1560.0</v>
-      </c>
-      <c r="H7" s="7">
-        <v>4560.0</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="7">
-        <v>2152388.0</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="7">
-        <v>720.0</v>
-      </c>
-      <c r="G8" s="7">
-        <v>11160.0</v>
-      </c>
-      <c r="H8" s="7">
-        <v>5940.0</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="7">
-        <v>3712.0</v>
-      </c>
-      <c r="G9" s="7">
-        <v>46723.0</v>
-      </c>
-      <c r="H9" s="7">
-        <v>213.0</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="7">
-        <v>73001.0</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F10" s="7">
-        <v>73787.0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>72000.0</v>
-      </c>
-      <c r="H10" s="7">
-        <v>109487.0</v>
-      </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="12"/>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="7">
-        <v>112268.0</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="7">
-        <v>3300.0</v>
-      </c>
-      <c r="G11" s="7">
-        <v>1800.0</v>
-      </c>
-      <c r="H11" s="7">
-        <v>3300.0</v>
-      </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="12"/>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="7">
-        <v>112379.0</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="7">
-        <v>4200.0</v>
-      </c>
-      <c r="G12" s="7">
-        <v>7500.0</v>
-      </c>
-      <c r="H12" s="7">
-        <v>3900.0</v>
-      </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="7">
-        <v>379471.0</v>
-      </c>
-      <c r="G13" s="7">
-        <v>392580.0</v>
-      </c>
-      <c r="H13" s="7">
-        <v>357186.0</v>
-      </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="12"/>
-    </row>
-    <row r="14">
-      <c r="I14" s="16"/>
-    </row>
-    <row r="15">
-      <c r="I15" s="16"/>
-    </row>
-    <row r="16">
-      <c r="I16" s="16"/>
-    </row>
-    <row r="17">
-      <c r="I17" s="16"/>
-    </row>
-    <row r="18">
-      <c r="I18" s="16"/>
+      <c r="G18" s="9">
+        <v>30600.0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>600.0</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="19">
       <c r="I19" s="16"/>
@@ -8552,13 +8813,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I13">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I18">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I14:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I19:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A13">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A18">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="97">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -68,66 +68,66 @@
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
+    <t>LANZA</t>
+  </si>
+  <si>
     <t>TAT MONTERIA</t>
   </si>
   <si>
-    <t>LANZA</t>
+    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
     <t>LUIS LOPEZ</t>
   </si>
   <si>
-    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
+    <t>6. Transformación De Referencias</t>
+  </si>
+  <si>
+    <t>Pendiente Transformar Roto GT Por manipulación</t>
   </si>
   <si>
     <t>3. Falla De Rotación</t>
   </si>
   <si>
-    <t>6. Transformación De Referencias</t>
-  </si>
-  <si>
-    <t>Pendiente Transformar Roto GT Por manipulación</t>
-  </si>
-  <si>
     <t>TAT MEDELLIN</t>
   </si>
   <si>
+    <t>HUEVO B X30 CARTON GRIS</t>
+  </si>
+  <si>
     <t>FABIO GOMEZ</t>
   </si>
   <si>
-    <t>HUEVO B X30 CARTON GRIS</t>
-  </si>
-  <si>
     <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
   </si>
   <si>
     <t>se equivocaron al cargar una estiba</t>
   </si>
   <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
     <t>TAT CARTAGENA</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
     <t>Dilan Barraza</t>
   </si>
   <si>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
-  </si>
-  <si>
     <t>4. Exigencia Del Cliente (Edad)</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
+  </si>
+  <si>
     <t>Venta FS</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
-  </si>
-  <si>
     <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
   </si>
   <si>
@@ -137,31 +137,34 @@
     <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+  </si>
+  <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
-  </si>
-  <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+  </si>
+  <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+    <t>HUEVO PICADO ROJO</t>
   </si>
   <si>
     <t>TAT CALI</t>
@@ -170,9 +173,6 @@
     <t>DIEGO ROJAS</t>
   </si>
   <si>
-    <t>HUEVO PICADO ROJO</t>
-  </si>
-  <si>
     <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
@@ -185,12 +185,12 @@
     <t>Clientes FS</t>
   </si>
   <si>
+    <t>HUEVO SUCIO DE JAULA</t>
+  </si>
+  <si>
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
-    <t>HUEVO SUCIO DE JAULA</t>
-  </si>
-  <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
   </si>
   <si>
@@ -203,18 +203,21 @@
     <t>ANDRES MEJIA</t>
   </si>
   <si>
+    <t>Cola de programación</t>
+  </si>
+  <si>
     <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
   </si>
   <si>
     <t>TAT POPAYAN</t>
   </si>
   <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
-    <t>Cola de programación</t>
-  </si>
-  <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
@@ -291,6 +294,15 @@
   </si>
   <si>
     <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
+  </si>
+  <si>
+    <t>Devolucion de huevo de 12 dias en mal estado</t>
+  </si>
+  <si>
+    <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
+  </si>
+  <si>
+    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
 </sst>
 </file>
@@ -354,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -409,9 +421,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -473,13 +482,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Cedis-style">
+    <tableStyle count="4" pivot="0" name="Plantas-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Plantas-style">
+    <tableStyle count="4" pivot="0" name="Cedis-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -502,7 +511,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J59" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J62" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -520,7 +529,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J18" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J19" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -816,10 +825,10 @@
         <v>46205.0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9">
         <v>2110402.0</v>
@@ -837,7 +846,7 @@
         <v>260675.0</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3" s="7"/>
     </row>
@@ -849,7 +858,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="9">
         <v>2110217.0</v>
@@ -876,7 +885,7 @@
         <v>46205.0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>32</v>
@@ -885,7 +894,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="9">
         <v>75680.0</v>
@@ -900,7 +909,7 @@
         <v>35</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
@@ -911,7 +920,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="9">
         <v>2110202.0</v>
@@ -932,7 +941,7 @@
         <v>15</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
@@ -943,13 +952,13 @@
         <v>25</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" s="9">
         <v>20640.0</v>
@@ -964,7 +973,7 @@
         <v>35</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
@@ -975,7 +984,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="9">
         <v>152384.0</v>
@@ -993,7 +1002,7 @@
         <v>9600.0</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" s="11"/>
     </row>
@@ -1002,10 +1011,10 @@
         <v>46206.0</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="9">
         <v>2110202.0</v>
@@ -1023,7 +1032,7 @@
         <v>124260.0</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="11"/>
     </row>
@@ -1041,7 +1050,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="9">
         <v>7830.0</v>
@@ -1053,7 +1062,7 @@
         <v>6030.0</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J10" s="15"/>
     </row>
@@ -1065,7 +1074,7 @@
         <v>25</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="9">
         <v>2110402.0</v>
@@ -1094,16 +1103,16 @@
         <v>46206.0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>51387.0</v>
@@ -1118,7 +1127,7 @@
         <v>35</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
@@ -1126,10 +1135,10 @@
         <v>46209.0</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="9">
         <v>2110402.0</v>
@@ -1150,7 +1159,7 @@
         <v>35</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
@@ -1158,7 +1167,7 @@
         <v>46209.0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>32</v>
@@ -1179,7 +1188,7 @@
         <v>424588.0</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>61</v>
@@ -1199,7 +1208,7 @@
         <v>2010102.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="9">
         <v>14160.0</v>
@@ -1214,7 +1223,7 @@
         <v>15</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
@@ -1222,16 +1231,16 @@
         <v>46210.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16" s="9">
         <v>149040.0</v>
@@ -1252,10 +1261,10 @@
         <v>46210.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" s="9">
         <v>2110217.0</v>
@@ -1282,16 +1291,16 @@
         <v>46210.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18" s="9">
         <v>222021.0</v>
@@ -1312,7 +1321,7 @@
         <v>46211.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>32</v>
@@ -1336,7 +1345,7 @@
         <v>15</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
@@ -1344,10 +1353,10 @@
         <v>46211.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D20" s="9">
         <v>2110402.0</v>
@@ -1374,16 +1383,16 @@
         <v>46211.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D21" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F21" s="9">
         <v>162125.0</v>
@@ -1398,7 +1407,7 @@
         <v>15</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
@@ -1445,7 +1454,7 @@
         <v>112271.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F23" s="9">
         <v>16500.0</v>
@@ -1457,7 +1466,7 @@
         <v>18000.0</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J23" s="11"/>
     </row>
@@ -1466,10 +1475,10 @@
         <v>46212.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D24" s="9">
         <v>2110202.0</v>
@@ -1487,7 +1496,7 @@
         <v>248481.0</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J24" s="11"/>
     </row>
@@ -1505,7 +1514,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F25" s="9">
         <v>178080.0</v>
@@ -1517,7 +1526,7 @@
         <v>203520.0</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J25" s="11"/>
     </row>
@@ -1550,7 +1559,7 @@
         <v>35</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
@@ -1567,7 +1576,7 @@
         <v>112271.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F27" s="9">
         <v>18000.0</v>
@@ -1579,7 +1588,7 @@
         <v>13500.0</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J27" s="11"/>
     </row>
@@ -1591,13 +1600,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D28" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" s="9">
         <v>208440.0</v>
@@ -1612,7 +1621,7 @@
         <v>15</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
@@ -1623,7 +1632,7 @@
         <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D29" s="9">
         <v>2110202.0</v>
@@ -1644,7 +1653,7 @@
         <v>15</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
@@ -1676,7 +1685,7 @@
         <v>35</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
@@ -1684,16 +1693,16 @@
         <v>46213.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D31" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F31" s="9">
         <v>316800.0</v>
@@ -1705,7 +1714,7 @@
         <v>229680.0</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J31" s="11"/>
     </row>
@@ -1714,16 +1723,16 @@
         <v>46213.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D32" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F32" s="9">
         <v>176850.0</v>
@@ -1735,7 +1744,7 @@
         <v>128971.0</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -1744,10 +1753,10 @@
         <v>46213.0</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D33" s="9">
         <v>2110402.0</v>
@@ -1765,7 +1774,7 @@
         <v>25440.0</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J33" s="11"/>
     </row>
@@ -1774,16 +1783,16 @@
         <v>46217.0</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D34" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F34" s="9">
         <v>481440.0</v>
@@ -1795,7 +1804,7 @@
         <v>151435.0</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J34" s="11"/>
     </row>
@@ -1807,7 +1816,7 @@
         <v>25</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D35" s="9">
         <v>2110202.0</v>
@@ -1837,13 +1846,13 @@
         <v>11</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D36" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F36" s="9">
         <v>35280.0</v>
@@ -1855,10 +1864,10 @@
         <v>37926.0</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
@@ -1869,13 +1878,13 @@
         <v>11</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F37" s="9">
         <v>272073.0</v>
@@ -1890,7 +1899,7 @@
         <v>35</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
@@ -1901,13 +1910,13 @@
         <v>11</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D38" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F38" s="9">
         <v>37926.0</v>
@@ -1919,10 +1928,10 @@
         <v>25746.0</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
@@ -1933,7 +1942,7 @@
         <v>25</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39" s="9">
         <v>2110402.0</v>
@@ -1954,7 +1963,7 @@
         <v>35</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
@@ -1965,13 +1974,13 @@
         <v>25</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D40" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F40" s="9">
         <v>10980.0</v>
@@ -1983,7 +1992,7 @@
         <v>13500.0</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J40" s="11"/>
     </row>
@@ -1995,13 +2004,13 @@
         <v>25</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D41" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F41" s="9">
         <v>130320.0</v>
@@ -2013,10 +2022,10 @@
         <v>90480.0</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
@@ -2024,16 +2033,16 @@
         <v>46219.0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D42" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F42" s="9">
         <v>36225.0</v>
@@ -2054,16 +2063,16 @@
         <v>46219.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D43" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F43" s="9">
         <v>152833.0</v>
@@ -2075,10 +2084,10 @@
         <v>96472.0</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
@@ -2086,16 +2095,16 @@
         <v>46219.0</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D44" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F44" s="9">
         <v>237828.0</v>
@@ -2107,7 +2116,7 @@
         <v>71560.0</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J44" s="11"/>
     </row>
@@ -2119,7 +2128,7 @@
         <v>11</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D45" s="9">
         <v>152384.0</v>
@@ -2140,7 +2149,7 @@
         <v>35</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
@@ -2151,13 +2160,13 @@
         <v>11</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D46" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F46" s="9">
         <v>25746.0</v>
@@ -2169,10 +2178,10 @@
         <v>28683.0</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
@@ -2183,13 +2192,13 @@
         <v>11</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D47" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F47" s="9">
         <v>261166.0</v>
@@ -2204,7 +2213,7 @@
         <v>35</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
@@ -2215,7 +2224,7 @@
         <v>11</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D48" s="9">
         <v>2110217.0</v>
@@ -2233,7 +2242,7 @@
         <v>119584.0</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J48" s="11"/>
     </row>
@@ -2242,10 +2251,10 @@
         <v>46224.0</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D49" s="9">
         <v>2110402.0</v>
@@ -2266,7 +2275,7 @@
         <v>35</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
@@ -2274,10 +2283,10 @@
         <v>46224.0</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D50" s="9">
         <v>2110402.0</v>
@@ -2298,7 +2307,7 @@
         <v>15</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
@@ -2315,7 +2324,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F51" s="9">
         <v>130560.0</v>
@@ -2327,10 +2336,10 @@
         <v>153840.0</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
@@ -2338,16 +2347,16 @@
         <v>46225.0</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D52" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F52" s="9">
         <v>87447.0</v>
@@ -2359,7 +2368,7 @@
         <v>104365.0</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J52" s="11"/>
     </row>
@@ -2371,7 +2380,7 @@
         <v>11</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D53" s="9">
         <v>2110402.0</v>
@@ -2389,10 +2398,10 @@
         <v>25920.0</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
@@ -2400,10 +2409,10 @@
         <v>46226.0</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D54" s="9">
         <v>2110402.0</v>
@@ -2421,10 +2430,10 @@
         <v>226069.0</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" ht="22.5" customHeight="1">
@@ -2453,7 +2462,7 @@
         <v>700200.0</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J55" s="11"/>
     </row>
@@ -2483,7 +2492,7 @@
         <v>668440.0</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J56" s="11"/>
     </row>
@@ -2492,9 +2501,11 @@
         <v>46227.0</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C57" s="19"/>
+        <v>31</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>92</v>
+      </c>
       <c r="D57" s="9">
         <v>2110402.0</v>
       </c>
@@ -2510,18 +2521,22 @@
       <c r="H57" s="9">
         <v>326391.0</v>
       </c>
-      <c r="I57" s="13"/>
-      <c r="J57" s="11"/>
+      <c r="I57" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="4">
         <v>46227.0</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D58" s="9">
         <v>2110202.0</v>
@@ -2539,7 +2554,7 @@
         <v>128160.0</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J58" s="11"/>
     </row>
@@ -2548,9 +2563,11 @@
         <v>46227.0</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C59" s="19"/>
+        <v>83</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="D59" s="9">
         <v>2110402.0</v>
       </c>
@@ -2566,17 +2583,100 @@
       <c r="H59" s="9">
         <v>166642.0</v>
       </c>
-      <c r="I59" s="13"/>
-      <c r="J59" s="11"/>
-    </row>
-    <row r="60">
-      <c r="I60" s="16"/>
-    </row>
-    <row r="61">
-      <c r="I61" s="16"/>
-    </row>
-    <row r="62">
-      <c r="I62" s="16"/>
+      <c r="I59" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="4">
+        <v>46230.0</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D60" s="9">
+        <v>2110403.0</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F60" s="9">
+        <v>9960.0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>6018.0</v>
+      </c>
+      <c r="H60" s="9">
+        <v>3660.0</v>
+      </c>
+      <c r="I60" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" s="11"/>
+    </row>
+    <row r="61" ht="22.5" customHeight="1">
+      <c r="A61" s="4">
+        <v>46230.0</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F61" s="9">
+        <v>306720.0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>164175.0</v>
+      </c>
+      <c r="H61" s="9">
+        <v>247096.0</v>
+      </c>
+      <c r="I61" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" s="11"/>
+    </row>
+    <row r="62" ht="22.5" customHeight="1">
+      <c r="A62" s="4">
+        <v>46230.0</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" s="9">
+        <v>437080.0</v>
+      </c>
+      <c r="G62" s="9">
+        <v>277785.0</v>
+      </c>
+      <c r="H62" s="9">
+        <v>353700.0</v>
+      </c>
+      <c r="I62" s="13"/>
+      <c r="J62" s="11"/>
     </row>
     <row r="63">
       <c r="I63" s="16"/>
@@ -5415,13 +5515,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I59">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I62">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I60:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I63:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A59">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A62">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -5518,14 +5618,14 @@
         <v>46224.0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="9">
         <v>2114158.0</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" s="9">
         <v>60.0</v>
@@ -5537,10 +5637,10 @@
         <v>60.0</v>
       </c>
       <c r="I3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
@@ -5555,7 +5655,7 @@
         <v>10501.0</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" s="9">
         <v>415093.0</v>
@@ -5567,7 +5667,7 @@
         <v>543038.0</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>29</v>
@@ -5585,7 +5685,7 @@
         <v>112379.0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="9">
         <v>3000.0</v>
@@ -5600,7 +5700,7 @@
         <v>15</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
@@ -5608,14 +5708,14 @@
         <v>46225.0</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="9">
         <v>112268.0</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" s="9">
         <v>3000.0</v>
@@ -5660,7 +5760,7 @@
         <v>15</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
@@ -5668,14 +5768,14 @@
         <v>46225.0</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="9">
         <v>720.0</v>
@@ -5690,7 +5790,7 @@
         <v>15</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
@@ -5720,7 +5820,7 @@
         <v>15</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
@@ -5728,14 +5828,14 @@
         <v>46226.0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="9">
         <v>73001.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F10" s="9">
         <v>73787.0</v>
@@ -5758,14 +5858,14 @@
         <v>46226.0</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="9">
         <v>112268.0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" s="9">
         <v>3300.0</v>
@@ -5777,7 +5877,7 @@
         <v>3300.0</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J11" s="11"/>
     </row>
@@ -5786,14 +5886,14 @@
         <v>46226.0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="9">
         <v>112379.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="9">
         <v>4200.0</v>
@@ -5805,7 +5905,7 @@
         <v>3900.0</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J12" s="11"/>
     </row>
@@ -5844,14 +5944,14 @@
         <v>46227.0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="9">
         <v>72001.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14" s="9">
         <v>21905.0</v>
@@ -5874,7 +5974,7 @@
         <v>46227.0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="9">
@@ -5904,14 +6004,14 @@
         <v>46227.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="9">
         <v>112379.0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" s="9">
         <v>3900.0</v>
@@ -5923,7 +6023,7 @@
         <v>1500.0</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J16" s="11"/>
     </row>
@@ -5932,14 +6032,14 @@
         <v>46227.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" s="9">
         <v>720.0</v>
@@ -5951,7 +6051,7 @@
         <v>2580.0</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J17" s="11"/>
     </row>
@@ -5960,14 +6060,14 @@
         <v>46227.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="9">
         <v>112268.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F18" s="9">
         <v>3300.0</v>
@@ -5982,11 +6082,34 @@
         <v>15</v>
       </c>
       <c r="J18" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="4">
+        <v>46230.0</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="9">
+        <v>2410401.0</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="I19" s="16"/>
+      <c r="F19" s="9">
+        <v>136538.0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>34080.0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>213000.0</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="11"/>
     </row>
     <row r="20">
       <c r="I20" s="16"/>
@@ -8813,13 +8936,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I18">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I19">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I19:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I20:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A18">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A19">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="98">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -44,40 +44,67 @@
     <t xml:space="preserve">Otro </t>
   </si>
   <si>
+    <t>TAT BOGOTA MONTEVIDEO</t>
+  </si>
+  <si>
+    <t>Daniel Castro</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2. Error De Registro De Inventario</t>
+  </si>
+  <si>
+    <t>TAT MONTERIA</t>
+  </si>
+  <si>
     <t>ALKA2</t>
   </si>
   <si>
-    <t>TAT BOGOTA MONTEVIDEO</t>
-  </si>
-  <si>
-    <t>Daniel Castro</t>
+    <t>LUIS LOPEZ</t>
   </si>
   <si>
     <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+    <t>3. Falla De Rotación</t>
+  </si>
+  <si>
+    <t>TAT MEDELLIN</t>
   </si>
   <si>
     <t>7. Otro</t>
   </si>
   <si>
+    <t>FABIO GOMEZ</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+  </si>
+  <si>
     <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
   </si>
   <si>
-    <t>2. Error De Registro De Inventario</t>
+    <t>TAT CARTAGENA</t>
+  </si>
+  <si>
+    <t>Dilan Barraza</t>
   </si>
   <si>
     <t>LANZA</t>
   </si>
   <si>
-    <t>TAT MONTERIA</t>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
     <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
-    <t>LUIS LOPEZ</t>
+    <t>4. Exigencia Del Cliente (Edad)</t>
+  </si>
+  <si>
+    <t>Venta FS</t>
   </si>
   <si>
     <t>6. Transformación De Referencias</t>
@@ -86,138 +113,111 @@
     <t>Pendiente Transformar Roto GT Por manipulación</t>
   </si>
   <si>
-    <t>3. Falla De Rotación</t>
-  </si>
-  <si>
-    <t>TAT MEDELLIN</t>
+    <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
     <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
-    <t>FABIO GOMEZ</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
     <t>se equivocaron al cargar una estiba</t>
   </si>
   <si>
+    <t>Se envía más fresco a Rionegro</t>
+  </si>
+  <si>
     <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
-    <t>TAT CARTAGENA</t>
-  </si>
-  <si>
-    <t>Dilan Barraza</t>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
     <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>4. Exigencia Del Cliente (Edad)</t>
+    <t>TAT CALI</t>
+  </si>
+  <si>
+    <t>DIEGO ROJAS</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
-    <t>Venta FS</t>
-  </si>
-  <si>
     <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
   </si>
   <si>
     <t>PALMAS</t>
   </si>
   <si>
+    <t>TAT CUCUTA</t>
+  </si>
+  <si>
+    <t>ALEXANDER PEÑA</t>
+  </si>
+  <si>
     <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
     <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
-    <t>Se dejó lote para revisión por calidad</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
-    <t>Se envía más fresco a Rionegro</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+    <t>Clientes FS</t>
   </si>
   <si>
     <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
   </si>
   <si>
-    <t>1. Ingreso Por Devolución</t>
-  </si>
-  <si>
     <t>HUEVO PICADO ROJO</t>
   </si>
   <si>
-    <t>TAT CALI</t>
-  </si>
-  <si>
-    <t>DIEGO ROJAS</t>
+    <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
     <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
-    <t>TAT CUCUTA</t>
-  </si>
-  <si>
-    <t>ALEXANDER PEÑA</t>
-  </si>
-  <si>
-    <t>Clientes FS</t>
+    <t>Transformación de PET</t>
+  </si>
+  <si>
+    <t>ANDRES MEJIA</t>
+  </si>
+  <si>
+    <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
+  </si>
+  <si>
+    <t>TAT POPAYAN</t>
+  </si>
+  <si>
+    <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
     <t>HUEVO SUCIO DE JAULA</t>
   </si>
   <si>
-    <t>Envío huevo fresco a Sincelejo</t>
-  </si>
-  <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
   </si>
   <si>
     <t>Esta para despacho hoy</t>
   </si>
   <si>
-    <t>Transformación de PET</t>
-  </si>
-  <si>
-    <t>ANDRES MEJIA</t>
-  </si>
-  <si>
     <t>Cola de programación</t>
   </si>
   <si>
-    <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
-  </si>
-  <si>
-    <t>TAT POPAYAN</t>
-  </si>
-  <si>
     <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
   </si>
   <si>
-    <t>JONATHAN MOSQUERA</t>
-  </si>
-  <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
+  </si>
+  <si>
+    <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
   </si>
 </sst>
 </file>
@@ -342,14 +345,14 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -380,43 +383,43 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -482,13 +485,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Plantas-style">
+    <tableStyle count="4" pivot="0" name="Cedis-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Cedis-style">
+    <tableStyle count="4" pivot="0" name="Plantas-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -511,7 +514,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J62" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J62" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -529,7 +532,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J19" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J19" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -792,1081 +795,1081 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>46204.0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="9">
+      <c r="F2" s="7">
+        <v>359100.0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>83486.0</v>
+      </c>
+      <c r="H2" s="7">
+        <v>206140.0</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" hidden="1" customHeight="1">
+      <c r="A3" s="9">
+        <v>46205.0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="7">
+        <v>298282.0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>42201.0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>260675.0</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
+      <c r="A4" s="9">
+        <v>46205.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2110217.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="7">
+        <v>21120.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>11039.0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>16920.0</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
+      <c r="A5" s="9">
+        <v>46205.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="7">
+        <v>75680.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>5640.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3134.0</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="7">
+        <v>189540.0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>161685.0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>144720.0</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="7">
+        <v>20640.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>3761.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>13920.0</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="7">
+        <v>152384.0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="7">
+        <v>14700.0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>6435.0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>9600.0</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="13"/>
+    </row>
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
+      <c r="A9" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7">
+        <v>228240.0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>77306.0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>124260.0</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
+      <c r="A10" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="7">
+        <v>7830.0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>1980.0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>6030.0</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="7">
+        <v>31680.0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>5526.0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>23040.0</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
+      <c r="A12" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="9">
-        <v>359100.0</v>
-      </c>
-      <c r="G2" s="9">
-        <v>83486.0</v>
-      </c>
-      <c r="H2" s="9">
-        <v>206140.0</v>
-      </c>
-      <c r="I2" s="12" t="s">
+      <c r="C12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="7">
+        <v>51387.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>10827.0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>12170.0</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
+      <c r="A13" s="9">
+        <v>46209.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="4">
-        <v>46205.0</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="F13" s="7">
+        <v>195810.0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>93809.0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>133410.0</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
+      <c r="A14" s="9">
+        <v>46209.0</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="7">
+        <v>526002.0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>301965.0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>424588.0</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="9">
+        <v>46209.0</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="9">
+      <c r="C15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="7">
+        <v>14160.0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>6692.0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>12360.0</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
+      <c r="A16" s="9">
+        <v>46210.0</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="7">
+        <v>149040.0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>119573.0</v>
+      </c>
+      <c r="H16" s="7">
+        <v>289680.0</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" ht="22.5" hidden="1" customHeight="1">
+      <c r="A17" s="9">
+        <v>46210.0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="7">
+        <v>2110217.0</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="7">
+        <v>22770.0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>3926.0</v>
+      </c>
+      <c r="H17" s="7">
+        <v>19770.0</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" ht="22.5" hidden="1" customHeight="1">
+      <c r="A18" s="9">
+        <v>46210.0</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="7">
+        <v>222021.0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>61385.0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>162125.0</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="13"/>
+    </row>
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
+      <c r="A19" s="9">
+        <v>46211.0</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="7">
+        <v>495833.0</v>
+      </c>
+      <c r="G19" s="7">
+        <v>148815.0</v>
+      </c>
+      <c r="H19" s="7">
+        <v>401280.0</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
+      <c r="A20" s="9">
+        <v>46211.0</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="7">
+        <v>139920.0</v>
+      </c>
+      <c r="G20" s="7">
+        <v>54384.0</v>
+      </c>
+      <c r="H20" s="7">
+        <v>74040.0</v>
+      </c>
+      <c r="I20" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="9">
-        <v>298282.0</v>
-      </c>
-      <c r="G3" s="9">
-        <v>42201.0</v>
-      </c>
-      <c r="H3" s="9">
-        <v>260675.0</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="4">
-        <v>46205.0</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
+      <c r="A21" s="9">
+        <v>46211.0</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="9">
-        <v>2110217.0</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="9">
-        <v>21120.0</v>
-      </c>
-      <c r="G4" s="9">
-        <v>11039.0</v>
-      </c>
-      <c r="H4" s="9">
-        <v>16920.0</v>
-      </c>
-      <c r="I4" s="13" t="s">
+      <c r="F21" s="7">
+        <v>162125.0</v>
+      </c>
+      <c r="G21" s="7">
+        <v>60138.0</v>
+      </c>
+      <c r="H21" s="7">
+        <v>100687.0</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" hidden="1" customHeight="1">
+      <c r="A22" s="9">
+        <v>46211.0</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="7">
+        <v>152384.0</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="7">
+        <v>32850.0</v>
+      </c>
+      <c r="G22" s="7">
+        <v>7065.0</v>
+      </c>
+      <c r="H22" s="7">
+        <v>32700.0</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J22" s="13"/>
+    </row>
+    <row r="23" ht="22.5" hidden="1" customHeight="1">
+      <c r="A23" s="9">
+        <v>46211.0</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="7">
+        <v>112271.0</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="7">
+        <v>16500.0</v>
+      </c>
+      <c r="G23" s="7">
+        <v>5310.0</v>
+      </c>
+      <c r="H23" s="7">
+        <v>18000.0</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J23" s="13"/>
+    </row>
+    <row r="24" ht="22.5" hidden="1" customHeight="1">
+      <c r="A24" s="9">
+        <v>46212.0</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="7">
+        <v>190047.0</v>
+      </c>
+      <c r="G24" s="7">
+        <v>59822.0</v>
+      </c>
+      <c r="H24" s="7">
+        <v>248481.0</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
+      <c r="A25" s="9">
+        <v>46212.0</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="7">
+        <v>178080.0</v>
+      </c>
+      <c r="G25" s="7">
+        <v>47784.0</v>
+      </c>
+      <c r="H25" s="7">
+        <v>203520.0</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
+      <c r="A26" s="9">
+        <v>46212.0</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="4">
-        <v>46205.0</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="9">
-        <v>75680.0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>5640.0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>3134.0</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="9">
-        <v>189540.0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>161685.0</v>
-      </c>
-      <c r="H6" s="9">
-        <v>144720.0</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="9">
-        <v>2010102.0</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="9">
-        <v>20640.0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>3761.0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>13920.0</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="9">
-        <v>152384.0</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="9">
-        <v>14700.0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>6435.0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>9600.0</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="11"/>
-    </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="9">
-        <v>228240.0</v>
-      </c>
-      <c r="G9" s="9">
-        <v>77306.0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>124260.0</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2152388.0</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="9">
-        <v>7830.0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>1980.0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>6030.0</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="9">
-        <v>31680.0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>5526.0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>23040.0</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="F26" s="7">
+        <v>10320.0</v>
+      </c>
+      <c r="G26" s="7">
+        <v>5869.0</v>
+      </c>
+      <c r="H26" s="7">
+        <v>13200.0</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
+      <c r="A27" s="9">
+        <v>46212.0</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="9">
-        <v>51387.0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>10827.0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>12170.0</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="4">
-        <v>46209.0</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="9">
-        <v>195810.0</v>
-      </c>
-      <c r="G13" s="9">
-        <v>93809.0</v>
-      </c>
-      <c r="H13" s="9">
-        <v>133410.0</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="4">
-        <v>46209.0</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="9">
-        <v>526002.0</v>
-      </c>
-      <c r="G14" s="9">
-        <v>301965.0</v>
-      </c>
-      <c r="H14" s="9">
-        <v>424588.0</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="4">
-        <v>46209.0</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="9">
-        <v>2010102.0</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="9">
-        <v>14160.0</v>
-      </c>
-      <c r="G15" s="9">
-        <v>6692.0</v>
-      </c>
-      <c r="H15" s="9">
-        <v>12360.0</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="4">
-        <v>46210.0</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="9">
-        <v>149040.0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>119573.0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>289680.0</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="4">
-        <v>46210.0</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="9">
-        <v>2110217.0</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="9">
-        <v>22770.0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>3926.0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>19770.0</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="4">
-        <v>46210.0</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="9">
-        <v>222021.0</v>
-      </c>
-      <c r="G18" s="9">
-        <v>61385.0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>162125.0</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="9">
-        <v>495833.0</v>
-      </c>
-      <c r="G19" s="9">
-        <v>148815.0</v>
-      </c>
-      <c r="H19" s="9">
-        <v>401280.0</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="9">
-        <v>139920.0</v>
-      </c>
-      <c r="G20" s="9">
-        <v>54384.0</v>
-      </c>
-      <c r="H20" s="9">
-        <v>74040.0</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="11"/>
-    </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="9">
-        <v>162125.0</v>
-      </c>
-      <c r="G21" s="9">
-        <v>60138.0</v>
-      </c>
-      <c r="H21" s="9">
-        <v>100687.0</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="9">
-        <v>152384.0</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="9">
-        <v>32850.0</v>
-      </c>
-      <c r="G22" s="9">
-        <v>7065.0</v>
-      </c>
-      <c r="H22" s="9">
-        <v>32700.0</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="11"/>
-    </row>
-    <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="C27" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="7">
         <v>112271.0</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="9">
-        <v>16500.0</v>
-      </c>
-      <c r="G23" s="9">
-        <v>5310.0</v>
-      </c>
-      <c r="H23" s="9">
+      <c r="F27" s="7">
         <v>18000.0</v>
       </c>
-      <c r="I23" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="J23" s="11"/>
-    </row>
-    <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="4">
-        <v>46212.0</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="9">
-        <v>190047.0</v>
-      </c>
-      <c r="G24" s="9">
-        <v>59822.0</v>
-      </c>
-      <c r="H24" s="9">
-        <v>248481.0</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="J24" s="11"/>
-    </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="4">
-        <v>46212.0</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="9">
-        <v>178080.0</v>
-      </c>
-      <c r="G25" s="9">
-        <v>47784.0</v>
-      </c>
-      <c r="H25" s="9">
-        <v>203520.0</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="J25" s="11"/>
-    </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="4">
-        <v>46212.0</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="9">
-        <v>10320.0</v>
-      </c>
-      <c r="G26" s="9">
-        <v>5869.0</v>
-      </c>
-      <c r="H26" s="9">
-        <v>13200.0</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="4">
-        <v>46212.0</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="9">
-        <v>112271.0</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" s="9">
-        <v>18000.0</v>
-      </c>
-      <c r="G27" s="9">
+      <c r="G27" s="7">
         <v>4485.0</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="7">
         <v>13500.0</v>
       </c>
-      <c r="I27" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="11"/>
+      <c r="I27" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="4">
+      <c r="A28" s="9">
         <v>46213.0</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="9">
+      <c r="E28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="7">
         <v>208440.0</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="7">
         <v>85608.0</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="7">
         <v>150833.0</v>
       </c>
-      <c r="I28" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="11" t="s">
+      <c r="I28" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="13" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="4">
+      <c r="A29" s="9">
         <v>46213.0</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="9">
+      <c r="E29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="7">
         <v>962820.0</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="7">
         <v>80644.0</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="7">
         <v>922140.0</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="11" t="s">
+      <c r="I29" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="13" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="4">
+      <c r="A30" s="9">
         <v>46213.0</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>25</v>
+      <c r="B30" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C30" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="7">
+        <v>335340.0</v>
+      </c>
+      <c r="G30" s="7">
+        <v>111433.0</v>
+      </c>
+      <c r="H30" s="7">
+        <v>381600.0</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="9">
+        <v>46213.0</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D31" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="7">
+        <v>316800.0</v>
+      </c>
+      <c r="G31" s="7">
+        <v>99546.0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>229680.0</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="13"/>
+    </row>
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
+      <c r="A32" s="9">
+        <v>46213.0</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="7">
+        <v>176850.0</v>
+      </c>
+      <c r="G32" s="7">
+        <v>47499.0</v>
+      </c>
+      <c r="H32" s="7">
+        <v>128971.0</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="13"/>
+    </row>
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
+      <c r="A33" s="9">
+        <v>46213.0</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="7">
+        <v>58080.0</v>
+      </c>
+      <c r="G33" s="7">
+        <v>20865.0</v>
+      </c>
+      <c r="H33" s="7">
+        <v>25440.0</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="13"/>
+    </row>
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
+      <c r="A34" s="9">
+        <v>46217.0</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="7">
+        <v>481440.0</v>
+      </c>
+      <c r="G34" s="7">
+        <v>464517.0</v>
+      </c>
+      <c r="H34" s="7">
+        <v>151435.0</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="13"/>
+    </row>
+    <row r="35" ht="22.5" hidden="1" customHeight="1">
+      <c r="A35" s="9">
+        <v>46217.0</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" s="9">
-        <v>335340.0</v>
-      </c>
-      <c r="G30" s="9">
-        <v>111433.0</v>
-      </c>
-      <c r="H30" s="9">
-        <v>381600.0</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="4">
-        <v>46213.0</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="9">
-        <v>316800.0</v>
-      </c>
-      <c r="G31" s="9">
-        <v>99546.0</v>
-      </c>
-      <c r="H31" s="9">
-        <v>229680.0</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="11"/>
-    </row>
-    <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="4">
-        <v>46213.0</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="9">
-        <v>176850.0</v>
-      </c>
-      <c r="G32" s="9">
-        <v>47499.0</v>
-      </c>
-      <c r="H32" s="9">
-        <v>128971.0</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="J32" s="11"/>
-    </row>
-    <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="4">
-        <v>46213.0</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E33" s="6" t="s">
+      <c r="E35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="7">
+        <v>355720.0</v>
+      </c>
+      <c r="G35" s="7">
+        <v>342811.0</v>
+      </c>
+      <c r="H35" s="7">
+        <v>302760.0</v>
+      </c>
+      <c r="I35" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="9">
-        <v>58080.0</v>
-      </c>
-      <c r="G33" s="9">
-        <v>20865.0</v>
-      </c>
-      <c r="H33" s="9">
-        <v>25440.0</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="11"/>
-    </row>
-    <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="4">
+      <c r="J35" s="13"/>
+    </row>
+    <row r="36" ht="22.5" hidden="1" customHeight="1">
+      <c r="A36" s="9">
         <v>46217.0</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="9">
-        <v>481440.0</v>
-      </c>
-      <c r="G34" s="9">
-        <v>464517.0</v>
-      </c>
-      <c r="H34" s="9">
-        <v>151435.0</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="11"/>
-    </row>
-    <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="4">
-        <v>46217.0</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="9">
-        <v>355720.0</v>
-      </c>
-      <c r="G35" s="9">
-        <v>342811.0</v>
-      </c>
-      <c r="H35" s="9">
-        <v>302760.0</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="11"/>
-    </row>
-    <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="4">
-        <v>46217.0</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="7">
         <v>2010102.0</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="9">
+      <c r="E36" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" s="7">
         <v>35280.0</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="7">
         <v>16988.0</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="7">
         <v>37926.0</v>
       </c>
-      <c r="I36" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="11" t="s">
+      <c r="I36" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="13" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1874,31 +1877,31 @@
       <c r="A37" s="18">
         <v>46218.0</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>11</v>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="9">
+      <c r="E37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="7">
         <v>272073.0</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="7">
         <v>76546.0</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="7">
         <v>275205.0</v>
       </c>
-      <c r="I37" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J37" s="11" t="s">
+      <c r="I37" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J37" s="13" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1906,31 +1909,31 @@
       <c r="A38" s="18">
         <v>46218.0</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>11</v>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="7">
         <v>2010102.0</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" s="9">
+      <c r="E38" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" s="7">
         <v>37926.0</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="7">
         <v>5633.0</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="7">
         <v>25746.0</v>
       </c>
-      <c r="I38" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" s="11" t="s">
+      <c r="I38" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="13" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1938,31 +1941,31 @@
       <c r="A39" s="18">
         <v>46218.0</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="9">
+      <c r="B39" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="9">
+      <c r="E39" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="7">
         <v>20640.0</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="7">
         <v>4951.0</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="7">
         <v>16320.0</v>
       </c>
-      <c r="I39" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J39" s="11" t="s">
+      <c r="I39" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39" s="13" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1970,713 +1973,717 @@
       <c r="A40" s="18">
         <v>46218.0</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="8" t="s">
+      <c r="B40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="7">
+        <v>2110317.0</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" s="7">
+        <v>10980.0</v>
+      </c>
+      <c r="G40" s="7">
+        <v>2379.0</v>
+      </c>
+      <c r="H40" s="7">
+        <v>13500.0</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" ht="22.5" hidden="1" customHeight="1">
+      <c r="A41" s="9">
+        <v>46219.0</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="9">
-        <v>2110317.0</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F40" s="9">
-        <v>10980.0</v>
-      </c>
-      <c r="G40" s="9">
-        <v>2379.0</v>
-      </c>
-      <c r="H40" s="9">
-        <v>13500.0</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J40" s="11"/>
-    </row>
-    <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="4">
+      <c r="F41" s="7">
+        <v>130320.0</v>
+      </c>
+      <c r="G41" s="7">
+        <v>47410.0</v>
+      </c>
+      <c r="H41" s="7">
+        <v>90480.0</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" ht="22.5" hidden="1" customHeight="1">
+      <c r="A42" s="9">
         <v>46219.0</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="9">
-        <v>130320.0</v>
-      </c>
-      <c r="G41" s="9">
-        <v>47410.0</v>
-      </c>
-      <c r="H41" s="9">
-        <v>90480.0</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="4">
-        <v>46219.0</v>
-      </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="7">
         <v>2152388.0</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42" s="7">
+        <v>36225.0</v>
+      </c>
+      <c r="G42" s="7">
+        <v>11746.0</v>
+      </c>
+      <c r="H42" s="7">
+        <v>27570.0</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" ht="22.5" hidden="1" customHeight="1">
+      <c r="A43" s="9">
+        <v>46219.0</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F42" s="9">
-        <v>36225.0</v>
-      </c>
-      <c r="G42" s="9">
-        <v>11746.0</v>
-      </c>
-      <c r="H42" s="9">
-        <v>27570.0</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="11"/>
-    </row>
-    <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="4">
+      <c r="D43" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="7">
+        <v>152833.0</v>
+      </c>
+      <c r="G43" s="7">
+        <v>50641.0</v>
+      </c>
+      <c r="H43" s="7">
+        <v>96472.0</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" hidden="1" customHeight="1">
+      <c r="A44" s="9">
         <v>46219.0</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F43" s="9">
-        <v>152833.0</v>
-      </c>
-      <c r="G43" s="9">
-        <v>50641.0</v>
-      </c>
-      <c r="H43" s="9">
-        <v>96472.0</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="4">
-        <v>46219.0</v>
-      </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F44" s="9">
+      <c r="E44" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="7">
         <v>237828.0</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="7">
         <v>173585.0</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="7">
         <v>71560.0</v>
       </c>
-      <c r="I44" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J44" s="11"/>
+      <c r="I44" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="4">
+      <c r="A45" s="9">
         <v>46219.0</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>11</v>
+      <c r="B45" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="7">
         <v>152384.0</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F45" s="9">
+      <c r="E45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F45" s="7">
         <v>31125.0</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="7">
         <v>7815.0</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="7">
         <v>31845.0</v>
       </c>
-      <c r="I45" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J45" s="11" t="s">
+      <c r="I45" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J45" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="4">
+      <c r="A46" s="9">
         <v>46219.0</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>11</v>
+      <c r="B46" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="7">
         <v>2010102.0</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F46" s="9">
+      <c r="E46" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F46" s="7">
         <v>25746.0</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="7">
         <v>6168.0</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="7">
         <v>28683.0</v>
       </c>
-      <c r="I46" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J46" s="11" t="s">
+      <c r="I46" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="4">
+      <c r="A47" s="9">
         <v>46220.0</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>11</v>
+      <c r="B47" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F47" s="9">
+      <c r="E47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="7">
         <v>261166.0</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="7">
         <v>74573.0</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="7">
         <v>221549.0</v>
       </c>
-      <c r="I47" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J47" s="11" t="s">
+      <c r="I47" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J47" s="13" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="4">
+      <c r="A48" s="9">
         <v>46220.0</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>11</v>
+      <c r="B48" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="7">
         <v>2110217.0</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F48" s="9">
+      <c r="E48" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="7">
         <v>115289.0</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="7">
         <v>26931.0</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="7">
         <v>119584.0</v>
       </c>
-      <c r="I48" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J48" s="11"/>
+      <c r="I48" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="4">
+      <c r="A49" s="9">
         <v>46224.0</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>19</v>
+      <c r="B49" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="9">
+        <v>16</v>
+      </c>
+      <c r="D49" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="9">
+      <c r="E49" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="7">
         <v>398570.0</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="7">
         <v>288226.0</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="7">
         <v>287235.0</v>
       </c>
-      <c r="I49" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J49" s="11" t="s">
+      <c r="I49" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J49" s="13" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="4">
+      <c r="A50" s="9">
         <v>46224.0</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9">
+      <c r="E50" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="7">
         <v>745107.0</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="7">
         <v>378927.0</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="7">
         <v>551645.0</v>
       </c>
-      <c r="I50" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" s="11" t="s">
+      <c r="I50" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="13" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="4">
+      <c r="A51" s="9">
         <v>46225.0</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" s="9">
+      <c r="B51" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F51" s="9">
+      <c r="E51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="7">
         <v>130560.0</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="7">
         <v>52658.0</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="7">
         <v>153840.0</v>
       </c>
-      <c r="I51" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J51" s="11" t="s">
+      <c r="I51" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" s="13" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="4">
+      <c r="A52" s="9">
         <v>46225.0</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D52" s="9">
+      <c r="B52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F52" s="9">
+      <c r="E52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="7">
         <v>87447.0</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="7">
         <v>59056.0</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="7">
         <v>104365.0</v>
       </c>
-      <c r="I52" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J52" s="11"/>
+      <c r="I52" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="4">
+      <c r="A53" s="9">
         <v>46225.0</v>
       </c>
-      <c r="B53" s="6" t="s">
-        <v>11</v>
+      <c r="B53" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="9">
+      <c r="E53" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="7">
         <v>25200.0</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="7">
         <v>2085.0</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="7">
         <v>25920.0</v>
       </c>
-      <c r="I53" s="13" t="s">
+      <c r="I53" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J53" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="4">
+      <c r="C54" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="7">
+        <v>285405.0</v>
+      </c>
+      <c r="G54" s="7">
+        <v>203180.0</v>
+      </c>
+      <c r="H54" s="7">
+        <v>226069.0</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J54" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="9">
         <v>46226.0</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="8" t="s">
+      <c r="B55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="7">
+        <v>692280.0</v>
+      </c>
+      <c r="G55" s="7">
+        <v>118381.0</v>
+      </c>
+      <c r="H55" s="7">
+        <v>700200.0</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J55" s="13"/>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="A56" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="7">
+        <v>700200.0</v>
+      </c>
+      <c r="G56" s="7">
+        <v>112628.0</v>
+      </c>
+      <c r="H56" s="7">
+        <v>668440.0</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="13"/>
+    </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D57" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="9">
-        <v>285405.0</v>
-      </c>
-      <c r="G54" s="9">
-        <v>203180.0</v>
-      </c>
-      <c r="H54" s="9">
+      <c r="E57" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="7">
         <v>226069.0</v>
       </c>
-      <c r="I54" s="13" t="s">
+      <c r="G57" s="7">
+        <v>193130.0</v>
+      </c>
+      <c r="H57" s="7">
+        <v>326391.0</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" ht="22.5" customHeight="1">
+      <c r="A58" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="7">
+        <v>144637.0</v>
+      </c>
+      <c r="G58" s="7">
+        <v>64227.0</v>
+      </c>
+      <c r="H58" s="7">
+        <v>128160.0</v>
+      </c>
+      <c r="I58" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="J54" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" s="9">
-        <v>692280.0</v>
-      </c>
-      <c r="G55" s="9">
-        <v>118381.0</v>
-      </c>
-      <c r="H55" s="9">
-        <v>700200.0</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="J55" s="11"/>
-    </row>
-    <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="4">
+      <c r="J58" s="13"/>
+    </row>
+    <row r="59" ht="22.5" customHeight="1">
+      <c r="A59" s="9">
         <v>46227.0</v>
       </c>
-      <c r="B56" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D56" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F56" s="9">
-        <v>700200.0</v>
-      </c>
-      <c r="G56" s="9">
-        <v>112628.0</v>
-      </c>
-      <c r="H56" s="9">
-        <v>668440.0</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J56" s="11"/>
-    </row>
-    <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D57" s="9">
+      <c r="B59" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D59" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="9">
-        <v>226069.0</v>
-      </c>
-      <c r="G57" s="9">
-        <v>193130.0</v>
-      </c>
-      <c r="H57" s="9">
-        <v>326391.0</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="58" ht="22.5" customHeight="1">
-      <c r="A58" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D58" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" s="9">
-        <v>144637.0</v>
-      </c>
-      <c r="G58" s="9">
-        <v>64227.0</v>
-      </c>
-      <c r="H58" s="9">
-        <v>128160.0</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="J58" s="11"/>
-    </row>
-    <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="E59" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="7">
+        <v>295359.0</v>
+      </c>
+      <c r="G59" s="7">
+        <v>126369.0</v>
+      </c>
+      <c r="H59" s="7">
+        <v>166642.0</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="9">
+        <v>46230.0</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C60" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="9">
-        <v>295359.0</v>
-      </c>
-      <c r="G59" s="9">
-        <v>126369.0</v>
-      </c>
-      <c r="H59" s="9">
-        <v>166642.0</v>
-      </c>
-      <c r="I59" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" s="4">
+      <c r="D60" s="7">
+        <v>2110403.0</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F60" s="7">
+        <v>9960.0</v>
+      </c>
+      <c r="G60" s="7">
+        <v>6018.0</v>
+      </c>
+      <c r="H60" s="7">
+        <v>3660.0</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" ht="22.5" customHeight="1">
+      <c r="A61" s="9">
         <v>46230.0</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D60" s="9">
-        <v>2110403.0</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F60" s="9">
-        <v>9960.0</v>
-      </c>
-      <c r="G60" s="9">
-        <v>6018.0</v>
-      </c>
-      <c r="H60" s="9">
-        <v>3660.0</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J60" s="11"/>
-    </row>
-    <row r="61" ht="22.5" customHeight="1">
-      <c r="A61" s="4">
-        <v>46230.0</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>11</v>
+      <c r="B61" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F61" s="9">
+      <c r="E61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" s="7">
         <v>306720.0</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G61" s="7">
         <v>164175.0</v>
       </c>
-      <c r="H61" s="9">
+      <c r="H61" s="7">
         <v>247096.0</v>
       </c>
-      <c r="I61" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J61" s="11"/>
+      <c r="I61" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="13"/>
     </row>
     <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="4">
+      <c r="A62" s="9">
         <v>46230.0</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D62" s="9">
+      <c r="B62" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F62" s="9">
+      <c r="E62" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="7">
         <v>437080.0</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62" s="7">
         <v>277785.0</v>
       </c>
-      <c r="H62" s="9">
+      <c r="H62" s="7">
         <v>353700.0</v>
       </c>
-      <c r="I62" s="13"/>
-      <c r="J62" s="11"/>
+      <c r="I62" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J62" s="13" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="63">
       <c r="I63" s="16"/>
@@ -5584,532 +5591,532 @@
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="9">
         <v>46224.0</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="9">
+      <c r="B2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="9">
+      <c r="E2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="7">
         <v>333.0</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="7">
         <v>6480.0</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="7">
         <v>3712.0</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="9">
+        <v>46224.0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="7">
+        <v>2114158.0</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="7">
+        <v>60.0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1000.0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>60.0</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="4">
-        <v>46224.0</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="7">
+        <v>10501.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="7">
+        <v>415093.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>115920.0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>543038.0</v>
+      </c>
+      <c r="I4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="9">
-        <v>2114158.0</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="J4" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>29400.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="I5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="9">
-        <v>60.0</v>
-      </c>
-      <c r="G3" s="9">
-        <v>1000.0</v>
-      </c>
-      <c r="H3" s="9">
-        <v>60.0</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="4">
+      <c r="J5" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="9">
         <v>46225.0</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="9">
-        <v>10501.0</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="9">
-        <v>415093.0</v>
-      </c>
-      <c r="G4" s="9">
-        <v>115920.0</v>
-      </c>
-      <c r="H4" s="9">
-        <v>543038.0</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="4">
+      <c r="C6" s="14"/>
+      <c r="D6" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>12300.0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="9">
         <v>46225.0</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="9">
+      <c r="B7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="7">
+        <v>132357.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1560.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1560.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>4560.0</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>11160.0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>5940.0</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="7">
+        <v>3712.0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>46723.0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>213.0</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="7">
+        <v>73001.0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="7">
+        <v>73787.0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>72000.0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>109487.0</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>1800.0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="7">
         <v>112379.0</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="9">
-        <v>3000.0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>29400.0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>3000.0</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="9">
+      <c r="E12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="7">
+        <v>4200.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>7500.0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>3900.0</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="7">
+        <v>379471.0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>392580.0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>357186.0</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="7">
+        <v>72001.0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="7">
+        <v>21905.0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>47670.0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>38000.0</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="7">
+        <v>2110327.0</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="7">
+        <v>69120.0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>57600.0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>40320.0</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="7">
+        <v>3900.0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>102600.0</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1500.0</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>9720.0</v>
+      </c>
+      <c r="H17" s="7">
+        <v>2580.0</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="7">
         <v>112268.0</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="9">
-        <v>3000.0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>12300.0</v>
-      </c>
-      <c r="H6" s="9">
+      <c r="E18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="7">
         <v>3300.0</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="9">
-        <v>132357.0</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="9">
-        <v>1560.0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>1560.0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>4560.0</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="9">
-        <v>2152388.0</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="9">
-        <v>720.0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>11160.0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>5940.0</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="9">
-        <v>3712.0</v>
-      </c>
-      <c r="G9" s="9">
-        <v>46723.0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>213.0</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="9">
-        <v>73001.0</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="9">
-        <v>73787.0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>72000.0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>109487.0</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="9">
-        <v>112268.0</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="9">
-        <v>3300.0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>1800.0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>3300.0</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="9">
-        <v>112379.0</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="9">
-        <v>4200.0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>7500.0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>3900.0</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="9">
-        <v>379471.0</v>
-      </c>
-      <c r="G13" s="9">
-        <v>392580.0</v>
-      </c>
-      <c r="H13" s="9">
-        <v>357186.0</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="9">
-        <v>72001.0</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="9">
-        <v>21905.0</v>
-      </c>
-      <c r="G14" s="9">
-        <v>47670.0</v>
-      </c>
-      <c r="H14" s="9">
-        <v>38000.0</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="9">
-        <v>2110327.0</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="9">
-        <v>69120.0</v>
-      </c>
-      <c r="G15" s="9">
-        <v>57600.0</v>
-      </c>
-      <c r="H15" s="9">
-        <v>40320.0</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="9">
-        <v>112379.0</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="9">
-        <v>3900.0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>102600.0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>1500.0</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="9">
-        <v>2152388.0</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="9">
-        <v>720.0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>9720.0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>2580.0</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="9">
-        <v>112268.0</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="9">
-        <v>3300.0</v>
-      </c>
-      <c r="G18" s="9">
+      <c r="G18" s="7">
         <v>30600.0</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="7">
         <v>600.0</v>
       </c>
-      <c r="I18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>63</v>
+      <c r="I18" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="4">
+      <c r="A19" s="9">
         <v>46230.0</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>39</v>
+      <c r="B19" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="C19" s="14"/>
-      <c r="D19" s="9">
+      <c r="D19" s="7">
         <v>2410401.0</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="9">
+      <c r="E19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="7">
         <v>136538.0</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="7">
         <v>34080.0</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="7">
         <v>213000.0</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="11"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20">
       <c r="I20" s="16"/>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="125">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -44,21 +44,21 @@
     <t xml:space="preserve">Otro </t>
   </si>
   <si>
+    <t>ALKA2</t>
+  </si>
+  <si>
     <t>TAT BOGOTA MONTEVIDEO</t>
   </si>
   <si>
-    <t>ALKA2</t>
-  </si>
-  <si>
     <t>Daniel Castro</t>
   </si>
   <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t>7. Otro</t>
   </si>
   <si>
@@ -89,12 +89,12 @@
     <t>3. Falla De Rotación</t>
   </si>
   <si>
+    <t>HUEVO B X30 CARTON GRIS</t>
+  </si>
+  <si>
     <t>TAT MEDELLIN</t>
   </si>
   <si>
-    <t>HUEVO B X30 CARTON GRIS</t>
-  </si>
-  <si>
     <t>FABIO GOMEZ</t>
   </si>
   <si>
@@ -110,13 +110,16 @@
     <t>TAT CARTAGENA</t>
   </si>
   <si>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
     <t>Dilan Barraza</t>
   </si>
   <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
     <t>4. Exigencia Del Cliente (Edad)</t>
@@ -125,49 +128,52 @@
     <t>Venta FS</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
-  </si>
-  <si>
     <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
   </si>
   <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+  </si>
+  <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
-    <t>PALMAS</t>
-  </si>
-  <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
-  </si>
-  <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+  </si>
+  <si>
     <t>TAT CALI</t>
   </si>
   <si>
     <t>DIEGO ROJAS</t>
   </si>
   <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+    <t>HUEVO PICADO ROJO</t>
+  </si>
+  <si>
+    <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
     <t>TAT CUCUTA</t>
@@ -176,12 +182,6 @@
     <t>ALEXANDER PEÑA</t>
   </si>
   <si>
-    <t>HUEVO PICADO ROJO</t>
-  </si>
-  <si>
-    <t>No se carga todod por capacidad de Vehiculo</t>
-  </si>
-  <si>
     <t>Clientes FS</t>
   </si>
   <si>
@@ -212,52 +212,67 @@
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
+    <t>Cola de programación</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+  </si>
+  <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
+    <t>HUEVO CX30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
+  </si>
+  <si>
     <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
-    <t>Cola de programación</t>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
   </si>
   <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
   </si>
   <si>
     <t>5. Ingreso De Planta</t>
   </si>
   <si>
-    <t>HUEVO CX30 CARTON GRIS</t>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
     <t>Se despacha par FS con producto más nuevo</t>
   </si>
   <si>
-    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
-  </si>
-  <si>
     <t>ANDREA QUIROGA</t>
   </si>
   <si>
     <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+    <t>ALKA1</t>
+  </si>
+  <si>
+    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
   </si>
   <si>
     <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
+    <t>HUEVO ROTO - ZF</t>
+  </si>
+  <si>
+    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
+  </si>
+  <si>
+    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
   </si>
   <si>
     <t>TAT PASTO</t>
@@ -266,33 +281,24 @@
     <t>CAROLINA VITERI</t>
   </si>
   <si>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
+  </si>
+  <si>
+    <t>Cargo en incubación</t>
+  </si>
+  <si>
     <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
-    <t>ALKA1</t>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
     <t>Pedido para villavicencio</t>
   </si>
   <si>
-    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
-  </si>
-  <si>
-    <t>HUEVO ROTO - ZF</t>
-  </si>
-  <si>
-    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
-  </si>
-  <si>
     <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
-    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
     <t>Inventario de Asesor de Rionegro que renuncio</t>
   </si>
   <si>
@@ -302,15 +308,9 @@
     <t>Jhonatan Gomez</t>
   </si>
   <si>
-    <t>Cargo en incubación</t>
-  </si>
-  <si>
     <t>Lote mezclado en la misma estiba</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
     <t>Supera edad solicitada clientes grandes superficies</t>
   </si>
   <si>
@@ -384,6 +384,9 @@
   </si>
   <si>
     <t>Se envía lotemás nuevo a Sincelejo</t>
+  </si>
+  <si>
+    <t>Se envía huevo más fresco para clientes FS</t>
   </si>
 </sst>
 </file>
@@ -423,14 +426,14 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -461,54 +464,54 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -572,13 +575,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Cedis-style">
+    <tableStyle count="4" pivot="0" name="Plantas-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Plantas-style">
+    <tableStyle count="4" pivot="0" name="Cedis-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -601,7 +604,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J83" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J87" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -619,7 +622,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J40" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J44" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -882,20 +885,20 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>46204.0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="9">
         <v>359100.0</v>
@@ -911,20 +914,20 @@
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>46205.0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="9">
         <v>298282.0</v>
@@ -938,16 +941,16 @@
       <c r="I3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="7"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>46205.0</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="9">
@@ -968,23 +971,23 @@
       <c r="I4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="7"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>46205.0</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>32</v>
+      <c r="C5" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D5" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="9">
         <v>75680.0</v>
@@ -996,27 +999,27 @@
         <v>3134.0</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>46206.0</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D6" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="9">
         <v>189540.0</v>
@@ -1031,24 +1034,24 @@
         <v>15</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>46206.0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="9">
         <v>20640.0</v>
@@ -1060,27 +1063,27 @@
         <v>13920.0</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>46206.0</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D8" s="9">
         <v>152384.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" s="9">
         <v>14700.0</v>
@@ -1097,20 +1100,20 @@
       <c r="J8" s="12"/>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>46206.0</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D9" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="9">
         <v>228240.0</v>
@@ -1127,20 +1130,20 @@
       <c r="J9" s="12"/>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>46206.0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="D10" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10" s="9">
         <v>7830.0</v>
@@ -1157,20 +1160,20 @@
       <c r="J10" s="15"/>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>46206.0</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="9">
         <v>31680.0</v>
@@ -1182,27 +1185,27 @@
         <v>23040.0</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>46206.0</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>51387.0</v>
@@ -1214,27 +1217,27 @@
         <v>12170.0</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>46209.0</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="9">
         <v>195810.0</v>
@@ -1246,27 +1249,27 @@
         <v>133410.0</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>46209.0</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>32</v>
+      <c r="C14" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D14" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="9">
         <v>526002.0</v>
@@ -1285,20 +1288,20 @@
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>46209.0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="9">
         <v>14160.0</v>
@@ -1317,20 +1320,20 @@
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <v>46210.0</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D16" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16" s="9">
         <v>149040.0</v>
@@ -1347,14 +1350,14 @@
       <c r="J16" s="12"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>46210.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D17" s="9">
         <v>2110217.0</v>
@@ -1377,20 +1380,20 @@
       <c r="J17" s="12"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <v>46210.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D18" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18" s="9">
         <v>222021.0</v>
@@ -1407,20 +1410,20 @@
       <c r="J18" s="12"/>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <v>46211.0</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>32</v>
+      <c r="C19" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="D19" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="9">
         <v>495833.0</v>
@@ -1435,24 +1438,24 @@
         <v>15</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="5">
+      <c r="A20" s="4">
         <v>46211.0</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="9">
         <v>139920.0</v>
@@ -1469,20 +1472,20 @@
       <c r="J20" s="12"/>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <v>46211.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D21" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F21" s="9">
         <v>162125.0</v>
@@ -1497,24 +1500,24 @@
         <v>15</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <v>46211.0</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="9">
         <v>152384.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F22" s="9">
         <v>32850.0</v>
@@ -1526,25 +1529,25 @@
         <v>32700.0</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J22" s="12"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <v>46211.0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>61</v>
       </c>
       <c r="D23" s="9">
         <v>112271.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F23" s="9">
         <v>16500.0</v>
@@ -1561,20 +1564,20 @@
       <c r="J23" s="12"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="5">
+      <c r="A24" s="4">
         <v>46212.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D24" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F24" s="9">
         <v>190047.0</v>
@@ -1591,11 +1594,11 @@
       <c r="J24" s="12"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <v>46212.0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>61</v>
@@ -1604,7 +1607,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F25" s="9">
         <v>178080.0</v>
@@ -1616,16 +1619,16 @@
         <v>203520.0</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J25" s="12"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="5">
+      <c r="A26" s="4">
         <v>46212.0</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>61</v>
@@ -1634,7 +1637,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="9">
         <v>10320.0</v>
@@ -1646,18 +1649,18 @@
         <v>13200.0</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="5">
+      <c r="A27" s="4">
         <v>46212.0</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>61</v>
@@ -1666,7 +1669,7 @@
         <v>112271.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F27" s="9">
         <v>18000.0</v>
@@ -1683,20 +1686,20 @@
       <c r="J27" s="12"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="5">
+      <c r="A28" s="4">
         <v>46213.0</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D28" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" s="9">
         <v>208440.0</v>
@@ -1711,24 +1714,24 @@
         <v>15</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="5">
+      <c r="A29" s="4">
         <v>46213.0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D29" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F29" s="9">
         <v>962820.0</v>
@@ -1743,15 +1746,15 @@
         <v>15</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="5">
+      <c r="A30" s="4">
         <v>46213.0</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>61</v>
@@ -1760,7 +1763,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" s="9">
         <v>335340.0</v>
@@ -1772,14 +1775,14 @@
         <v>381600.0</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="5">
+      <c r="A31" s="4">
         <v>46213.0</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -1792,7 +1795,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F31" s="9">
         <v>316800.0</v>
@@ -1809,20 +1812,20 @@
       <c r="J31" s="12"/>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="5">
+      <c r="A32" s="4">
         <v>46213.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D32" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F32" s="9">
         <v>176850.0</v>
@@ -1839,7 +1842,7 @@
       <c r="J32" s="12"/>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="5">
+      <c r="A33" s="4">
         <v>46213.0</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -1852,7 +1855,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33" s="9">
         <v>58080.0</v>
@@ -1869,20 +1872,20 @@
       <c r="J33" s="12"/>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="5">
+      <c r="A34" s="4">
         <v>46217.0</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="D34" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F34" s="9">
         <v>481440.0</v>
@@ -1899,20 +1902,20 @@
       <c r="J34" s="12"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="5">
+      <c r="A35" s="4">
         <v>46217.0</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D35" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F35" s="9">
         <v>355720.0</v>
@@ -1929,20 +1932,20 @@
       <c r="J35" s="12"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="5">
+      <c r="A36" s="4">
         <v>46217.0</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D36" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F36" s="9">
         <v>35280.0</v>
@@ -1957,24 +1960,24 @@
         <v>24</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
-      <c r="A37" s="17">
+      <c r="A37" s="19">
         <v>46218.0</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D37" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F37" s="9">
         <v>272073.0</v>
@@ -1986,27 +1989,27 @@
         <v>275205.0</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
-      <c r="A38" s="17">
+      <c r="A38" s="19">
         <v>46218.0</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D38" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F38" s="9">
         <v>37926.0</v>
@@ -2021,24 +2024,24 @@
         <v>24</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
-      <c r="A39" s="17">
+      <c r="A39" s="19">
         <v>46218.0</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D39" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" s="9">
         <v>20640.0</v>
@@ -2050,27 +2053,27 @@
         <v>16320.0</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
-      <c r="A40" s="17">
+      <c r="A40" s="19">
         <v>46218.0</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D40" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F40" s="9">
         <v>10980.0</v>
@@ -2087,11 +2090,11 @@
       <c r="J40" s="12"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="5">
+      <c r="A41" s="4">
         <v>46219.0</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>27</v>
@@ -2100,7 +2103,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F41" s="9">
         <v>130320.0</v>
@@ -2115,24 +2118,24 @@
         <v>48</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="5">
+      <c r="A42" s="4">
         <v>46219.0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D42" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F42" s="9">
         <v>36225.0</v>
@@ -2149,20 +2152,20 @@
       <c r="J42" s="12"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="5">
+      <c r="A43" s="4">
         <v>46219.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D43" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F43" s="9">
         <v>152833.0</v>
@@ -2174,27 +2177,27 @@
         <v>96472.0</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="5">
+      <c r="A44" s="4">
         <v>46219.0</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D44" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F44" s="9">
         <v>237828.0</v>
@@ -2211,20 +2214,20 @@
       <c r="J44" s="12"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="5">
+      <c r="A45" s="4">
         <v>46219.0</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D45" s="9">
         <v>152384.0</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F45" s="9">
         <v>31125.0</v>
@@ -2236,27 +2239,27 @@
         <v>31845.0</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="5">
+      <c r="A46" s="4">
         <v>46219.0</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D46" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F46" s="9">
         <v>25746.0</v>
@@ -2271,24 +2274,24 @@
         <v>24</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="5">
+      <c r="A47" s="4">
         <v>46220.0</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D47" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F47" s="9">
         <v>261166.0</v>
@@ -2300,21 +2303,21 @@
         <v>221549.0</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="5">
+      <c r="A48" s="4">
         <v>46220.0</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D48" s="9">
         <v>2110217.0</v>
@@ -2337,7 +2340,7 @@
       <c r="J48" s="12"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="5">
+      <c r="A49" s="4">
         <v>46224.0</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -2350,7 +2353,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" s="9">
         <v>398570.0</v>
@@ -2362,27 +2365,27 @@
         <v>287235.0</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J49" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="5">
+      <c r="A50" s="4">
         <v>46224.0</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D50" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F50" s="9">
         <v>745107.0</v>
@@ -2401,20 +2404,20 @@
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="5">
+      <c r="A51" s="4">
         <v>46225.0</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>61</v>
       </c>
       <c r="D51" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F51" s="9">
         <v>130560.0</v>
@@ -2433,20 +2436,20 @@
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="5">
+      <c r="A52" s="4">
         <v>46225.0</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D52" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F52" s="9">
         <v>87447.0</v>
@@ -2463,20 +2466,20 @@
       <c r="J52" s="12"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="5">
+      <c r="A53" s="4">
         <v>46225.0</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D53" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" s="9">
         <v>25200.0</v>
@@ -2495,20 +2498,20 @@
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
-      <c r="A54" s="5">
+      <c r="A54" s="4">
         <v>46226.0</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="7" t="s">
         <v>105</v>
       </c>
       <c r="D54" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F54" s="9">
         <v>285405.0</v>
@@ -2520,27 +2523,27 @@
         <v>226069.0</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
-      <c r="A55" s="5">
+      <c r="A55" s="4">
         <v>46226.0</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>61</v>
       </c>
       <c r="D55" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F55" s="9">
         <v>692280.0</v>
@@ -2552,25 +2555,25 @@
         <v>700200.0</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J55" s="12"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
-      <c r="A56" s="5">
+      <c r="A56" s="4">
         <v>46227.0</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C56" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>61</v>
       </c>
       <c r="D56" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F56" s="9">
         <v>700200.0</v>
@@ -2587,20 +2590,20 @@
       <c r="J56" s="12"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
-      <c r="A57" s="5">
+      <c r="A57" s="4">
         <v>46227.0</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>105</v>
       </c>
       <c r="D57" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F57" s="9">
         <v>226069.0</v>
@@ -2619,20 +2622,20 @@
       </c>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
-      <c r="A58" s="5">
+      <c r="A58" s="4">
         <v>46227.0</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C58" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D58" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F58" s="9">
         <v>144637.0</v>
@@ -2644,25 +2647,25 @@
         <v>128160.0</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J58" s="12"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="5">
+      <c r="A59" s="4">
         <v>46227.0</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="D59" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F59" s="9">
         <v>295359.0</v>
@@ -2681,14 +2684,14 @@
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="5">
+      <c r="A60" s="4">
         <v>46230.0</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="D60" s="9">
         <v>2110403.0</v>
@@ -2711,20 +2714,20 @@
       <c r="J60" s="12"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="5">
+      <c r="A61" s="4">
         <v>46230.0</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D61" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F61" s="9">
         <v>306720.0</v>
@@ -2741,20 +2744,20 @@
       <c r="J61" s="12"/>
     </row>
     <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="5">
+      <c r="A62" s="4">
         <v>46230.0</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C62" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D62" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F62" s="9">
         <v>437080.0</v>
@@ -2766,27 +2769,27 @@
         <v>353700.0</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J62" s="12" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="5">
+      <c r="A63" s="4">
         <v>46231.0</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D63" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" s="9">
         <v>165466.0</v>
@@ -2798,27 +2801,27 @@
         <v>375549.0</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J63" s="12" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
-      <c r="A64" s="5">
+      <c r="A64" s="4">
         <v>46231.0</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C64" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D64" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F64" s="9">
         <v>238497.0</v>
@@ -2837,20 +2840,20 @@
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
-      <c r="A65" s="5">
+      <c r="A65" s="4">
         <v>46231.0</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C65" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D65" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F65" s="9">
         <v>8190.0</v>
@@ -2869,20 +2872,20 @@
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
-      <c r="A66" s="5">
+      <c r="A66" s="4">
         <v>46231.0</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C66" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D66" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F66" s="9">
         <v>146224.0</v>
@@ -2901,7 +2904,7 @@
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
-      <c r="A67" s="5">
+      <c r="A67" s="4">
         <v>46232.0</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -2912,7 +2915,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F67" s="9">
         <v>14599.0</v>
@@ -2929,18 +2932,18 @@
       <c r="J67" s="12"/>
     </row>
     <row r="68" ht="22.5" hidden="1" customHeight="1">
-      <c r="A68" s="5">
+      <c r="A68" s="4">
         <v>46232.0</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C68" s="21"/>
       <c r="D68" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F68" s="9">
         <v>22080.0</v>
@@ -2957,7 +2960,7 @@
       <c r="J68" s="12"/>
     </row>
     <row r="69" ht="22.5" hidden="1" customHeight="1">
-      <c r="A69" s="5">
+      <c r="A69" s="4">
         <v>46232.0</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -2968,7 +2971,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F69" s="9">
         <v>353905.0</v>
@@ -2985,18 +2988,18 @@
       <c r="J69" s="12"/>
     </row>
     <row r="70" ht="22.5" hidden="1" customHeight="1">
-      <c r="A70" s="5">
+      <c r="A70" s="4">
         <v>46232.0</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C70" s="21"/>
       <c r="D70" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F70" s="9">
         <v>5913.0</v>
@@ -3013,18 +3016,18 @@
       <c r="J70" s="12"/>
     </row>
     <row r="71" ht="22.5" hidden="1" customHeight="1">
-      <c r="A71" s="5">
+      <c r="A71" s="4">
         <v>46232.0</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="21"/>
       <c r="D71" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F71" s="9">
         <v>256613.0</v>
@@ -3041,18 +3044,18 @@
       <c r="J71" s="12"/>
     </row>
     <row r="72" ht="22.5" hidden="1" customHeight="1">
-      <c r="A72" s="5">
+      <c r="A72" s="4">
         <v>46232.0</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C72" s="21"/>
       <c r="D72" s="9">
         <v>152384.0</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F72" s="9">
         <v>21300.0</v>
@@ -3069,18 +3072,18 @@
       <c r="J72" s="12"/>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
-      <c r="A73" s="5">
+      <c r="A73" s="4">
         <v>46232.0</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C73" s="21"/>
       <c r="D73" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F73" s="9">
         <v>351733.0</v>
@@ -3097,20 +3100,20 @@
       <c r="J73" s="12"/>
     </row>
     <row r="74" ht="22.5" customHeight="1">
-      <c r="A74" s="17">
+      <c r="A74" s="19">
         <v>46233.0</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D74" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F74" s="9">
         <v>158761.0</v>
@@ -3122,27 +3125,27 @@
         <v>183014.0</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J74" s="12" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
-      <c r="A75" s="17">
+      <c r="A75" s="19">
         <v>46233.0</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D75" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F75" s="9">
         <v>117430.0</v>
@@ -3159,20 +3162,20 @@
       <c r="J75" s="12"/>
     </row>
     <row r="76" ht="22.5" customHeight="1">
-      <c r="A76" s="5">
+      <c r="A76" s="4">
         <v>46234.0</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>76</v>
+        <v>11</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D76" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F76" s="9">
         <v>265693.0</v>
@@ -3189,20 +3192,20 @@
       <c r="J76" s="12"/>
     </row>
     <row r="77" ht="22.5" customHeight="1">
-      <c r="A77" s="5">
+      <c r="A77" s="4">
         <v>46234.0</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="7" t="s">
         <v>116</v>
       </c>
       <c r="D77" s="9">
         <v>112357.0</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F77" s="9">
         <v>720.0</v>
@@ -3221,20 +3224,20 @@
       </c>
     </row>
     <row r="78" ht="22.5" customHeight="1">
-      <c r="A78" s="5">
+      <c r="A78" s="4">
         <v>46234.0</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C78" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D78" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F78" s="9">
         <v>5580.0</v>
@@ -3253,20 +3256,20 @@
       </c>
     </row>
     <row r="79" ht="22.5" customHeight="1">
-      <c r="A79" s="19">
+      <c r="A79" s="18">
         <v>46237.0</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C79" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D79" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F79" s="9">
         <v>192903.0</v>
@@ -3285,20 +3288,20 @@
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
-      <c r="A80" s="19">
+      <c r="A80" s="18">
         <v>46237.0</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C80" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="D80" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F80" s="9">
         <v>152062.0</v>
@@ -3317,20 +3320,20 @@
       </c>
     </row>
     <row r="81" ht="22.5" customHeight="1">
-      <c r="A81" s="19">
+      <c r="A81" s="18">
         <v>46237.0</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C81" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C81" s="7" t="s">
         <v>120</v>
       </c>
       <c r="D81" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F81" s="9">
         <v>153692.0</v>
@@ -3342,27 +3345,27 @@
         <v>63920.0</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J81" s="12" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" ht="22.5" customHeight="1">
-      <c r="A82" s="19">
+      <c r="A82" s="18">
         <v>46237.0</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C82" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" s="7" t="s">
         <v>122</v>
       </c>
       <c r="D82" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" s="9">
         <v>45564.0</v>
@@ -3379,20 +3382,20 @@
       <c r="J82" s="12"/>
     </row>
     <row r="83" ht="22.5" customHeight="1">
-      <c r="A83" s="19">
+      <c r="A83" s="18">
         <v>46237.0</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D83" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F83" s="9">
         <v>93517.0</v>
@@ -3404,23 +3407,133 @@
         <v>48804.0</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J83" s="12" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="84">
-      <c r="I84" s="20"/>
-    </row>
-    <row r="85">
-      <c r="I85" s="20"/>
-    </row>
-    <row r="86">
-      <c r="I86" s="20"/>
-    </row>
-    <row r="87">
-      <c r="I87" s="20"/>
+    <row r="84" ht="22.5" customHeight="1">
+      <c r="A84" s="4">
+        <v>46238.0</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D84" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F84" s="9">
+        <v>43200.0</v>
+      </c>
+      <c r="G84" s="9">
+        <v>5340.0</v>
+      </c>
+      <c r="H84" s="9">
+        <v>40890.0</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J84" s="12"/>
+    </row>
+    <row r="85" ht="22.5" customHeight="1">
+      <c r="A85" s="4">
+        <v>46238.0</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D85" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F85" s="9">
+        <v>25350.0</v>
+      </c>
+      <c r="G85" s="9">
+        <v>6240.0</v>
+      </c>
+      <c r="H85" s="9">
+        <v>30750.0</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J85" s="12"/>
+    </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="A86" s="4">
+        <v>46238.0</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D86" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F86" s="9">
+        <v>5040.0</v>
+      </c>
+      <c r="G86" s="9">
+        <v>720.0</v>
+      </c>
+      <c r="H86" s="9">
+        <v>4680.0</v>
+      </c>
+      <c r="I86" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J86" s="12"/>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="4">
+        <v>46238.0</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F87" s="9">
+        <v>124423.0</v>
+      </c>
+      <c r="G87" s="9">
+        <v>60002.0</v>
+      </c>
+      <c r="H87" s="9">
+        <v>69217.0</v>
+      </c>
+      <c r="I87" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="88">
       <c r="I88" s="20"/>
@@ -6184,13 +6297,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I83">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I87">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I84:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I88:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A83">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A87">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -6253,18 +6366,18 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>46224.0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="C2" s="8"/>
       <c r="D2" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="9">
         <v>333.0</v>
@@ -6283,13 +6396,13 @@
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>46224.0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="8"/>
       <c r="D3" s="9">
         <v>2114158.0</v>
       </c>
@@ -6313,18 +6426,18 @@
       </c>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>46225.0</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="9">
         <v>10501.0</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="9">
         <v>415093.0</v>
@@ -6343,11 +6456,11 @@
       </c>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>46225.0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="9">
@@ -6369,11 +6482,11 @@
         <v>15</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>46225.0</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -6384,7 +6497,7 @@
         <v>112268.0</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F6" s="9">
         <v>3000.0</v>
@@ -6403,18 +6516,18 @@
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>46225.0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="9">
         <v>132357.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" s="9">
         <v>1560.0</v>
@@ -6429,11 +6542,11 @@
         <v>15</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>46225.0</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -6444,7 +6557,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" s="9">
         <v>720.0</v>
@@ -6459,22 +6572,22 @@
         <v>15</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>46225.0</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="9">
         <v>3712.0</v>
@@ -6489,11 +6602,11 @@
         <v>15</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>46226.0</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -6504,7 +6617,7 @@
         <v>73001.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F10" s="9">
         <v>73787.0</v>
@@ -6519,11 +6632,11 @@
         <v>15</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>46226.0</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -6534,7 +6647,7 @@
         <v>112268.0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F11" s="9">
         <v>3300.0</v>
@@ -6551,7 +6664,7 @@
       <c r="J11" s="12"/>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>46226.0</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -6579,18 +6692,18 @@
       <c r="J12" s="12"/>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>46226.0</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" s="9">
         <v>379471.0</v>
@@ -6605,11 +6718,11 @@
         <v>15</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>46227.0</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -6635,11 +6748,11 @@
         <v>15</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>46227.0</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -6669,7 +6782,7 @@
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <v>46227.0</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -6697,7 +6810,7 @@
       <c r="J16" s="12"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>46227.0</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -6708,7 +6821,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="9">
         <v>720.0</v>
@@ -6725,7 +6838,7 @@
       <c r="J17" s="12"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <v>46227.0</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -6736,7 +6849,7 @@
         <v>112268.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F18" s="9">
         <v>3300.0</v>
@@ -6751,22 +6864,22 @@
         <v>15</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
+      <c r="A19" s="4">
         <v>46230.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="9">
         <v>2410401.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F19" s="9">
         <v>136538.0</v>
@@ -6781,22 +6894,22 @@
         <v>15</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
+      <c r="A20" s="4">
         <v>46231.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20" s="9">
         <v>591750.0</v>
@@ -6811,22 +6924,22 @@
         <v>15</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
+      <c r="A21" s="4">
         <v>46231.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="9">
         <v>10601.0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F21" s="9">
         <v>1230.0</v>
@@ -6841,11 +6954,11 @@
         <v>15</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" hidden="1" customHeight="1">
+      <c r="A22" s="4">
         <v>46231.0</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -6856,7 +6969,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F22" s="9">
         <v>4320.0</v>
@@ -6872,8 +6985,8 @@
       </c>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="5">
+    <row r="23" ht="22.5" hidden="1" customHeight="1">
+      <c r="A23" s="4">
         <v>46231.0</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -6884,7 +6997,7 @@
         <v>114357.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F23" s="9">
         <v>240.0</v>
@@ -6901,18 +7014,18 @@
       <c r="J23" s="12"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="5">
+      <c r="A24" s="4">
         <v>46232.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="9">
         <v>10501.0</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="9">
         <v>19663.0</v>
@@ -6929,7 +7042,7 @@
       <c r="J24" s="12"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <v>46232.0</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -6940,7 +7053,7 @@
         <v>112268.0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F25" s="9">
         <v>5700.0</v>
@@ -6957,7 +7070,7 @@
       <c r="J25" s="12"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="5">
+      <c r="A26" s="4">
         <v>46232.0</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -6968,7 +7081,7 @@
         <v>2110317.0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F26" s="9">
         <v>720.0</v>
@@ -6985,7 +7098,7 @@
       <c r="J26" s="12"/>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="5">
+      <c r="A27" s="4">
         <v>46232.0</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -6996,7 +7109,7 @@
         <v>2114357.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F27" s="9">
         <v>432.0</v>
@@ -7013,18 +7126,18 @@
       <c r="J27" s="12"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="5">
+      <c r="A28" s="4">
         <v>46232.0</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="9">
         <v>10501.0</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F28" s="9">
         <v>219540.0</v>
@@ -7040,8 +7153,8 @@
       </c>
       <c r="J28" s="12"/>
     </row>
-    <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="5">
+    <row r="29" ht="22.5" hidden="1" customHeight="1">
+      <c r="A29" s="4">
         <v>46233.0</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -7052,7 +7165,7 @@
         <v>112268.0</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F29" s="9">
         <v>5100.0</v>
@@ -7064,12 +7177,12 @@
         <v>4800.0</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J29" s="12"/>
     </row>
-    <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="5">
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
+      <c r="A30" s="4">
         <v>46233.0</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -7080,7 +7193,7 @@
         <v>114357.0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F30" s="9">
         <v>240.0</v>
@@ -7092,23 +7205,23 @@
         <v>1560.0</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="5">
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="4">
         <v>46233.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="9">
         <v>10601.0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F31" s="9">
         <v>7717.0</v>
@@ -7123,22 +7236,22 @@
         <v>15</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
+      <c r="A32" s="4">
         <v>46234.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="9">
         <v>79110.0</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F32" s="9">
         <v>48000.0</v>
@@ -7152,23 +7265,23 @@
       <c r="I32" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="5">
+      <c r="J32" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
+      <c r="A33" s="4">
         <v>46234.0</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="9">
         <v>10501.0</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F33" s="9">
         <v>95574.0</v>
@@ -7182,12 +7295,12 @@
       <c r="I33" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J33" s="18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="5">
+      <c r="J33" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
+      <c r="A34" s="4">
         <v>46234.0</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -7198,7 +7311,7 @@
         <v>73001.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F34" s="9">
         <v>73367.0</v>
@@ -7214,8 +7327,8 @@
       </c>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="5">
+    <row r="35" ht="22.5" hidden="1" customHeight="1">
+      <c r="A35" s="4">
         <v>46234.0</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -7226,7 +7339,7 @@
         <v>112357.0</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F35" s="9">
         <v>840.0</v>
@@ -7243,7 +7356,7 @@
       <c r="J35" s="12"/>
     </row>
     <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="19">
+      <c r="A36" s="18">
         <v>46237.0</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -7254,7 +7367,7 @@
         <v>10601.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F36" s="9">
         <v>17934.0</v>
@@ -7269,11 +7382,11 @@
         <v>15</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="19">
+      <c r="A37" s="18">
         <v>46237.0</v>
       </c>
       <c r="B37" s="6" t="s">
@@ -7284,7 +7397,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F37" s="9">
         <v>194520.0</v>
@@ -7301,7 +7414,7 @@
       <c r="J37" s="12"/>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="19">
+      <c r="A38" s="18">
         <v>46237.0</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -7312,7 +7425,7 @@
         <v>114379.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F38" s="9">
         <v>52200.0</v>
@@ -7324,12 +7437,12 @@
         <v>7500.0</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J38" s="12"/>
     </row>
     <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="19">
+      <c r="A39" s="18">
         <v>46237.0</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -7340,7 +7453,7 @@
         <v>2110317.0</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F39" s="9">
         <v>6450.0</v>
@@ -7357,7 +7470,7 @@
       <c r="J39" s="12"/>
     </row>
     <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="19">
+      <c r="A40" s="18">
         <v>46237.0</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -7368,7 +7481,7 @@
         <v>2010102.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F40" s="9">
         <v>1398.0</v>
@@ -7384,17 +7497,115 @@
       </c>
       <c r="J40" s="12"/>
     </row>
-    <row r="41">
-      <c r="I41" s="20"/>
-    </row>
-    <row r="42">
-      <c r="I42" s="20"/>
-    </row>
-    <row r="43">
-      <c r="I43" s="20"/>
-    </row>
-    <row r="44">
-      <c r="I44" s="20"/>
+    <row r="41" ht="22.5" customHeight="1">
+      <c r="A41" s="4">
+        <v>46238.0</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="14"/>
+      <c r="D41" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="9">
+        <v>2460.0</v>
+      </c>
+      <c r="G41" s="9">
+        <v>17640.0</v>
+      </c>
+      <c r="H41" s="9">
+        <v>3240.0</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="12"/>
+    </row>
+    <row r="42" ht="22.5" customHeight="1">
+      <c r="A42" s="4">
+        <v>46238.0</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="14"/>
+      <c r="D42" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" s="9">
+        <v>3600.0</v>
+      </c>
+      <c r="G42" s="9">
+        <v>1500.0</v>
+      </c>
+      <c r="H42" s="9">
+        <v>3900.0</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" s="12"/>
+    </row>
+    <row r="43" ht="22.5" customHeight="1">
+      <c r="A43" s="4">
+        <v>46238.0</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="14"/>
+      <c r="D43" s="9">
+        <v>114379.0</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" s="9">
+        <v>7500.0</v>
+      </c>
+      <c r="G43" s="9">
+        <v>54900.0</v>
+      </c>
+      <c r="H43" s="9">
+        <v>8400.0</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" s="12"/>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="4">
+        <v>46238.0</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="14"/>
+      <c r="D44" s="9">
+        <v>114357.0</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F44" s="9">
+        <v>240.0</v>
+      </c>
+      <c r="G44" s="9">
+        <v>7680.0</v>
+      </c>
+      <c r="H44" s="9">
+        <v>360.0</v>
+      </c>
+      <c r="I44" s="10"/>
+      <c r="J44" s="12"/>
     </row>
     <row r="45">
       <c r="I45" s="20"/>
@@ -10146,13 +10357,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I40">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I44">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I41:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I45:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A40">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A44">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="131">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -53,21 +53,21 @@
     <t>Daniel Castro</t>
   </si>
   <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t>7. Otro</t>
   </si>
   <si>
+    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
+  </si>
+  <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
-    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
-  </si>
-  <si>
     <t>LANZA</t>
   </si>
   <si>
@@ -83,105 +83,105 @@
     <t>6. Transformación De Referencias</t>
   </si>
   <si>
+    <t>3. Falla De Rotación</t>
+  </si>
+  <si>
     <t>Pendiente Transformar Roto GT Por manipulación</t>
   </si>
   <si>
-    <t>3. Falla De Rotación</t>
+    <t>TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>FABIO GOMEZ</t>
   </si>
   <si>
     <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
-    <t>TAT MEDELLIN</t>
-  </si>
-  <si>
-    <t>FABIO GOMEZ</t>
-  </si>
-  <si>
     <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
   </si>
   <si>
     <t>se equivocaron al cargar una estiba</t>
   </si>
   <si>
+    <t>TAT CARTAGENA</t>
+  </si>
+  <si>
     <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
-    <t>TAT CARTAGENA</t>
+    <t>Dilan Barraza</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
     <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
   </si>
   <si>
-    <t>Dilan Barraza</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+    <t>4. Exigencia Del Cliente (Edad)</t>
+  </si>
+  <si>
+    <t>Venta FS</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
-    <t>4. Exigencia Del Cliente (Edad)</t>
-  </si>
-  <si>
-    <t>Venta FS</t>
-  </si>
-  <si>
     <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
   </si>
   <si>
+    <t>Se dejó lote para revisión por calidad</t>
+  </si>
+  <si>
     <t>PALMAS</t>
   </si>
   <si>
     <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
-    <t>Se dejó lote para revisión por calidad</t>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
     <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
+    <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
     <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+  </si>
+  <si>
     <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
-    <t>Se envía más fresco a Rionegro</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
+    <t>TAT CALI</t>
+  </si>
+  <si>
+    <t>DIEGO ROJAS</t>
+  </si>
+  <si>
     <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
   </si>
   <si>
-    <t>TAT CALI</t>
-  </si>
-  <si>
-    <t>DIEGO ROJAS</t>
+    <t>TAT CUCUTA</t>
   </si>
   <si>
     <t>HUEVO PICADO ROJO</t>
   </si>
   <si>
+    <t>ALEXANDER PEÑA</t>
+  </si>
+  <si>
     <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
-    <t>TAT CUCUTA</t>
-  </si>
-  <si>
-    <t>ALEXANDER PEÑA</t>
-  </si>
-  <si>
     <t>Clientes FS</t>
   </si>
   <si>
@@ -194,18 +194,18 @@
     <t>Transformación de PET</t>
   </si>
   <si>
+    <t>ANDRES MEJIA</t>
+  </si>
+  <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
   </si>
   <si>
-    <t>ANDRES MEJIA</t>
+    <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
   </si>
   <si>
     <t>Esta para despacho hoy</t>
   </si>
   <si>
-    <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
-  </si>
-  <si>
     <t>TAT POPAYAN</t>
   </si>
   <si>
@@ -218,12 +218,12 @@
     <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
   </si>
   <si>
+    <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
+  </si>
+  <si>
     <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
   </si>
   <si>
-    <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
-  </si>
-  <si>
     <t>HUEVO CX30 CARTON GRIS</t>
   </si>
   <si>
@@ -263,42 +263,48 @@
     <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
   </si>
   <si>
+    <t>HUEVO ROTO - ZF</t>
+  </si>
+  <si>
+    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
+  </si>
+  <si>
     <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
-    <t>HUEVO ROTO - ZF</t>
-  </si>
-  <si>
-    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
-  </si>
-  <si>
     <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
   </si>
   <si>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
+  </si>
+  <si>
     <t>TAT PASTO</t>
   </si>
   <si>
     <t>CAROLINA VITERI</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
     <t>Cargo en incubación</t>
   </si>
   <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
     <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
     <t>Pedido para villavicencio</t>
   </si>
   <si>
     <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
+    <t>BELLAVISTA</t>
+  </si>
+  <si>
+    <t>Traslado a cedi, producto de devolución</t>
+  </si>
+  <si>
     <t>Inventario de Asesor de Rionegro que renuncio</t>
   </si>
   <si>
@@ -308,12 +314,21 @@
     <t>Jhonatan Gomez</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CANASTA</t>
+  </si>
+  <si>
     <t>Lote mezclado en la misma estiba</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
     <t>Supera edad solicitada clientes grandes superficies</t>
   </si>
   <si>
+    <t>HUEVO SUCIO ZF MARCADO</t>
+  </si>
+  <si>
     <t>Pedido para villacicencio</t>
   </si>
   <si>
@@ -387,6 +402,9 @@
   </si>
   <si>
     <t>Se envía huevo más fresco para clientes FS</t>
+  </si>
+  <si>
+    <t>Producto enviado a Rionegro y para FS más fresco</t>
   </si>
 </sst>
 </file>
@@ -426,14 +444,14 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -466,52 +484,52 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -604,7 +622,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J87" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J89" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -622,7 +640,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J44" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J53" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -885,273 +903,273 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>46204.0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="9">
+      <c r="E2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="8">
         <v>359100.0</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <v>83486.0</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="8">
         <v>206140.0</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>16</v>
+      <c r="I2" s="12" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
       <c r="A3" s="4">
         <v>46205.0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="9">
+      <c r="E3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="8">
         <v>298282.0</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>42201.0</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>260675.0</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
       <c r="A4" s="4">
         <v>46205.0</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>2110217.0</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>21120.0</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <v>11039.0</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>16920.0</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="8"/>
+        <v>17</v>
+      </c>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
       <c r="A5" s="4">
         <v>46205.0</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>75680.0</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>5640.0</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>3134.0</v>
       </c>
       <c r="I5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
       <c r="A6" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="E6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8">
         <v>189540.0</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>161685.0</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>144720.0</v>
       </c>
       <c r="I6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>41</v>
+      <c r="J6" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
       <c r="A7" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>2010102.0</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="E7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="8">
         <v>20640.0</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>3761.0</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>13920.0</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>46</v>
+        <v>35</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
       <c r="A8" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>152384.0</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="9">
+      <c r="E8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="8">
         <v>14700.0</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>6435.0</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>9600.0</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="12"/>
+      <c r="J8" s="11"/>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
       <c r="A9" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="9">
+      <c r="E9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="8">
         <v>228240.0</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>77306.0</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>124260.0</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="12"/>
+      <c r="J9" s="11"/>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
       <c r="A10" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>2152388.0</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="9">
+      <c r="E10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="8">
         <v>7830.0</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>1980.0</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>6030.0</v>
       </c>
       <c r="I10" s="13" t="s">
@@ -1163,31 +1181,31 @@
       <c r="A11" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="9">
+      <c r="E11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="8">
         <v>31680.0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>5526.0</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>23040.0</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1195,31 +1213,31 @@
       <c r="A12" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="9">
+      <c r="E12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="8">
         <v>51387.0</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <v>10827.0</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <v>12170.0</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="11" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1227,31 +1245,31 @@
       <c r="A13" s="4">
         <v>46209.0</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="9">
+      <c r="E13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="8">
         <v>195810.0</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>93809.0</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>133410.0</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1259,31 +1277,31 @@
       <c r="A14" s="4">
         <v>46209.0</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="9">
+      <c r="B14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="9">
+      <c r="E14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="8">
         <v>526002.0</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <v>301965.0</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <v>424588.0</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="11" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1291,215 +1309,215 @@
       <c r="A15" s="4">
         <v>46209.0</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="9">
+      <c r="B15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="8">
         <v>2010102.0</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="9">
+      <c r="E15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="8">
         <v>14160.0</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <v>6692.0</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>12360.0</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>63</v>
+      <c r="J15" s="11" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
       <c r="A16" s="4">
         <v>46210.0</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="9">
+      <c r="E16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="8">
         <v>149040.0</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <v>119573.0</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <v>289680.0</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J16" s="11"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
       <c r="A17" s="4">
         <v>46210.0</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>2110217.0</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="8">
         <v>22770.0</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <v>3926.0</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <v>19770.0</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J17" s="11"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
       <c r="A18" s="4">
         <v>46210.0</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="9">
+      <c r="E18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="8">
         <v>222021.0</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="8">
         <v>61385.0</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>162125.0</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J18" s="11"/>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
       <c r="A19" s="4">
         <v>46211.0</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="9">
+      <c r="B19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="9">
+      <c r="E19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="8">
         <v>495833.0</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>148815.0</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <v>401280.0</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="12" t="s">
-        <v>69</v>
+      <c r="J19" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
       <c r="A20" s="4">
         <v>46211.0</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="9">
+      <c r="E20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="8">
         <v>139920.0</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>54384.0</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <v>74040.0</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J20" s="11"/>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
       <c r="A21" s="4">
         <v>46211.0</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="9">
+      <c r="E21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="8">
         <v>162125.0</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>60138.0</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>100687.0</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="11" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1507,151 +1525,151 @@
       <c r="A22" s="4">
         <v>46211.0</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>152384.0</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="9">
+      <c r="E22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="8">
         <v>32850.0</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="8">
         <v>7065.0</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="8">
         <v>32700.0</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J22" s="12"/>
+        <v>35</v>
+      </c>
+      <c r="J22" s="11"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
       <c r="A23" s="4">
         <v>46211.0</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="B23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="8">
         <v>112271.0</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="8">
         <v>16500.0</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="8">
         <v>5310.0</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="8">
         <v>18000.0</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J23" s="12"/>
+      <c r="J23" s="11"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
       <c r="A24" s="4">
         <v>46212.0</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="9">
+      <c r="E24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="8">
         <v>190047.0</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="8">
         <v>59822.0</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="8">
         <v>248481.0</v>
       </c>
       <c r="I24" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J24" s="12"/>
+      <c r="J24" s="11"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
       <c r="A25" s="4">
         <v>46212.0</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>26</v>
+      <c r="B25" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="9">
+        <v>60</v>
+      </c>
+      <c r="D25" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="9">
+      <c r="E25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="8">
         <v>178080.0</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="8">
         <v>47784.0</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="8">
         <v>203520.0</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="11"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
       <c r="A26" s="4">
         <v>46212.0</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>26</v>
+      <c r="B26" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="9">
+        <v>60</v>
+      </c>
+      <c r="D26" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="9">
+      <c r="E26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="8">
         <v>10320.0</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="8">
         <v>5869.0</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="8">
         <v>13200.0</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J26" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="11" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1659,61 +1677,61 @@
       <c r="A27" s="4">
         <v>46212.0</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>26</v>
+      <c r="B27" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="9">
+        <v>60</v>
+      </c>
+      <c r="D27" s="8">
         <v>112271.0</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="8">
         <v>18000.0</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="8">
         <v>4485.0</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="8">
         <v>13500.0</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J27" s="11"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
       <c r="A28" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="9">
+      <c r="E28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="8">
         <v>208440.0</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="8">
         <v>85608.0</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="8">
         <v>150833.0</v>
       </c>
       <c r="I28" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="11" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1721,31 +1739,31 @@
       <c r="A29" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="9">
+      <c r="E29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="8">
         <v>962820.0</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="8">
         <v>80644.0</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="8">
         <v>922140.0</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="11" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1753,245 +1771,245 @@
       <c r="A30" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>26</v>
+      <c r="B30" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" s="9">
+        <v>60</v>
+      </c>
+      <c r="D30" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="9">
+      <c r="E30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="8">
         <v>335340.0</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="8">
         <v>111433.0</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="8">
         <v>381600.0</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>83</v>
+        <v>35</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
       <c r="A31" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="9">
+      <c r="E31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="8">
         <v>316800.0</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="8">
         <v>99546.0</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="8">
         <v>229680.0</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J31" s="11"/>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
       <c r="A32" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="9">
+      <c r="E32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="8">
         <v>176850.0</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="8">
         <v>47499.0</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="8">
         <v>128971.0</v>
       </c>
       <c r="I32" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J32" s="12"/>
+      <c r="J32" s="11"/>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
       <c r="A33" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="9">
+      <c r="E33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="8">
         <v>58080.0</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="8">
         <v>20865.0</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="8">
         <v>25440.0</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J33" s="11"/>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
       <c r="A34" s="4">
         <v>46217.0</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="7" t="s">
+      <c r="B34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="9">
+      <c r="C34" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="9">
+      <c r="E34" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="8">
         <v>481440.0</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="8">
         <v>464517.0</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="8">
         <v>151435.0</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J34" s="11"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
       <c r="A35" s="4">
         <v>46217.0</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="9">
+      <c r="D35" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="9">
+      <c r="E35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="8">
         <v>355720.0</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="8">
         <v>342811.0</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="8">
         <v>302760.0</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J35" s="11"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
       <c r="A36" s="4">
         <v>46217.0</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="8">
         <v>2010102.0</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" s="9">
+      <c r="E36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="8">
         <v>35280.0</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="8">
         <v>16988.0</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="8">
         <v>37926.0</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>91</v>
+        <v>23</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
       <c r="A37" s="19">
         <v>46218.0</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="9">
+      <c r="E37" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="8">
         <v>272073.0</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="8">
         <v>76546.0</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="8">
         <v>275205.0</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J37" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J37" s="11" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1999,63 +2017,63 @@
       <c r="A38" s="19">
         <v>46218.0</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>2010102.0</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="9">
+      <c r="E38" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="8">
         <v>37926.0</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="8">
         <v>5633.0</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="8">
         <v>25746.0</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>91</v>
+        <v>23</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
       <c r="A39" s="19">
         <v>46218.0</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="9">
+      <c r="D39" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="9">
+      <c r="E39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="8">
         <v>20640.0</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="8">
         <v>4951.0</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="8">
         <v>16320.0</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J39" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J39" s="11" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2063,1483 +2081,1539 @@
       <c r="A40" s="19">
         <v>46218.0</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" s="9">
+      <c r="D40" s="8">
         <v>2110317.0</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="8">
         <v>10980.0</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="8">
         <v>2379.0</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="8">
         <v>13500.0</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J40" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J40" s="11"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
       <c r="A41" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" s="9">
+      <c r="D41" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="9">
+      <c r="E41" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F41" s="8">
         <v>130320.0</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="8">
         <v>47410.0</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="8">
         <v>90480.0</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J41" s="12" t="s">
-        <v>95</v>
+      <c r="J41" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
       <c r="A42" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>96</v>
+      <c r="B42" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D42" s="9">
+        <v>99</v>
+      </c>
+      <c r="D42" s="8">
         <v>2152388.0</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="9">
+      <c r="E42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42" s="8">
         <v>36225.0</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="8">
         <v>11746.0</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="8">
         <v>27570.0</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J42" s="11"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
       <c r="A43" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="9">
+      <c r="D43" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F43" s="9">
+      <c r="E43" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="8">
         <v>152833.0</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="8">
         <v>50641.0</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="8">
         <v>96472.0</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J43" s="12" t="s">
-        <v>98</v>
+      <c r="J43" s="11" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
       <c r="A44" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>87</v>
+      <c r="B44" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" s="9">
+        <v>89</v>
+      </c>
+      <c r="D44" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F44" s="9">
+      <c r="E44" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="8">
         <v>237828.0</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="8">
         <v>173585.0</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="8">
         <v>71560.0</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J44" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J44" s="11"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
       <c r="A45" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="8">
         <v>152384.0</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F45" s="9">
+      <c r="E45" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F45" s="8">
         <v>31125.0</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="8">
         <v>7815.0</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="8">
         <v>31845.0</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>99</v>
+        <v>35</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
       <c r="A46" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="8">
         <v>2010102.0</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F46" s="9">
+      <c r="E46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="8">
         <v>25746.0</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="8">
         <v>6168.0</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="8">
         <v>28683.0</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J46" s="12" t="s">
-        <v>91</v>
+        <v>23</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
       <c r="A47" s="4">
         <v>46220.0</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F47" s="9">
+      <c r="E47" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="8">
         <v>261166.0</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="8">
         <v>74573.0</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="8">
         <v>221549.0</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
       <c r="A48" s="4">
         <v>46220.0</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="8">
         <v>2110217.0</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="8">
         <v>115289.0</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="8">
         <v>26931.0</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="8">
         <v>119584.0</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J48" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J48" s="11"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
       <c r="A49" s="4">
         <v>46224.0</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" s="9">
+      <c r="E49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="8">
         <v>398570.0</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="8">
         <v>288226.0</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="8">
         <v>287235.0</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>101</v>
+        <v>35</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
       <c r="A50" s="4">
         <v>46224.0</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>96</v>
+      <c r="B50" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" s="9">
+        <v>99</v>
+      </c>
+      <c r="D50" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F50" s="9">
+      <c r="E50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="8">
         <v>745107.0</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="8">
         <v>378927.0</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="8">
         <v>551645.0</v>
       </c>
       <c r="I50" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J50" s="12" t="s">
-        <v>102</v>
+      <c r="J50" s="11" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
       <c r="A51" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" s="9">
+      <c r="B51" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F51" s="9">
+      <c r="E51" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" s="8">
         <v>130560.0</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="8">
         <v>52658.0</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="8">
         <v>153840.0</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J51" s="12" t="s">
-        <v>103</v>
+      <c r="J51" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
       <c r="A52" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C52" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D52" s="9">
+      <c r="D52" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F52" s="9">
+      <c r="E52" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="8">
         <v>87447.0</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="8">
         <v>59056.0</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="8">
         <v>104365.0</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J52" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J52" s="11"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
       <c r="A53" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" s="9">
+      <c r="E53" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="8">
         <v>25200.0</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="8">
         <v>2085.0</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="8">
         <v>25920.0</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>104</v>
+        <v>23</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
       <c r="A54" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D54" s="9">
+      <c r="B54" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="9">
+      <c r="E54" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="8">
         <v>285405.0</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="8">
         <v>203180.0</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54" s="8">
         <v>226069.0</v>
       </c>
       <c r="I54" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J54" s="12" t="s">
-        <v>106</v>
+      <c r="J54" s="11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
       <c r="A55" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B55" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D55" s="9">
+      <c r="B55" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="9">
+      <c r="E55" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="8">
         <v>692280.0</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="8">
         <v>118381.0</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H55" s="8">
         <v>700200.0</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J55" s="12"/>
+      <c r="J55" s="11"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
       <c r="A56" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D56" s="9">
+      <c r="B56" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="9">
+      <c r="E56" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" s="8">
         <v>700200.0</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="8">
         <v>112628.0</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56" s="8">
         <v>668440.0</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J56" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J56" s="11"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
       <c r="A57" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B57" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D57" s="9">
+      <c r="B57" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D57" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F57" s="9">
+      <c r="E57" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="8">
         <v>226069.0</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="8">
         <v>193130.0</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57" s="8">
         <v>326391.0</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J57" s="12" t="s">
-        <v>107</v>
+      <c r="J57" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
       <c r="A58" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D58" s="9">
+      <c r="D58" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="9">
+      <c r="E58" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="8">
         <v>144637.0</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58" s="8">
         <v>64227.0</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58" s="8">
         <v>128160.0</v>
       </c>
       <c r="I58" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J58" s="12"/>
+      <c r="J58" s="11"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
       <c r="A59" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B59" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D59" s="9">
+      <c r="B59" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D59" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F59" s="9">
+      <c r="E59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="8">
         <v>295359.0</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G59" s="8">
         <v>126369.0</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H59" s="8">
         <v>166642.0</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J59" s="12" t="s">
-        <v>108</v>
+      <c r="J59" s="11" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
       <c r="A60" s="4">
         <v>46230.0</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D60" s="9">
+      <c r="B60" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D60" s="8">
         <v>2110403.0</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F60" s="9">
+      <c r="E60" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F60" s="8">
         <v>9960.0</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="8">
         <v>6018.0</v>
       </c>
-      <c r="H60" s="9">
+      <c r="H60" s="8">
         <v>3660.0</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J60" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J60" s="11"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
       <c r="A61" s="4">
         <v>46230.0</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C61" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F61" s="9">
+      <c r="E61" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" s="8">
         <v>306720.0</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G61" s="8">
         <v>164175.0</v>
       </c>
-      <c r="H61" s="9">
+      <c r="H61" s="8">
         <v>247096.0</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J61" s="12"/>
-    </row>
-    <row r="62" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J61" s="11"/>
+    </row>
+    <row r="62" ht="22.5" hidden="1" customHeight="1">
       <c r="A62" s="4">
         <v>46230.0</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C62" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D62" s="9">
+      <c r="D62" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="9">
+      <c r="E62" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" s="8">
         <v>437080.0</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62" s="8">
         <v>277785.0</v>
       </c>
-      <c r="H62" s="9">
+      <c r="H62" s="8">
         <v>353700.0</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J62" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="63" ht="22.5" customHeight="1">
+        <v>35</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="63" ht="22.5" hidden="1" customHeight="1">
       <c r="A63" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D63" s="9">
+      <c r="D63" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" s="9">
+      <c r="E63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="8">
         <v>165466.0</v>
       </c>
-      <c r="G63" s="9">
+      <c r="G63" s="8">
         <v>113462.0</v>
       </c>
-      <c r="H63" s="9">
+      <c r="H63" s="8">
         <v>375549.0</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="64" ht="22.5" customHeight="1">
+        <v>35</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="64" ht="22.5" hidden="1" customHeight="1">
       <c r="A64" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C64" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D64" s="9">
+      <c r="D64" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F64" s="9">
+      <c r="E64" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F64" s="8">
         <v>238497.0</v>
       </c>
-      <c r="G64" s="9">
+      <c r="G64" s="8">
         <v>56526.0</v>
       </c>
-      <c r="H64" s="9">
+      <c r="H64" s="8">
         <v>181858.0</v>
       </c>
       <c r="I64" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J64" s="12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="65" ht="22.5" customHeight="1">
+      <c r="J64" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="65" ht="22.5" hidden="1" customHeight="1">
       <c r="A65" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C65" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C65" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D65" s="9">
+      <c r="D65" s="8">
         <v>2110317.0</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F65" s="9">
+      <c r="F65" s="8">
         <v>8190.0</v>
       </c>
-      <c r="G65" s="9">
+      <c r="G65" s="8">
         <v>2049.0</v>
       </c>
-      <c r="H65" s="9">
+      <c r="H65" s="8">
         <v>7200.0</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J65" s="12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="66" ht="22.5" customHeight="1">
+      <c r="J65" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="66" ht="22.5" hidden="1" customHeight="1">
       <c r="A66" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C66" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C66" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D66" s="9">
+      <c r="D66" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="9">
+      <c r="E66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" s="8">
         <v>146224.0</v>
       </c>
-      <c r="G66" s="9">
+      <c r="G66" s="8">
         <v>78064.0</v>
       </c>
-      <c r="H66" s="9">
+      <c r="H66" s="8">
         <v>98850.0</v>
       </c>
       <c r="I66" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J66" s="12" t="s">
-        <v>112</v>
+      <c r="J66" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
       <c r="A67" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>113</v>
+      <c r="B67" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="C67" s="21"/>
-      <c r="D67" s="9">
+      <c r="D67" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="9">
+      <c r="E67" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" s="8">
         <v>14599.0</v>
       </c>
-      <c r="G67" s="9">
+      <c r="G67" s="8">
         <v>3782.0</v>
       </c>
-      <c r="H67" s="9">
+      <c r="H67" s="8">
         <v>7263.0</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J67" s="12"/>
+      <c r="J67" s="11"/>
     </row>
     <row r="68" ht="22.5" hidden="1" customHeight="1">
       <c r="A68" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B68" s="6" t="s">
-        <v>26</v>
+      <c r="B68" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C68" s="21"/>
-      <c r="D68" s="9">
+      <c r="D68" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F68" s="9">
+      <c r="E68" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="8">
         <v>22080.0</v>
       </c>
-      <c r="G68" s="9">
+      <c r="G68" s="8">
         <v>5686.0</v>
       </c>
-      <c r="H68" s="9">
+      <c r="H68" s="8">
         <v>36720.0</v>
       </c>
       <c r="I68" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J68" s="12"/>
+      <c r="J68" s="11"/>
     </row>
     <row r="69" ht="22.5" hidden="1" customHeight="1">
       <c r="A69" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>31</v>
+      <c r="B69" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C69" s="21"/>
-      <c r="D69" s="9">
+      <c r="D69" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F69" s="9">
+      <c r="E69" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="8">
         <v>353905.0</v>
       </c>
-      <c r="G69" s="9">
+      <c r="G69" s="8">
         <v>208296.0</v>
       </c>
-      <c r="H69" s="9">
+      <c r="H69" s="8">
         <v>117570.0</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J69" s="12"/>
+      <c r="J69" s="11"/>
     </row>
     <row r="70" ht="22.5" hidden="1" customHeight="1">
       <c r="A70" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B70" s="6" t="s">
-        <v>50</v>
+      <c r="B70" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C70" s="21"/>
-      <c r="D70" s="9">
+      <c r="D70" s="8">
         <v>2010102.0</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F70" s="9">
+      <c r="E70" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" s="8">
         <v>5913.0</v>
       </c>
-      <c r="G70" s="9">
+      <c r="G70" s="8">
         <v>902.0</v>
       </c>
-      <c r="H70" s="9">
+      <c r="H70" s="8">
         <v>5893.0</v>
       </c>
       <c r="I70" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J70" s="12"/>
+      <c r="J70" s="11"/>
     </row>
     <row r="71" ht="22.5" hidden="1" customHeight="1">
       <c r="A71" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="21"/>
-      <c r="D71" s="9">
+      <c r="D71" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F71" s="9">
+      <c r="E71" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71" s="8">
         <v>256613.0</v>
       </c>
-      <c r="G71" s="9">
+      <c r="G71" s="8">
         <v>86092.0</v>
       </c>
-      <c r="H71" s="9">
+      <c r="H71" s="8">
         <v>142320.0</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J71" s="12"/>
+      <c r="J71" s="11"/>
     </row>
     <row r="72" ht="22.5" hidden="1" customHeight="1">
       <c r="A72" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="21"/>
-      <c r="D72" s="9">
+      <c r="D72" s="8">
         <v>152384.0</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F72" s="9">
+      <c r="E72" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F72" s="8">
         <v>21300.0</v>
       </c>
-      <c r="G72" s="9">
+      <c r="G72" s="8">
         <v>9765.0</v>
       </c>
-      <c r="H72" s="9">
+      <c r="H72" s="8">
         <v>18690.0</v>
       </c>
       <c r="I72" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J72" s="12"/>
+      <c r="J72" s="11"/>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
       <c r="A73" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B73" s="6" t="s">
-        <v>96</v>
+      <c r="B73" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="C73" s="21"/>
-      <c r="D73" s="9">
+      <c r="D73" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="9">
+      <c r="E73" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="8">
         <v>351733.0</v>
       </c>
-      <c r="G73" s="9">
+      <c r="G73" s="8">
         <v>145994.0</v>
       </c>
-      <c r="H73" s="9">
+      <c r="H73" s="8">
         <v>200114.0</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J73" s="12"/>
-    </row>
-    <row r="74" ht="22.5" customHeight="1">
+      <c r="J73" s="11"/>
+    </row>
+    <row r="74" ht="22.5" hidden="1" customHeight="1">
       <c r="A74" s="19">
         <v>46233.0</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C74" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C74" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D74" s="9">
+      <c r="D74" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F74" s="9">
+      <c r="E74" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F74" s="8">
         <v>158761.0</v>
       </c>
-      <c r="G74" s="9">
+      <c r="G74" s="8">
         <v>68908.0</v>
       </c>
-      <c r="H74" s="9">
+      <c r="H74" s="8">
         <v>183014.0</v>
       </c>
       <c r="I74" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J74" s="12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="75" ht="22.5" customHeight="1">
+      <c r="J74" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="75" ht="22.5" hidden="1" customHeight="1">
       <c r="A75" s="19">
         <v>46233.0</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C75" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C75" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D75" s="9">
+      <c r="D75" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F75" s="9">
+      <c r="E75" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F75" s="8">
         <v>117430.0</v>
       </c>
-      <c r="G75" s="9">
+      <c r="G75" s="8">
         <v>57323.0</v>
       </c>
-      <c r="H75" s="9">
+      <c r="H75" s="8">
         <v>86643.0</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J75" s="12"/>
-    </row>
-    <row r="76" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J75" s="11"/>
+    </row>
+    <row r="76" ht="22.5" hidden="1" customHeight="1">
       <c r="A76" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F76" s="9">
+      <c r="E76" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F76" s="8">
         <v>265693.0</v>
       </c>
-      <c r="G76" s="9">
+      <c r="G76" s="8">
         <v>83477.0</v>
       </c>
-      <c r="H76" s="9">
+      <c r="H76" s="8">
         <v>116000.0</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J76" s="12"/>
-    </row>
-    <row r="77" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J76" s="11"/>
+    </row>
+    <row r="77" ht="22.5" hidden="1" customHeight="1">
       <c r="A77" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B77" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D77" s="9">
+      <c r="B77" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D77" s="8">
         <v>112357.0</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F77" s="9">
+      <c r="E77" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F77" s="8">
         <v>720.0</v>
       </c>
-      <c r="G77" s="9">
+      <c r="G77" s="8">
         <v>360.0</v>
       </c>
-      <c r="H77" s="9">
+      <c r="H77" s="8">
         <v>2040.0</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J77" s="12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="78" ht="22.5" customHeight="1">
+      <c r="J77" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="78" ht="22.5" hidden="1" customHeight="1">
       <c r="A78" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C78" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D78" s="9">
+      <c r="D78" s="8">
         <v>2110317.0</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="E78" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78" s="8">
         <v>5580.0</v>
       </c>
-      <c r="G78" s="9">
+      <c r="G78" s="8">
         <v>2192.0</v>
       </c>
-      <c r="H78" s="9">
+      <c r="H78" s="8">
         <v>3984.0</v>
       </c>
       <c r="I78" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J78" s="12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" ht="22.5" customHeight="1">
+      <c r="J78" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="79" ht="22.5" hidden="1" customHeight="1">
       <c r="A79" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C79" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C79" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D79" s="9">
+      <c r="D79" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E79" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="9">
+      <c r="E79" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" s="8">
         <v>192903.0</v>
       </c>
-      <c r="G79" s="9">
+      <c r="G79" s="8">
         <v>150030.0</v>
       </c>
-      <c r="H79" s="9">
+      <c r="H79" s="8">
         <v>77501.0</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J79" s="12" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="80" ht="22.5" customHeight="1">
+      <c r="J79" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="80" ht="22.5" hidden="1" customHeight="1">
       <c r="A80" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C80" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C80" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D80" s="9">
+      <c r="D80" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E80" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F80" s="9">
+      <c r="E80" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F80" s="8">
         <v>152062.0</v>
       </c>
-      <c r="G80" s="9">
+      <c r="G80" s="8">
         <v>112769.0</v>
       </c>
-      <c r="H80" s="9">
+      <c r="H80" s="8">
         <v>124423.0</v>
       </c>
       <c r="I80" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J80" s="12" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="81" ht="22.5" customHeight="1">
+      <c r="J80" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="81" ht="22.5" hidden="1" customHeight="1">
       <c r="A81" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B81" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D81" s="9">
+      <c r="B81" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D81" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E81" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F81" s="9">
+      <c r="E81" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F81" s="8">
         <v>153692.0</v>
       </c>
-      <c r="G81" s="9">
+      <c r="G81" s="8">
         <v>136980.0</v>
       </c>
-      <c r="H81" s="9">
+      <c r="H81" s="8">
         <v>63920.0</v>
       </c>
       <c r="I81" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J81" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="82" ht="22.5" customHeight="1">
+      <c r="J81" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="82" ht="22.5" hidden="1" customHeight="1">
       <c r="A82" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D82" s="9">
+      <c r="B82" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D82" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F82" s="9">
+      <c r="E82" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="8">
         <v>45564.0</v>
       </c>
-      <c r="G82" s="9">
+      <c r="G82" s="8">
         <v>10456.0</v>
       </c>
-      <c r="H82" s="9">
+      <c r="H82" s="8">
         <v>40560.0</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J82" s="12"/>
-    </row>
-    <row r="83" ht="22.5" customHeight="1">
+        <v>17</v>
+      </c>
+      <c r="J82" s="11"/>
+    </row>
+    <row r="83" ht="22.5" hidden="1" customHeight="1">
       <c r="A83" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D83" s="9">
+      <c r="D83" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E83" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F83" s="9">
+      <c r="E83" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F83" s="8">
         <v>93517.0</v>
       </c>
-      <c r="G83" s="9">
+      <c r="G83" s="8">
         <v>18622.0</v>
       </c>
-      <c r="H83" s="9">
+      <c r="H83" s="8">
         <v>48804.0</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J83" s="12" t="s">
-        <v>123</v>
+        <v>35</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="8">
         <v>2110317.0</v>
       </c>
-      <c r="E84" s="6" t="s">
+      <c r="E84" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F84" s="9">
+      <c r="F84" s="8">
         <v>43200.0</v>
       </c>
-      <c r="G84" s="9">
+      <c r="G84" s="8">
         <v>5340.0</v>
       </c>
-      <c r="H84" s="9">
+      <c r="H84" s="8">
         <v>40890.0</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J84" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J84" s="11"/>
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="8">
         <v>152384.0</v>
       </c>
-      <c r="E85" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F85" s="9">
+      <c r="E85" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F85" s="8">
         <v>25350.0</v>
       </c>
-      <c r="G85" s="9">
+      <c r="G85" s="8">
         <v>6240.0</v>
       </c>
-      <c r="H85" s="9">
+      <c r="H85" s="8">
         <v>30750.0</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J85" s="12"/>
+        <v>35</v>
+      </c>
+      <c r="J85" s="11"/>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="8">
         <v>2152388.0</v>
       </c>
-      <c r="E86" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F86" s="9">
+      <c r="E86" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F86" s="8">
         <v>5040.0</v>
       </c>
-      <c r="G86" s="9">
+      <c r="G86" s="8">
         <v>720.0</v>
       </c>
-      <c r="H86" s="9">
+      <c r="H86" s="8">
         <v>4680.0</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J86" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J86" s="11"/>
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C87" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C87" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D87" s="9">
+      <c r="D87" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E87" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F87" s="9">
+      <c r="E87" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F87" s="8">
         <v>124423.0</v>
       </c>
-      <c r="G87" s="9">
+      <c r="G87" s="8">
         <v>60002.0</v>
       </c>
-      <c r="H87" s="9">
+      <c r="H87" s="8">
         <v>69217.0</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J87" s="12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="I88" s="20"/>
-    </row>
-    <row r="89">
-      <c r="I89" s="20"/>
+        <v>35</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="88" ht="22.5" customHeight="1">
+      <c r="A88" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D88" s="8">
+        <v>152384.0</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F88" s="8">
+        <v>30750.0</v>
+      </c>
+      <c r="G88" s="8">
+        <v>9975.0</v>
+      </c>
+      <c r="H88" s="8">
+        <v>36300.0</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J88" s="11"/>
+    </row>
+    <row r="89" ht="22.5" customHeight="1">
+      <c r="A89" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D89" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F89" s="8">
+        <v>58320.0</v>
+      </c>
+      <c r="G89" s="8">
+        <v>53468.0</v>
+      </c>
+      <c r="H89" s="8">
+        <v>12480.0</v>
+      </c>
+      <c r="I89" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J89" s="11" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="90">
       <c r="I90" s="20"/>
@@ -6297,13 +6371,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I87">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I89">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I88:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I90:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A87">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A89">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -6369,89 +6443,89 @@
       <c r="A2" s="4">
         <v>46224.0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="9">
+      <c r="E2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="8">
         <v>333.0</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <v>6480.0</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="8">
         <v>3712.0</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>17</v>
+      <c r="J2" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
       <c r="A3" s="4">
         <v>46224.0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9">
+      <c r="C3" s="7"/>
+      <c r="D3" s="8">
         <v>2114158.0</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>60.0</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>1000.0</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>60.0</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="12" t="s">
-        <v>23</v>
+      <c r="J3" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
       <c r="A4" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="14"/>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>10501.0</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="9">
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="8">
         <v>415093.0</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <v>115920.0</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>543038.0</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6459,59 +6533,59 @@
       <c r="A5" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="14"/>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>112379.0</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="9">
+      <c r="E5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="8">
         <v>3000.0</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>29400.0</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>3000.0</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>32</v>
+      <c r="J5" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
       <c r="A6" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="14"/>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>112268.0</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="E6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="8">
         <v>3000.0</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>12300.0</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>3300.0</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="11" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6519,351 +6593,351 @@
       <c r="A7" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>39</v>
+      <c r="B7" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C7" s="14"/>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>132357.0</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="E7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="8">
         <v>1560.0</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>1560.0</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>4560.0</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>42</v>
+      <c r="J7" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
       <c r="A8" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="14"/>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>2152388.0</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="9">
+      <c r="E8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="8">
         <v>720.0</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>11160.0</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>5940.0</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="12" t="s">
-        <v>45</v>
+      <c r="J8" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
       <c r="A9" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="14"/>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="9">
+      <c r="E9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
         <v>3712.0</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>46723.0</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>213.0</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="12" t="s">
-        <v>49</v>
+      <c r="J9" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
       <c r="A10" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="14"/>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>73001.0</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="9">
+      <c r="E10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="8">
         <v>73787.0</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>72000.0</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>109487.0</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>53</v>
+      <c r="J10" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
       <c r="A11" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="14"/>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>112268.0</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="9">
+      <c r="E11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="8">
         <v>3300.0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>1800.0</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>3300.0</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="12"/>
+      <c r="J11" s="11"/>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
       <c r="A12" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="14"/>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>112379.0</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="9">
+      <c r="E12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="8">
         <v>4200.0</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <v>7500.0</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <v>3900.0</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="12"/>
+      <c r="J12" s="11"/>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
       <c r="A13" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>39</v>
+      <c r="B13" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C13" s="14"/>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="9">
+      <c r="E13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="8">
         <v>379471.0</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>392580.0</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>357186.0</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>53</v>
+      <c r="J13" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
       <c r="A14" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="14"/>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>72001.0</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <v>21905.0</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <v>47670.0</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <v>38000.0</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>53</v>
+      <c r="J14" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
       <c r="A15" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="14"/>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>2110327.0</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="9">
+      <c r="E15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="8">
         <v>69120.0</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <v>57600.0</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>40320.0</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>62</v>
+      <c r="J15" s="11" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
       <c r="A16" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="14"/>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>112379.0</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="9">
+      <c r="E16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="8">
         <v>3900.0</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <v>102600.0</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <v>1500.0</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="12"/>
+      <c r="J16" s="11"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
       <c r="A17" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="14"/>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>2152388.0</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="9">
+      <c r="E17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="8">
         <v>720.0</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <v>9720.0</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <v>2580.0</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="12"/>
+      <c r="J17" s="11"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
       <c r="A18" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="14"/>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>112268.0</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="9">
+      <c r="E18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="8">
         <v>3300.0</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="8">
         <v>30600.0</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>600.0</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="11" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6871,89 +6945,89 @@
       <c r="A19" s="4">
         <v>46230.0</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>39</v>
+      <c r="B19" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C19" s="14"/>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <v>2410401.0</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <v>136538.0</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>34080.0</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <v>213000.0</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="12" t="s">
-        <v>68</v>
+      <c r="J19" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
       <c r="A20" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>39</v>
+      <c r="B20" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C20" s="14"/>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="9">
+      <c r="E20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="8">
         <v>591750.0</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>239760.0</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <v>577207.0</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="12" t="s">
-        <v>68</v>
+      <c r="J20" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
       <c r="A21" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>39</v>
+      <c r="B21" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C21" s="14"/>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>10601.0</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="8">
         <v>1230.0</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>8626.0</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>1958.0</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="11" t="s">
         <v>71</v>
       </c>
     </row>
@@ -6961,281 +7035,281 @@
       <c r="A22" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="14"/>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>2152388.0</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="9">
+      <c r="E22" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="8">
         <v>4320.0</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="8">
         <v>2700.0</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="8">
         <v>3420.0</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="12"/>
+      <c r="J22" s="11"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
       <c r="A23" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="14"/>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <v>114357.0</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="8">
         <v>240.0</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="8">
         <v>52320.0</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="8">
         <v>240.0</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="12"/>
+      <c r="J23" s="11"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
       <c r="A24" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>39</v>
+      <c r="B24" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C24" s="14"/>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>10501.0</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="9">
+      <c r="E24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="8">
         <v>19663.0</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="8">
         <v>49540.0</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="8">
         <v>29632.0</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="12"/>
+      <c r="J24" s="11"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
       <c r="A25" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="14"/>
-      <c r="D25" s="9">
+      <c r="D25" s="8">
         <v>112268.0</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="9">
+      <c r="E25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="8">
         <v>5700.0</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="8">
         <v>34800.0</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="8">
         <v>5100.0</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="11"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
       <c r="A26" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="14"/>
-      <c r="D26" s="9">
+      <c r="D26" s="8">
         <v>2110317.0</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="8">
         <v>720.0</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="8">
         <v>7920.0</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="8">
         <v>720.0</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J26" s="12"/>
+      <c r="J26" s="11"/>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
       <c r="A27" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="14"/>
-      <c r="D27" s="9">
+      <c r="D27" s="8">
         <v>2114357.0</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="8">
         <v>432.0</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="8">
         <v>576.0</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="8">
         <v>432.0</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J27" s="12"/>
+      <c r="J27" s="11"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
       <c r="A28" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="14"/>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <v>10501.0</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="9">
+      <c r="E28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="8">
         <v>219540.0</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="8">
         <v>272160.0</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="8">
         <v>16698.0</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="12"/>
+      <c r="J28" s="11"/>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
       <c r="A29" s="4">
         <v>46233.0</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C29" s="14"/>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>112268.0</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="8">
+        <v>5100.0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>3300.0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>4800.0</v>
+      </c>
+      <c r="I29" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F29" s="9">
-        <v>5100.0</v>
-      </c>
-      <c r="G29" s="9">
-        <v>3300.0</v>
-      </c>
-      <c r="H29" s="9">
-        <v>4800.0</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J29" s="12"/>
+      <c r="J29" s="11"/>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
       <c r="A30" s="4">
         <v>46233.0</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="14"/>
-      <c r="D30" s="9">
+      <c r="D30" s="8">
         <v>114357.0</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="8">
         <v>240.0</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="8">
         <v>7800.0</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="8">
         <v>1560.0</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J30" s="12"/>
+        <v>35</v>
+      </c>
+      <c r="J30" s="11"/>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
       <c r="A31" s="4">
         <v>46233.0</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C31" s="14"/>
-      <c r="D31" s="9">
+      <c r="D31" s="8">
         <v>10601.0</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="8">
         <v>7717.0</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="8">
         <v>10080.0</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="8">
         <v>12867.0</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J31" s="12" t="s">
+      <c r="J31" s="11" t="s">
         <v>82</v>
       </c>
     </row>
@@ -7243,53 +7317,53 @@
       <c r="A32" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C32" s="14"/>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <v>79110.0</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" s="8">
+        <v>48000.0</v>
+      </c>
+      <c r="G32" s="8">
+        <v>24600.0</v>
+      </c>
+      <c r="H32" s="8">
+        <v>36300.0</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" s="17" t="s">
         <v>84</v>
-      </c>
-      <c r="F32" s="9">
-        <v>48000.0</v>
-      </c>
-      <c r="G32" s="9">
-        <v>24600.0</v>
-      </c>
-      <c r="H32" s="9">
-        <v>36300.0</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
       <c r="A33" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="14"/>
-      <c r="D33" s="9">
+      <c r="D33" s="8">
         <v>10501.0</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="9">
+      <c r="E33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="8">
         <v>95574.0</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="8">
         <v>78469.0</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="8">
         <v>142801.0</v>
       </c>
       <c r="I33" s="10" t="s">
@@ -7303,85 +7377,85 @@
       <c r="A34" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="14"/>
-      <c r="D34" s="9">
+      <c r="D34" s="8">
         <v>73001.0</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F34" s="9">
+      <c r="E34" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="8">
         <v>73367.0</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="8">
         <v>94608.0</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="8">
         <v>39150.0</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J34" s="12"/>
+      <c r="J34" s="11"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
       <c r="A35" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="14"/>
-      <c r="D35" s="9">
+      <c r="D35" s="8">
         <v>112357.0</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F35" s="9">
+      <c r="E35" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="8">
         <v>840.0</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="8">
         <v>5160.0</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="8">
         <v>480.0</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J35" s="12"/>
+      <c r="J35" s="11"/>
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C36" s="14"/>
-      <c r="D36" s="9">
+      <c r="D36" s="8">
         <v>10601.0</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="8">
         <v>17934.0</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="8">
         <v>64980.0</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="8">
         <v>21714.0</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J36" s="12" t="s">
+      <c r="J36" s="11" t="s">
         <v>90</v>
       </c>
     </row>
@@ -7389,250 +7463,473 @@
       <c r="A37" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="14"/>
-      <c r="D37" s="9">
+      <c r="D37" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="9">
+      <c r="E37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="8">
         <v>194520.0</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="8">
         <v>84060.0</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="8">
         <v>122840.0</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J37" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J37" s="11"/>
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="14"/>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>114379.0</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F38" s="9">
+      <c r="E38" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="8">
         <v>52200.0</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="8">
         <v>16200.0</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="8">
         <v>7500.0</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J38" s="12"/>
+        <v>35</v>
+      </c>
+      <c r="J38" s="11"/>
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C39" s="14"/>
-      <c r="D39" s="9">
+      <c r="D39" s="8">
         <v>2110317.0</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="8">
         <v>6450.0</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="8">
         <v>16920.0</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="8">
         <v>6480.0</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J39" s="11"/>
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="14"/>
-      <c r="D40" s="9">
+      <c r="D40" s="8">
         <v>2010102.0</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" s="9">
+      <c r="E40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="8">
         <v>1398.0</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="8">
         <v>1320.0</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="8">
         <v>438.0</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J40" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J40" s="11"/>
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="14"/>
-      <c r="D41" s="9">
+      <c r="D41" s="8">
         <v>2152388.0</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="9">
+      <c r="E41" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" s="8">
         <v>2460.0</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="8">
         <v>17640.0</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="8">
         <v>3240.0</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J41" s="11"/>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C42" s="14"/>
-      <c r="D42" s="9">
+      <c r="D42" s="8">
         <v>112268.0</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F42" s="9">
+      <c r="E42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F42" s="8">
         <v>3600.0</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="8">
         <v>1500.0</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="8">
         <v>3900.0</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J42" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J42" s="11"/>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="14"/>
-      <c r="D43" s="9">
+      <c r="D43" s="8">
         <v>114379.0</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F43" s="9">
+      <c r="E43" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F43" s="8">
         <v>7500.0</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="8">
         <v>54900.0</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="8">
         <v>8400.0</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J43" s="12"/>
+      <c r="J43" s="11"/>
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C44" s="14"/>
-      <c r="D44" s="9">
+      <c r="D44" s="8">
         <v>114357.0</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="8">
         <v>240.0</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="8">
         <v>7680.0</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="8">
         <v>360.0</v>
       </c>
-      <c r="I44" s="10"/>
-      <c r="J44" s="12"/>
-    </row>
-    <row r="45">
-      <c r="I45" s="20"/>
-    </row>
-    <row r="46">
-      <c r="I46" s="20"/>
-    </row>
-    <row r="47">
-      <c r="I47" s="20"/>
-    </row>
-    <row r="48">
-      <c r="I48" s="20"/>
-    </row>
-    <row r="49">
-      <c r="I49" s="20"/>
-    </row>
-    <row r="50">
-      <c r="I50" s="20"/>
-    </row>
-    <row r="51">
-      <c r="I51" s="20"/>
-    </row>
-    <row r="52">
-      <c r="I52" s="20"/>
-    </row>
-    <row r="53">
-      <c r="I53" s="20"/>
+      <c r="I44" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="14"/>
+      <c r="D45" s="8">
+        <v>10601.0</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F45" s="8">
+        <v>1115.0</v>
+      </c>
+      <c r="G45" s="8">
+        <v>5267.0</v>
+      </c>
+      <c r="H45" s="8">
+        <v>1590.0</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="A46" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="14"/>
+      <c r="D46" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="8">
+        <v>114240.0</v>
+      </c>
+      <c r="G46" s="8">
+        <v>79680.0</v>
+      </c>
+      <c r="H46" s="8">
+        <v>191130.0</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" s="11"/>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="A47" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="14"/>
+      <c r="D47" s="8">
+        <v>2112207.0</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" s="8">
+        <v>1800.0</v>
+      </c>
+      <c r="G47" s="8">
+        <v>1800.0</v>
+      </c>
+      <c r="H47" s="8">
+        <v>1980.0</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" s="8">
+        <v>112268.0</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" s="8">
+        <v>3900.0</v>
+      </c>
+      <c r="G48" s="8">
+        <v>34200.0</v>
+      </c>
+      <c r="H48" s="8">
+        <v>1200.0</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J48" s="11"/>
+    </row>
+    <row r="49" ht="22.5" customHeight="1">
+      <c r="A49" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" s="8">
+        <v>112357.0</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F49" s="8">
+        <v>600.0</v>
+      </c>
+      <c r="G49" s="8">
+        <v>8400.0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>600.0</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J49" s="11"/>
+    </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="14"/>
+      <c r="D50" s="8">
+        <v>114268.0</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" s="8">
+        <v>2700.0</v>
+      </c>
+      <c r="G50" s="8">
+        <v>5700.0</v>
+      </c>
+      <c r="H50" s="8">
+        <v>300.0</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="14"/>
+      <c r="D51" s="8">
+        <v>10501.0</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="8">
+        <v>68651.0</v>
+      </c>
+      <c r="G51" s="8">
+        <v>64050.0</v>
+      </c>
+      <c r="H51" s="8">
+        <v>13421.0</v>
+      </c>
+      <c r="I51" s="10"/>
+      <c r="J51" s="11"/>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" s="14"/>
+      <c r="D52" s="8">
+        <v>72003.0</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F52" s="8">
+        <v>1391.0</v>
+      </c>
+      <c r="G52" s="8">
+        <v>3885.0</v>
+      </c>
+      <c r="H52" s="8">
+        <v>2407.0</v>
+      </c>
+      <c r="I52" s="10"/>
+      <c r="J52" s="11"/>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="14"/>
+      <c r="D53" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="8">
+        <v>2974.0</v>
+      </c>
+      <c r="G53" s="8">
+        <v>1200.0</v>
+      </c>
+      <c r="H53" s="8">
+        <v>3317.0</v>
+      </c>
+      <c r="I53" s="10"/>
+      <c r="J53" s="11"/>
     </row>
     <row r="54">
       <c r="I54" s="20"/>
@@ -10357,13 +10654,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I44">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I53">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I45:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I54:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A44">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A53">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="135">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -44,19 +44,22 @@
     <t xml:space="preserve">Otro </t>
   </si>
   <si>
+    <t>TAT BOGOTA MONTEVIDEO</t>
+  </si>
+  <si>
     <t>ALKA2</t>
   </si>
   <si>
-    <t>TAT BOGOTA MONTEVIDEO</t>
-  </si>
-  <si>
     <t>Daniel Castro</t>
   </si>
   <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+    <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
     <t>7. Otro</t>
@@ -65,27 +68,24 @@
     <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
   </si>
   <si>
-    <t>2. Error De Registro De Inventario</t>
+    <t>TAT MONTERIA</t>
+  </si>
+  <si>
+    <t>LUIS LOPEZ</t>
   </si>
   <si>
     <t>LANZA</t>
   </si>
   <si>
-    <t>TAT MONTERIA</t>
-  </si>
-  <si>
-    <t>LUIS LOPEZ</t>
-  </si>
-  <si>
     <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
+    <t>3. Falla De Rotación</t>
+  </si>
+  <si>
     <t>6. Transformación De Referencias</t>
   </si>
   <si>
-    <t>3. Falla De Rotación</t>
-  </si>
-  <si>
     <t>Pendiente Transformar Roto GT Por manipulación</t>
   </si>
   <si>
@@ -95,90 +95,90 @@
     <t>FABIO GOMEZ</t>
   </si>
   <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+  </si>
+  <si>
     <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+    <t>TAT CARTAGENA</t>
+  </si>
+  <si>
+    <t>Dilan Barraza</t>
   </si>
   <si>
     <t>se equivocaron al cargar una estiba</t>
   </si>
   <si>
-    <t>TAT CARTAGENA</t>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>4. Exigencia Del Cliente (Edad)</t>
+  </si>
+  <si>
+    <t>Venta FS</t>
   </si>
   <si>
     <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
-    <t>Dilan Barraza</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
   </si>
   <si>
-    <t>4. Exigencia Del Cliente (Edad)</t>
-  </si>
-  <si>
-    <t>Venta FS</t>
+    <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
   </si>
   <si>
-    <t>Se dejó lote para revisión por calidad</t>
-  </si>
-  <si>
     <t>PALMAS</t>
   </si>
   <si>
+    <t>Se envía más fresco a Rionegro</t>
+  </si>
+  <si>
     <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
     <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
-    <t>Se envía más fresco a Rionegro</t>
+    <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
     <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+    <t>TAT CALI</t>
+  </si>
+  <si>
+    <t>DIEGO ROJAS</t>
   </si>
   <si>
     <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
-    <t>1. Ingreso Por Devolución</t>
-  </si>
-  <si>
-    <t>TAT CALI</t>
-  </si>
-  <si>
-    <t>DIEGO ROJAS</t>
+    <t>TAT CUCUTA</t>
+  </si>
+  <si>
+    <t>ALEXANDER PEÑA</t>
   </si>
   <si>
     <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
   </si>
   <si>
-    <t>TAT CUCUTA</t>
-  </si>
-  <si>
     <t>HUEVO PICADO ROJO</t>
   </si>
   <si>
-    <t>ALEXANDER PEÑA</t>
-  </si>
-  <si>
     <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
@@ -188,28 +188,31 @@
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
+    <t>Transformación de PET</t>
+  </si>
+  <si>
+    <t>ANDRES MEJIA</t>
+  </si>
+  <si>
+    <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
+  </si>
+  <si>
+    <t>TAT POPAYAN</t>
+  </si>
+  <si>
+    <t>JONATHAN MOSQUERA</t>
+  </si>
+  <si>
     <t>HUEVO SUCIO DE JAULA</t>
   </si>
   <si>
-    <t>Transformación de PET</t>
-  </si>
-  <si>
-    <t>ANDRES MEJIA</t>
-  </si>
-  <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
   </si>
   <si>
-    <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
-  </si>
-  <si>
     <t>Esta para despacho hoy</t>
   </si>
   <si>
-    <t>TAT POPAYAN</t>
-  </si>
-  <si>
-    <t>JONATHAN MOSQUERA</t>
+    <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
     <t>Cola de programación</t>
@@ -218,48 +221,54 @@
     <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
   </si>
   <si>
-    <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
+    <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
     <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+  </si>
+  <si>
     <t>HUEVO CX30 CARTON GRIS</t>
   </si>
   <si>
     <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
   </si>
   <si>
-    <t>Producto con novedades de calidad, se está bandejeando</t>
-  </si>
-  <si>
     <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+    <t>5. Ingreso De Planta</t>
+  </si>
+  <si>
+    <t>Se despacha par FS con producto más nuevo</t>
+  </si>
+  <si>
+    <t>ANDREA QUIROGA</t>
+  </si>
+  <si>
+    <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
   </si>
   <si>
     <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
   </si>
   <si>
-    <t>5. Ingreso De Planta</t>
-  </si>
-  <si>
     <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
-    <t>Se despacha par FS con producto más nuevo</t>
-  </si>
-  <si>
-    <t>ANDREA QUIROGA</t>
-  </si>
-  <si>
-    <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
+    <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
     <t>ALKA1</t>
   </si>
   <si>
+    <t>TAT PASTO</t>
+  </si>
+  <si>
+    <t>CAROLINA VITERI</t>
+  </si>
+  <si>
     <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
   </si>
   <si>
@@ -269,19 +278,19 @@
     <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
   </si>
   <si>
-    <t>Se despacha producto más nuevo para Rionegro</t>
+    <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
     <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
   </si>
   <si>
+    <t>Pedido para villavicencio</t>
+  </si>
+  <si>
     <t>HUEVO L X 12 PET CAJA X 120</t>
   </si>
   <si>
-    <t>TAT PASTO</t>
-  </si>
-  <si>
-    <t>CAROLINA VITERI</t>
+    <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
     <t>Cargo en incubación</t>
@@ -290,66 +299,63 @@
     <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>Asignacion a canal Tat para sugeridos de hoy</t>
-  </si>
-  <si>
-    <t>Pedido para villavicencio</t>
-  </si>
-  <si>
-    <t>Se entrega inventario nuevo para FS</t>
+    <t>Inventario de Asesor de Rionegro que renuncio</t>
+  </si>
+  <si>
+    <t>TAT BARRANQUILLA</t>
+  </si>
+  <si>
+    <t>Jhonatan Gomez</t>
+  </si>
+  <si>
+    <t>Lote mezclado en la misma estiba</t>
+  </si>
+  <si>
+    <t>Supera edad solicitada clientes grandes superficies</t>
   </si>
   <si>
     <t>BELLAVISTA</t>
   </si>
   <si>
+    <t>Pedido para villacicencio</t>
+  </si>
+  <si>
     <t>Traslado a cedi, producto de devolución</t>
   </si>
   <si>
-    <t>Inventario de Asesor de Rionegro que renuncio</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA</t>
-  </si>
-  <si>
-    <t>Jhonatan Gomez</t>
-  </si>
-  <si>
     <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
-    <t>Lote mezclado en la misma estiba</t>
+    <t>Se envía huevo más fresco a Sincelejo</t>
+  </si>
+  <si>
+    <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
+  </si>
+  <si>
+    <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>Supera edad solicitada clientes grandes superficies</t>
+    <t>SalIO en sugeridos de hoy 22/07/2026</t>
+  </si>
+  <si>
+    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
+  </si>
+  <si>
+    <t>Yovanis Arevalo</t>
   </si>
   <si>
     <t>HUEVO SUCIO ZF MARCADO</t>
   </si>
   <si>
-    <t>Pedido para villacicencio</t>
-  </si>
-  <si>
-    <t>Se envía huevo más fresco a Sincelejo</t>
-  </si>
-  <si>
-    <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
-  </si>
-  <si>
-    <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
-  </si>
-  <si>
-    <t>SalIO en sugeridos de hoy 22/07/2026</t>
-  </si>
-  <si>
-    <t>Yovanis Arevalo</t>
-  </si>
-  <si>
     <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
   </si>
   <si>
+    <t>vehiculo con flata de capacidad / TAT cali</t>
+  </si>
+  <si>
     <t>Devolucion de huevo de 12 dias en mal estado</t>
   </si>
   <si>
@@ -405,6 +411,12 @@
   </si>
   <si>
     <t>Producto enviado a Rionegro y para FS más fresco</t>
+  </si>
+  <si>
+    <t>Identificación producto averiado en el momento de la entrega del TAT, se bandejea</t>
+  </si>
+  <si>
+    <t>yOVANIS AREVALO</t>
   </si>
 </sst>
 </file>
@@ -444,14 +456,14 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -482,54 +494,54 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -593,13 +605,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Plantas-style">
+    <tableStyle count="4" pivot="0" name="Cedis-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Cedis-style">
+    <tableStyle count="4" pivot="0" name="Plantas-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -622,7 +634,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J89" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J92" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -640,7 +652,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J53" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J57" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -903,2726 +915,2805 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="6">
+      <c r="A2" s="4">
         <v>46204.0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="B2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="9">
+        <v>359100.0</v>
+      </c>
+      <c r="G2" s="9">
+        <v>83486.0</v>
+      </c>
+      <c r="H2" s="9">
+        <v>206140.0</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" hidden="1" customHeight="1">
+      <c r="A3" s="5">
+        <v>46205.0</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="8">
-        <v>359100.0</v>
-      </c>
-      <c r="G2" s="8">
-        <v>83486.0</v>
-      </c>
-      <c r="H2" s="8">
-        <v>206140.0</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="4">
+      <c r="F3" s="9">
+        <v>298282.0</v>
+      </c>
+      <c r="G3" s="9">
+        <v>42201.0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>260675.0</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
+      <c r="A4" s="5">
         <v>46205.0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2110217.0</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="9">
+        <v>21120.0</v>
+      </c>
+      <c r="G4" s="9">
+        <v>11039.0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>16920.0</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
+      <c r="A5" s="5">
+        <v>46205.0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="9">
+        <v>75680.0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>5640.0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>3134.0</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="5">
+        <v>46206.0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="9">
+        <v>189540.0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>161685.0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>144720.0</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="5">
+        <v>46206.0</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="9">
+        <v>20640.0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>3761.0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>13920.0</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="5">
+        <v>46206.0</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="9">
+        <v>14700.0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>6435.0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>9600.0</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
+      <c r="A9" s="5">
+        <v>46206.0</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="9">
+        <v>228240.0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>77306.0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>124260.0</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
+      <c r="A10" s="5">
+        <v>46206.0</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="9">
+        <v>7830.0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>1980.0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>6030.0</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="5">
+        <v>46206.0</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="9">
+        <v>31680.0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>5526.0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>23040.0</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
+      <c r="A12" s="5">
+        <v>46206.0</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="8">
+      <c r="D12" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="9">
+        <v>51387.0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>10827.0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>12170.0</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
+      <c r="A13" s="5">
+        <v>46209.0</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="9">
+        <v>195810.0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>93809.0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>133410.0</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
+      <c r="A14" s="5">
+        <v>46209.0</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="9">
+        <v>526002.0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>301965.0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>424588.0</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="5">
+        <v>46209.0</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="9">
+        <v>14160.0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>6692.0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>12360.0</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
+      <c r="A16" s="5">
+        <v>46210.0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="9">
+        <v>149040.0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>119573.0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>289680.0</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" ht="22.5" hidden="1" customHeight="1">
+      <c r="A17" s="5">
+        <v>46210.0</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="9">
+        <v>2110217.0</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="9">
+        <v>22770.0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>3926.0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>19770.0</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="12"/>
+    </row>
+    <row r="18" ht="22.5" hidden="1" customHeight="1">
+      <c r="A18" s="5">
+        <v>46210.0</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="9">
+        <v>222021.0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>61385.0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>162125.0</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="12"/>
+    </row>
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
+      <c r="A19" s="5">
+        <v>46211.0</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="9">
+        <v>495833.0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>148815.0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>401280.0</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
+      <c r="A20" s="5">
+        <v>46211.0</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="9">
+        <v>139920.0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>54384.0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>74040.0</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="12"/>
+    </row>
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
+      <c r="A21" s="5">
+        <v>46211.0</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="9">
+        <v>162125.0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>60138.0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>100687.0</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" hidden="1" customHeight="1">
+      <c r="A22" s="5">
+        <v>46211.0</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="9">
+        <v>32850.0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>7065.0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>32700.0</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22" s="12"/>
+    </row>
+    <row r="23" ht="22.5" hidden="1" customHeight="1">
+      <c r="A23" s="5">
+        <v>46211.0</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="9">
+        <v>112271.0</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="9">
+        <v>16500.0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>5310.0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>18000.0</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="12"/>
+    </row>
+    <row r="24" ht="22.5" hidden="1" customHeight="1">
+      <c r="A24" s="5">
+        <v>46212.0</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="8">
-        <v>298282.0</v>
-      </c>
-      <c r="G3" s="8">
-        <v>42201.0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>260675.0</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="4">
-        <v>46205.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="F24" s="9">
+        <v>190047.0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>59822.0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>248481.0</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="12"/>
+    </row>
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
+      <c r="A25" s="5">
+        <v>46212.0</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="9">
+        <v>178080.0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>47784.0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>203520.0</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
+      <c r="A26" s="5">
+        <v>46212.0</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="9">
+        <v>10320.0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>5869.0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>13200.0</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
+      <c r="A27" s="5">
+        <v>46212.0</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="9">
+        <v>112271.0</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="9">
+        <v>18000.0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>4485.0</v>
+      </c>
+      <c r="H27" s="9">
+        <v>13500.0</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="12"/>
+    </row>
+    <row r="28" ht="22.5" hidden="1" customHeight="1">
+      <c r="A28" s="5">
+        <v>46213.0</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="9">
+        <v>208440.0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>85608.0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>150833.0</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" hidden="1" customHeight="1">
+      <c r="A29" s="5">
+        <v>46213.0</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="9">
+        <v>962820.0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>80644.0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>922140.0</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
+      <c r="A30" s="5">
+        <v>46213.0</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="9">
+        <v>335340.0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>111433.0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>381600.0</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="5">
+        <v>46213.0</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="9">
+        <v>316800.0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>99546.0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>229680.0</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" s="12"/>
+    </row>
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
+      <c r="A32" s="5">
+        <v>46213.0</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" s="9">
+        <v>176850.0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>47499.0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>128971.0</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J32" s="12"/>
+    </row>
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
+      <c r="A33" s="5">
+        <v>46213.0</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="9">
+        <v>58080.0</v>
+      </c>
+      <c r="G33" s="9">
+        <v>20865.0</v>
+      </c>
+      <c r="H33" s="9">
+        <v>25440.0</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="12"/>
+    </row>
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
+      <c r="A34" s="5">
+        <v>46217.0</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" s="9">
+        <v>481440.0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>464517.0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>151435.0</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="12"/>
+    </row>
+    <row r="35" ht="22.5" hidden="1" customHeight="1">
+      <c r="A35" s="5">
+        <v>46217.0</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="8">
-        <v>2110217.0</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="8">
-        <v>21120.0</v>
-      </c>
-      <c r="G4" s="8">
-        <v>11039.0</v>
-      </c>
-      <c r="H4" s="8">
-        <v>16920.0</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="4">
-        <v>46205.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="D35" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="9">
+        <v>355720.0</v>
+      </c>
+      <c r="G35" s="9">
+        <v>342811.0</v>
+      </c>
+      <c r="H35" s="9">
+        <v>302760.0</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="12"/>
+    </row>
+    <row r="36" ht="22.5" hidden="1" customHeight="1">
+      <c r="A36" s="5">
+        <v>46217.0</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" s="9">
+        <v>35280.0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>16988.0</v>
+      </c>
+      <c r="H36" s="9">
+        <v>37926.0</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" hidden="1" customHeight="1">
+      <c r="A37" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="F37" s="9">
+        <v>272073.0</v>
+      </c>
+      <c r="G37" s="9">
+        <v>76546.0</v>
+      </c>
+      <c r="H37" s="9">
+        <v>275205.0</v>
+      </c>
+      <c r="I37" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="8">
-        <v>75680.0</v>
-      </c>
-      <c r="G5" s="8">
-        <v>5640.0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>3134.0</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="J37" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" ht="22.5" hidden="1" customHeight="1">
+      <c r="A38" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" s="9">
+        <v>37926.0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>5633.0</v>
+      </c>
+      <c r="H38" s="9">
+        <v>25746.0</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" ht="22.5" hidden="1" customHeight="1">
+      <c r="A39" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C39" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D39" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="8">
-        <v>189540.0</v>
-      </c>
-      <c r="G6" s="8">
-        <v>161685.0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>144720.0</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="F39" s="9">
+        <v>20640.0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>4951.0</v>
+      </c>
+      <c r="H39" s="9">
+        <v>16320.0</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" ht="22.5" hidden="1" customHeight="1">
+      <c r="A40" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C40" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="8">
-        <v>20640.0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>3761.0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>13920.0</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="8">
-        <v>152384.0</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="8">
-        <v>14700.0</v>
-      </c>
-      <c r="G8" s="8">
-        <v>6435.0</v>
-      </c>
-      <c r="H8" s="8">
-        <v>9600.0</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="11"/>
-    </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="8">
-        <v>228240.0</v>
-      </c>
-      <c r="G9" s="8">
-        <v>77306.0</v>
-      </c>
-      <c r="H9" s="8">
-        <v>124260.0</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="8">
-        <v>2152388.0</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="8">
-        <v>7830.0</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1980.0</v>
-      </c>
-      <c r="H10" s="8">
-        <v>6030.0</v>
-      </c>
-      <c r="I10" s="13" t="s">
+      <c r="D40" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F40" s="9">
+        <v>10980.0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>2379.0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>13500.0</v>
+      </c>
+      <c r="I40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="8">
-        <v>31680.0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>5526.0</v>
-      </c>
-      <c r="H11" s="8">
-        <v>23040.0</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="4">
-        <v>46206.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="8">
-        <v>51387.0</v>
-      </c>
-      <c r="G12" s="8">
-        <v>10827.0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>12170.0</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="4">
-        <v>46209.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="8">
-        <v>195810.0</v>
-      </c>
-      <c r="G13" s="8">
-        <v>93809.0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>133410.0</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="4">
-        <v>46209.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="8">
-        <v>526002.0</v>
-      </c>
-      <c r="G14" s="8">
-        <v>301965.0</v>
-      </c>
-      <c r="H14" s="8">
-        <v>424588.0</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="4">
-        <v>46209.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="8">
-        <v>14160.0</v>
-      </c>
-      <c r="G15" s="8">
-        <v>6692.0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>12360.0</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="4">
-        <v>46210.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="8">
-        <v>149040.0</v>
-      </c>
-      <c r="G16" s="8">
-        <v>119573.0</v>
-      </c>
-      <c r="H16" s="8">
-        <v>289680.0</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="4">
-        <v>46210.0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="8">
-        <v>2110217.0</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="8">
-        <v>22770.0</v>
-      </c>
-      <c r="G17" s="8">
-        <v>3926.0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>19770.0</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="4">
-        <v>46210.0</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="8">
-        <v>222021.0</v>
-      </c>
-      <c r="G18" s="8">
-        <v>61385.0</v>
-      </c>
-      <c r="H18" s="8">
-        <v>162125.0</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="8">
-        <v>495833.0</v>
-      </c>
-      <c r="G19" s="8">
-        <v>148815.0</v>
-      </c>
-      <c r="H19" s="8">
-        <v>401280.0</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="8">
-        <v>139920.0</v>
-      </c>
-      <c r="G20" s="8">
-        <v>54384.0</v>
-      </c>
-      <c r="H20" s="8">
-        <v>74040.0</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="11"/>
-    </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="8">
-        <v>162125.0</v>
-      </c>
-      <c r="G21" s="8">
-        <v>60138.0</v>
-      </c>
-      <c r="H21" s="8">
-        <v>100687.0</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="8">
-        <v>152384.0</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="8">
-        <v>32850.0</v>
-      </c>
-      <c r="G22" s="8">
-        <v>7065.0</v>
-      </c>
-      <c r="H22" s="8">
-        <v>32700.0</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="11"/>
-    </row>
-    <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="8">
-        <v>112271.0</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="8">
-        <v>16500.0</v>
-      </c>
-      <c r="G23" s="8">
-        <v>5310.0</v>
-      </c>
-      <c r="H23" s="8">
-        <v>18000.0</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J23" s="11"/>
-    </row>
-    <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="4">
-        <v>46212.0</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="8">
-        <v>190047.0</v>
-      </c>
-      <c r="G24" s="8">
-        <v>59822.0</v>
-      </c>
-      <c r="H24" s="8">
-        <v>248481.0</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J24" s="11"/>
-    </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="4">
-        <v>46212.0</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F25" s="8">
-        <v>178080.0</v>
-      </c>
-      <c r="G25" s="8">
-        <v>47784.0</v>
-      </c>
-      <c r="H25" s="8">
-        <v>203520.0</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J25" s="11"/>
-    </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="4">
-        <v>46212.0</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="8">
-        <v>10320.0</v>
-      </c>
-      <c r="G26" s="8">
-        <v>5869.0</v>
-      </c>
-      <c r="H26" s="8">
-        <v>13200.0</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="4">
-        <v>46212.0</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="8">
-        <v>112271.0</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="8">
-        <v>18000.0</v>
-      </c>
-      <c r="G27" s="8">
-        <v>4485.0</v>
-      </c>
-      <c r="H27" s="8">
-        <v>13500.0</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" s="11"/>
-    </row>
-    <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="4">
-        <v>46213.0</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F28" s="8">
-        <v>208440.0</v>
-      </c>
-      <c r="G28" s="8">
-        <v>85608.0</v>
-      </c>
-      <c r="H28" s="8">
-        <v>150833.0</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="4">
-        <v>46213.0</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="8">
-        <v>962820.0</v>
-      </c>
-      <c r="G29" s="8">
-        <v>80644.0</v>
-      </c>
-      <c r="H29" s="8">
-        <v>922140.0</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="4">
-        <v>46213.0</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" s="8">
-        <v>335340.0</v>
-      </c>
-      <c r="G30" s="8">
-        <v>111433.0</v>
-      </c>
-      <c r="H30" s="8">
-        <v>381600.0</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="4">
-        <v>46213.0</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" s="8">
-        <v>316800.0</v>
-      </c>
-      <c r="G31" s="8">
-        <v>99546.0</v>
-      </c>
-      <c r="H31" s="8">
-        <v>229680.0</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" s="11"/>
-    </row>
-    <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="4">
-        <v>46213.0</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F32" s="8">
-        <v>176850.0</v>
-      </c>
-      <c r="G32" s="8">
-        <v>47499.0</v>
-      </c>
-      <c r="H32" s="8">
-        <v>128971.0</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J32" s="11"/>
-    </row>
-    <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="4">
-        <v>46213.0</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="8">
-        <v>58080.0</v>
-      </c>
-      <c r="G33" s="8">
-        <v>20865.0</v>
-      </c>
-      <c r="H33" s="8">
-        <v>25440.0</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" s="11"/>
-    </row>
-    <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="4">
-        <v>46217.0</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F34" s="8">
-        <v>481440.0</v>
-      </c>
-      <c r="G34" s="8">
-        <v>464517.0</v>
-      </c>
-      <c r="H34" s="8">
-        <v>151435.0</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J34" s="11"/>
-    </row>
-    <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="4">
-        <v>46217.0</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="8">
-        <v>355720.0</v>
-      </c>
-      <c r="G35" s="8">
-        <v>342811.0</v>
-      </c>
-      <c r="H35" s="8">
-        <v>302760.0</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="11"/>
-    </row>
-    <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="4">
-        <v>46217.0</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="8">
-        <v>35280.0</v>
-      </c>
-      <c r="G36" s="8">
-        <v>16988.0</v>
-      </c>
-      <c r="H36" s="8">
-        <v>37926.0</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" ht="22.5" hidden="1" customHeight="1">
-      <c r="A37" s="19">
-        <v>46218.0</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F37" s="8">
-        <v>272073.0</v>
-      </c>
-      <c r="G37" s="8">
-        <v>76546.0</v>
-      </c>
-      <c r="H37" s="8">
-        <v>275205.0</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" ht="22.5" hidden="1" customHeight="1">
-      <c r="A38" s="19">
-        <v>46218.0</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="8">
-        <v>37926.0</v>
-      </c>
-      <c r="G38" s="8">
-        <v>5633.0</v>
-      </c>
-      <c r="H38" s="8">
-        <v>25746.0</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" ht="22.5" hidden="1" customHeight="1">
-      <c r="A39" s="19">
-        <v>46218.0</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D39" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="8">
-        <v>20640.0</v>
-      </c>
-      <c r="G39" s="8">
-        <v>4951.0</v>
-      </c>
-      <c r="H39" s="8">
-        <v>16320.0</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" ht="22.5" hidden="1" customHeight="1">
-      <c r="A40" s="19">
-        <v>46218.0</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D40" s="8">
-        <v>2110317.0</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F40" s="8">
-        <v>10980.0</v>
-      </c>
-      <c r="G40" s="8">
-        <v>2379.0</v>
-      </c>
-      <c r="H40" s="8">
-        <v>13500.0</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" s="11"/>
+      <c r="J40" s="12"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="4">
+      <c r="A41" s="5">
         <v>46219.0</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" s="9">
+        <v>130320.0</v>
+      </c>
+      <c r="G41" s="9">
+        <v>47410.0</v>
+      </c>
+      <c r="H41" s="9">
+        <v>90480.0</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" ht="22.5" hidden="1" customHeight="1">
+      <c r="A42" s="5">
+        <v>46219.0</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F42" s="9">
+        <v>36225.0</v>
+      </c>
+      <c r="G42" s="9">
+        <v>11746.0</v>
+      </c>
+      <c r="H42" s="9">
+        <v>27570.0</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="12"/>
+    </row>
+    <row r="43" ht="22.5" hidden="1" customHeight="1">
+      <c r="A43" s="5">
+        <v>46219.0</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D43" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" s="9">
+        <v>152833.0</v>
+      </c>
+      <c r="G43" s="9">
+        <v>50641.0</v>
+      </c>
+      <c r="H43" s="9">
+        <v>96472.0</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" hidden="1" customHeight="1">
+      <c r="A44" s="5">
+        <v>46219.0</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" s="9">
+        <v>237828.0</v>
+      </c>
+      <c r="G44" s="9">
+        <v>173585.0</v>
+      </c>
+      <c r="H44" s="9">
+        <v>71560.0</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" s="12"/>
+    </row>
+    <row r="45" ht="22.5" hidden="1" customHeight="1">
+      <c r="A45" s="5">
+        <v>46219.0</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D45" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F45" s="9">
+        <v>31125.0</v>
+      </c>
+      <c r="G45" s="9">
+        <v>7815.0</v>
+      </c>
+      <c r="H45" s="9">
+        <v>31845.0</v>
+      </c>
+      <c r="I45" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="8">
-        <v>130320.0</v>
-      </c>
-      <c r="G41" s="8">
-        <v>47410.0</v>
-      </c>
-      <c r="H41" s="8">
-        <v>90480.0</v>
-      </c>
-      <c r="I41" s="13" t="s">
+      <c r="J45" s="12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" hidden="1" customHeight="1">
+      <c r="A46" s="5">
+        <v>46219.0</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D46" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46" s="9">
+        <v>25746.0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>6168.0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>28683.0</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" ht="22.5" hidden="1" customHeight="1">
+      <c r="A47" s="5">
+        <v>46220.0</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D47" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" s="9">
+        <v>261166.0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>74573.0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>221549.0</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" ht="22.5" hidden="1" customHeight="1">
+      <c r="A48" s="5">
+        <v>46220.0</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D48" s="9">
+        <v>2110217.0</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" s="9">
+        <v>115289.0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>26931.0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>119584.0</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" s="12"/>
+    </row>
+    <row r="49" ht="22.5" hidden="1" customHeight="1">
+      <c r="A49" s="5">
+        <v>46224.0</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" s="9">
+        <v>398570.0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>288226.0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>287235.0</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" ht="22.5" hidden="1" customHeight="1">
+      <c r="A50" s="5">
+        <v>46224.0</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" s="9">
+        <v>745107.0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>378927.0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>551645.0</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" ht="22.5" hidden="1" customHeight="1">
+      <c r="A51" s="5">
+        <v>46225.0</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" s="9">
+        <v>130560.0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>52658.0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>153840.0</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" hidden="1" customHeight="1">
+      <c r="A52" s="5">
+        <v>46225.0</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J41" s="11" t="s">
+      <c r="C52" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D52" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52" s="9">
+        <v>87447.0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>59056.0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>104365.0</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J52" s="12"/>
+    </row>
+    <row r="53" ht="22.5" hidden="1" customHeight="1">
+      <c r="A53" s="5">
+        <v>46225.0</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" s="9">
+        <v>25200.0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>2085.0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>25920.0</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" hidden="1" customHeight="1">
+      <c r="A54" s="5">
+        <v>46226.0</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="9">
+        <v>285405.0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>203180.0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>226069.0</v>
+      </c>
+      <c r="I54" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" hidden="1" customHeight="1">
+      <c r="A55" s="5">
+        <v>46226.0</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="9">
+        <v>692280.0</v>
+      </c>
+      <c r="G55" s="9">
+        <v>118381.0</v>
+      </c>
+      <c r="H55" s="9">
+        <v>700200.0</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J55" s="12"/>
+    </row>
+    <row r="56" ht="22.5" hidden="1" customHeight="1">
+      <c r="A56" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="9">
+        <v>700200.0</v>
+      </c>
+      <c r="G56" s="9">
+        <v>112628.0</v>
+      </c>
+      <c r="H56" s="9">
+        <v>668440.0</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" s="12"/>
+    </row>
+    <row r="57" ht="22.5" hidden="1" customHeight="1">
+      <c r="A57" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D57" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" s="9">
+        <v>226069.0</v>
+      </c>
+      <c r="G57" s="9">
+        <v>193130.0</v>
+      </c>
+      <c r="H57" s="9">
+        <v>326391.0</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" ht="22.5" hidden="1" customHeight="1">
+      <c r="A58" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D58" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="9">
+        <v>144637.0</v>
+      </c>
+      <c r="G58" s="9">
+        <v>64227.0</v>
+      </c>
+      <c r="H58" s="9">
+        <v>128160.0</v>
+      </c>
+      <c r="I58" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J58" s="12"/>
+    </row>
+    <row r="59" ht="22.5" hidden="1" customHeight="1">
+      <c r="A59" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="4">
-        <v>46219.0</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" s="8">
+      <c r="D59" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" s="9">
+        <v>295359.0</v>
+      </c>
+      <c r="G59" s="9">
+        <v>126369.0</v>
+      </c>
+      <c r="H59" s="9">
+        <v>166642.0</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" ht="22.5" hidden="1" customHeight="1">
+      <c r="A60" s="5">
+        <v>46230.0</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D60" s="9">
+        <v>2110403.0</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F60" s="9">
+        <v>9960.0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>6018.0</v>
+      </c>
+      <c r="H60" s="9">
+        <v>3660.0</v>
+      </c>
+      <c r="I60" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J60" s="12"/>
+    </row>
+    <row r="61" ht="22.5" hidden="1" customHeight="1">
+      <c r="A61" s="5">
+        <v>46230.0</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D61" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61" s="9">
+        <v>306720.0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>164175.0</v>
+      </c>
+      <c r="H61" s="9">
+        <v>247096.0</v>
+      </c>
+      <c r="I61" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" s="12"/>
+    </row>
+    <row r="62" ht="22.5" hidden="1" customHeight="1">
+      <c r="A62" s="5">
+        <v>46230.0</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="9">
+        <v>437080.0</v>
+      </c>
+      <c r="G62" s="9">
+        <v>277785.0</v>
+      </c>
+      <c r="H62" s="9">
+        <v>353700.0</v>
+      </c>
+      <c r="I62" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J62" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="63" ht="22.5" hidden="1" customHeight="1">
+      <c r="A63" s="5">
+        <v>46231.0</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" s="9">
+        <v>165466.0</v>
+      </c>
+      <c r="G63" s="9">
+        <v>113462.0</v>
+      </c>
+      <c r="H63" s="9">
+        <v>375549.0</v>
+      </c>
+      <c r="I63" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="64" ht="22.5" hidden="1" customHeight="1">
+      <c r="A64" s="5">
+        <v>46231.0</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D64" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64" s="9">
+        <v>238497.0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>56526.0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>181858.0</v>
+      </c>
+      <c r="I64" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" ht="22.5" hidden="1" customHeight="1">
+      <c r="A65" s="5">
+        <v>46231.0</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D65" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F65" s="9">
+        <v>8190.0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>2049.0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>7200.0</v>
+      </c>
+      <c r="I65" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" ht="22.5" hidden="1" customHeight="1">
+      <c r="A66" s="5">
+        <v>46231.0</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D66" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="9">
+        <v>146224.0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>78064.0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>98850.0</v>
+      </c>
+      <c r="I66" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" ht="22.5" hidden="1" customHeight="1">
+      <c r="A67" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C67" s="21"/>
+      <c r="D67" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="9">
+        <v>14599.0</v>
+      </c>
+      <c r="G67" s="9">
+        <v>3782.0</v>
+      </c>
+      <c r="H67" s="9">
+        <v>7263.0</v>
+      </c>
+      <c r="I67" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" s="12"/>
+    </row>
+    <row r="68" ht="22.5" hidden="1" customHeight="1">
+      <c r="A68" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" s="21"/>
+      <c r="D68" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" s="9">
+        <v>22080.0</v>
+      </c>
+      <c r="G68" s="9">
+        <v>5686.0</v>
+      </c>
+      <c r="H68" s="9">
+        <v>36720.0</v>
+      </c>
+      <c r="I68" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" s="12"/>
+    </row>
+    <row r="69" ht="22.5" hidden="1" customHeight="1">
+      <c r="A69" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" s="21"/>
+      <c r="D69" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" s="9">
+        <v>353905.0</v>
+      </c>
+      <c r="G69" s="9">
+        <v>208296.0</v>
+      </c>
+      <c r="H69" s="9">
+        <v>117570.0</v>
+      </c>
+      <c r="I69" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" s="12"/>
+    </row>
+    <row r="70" ht="22.5" hidden="1" customHeight="1">
+      <c r="A70" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" s="21"/>
+      <c r="D70" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F70" s="9">
+        <v>5913.0</v>
+      </c>
+      <c r="G70" s="9">
+        <v>902.0</v>
+      </c>
+      <c r="H70" s="9">
+        <v>5893.0</v>
+      </c>
+      <c r="I70" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" s="12"/>
+    </row>
+    <row r="71" ht="22.5" hidden="1" customHeight="1">
+      <c r="A71" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="21"/>
+      <c r="D71" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F71" s="9">
+        <v>256613.0</v>
+      </c>
+      <c r="G71" s="9">
+        <v>86092.0</v>
+      </c>
+      <c r="H71" s="9">
+        <v>142320.0</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" s="12"/>
+    </row>
+    <row r="72" ht="22.5" hidden="1" customHeight="1">
+      <c r="A72" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="21"/>
+      <c r="D72" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F72" s="9">
+        <v>21300.0</v>
+      </c>
+      <c r="G72" s="9">
+        <v>9765.0</v>
+      </c>
+      <c r="H72" s="9">
+        <v>18690.0</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="12"/>
+    </row>
+    <row r="73" ht="22.5" hidden="1" customHeight="1">
+      <c r="A73" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" s="21"/>
+      <c r="D73" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" s="9">
+        <v>351733.0</v>
+      </c>
+      <c r="G73" s="9">
+        <v>145994.0</v>
+      </c>
+      <c r="H73" s="9">
+        <v>200114.0</v>
+      </c>
+      <c r="I73" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="12"/>
+    </row>
+    <row r="74" ht="22.5" hidden="1" customHeight="1">
+      <c r="A74" s="18">
+        <v>46233.0</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D74" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74" s="9">
+        <v>158761.0</v>
+      </c>
+      <c r="G74" s="9">
+        <v>68908.0</v>
+      </c>
+      <c r="H74" s="9">
+        <v>183014.0</v>
+      </c>
+      <c r="I74" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="75" ht="22.5" hidden="1" customHeight="1">
+      <c r="A75" s="18">
+        <v>46233.0</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D75" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F75" s="9">
+        <v>117430.0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>57323.0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>86643.0</v>
+      </c>
+      <c r="I75" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J75" s="12"/>
+    </row>
+    <row r="76" ht="22.5" hidden="1" customHeight="1">
+      <c r="A76" s="5">
+        <v>46234.0</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D76" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F76" s="9">
+        <v>265693.0</v>
+      </c>
+      <c r="G76" s="9">
+        <v>83477.0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>116000.0</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J76" s="12"/>
+    </row>
+    <row r="77" ht="22.5" hidden="1" customHeight="1">
+      <c r="A77" s="5">
+        <v>46234.0</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D77" s="9">
+        <v>112357.0</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F77" s="9">
+        <v>720.0</v>
+      </c>
+      <c r="G77" s="9">
+        <v>360.0</v>
+      </c>
+      <c r="H77" s="9">
+        <v>2040.0</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="78" ht="22.5" hidden="1" customHeight="1">
+      <c r="A78" s="5">
+        <v>46234.0</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D78" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F78" s="9">
+        <v>5580.0</v>
+      </c>
+      <c r="G78" s="9">
+        <v>2192.0</v>
+      </c>
+      <c r="H78" s="9">
+        <v>3984.0</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="79" ht="22.5" hidden="1" customHeight="1">
+      <c r="A79" s="19">
+        <v>46237.0</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D79" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="9">
+        <v>192903.0</v>
+      </c>
+      <c r="G79" s="9">
+        <v>150030.0</v>
+      </c>
+      <c r="H79" s="9">
+        <v>77501.0</v>
+      </c>
+      <c r="I79" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="80" ht="22.5" hidden="1" customHeight="1">
+      <c r="A80" s="19">
+        <v>46237.0</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D80" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F80" s="9">
+        <v>152062.0</v>
+      </c>
+      <c r="G80" s="9">
+        <v>112769.0</v>
+      </c>
+      <c r="H80" s="9">
+        <v>124423.0</v>
+      </c>
+      <c r="I80" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="81" ht="22.5" hidden="1" customHeight="1">
+      <c r="A81" s="19">
+        <v>46237.0</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D81" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F81" s="9">
+        <v>153692.0</v>
+      </c>
+      <c r="G81" s="9">
+        <v>136980.0</v>
+      </c>
+      <c r="H81" s="9">
+        <v>63920.0</v>
+      </c>
+      <c r="I81" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="82" ht="22.5" hidden="1" customHeight="1">
+      <c r="A82" s="19">
+        <v>46237.0</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D82" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" s="9">
+        <v>45564.0</v>
+      </c>
+      <c r="G82" s="9">
+        <v>10456.0</v>
+      </c>
+      <c r="H82" s="9">
+        <v>40560.0</v>
+      </c>
+      <c r="I82" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" s="12"/>
+    </row>
+    <row r="83" ht="22.5" hidden="1" customHeight="1">
+      <c r="A83" s="19">
+        <v>46237.0</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F83" s="9">
+        <v>93517.0</v>
+      </c>
+      <c r="G83" s="9">
+        <v>18622.0</v>
+      </c>
+      <c r="H83" s="9">
+        <v>48804.0</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="84" ht="22.5" customHeight="1">
+      <c r="A84" s="5">
+        <v>46238.0</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D84" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F84" s="9">
+        <v>43200.0</v>
+      </c>
+      <c r="G84" s="9">
+        <v>5340.0</v>
+      </c>
+      <c r="H84" s="9">
+        <v>40890.0</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J84" s="12"/>
+    </row>
+    <row r="85" ht="22.5" customHeight="1">
+      <c r="A85" s="5">
+        <v>46238.0</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D85" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F85" s="9">
+        <v>25350.0</v>
+      </c>
+      <c r="G85" s="9">
+        <v>6240.0</v>
+      </c>
+      <c r="H85" s="9">
+        <v>30750.0</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J85" s="12"/>
+    </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="A86" s="5">
+        <v>46238.0</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D86" s="9">
         <v>2152388.0</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F42" s="8">
-        <v>36225.0</v>
-      </c>
-      <c r="G42" s="8">
-        <v>11746.0</v>
-      </c>
-      <c r="H42" s="8">
-        <v>27570.0</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="11"/>
-    </row>
-    <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="4">
-        <v>46219.0</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="E86" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F86" s="9">
+        <v>5040.0</v>
+      </c>
+      <c r="G86" s="9">
+        <v>720.0</v>
+      </c>
+      <c r="H86" s="9">
+        <v>4680.0</v>
+      </c>
+      <c r="I86" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J86" s="12"/>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="5">
+        <v>46238.0</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C87" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D43" s="8">
+      <c r="D87" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E87" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" s="9">
+        <v>124423.0</v>
+      </c>
+      <c r="G87" s="9">
+        <v>60002.0</v>
+      </c>
+      <c r="H87" s="9">
+        <v>69217.0</v>
+      </c>
+      <c r="I87" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F43" s="8">
-        <v>152833.0</v>
-      </c>
-      <c r="G43" s="8">
-        <v>50641.0</v>
-      </c>
-      <c r="H43" s="8">
-        <v>96472.0</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="4">
-        <v>46219.0</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="8">
+      <c r="J87" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="88" ht="22.5" customHeight="1">
+      <c r="A88" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D88" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="9">
+        <v>30750.0</v>
+      </c>
+      <c r="G88" s="9">
+        <v>9975.0</v>
+      </c>
+      <c r="H88" s="9">
+        <v>36300.0</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" s="12"/>
+    </row>
+    <row r="89" ht="22.5" customHeight="1">
+      <c r="A89" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D89" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E89" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F89" s="9">
+        <v>58320.0</v>
+      </c>
+      <c r="G89" s="9">
+        <v>53468.0</v>
+      </c>
+      <c r="H89" s="9">
+        <v>12480.0</v>
+      </c>
+      <c r="I89" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F44" s="8">
-        <v>237828.0</v>
-      </c>
-      <c r="G44" s="8">
-        <v>173585.0</v>
-      </c>
-      <c r="H44" s="8">
-        <v>71560.0</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" s="11"/>
-    </row>
-    <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="4">
-        <v>46219.0</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D45" s="8">
-        <v>152384.0</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F45" s="8">
-        <v>31125.0</v>
-      </c>
-      <c r="G45" s="8">
-        <v>7815.0</v>
-      </c>
-      <c r="H45" s="8">
-        <v>31845.0</v>
-      </c>
-      <c r="I45" s="13" t="s">
+      <c r="J89" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="90" ht="22.5" customHeight="1">
+      <c r="A90" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D90" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="9">
+        <v>254880.0</v>
+      </c>
+      <c r="G90" s="9">
+        <v>151786.0</v>
+      </c>
+      <c r="H90" s="9">
+        <v>27180.0</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="91" ht="22.5" customHeight="1">
+      <c r="A91" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D91" s="9">
+        <v>112379.0</v>
+      </c>
+      <c r="E91" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J45" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="4">
-        <v>46219.0</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D46" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F46" s="8">
-        <v>25746.0</v>
-      </c>
-      <c r="G46" s="8">
-        <v>6168.0</v>
-      </c>
-      <c r="H46" s="8">
-        <v>28683.0</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="4">
-        <v>46220.0</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D47" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E47" s="5" t="s">
+      <c r="F91" s="9">
+        <v>13800.0</v>
+      </c>
+      <c r="G91" s="9">
+        <v>900.0</v>
+      </c>
+      <c r="H91" s="9">
+        <v>12132.0</v>
+      </c>
+      <c r="I91" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="F47" s="8">
-        <v>261166.0</v>
-      </c>
-      <c r="G47" s="8">
-        <v>74573.0</v>
-      </c>
-      <c r="H47" s="8">
-        <v>221549.0</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="4">
-        <v>46220.0</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" s="8">
-        <v>2110217.0</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F48" s="8">
-        <v>115289.0</v>
-      </c>
-      <c r="G48" s="8">
-        <v>26931.0</v>
-      </c>
-      <c r="H48" s="8">
-        <v>119584.0</v>
-      </c>
-      <c r="I48" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J48" s="11"/>
-    </row>
-    <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="4">
-        <v>46224.0</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="8">
-        <v>398570.0</v>
-      </c>
-      <c r="G49" s="8">
-        <v>288226.0</v>
-      </c>
-      <c r="H49" s="8">
-        <v>287235.0</v>
-      </c>
-      <c r="I49" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="4">
-        <v>46224.0</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D50" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="8">
-        <v>745107.0</v>
-      </c>
-      <c r="G50" s="8">
-        <v>378927.0</v>
-      </c>
-      <c r="H50" s="8">
-        <v>551645.0</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D51" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F51" s="8">
-        <v>130560.0</v>
-      </c>
-      <c r="G51" s="8">
-        <v>52658.0</v>
-      </c>
-      <c r="H51" s="8">
-        <v>153840.0</v>
-      </c>
-      <c r="I51" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D52" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F52" s="8">
-        <v>87447.0</v>
-      </c>
-      <c r="G52" s="8">
-        <v>59056.0</v>
-      </c>
-      <c r="H52" s="8">
-        <v>104365.0</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J52" s="11"/>
-    </row>
-    <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D53" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="8">
-        <v>25200.0</v>
-      </c>
-      <c r="G53" s="8">
-        <v>2085.0</v>
-      </c>
-      <c r="H53" s="8">
-        <v>25920.0</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="54" ht="22.5" hidden="1" customHeight="1">
-      <c r="A54" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D54" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="8">
-        <v>285405.0</v>
-      </c>
-      <c r="G54" s="8">
-        <v>203180.0</v>
-      </c>
-      <c r="H54" s="8">
-        <v>226069.0</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" ht="22.5" hidden="1" customHeight="1">
-      <c r="A55" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" s="8">
-        <v>692280.0</v>
-      </c>
-      <c r="G55" s="8">
-        <v>118381.0</v>
-      </c>
-      <c r="H55" s="8">
-        <v>700200.0</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J55" s="11"/>
-    </row>
-    <row r="56" ht="22.5" hidden="1" customHeight="1">
-      <c r="A56" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D56" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F56" s="8">
-        <v>700200.0</v>
-      </c>
-      <c r="G56" s="8">
-        <v>112628.0</v>
-      </c>
-      <c r="H56" s="8">
-        <v>668440.0</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J56" s="11"/>
-    </row>
-    <row r="57" ht="22.5" hidden="1" customHeight="1">
-      <c r="A57" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D57" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="8">
-        <v>226069.0</v>
-      </c>
-      <c r="G57" s="8">
-        <v>193130.0</v>
-      </c>
-      <c r="H57" s="8">
-        <v>326391.0</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="58" ht="22.5" hidden="1" customHeight="1">
-      <c r="A58" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D58" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" s="8">
-        <v>144637.0</v>
-      </c>
-      <c r="G58" s="8">
-        <v>64227.0</v>
-      </c>
-      <c r="H58" s="8">
-        <v>128160.0</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J58" s="11"/>
-    </row>
-    <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D59" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="8">
-        <v>295359.0</v>
-      </c>
-      <c r="G59" s="8">
-        <v>126369.0</v>
-      </c>
-      <c r="H59" s="8">
-        <v>166642.0</v>
-      </c>
-      <c r="I59" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="4">
-        <v>46230.0</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D60" s="8">
-        <v>2110403.0</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F60" s="8">
-        <v>9960.0</v>
-      </c>
-      <c r="G60" s="8">
-        <v>6018.0</v>
-      </c>
-      <c r="H60" s="8">
-        <v>3660.0</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J60" s="11"/>
-    </row>
-    <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="4">
-        <v>46230.0</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D61" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F61" s="8">
-        <v>306720.0</v>
-      </c>
-      <c r="G61" s="8">
-        <v>164175.0</v>
-      </c>
-      <c r="H61" s="8">
-        <v>247096.0</v>
-      </c>
-      <c r="I61" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J61" s="11"/>
-    </row>
-    <row r="62" ht="22.5" hidden="1" customHeight="1">
-      <c r="A62" s="4">
-        <v>46230.0</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D62" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F62" s="8">
-        <v>437080.0</v>
-      </c>
-      <c r="G62" s="8">
-        <v>277785.0</v>
-      </c>
-      <c r="H62" s="8">
-        <v>353700.0</v>
-      </c>
-      <c r="I62" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="63" ht="22.5" hidden="1" customHeight="1">
-      <c r="A63" s="4">
-        <v>46231.0</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D63" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="8">
-        <v>165466.0</v>
-      </c>
-      <c r="G63" s="8">
-        <v>113462.0</v>
-      </c>
-      <c r="H63" s="8">
-        <v>375549.0</v>
-      </c>
-      <c r="I63" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="64" ht="22.5" hidden="1" customHeight="1">
-      <c r="A64" s="4">
-        <v>46231.0</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D64" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F64" s="8">
-        <v>238497.0</v>
-      </c>
-      <c r="G64" s="8">
-        <v>56526.0</v>
-      </c>
-      <c r="H64" s="8">
-        <v>181858.0</v>
-      </c>
-      <c r="I64" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="65" ht="22.5" hidden="1" customHeight="1">
-      <c r="A65" s="4">
-        <v>46231.0</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D65" s="8">
-        <v>2110317.0</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F65" s="8">
-        <v>8190.0</v>
-      </c>
-      <c r="G65" s="8">
-        <v>2049.0</v>
-      </c>
-      <c r="H65" s="8">
-        <v>7200.0</v>
-      </c>
-      <c r="I65" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="66" ht="22.5" hidden="1" customHeight="1">
-      <c r="A66" s="4">
-        <v>46231.0</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D66" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F66" s="8">
-        <v>146224.0</v>
-      </c>
-      <c r="G66" s="8">
-        <v>78064.0</v>
-      </c>
-      <c r="H66" s="8">
-        <v>98850.0</v>
-      </c>
-      <c r="I66" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="67" ht="22.5" hidden="1" customHeight="1">
-      <c r="A67" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C67" s="21"/>
-      <c r="D67" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F67" s="8">
-        <v>14599.0</v>
-      </c>
-      <c r="G67" s="8">
-        <v>3782.0</v>
-      </c>
-      <c r="H67" s="8">
-        <v>7263.0</v>
-      </c>
-      <c r="I67" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J67" s="11"/>
-    </row>
-    <row r="68" ht="22.5" hidden="1" customHeight="1">
-      <c r="A68" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C68" s="21"/>
-      <c r="D68" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="8">
-        <v>22080.0</v>
-      </c>
-      <c r="G68" s="8">
-        <v>5686.0</v>
-      </c>
-      <c r="H68" s="8">
-        <v>36720.0</v>
-      </c>
-      <c r="I68" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J68" s="11"/>
-    </row>
-    <row r="69" ht="22.5" hidden="1" customHeight="1">
-      <c r="A69" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C69" s="21"/>
-      <c r="D69" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="8">
-        <v>353905.0</v>
-      </c>
-      <c r="G69" s="8">
-        <v>208296.0</v>
-      </c>
-      <c r="H69" s="8">
-        <v>117570.0</v>
-      </c>
-      <c r="I69" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J69" s="11"/>
-    </row>
-    <row r="70" ht="22.5" hidden="1" customHeight="1">
-      <c r="A70" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C70" s="21"/>
-      <c r="D70" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F70" s="8">
-        <v>5913.0</v>
-      </c>
-      <c r="G70" s="8">
-        <v>902.0</v>
-      </c>
-      <c r="H70" s="8">
-        <v>5893.0</v>
-      </c>
-      <c r="I70" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J70" s="11"/>
-    </row>
-    <row r="71" ht="22.5" hidden="1" customHeight="1">
-      <c r="A71" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F71" s="8">
-        <v>256613.0</v>
-      </c>
-      <c r="G71" s="8">
-        <v>86092.0</v>
-      </c>
-      <c r="H71" s="8">
-        <v>142320.0</v>
-      </c>
-      <c r="I71" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J71" s="11"/>
-    </row>
-    <row r="72" ht="22.5" hidden="1" customHeight="1">
-      <c r="A72" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="8">
-        <v>152384.0</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F72" s="8">
-        <v>21300.0</v>
-      </c>
-      <c r="G72" s="8">
-        <v>9765.0</v>
-      </c>
-      <c r="H72" s="8">
-        <v>18690.0</v>
-      </c>
-      <c r="I72" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J72" s="11"/>
-    </row>
-    <row r="73" ht="22.5" hidden="1" customHeight="1">
-      <c r="A73" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="8">
-        <v>351733.0</v>
-      </c>
-      <c r="G73" s="8">
-        <v>145994.0</v>
-      </c>
-      <c r="H73" s="8">
-        <v>200114.0</v>
-      </c>
-      <c r="I73" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J73" s="11"/>
-    </row>
-    <row r="74" ht="22.5" hidden="1" customHeight="1">
-      <c r="A74" s="19">
-        <v>46233.0</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C74" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D74" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F74" s="8">
-        <v>158761.0</v>
-      </c>
-      <c r="G74" s="8">
-        <v>68908.0</v>
-      </c>
-      <c r="H74" s="8">
-        <v>183014.0</v>
-      </c>
-      <c r="I74" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="75" ht="22.5" hidden="1" customHeight="1">
-      <c r="A75" s="19">
-        <v>46233.0</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D75" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F75" s="8">
-        <v>117430.0</v>
-      </c>
-      <c r="G75" s="8">
-        <v>57323.0</v>
-      </c>
-      <c r="H75" s="8">
-        <v>86643.0</v>
-      </c>
-      <c r="I75" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J75" s="11"/>
-    </row>
-    <row r="76" ht="22.5" hidden="1" customHeight="1">
-      <c r="A76" s="4">
-        <v>46234.0</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D76" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F76" s="8">
-        <v>265693.0</v>
-      </c>
-      <c r="G76" s="8">
-        <v>83477.0</v>
-      </c>
-      <c r="H76" s="8">
-        <v>116000.0</v>
-      </c>
-      <c r="I76" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J76" s="11"/>
-    </row>
-    <row r="77" ht="22.5" hidden="1" customHeight="1">
-      <c r="A77" s="4">
-        <v>46234.0</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D77" s="8">
-        <v>112357.0</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F77" s="8">
-        <v>720.0</v>
-      </c>
-      <c r="G77" s="8">
-        <v>360.0</v>
-      </c>
-      <c r="H77" s="8">
-        <v>2040.0</v>
-      </c>
-      <c r="I77" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J77" s="11" t="s">
+      <c r="J91" s="12"/>
+    </row>
+    <row r="92" ht="22.5" customHeight="1">
+      <c r="A92" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B92" s="6" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="78" ht="22.5" hidden="1" customHeight="1">
-      <c r="A78" s="4">
-        <v>46234.0</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D78" s="8">
-        <v>2110317.0</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F78" s="8">
-        <v>5580.0</v>
-      </c>
-      <c r="G78" s="8">
-        <v>2192.0</v>
-      </c>
-      <c r="H78" s="8">
-        <v>3984.0</v>
-      </c>
-      <c r="I78" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J78" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="79" ht="22.5" hidden="1" customHeight="1">
-      <c r="A79" s="18">
-        <v>46237.0</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D79" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F79" s="8">
-        <v>192903.0</v>
-      </c>
-      <c r="G79" s="8">
-        <v>150030.0</v>
-      </c>
-      <c r="H79" s="8">
-        <v>77501.0</v>
-      </c>
-      <c r="I79" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="80" ht="22.5" hidden="1" customHeight="1">
-      <c r="A80" s="18">
-        <v>46237.0</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D80" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F80" s="8">
-        <v>152062.0</v>
-      </c>
-      <c r="G80" s="8">
-        <v>112769.0</v>
-      </c>
-      <c r="H80" s="8">
-        <v>124423.0</v>
-      </c>
-      <c r="I80" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="81" ht="22.5" hidden="1" customHeight="1">
-      <c r="A81" s="18">
-        <v>46237.0</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D81" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F81" s="8">
-        <v>153692.0</v>
-      </c>
-      <c r="G81" s="8">
-        <v>136980.0</v>
-      </c>
-      <c r="H81" s="8">
-        <v>63920.0</v>
-      </c>
-      <c r="I81" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="82" ht="22.5" hidden="1" customHeight="1">
-      <c r="A82" s="18">
-        <v>46237.0</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D82" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="8">
-        <v>45564.0</v>
-      </c>
-      <c r="G82" s="8">
-        <v>10456.0</v>
-      </c>
-      <c r="H82" s="8">
-        <v>40560.0</v>
-      </c>
-      <c r="I82" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="11"/>
-    </row>
-    <row r="83" ht="22.5" hidden="1" customHeight="1">
-      <c r="A83" s="18">
-        <v>46237.0</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D83" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F83" s="8">
-        <v>93517.0</v>
-      </c>
-      <c r="G83" s="8">
-        <v>18622.0</v>
-      </c>
-      <c r="H83" s="8">
-        <v>48804.0</v>
-      </c>
-      <c r="I83" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="84" ht="22.5" customHeight="1">
-      <c r="A84" s="4">
-        <v>46238.0</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D84" s="8">
-        <v>2110317.0</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F84" s="8">
-        <v>43200.0</v>
-      </c>
-      <c r="G84" s="8">
-        <v>5340.0</v>
-      </c>
-      <c r="H84" s="8">
-        <v>40890.0</v>
-      </c>
-      <c r="I84" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J84" s="11"/>
-    </row>
-    <row r="85" ht="22.5" customHeight="1">
-      <c r="A85" s="4">
-        <v>46238.0</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D85" s="8">
-        <v>152384.0</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F85" s="8">
-        <v>25350.0</v>
-      </c>
-      <c r="G85" s="8">
-        <v>6240.0</v>
-      </c>
-      <c r="H85" s="8">
-        <v>30750.0</v>
-      </c>
-      <c r="I85" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J85" s="11"/>
-    </row>
-    <row r="86" ht="22.5" customHeight="1">
-      <c r="A86" s="4">
-        <v>46238.0</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D86" s="8">
+      <c r="C92" s="21"/>
+      <c r="D92" s="9">
         <v>2152388.0</v>
       </c>
-      <c r="E86" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F86" s="8">
-        <v>5040.0</v>
-      </c>
-      <c r="G86" s="8">
-        <v>720.0</v>
-      </c>
-      <c r="H86" s="8">
-        <v>4680.0</v>
-      </c>
-      <c r="I86" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J86" s="11"/>
-    </row>
-    <row r="87" ht="22.5" customHeight="1">
-      <c r="A87" s="4">
-        <v>46238.0</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D87" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F87" s="8">
-        <v>124423.0</v>
-      </c>
-      <c r="G87" s="8">
-        <v>60002.0</v>
-      </c>
-      <c r="H87" s="8">
-        <v>69217.0</v>
-      </c>
-      <c r="I87" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="88" ht="22.5" customHeight="1">
-      <c r="A88" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D88" s="8">
-        <v>152384.0</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F88" s="8">
-        <v>30750.0</v>
-      </c>
-      <c r="G88" s="8">
-        <v>9975.0</v>
-      </c>
-      <c r="H88" s="8">
-        <v>36300.0</v>
-      </c>
-      <c r="I88" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J88" s="11"/>
-    </row>
-    <row r="89" ht="22.5" customHeight="1">
-      <c r="A89" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D89" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F89" s="8">
-        <v>58320.0</v>
-      </c>
-      <c r="G89" s="8">
-        <v>53468.0</v>
-      </c>
-      <c r="H89" s="8">
-        <v>12480.0</v>
-      </c>
-      <c r="I89" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J89" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="I90" s="20"/>
-    </row>
-    <row r="91">
-      <c r="I91" s="20"/>
-    </row>
-    <row r="92">
-      <c r="I92" s="20"/>
+      <c r="E92" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F92" s="9">
+        <v>4575.0</v>
+      </c>
+      <c r="G92" s="9">
+        <v>570.0</v>
+      </c>
+      <c r="H92" s="9">
+        <v>4213.0</v>
+      </c>
+      <c r="I92" s="13"/>
+      <c r="J92" s="12"/>
     </row>
     <row r="93">
       <c r="I93" s="20"/>
@@ -6371,13 +6462,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I89">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I92">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I90:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I93:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A89">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A92">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -6440,1508 +6531,1610 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>46224.0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8">
+      <c r="B2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="9">
+        <v>333.0</v>
+      </c>
+      <c r="G2" s="9">
+        <v>6480.0</v>
+      </c>
+      <c r="H2" s="9">
+        <v>3712.0</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" hidden="1" customHeight="1">
+      <c r="A3" s="5">
+        <v>46224.0</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9">
+        <v>2114158.0</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="G3" s="9">
+        <v>1000.0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>60.0</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
+      <c r="A4" s="5">
+        <v>46225.0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="9">
+        <v>10501.0</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="9">
+        <v>415093.0</v>
+      </c>
+      <c r="G4" s="9">
+        <v>115920.0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>543038.0</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
+      <c r="A5" s="5">
+        <v>46225.0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="9">
+        <v>112379.0</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="9">
+        <v>3000.0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>29400.0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>3000.0</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="5">
+        <v>46225.0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="9">
+        <v>3000.0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>12300.0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>3300.0</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="5">
+        <v>46225.0</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="9">
+        <v>132357.0</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="9">
+        <v>1560.0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>1560.0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>4560.0</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="5">
+        <v>46225.0</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="9">
+        <v>720.0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>11160.0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>5940.0</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
+      <c r="A9" s="5">
+        <v>46225.0</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="9">
+        <v>3712.0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>46723.0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>213.0</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
+      <c r="A10" s="5">
+        <v>46226.0</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="9">
+        <v>73001.0</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="9">
+        <v>73787.0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>72000.0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>109487.0</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="5">
+        <v>46226.0</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="9">
+        <v>3300.0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>1800.0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>3300.0</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="12"/>
+    </row>
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
+      <c r="A12" s="5">
+        <v>46226.0</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="9">
+        <v>112379.0</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="9">
+        <v>4200.0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>7500.0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>3900.0</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="12"/>
+    </row>
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
+      <c r="A13" s="5">
+        <v>46226.0</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="8">
-        <v>333.0</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="F13" s="9">
+        <v>379471.0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>392580.0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>357186.0</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
+      <c r="A14" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="9">
+        <v>72001.0</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="9">
+        <v>21905.0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>47670.0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>38000.0</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="9">
+        <v>2110327.0</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="9">
+        <v>69120.0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>57600.0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>40320.0</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
+      <c r="A16" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="9">
+        <v>112379.0</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="9">
+        <v>3900.0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>102600.0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>1500.0</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" ht="22.5" hidden="1" customHeight="1">
+      <c r="A17" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="9">
+        <v>720.0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>9720.0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>2580.0</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="12"/>
+    </row>
+    <row r="18" ht="22.5" hidden="1" customHeight="1">
+      <c r="A18" s="5">
+        <v>46227.0</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="9">
+        <v>3300.0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>30600.0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>600.0</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
+      <c r="A19" s="5">
+        <v>46230.0</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="9">
+        <v>2410401.0</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="9">
+        <v>136538.0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>34080.0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>213000.0</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
+      <c r="A20" s="5">
+        <v>46231.0</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="9">
+        <v>591750.0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>239760.0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>577207.0</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
+      <c r="A21" s="5">
+        <v>46231.0</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="9">
+        <v>10601.0</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="9">
+        <v>1230.0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>8626.0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>1958.0</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" hidden="1" customHeight="1">
+      <c r="A22" s="5">
+        <v>46231.0</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="9">
+        <v>4320.0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>2700.0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>3420.0</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="12"/>
+    </row>
+    <row r="23" ht="22.5" hidden="1" customHeight="1">
+      <c r="A23" s="5">
+        <v>46231.0</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="9">
+        <v>114357.0</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="9">
+        <v>240.0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>52320.0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>240.0</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="12"/>
+    </row>
+    <row r="24" ht="22.5" hidden="1" customHeight="1">
+      <c r="A24" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="9">
+        <v>10501.0</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="9">
+        <v>19663.0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>49540.0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>29632.0</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="12"/>
+    </row>
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
+      <c r="A25" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="9">
+        <v>5700.0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>34800.0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>5100.0</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
+      <c r="A26" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="9">
+        <v>720.0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>7920.0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>720.0</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="12"/>
+    </row>
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
+      <c r="A27" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="9">
+        <v>2114357.0</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" s="9">
+        <v>432.0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>576.0</v>
+      </c>
+      <c r="H27" s="9">
+        <v>432.0</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="12"/>
+    </row>
+    <row r="28" ht="22.5" hidden="1" customHeight="1">
+      <c r="A28" s="5">
+        <v>46232.0</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="9">
+        <v>10501.0</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="9">
+        <v>219540.0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>272160.0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>16698.0</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="12"/>
+    </row>
+    <row r="29" ht="22.5" hidden="1" customHeight="1">
+      <c r="A29" s="5">
+        <v>46233.0</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="9">
+        <v>5100.0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>3300.0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>4800.0</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J29" s="12"/>
+    </row>
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
+      <c r="A30" s="5">
+        <v>46233.0</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="9">
+        <v>114357.0</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="9">
+        <v>240.0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>7800.0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>1560.0</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="12"/>
+    </row>
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="5">
+        <v>46233.0</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="9">
+        <v>10601.0</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="9">
+        <v>7717.0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>10080.0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>12867.0</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
+      <c r="A32" s="5">
+        <v>46234.0</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="9">
+        <v>79110.0</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="9">
+        <v>48000.0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>24600.0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>36300.0</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
+      <c r="A33" s="5">
+        <v>46234.0</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="9">
+        <v>10501.0</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="9">
+        <v>95574.0</v>
+      </c>
+      <c r="G33" s="9">
+        <v>78469.0</v>
+      </c>
+      <c r="H33" s="9">
+        <v>142801.0</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
+      <c r="A34" s="5">
+        <v>46234.0</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" s="9">
+        <v>73001.0</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34" s="9">
+        <v>73367.0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>94608.0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>39150.0</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="12"/>
+    </row>
+    <row r="35" ht="22.5" hidden="1" customHeight="1">
+      <c r="A35" s="5">
+        <v>46234.0</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="14"/>
+      <c r="D35" s="9">
+        <v>112357.0</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" s="9">
+        <v>840.0</v>
+      </c>
+      <c r="G35" s="9">
+        <v>5160.0</v>
+      </c>
+      <c r="H35" s="9">
+        <v>480.0</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="12"/>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="A36" s="19">
+        <v>46237.0</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="9">
+        <v>10601.0</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="9">
+        <v>17934.0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>64980.0</v>
+      </c>
+      <c r="H36" s="9">
+        <v>21714.0</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" customHeight="1">
+      <c r="A37" s="19">
+        <v>46237.0</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="14"/>
+      <c r="D37" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="9">
+        <v>194520.0</v>
+      </c>
+      <c r="G37" s="9">
+        <v>84060.0</v>
+      </c>
+      <c r="H37" s="9">
+        <v>122840.0</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="12"/>
+    </row>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="19">
+        <v>46237.0</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="14"/>
+      <c r="D38" s="9">
+        <v>114379.0</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="9">
+        <v>52200.0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>16200.0</v>
+      </c>
+      <c r="H38" s="9">
+        <v>7500.0</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J38" s="12"/>
+    </row>
+    <row r="39" ht="22.5" customHeight="1">
+      <c r="A39" s="19">
+        <v>46237.0</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="14"/>
+      <c r="D39" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="9">
+        <v>6450.0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>16920.0</v>
+      </c>
+      <c r="H39" s="9">
         <v>6480.0</v>
       </c>
-      <c r="H2" s="8">
-        <v>3712.0</v>
-      </c>
-      <c r="I2" s="10" t="s">
+      <c r="I39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" s="12"/>
+    </row>
+    <row r="40" ht="22.5" customHeight="1">
+      <c r="A40" s="19">
+        <v>46237.0</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F40" s="9">
+        <v>1398.0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>1320.0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>438.0</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" s="12"/>
+    </row>
+    <row r="41" ht="22.5" customHeight="1">
+      <c r="A41" s="5">
+        <v>46238.0</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="14"/>
+      <c r="D41" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F41" s="9">
+        <v>2460.0</v>
+      </c>
+      <c r="G41" s="9">
+        <v>17640.0</v>
+      </c>
+      <c r="H41" s="9">
+        <v>3240.0</v>
+      </c>
+      <c r="I41" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J41" s="12"/>
+    </row>
+    <row r="42" ht="22.5" customHeight="1">
+      <c r="A42" s="5">
+        <v>46238.0</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="14"/>
+      <c r="D42" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F42" s="9">
+        <v>3600.0</v>
+      </c>
+      <c r="G42" s="9">
+        <v>1500.0</v>
+      </c>
+      <c r="H42" s="9">
+        <v>3900.0</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" s="12"/>
+    </row>
+    <row r="43" ht="22.5" customHeight="1">
+      <c r="A43" s="5">
+        <v>46238.0</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="14"/>
+      <c r="D43" s="9">
+        <v>114379.0</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F43" s="9">
+        <v>7500.0</v>
+      </c>
+      <c r="G43" s="9">
+        <v>54900.0</v>
+      </c>
+      <c r="H43" s="9">
+        <v>8400.0</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" s="12"/>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="5">
+        <v>46238.0</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="14"/>
+      <c r="D44" s="9">
+        <v>114357.0</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F44" s="9">
+        <v>240.0</v>
+      </c>
+      <c r="G44" s="9">
+        <v>7680.0</v>
+      </c>
+      <c r="H44" s="9">
+        <v>360.0</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" s="12"/>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="14"/>
+      <c r="D45" s="9">
+        <v>10601.0</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" s="9">
+        <v>1115.0</v>
+      </c>
+      <c r="G45" s="9">
+        <v>5267.0</v>
+      </c>
+      <c r="H45" s="9">
+        <v>1590.0</v>
+      </c>
+      <c r="I45" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="4">
-        <v>46224.0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8">
-        <v>2114158.0</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="8">
-        <v>60.0</v>
-      </c>
-      <c r="G3" s="8">
-        <v>1000.0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>60.0</v>
-      </c>
-      <c r="I3" s="10" t="s">
+      <c r="J45" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="A46" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="14"/>
+      <c r="D46" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" s="9">
+        <v>114240.0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>79680.0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>191130.0</v>
+      </c>
+      <c r="I46" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="8">
+      <c r="J46" s="12"/>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="A47" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="14"/>
+      <c r="D47" s="9">
+        <v>2112207.0</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="9">
+        <v>1800.0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>1800.0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>1980.0</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J47" s="12"/>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F48" s="9">
+        <v>3900.0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>34200.0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>1200.0</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J48" s="12"/>
+    </row>
+    <row r="49" ht="22.5" customHeight="1">
+      <c r="A49" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" s="9">
+        <v>112357.0</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F49" s="9">
+        <v>600.0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>8400.0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>600.0</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J49" s="12"/>
+    </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="14"/>
+      <c r="D50" s="9">
+        <v>114268.0</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F50" s="9">
+        <v>2700.0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>5700.0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>300.0</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J50" s="12"/>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="14"/>
+      <c r="D51" s="9">
         <v>10501.0</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="8">
-        <v>415093.0</v>
-      </c>
-      <c r="G4" s="8">
-        <v>115920.0</v>
-      </c>
-      <c r="H4" s="8">
-        <v>543038.0</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="8">
+      <c r="E51" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="9">
+        <v>68651.0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>64050.0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>13421.0</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="14"/>
+      <c r="D52" s="9">
+        <v>72003.0</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F52" s="9">
+        <v>1391.0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>3885.0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>2407.0</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" s="12"/>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="14"/>
+      <c r="D53" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" s="9">
+        <v>2974.0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>1200.0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>3317.0</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="14"/>
+      <c r="D54" s="9">
         <v>112379.0</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="8">
-        <v>3000.0</v>
-      </c>
-      <c r="G5" s="8">
-        <v>29400.0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>3000.0</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="8">
-        <v>3000.0</v>
-      </c>
-      <c r="G6" s="8">
-        <v>12300.0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>3300.0</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="8">
-        <v>132357.0</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1560.0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1560.0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>4560.0</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="8">
-        <v>2152388.0</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="8">
-        <v>720.0</v>
-      </c>
-      <c r="G8" s="8">
-        <v>11160.0</v>
-      </c>
-      <c r="H8" s="8">
-        <v>5940.0</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="8">
-        <v>3712.0</v>
-      </c>
-      <c r="G9" s="8">
-        <v>46723.0</v>
-      </c>
-      <c r="H9" s="8">
-        <v>213.0</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="8">
+      <c r="E54" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F54" s="9">
+        <v>3600.0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>26100.0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>6900.0</v>
+      </c>
+      <c r="I54" s="11"/>
+      <c r="J54" s="12"/>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="14"/>
+      <c r="D55" s="9">
         <v>73001.0</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="8">
-        <v>73787.0</v>
-      </c>
-      <c r="G10" s="8">
-        <v>72000.0</v>
-      </c>
-      <c r="H10" s="8">
-        <v>109487.0</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="8">
-        <v>3300.0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>1800.0</v>
-      </c>
-      <c r="H11" s="8">
-        <v>3300.0</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="8">
-        <v>112379.0</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="8">
-        <v>4200.0</v>
-      </c>
-      <c r="G12" s="8">
-        <v>7500.0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>3900.0</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="8">
-        <v>379471.0</v>
-      </c>
-      <c r="G13" s="8">
-        <v>392580.0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>357186.0</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="8">
-        <v>72001.0</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="8">
-        <v>21905.0</v>
-      </c>
-      <c r="G14" s="8">
-        <v>47670.0</v>
-      </c>
-      <c r="H14" s="8">
-        <v>38000.0</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="8">
-        <v>2110327.0</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="8">
-        <v>69120.0</v>
-      </c>
-      <c r="G15" s="8">
-        <v>57600.0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>40320.0</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="8">
-        <v>112379.0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="8">
-        <v>3900.0</v>
-      </c>
-      <c r="G16" s="8">
-        <v>102600.0</v>
-      </c>
-      <c r="H16" s="8">
-        <v>1500.0</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="8">
-        <v>2152388.0</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="8">
-        <v>720.0</v>
-      </c>
-      <c r="G17" s="8">
-        <v>9720.0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>2580.0</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="8">
-        <v>3300.0</v>
-      </c>
-      <c r="G18" s="8">
-        <v>30600.0</v>
-      </c>
-      <c r="H18" s="8">
+      <c r="E55" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F55" s="9">
+        <v>2415.0</v>
+      </c>
+      <c r="G55" s="9">
+        <v>26490.0</v>
+      </c>
+      <c r="H55" s="9">
+        <v>2415.0</v>
+      </c>
+      <c r="I55" s="11"/>
+      <c r="J55" s="12"/>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="A56" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="14"/>
+      <c r="D56" s="9">
+        <v>112357.0</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F56" s="9">
         <v>600.0</v>
       </c>
-      <c r="I18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="4">
-        <v>46230.0</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="8">
-        <v>2410401.0</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" s="8">
-        <v>136538.0</v>
-      </c>
-      <c r="G19" s="8">
-        <v>34080.0</v>
-      </c>
-      <c r="H19" s="8">
-        <v>213000.0</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="4">
-        <v>46231.0</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="8">
-        <v>591750.0</v>
-      </c>
-      <c r="G20" s="8">
-        <v>239760.0</v>
-      </c>
-      <c r="H20" s="8">
-        <v>577207.0</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="4">
-        <v>46231.0</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="8">
-        <v>10601.0</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="8">
-        <v>1230.0</v>
-      </c>
-      <c r="G21" s="8">
-        <v>8626.0</v>
-      </c>
-      <c r="H21" s="8">
-        <v>1958.0</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="4">
-        <v>46231.0</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="8">
-        <v>2152388.0</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" s="8">
-        <v>4320.0</v>
-      </c>
-      <c r="G22" s="8">
-        <v>2700.0</v>
-      </c>
-      <c r="H22" s="8">
-        <v>3420.0</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="11"/>
-    </row>
-    <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="4">
-        <v>46231.0</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="8">
-        <v>114357.0</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="8">
-        <v>240.0</v>
-      </c>
-      <c r="G23" s="8">
-        <v>52320.0</v>
-      </c>
-      <c r="H23" s="8">
-        <v>240.0</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="11"/>
-    </row>
-    <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="8">
-        <v>10501.0</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="8">
-        <v>19663.0</v>
-      </c>
-      <c r="G24" s="8">
-        <v>49540.0</v>
-      </c>
-      <c r="H24" s="8">
-        <v>29632.0</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="11"/>
-    </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="8">
-        <v>5700.0</v>
-      </c>
-      <c r="G25" s="8">
-        <v>34800.0</v>
-      </c>
-      <c r="H25" s="8">
-        <v>5100.0</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="11"/>
-    </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="8">
-        <v>2110317.0</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="8">
-        <v>720.0</v>
-      </c>
-      <c r="G26" s="8">
-        <v>7920.0</v>
-      </c>
-      <c r="H26" s="8">
-        <v>720.0</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="11"/>
-    </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="8">
-        <v>2114357.0</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="8">
-        <v>432.0</v>
-      </c>
-      <c r="G27" s="8">
-        <v>576.0</v>
-      </c>
-      <c r="H27" s="8">
-        <v>432.0</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="11"/>
-    </row>
-    <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="8">
-        <v>10501.0</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28" s="8">
-        <v>219540.0</v>
-      </c>
-      <c r="G28" s="8">
-        <v>272160.0</v>
-      </c>
-      <c r="H28" s="8">
-        <v>16698.0</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="11"/>
-    </row>
-    <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="4">
-        <v>46233.0</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="8">
-        <v>5100.0</v>
-      </c>
-      <c r="G29" s="8">
-        <v>3300.0</v>
-      </c>
-      <c r="H29" s="8">
-        <v>4800.0</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29" s="11"/>
-    </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="4">
-        <v>46233.0</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="8">
-        <v>114357.0</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="8">
-        <v>240.0</v>
-      </c>
-      <c r="G30" s="8">
-        <v>7800.0</v>
-      </c>
-      <c r="H30" s="8">
-        <v>1560.0</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="11"/>
-    </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="4">
-        <v>46233.0</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="8">
-        <v>10601.0</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" s="8">
-        <v>7717.0</v>
-      </c>
-      <c r="G31" s="8">
-        <v>10080.0</v>
-      </c>
-      <c r="H31" s="8">
-        <v>12867.0</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="4">
-        <v>46234.0</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="8">
-        <v>79110.0</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F32" s="8">
-        <v>48000.0</v>
-      </c>
-      <c r="G32" s="8">
-        <v>24600.0</v>
-      </c>
-      <c r="H32" s="8">
-        <v>36300.0</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="4">
-        <v>46234.0</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="8">
-        <v>10501.0</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F33" s="8">
-        <v>95574.0</v>
-      </c>
-      <c r="G33" s="8">
-        <v>78469.0</v>
-      </c>
-      <c r="H33" s="8">
-        <v>142801.0</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="4">
-        <v>46234.0</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="8">
-        <v>73001.0</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" s="8">
-        <v>73367.0</v>
-      </c>
-      <c r="G34" s="8">
-        <v>94608.0</v>
-      </c>
-      <c r="H34" s="8">
-        <v>39150.0</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="11"/>
-    </row>
-    <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="4">
-        <v>46234.0</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="8">
-        <v>112357.0</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F35" s="8">
-        <v>840.0</v>
-      </c>
-      <c r="G35" s="8">
-        <v>5160.0</v>
-      </c>
-      <c r="H35" s="8">
-        <v>480.0</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="11"/>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="18">
-        <v>46237.0</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="8">
-        <v>10601.0</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="8">
-        <v>17934.0</v>
-      </c>
-      <c r="G36" s="8">
-        <v>64980.0</v>
-      </c>
-      <c r="H36" s="8">
-        <v>21714.0</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="18">
-        <v>46237.0</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" s="8">
-        <v>194520.0</v>
-      </c>
-      <c r="G37" s="8">
-        <v>84060.0</v>
-      </c>
-      <c r="H37" s="8">
-        <v>122840.0</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="11"/>
-    </row>
-    <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="18">
-        <v>46237.0</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="8">
+      <c r="G56" s="9">
+        <v>3960.0</v>
+      </c>
+      <c r="H56" s="9">
+        <v>600.0</v>
+      </c>
+      <c r="I56" s="11"/>
+      <c r="J56" s="12"/>
+    </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="5">
+        <v>46239.0</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="14"/>
+      <c r="D57" s="9">
         <v>114379.0</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F38" s="8">
-        <v>52200.0</v>
-      </c>
-      <c r="G38" s="8">
-        <v>16200.0</v>
-      </c>
-      <c r="H38" s="8">
-        <v>7500.0</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J38" s="11"/>
-    </row>
-    <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="18">
-        <v>46237.0</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="8">
-        <v>2110317.0</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39" s="8">
-        <v>6450.0</v>
-      </c>
-      <c r="G39" s="8">
-        <v>16920.0</v>
-      </c>
-      <c r="H39" s="8">
-        <v>6480.0</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" s="11"/>
-    </row>
-    <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="18">
-        <v>46237.0</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" s="8">
-        <v>1398.0</v>
-      </c>
-      <c r="G40" s="8">
-        <v>1320.0</v>
-      </c>
-      <c r="H40" s="8">
-        <v>438.0</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" s="11"/>
-    </row>
-    <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="4">
-        <v>46238.0</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="8">
-        <v>2152388.0</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F41" s="8">
-        <v>2460.0</v>
-      </c>
-      <c r="G41" s="8">
-        <v>17640.0</v>
-      </c>
-      <c r="H41" s="8">
-        <v>3240.0</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="11"/>
-    </row>
-    <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="4">
-        <v>46238.0</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F42" s="8">
-        <v>3600.0</v>
-      </c>
-      <c r="G42" s="8">
-        <v>1500.0</v>
-      </c>
-      <c r="H42" s="8">
-        <v>3900.0</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J42" s="11"/>
-    </row>
-    <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="4">
-        <v>46238.0</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="14"/>
-      <c r="D43" s="8">
-        <v>114379.0</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F43" s="8">
-        <v>7500.0</v>
-      </c>
-      <c r="G43" s="8">
-        <v>54900.0</v>
-      </c>
-      <c r="H43" s="8">
-        <v>8400.0</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J43" s="11"/>
-    </row>
-    <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="4">
-        <v>46238.0</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="14"/>
-      <c r="D44" s="8">
-        <v>114357.0</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F44" s="8">
-        <v>240.0</v>
-      </c>
-      <c r="G44" s="8">
-        <v>7680.0</v>
-      </c>
-      <c r="H44" s="8">
-        <v>360.0</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" s="11"/>
-    </row>
-    <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" s="14"/>
-      <c r="D45" s="8">
-        <v>10601.0</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F45" s="8">
-        <v>1115.0</v>
-      </c>
-      <c r="G45" s="8">
-        <v>5267.0</v>
-      </c>
-      <c r="H45" s="8">
-        <v>1590.0</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="14"/>
-      <c r="D46" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F46" s="8">
-        <v>114240.0</v>
-      </c>
-      <c r="G46" s="8">
-        <v>79680.0</v>
-      </c>
-      <c r="H46" s="8">
-        <v>191130.0</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" s="11"/>
-    </row>
-    <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" s="14"/>
-      <c r="D47" s="8">
-        <v>2112207.0</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F47" s="8">
-        <v>1800.0</v>
-      </c>
-      <c r="G47" s="8">
-        <v>1800.0</v>
-      </c>
-      <c r="H47" s="8">
-        <v>1980.0</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J47" s="11"/>
-    </row>
-    <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F48" s="8">
-        <v>3900.0</v>
-      </c>
-      <c r="G48" s="8">
-        <v>34200.0</v>
-      </c>
-      <c r="H48" s="8">
-        <v>1200.0</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J48" s="11"/>
-    </row>
-    <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" s="14"/>
-      <c r="D49" s="8">
-        <v>112357.0</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F49" s="8">
-        <v>600.0</v>
-      </c>
-      <c r="G49" s="8">
-        <v>8400.0</v>
-      </c>
-      <c r="H49" s="8">
-        <v>600.0</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J49" s="11"/>
-    </row>
-    <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" s="14"/>
-      <c r="D50" s="8">
-        <v>114268.0</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F50" s="8">
-        <v>2700.0</v>
-      </c>
-      <c r="G50" s="8">
-        <v>5700.0</v>
-      </c>
-      <c r="H50" s="8">
+      <c r="E57" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" s="9">
+        <v>2400.0</v>
+      </c>
+      <c r="G57" s="9">
+        <v>15000.0</v>
+      </c>
+      <c r="H57" s="9">
         <v>300.0</v>
       </c>
-      <c r="I50" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J50" s="11"/>
-    </row>
-    <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" s="14"/>
-      <c r="D51" s="8">
-        <v>10501.0</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F51" s="8">
-        <v>68651.0</v>
-      </c>
-      <c r="G51" s="8">
-        <v>64050.0</v>
-      </c>
-      <c r="H51" s="8">
-        <v>13421.0</v>
-      </c>
-      <c r="I51" s="10"/>
-      <c r="J51" s="11"/>
-    </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C52" s="14"/>
-      <c r="D52" s="8">
-        <v>72003.0</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F52" s="8">
-        <v>1391.0</v>
-      </c>
-      <c r="G52" s="8">
-        <v>3885.0</v>
-      </c>
-      <c r="H52" s="8">
-        <v>2407.0</v>
-      </c>
-      <c r="I52" s="10"/>
-      <c r="J52" s="11"/>
-    </row>
-    <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="4">
-        <v>46239.0</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C53" s="14"/>
-      <c r="D53" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="8">
-        <v>2974.0</v>
-      </c>
-      <c r="G53" s="8">
-        <v>1200.0</v>
-      </c>
-      <c r="H53" s="8">
-        <v>3317.0</v>
-      </c>
-      <c r="I53" s="10"/>
-      <c r="J53" s="11"/>
-    </row>
-    <row r="54">
-      <c r="I54" s="20"/>
-    </row>
-    <row r="55">
-      <c r="I55" s="20"/>
-    </row>
-    <row r="56">
-      <c r="I56" s="20"/>
-    </row>
-    <row r="57">
-      <c r="I57" s="20"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="12"/>
     </row>
     <row r="58">
       <c r="I58" s="20"/>
@@ -10654,13 +10847,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I53">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I57">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I54:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I58:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A53">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A57">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -47,76 +47,151 @@
     <t>TAT BOGOTA MONTEVIDEO</t>
   </si>
   <si>
+    <t>Daniel Castro</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>2. Error De Registro De Inventario</t>
+  </si>
+  <si>
+    <t>TAT MONTERIA</t>
+  </si>
+  <si>
+    <t>LUIS LOPEZ</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>3. Falla De Rotación</t>
+  </si>
+  <si>
+    <t>TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>FABIO GOMEZ</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+  </si>
+  <si>
+    <t>TAT CARTAGENA</t>
+  </si>
+  <si>
+    <t>Dilan Barraza</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>4. Exigencia Del Cliente (Edad)</t>
+  </si>
+  <si>
+    <t>Venta FS</t>
+  </si>
+  <si>
+    <t>7. Otro</t>
+  </si>
+  <si>
+    <t>Se dejó lote para revisión por calidad</t>
+  </si>
+  <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>Se envía más fresco a Rionegro</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>1. Ingreso Por Devolución</t>
+  </si>
+  <si>
+    <t>TAT CALI</t>
+  </si>
+  <si>
+    <t>DIEGO ROJAS</t>
+  </si>
+  <si>
+    <t>TAT CUCUTA</t>
+  </si>
+  <si>
+    <t>ALEXANDER PEÑA</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
+    <t>6. Transformación De Referencias</t>
+  </si>
+  <si>
+    <t>Clientes FS</t>
+  </si>
+  <si>
+    <t>Envío huevo fresco a Sincelejo</t>
+  </si>
+  <si>
+    <t>Transformación de PET</t>
+  </si>
+  <si>
+    <t>ANDRES MEJIA</t>
+  </si>
+  <si>
+    <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
+  </si>
+  <si>
+    <t>TAT POPAYAN</t>
+  </si>
+  <si>
+    <t>JONATHAN MOSQUERA</t>
+  </si>
+  <si>
+    <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
+  </si>
+  <si>
+    <t>Producto con novedades de calidad, se está bandejeando</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+  </si>
+  <si>
+    <t>5. Ingreso De Planta</t>
+  </si>
+  <si>
+    <t>Se despacha par FS con producto más nuevo</t>
+  </si>
+  <si>
     <t>ALKA2</t>
   </si>
   <si>
-    <t>Daniel Castro</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>2. Error De Registro De Inventario</t>
-  </si>
-  <si>
-    <t>7. Otro</t>
-  </si>
-  <si>
     <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
   </si>
   <si>
-    <t>TAT MONTERIA</t>
-  </si>
-  <si>
-    <t>LUIS LOPEZ</t>
+    <t>ANDREA QUIROGA</t>
   </si>
   <si>
     <t>LANZA</t>
   </si>
   <si>
+    <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
+  </si>
+  <si>
     <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
-    <t>3. Falla De Rotación</t>
-  </si>
-  <si>
-    <t>6. Transformación De Referencias</t>
-  </si>
-  <si>
     <t>Pendiente Transformar Roto GT Por manipulación</t>
   </si>
   <si>
-    <t>TAT MEDELLIN</t>
-  </si>
-  <si>
-    <t>FABIO GOMEZ</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
-  </si>
-  <si>
     <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
-    <t>TAT CARTAGENA</t>
-  </si>
-  <si>
-    <t>Dilan Barraza</t>
-  </si>
-  <si>
     <t>se equivocaron al cargar una estiba</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>4. Exigencia Del Cliente (Edad)</t>
-  </si>
-  <si>
-    <t>Venta FS</t>
+    <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
     <t>HUEVO L X 30 PET CAJA X 300</t>
@@ -125,82 +200,49 @@
     <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
   </si>
   <si>
-    <t>Se dejó lote para revisión por calidad</t>
-  </si>
-  <si>
     <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
   </si>
   <si>
     <t>PALMAS</t>
   </si>
   <si>
-    <t>Se envía más fresco a Rionegro</t>
-  </si>
-  <si>
     <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
     <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
-    <t>1. Ingreso Por Devolución</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
-    <t>TAT CALI</t>
-  </si>
-  <si>
-    <t>DIEGO ROJAS</t>
+    <t>TAT PASTO</t>
+  </si>
+  <si>
+    <t>CAROLINA VITERI</t>
   </si>
   <si>
     <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
-    <t>TAT CUCUTA</t>
-  </si>
-  <si>
-    <t>ALEXANDER PEÑA</t>
-  </si>
-  <si>
     <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
   </si>
   <si>
     <t>HUEVO PICADO ROJO</t>
   </si>
   <si>
+    <t>Asignacion a canal Tat para sugeridos de hoy</t>
+  </si>
+  <si>
     <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
-    <t>Clientes FS</t>
-  </si>
-  <si>
-    <t>Envío huevo fresco a Sincelejo</t>
-  </si>
-  <si>
-    <t>Transformación de PET</t>
-  </si>
-  <si>
-    <t>ANDRES MEJIA</t>
-  </si>
-  <si>
-    <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
-  </si>
-  <si>
-    <t>TAT POPAYAN</t>
-  </si>
-  <si>
-    <t>JONATHAN MOSQUERA</t>
+    <t>Pedido para villavicencio</t>
+  </si>
+  <si>
+    <t>Se entrega inventario nuevo para FS</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
   </si>
   <si>
     <t>HUEVO SUCIO DE JAULA</t>
@@ -209,10 +251,16 @@
     <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
   </si>
   <si>
+    <t>Inventario de Asesor de Rionegro que renuncio</t>
+  </si>
+  <si>
     <t>Esta para despacho hoy</t>
   </si>
   <si>
-    <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
+    <t>TAT BARRANQUILLA</t>
+  </si>
+  <si>
+    <t>Jhonatan Gomez</t>
   </si>
   <si>
     <t>Cola de programación</t>
@@ -221,15 +269,9 @@
     <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
   </si>
   <si>
-    <t>Producto con novedades de calidad, se está bandejeando</t>
-  </si>
-  <si>
     <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
-  </si>
-  <si>
     <t>HUEVO CX30 CARTON GRIS</t>
   </si>
   <si>
@@ -239,34 +281,22 @@
     <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
-    <t>5. Ingreso De Planta</t>
-  </si>
-  <si>
-    <t>Se despacha par FS con producto más nuevo</t>
-  </si>
-  <si>
-    <t>ANDREA QUIROGA</t>
-  </si>
-  <si>
-    <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
+    <t>Lote mezclado en la misma estiba</t>
+  </si>
+  <si>
+    <t>Supera edad solicitada clientes grandes superficies</t>
   </si>
   <si>
     <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
-    <t>Se despacha producto más nuevo para Rionegro</t>
+    <t>Pedido para villacicencio</t>
   </si>
   <si>
     <t>ALKA1</t>
   </si>
   <si>
-    <t>TAT PASTO</t>
-  </si>
-  <si>
-    <t>CAROLINA VITERI</t>
+    <t>Se envía huevo más fresco a Sincelejo</t>
   </si>
   <si>
     <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
@@ -275,22 +305,28 @@
     <t>HUEVO ROTO - ZF</t>
   </si>
   <si>
+    <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
+  </si>
+  <si>
     <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
   </si>
   <si>
-    <t>Asignacion a canal Tat para sugeridos de hoy</t>
+    <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
   </si>
   <si>
     <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
   </si>
   <si>
-    <t>Pedido para villavicencio</t>
+    <t>SalIO en sugeridos de hoy 22/07/2026</t>
+  </si>
+  <si>
+    <t>Yovanis Arevalo</t>
   </si>
   <si>
     <t>HUEVO L X 12 PET CAJA X 120</t>
   </si>
   <si>
-    <t>Se entrega inventario nuevo para FS</t>
+    <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
   </si>
   <si>
     <t>Cargo en incubación</t>
@@ -299,70 +335,34 @@
     <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>Inventario de Asesor de Rionegro que renuncio</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA</t>
-  </si>
-  <si>
-    <t>Jhonatan Gomez</t>
-  </si>
-  <si>
-    <t>Lote mezclado en la misma estiba</t>
-  </si>
-  <si>
-    <t>Supera edad solicitada clientes grandes superficies</t>
+    <t>Devolucion de huevo de 12 dias en mal estado</t>
+  </si>
+  <si>
+    <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
+  </si>
+  <si>
+    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
     <t>BELLAVISTA</t>
   </si>
   <si>
-    <t>Pedido para villacicencio</t>
-  </si>
-  <si>
     <t>Traslado a cedi, producto de devolución</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
-    <t>Se envía huevo más fresco a Sincelejo</t>
-  </si>
-  <si>
-    <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
-  </si>
-  <si>
-    <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
-  </si>
-  <si>
     <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>SalIO en sugeridos de hoy 22/07/2026</t>
-  </si>
-  <si>
     <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
   </si>
   <si>
-    <t>Yovanis Arevalo</t>
-  </si>
-  <si>
     <t>HUEVO SUCIO ZF MARCADO</t>
   </si>
   <si>
-    <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
-  </si>
-  <si>
     <t>vehiculo con flata de capacidad / TAT cali</t>
-  </si>
-  <si>
-    <t>Devolucion de huevo de 12 dias en mal estado</t>
-  </si>
-  <si>
-    <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
-  </si>
-  <si>
-    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
     <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
@@ -496,11 +496,20 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -508,23 +517,8 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -533,10 +527,16 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -634,7 +634,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J92" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J92" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -652,7 +652,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J57" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J57" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -918,2368 +918,2368 @@
       <c r="A2" s="4">
         <v>46204.0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="9">
+      <c r="F2" s="7">
+        <v>359100.0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>83486.0</v>
+      </c>
+      <c r="H2" s="7">
+        <v>206140.0</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" hidden="1" customHeight="1">
+      <c r="A3" s="9">
+        <v>46205.0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="7">
+        <v>298282.0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>42201.0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>260675.0</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
+      <c r="A4" s="9">
+        <v>46205.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2110217.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="7">
+        <v>21120.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>11039.0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>16920.0</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
+      <c r="A5" s="9">
+        <v>46205.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="7">
+        <v>75680.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>5640.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3134.0</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="7">
+        <v>189540.0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>161685.0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>144720.0</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="7">
+        <v>20640.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>3761.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>13920.0</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7">
+        <v>152384.0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="7">
+        <v>14700.0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>6435.0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>9600.0</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
+      <c r="A9" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7">
+        <v>228240.0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>77306.0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>124260.0</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
+      <c r="A10" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="7">
+        <v>7830.0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>1980.0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>6030.0</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="7">
+        <v>31680.0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>5526.0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>23040.0</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
+      <c r="A12" s="9">
+        <v>46206.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="7">
+        <v>51387.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>10827.0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>12170.0</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
+      <c r="A13" s="9">
+        <v>46209.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="7">
+        <v>195810.0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>93809.0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>133410.0</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
+      <c r="A14" s="9">
+        <v>46209.0</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="7">
+        <v>526002.0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>301965.0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>424588.0</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="9">
+        <v>46209.0</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="7">
+        <v>14160.0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>6692.0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>12360.0</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
+      <c r="A16" s="9">
+        <v>46210.0</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="7">
+        <v>149040.0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>119573.0</v>
+      </c>
+      <c r="H16" s="7">
+        <v>289680.0</v>
+      </c>
+      <c r="I16" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="9">
-        <v>359100.0</v>
-      </c>
-      <c r="G2" s="9">
-        <v>83486.0</v>
-      </c>
-      <c r="H2" s="9">
-        <v>206140.0</v>
-      </c>
-      <c r="I2" s="10" t="s">
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" ht="22.5" hidden="1" customHeight="1">
+      <c r="A17" s="9">
+        <v>46210.0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="7">
+        <v>2110217.0</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="7">
+        <v>22770.0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>3926.0</v>
+      </c>
+      <c r="H17" s="7">
+        <v>19770.0</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="12"/>
+    </row>
+    <row r="18" ht="22.5" hidden="1" customHeight="1">
+      <c r="A18" s="9">
+        <v>46210.0</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="7">
+        <v>222021.0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>61385.0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>162125.0</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="12"/>
+    </row>
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
+      <c r="A19" s="9">
+        <v>46211.0</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="7">
+        <v>495833.0</v>
+      </c>
+      <c r="G19" s="7">
+        <v>148815.0</v>
+      </c>
+      <c r="H19" s="7">
+        <v>401280.0</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
+      <c r="A20" s="9">
+        <v>46211.0</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="5">
-        <v>46205.0</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="D20" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="7">
+        <v>139920.0</v>
+      </c>
+      <c r="G20" s="7">
+        <v>54384.0</v>
+      </c>
+      <c r="H20" s="7">
+        <v>74040.0</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="12"/>
+    </row>
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
+      <c r="A21" s="9">
+        <v>46211.0</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="7">
+        <v>162125.0</v>
+      </c>
+      <c r="G21" s="7">
+        <v>60138.0</v>
+      </c>
+      <c r="H21" s="7">
+        <v>100687.0</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" hidden="1" customHeight="1">
+      <c r="A22" s="9">
+        <v>46211.0</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="7">
+        <v>152384.0</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="7">
+        <v>32850.0</v>
+      </c>
+      <c r="G22" s="7">
+        <v>7065.0</v>
+      </c>
+      <c r="H22" s="7">
+        <v>32700.0</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="12"/>
+    </row>
+    <row r="23" ht="22.5" hidden="1" customHeight="1">
+      <c r="A23" s="9">
+        <v>46211.0</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="7">
+        <v>112271.0</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="7">
+        <v>16500.0</v>
+      </c>
+      <c r="G23" s="7">
+        <v>5310.0</v>
+      </c>
+      <c r="H23" s="7">
+        <v>18000.0</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="12"/>
+    </row>
+    <row r="24" ht="22.5" hidden="1" customHeight="1">
+      <c r="A24" s="9">
+        <v>46212.0</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="7">
+        <v>190047.0</v>
+      </c>
+      <c r="G24" s="7">
+        <v>59822.0</v>
+      </c>
+      <c r="H24" s="7">
+        <v>248481.0</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="12"/>
+    </row>
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
+      <c r="A25" s="9">
+        <v>46212.0</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="7">
+        <v>178080.0</v>
+      </c>
+      <c r="G25" s="7">
+        <v>47784.0</v>
+      </c>
+      <c r="H25" s="7">
+        <v>203520.0</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
+      <c r="A26" s="9">
+        <v>46212.0</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="7">
+        <v>10320.0</v>
+      </c>
+      <c r="G26" s="7">
+        <v>5869.0</v>
+      </c>
+      <c r="H26" s="7">
+        <v>13200.0</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
+      <c r="A27" s="9">
+        <v>46212.0</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="7">
+        <v>112271.0</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="7">
+        <v>18000.0</v>
+      </c>
+      <c r="G27" s="7">
+        <v>4485.0</v>
+      </c>
+      <c r="H27" s="7">
+        <v>13500.0</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="12"/>
+    </row>
+    <row r="28" ht="22.5" hidden="1" customHeight="1">
+      <c r="A28" s="9">
+        <v>46213.0</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="7">
+        <v>208440.0</v>
+      </c>
+      <c r="G28" s="7">
+        <v>85608.0</v>
+      </c>
+      <c r="H28" s="7">
+        <v>150833.0</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" hidden="1" customHeight="1">
+      <c r="A29" s="9">
+        <v>46213.0</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="7">
+        <v>962820.0</v>
+      </c>
+      <c r="G29" s="7">
+        <v>80644.0</v>
+      </c>
+      <c r="H29" s="7">
+        <v>922140.0</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
+      <c r="A30" s="9">
+        <v>46213.0</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="7">
+        <v>335340.0</v>
+      </c>
+      <c r="G30" s="7">
+        <v>111433.0</v>
+      </c>
+      <c r="H30" s="7">
+        <v>381600.0</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="9">
+        <v>46213.0</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="7">
+        <v>316800.0</v>
+      </c>
+      <c r="G31" s="7">
+        <v>99546.0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>229680.0</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="12"/>
+    </row>
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
+      <c r="A32" s="9">
+        <v>46213.0</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="7">
+        <v>176850.0</v>
+      </c>
+      <c r="G32" s="7">
+        <v>47499.0</v>
+      </c>
+      <c r="H32" s="7">
+        <v>128971.0</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="12"/>
+    </row>
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
+      <c r="A33" s="9">
+        <v>46213.0</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="7">
+        <v>58080.0</v>
+      </c>
+      <c r="G33" s="7">
+        <v>20865.0</v>
+      </c>
+      <c r="H33" s="7">
+        <v>25440.0</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="12"/>
+    </row>
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
+      <c r="A34" s="9">
+        <v>46217.0</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="7">
+        <v>481440.0</v>
+      </c>
+      <c r="G34" s="7">
+        <v>464517.0</v>
+      </c>
+      <c r="H34" s="7">
+        <v>151435.0</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="12"/>
+    </row>
+    <row r="35" ht="22.5" hidden="1" customHeight="1">
+      <c r="A35" s="9">
+        <v>46217.0</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D35" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="7">
+        <v>355720.0</v>
+      </c>
+      <c r="G35" s="7">
+        <v>342811.0</v>
+      </c>
+      <c r="H35" s="7">
+        <v>302760.0</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="12"/>
+    </row>
+    <row r="36" ht="22.5" hidden="1" customHeight="1">
+      <c r="A36" s="9">
+        <v>46217.0</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="7">
+        <v>35280.0</v>
+      </c>
+      <c r="G36" s="7">
+        <v>16988.0</v>
+      </c>
+      <c r="H36" s="7">
+        <v>37926.0</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" hidden="1" customHeight="1">
+      <c r="A37" s="17">
+        <v>46218.0</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" s="7">
+        <v>272073.0</v>
+      </c>
+      <c r="G37" s="7">
+        <v>76546.0</v>
+      </c>
+      <c r="H37" s="7">
+        <v>275205.0</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" ht="22.5" hidden="1" customHeight="1">
+      <c r="A38" s="17">
+        <v>46218.0</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="7">
+        <v>37926.0</v>
+      </c>
+      <c r="G38" s="7">
+        <v>5633.0</v>
+      </c>
+      <c r="H38" s="7">
+        <v>25746.0</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" ht="22.5" hidden="1" customHeight="1">
+      <c r="A39" s="17">
+        <v>46218.0</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="7">
+        <v>20640.0</v>
+      </c>
+      <c r="G39" s="7">
+        <v>4951.0</v>
+      </c>
+      <c r="H39" s="7">
+        <v>16320.0</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" ht="22.5" hidden="1" customHeight="1">
+      <c r="A40" s="17">
+        <v>46218.0</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="7">
+        <v>2110317.0</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="7">
+        <v>10980.0</v>
+      </c>
+      <c r="G40" s="7">
+        <v>2379.0</v>
+      </c>
+      <c r="H40" s="7">
+        <v>13500.0</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="12"/>
+    </row>
+    <row r="41" ht="22.5" hidden="1" customHeight="1">
+      <c r="A41" s="9">
+        <v>46219.0</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="7">
+        <v>130320.0</v>
+      </c>
+      <c r="G41" s="7">
+        <v>47410.0</v>
+      </c>
+      <c r="H41" s="7">
+        <v>90480.0</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" ht="22.5" hidden="1" customHeight="1">
+      <c r="A42" s="9">
+        <v>46219.0</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="7">
+        <v>36225.0</v>
+      </c>
+      <c r="G42" s="7">
+        <v>11746.0</v>
+      </c>
+      <c r="H42" s="7">
+        <v>27570.0</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="12"/>
+    </row>
+    <row r="43" ht="22.5" hidden="1" customHeight="1">
+      <c r="A43" s="9">
+        <v>46219.0</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="7">
+        <v>152833.0</v>
+      </c>
+      <c r="G43" s="7">
+        <v>50641.0</v>
+      </c>
+      <c r="H43" s="7">
+        <v>96472.0</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" hidden="1" customHeight="1">
+      <c r="A44" s="9">
+        <v>46219.0</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" s="7">
+        <v>237828.0</v>
+      </c>
+      <c r="G44" s="7">
+        <v>173585.0</v>
+      </c>
+      <c r="H44" s="7">
+        <v>71560.0</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="12"/>
+    </row>
+    <row r="45" ht="22.5" hidden="1" customHeight="1">
+      <c r="A45" s="9">
+        <v>46219.0</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="7">
+        <v>152384.0</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F45" s="7">
+        <v>31125.0</v>
+      </c>
+      <c r="G45" s="7">
+        <v>7815.0</v>
+      </c>
+      <c r="H45" s="7">
+        <v>31845.0</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" hidden="1" customHeight="1">
+      <c r="A46" s="9">
+        <v>46219.0</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="7">
+        <v>25746.0</v>
+      </c>
+      <c r="G46" s="7">
+        <v>6168.0</v>
+      </c>
+      <c r="H46" s="7">
+        <v>28683.0</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" ht="22.5" hidden="1" customHeight="1">
+      <c r="A47" s="9">
+        <v>46220.0</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="7">
+        <v>261166.0</v>
+      </c>
+      <c r="G47" s="7">
+        <v>74573.0</v>
+      </c>
+      <c r="H47" s="7">
+        <v>221549.0</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" ht="22.5" hidden="1" customHeight="1">
+      <c r="A48" s="9">
+        <v>46220.0</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" s="7">
+        <v>2110217.0</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="7">
+        <v>115289.0</v>
+      </c>
+      <c r="G48" s="7">
+        <v>26931.0</v>
+      </c>
+      <c r="H48" s="7">
+        <v>119584.0</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="12"/>
+    </row>
+    <row r="49" ht="22.5" hidden="1" customHeight="1">
+      <c r="A49" s="9">
+        <v>46224.0</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="9">
-        <v>298282.0</v>
-      </c>
-      <c r="G3" s="9">
-        <v>42201.0</v>
-      </c>
-      <c r="H3" s="9">
-        <v>260675.0</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="5">
-        <v>46205.0</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="C49" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="7">
+        <v>398570.0</v>
+      </c>
+      <c r="G49" s="7">
+        <v>288226.0</v>
+      </c>
+      <c r="H49" s="7">
+        <v>287235.0</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" ht="22.5" hidden="1" customHeight="1">
+      <c r="A50" s="9">
+        <v>46224.0</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="7">
+        <v>745107.0</v>
+      </c>
+      <c r="G50" s="7">
+        <v>378927.0</v>
+      </c>
+      <c r="H50" s="7">
+        <v>551645.0</v>
+      </c>
+      <c r="I50" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="9">
-        <v>2110217.0</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="9">
-        <v>21120.0</v>
-      </c>
-      <c r="G4" s="9">
-        <v>11039.0</v>
-      </c>
-      <c r="H4" s="9">
-        <v>16920.0</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="5">
-        <v>46205.0</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="9">
+      <c r="J50" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" ht="22.5" hidden="1" customHeight="1">
+      <c r="A51" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D51" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E51" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" s="7">
+        <v>130560.0</v>
+      </c>
+      <c r="G51" s="7">
+        <v>52658.0</v>
+      </c>
+      <c r="H51" s="7">
+        <v>153840.0</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" hidden="1" customHeight="1">
+      <c r="A52" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="9">
-        <v>75680.0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>5640.0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>3134.0</v>
-      </c>
-      <c r="I5" s="13" t="s">
+      <c r="C52" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="5">
-        <v>46206.0</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="D52" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="7">
+        <v>87447.0</v>
+      </c>
+      <c r="G52" s="7">
+        <v>59056.0</v>
+      </c>
+      <c r="H52" s="7">
+        <v>104365.0</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="12"/>
+    </row>
+    <row r="53" ht="22.5" hidden="1" customHeight="1">
+      <c r="A53" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="7">
+        <v>25200.0</v>
+      </c>
+      <c r="G53" s="7">
+        <v>2085.0</v>
+      </c>
+      <c r="H53" s="7">
+        <v>25920.0</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" hidden="1" customHeight="1">
+      <c r="A54" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D54" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" s="7">
+        <v>285405.0</v>
+      </c>
+      <c r="G54" s="7">
+        <v>203180.0</v>
+      </c>
+      <c r="H54" s="7">
+        <v>226069.0</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" hidden="1" customHeight="1">
+      <c r="A55" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D55" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="7">
+        <v>692280.0</v>
+      </c>
+      <c r="G55" s="7">
+        <v>118381.0</v>
+      </c>
+      <c r="H55" s="7">
+        <v>700200.0</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J55" s="12"/>
+    </row>
+    <row r="56" ht="22.5" hidden="1" customHeight="1">
+      <c r="A56" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="7">
+        <v>700200.0</v>
+      </c>
+      <c r="G56" s="7">
+        <v>112628.0</v>
+      </c>
+      <c r="H56" s="7">
+        <v>668440.0</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="12"/>
+    </row>
+    <row r="57" ht="22.5" hidden="1" customHeight="1">
+      <c r="A57" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D57" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="7">
+        <v>226069.0</v>
+      </c>
+      <c r="G57" s="7">
+        <v>193130.0</v>
+      </c>
+      <c r="H57" s="7">
+        <v>326391.0</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" ht="22.5" hidden="1" customHeight="1">
+      <c r="A58" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="7">
+        <v>144637.0</v>
+      </c>
+      <c r="G58" s="7">
+        <v>64227.0</v>
+      </c>
+      <c r="H58" s="7">
+        <v>128160.0</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J58" s="12"/>
+    </row>
+    <row r="59" ht="22.5" hidden="1" customHeight="1">
+      <c r="A59" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" s="7">
+        <v>295359.0</v>
+      </c>
+      <c r="G59" s="7">
+        <v>126369.0</v>
+      </c>
+      <c r="H59" s="7">
+        <v>166642.0</v>
+      </c>
+      <c r="I59" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="9">
+      <c r="J59" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" ht="22.5" hidden="1" customHeight="1">
+      <c r="A60" s="9">
+        <v>46230.0</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="7">
+        <v>2110403.0</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F60" s="7">
+        <v>9960.0</v>
+      </c>
+      <c r="G60" s="7">
+        <v>6018.0</v>
+      </c>
+      <c r="H60" s="7">
+        <v>3660.0</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="12"/>
+    </row>
+    <row r="61" ht="22.5" hidden="1" customHeight="1">
+      <c r="A61" s="9">
+        <v>46230.0</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61" s="7">
+        <v>306720.0</v>
+      </c>
+      <c r="G61" s="7">
+        <v>164175.0</v>
+      </c>
+      <c r="H61" s="7">
+        <v>247096.0</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="12"/>
+    </row>
+    <row r="62" ht="22.5" hidden="1" customHeight="1">
+      <c r="A62" s="9">
+        <v>46230.0</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="9">
-        <v>189540.0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>161685.0</v>
-      </c>
-      <c r="H6" s="9">
-        <v>144720.0</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="5">
-        <v>46206.0</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="9">
-        <v>2010102.0</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="9">
-        <v>20640.0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>3761.0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>13920.0</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="5">
-        <v>46206.0</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="9">
-        <v>152384.0</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="9">
-        <v>14700.0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>6435.0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>9600.0</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="5">
-        <v>46206.0</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="9">
-        <v>228240.0</v>
-      </c>
-      <c r="G9" s="9">
-        <v>77306.0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>124260.0</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="5">
-        <v>46206.0</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2152388.0</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="9">
-        <v>7830.0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>1980.0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>6030.0</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="5">
-        <v>46206.0</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="9">
-        <v>31680.0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>5526.0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>23040.0</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="5">
-        <v>46206.0</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="9">
-        <v>51387.0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>10827.0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>12170.0</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="5">
-        <v>46209.0</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="9">
-        <v>195810.0</v>
-      </c>
-      <c r="G13" s="9">
-        <v>93809.0</v>
-      </c>
-      <c r="H13" s="9">
-        <v>133410.0</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="5">
-        <v>46209.0</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="9">
-        <v>526002.0</v>
-      </c>
-      <c r="G14" s="9">
-        <v>301965.0</v>
-      </c>
-      <c r="H14" s="9">
-        <v>424588.0</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="5">
-        <v>46209.0</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="9">
-        <v>2010102.0</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="9">
-        <v>14160.0</v>
-      </c>
-      <c r="G15" s="9">
-        <v>6692.0</v>
-      </c>
-      <c r="H15" s="9">
-        <v>12360.0</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="5">
-        <v>46210.0</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="9">
-        <v>149040.0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>119573.0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>289680.0</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="5">
-        <v>46210.0</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="9">
-        <v>2110217.0</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="9">
-        <v>22770.0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>3926.0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>19770.0</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="12"/>
-    </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="5">
-        <v>46210.0</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="9">
-        <v>222021.0</v>
-      </c>
-      <c r="G18" s="9">
-        <v>61385.0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>162125.0</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="12"/>
-    </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="5">
-        <v>46211.0</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="9">
-        <v>495833.0</v>
-      </c>
-      <c r="G19" s="9">
-        <v>148815.0</v>
-      </c>
-      <c r="H19" s="9">
-        <v>401280.0</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="5">
-        <v>46211.0</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="9">
-        <v>139920.0</v>
-      </c>
-      <c r="G20" s="9">
-        <v>54384.0</v>
-      </c>
-      <c r="H20" s="9">
-        <v>74040.0</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="12"/>
-    </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="5">
-        <v>46211.0</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="9">
-        <v>162125.0</v>
-      </c>
-      <c r="G21" s="9">
-        <v>60138.0</v>
-      </c>
-      <c r="H21" s="9">
-        <v>100687.0</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="5">
-        <v>46211.0</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="E62" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="9">
-        <v>152384.0</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="9">
-        <v>32850.0</v>
-      </c>
-      <c r="G22" s="9">
-        <v>7065.0</v>
-      </c>
-      <c r="H22" s="9">
-        <v>32700.0</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="12"/>
-    </row>
-    <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="5">
-        <v>46211.0</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="9">
-        <v>112271.0</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F23" s="9">
-        <v>16500.0</v>
-      </c>
-      <c r="G23" s="9">
-        <v>5310.0</v>
-      </c>
-      <c r="H23" s="9">
-        <v>18000.0</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" s="12"/>
-    </row>
-    <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="5">
-        <v>46212.0</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="9">
-        <v>190047.0</v>
-      </c>
-      <c r="G24" s="9">
-        <v>59822.0</v>
-      </c>
-      <c r="H24" s="9">
-        <v>248481.0</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J24" s="12"/>
-    </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="5">
-        <v>46212.0</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="9">
-        <v>178080.0</v>
-      </c>
-      <c r="G25" s="9">
-        <v>47784.0</v>
-      </c>
-      <c r="H25" s="9">
-        <v>203520.0</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="J25" s="12"/>
-    </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="5">
-        <v>46212.0</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="9">
-        <v>10320.0</v>
-      </c>
-      <c r="G26" s="9">
-        <v>5869.0</v>
-      </c>
-      <c r="H26" s="9">
-        <v>13200.0</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="5">
-        <v>46212.0</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="9">
-        <v>112271.0</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27" s="9">
-        <v>18000.0</v>
-      </c>
-      <c r="G27" s="9">
-        <v>4485.0</v>
-      </c>
-      <c r="H27" s="9">
-        <v>13500.0</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="12"/>
-    </row>
-    <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="5">
-        <v>46213.0</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D28" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="9">
-        <v>208440.0</v>
-      </c>
-      <c r="G28" s="9">
-        <v>85608.0</v>
-      </c>
-      <c r="H28" s="9">
-        <v>150833.0</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="5">
-        <v>46213.0</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="9">
-        <v>962820.0</v>
-      </c>
-      <c r="G29" s="9">
-        <v>80644.0</v>
-      </c>
-      <c r="H29" s="9">
-        <v>922140.0</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="5">
-        <v>46213.0</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="9">
-        <v>335340.0</v>
-      </c>
-      <c r="G30" s="9">
-        <v>111433.0</v>
-      </c>
-      <c r="H30" s="9">
-        <v>381600.0</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="5">
-        <v>46213.0</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="9">
-        <v>316800.0</v>
-      </c>
-      <c r="G31" s="9">
-        <v>99546.0</v>
-      </c>
-      <c r="H31" s="9">
-        <v>229680.0</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" s="12"/>
-    </row>
-    <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="5">
-        <v>46213.0</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="9">
-        <v>176850.0</v>
-      </c>
-      <c r="G32" s="9">
-        <v>47499.0</v>
-      </c>
-      <c r="H32" s="9">
-        <v>128971.0</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J32" s="12"/>
-    </row>
-    <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="5">
-        <v>46213.0</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="9">
-        <v>58080.0</v>
-      </c>
-      <c r="G33" s="9">
-        <v>20865.0</v>
-      </c>
-      <c r="H33" s="9">
-        <v>25440.0</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="12"/>
-    </row>
-    <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="5">
-        <v>46217.0</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" s="9">
-        <v>481440.0</v>
-      </c>
-      <c r="G34" s="9">
-        <v>464517.0</v>
-      </c>
-      <c r="H34" s="9">
-        <v>151435.0</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="12"/>
-    </row>
-    <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="5">
-        <v>46217.0</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="9">
-        <v>355720.0</v>
-      </c>
-      <c r="G35" s="9">
-        <v>342811.0</v>
-      </c>
-      <c r="H35" s="9">
-        <v>302760.0</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="12"/>
-    </row>
-    <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="5">
-        <v>46217.0</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" s="9">
-        <v>2010102.0</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F36" s="9">
-        <v>35280.0</v>
-      </c>
-      <c r="G36" s="9">
-        <v>16988.0</v>
-      </c>
-      <c r="H36" s="9">
-        <v>37926.0</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37" ht="22.5" hidden="1" customHeight="1">
-      <c r="A37" s="18">
-        <v>46218.0</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D37" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" s="9">
-        <v>272073.0</v>
-      </c>
-      <c r="G37" s="9">
-        <v>76546.0</v>
-      </c>
-      <c r="H37" s="9">
-        <v>275205.0</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" ht="22.5" hidden="1" customHeight="1">
-      <c r="A38" s="18">
-        <v>46218.0</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D38" s="9">
-        <v>2010102.0</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F38" s="9">
-        <v>37926.0</v>
-      </c>
-      <c r="G38" s="9">
-        <v>5633.0</v>
-      </c>
-      <c r="H38" s="9">
-        <v>25746.0</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" ht="22.5" hidden="1" customHeight="1">
-      <c r="A39" s="18">
-        <v>46218.0</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D39" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="9">
-        <v>20640.0</v>
-      </c>
-      <c r="G39" s="9">
-        <v>4951.0</v>
-      </c>
-      <c r="H39" s="9">
-        <v>16320.0</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" ht="22.5" hidden="1" customHeight="1">
-      <c r="A40" s="18">
-        <v>46218.0</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D40" s="9">
-        <v>2110317.0</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F40" s="9">
-        <v>10980.0</v>
-      </c>
-      <c r="G40" s="9">
-        <v>2379.0</v>
-      </c>
-      <c r="H40" s="9">
-        <v>13500.0</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J40" s="12"/>
-    </row>
-    <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="5">
-        <v>46219.0</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D41" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="9">
-        <v>130320.0</v>
-      </c>
-      <c r="G41" s="9">
-        <v>47410.0</v>
-      </c>
-      <c r="H41" s="9">
-        <v>90480.0</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="5">
-        <v>46219.0</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D42" s="9">
-        <v>2152388.0</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F42" s="9">
-        <v>36225.0</v>
-      </c>
-      <c r="G42" s="9">
-        <v>11746.0</v>
-      </c>
-      <c r="H42" s="9">
-        <v>27570.0</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" s="12"/>
-    </row>
-    <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="5">
-        <v>46219.0</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F43" s="9">
-        <v>152833.0</v>
-      </c>
-      <c r="G43" s="9">
-        <v>50641.0</v>
-      </c>
-      <c r="H43" s="9">
-        <v>96472.0</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="5">
-        <v>46219.0</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D44" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F44" s="9">
-        <v>237828.0</v>
-      </c>
-      <c r="G44" s="9">
-        <v>173585.0</v>
-      </c>
-      <c r="H44" s="9">
-        <v>71560.0</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" s="12"/>
-    </row>
-    <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="5">
-        <v>46219.0</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D45" s="9">
-        <v>152384.0</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F45" s="9">
-        <v>31125.0</v>
-      </c>
-      <c r="G45" s="9">
-        <v>7815.0</v>
-      </c>
-      <c r="H45" s="9">
-        <v>31845.0</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="5">
-        <v>46219.0</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D46" s="9">
-        <v>2010102.0</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F46" s="9">
-        <v>25746.0</v>
-      </c>
-      <c r="G46" s="9">
-        <v>6168.0</v>
-      </c>
-      <c r="H46" s="9">
-        <v>28683.0</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="5">
-        <v>46220.0</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D47" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F47" s="9">
-        <v>261166.0</v>
-      </c>
-      <c r="G47" s="9">
-        <v>74573.0</v>
-      </c>
-      <c r="H47" s="9">
-        <v>221549.0</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="5">
-        <v>46220.0</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D48" s="9">
-        <v>2110217.0</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F48" s="9">
-        <v>115289.0</v>
-      </c>
-      <c r="G48" s="9">
-        <v>26931.0</v>
-      </c>
-      <c r="H48" s="9">
-        <v>119584.0</v>
-      </c>
-      <c r="I48" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J48" s="12"/>
-    </row>
-    <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="5">
-        <v>46224.0</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" s="9">
-        <v>398570.0</v>
-      </c>
-      <c r="G49" s="9">
-        <v>288226.0</v>
-      </c>
-      <c r="H49" s="9">
-        <v>287235.0</v>
-      </c>
-      <c r="I49" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="5">
-        <v>46224.0</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F50" s="9">
-        <v>745107.0</v>
-      </c>
-      <c r="G50" s="9">
-        <v>378927.0</v>
-      </c>
-      <c r="H50" s="9">
-        <v>551645.0</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F51" s="9">
-        <v>130560.0</v>
-      </c>
-      <c r="G51" s="9">
-        <v>52658.0</v>
-      </c>
-      <c r="H51" s="9">
-        <v>153840.0</v>
-      </c>
-      <c r="I51" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D52" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F52" s="9">
-        <v>87447.0</v>
-      </c>
-      <c r="G52" s="9">
-        <v>59056.0</v>
-      </c>
-      <c r="H52" s="9">
-        <v>104365.0</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J52" s="12"/>
-    </row>
-    <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D53" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" s="9">
-        <v>25200.0</v>
-      </c>
-      <c r="G53" s="9">
-        <v>2085.0</v>
-      </c>
-      <c r="H53" s="9">
-        <v>25920.0</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" ht="22.5" hidden="1" customHeight="1">
-      <c r="A54" s="5">
-        <v>46226.0</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D54" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="9">
-        <v>285405.0</v>
-      </c>
-      <c r="G54" s="9">
-        <v>203180.0</v>
-      </c>
-      <c r="H54" s="9">
-        <v>226069.0</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="55" ht="22.5" hidden="1" customHeight="1">
-      <c r="A55" s="5">
-        <v>46226.0</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D55" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="9">
-        <v>692280.0</v>
-      </c>
-      <c r="G55" s="9">
-        <v>118381.0</v>
-      </c>
-      <c r="H55" s="9">
-        <v>700200.0</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="J55" s="12"/>
-    </row>
-    <row r="56" ht="22.5" hidden="1" customHeight="1">
-      <c r="A56" s="5">
-        <v>46227.0</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="9">
-        <v>700200.0</v>
-      </c>
-      <c r="G56" s="9">
-        <v>112628.0</v>
-      </c>
-      <c r="H56" s="9">
-        <v>668440.0</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J56" s="12"/>
-    </row>
-    <row r="57" ht="22.5" hidden="1" customHeight="1">
-      <c r="A57" s="5">
-        <v>46227.0</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D57" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F57" s="9">
-        <v>226069.0</v>
-      </c>
-      <c r="G57" s="9">
-        <v>193130.0</v>
-      </c>
-      <c r="H57" s="9">
-        <v>326391.0</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J57" s="12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" ht="22.5" hidden="1" customHeight="1">
-      <c r="A58" s="5">
-        <v>46227.0</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D58" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="9">
-        <v>144637.0</v>
-      </c>
-      <c r="G58" s="9">
-        <v>64227.0</v>
-      </c>
-      <c r="H58" s="9">
-        <v>128160.0</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="J58" s="12"/>
-    </row>
-    <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="5">
-        <v>46227.0</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D59" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F59" s="9">
-        <v>295359.0</v>
-      </c>
-      <c r="G59" s="9">
-        <v>126369.0</v>
-      </c>
-      <c r="H59" s="9">
-        <v>166642.0</v>
-      </c>
-      <c r="I59" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="5">
-        <v>46230.0</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D60" s="9">
-        <v>2110403.0</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F60" s="9">
-        <v>9960.0</v>
-      </c>
-      <c r="G60" s="9">
-        <v>6018.0</v>
-      </c>
-      <c r="H60" s="9">
-        <v>3660.0</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J60" s="12"/>
-    </row>
-    <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="5">
-        <v>46230.0</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D61" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F61" s="9">
-        <v>306720.0</v>
-      </c>
-      <c r="G61" s="9">
-        <v>164175.0</v>
-      </c>
-      <c r="H61" s="9">
-        <v>247096.0</v>
-      </c>
-      <c r="I61" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61" s="12"/>
-    </row>
-    <row r="62" ht="22.5" hidden="1" customHeight="1">
-      <c r="A62" s="5">
-        <v>46230.0</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D62" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="9">
+      <c r="F62" s="7">
         <v>437080.0</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62" s="7">
         <v>277785.0</v>
       </c>
-      <c r="H62" s="9">
+      <c r="H62" s="7">
         <v>353700.0</v>
       </c>
-      <c r="I62" s="13" t="s">
-        <v>33</v>
+      <c r="I62" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J62" s="12" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
-      <c r="A63" s="5">
+      <c r="A63" s="9">
         <v>46231.0</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D63" s="9">
+      <c r="B63" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" s="9">
+      <c r="E63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="7">
         <v>165466.0</v>
       </c>
-      <c r="G63" s="9">
+      <c r="G63" s="7">
         <v>113462.0</v>
       </c>
-      <c r="H63" s="9">
+      <c r="H63" s="7">
         <v>375549.0</v>
       </c>
-      <c r="I63" s="13" t="s">
-        <v>33</v>
+      <c r="I63" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J63" s="12" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
-      <c r="A64" s="5">
+      <c r="A64" s="9">
         <v>46231.0</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D64" s="9">
+      <c r="B64" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F64" s="9">
+      <c r="E64" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" s="7">
         <v>238497.0</v>
       </c>
-      <c r="G64" s="9">
+      <c r="G64" s="7">
         <v>56526.0</v>
       </c>
-      <c r="H64" s="9">
+      <c r="H64" s="7">
         <v>181858.0</v>
       </c>
-      <c r="I64" s="13" t="s">
-        <v>46</v>
+      <c r="I64" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="J64" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
-      <c r="A65" s="5">
+      <c r="A65" s="9">
         <v>46231.0</v>
       </c>
-      <c r="B65" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D65" s="9">
+      <c r="B65" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="7">
         <v>2110317.0</v>
       </c>
-      <c r="E65" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F65" s="9">
+      <c r="E65" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F65" s="7">
         <v>8190.0</v>
       </c>
-      <c r="G65" s="9">
+      <c r="G65" s="7">
         <v>2049.0</v>
       </c>
-      <c r="H65" s="9">
+      <c r="H65" s="7">
         <v>7200.0</v>
       </c>
-      <c r="I65" s="13" t="s">
-        <v>46</v>
+      <c r="I65" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
-      <c r="A66" s="5">
+      <c r="A66" s="9">
         <v>46231.0</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D66" s="9">
+      <c r="B66" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D66" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="9">
+      <c r="E66" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="7">
         <v>146224.0</v>
       </c>
-      <c r="G66" s="9">
+      <c r="G66" s="7">
         <v>78064.0</v>
       </c>
-      <c r="H66" s="9">
+      <c r="H66" s="7">
         <v>98850.0</v>
       </c>
-      <c r="I66" s="13" t="s">
-        <v>46</v>
+      <c r="I66" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
-      <c r="A67" s="5">
+      <c r="A67" s="9">
         <v>46232.0</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="5" t="s">
         <v>120</v>
       </c>
       <c r="C67" s="21"/>
-      <c r="D67" s="9">
+      <c r="D67" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="9">
+      <c r="E67" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="7">
         <v>14599.0</v>
       </c>
-      <c r="G67" s="9">
+      <c r="G67" s="7">
         <v>3782.0</v>
       </c>
-      <c r="H67" s="9">
+      <c r="H67" s="7">
         <v>7263.0</v>
       </c>
-      <c r="I67" s="13" t="s">
+      <c r="I67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J67" s="12"/>
+    </row>
+    <row r="68" ht="22.5" hidden="1" customHeight="1">
+      <c r="A68" s="9">
+        <v>46232.0</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="21"/>
+      <c r="D68" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J67" s="12"/>
-    </row>
-    <row r="68" ht="22.5" hidden="1" customHeight="1">
-      <c r="A68" s="5">
+      <c r="F68" s="7">
+        <v>22080.0</v>
+      </c>
+      <c r="G68" s="7">
+        <v>5686.0</v>
+      </c>
+      <c r="H68" s="7">
+        <v>36720.0</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J68" s="12"/>
+    </row>
+    <row r="69" ht="22.5" hidden="1" customHeight="1">
+      <c r="A69" s="9">
         <v>46232.0</v>
       </c>
-      <c r="B68" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C68" s="21"/>
-      <c r="D68" s="9">
+      <c r="B69" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" s="21"/>
+      <c r="D69" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F68" s="9">
-        <v>22080.0</v>
-      </c>
-      <c r="G68" s="9">
-        <v>5686.0</v>
-      </c>
-      <c r="H68" s="9">
-        <v>36720.0</v>
-      </c>
-      <c r="I68" s="13" t="s">
+      <c r="E69" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J68" s="12"/>
-    </row>
-    <row r="69" ht="22.5" hidden="1" customHeight="1">
-      <c r="A69" s="5">
+      <c r="F69" s="7">
+        <v>353905.0</v>
+      </c>
+      <c r="G69" s="7">
+        <v>208296.0</v>
+      </c>
+      <c r="H69" s="7">
+        <v>117570.0</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J69" s="12"/>
+    </row>
+    <row r="70" ht="22.5" hidden="1" customHeight="1">
+      <c r="A70" s="9">
         <v>46232.0</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C69" s="21"/>
-      <c r="D69" s="9">
+      <c r="B70" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" s="21"/>
+      <c r="D70" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F70" s="7">
+        <v>5913.0</v>
+      </c>
+      <c r="G70" s="7">
+        <v>902.0</v>
+      </c>
+      <c r="H70" s="7">
+        <v>5893.0</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J70" s="12"/>
+    </row>
+    <row r="71" ht="22.5" hidden="1" customHeight="1">
+      <c r="A71" s="9">
+        <v>46232.0</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="21"/>
+      <c r="D71" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71" s="7">
+        <v>256613.0</v>
+      </c>
+      <c r="G71" s="7">
+        <v>86092.0</v>
+      </c>
+      <c r="H71" s="7">
+        <v>142320.0</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J71" s="12"/>
+    </row>
+    <row r="72" ht="22.5" hidden="1" customHeight="1">
+      <c r="A72" s="9">
+        <v>46232.0</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="21"/>
+      <c r="D72" s="7">
+        <v>152384.0</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F72" s="7">
+        <v>21300.0</v>
+      </c>
+      <c r="G72" s="7">
+        <v>9765.0</v>
+      </c>
+      <c r="H72" s="7">
+        <v>18690.0</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J72" s="12"/>
+    </row>
+    <row r="73" ht="22.5" hidden="1" customHeight="1">
+      <c r="A73" s="9">
+        <v>46232.0</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" s="21"/>
+      <c r="D73" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F69" s="9">
-        <v>353905.0</v>
-      </c>
-      <c r="G69" s="9">
-        <v>208296.0</v>
-      </c>
-      <c r="H69" s="9">
-        <v>117570.0</v>
-      </c>
-      <c r="I69" s="13" t="s">
+      <c r="E73" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J69" s="12"/>
-    </row>
-    <row r="70" ht="22.5" hidden="1" customHeight="1">
-      <c r="A70" s="5">
-        <v>46232.0</v>
-      </c>
-      <c r="B70" s="6" t="s">
+      <c r="F73" s="7">
+        <v>351733.0</v>
+      </c>
+      <c r="G73" s="7">
+        <v>145994.0</v>
+      </c>
+      <c r="H73" s="7">
+        <v>200114.0</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J73" s="12"/>
+    </row>
+    <row r="74" ht="22.5" hidden="1" customHeight="1">
+      <c r="A74" s="17">
+        <v>46233.0</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D74" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74" s="7">
+        <v>158761.0</v>
+      </c>
+      <c r="G74" s="7">
+        <v>68908.0</v>
+      </c>
+      <c r="H74" s="7">
+        <v>183014.0</v>
+      </c>
+      <c r="I74" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="C70" s="21"/>
-      <c r="D70" s="9">
-        <v>2010102.0</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F70" s="9">
-        <v>5913.0</v>
-      </c>
-      <c r="G70" s="9">
-        <v>902.0</v>
-      </c>
-      <c r="H70" s="9">
-        <v>5893.0</v>
-      </c>
-      <c r="I70" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J70" s="12"/>
-    </row>
-    <row r="71" ht="22.5" hidden="1" customHeight="1">
-      <c r="A71" s="5">
-        <v>46232.0</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F71" s="9">
-        <v>256613.0</v>
-      </c>
-      <c r="G71" s="9">
-        <v>86092.0</v>
-      </c>
-      <c r="H71" s="9">
-        <v>142320.0</v>
-      </c>
-      <c r="I71" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J71" s="12"/>
-    </row>
-    <row r="72" ht="22.5" hidden="1" customHeight="1">
-      <c r="A72" s="5">
-        <v>46232.0</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="9">
-        <v>152384.0</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F72" s="9">
-        <v>21300.0</v>
-      </c>
-      <c r="G72" s="9">
-        <v>9765.0</v>
-      </c>
-      <c r="H72" s="9">
-        <v>18690.0</v>
-      </c>
-      <c r="I72" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" s="12"/>
-    </row>
-    <row r="73" ht="22.5" hidden="1" customHeight="1">
-      <c r="A73" s="5">
-        <v>46232.0</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="9">
-        <v>351733.0</v>
-      </c>
-      <c r="G73" s="9">
-        <v>145994.0</v>
-      </c>
-      <c r="H73" s="9">
-        <v>200114.0</v>
-      </c>
-      <c r="I73" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" s="12"/>
-    </row>
-    <row r="74" ht="22.5" hidden="1" customHeight="1">
-      <c r="A74" s="18">
-        <v>46233.0</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C74" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D74" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F74" s="9">
-        <v>158761.0</v>
-      </c>
-      <c r="G74" s="9">
-        <v>68908.0</v>
-      </c>
-      <c r="H74" s="9">
-        <v>183014.0</v>
-      </c>
-      <c r="I74" s="13" t="s">
-        <v>75</v>
       </c>
       <c r="J74" s="12" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
-      <c r="A75" s="18">
+      <c r="A75" s="17">
         <v>46233.0</v>
       </c>
-      <c r="B75" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D75" s="9">
+      <c r="B75" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D75" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F75" s="9">
+      <c r="E75" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75" s="7">
         <v>117430.0</v>
       </c>
-      <c r="G75" s="9">
+      <c r="G75" s="7">
         <v>57323.0</v>
       </c>
-      <c r="H75" s="9">
+      <c r="H75" s="7">
         <v>86643.0</v>
       </c>
-      <c r="I75" s="13" t="s">
-        <v>22</v>
+      <c r="I75" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="J75" s="12"/>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
-      <c r="A76" s="5">
+      <c r="A76" s="9">
         <v>46234.0</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C76" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D76" s="9">
+      <c r="C76" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D76" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F76" s="9">
+      <c r="E76" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76" s="7">
         <v>265693.0</v>
       </c>
-      <c r="G76" s="9">
+      <c r="G76" s="7">
         <v>83477.0</v>
       </c>
-      <c r="H76" s="9">
+      <c r="H76" s="7">
         <v>116000.0</v>
       </c>
-      <c r="I76" s="13" t="s">
-        <v>22</v>
+      <c r="I76" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="J76" s="12"/>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
-      <c r="A77" s="5">
+      <c r="A77" s="9">
         <v>46234.0</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D77" s="9">
+      <c r="D77" s="7">
         <v>112357.0</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F77" s="9">
+      <c r="E77" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F77" s="7">
         <v>720.0</v>
       </c>
-      <c r="G77" s="9">
+      <c r="G77" s="7">
         <v>360.0</v>
       </c>
-      <c r="H77" s="9">
+      <c r="H77" s="7">
         <v>2040.0</v>
       </c>
-      <c r="I77" s="13" t="s">
-        <v>16</v>
+      <c r="I77" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="J77" s="12" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
-      <c r="A78" s="5">
+      <c r="A78" s="9">
         <v>46234.0</v>
       </c>
-      <c r="B78" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D78" s="9">
+      <c r="B78" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" s="7">
         <v>2110317.0</v>
       </c>
-      <c r="E78" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F78" s="9">
+      <c r="E78" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F78" s="7">
         <v>5580.0</v>
       </c>
-      <c r="G78" s="9">
+      <c r="G78" s="7">
         <v>2192.0</v>
       </c>
-      <c r="H78" s="9">
+      <c r="H78" s="7">
         <v>3984.0</v>
       </c>
-      <c r="I78" s="13" t="s">
-        <v>46</v>
+      <c r="I78" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="J78" s="12" t="s">
         <v>125</v>
@@ -3289,29 +3289,29 @@
       <c r="A79" s="19">
         <v>46237.0</v>
       </c>
-      <c r="B79" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D79" s="9">
+      <c r="B79" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D79" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E79" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="9">
+      <c r="E79" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="7">
         <v>192903.0</v>
       </c>
-      <c r="G79" s="9">
+      <c r="G79" s="7">
         <v>150030.0</v>
       </c>
-      <c r="H79" s="9">
+      <c r="H79" s="7">
         <v>77501.0</v>
       </c>
-      <c r="I79" s="13" t="s">
-        <v>46</v>
+      <c r="I79" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="J79" s="12" t="s">
         <v>126</v>
@@ -3321,29 +3321,29 @@
       <c r="A80" s="19">
         <v>46237.0</v>
       </c>
-      <c r="B80" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D80" s="9">
+      <c r="B80" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D80" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E80" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F80" s="9">
+      <c r="E80" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80" s="7">
         <v>152062.0</v>
       </c>
-      <c r="G80" s="9">
+      <c r="G80" s="7">
         <v>112769.0</v>
       </c>
-      <c r="H80" s="9">
+      <c r="H80" s="7">
         <v>124423.0</v>
       </c>
-      <c r="I80" s="13" t="s">
-        <v>46</v>
+      <c r="I80" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="J80" s="12" t="s">
         <v>126</v>
@@ -3353,29 +3353,29 @@
       <c r="A81" s="19">
         <v>46237.0</v>
       </c>
-      <c r="B81" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C81" s="7" t="s">
+      <c r="B81" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C81" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D81" s="9">
+      <c r="D81" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E81" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F81" s="9">
+      <c r="E81" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F81" s="7">
         <v>153692.0</v>
       </c>
-      <c r="G81" s="9">
+      <c r="G81" s="7">
         <v>136980.0</v>
       </c>
-      <c r="H81" s="9">
+      <c r="H81" s="7">
         <v>63920.0</v>
       </c>
-      <c r="I81" s="13" t="s">
-        <v>75</v>
+      <c r="I81" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="J81" s="12" t="s">
         <v>128</v>
@@ -3385,29 +3385,29 @@
       <c r="A82" s="19">
         <v>46237.0</v>
       </c>
-      <c r="B82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C82" s="7" t="s">
+      <c r="B82" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D82" s="9">
+      <c r="D82" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F82" s="9">
+      <c r="E82" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F82" s="7">
         <v>45564.0</v>
       </c>
-      <c r="G82" s="9">
+      <c r="G82" s="7">
         <v>10456.0</v>
       </c>
-      <c r="H82" s="9">
+      <c r="H82" s="7">
         <v>40560.0</v>
       </c>
-      <c r="I82" s="13" t="s">
-        <v>15</v>
+      <c r="I82" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="J82" s="12"/>
     </row>
@@ -3415,304 +3415,304 @@
       <c r="A83" s="19">
         <v>46237.0</v>
       </c>
-      <c r="B83" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D83" s="9">
+      <c r="B83" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E83" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F83" s="9">
+      <c r="E83" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83" s="7">
         <v>93517.0</v>
       </c>
-      <c r="G83" s="9">
+      <c r="G83" s="7">
         <v>18622.0</v>
       </c>
-      <c r="H83" s="9">
+      <c r="H83" s="7">
         <v>48804.0</v>
       </c>
-      <c r="I83" s="13" t="s">
-        <v>33</v>
+      <c r="I83" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J83" s="12" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
-      <c r="A84" s="5">
+      <c r="A84" s="9">
         <v>46238.0</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D84" s="9">
+      <c r="C84" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D84" s="7">
         <v>2110317.0</v>
       </c>
-      <c r="E84" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F84" s="9">
+      <c r="E84" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F84" s="7">
         <v>43200.0</v>
       </c>
-      <c r="G84" s="9">
+      <c r="G84" s="7">
         <v>5340.0</v>
       </c>
-      <c r="H84" s="9">
+      <c r="H84" s="7">
         <v>40890.0</v>
       </c>
-      <c r="I84" s="13" t="s">
-        <v>22</v>
+      <c r="I84" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="J84" s="12"/>
     </row>
     <row r="85" ht="22.5" customHeight="1">
-      <c r="A85" s="5">
+      <c r="A85" s="9">
         <v>46238.0</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C85" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D85" s="9">
+      <c r="C85" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D85" s="7">
         <v>152384.0</v>
       </c>
-      <c r="E85" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F85" s="9">
+      <c r="E85" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F85" s="7">
         <v>25350.0</v>
       </c>
-      <c r="G85" s="9">
+      <c r="G85" s="7">
         <v>6240.0</v>
       </c>
-      <c r="H85" s="9">
+      <c r="H85" s="7">
         <v>30750.0</v>
       </c>
-      <c r="I85" s="13" t="s">
+      <c r="I85" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J85" s="12"/>
+    </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="A86" s="9">
+        <v>46238.0</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D86" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F86" s="7">
+        <v>5040.0</v>
+      </c>
+      <c r="G86" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="H86" s="7">
+        <v>4680.0</v>
+      </c>
+      <c r="I86" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="12"/>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="9">
+        <v>46238.0</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C87" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J85" s="12"/>
-    </row>
-    <row r="86" ht="22.5" customHeight="1">
-      <c r="A86" s="5">
-        <v>46238.0</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D86" s="9">
-        <v>2152388.0</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F86" s="9">
-        <v>5040.0</v>
-      </c>
-      <c r="G86" s="9">
-        <v>720.0</v>
-      </c>
-      <c r="H86" s="9">
-        <v>4680.0</v>
-      </c>
-      <c r="I86" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J86" s="12"/>
-    </row>
-    <row r="87" ht="22.5" customHeight="1">
-      <c r="A87" s="5">
-        <v>46238.0</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D87" s="9">
+      <c r="D87" s="7">
         <v>2110302.0</v>
       </c>
-      <c r="E87" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F87" s="9">
+      <c r="E87" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87" s="7">
         <v>124423.0</v>
       </c>
-      <c r="G87" s="9">
+      <c r="G87" s="7">
         <v>60002.0</v>
       </c>
-      <c r="H87" s="9">
+      <c r="H87" s="7">
         <v>69217.0</v>
       </c>
-      <c r="I87" s="13" t="s">
-        <v>33</v>
+      <c r="I87" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J87" s="12" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
-      <c r="A88" s="5">
+      <c r="A88" s="9">
         <v>46239.0</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C88" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D88" s="9">
+      <c r="C88" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D88" s="7">
         <v>152384.0</v>
       </c>
-      <c r="E88" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="9">
+      <c r="E88" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F88" s="7">
         <v>30750.0</v>
       </c>
-      <c r="G88" s="9">
+      <c r="G88" s="7">
         <v>9975.0</v>
       </c>
-      <c r="H88" s="9">
+      <c r="H88" s="7">
         <v>36300.0</v>
       </c>
-      <c r="I88" s="13" t="s">
+      <c r="I88" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J88" s="12"/>
+    </row>
+    <row r="89" ht="22.5" customHeight="1">
+      <c r="A89" s="9">
+        <v>46239.0</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J88" s="12"/>
-    </row>
-    <row r="89" ht="22.5" customHeight="1">
-      <c r="A89" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D89" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F89" s="9">
+      <c r="F89" s="7">
         <v>58320.0</v>
       </c>
-      <c r="G89" s="9">
+      <c r="G89" s="7">
         <v>53468.0</v>
       </c>
-      <c r="H89" s="9">
+      <c r="H89" s="7">
         <v>12480.0</v>
       </c>
-      <c r="I89" s="13" t="s">
-        <v>33</v>
+      <c r="I89" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J89" s="12" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
-      <c r="A90" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C90" s="7" t="s">
+      <c r="A90" s="19">
+        <v>46240.0</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="7">
+        <v>254880.0</v>
+      </c>
+      <c r="G90" s="7">
+        <v>151786.0</v>
+      </c>
+      <c r="H90" s="7">
+        <v>27180.0</v>
+      </c>
+      <c r="I90" s="10" t="s">
         <v>26</v>
-      </c>
-      <c r="D90" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F90" s="9">
-        <v>254880.0</v>
-      </c>
-      <c r="G90" s="9">
-        <v>151786.0</v>
-      </c>
-      <c r="H90" s="9">
-        <v>27180.0</v>
-      </c>
-      <c r="I90" s="13" t="s">
-        <v>16</v>
       </c>
       <c r="J90" s="12" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
-      <c r="A91" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C91" s="7" t="s">
+      <c r="A91" s="19">
+        <v>46240.0</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="7">
         <v>112379.0</v>
       </c>
-      <c r="E91" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F91" s="9">
+      <c r="E91" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F91" s="7">
         <v>13800.0</v>
       </c>
-      <c r="G91" s="9">
+      <c r="G91" s="7">
         <v>900.0</v>
       </c>
-      <c r="H91" s="9">
+      <c r="H91" s="7">
         <v>12132.0</v>
       </c>
-      <c r="I91" s="13" t="s">
-        <v>33</v>
+      <c r="I91" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J91" s="12"/>
     </row>
     <row r="92" ht="22.5" customHeight="1">
-      <c r="A92" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B92" s="6" t="s">
+      <c r="A92" s="19">
+        <v>46240.0</v>
+      </c>
+      <c r="B92" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C92" s="21"/>
-      <c r="D92" s="9">
+      <c r="D92" s="7">
         <v>2152388.0</v>
       </c>
-      <c r="E92" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F92" s="9">
+      <c r="E92" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F92" s="7">
         <v>4575.0</v>
       </c>
-      <c r="G92" s="9">
+      <c r="G92" s="7">
         <v>570.0</v>
       </c>
-      <c r="H92" s="9">
+      <c r="H92" s="7">
         <v>4213.0</v>
       </c>
-      <c r="I92" s="13"/>
+      <c r="I92" s="10"/>
       <c r="J92" s="12"/>
     </row>
     <row r="93">
@@ -6531,992 +6531,992 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="5">
+      <c r="A2" s="9">
         <v>46224.0</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9">
+      <c r="B2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="7">
         <v>2110402.0</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="9">
+      <c r="E2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="7">
         <v>333.0</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="7">
         <v>6480.0</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="7">
         <v>3712.0</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" hidden="1" customHeight="1">
+      <c r="A3" s="9">
+        <v>46224.0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="7">
+        <v>2114158.0</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="7">
+        <v>60.0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1000.0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>60.0</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
+      <c r="A4" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="7">
+        <v>10501.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="7">
+        <v>415093.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>115920.0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>543038.0</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
+      <c r="A5" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>29400.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>12300.0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="7">
+        <v>132357.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1560.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1560.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>4560.0</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>11160.0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>5940.0</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
+      <c r="A9" s="9">
+        <v>46225.0</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="F9" s="7">
+        <v>3712.0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>46723.0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>213.0</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
+      <c r="A10" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="7">
+        <v>73001.0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="7">
+        <v>73787.0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>72000.0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>109487.0</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>1800.0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="12"/>
+    </row>
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
+      <c r="A12" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="7">
+        <v>4200.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>7500.0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>3900.0</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="12"/>
+    </row>
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
+      <c r="A13" s="9">
+        <v>46226.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="7">
+        <v>379471.0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>392580.0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>357186.0</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
+      <c r="A14" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="7">
+        <v>72001.0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="7">
+        <v>21905.0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>47670.0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>38000.0</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="7">
+        <v>2110327.0</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="7">
+        <v>69120.0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>57600.0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>40320.0</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
+      <c r="A16" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="7">
+        <v>3900.0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>102600.0</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1500.0</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" ht="22.5" hidden="1" customHeight="1">
+      <c r="A17" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>9720.0</v>
+      </c>
+      <c r="H17" s="7">
+        <v>2580.0</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="12"/>
+    </row>
+    <row r="18" ht="22.5" hidden="1" customHeight="1">
+      <c r="A18" s="9">
+        <v>46227.0</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>30600.0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>600.0</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
+      <c r="A19" s="9">
+        <v>46230.0</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="7">
+        <v>2410401.0</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="7">
+        <v>136538.0</v>
+      </c>
+      <c r="G19" s="7">
+        <v>34080.0</v>
+      </c>
+      <c r="H19" s="7">
+        <v>213000.0</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
+      <c r="A20" s="9">
+        <v>46231.0</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="7">
+        <v>591750.0</v>
+      </c>
+      <c r="G20" s="7">
+        <v>239760.0</v>
+      </c>
+      <c r="H20" s="7">
+        <v>577207.0</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
+      <c r="A21" s="9">
+        <v>46231.0</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="7">
+        <v>10601.0</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1230.0</v>
+      </c>
+      <c r="G21" s="7">
+        <v>8626.0</v>
+      </c>
+      <c r="H21" s="7">
+        <v>1958.0</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" hidden="1" customHeight="1">
+      <c r="A22" s="9">
+        <v>46231.0</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="7">
+        <v>4320.0</v>
+      </c>
+      <c r="G22" s="7">
+        <v>2700.0</v>
+      </c>
+      <c r="H22" s="7">
+        <v>3420.0</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="12"/>
+    </row>
+    <row r="23" ht="22.5" hidden="1" customHeight="1">
+      <c r="A23" s="9">
+        <v>46231.0</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="7">
+        <v>114357.0</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="7">
+        <v>240.0</v>
+      </c>
+      <c r="G23" s="7">
+        <v>52320.0</v>
+      </c>
+      <c r="H23" s="7">
+        <v>240.0</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="12"/>
+    </row>
+    <row r="24" ht="22.5" hidden="1" customHeight="1">
+      <c r="A24" s="9">
+        <v>46232.0</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="7">
+        <v>10501.0</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="7">
+        <v>19663.0</v>
+      </c>
+      <c r="G24" s="7">
+        <v>49540.0</v>
+      </c>
+      <c r="H24" s="7">
+        <v>29632.0</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="12"/>
+    </row>
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
+      <c r="A25" s="9">
+        <v>46232.0</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="7">
+        <v>5700.0</v>
+      </c>
+      <c r="G25" s="7">
+        <v>34800.0</v>
+      </c>
+      <c r="H25" s="7">
+        <v>5100.0</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
+      <c r="A26" s="9">
+        <v>46232.0</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="7">
+        <v>2110317.0</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="G26" s="7">
+        <v>7920.0</v>
+      </c>
+      <c r="H26" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" s="12"/>
+    </row>
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
+      <c r="A27" s="9">
+        <v>46232.0</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="7">
+        <v>2114357.0</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="7">
+        <v>432.0</v>
+      </c>
+      <c r="G27" s="7">
+        <v>576.0</v>
+      </c>
+      <c r="H27" s="7">
+        <v>432.0</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="12"/>
+    </row>
+    <row r="28" ht="22.5" hidden="1" customHeight="1">
+      <c r="A28" s="9">
+        <v>46232.0</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="7">
+        <v>10501.0</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="7">
+        <v>219540.0</v>
+      </c>
+      <c r="G28" s="7">
+        <v>272160.0</v>
+      </c>
+      <c r="H28" s="7">
+        <v>16698.0</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" s="12"/>
+    </row>
+    <row r="29" ht="22.5" hidden="1" customHeight="1">
+      <c r="A29" s="9">
+        <v>46233.0</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="7">
+        <v>5100.0</v>
+      </c>
+      <c r="G29" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="H29" s="7">
+        <v>4800.0</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="12"/>
+    </row>
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
+      <c r="A30" s="9">
+        <v>46233.0</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="7">
+        <v>114357.0</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="7">
+        <v>240.0</v>
+      </c>
+      <c r="G30" s="7">
+        <v>7800.0</v>
+      </c>
+      <c r="H30" s="7">
+        <v>1560.0</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" s="12"/>
+    </row>
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="9">
+        <v>46233.0</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="7">
+        <v>10601.0</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="7">
+        <v>7717.0</v>
+      </c>
+      <c r="G31" s="7">
+        <v>10080.0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>12867.0</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
+      <c r="A32" s="9">
+        <v>46234.0</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="7">
+        <v>79110.0</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F32" s="7">
+        <v>48000.0</v>
+      </c>
+      <c r="G32" s="7">
+        <v>24600.0</v>
+      </c>
+      <c r="H32" s="7">
+        <v>36300.0</v>
+      </c>
+      <c r="I32" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="5">
-        <v>46224.0</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9">
-        <v>2114158.0</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="9">
-        <v>60.0</v>
-      </c>
-      <c r="G3" s="9">
-        <v>1000.0</v>
-      </c>
-      <c r="H3" s="9">
-        <v>60.0</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="9">
+      <c r="J32" s="18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
+      <c r="A33" s="9">
+        <v>46234.0</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="7">
         <v>10501.0</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="9">
-        <v>415093.0</v>
-      </c>
-      <c r="G4" s="9">
-        <v>115920.0</v>
-      </c>
-      <c r="H4" s="9">
-        <v>543038.0</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="9">
-        <v>112379.0</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="9">
-        <v>3000.0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>29400.0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>3000.0</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="9">
-        <v>112268.0</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="9">
-        <v>3000.0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>12300.0</v>
-      </c>
-      <c r="H6" s="9">
-        <v>3300.0</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="9">
-        <v>132357.0</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="9">
-        <v>1560.0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>1560.0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>4560.0</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="9">
-        <v>2152388.0</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="9">
-        <v>720.0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>11160.0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>5940.0</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="9">
-        <v>3712.0</v>
-      </c>
-      <c r="G9" s="9">
-        <v>46723.0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>213.0</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="12" t="s">
+      <c r="E33" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="7">
+        <v>95574.0</v>
+      </c>
+      <c r="G33" s="7">
+        <v>78469.0</v>
+      </c>
+      <c r="H33" s="7">
+        <v>142801.0</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
+      <c r="A34" s="9">
+        <v>46234.0</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="5">
-        <v>46226.0</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="9">
+      <c r="C34" s="16"/>
+      <c r="D34" s="7">
         <v>73001.0</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="9">
-        <v>73787.0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>72000.0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>109487.0</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="5">
-        <v>46226.0</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="9">
-        <v>112268.0</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="9">
-        <v>3300.0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>1800.0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>3300.0</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="12"/>
-    </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="5">
-        <v>46226.0</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="9">
-        <v>112379.0</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="9">
-        <v>4200.0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>7500.0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>3900.0</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="5">
-        <v>46226.0</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="9">
-        <v>379471.0</v>
-      </c>
-      <c r="G13" s="9">
-        <v>392580.0</v>
-      </c>
-      <c r="H13" s="9">
-        <v>357186.0</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="5">
-        <v>46227.0</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="9">
-        <v>72001.0</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="9">
-        <v>21905.0</v>
-      </c>
-      <c r="G14" s="9">
-        <v>47670.0</v>
-      </c>
-      <c r="H14" s="9">
-        <v>38000.0</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="5">
-        <v>46227.0</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="9">
-        <v>2110327.0</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="9">
-        <v>69120.0</v>
-      </c>
-      <c r="G15" s="9">
-        <v>57600.0</v>
-      </c>
-      <c r="H15" s="9">
-        <v>40320.0</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="5">
-        <v>46227.0</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="9">
-        <v>112379.0</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="9">
-        <v>3900.0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>102600.0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>1500.0</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="5">
-        <v>46227.0</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="9">
-        <v>2152388.0</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="9">
-        <v>720.0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>9720.0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>2580.0</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" s="12"/>
-    </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="5">
-        <v>46227.0</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="9">
-        <v>112268.0</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="9">
-        <v>3300.0</v>
-      </c>
-      <c r="G18" s="9">
-        <v>30600.0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>600.0</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="5">
-        <v>46230.0</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="9">
-        <v>2410401.0</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="9">
-        <v>136538.0</v>
-      </c>
-      <c r="G19" s="9">
-        <v>34080.0</v>
-      </c>
-      <c r="H19" s="9">
-        <v>213000.0</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="5">
-        <v>46231.0</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="9">
-        <v>2110202.0</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="9">
-        <v>591750.0</v>
-      </c>
-      <c r="G20" s="9">
-        <v>239760.0</v>
-      </c>
-      <c r="H20" s="9">
-        <v>577207.0</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="5">
-        <v>46231.0</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="9">
-        <v>10601.0</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="9">
-        <v>1230.0</v>
-      </c>
-      <c r="G21" s="9">
-        <v>8626.0</v>
-      </c>
-      <c r="H21" s="9">
-        <v>1958.0</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="5">
-        <v>46231.0</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="9">
-        <v>2152388.0</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="9">
-        <v>4320.0</v>
-      </c>
-      <c r="G22" s="9">
-        <v>2700.0</v>
-      </c>
-      <c r="H22" s="9">
-        <v>3420.0</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="12"/>
-    </row>
-    <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="5">
-        <v>46231.0</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="9">
-        <v>114357.0</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="9">
-        <v>240.0</v>
-      </c>
-      <c r="G23" s="9">
-        <v>52320.0</v>
-      </c>
-      <c r="H23" s="9">
-        <v>240.0</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="12"/>
-    </row>
-    <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="5">
-        <v>46232.0</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="9">
-        <v>10501.0</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="9">
-        <v>19663.0</v>
-      </c>
-      <c r="G24" s="9">
-        <v>49540.0</v>
-      </c>
-      <c r="H24" s="9">
-        <v>29632.0</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="12"/>
-    </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="5">
-        <v>46232.0</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="9">
-        <v>112268.0</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="9">
-        <v>5700.0</v>
-      </c>
-      <c r="G25" s="9">
-        <v>34800.0</v>
-      </c>
-      <c r="H25" s="9">
-        <v>5100.0</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="12"/>
-    </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="5">
-        <v>46232.0</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="9">
-        <v>2110317.0</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="9">
-        <v>720.0</v>
-      </c>
-      <c r="G26" s="9">
-        <v>7920.0</v>
-      </c>
-      <c r="H26" s="9">
-        <v>720.0</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="12"/>
-    </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="5">
-        <v>46232.0</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="9">
-        <v>2114357.0</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" s="9">
-        <v>432.0</v>
-      </c>
-      <c r="G27" s="9">
-        <v>576.0</v>
-      </c>
-      <c r="H27" s="9">
-        <v>432.0</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="12"/>
-    </row>
-    <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="5">
-        <v>46232.0</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="9">
-        <v>10501.0</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="9">
-        <v>219540.0</v>
-      </c>
-      <c r="G28" s="9">
-        <v>272160.0</v>
-      </c>
-      <c r="H28" s="9">
-        <v>16698.0</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="12"/>
-    </row>
-    <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="5">
-        <v>46233.0</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="9">
-        <v>112268.0</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="9">
-        <v>5100.0</v>
-      </c>
-      <c r="G29" s="9">
-        <v>3300.0</v>
-      </c>
-      <c r="H29" s="9">
-        <v>4800.0</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" s="12"/>
-    </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="5">
-        <v>46233.0</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="9">
-        <v>114357.0</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="9">
-        <v>240.0</v>
-      </c>
-      <c r="G30" s="9">
-        <v>7800.0</v>
-      </c>
-      <c r="H30" s="9">
-        <v>1560.0</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J30" s="12"/>
-    </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="5">
-        <v>46233.0</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="9">
-        <v>10601.0</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F31" s="9">
-        <v>7717.0</v>
-      </c>
-      <c r="G31" s="9">
-        <v>10080.0</v>
-      </c>
-      <c r="H31" s="9">
-        <v>12867.0</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="5">
+      <c r="E34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="7">
+        <v>73367.0</v>
+      </c>
+      <c r="G34" s="7">
+        <v>94608.0</v>
+      </c>
+      <c r="H34" s="7">
+        <v>39150.0</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="12"/>
+    </row>
+    <row r="35" ht="22.5" hidden="1" customHeight="1">
+      <c r="A35" s="9">
         <v>46234.0</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="9">
-        <v>79110.0</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32" s="9">
-        <v>48000.0</v>
-      </c>
-      <c r="G32" s="9">
-        <v>24600.0</v>
-      </c>
-      <c r="H32" s="9">
-        <v>36300.0</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="5">
-        <v>46234.0</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="9">
-        <v>10501.0</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="9">
-        <v>95574.0</v>
-      </c>
-      <c r="G33" s="9">
-        <v>78469.0</v>
-      </c>
-      <c r="H33" s="9">
-        <v>142801.0</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="5">
-        <v>46234.0</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="9">
-        <v>73001.0</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F34" s="9">
-        <v>73367.0</v>
-      </c>
-      <c r="G34" s="9">
-        <v>94608.0</v>
-      </c>
-      <c r="H34" s="9">
-        <v>39150.0</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="12"/>
-    </row>
-    <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="5">
-        <v>46234.0</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="9">
+      <c r="B35" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="16"/>
+      <c r="D35" s="7">
         <v>112357.0</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F35" s="9">
+      <c r="E35" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="7">
         <v>840.0</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="7">
         <v>5160.0</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="7">
         <v>480.0</v>
       </c>
-      <c r="I35" s="11" t="s">
-        <v>16</v>
+      <c r="I35" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="J35" s="12"/>
     </row>
@@ -7524,57 +7524,57 @@
       <c r="A36" s="19">
         <v>46237.0</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="9">
+      <c r="B36" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="16"/>
+      <c r="D36" s="7">
         <v>10601.0</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F36" s="9">
+      <c r="E36" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36" s="7">
         <v>17934.0</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="7">
         <v>64980.0</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="7">
         <v>21714.0</v>
       </c>
-      <c r="I36" s="11" t="s">
-        <v>16</v>
+      <c r="I36" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="19">
         <v>46237.0</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="9">
+      <c r="B37" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="D37" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="9">
+      <c r="E37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="7">
         <v>194520.0</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="7">
         <v>84060.0</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="7">
         <v>122840.0</v>
       </c>
-      <c r="I37" s="11" t="s">
-        <v>22</v>
+      <c r="I37" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="J37" s="12"/>
     </row>
@@ -7582,27 +7582,27 @@
       <c r="A38" s="19">
         <v>46237.0</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="9">
+      <c r="B38" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="16"/>
+      <c r="D38" s="7">
         <v>114379.0</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F38" s="9">
+      <c r="E38" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="7">
         <v>52200.0</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="7">
         <v>16200.0</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="7">
         <v>7500.0</v>
       </c>
-      <c r="I38" s="11" t="s">
-        <v>33</v>
+      <c r="I38" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="J38" s="12"/>
     </row>
@@ -7610,27 +7610,27 @@
       <c r="A39" s="19">
         <v>46237.0</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="9">
+      <c r="B39" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="16"/>
+      <c r="D39" s="7">
         <v>2110317.0</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F39" s="9">
+      <c r="E39" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="7">
         <v>6450.0</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="7">
         <v>16920.0</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="7">
         <v>6480.0</v>
       </c>
-      <c r="I39" s="11" t="s">
-        <v>22</v>
+      <c r="I39" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="J39" s="12"/>
     </row>
@@ -7638,502 +7638,502 @@
       <c r="A40" s="19">
         <v>46237.0</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="9">
+      <c r="B40" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="16"/>
+      <c r="D40" s="7">
         <v>2010102.0</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F40" s="9">
+      <c r="E40" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="7">
         <v>1398.0</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="7">
         <v>1320.0</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="7">
         <v>438.0</v>
       </c>
-      <c r="I40" s="11" t="s">
-        <v>22</v>
+      <c r="I40" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="J40" s="12"/>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="5">
+      <c r="A41" s="9">
         <v>46238.0</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="9">
+      <c r="B41" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="16"/>
+      <c r="D41" s="7">
         <v>2152388.0</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F41" s="9">
+      <c r="E41" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="7">
         <v>2460.0</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="7">
         <v>17640.0</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="7">
         <v>3240.0</v>
       </c>
-      <c r="I41" s="11" t="s">
-        <v>15</v>
+      <c r="I41" s="15" t="s">
+        <v>13</v>
       </c>
       <c r="J41" s="12"/>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="5">
+      <c r="A42" s="9">
         <v>46238.0</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="9">
+      <c r="B42" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="7">
         <v>112268.0</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F42" s="9">
+      <c r="E42" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F42" s="7">
         <v>3600.0</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="7">
         <v>1500.0</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="7">
         <v>3900.0</v>
       </c>
-      <c r="I42" s="11" t="s">
-        <v>22</v>
+      <c r="I42" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="J42" s="12"/>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="5">
+      <c r="A43" s="9">
         <v>46238.0</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="14"/>
-      <c r="D43" s="9">
+      <c r="B43" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="16"/>
+      <c r="D43" s="7">
         <v>114379.0</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F43" s="9">
+      <c r="E43" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="7">
         <v>7500.0</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="7">
         <v>54900.0</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="7">
         <v>8400.0</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" s="12"/>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="9">
+        <v>46238.0</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="7">
+        <v>114357.0</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" s="7">
+        <v>240.0</v>
+      </c>
+      <c r="G44" s="7">
+        <v>7680.0</v>
+      </c>
+      <c r="H44" s="7">
+        <v>360.0</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" s="12"/>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="9">
+        <v>46239.0</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="16"/>
+      <c r="D45" s="7">
+        <v>10601.0</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" s="7">
+        <v>1115.0</v>
+      </c>
+      <c r="G45" s="7">
+        <v>5267.0</v>
+      </c>
+      <c r="H45" s="7">
+        <v>1590.0</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="A46" s="9">
+        <v>46239.0</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="16"/>
+      <c r="D46" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J43" s="12"/>
-    </row>
-    <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="5">
-        <v>46238.0</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="14"/>
-      <c r="D44" s="9">
-        <v>114357.0</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F44" s="9">
-        <v>240.0</v>
-      </c>
-      <c r="G44" s="9">
-        <v>7680.0</v>
-      </c>
-      <c r="H44" s="9">
-        <v>360.0</v>
-      </c>
-      <c r="I44" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" s="12"/>
-    </row>
-    <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="5">
+      <c r="F46" s="7">
+        <v>114240.0</v>
+      </c>
+      <c r="G46" s="7">
+        <v>79680.0</v>
+      </c>
+      <c r="H46" s="7">
+        <v>191130.0</v>
+      </c>
+      <c r="I46" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="12"/>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="A47" s="9">
         <v>46239.0</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="14"/>
-      <c r="D45" s="9">
-        <v>10601.0</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F45" s="9">
-        <v>1115.0</v>
-      </c>
-      <c r="G45" s="9">
-        <v>5267.0</v>
-      </c>
-      <c r="H45" s="9">
-        <v>1590.0</v>
-      </c>
-      <c r="I45" s="11" t="s">
+      <c r="B47" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="16"/>
+      <c r="D47" s="7">
+        <v>2112207.0</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F47" s="7">
+        <v>1800.0</v>
+      </c>
+      <c r="G47" s="7">
+        <v>1800.0</v>
+      </c>
+      <c r="H47" s="7">
+        <v>1980.0</v>
+      </c>
+      <c r="I47" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="12"/>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="9">
+        <v>46239.0</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="16"/>
+      <c r="D48" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F48" s="7">
+        <v>3900.0</v>
+      </c>
+      <c r="G48" s="7">
+        <v>34200.0</v>
+      </c>
+      <c r="H48" s="7">
+        <v>1200.0</v>
+      </c>
+      <c r="I48" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" s="12"/>
+    </row>
+    <row r="49" ht="22.5" customHeight="1">
+      <c r="A49" s="9">
+        <v>46239.0</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="16"/>
+      <c r="D49" s="7">
+        <v>112357.0</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F49" s="7">
+        <v>600.0</v>
+      </c>
+      <c r="G49" s="7">
+        <v>8400.0</v>
+      </c>
+      <c r="H49" s="7">
+        <v>600.0</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" s="12"/>
+    </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="9">
+        <v>46239.0</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="16"/>
+      <c r="D50" s="7">
+        <v>114268.0</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F50" s="7">
+        <v>2700.0</v>
+      </c>
+      <c r="G50" s="7">
+        <v>5700.0</v>
+      </c>
+      <c r="H50" s="7">
+        <v>300.0</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50" s="12"/>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="9">
+        <v>46239.0</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" s="16"/>
+      <c r="D51" s="7">
+        <v>10501.0</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="7">
+        <v>68651.0</v>
+      </c>
+      <c r="G51" s="7">
+        <v>64050.0</v>
+      </c>
+      <c r="H51" s="7">
+        <v>13421.0</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="9">
+        <v>46239.0</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" s="16"/>
+      <c r="D52" s="7">
+        <v>72003.0</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F52" s="7">
+        <v>1391.0</v>
+      </c>
+      <c r="G52" s="7">
+        <v>3885.0</v>
+      </c>
+      <c r="H52" s="7">
+        <v>2407.0</v>
+      </c>
+      <c r="I52" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="12"/>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="9">
+        <v>46239.0</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" s="16"/>
+      <c r="D53" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J45" s="12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="14"/>
-      <c r="D46" s="9">
-        <v>2110302.0</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" s="9">
-        <v>114240.0</v>
-      </c>
-      <c r="G46" s="9">
-        <v>79680.0</v>
-      </c>
-      <c r="H46" s="9">
-        <v>191130.0</v>
-      </c>
-      <c r="I46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="12"/>
-    </row>
-    <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="14"/>
-      <c r="D47" s="9">
-        <v>2112207.0</v>
-      </c>
-      <c r="E47" s="6" t="s">
+      <c r="F53" s="7">
+        <v>2974.0</v>
+      </c>
+      <c r="G53" s="7">
+        <v>1200.0</v>
+      </c>
+      <c r="H53" s="7">
+        <v>3317.0</v>
+      </c>
+      <c r="I53" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="19">
+        <v>46240.0</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="16"/>
+      <c r="D54" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="7">
+        <v>3600.0</v>
+      </c>
+      <c r="G54" s="7">
+        <v>26100.0</v>
+      </c>
+      <c r="H54" s="7">
+        <v>6900.0</v>
+      </c>
+      <c r="I54" s="15"/>
+      <c r="J54" s="12"/>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="19">
+        <v>46240.0</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="16"/>
+      <c r="D55" s="7">
+        <v>73001.0</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" s="7">
+        <v>2415.0</v>
+      </c>
+      <c r="G55" s="7">
+        <v>26490.0</v>
+      </c>
+      <c r="H55" s="7">
+        <v>2415.0</v>
+      </c>
+      <c r="I55" s="15"/>
+      <c r="J55" s="12"/>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="A56" s="19">
+        <v>46240.0</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" s="16"/>
+      <c r="D56" s="7">
+        <v>112357.0</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="9">
-        <v>1800.0</v>
-      </c>
-      <c r="G47" s="9">
-        <v>1800.0</v>
-      </c>
-      <c r="H47" s="9">
-        <v>1980.0</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J47" s="12"/>
-    </row>
-    <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="9">
-        <v>112268.0</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F48" s="9">
-        <v>3900.0</v>
-      </c>
-      <c r="G48" s="9">
-        <v>34200.0</v>
-      </c>
-      <c r="H48" s="9">
-        <v>1200.0</v>
-      </c>
-      <c r="I48" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J48" s="12"/>
-    </row>
-    <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="14"/>
-      <c r="D49" s="9">
-        <v>112357.0</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F49" s="9">
+      <c r="F56" s="7">
         <v>600.0</v>
       </c>
-      <c r="G49" s="9">
-        <v>8400.0</v>
-      </c>
-      <c r="H49" s="9">
+      <c r="G56" s="7">
+        <v>3960.0</v>
+      </c>
+      <c r="H56" s="7">
         <v>600.0</v>
       </c>
-      <c r="I49" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J49" s="12"/>
-    </row>
-    <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="14"/>
-      <c r="D50" s="9">
-        <v>114268.0</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F50" s="9">
-        <v>2700.0</v>
-      </c>
-      <c r="G50" s="9">
-        <v>5700.0</v>
-      </c>
-      <c r="H50" s="9">
+      <c r="I56" s="15"/>
+      <c r="J56" s="12"/>
+    </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="19">
+        <v>46240.0</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="16"/>
+      <c r="D57" s="7">
+        <v>114379.0</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F57" s="7">
+        <v>2400.0</v>
+      </c>
+      <c r="G57" s="7">
+        <v>15000.0</v>
+      </c>
+      <c r="H57" s="7">
         <v>300.0</v>
       </c>
-      <c r="I50" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J50" s="12"/>
-    </row>
-    <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="14"/>
-      <c r="D51" s="9">
-        <v>10501.0</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F51" s="9">
-        <v>68651.0</v>
-      </c>
-      <c r="G51" s="9">
-        <v>64050.0</v>
-      </c>
-      <c r="H51" s="9">
-        <v>13421.0</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C52" s="14"/>
-      <c r="D52" s="9">
-        <v>72003.0</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F52" s="9">
-        <v>1391.0</v>
-      </c>
-      <c r="G52" s="9">
-        <v>3885.0</v>
-      </c>
-      <c r="H52" s="9">
-        <v>2407.0</v>
-      </c>
-      <c r="I52" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J52" s="12"/>
-    </row>
-    <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" s="14"/>
-      <c r="D53" s="9">
-        <v>2110402.0</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" s="9">
-        <v>2974.0</v>
-      </c>
-      <c r="G53" s="9">
-        <v>1200.0</v>
-      </c>
-      <c r="H53" s="9">
-        <v>3317.0</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="14"/>
-      <c r="D54" s="9">
-        <v>112379.0</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F54" s="9">
-        <v>3600.0</v>
-      </c>
-      <c r="G54" s="9">
-        <v>26100.0</v>
-      </c>
-      <c r="H54" s="9">
-        <v>6900.0</v>
-      </c>
-      <c r="I54" s="11"/>
-      <c r="J54" s="12"/>
-    </row>
-    <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" s="14"/>
-      <c r="D55" s="9">
-        <v>73001.0</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F55" s="9">
-        <v>2415.0</v>
-      </c>
-      <c r="G55" s="9">
-        <v>26490.0</v>
-      </c>
-      <c r="H55" s="9">
-        <v>2415.0</v>
-      </c>
-      <c r="I55" s="11"/>
-      <c r="J55" s="12"/>
-    </row>
-    <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="14"/>
-      <c r="D56" s="9">
-        <v>112357.0</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F56" s="9">
-        <v>600.0</v>
-      </c>
-      <c r="G56" s="9">
-        <v>3960.0</v>
-      </c>
-      <c r="H56" s="9">
-        <v>600.0</v>
-      </c>
-      <c r="I56" s="11"/>
-      <c r="J56" s="12"/>
-    </row>
-    <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="5">
-        <v>46239.0</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" s="14"/>
-      <c r="D57" s="9">
-        <v>114379.0</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F57" s="9">
-        <v>2400.0</v>
-      </c>
-      <c r="G57" s="9">
-        <v>15000.0</v>
-      </c>
-      <c r="H57" s="9">
-        <v>300.0</v>
-      </c>
-      <c r="I57" s="11"/>
+      <c r="I57" s="15"/>
       <c r="J57" s="12"/>
     </row>
     <row r="58">

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="137">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -50,24 +50,45 @@
     <t>Daniel Castro</t>
   </si>
   <si>
+    <t>ALKA2</t>
+  </si>
+  <si>
     <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
+    <t>7. Otro</t>
+  </si>
+  <si>
+    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
+  </si>
+  <si>
     <t>TAT MONTERIA</t>
   </si>
   <si>
     <t>LUIS LOPEZ</t>
   </si>
   <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+    <t>LANZA</t>
+  </si>
+  <si>
+    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
     <t>3. Falla De Rotación</t>
   </si>
   <si>
+    <t>6. Transformación De Referencias</t>
+  </si>
+  <si>
+    <t>Pendiente Transformar Roto GT Por manipulación</t>
+  </si>
+  <si>
     <t>TAT MEDELLIN</t>
   </si>
   <si>
@@ -77,6 +98,12 @@
     <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
   </si>
   <si>
+    <t>HUEVO B X30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>se equivocaron al cargar una estiba</t>
+  </si>
+  <si>
     <t>TAT CARTAGENA</t>
   </si>
   <si>
@@ -86,255 +113,249 @@
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
     <t>4. Exigencia Del Cliente (Edad)</t>
   </si>
   <si>
     <t>Venta FS</t>
   </si>
   <si>
-    <t>7. Otro</t>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
   </si>
   <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+  </si>
+  <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+  </si>
+  <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
+  </si>
+  <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+  </si>
+  <si>
     <t>TAT CALI</t>
   </si>
   <si>
     <t>DIEGO ROJAS</t>
   </si>
   <si>
+    <t>HUEVO PICADO ROJO</t>
+  </si>
+  <si>
+    <t>No se carga todod por capacidad de Vehiculo</t>
+  </si>
+  <si>
     <t>TAT CUCUTA</t>
   </si>
   <si>
     <t>ALEXANDER PEÑA</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
-    <t>6. Transformación De Referencias</t>
-  </si>
-  <si>
     <t>Clientes FS</t>
   </si>
   <si>
+    <t>HUEVO SUCIO DE JAULA</t>
+  </si>
+  <si>
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
+    <t>Esta para despacho hoy</t>
+  </si>
+  <si>
     <t>Transformación de PET</t>
   </si>
   <si>
     <t>ANDRES MEJIA</t>
   </si>
   <si>
+    <t>Cola de programación</t>
+  </si>
+  <si>
     <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
   </si>
   <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+  </si>
+  <si>
     <t>TAT POPAYAN</t>
   </si>
   <si>
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
+    <t>HUEVO CX30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+  </si>
+  <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
+  </si>
+  <si>
     <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
+  </si>
+  <si>
     <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
   </si>
   <si>
+    <t>ALKA1</t>
+  </si>
+  <si>
+    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
+  </si>
+  <si>
+    <t>HUEVO ROTO - ZF</t>
+  </si>
+  <si>
+    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
+  </si>
+  <si>
     <t>5. Ingreso De Planta</t>
   </si>
   <si>
+    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
+  </si>
+  <si>
     <t>Se despacha par FS con producto más nuevo</t>
   </si>
   <si>
-    <t>ALKA2</t>
-  </si>
-  <si>
-    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
   </si>
   <si>
     <t>ANDREA QUIROGA</t>
   </si>
   <si>
-    <t>LANZA</t>
+    <t>Cargo en incubación</t>
   </si>
   <si>
     <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
   </si>
   <si>
-    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
-  </si>
-  <si>
-    <t>Pendiente Transformar Roto GT Por manipulación</t>
-  </si>
-  <si>
-    <t>HUEVO B X30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>se equivocaron al cargar una estiba</t>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
     <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
-  </si>
-  <si>
-    <t>PALMAS</t>
-  </si>
-  <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
-  </si>
-  <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
-  </si>
-  <si>
     <t>TAT PASTO</t>
   </si>
   <si>
     <t>CAROLINA VITERI</t>
   </si>
   <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
-  </si>
-  <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
-  </si>
-  <si>
-    <t>HUEVO PICADO ROJO</t>
+    <t>BELLAVISTA</t>
+  </si>
+  <si>
+    <t>Traslado a cedi, producto de devolución</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
     <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
-    <t>No se carga todod por capacidad de Vehiculo</t>
-  </si>
-  <si>
     <t>Pedido para villavicencio</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
+  </si>
+  <si>
+    <t>HUEVO SUCIO ZF MARCADO</t>
+  </si>
+  <si>
     <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
-  </si>
-  <si>
-    <t>HUEVO SUCIO DE JAULA</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+    <t>vehiculo con flata de capacidad / TAT cali</t>
   </si>
   <si>
     <t>Inventario de Asesor de Rionegro que renuncio</t>
   </si>
   <si>
-    <t>Esta para despacho hoy</t>
-  </si>
-  <si>
     <t>TAT BARRANQUILLA</t>
   </si>
   <si>
     <t>Jhonatan Gomez</t>
   </si>
   <si>
-    <t>Cola de programación</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
-  </si>
-  <si>
-    <t>HUEVO CX30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
-  </si>
-  <si>
     <t>Lote mezclado en la misma estiba</t>
   </si>
   <si>
     <t>Supera edad solicitada clientes grandes superficies</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
-  </si>
-  <si>
     <t>Pedido para villacicencio</t>
   </si>
   <si>
-    <t>ALKA1</t>
-  </si>
-  <si>
     <t>Se envía huevo más fresco a Sincelejo</t>
   </si>
   <si>
-    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
-  </si>
-  <si>
-    <t>HUEVO ROTO - ZF</t>
-  </si>
-  <si>
     <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
   </si>
   <si>
-    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
-  </si>
-  <si>
     <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
   </si>
   <si>
-    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
-  </si>
-  <si>
     <t>SalIO en sugeridos de hoy 22/07/2026</t>
   </si>
   <si>
     <t>Yovanis Arevalo</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
     <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
   </si>
   <si>
-    <t>Cargo en incubación</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
     <t>Devolucion de huevo de 12 dias en mal estado</t>
   </si>
   <si>
@@ -344,27 +365,6 @@
     <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
-    <t>BELLAVISTA</t>
-  </si>
-  <si>
-    <t>Traslado a cedi, producto de devolución</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CANASTA</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
-  </si>
-  <si>
-    <t>HUEVO SUCIO ZF MARCADO</t>
-  </si>
-  <si>
-    <t>vehiculo con flata de capacidad / TAT cali</t>
-  </si>
-  <si>
     <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
   </si>
   <si>
@@ -417,6 +417,12 @@
   </si>
   <si>
     <t>yOVANIS AREVALO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEV CLIENTE MAS POR MENOS </t>
+  </si>
+  <si>
+    <t>Se envía huevo fresco a Rionegro</t>
   </si>
 </sst>
 </file>
@@ -480,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -499,26 +505,32 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -527,23 +539,20 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -605,13 +614,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Cedis-style">
+    <tableStyle count="4" pivot="0" name="Plantas-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Plantas-style">
+    <tableStyle count="4" pivot="0" name="Cedis-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -634,7 +643,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J92" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J96" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -652,7 +661,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J57" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J58" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -921,2811 +930,2931 @@
       <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="7">
+        <v>13</v>
+      </c>
+      <c r="F2" s="8">
         <v>359100.0</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="8">
         <v>83486.0</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="8">
         <v>206140.0</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" hidden="1" customHeight="1">
+      <c r="A3" s="6">
+        <v>46205.0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8">
+        <v>298282.0</v>
+      </c>
+      <c r="G3" s="8">
+        <v>42201.0</v>
+      </c>
+      <c r="H3" s="8">
+        <v>260675.0</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
+      <c r="A4" s="6">
+        <v>46205.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="8">
+        <v>2110217.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="8">
+        <v>21120.0</v>
+      </c>
+      <c r="G4" s="8">
+        <v>11039.0</v>
+      </c>
+      <c r="H4" s="8">
+        <v>16920.0</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
+      <c r="A5" s="6">
+        <v>46205.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="8">
+        <v>75680.0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>5640.0</v>
+      </c>
+      <c r="H5" s="8">
+        <v>3134.0</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="6">
+        <v>46206.0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="9">
-        <v>46205.0</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="F6" s="8">
+        <v>189540.0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>161685.0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>144720.0</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="6">
+        <v>46206.0</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8">
+        <v>2010102.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="8">
+        <v>20640.0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>3761.0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>13920.0</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="6">
+        <v>46206.0</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="8">
+        <v>152384.0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="8">
+        <v>14700.0</v>
+      </c>
+      <c r="G8" s="8">
+        <v>6435.0</v>
+      </c>
+      <c r="H8" s="8">
+        <v>9600.0</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
+      <c r="A9" s="6">
+        <v>46206.0</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
+        <v>228240.0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>77306.0</v>
+      </c>
+      <c r="H9" s="8">
+        <v>124260.0</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
+      <c r="A10" s="6">
+        <v>46206.0</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="8">
+        <v>2152388.0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="8">
+        <v>7830.0</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1980.0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>6030.0</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="6">
+        <v>46206.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="F11" s="8">
+        <v>31680.0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>5526.0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>23040.0</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
+      <c r="A12" s="6">
+        <v>46206.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="8">
+        <v>51387.0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>10827.0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>12170.0</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
+      <c r="A13" s="6">
+        <v>46209.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="8">
+        <v>195810.0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>93809.0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>133410.0</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
+      <c r="A14" s="6">
+        <v>46209.0</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="8">
+        <v>526002.0</v>
+      </c>
+      <c r="G14" s="8">
+        <v>301965.0</v>
+      </c>
+      <c r="H14" s="8">
+        <v>424588.0</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="6">
+        <v>46209.0</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="8">
+        <v>2010102.0</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="8">
+        <v>14160.0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>6692.0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>12360.0</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
+      <c r="A16" s="6">
+        <v>46210.0</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="8">
+        <v>149040.0</v>
+      </c>
+      <c r="G16" s="8">
+        <v>119573.0</v>
+      </c>
+      <c r="H16" s="8">
+        <v>289680.0</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="7">
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" ht="22.5" hidden="1" customHeight="1">
+      <c r="A17" s="6">
+        <v>46210.0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="8">
+        <v>2110217.0</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="8">
+        <v>22770.0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>3926.0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>19770.0</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="12"/>
+    </row>
+    <row r="18" ht="22.5" hidden="1" customHeight="1">
+      <c r="A18" s="6">
+        <v>46210.0</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="8">
+        <v>222021.0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>61385.0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>162125.0</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="12"/>
+    </row>
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
+      <c r="A19" s="6">
+        <v>46211.0</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="8">
+        <v>495833.0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>148815.0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>401280.0</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="7">
-        <v>298282.0</v>
-      </c>
-      <c r="G3" s="7">
-        <v>42201.0</v>
-      </c>
-      <c r="H3" s="7">
-        <v>260675.0</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="9">
-        <v>46205.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="J19" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
+      <c r="A20" s="6">
+        <v>46211.0</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="7">
-        <v>2110217.0</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="7">
-        <v>21120.0</v>
-      </c>
-      <c r="G4" s="7">
-        <v>11039.0</v>
-      </c>
-      <c r="H4" s="7">
-        <v>16920.0</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="11"/>
-    </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="9">
-        <v>46205.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="D20" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="8">
+        <v>139920.0</v>
+      </c>
+      <c r="G20" s="8">
+        <v>54384.0</v>
+      </c>
+      <c r="H20" s="8">
+        <v>74040.0</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="12"/>
+    </row>
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
+      <c r="A21" s="6">
+        <v>46211.0</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="8">
         <v>2110302.0</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="7">
-        <v>75680.0</v>
-      </c>
-      <c r="G5" s="7">
-        <v>5640.0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>3134.0</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="7">
-        <v>189540.0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>161685.0</v>
-      </c>
-      <c r="H6" s="7">
-        <v>144720.0</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="7">
-        <v>2010102.0</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="7">
-        <v>20640.0</v>
-      </c>
-      <c r="G7" s="7">
-        <v>3761.0</v>
-      </c>
-      <c r="H7" s="7">
-        <v>13920.0</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="7">
-        <v>152384.0</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="7">
-        <v>14700.0</v>
-      </c>
-      <c r="G8" s="7">
-        <v>6435.0</v>
-      </c>
-      <c r="H8" s="7">
-        <v>9600.0</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="7">
-        <v>228240.0</v>
-      </c>
-      <c r="G9" s="7">
-        <v>77306.0</v>
-      </c>
-      <c r="H9" s="7">
-        <v>124260.0</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="7">
-        <v>2152388.0</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="7">
-        <v>7830.0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>1980.0</v>
-      </c>
-      <c r="H10" s="7">
-        <v>6030.0</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="13"/>
-    </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="F21" s="8">
+        <v>162125.0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>60138.0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>100687.0</v>
+      </c>
+      <c r="I21" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="7">
-        <v>31680.0</v>
-      </c>
-      <c r="G11" s="7">
-        <v>5526.0</v>
-      </c>
-      <c r="H11" s="7">
-        <v>23040.0</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="9">
-        <v>46206.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="7">
-        <v>51387.0</v>
-      </c>
-      <c r="G12" s="7">
-        <v>10827.0</v>
-      </c>
-      <c r="H12" s="7">
-        <v>12170.0</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="9">
-        <v>46209.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="7">
-        <v>195810.0</v>
-      </c>
-      <c r="G13" s="7">
-        <v>93809.0</v>
-      </c>
-      <c r="H13" s="7">
-        <v>133410.0</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="9">
-        <v>46209.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="7">
-        <v>526002.0</v>
-      </c>
-      <c r="G14" s="7">
-        <v>301965.0</v>
-      </c>
-      <c r="H14" s="7">
-        <v>424588.0</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="9">
-        <v>46209.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="7">
-        <v>2010102.0</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="7">
-        <v>14160.0</v>
-      </c>
-      <c r="G15" s="7">
-        <v>6692.0</v>
-      </c>
-      <c r="H15" s="7">
-        <v>12360.0</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="9">
-        <v>46210.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="7">
-        <v>149040.0</v>
-      </c>
-      <c r="G16" s="7">
-        <v>119573.0</v>
-      </c>
-      <c r="H16" s="7">
-        <v>289680.0</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="9">
-        <v>46210.0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="7">
-        <v>2110217.0</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="7">
-        <v>22770.0</v>
-      </c>
-      <c r="G17" s="7">
-        <v>3926.0</v>
-      </c>
-      <c r="H17" s="7">
-        <v>19770.0</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="12"/>
-    </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="9">
-        <v>46210.0</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="7">
-        <v>222021.0</v>
-      </c>
-      <c r="G18" s="7">
-        <v>61385.0</v>
-      </c>
-      <c r="H18" s="7">
-        <v>162125.0</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="12"/>
-    </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="9">
-        <v>46211.0</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="7">
-        <v>495833.0</v>
-      </c>
-      <c r="G19" s="7">
-        <v>148815.0</v>
-      </c>
-      <c r="H19" s="7">
-        <v>401280.0</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="9">
-        <v>46211.0</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="7">
-        <v>139920.0</v>
-      </c>
-      <c r="G20" s="7">
-        <v>54384.0</v>
-      </c>
-      <c r="H20" s="7">
-        <v>74040.0</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="12"/>
-    </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="9">
-        <v>46211.0</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="7">
-        <v>162125.0</v>
-      </c>
-      <c r="G21" s="7">
-        <v>60138.0</v>
-      </c>
-      <c r="H21" s="7">
-        <v>100687.0</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>26</v>
-      </c>
       <c r="J21" s="12" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="9">
+      <c r="A22" s="6">
         <v>46211.0</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <v>152384.0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="7">
+        <v>47</v>
+      </c>
+      <c r="F22" s="8">
         <v>32850.0</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="8">
         <v>7065.0</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="8">
         <v>32700.0</v>
       </c>
-      <c r="I22" s="10" t="s">
-        <v>24</v>
+      <c r="I22" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J22" s="12"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="9">
+      <c r="A23" s="6">
         <v>46211.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="7">
+        <v>25</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="8">
         <v>112271.0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="7">
+        <v>76</v>
+      </c>
+      <c r="F23" s="8">
         <v>16500.0</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="8">
         <v>5310.0</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="8">
         <v>18000.0</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>31</v>
+      <c r="I23" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="J23" s="12"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="9">
+      <c r="A24" s="6">
         <v>46212.0</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="8">
+        <v>190047.0</v>
+      </c>
+      <c r="G24" s="8">
+        <v>59822.0</v>
+      </c>
+      <c r="H24" s="8">
+        <v>248481.0</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J24" s="12"/>
+    </row>
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
+      <c r="A25" s="6">
+        <v>46212.0</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="7">
-        <v>190047.0</v>
-      </c>
-      <c r="G24" s="7">
-        <v>59822.0</v>
-      </c>
-      <c r="H24" s="7">
-        <v>248481.0</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" s="12"/>
-    </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="9">
+      <c r="F25" s="8">
+        <v>178080.0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>47784.0</v>
+      </c>
+      <c r="H25" s="8">
+        <v>203520.0</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
+      <c r="A26" s="6">
         <v>46212.0</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="7">
-        <v>178080.0</v>
-      </c>
-      <c r="G25" s="7">
-        <v>47784.0</v>
-      </c>
-      <c r="H25" s="7">
-        <v>203520.0</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J25" s="12"/>
-    </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="9">
+      <c r="B26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="8">
+        <v>10320.0</v>
+      </c>
+      <c r="G26" s="8">
+        <v>5869.0</v>
+      </c>
+      <c r="H26" s="8">
+        <v>13200.0</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
+      <c r="A27" s="6">
         <v>46212.0</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" s="7">
-        <v>10320.0</v>
-      </c>
-      <c r="G26" s="7">
-        <v>5869.0</v>
-      </c>
-      <c r="H26" s="7">
-        <v>13200.0</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="9">
-        <v>46212.0</v>
-      </c>
       <c r="B27" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="7">
+        <v>25</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="8">
         <v>112271.0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F27" s="7">
+        <v>76</v>
+      </c>
+      <c r="F27" s="8">
         <v>18000.0</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="8">
         <v>4485.0</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="8">
         <v>13500.0</v>
       </c>
-      <c r="I27" s="10" t="s">
-        <v>17</v>
+      <c r="I27" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J27" s="12"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="9">
+      <c r="A28" s="6">
         <v>46213.0</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="C28" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="7">
+        <v>32</v>
+      </c>
+      <c r="F28" s="8">
         <v>208440.0</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="8">
         <v>85608.0</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="8">
         <v>150833.0</v>
       </c>
-      <c r="I28" s="10" t="s">
-        <v>26</v>
+      <c r="I28" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="9">
+      <c r="A29" s="6">
         <v>46213.0</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="7">
+      <c r="C29" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="7">
+        <v>13</v>
+      </c>
+      <c r="F29" s="8">
         <v>962820.0</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="8">
         <v>80644.0</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="8">
         <v>922140.0</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
+      <c r="A30" s="6">
+        <v>46213.0</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="8">
+        <v>335340.0</v>
+      </c>
+      <c r="G30" s="8">
+        <v>111433.0</v>
+      </c>
+      <c r="H30" s="8">
+        <v>381600.0</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="6">
+        <v>46213.0</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" s="8">
+        <v>316800.0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>99546.0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>229680.0</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" s="12"/>
+    </row>
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
+      <c r="A32" s="6">
+        <v>46213.0</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" s="8">
+        <v>176850.0</v>
+      </c>
+      <c r="G32" s="8">
+        <v>47499.0</v>
+      </c>
+      <c r="H32" s="8">
+        <v>128971.0</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J32" s="12"/>
+    </row>
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
+      <c r="A33" s="6">
+        <v>46213.0</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="8">
+        <v>58080.0</v>
+      </c>
+      <c r="G33" s="8">
+        <v>20865.0</v>
+      </c>
+      <c r="H33" s="8">
+        <v>25440.0</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="12"/>
+    </row>
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
+      <c r="A34" s="6">
+        <v>46217.0</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" s="8">
+        <v>481440.0</v>
+      </c>
+      <c r="G34" s="8">
+        <v>464517.0</v>
+      </c>
+      <c r="H34" s="8">
+        <v>151435.0</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="12"/>
+    </row>
+    <row r="35" ht="22.5" hidden="1" customHeight="1">
+      <c r="A35" s="6">
+        <v>46217.0</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J29" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="9">
-        <v>46213.0</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="7">
+      <c r="D35" s="8">
         <v>2110202.0</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="7">
-        <v>335340.0</v>
-      </c>
-      <c r="G30" s="7">
-        <v>111433.0</v>
-      </c>
-      <c r="H30" s="7">
-        <v>381600.0</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="9">
-        <v>46213.0</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="7">
-        <v>316800.0</v>
-      </c>
-      <c r="G31" s="7">
-        <v>99546.0</v>
-      </c>
-      <c r="H31" s="7">
-        <v>229680.0</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="12"/>
-    </row>
-    <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="9">
-        <v>46213.0</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="7">
-        <v>176850.0</v>
-      </c>
-      <c r="G32" s="7">
-        <v>47499.0</v>
-      </c>
-      <c r="H32" s="7">
-        <v>128971.0</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="12"/>
-    </row>
-    <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="9">
-        <v>46213.0</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="7">
-        <v>58080.0</v>
-      </c>
-      <c r="G33" s="7">
-        <v>20865.0</v>
-      </c>
-      <c r="H33" s="7">
-        <v>25440.0</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="12"/>
-    </row>
-    <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="9">
-        <v>46217.0</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="7">
-        <v>481440.0</v>
-      </c>
-      <c r="G34" s="7">
-        <v>464517.0</v>
-      </c>
-      <c r="H34" s="7">
-        <v>151435.0</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="12"/>
-    </row>
-    <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="9">
-        <v>46217.0</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="7">
-        <v>2110202.0</v>
-      </c>
       <c r="E35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="7">
+        <v>13</v>
+      </c>
+      <c r="F35" s="8">
         <v>355720.0</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="8">
         <v>342811.0</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="8">
         <v>302760.0</v>
       </c>
-      <c r="I35" s="10" t="s">
-        <v>13</v>
+      <c r="I35" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J35" s="12"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="9">
+      <c r="A36" s="6">
         <v>46217.0</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="7">
+      <c r="C36" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="7">
+        <v>42</v>
+      </c>
+      <c r="F36" s="8">
         <v>35280.0</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="8">
         <v>16988.0</v>
       </c>
-      <c r="H36" s="7">
+      <c r="H36" s="8">
         <v>37926.0</v>
       </c>
-      <c r="I36" s="10" t="s">
-        <v>17</v>
+      <c r="I36" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
-      <c r="A37" s="17">
+      <c r="A37" s="19">
         <v>46218.0</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="7">
+      <c r="C37" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F37" s="7">
+        <v>32</v>
+      </c>
+      <c r="F37" s="8">
         <v>272073.0</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="8">
         <v>76546.0</v>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="8">
         <v>275205.0</v>
       </c>
-      <c r="I37" s="10" t="s">
-        <v>24</v>
+      <c r="I37" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
-      <c r="A38" s="17">
+      <c r="A38" s="19">
         <v>46218.0</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="7">
+      <c r="C38" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="7">
+        <v>42</v>
+      </c>
+      <c r="F38" s="8">
         <v>37926.0</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="8">
         <v>5633.0</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38" s="8">
         <v>25746.0</v>
       </c>
-      <c r="I38" s="10" t="s">
-        <v>17</v>
+      <c r="I38" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
-      <c r="A39" s="17">
+      <c r="A39" s="19">
         <v>46218.0</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="7">
+        <v>25</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="8">
         <v>2110402.0</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F39" s="7">
+        <v>14</v>
+      </c>
+      <c r="F39" s="8">
         <v>20640.0</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="8">
         <v>4951.0</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="8">
         <v>16320.0</v>
       </c>
-      <c r="I39" s="10" t="s">
-        <v>24</v>
+      <c r="I39" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
-      <c r="A40" s="17">
+      <c r="A40" s="19">
         <v>46218.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="7">
+        <v>25</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F40" s="7">
+        <v>73</v>
+      </c>
+      <c r="F40" s="8">
         <v>10980.0</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="8">
         <v>2379.0</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40" s="8">
         <v>13500.0</v>
       </c>
-      <c r="I40" s="10" t="s">
-        <v>17</v>
+      <c r="I40" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J40" s="12"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="9">
+      <c r="A41" s="6">
         <v>46219.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="7">
+        <v>25</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F41" s="7">
+        <v>32</v>
+      </c>
+      <c r="F41" s="8">
         <v>130320.0</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="8">
         <v>47410.0</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41" s="8">
         <v>90480.0</v>
       </c>
-      <c r="I41" s="10" t="s">
-        <v>31</v>
+      <c r="I41" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="9">
+      <c r="A42" s="6">
         <v>46219.0</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="8">
+        <v>2152388.0</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42" s="8">
+        <v>36225.0</v>
+      </c>
+      <c r="G42" s="8">
+        <v>11746.0</v>
+      </c>
+      <c r="H42" s="8">
+        <v>27570.0</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="12"/>
+    </row>
+    <row r="43" ht="22.5" hidden="1" customHeight="1">
+      <c r="A43" s="6">
+        <v>46219.0</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" s="8">
+        <v>152833.0</v>
+      </c>
+      <c r="G43" s="8">
+        <v>50641.0</v>
+      </c>
+      <c r="H43" s="8">
+        <v>96472.0</v>
+      </c>
+      <c r="I43" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" s="7">
-        <v>2152388.0</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42" s="7">
-        <v>36225.0</v>
-      </c>
-      <c r="G42" s="7">
-        <v>11746.0</v>
-      </c>
-      <c r="H42" s="7">
-        <v>27570.0</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="12"/>
-    </row>
-    <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="9">
+      <c r="J43" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" hidden="1" customHeight="1">
+      <c r="A44" s="6">
         <v>46219.0</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B44" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F43" s="7">
-        <v>152833.0</v>
-      </c>
-      <c r="G43" s="7">
-        <v>50641.0</v>
-      </c>
-      <c r="H43" s="7">
-        <v>96472.0</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="9">
-        <v>46219.0</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D44" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F44" s="7">
+      <c r="F44" s="8">
         <v>237828.0</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="8">
         <v>173585.0</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="8">
         <v>71560.0</v>
       </c>
-      <c r="I44" s="10" t="s">
-        <v>17</v>
+      <c r="I44" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J44" s="12"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="9">
+      <c r="A45" s="6">
         <v>46219.0</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="7">
+      <c r="C45" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D45" s="8">
         <v>152384.0</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F45" s="7">
+        <v>47</v>
+      </c>
+      <c r="F45" s="8">
         <v>31125.0</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="8">
         <v>7815.0</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H45" s="8">
         <v>31845.0</v>
       </c>
-      <c r="I45" s="10" t="s">
-        <v>24</v>
+      <c r="I45" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="9">
+      <c r="A46" s="6">
         <v>46219.0</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="7">
+      <c r="C46" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" s="7">
+        <v>42</v>
+      </c>
+      <c r="F46" s="8">
         <v>25746.0</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46" s="8">
         <v>6168.0</v>
       </c>
-      <c r="H46" s="7">
+      <c r="H46" s="8">
         <v>28683.0</v>
       </c>
-      <c r="I46" s="10" t="s">
-        <v>17</v>
+      <c r="I46" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="9">
+      <c r="A47" s="6">
         <v>46220.0</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="C47" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D47" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F47" s="7">
+        <v>32</v>
+      </c>
+      <c r="F47" s="8">
         <v>261166.0</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="8">
         <v>74573.0</v>
       </c>
-      <c r="H47" s="7">
+      <c r="H47" s="8">
         <v>221549.0</v>
       </c>
-      <c r="I47" s="10" t="s">
-        <v>24</v>
+      <c r="I47" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="9">
+      <c r="A48" s="6">
         <v>46220.0</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="7">
+      <c r="C48" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" s="8">
         <v>2110217.0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F48" s="7">
+        <v>27</v>
+      </c>
+      <c r="F48" s="8">
         <v>115289.0</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="8">
         <v>26931.0</v>
       </c>
-      <c r="H48" s="7">
+      <c r="H48" s="8">
         <v>119584.0</v>
       </c>
-      <c r="I48" s="10" t="s">
-        <v>17</v>
+      <c r="I48" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J48" s="12"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="9">
+      <c r="A49" s="6">
         <v>46224.0</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="7">
+      <c r="F49" s="8">
+        <v>398570.0</v>
+      </c>
+      <c r="G49" s="8">
+        <v>288226.0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>287235.0</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" ht="22.5" hidden="1" customHeight="1">
+      <c r="A50" s="6">
+        <v>46224.0</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="8">
         <v>2110402.0</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" s="8">
+        <v>745107.0</v>
+      </c>
+      <c r="G50" s="8">
+        <v>378927.0</v>
+      </c>
+      <c r="H50" s="8">
+        <v>551645.0</v>
+      </c>
+      <c r="I50" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F49" s="7">
-        <v>398570.0</v>
-      </c>
-      <c r="G49" s="7">
-        <v>288226.0</v>
-      </c>
-      <c r="H49" s="7">
-        <v>287235.0</v>
-      </c>
-      <c r="I49" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="9">
-        <v>46224.0</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D50" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" s="7">
-        <v>745107.0</v>
-      </c>
-      <c r="G50" s="7">
-        <v>378927.0</v>
-      </c>
-      <c r="H50" s="7">
-        <v>551645.0</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>26</v>
-      </c>
       <c r="J50" s="12" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="9">
+      <c r="A51" s="6">
         <v>46225.0</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D51" s="7">
+        <v>25</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E51" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" s="8">
+        <v>130560.0</v>
+      </c>
+      <c r="G51" s="8">
+        <v>52658.0</v>
+      </c>
+      <c r="H51" s="8">
+        <v>153840.0</v>
+      </c>
+      <c r="I51" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="F51" s="7">
-        <v>130560.0</v>
-      </c>
-      <c r="G51" s="7">
-        <v>52658.0</v>
-      </c>
-      <c r="H51" s="7">
-        <v>153840.0</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>37</v>
-      </c>
       <c r="J51" s="12" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="9">
+      <c r="A52" s="6">
         <v>46225.0</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D52" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F52" s="7">
+      <c r="F52" s="8">
         <v>87447.0</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G52" s="8">
         <v>59056.0</v>
       </c>
-      <c r="H52" s="7">
+      <c r="H52" s="8">
         <v>104365.0</v>
       </c>
-      <c r="I52" s="10" t="s">
-        <v>17</v>
+      <c r="I52" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J52" s="12"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="9">
+      <c r="A53" s="6">
         <v>46225.0</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D53" s="7">
+      <c r="C53" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D53" s="8">
         <v>2110402.0</v>
       </c>
       <c r="E53" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" s="8">
+        <v>25200.0</v>
+      </c>
+      <c r="G53" s="8">
+        <v>2085.0</v>
+      </c>
+      <c r="H53" s="8">
+        <v>25920.0</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" hidden="1" customHeight="1">
+      <c r="A54" s="6">
+        <v>46226.0</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="8">
+        <v>285405.0</v>
+      </c>
+      <c r="G54" s="8">
+        <v>203180.0</v>
+      </c>
+      <c r="H54" s="8">
+        <v>226069.0</v>
+      </c>
+      <c r="I54" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" hidden="1" customHeight="1">
+      <c r="A55" s="6">
+        <v>46226.0</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="8">
+        <v>692280.0</v>
+      </c>
+      <c r="G55" s="8">
+        <v>118381.0</v>
+      </c>
+      <c r="H55" s="8">
+        <v>700200.0</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J55" s="12"/>
+    </row>
+    <row r="56" ht="22.5" hidden="1" customHeight="1">
+      <c r="A56" s="6">
+        <v>46227.0</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="8">
+        <v>700200.0</v>
+      </c>
+      <c r="G56" s="8">
+        <v>112628.0</v>
+      </c>
+      <c r="H56" s="8">
+        <v>668440.0</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" s="12"/>
+    </row>
+    <row r="57" ht="22.5" hidden="1" customHeight="1">
+      <c r="A57" s="6">
+        <v>46227.0</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" s="8">
+        <v>226069.0</v>
+      </c>
+      <c r="G57" s="8">
+        <v>193130.0</v>
+      </c>
+      <c r="H57" s="8">
+        <v>326391.0</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" ht="22.5" hidden="1" customHeight="1">
+      <c r="A58" s="6">
+        <v>46227.0</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="8">
+        <v>144637.0</v>
+      </c>
+      <c r="G58" s="8">
+        <v>64227.0</v>
+      </c>
+      <c r="H58" s="8">
+        <v>128160.0</v>
+      </c>
+      <c r="I58" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J58" s="12"/>
+    </row>
+    <row r="59" ht="22.5" hidden="1" customHeight="1">
+      <c r="A59" s="6">
+        <v>46227.0</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" s="8">
+        <v>295359.0</v>
+      </c>
+      <c r="G59" s="8">
+        <v>126369.0</v>
+      </c>
+      <c r="H59" s="8">
+        <v>166642.0</v>
+      </c>
+      <c r="I59" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F53" s="7">
-        <v>25200.0</v>
-      </c>
-      <c r="G53" s="7">
-        <v>2085.0</v>
-      </c>
-      <c r="H53" s="7">
-        <v>25920.0</v>
-      </c>
-      <c r="I53" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" ht="22.5" hidden="1" customHeight="1">
-      <c r="A54" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D54" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" s="7">
-        <v>285405.0</v>
-      </c>
-      <c r="G54" s="7">
-        <v>203180.0</v>
-      </c>
-      <c r="H54" s="7">
-        <v>226069.0</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J54" s="12" t="s">
+      <c r="J59" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" ht="22.5" hidden="1" customHeight="1">
+      <c r="A60" s="6">
+        <v>46230.0</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="55" ht="22.5" hidden="1" customHeight="1">
-      <c r="A55" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D55" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" s="7">
-        <v>692280.0</v>
-      </c>
-      <c r="G55" s="7">
-        <v>118381.0</v>
-      </c>
-      <c r="H55" s="7">
-        <v>700200.0</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J55" s="12"/>
-    </row>
-    <row r="56" ht="22.5" hidden="1" customHeight="1">
-      <c r="A56" s="9">
-        <v>46227.0</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D56" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="7">
-        <v>700200.0</v>
-      </c>
-      <c r="G56" s="7">
-        <v>112628.0</v>
-      </c>
-      <c r="H56" s="7">
-        <v>668440.0</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="12"/>
-    </row>
-    <row r="57" ht="22.5" hidden="1" customHeight="1">
-      <c r="A57" s="9">
-        <v>46227.0</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D57" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F57" s="7">
-        <v>226069.0</v>
-      </c>
-      <c r="G57" s="7">
-        <v>193130.0</v>
-      </c>
-      <c r="H57" s="7">
-        <v>326391.0</v>
-      </c>
-      <c r="I57" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J57" s="12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="58" ht="22.5" hidden="1" customHeight="1">
-      <c r="A58" s="9">
-        <v>46227.0</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="7">
-        <v>144637.0</v>
-      </c>
-      <c r="G58" s="7">
-        <v>64227.0</v>
-      </c>
-      <c r="H58" s="7">
-        <v>128160.0</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J58" s="12"/>
-    </row>
-    <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="9">
-        <v>46227.0</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D59" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F59" s="7">
-        <v>295359.0</v>
-      </c>
-      <c r="G59" s="7">
-        <v>126369.0</v>
-      </c>
-      <c r="H59" s="7">
-        <v>166642.0</v>
-      </c>
-      <c r="I59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="9">
-        <v>46230.0</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="7">
+      <c r="D60" s="8">
         <v>2110403.0</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F60" s="7">
+        <v>116</v>
+      </c>
+      <c r="F60" s="8">
         <v>9960.0</v>
       </c>
-      <c r="G60" s="7">
+      <c r="G60" s="8">
         <v>6018.0</v>
       </c>
-      <c r="H60" s="7">
+      <c r="H60" s="8">
         <v>3660.0</v>
       </c>
-      <c r="I60" s="10" t="s">
-        <v>17</v>
+      <c r="I60" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J60" s="12"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="9">
+      <c r="A61" s="6">
         <v>46230.0</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C61" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D61" s="7">
+      <c r="C61" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D61" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F61" s="7">
+        <v>32</v>
+      </c>
+      <c r="F61" s="8">
         <v>306720.0</v>
       </c>
-      <c r="G61" s="7">
+      <c r="G61" s="8">
         <v>164175.0</v>
       </c>
-      <c r="H61" s="7">
+      <c r="H61" s="8">
         <v>247096.0</v>
       </c>
-      <c r="I61" s="10" t="s">
-        <v>17</v>
+      <c r="I61" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J61" s="12"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
-      <c r="A62" s="9">
+      <c r="A62" s="6">
         <v>46230.0</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D62" s="7">
+        <v>25</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="7">
+        <v>13</v>
+      </c>
+      <c r="F62" s="8">
         <v>437080.0</v>
       </c>
-      <c r="G62" s="7">
+      <c r="G62" s="8">
         <v>277785.0</v>
       </c>
-      <c r="H62" s="7">
+      <c r="H62" s="8">
         <v>353700.0</v>
       </c>
-      <c r="I62" s="10" t="s">
-        <v>24</v>
+      <c r="I62" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J62" s="12" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
-      <c r="A63" s="9">
+      <c r="A63" s="6">
         <v>46231.0</v>
       </c>
       <c r="B63" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F63" s="7">
+      <c r="F63" s="8">
         <v>165466.0</v>
       </c>
-      <c r="G63" s="7">
+      <c r="G63" s="8">
         <v>113462.0</v>
       </c>
-      <c r="H63" s="7">
+      <c r="H63" s="8">
         <v>375549.0</v>
       </c>
-      <c r="I63" s="10" t="s">
-        <v>24</v>
+      <c r="I63" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J63" s="12" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
-      <c r="A64" s="9">
+      <c r="A64" s="6">
         <v>46231.0</v>
       </c>
       <c r="B64" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D64" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D64" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F64" s="7">
+      <c r="F64" s="8">
         <v>238497.0</v>
       </c>
-      <c r="G64" s="7">
+      <c r="G64" s="8">
         <v>56526.0</v>
       </c>
-      <c r="H64" s="7">
+      <c r="H64" s="8">
         <v>181858.0</v>
       </c>
-      <c r="I64" s="10" t="s">
-        <v>31</v>
+      <c r="I64" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="J64" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
-      <c r="A65" s="9">
+      <c r="A65" s="6">
         <v>46231.0</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D65" s="7">
+        <v>50</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D65" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F65" s="7">
+        <v>73</v>
+      </c>
+      <c r="F65" s="8">
         <v>8190.0</v>
       </c>
-      <c r="G65" s="7">
+      <c r="G65" s="8">
         <v>2049.0</v>
       </c>
-      <c r="H65" s="7">
+      <c r="H65" s="8">
         <v>7200.0</v>
       </c>
-      <c r="I65" s="10" t="s">
-        <v>31</v>
+      <c r="I65" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
-      <c r="A66" s="9">
+      <c r="A66" s="6">
         <v>46231.0</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D66" s="7">
+        <v>50</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D66" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" s="7">
+        <v>13</v>
+      </c>
+      <c r="F66" s="8">
         <v>146224.0</v>
       </c>
-      <c r="G66" s="7">
+      <c r="G66" s="8">
         <v>78064.0</v>
       </c>
-      <c r="H66" s="7">
+      <c r="H66" s="8">
         <v>98850.0</v>
       </c>
-      <c r="I66" s="10" t="s">
-        <v>31</v>
+      <c r="I66" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
-      <c r="A67" s="9">
+      <c r="A67" s="6">
         <v>46232.0</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>120</v>
       </c>
       <c r="C67" s="21"/>
-      <c r="D67" s="7">
+      <c r="D67" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" s="7">
+        <v>13</v>
+      </c>
+      <c r="F67" s="8">
         <v>14599.0</v>
       </c>
-      <c r="G67" s="7">
+      <c r="G67" s="8">
         <v>3782.0</v>
       </c>
-      <c r="H67" s="7">
+      <c r="H67" s="8">
         <v>7263.0</v>
       </c>
-      <c r="I67" s="10" t="s">
-        <v>26</v>
+      <c r="I67" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="J67" s="12"/>
     </row>
     <row r="68" ht="22.5" hidden="1" customHeight="1">
-      <c r="A68" s="9">
+      <c r="A68" s="6">
         <v>46232.0</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C68" s="21"/>
-      <c r="D68" s="7">
+      <c r="D68" s="8">
         <v>2110402.0</v>
       </c>
       <c r="E68" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" s="8">
+        <v>22080.0</v>
+      </c>
+      <c r="G68" s="8">
+        <v>5686.0</v>
+      </c>
+      <c r="H68" s="8">
+        <v>36720.0</v>
+      </c>
+      <c r="I68" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F68" s="7">
-        <v>22080.0</v>
-      </c>
-      <c r="G68" s="7">
-        <v>5686.0</v>
-      </c>
-      <c r="H68" s="7">
-        <v>36720.0</v>
-      </c>
-      <c r="I68" s="10" t="s">
-        <v>26</v>
-      </c>
       <c r="J68" s="12"/>
     </row>
     <row r="69" ht="22.5" hidden="1" customHeight="1">
-      <c r="A69" s="9">
+      <c r="A69" s="6">
         <v>46232.0</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C69" s="21"/>
-      <c r="D69" s="7">
+      <c r="D69" s="8">
         <v>2110402.0</v>
       </c>
       <c r="E69" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" s="8">
+        <v>353905.0</v>
+      </c>
+      <c r="G69" s="8">
+        <v>208296.0</v>
+      </c>
+      <c r="H69" s="8">
+        <v>117570.0</v>
+      </c>
+      <c r="I69" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F69" s="7">
-        <v>353905.0</v>
-      </c>
-      <c r="G69" s="7">
-        <v>208296.0</v>
-      </c>
-      <c r="H69" s="7">
-        <v>117570.0</v>
-      </c>
-      <c r="I69" s="10" t="s">
-        <v>26</v>
-      </c>
       <c r="J69" s="12"/>
     </row>
     <row r="70" ht="22.5" hidden="1" customHeight="1">
-      <c r="A70" s="9">
+      <c r="A70" s="6">
         <v>46232.0</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C70" s="21"/>
-      <c r="D70" s="7">
+      <c r="D70" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F70" s="7">
+        <v>42</v>
+      </c>
+      <c r="F70" s="8">
         <v>5913.0</v>
       </c>
-      <c r="G70" s="7">
+      <c r="G70" s="8">
         <v>902.0</v>
       </c>
-      <c r="H70" s="7">
+      <c r="H70" s="8">
         <v>5893.0</v>
       </c>
-      <c r="I70" s="10" t="s">
-        <v>26</v>
+      <c r="I70" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="J70" s="12"/>
     </row>
     <row r="71" ht="22.5" hidden="1" customHeight="1">
-      <c r="A71" s="9">
+      <c r="A71" s="6">
         <v>46232.0</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="21"/>
-      <c r="D71" s="7">
+      <c r="D71" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F71" s="7">
+        <v>32</v>
+      </c>
+      <c r="F71" s="8">
         <v>256613.0</v>
       </c>
-      <c r="G71" s="7">
+      <c r="G71" s="8">
         <v>86092.0</v>
       </c>
-      <c r="H71" s="7">
+      <c r="H71" s="8">
         <v>142320.0</v>
       </c>
-      <c r="I71" s="10" t="s">
-        <v>26</v>
+      <c r="I71" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="J71" s="12"/>
     </row>
     <row r="72" ht="22.5" hidden="1" customHeight="1">
-      <c r="A72" s="9">
+      <c r="A72" s="6">
         <v>46232.0</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="21"/>
-      <c r="D72" s="7">
+      <c r="D72" s="8">
         <v>152384.0</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F72" s="7">
+        <v>47</v>
+      </c>
+      <c r="F72" s="8">
         <v>21300.0</v>
       </c>
-      <c r="G72" s="7">
+      <c r="G72" s="8">
         <v>9765.0</v>
       </c>
-      <c r="H72" s="7">
+      <c r="H72" s="8">
         <v>18690.0</v>
       </c>
-      <c r="I72" s="10" t="s">
-        <v>26</v>
+      <c r="I72" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="J72" s="12"/>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
-      <c r="A73" s="9">
+      <c r="A73" s="6">
         <v>46232.0</v>
       </c>
       <c r="B73" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C73" s="21"/>
+      <c r="D73" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" s="8">
+        <v>351733.0</v>
+      </c>
+      <c r="G73" s="8">
+        <v>145994.0</v>
+      </c>
+      <c r="H73" s="8">
+        <v>200114.0</v>
+      </c>
+      <c r="I73" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="12"/>
+    </row>
+    <row r="74" ht="22.5" hidden="1" customHeight="1">
+      <c r="A74" s="19">
+        <v>46233.0</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D74" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74" s="8">
+        <v>158761.0</v>
+      </c>
+      <c r="G74" s="8">
+        <v>68908.0</v>
+      </c>
+      <c r="H74" s="8">
+        <v>183014.0</v>
+      </c>
+      <c r="I74" s="13" t="s">
         <v>81</v>
-      </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F73" s="7">
-        <v>351733.0</v>
-      </c>
-      <c r="G73" s="7">
-        <v>145994.0</v>
-      </c>
-      <c r="H73" s="7">
-        <v>200114.0</v>
-      </c>
-      <c r="I73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J73" s="12"/>
-    </row>
-    <row r="74" ht="22.5" hidden="1" customHeight="1">
-      <c r="A74" s="17">
-        <v>46233.0</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D74" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F74" s="7">
-        <v>158761.0</v>
-      </c>
-      <c r="G74" s="7">
-        <v>68908.0</v>
-      </c>
-      <c r="H74" s="7">
-        <v>183014.0</v>
-      </c>
-      <c r="I74" s="10" t="s">
-        <v>48</v>
       </c>
       <c r="J74" s="12" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
-      <c r="A75" s="17">
+      <c r="A75" s="19">
         <v>46233.0</v>
       </c>
       <c r="B75" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D75" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E75" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C75" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D75" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F75" s="7">
+      <c r="F75" s="8">
         <v>117430.0</v>
       </c>
-      <c r="G75" s="7">
+      <c r="G75" s="8">
         <v>57323.0</v>
       </c>
-      <c r="H75" s="7">
+      <c r="H75" s="8">
         <v>86643.0</v>
       </c>
-      <c r="I75" s="10" t="s">
-        <v>17</v>
+      <c r="I75" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J75" s="12"/>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
-      <c r="A76" s="9">
+      <c r="A76" s="6">
         <v>46234.0</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C76" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D76" s="7">
+      <c r="C76" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D76" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F76" s="7">
+        <v>32</v>
+      </c>
+      <c r="F76" s="8">
         <v>265693.0</v>
       </c>
-      <c r="G76" s="7">
+      <c r="G76" s="8">
         <v>83477.0</v>
       </c>
-      <c r="H76" s="7">
+      <c r="H76" s="8">
         <v>116000.0</v>
       </c>
-      <c r="I76" s="10" t="s">
-        <v>17</v>
+      <c r="I76" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J76" s="12"/>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
-      <c r="A77" s="9">
+      <c r="A77" s="6">
         <v>46234.0</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D77" s="8">
         <v>112357.0</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F77" s="7">
+        <v>84</v>
+      </c>
+      <c r="F77" s="8">
         <v>720.0</v>
       </c>
-      <c r="G77" s="7">
+      <c r="G77" s="8">
         <v>360.0</v>
       </c>
-      <c r="H77" s="7">
+      <c r="H77" s="8">
         <v>2040.0</v>
       </c>
-      <c r="I77" s="10" t="s">
-        <v>26</v>
+      <c r="I77" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="J77" s="12" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
-      <c r="A78" s="9">
+      <c r="A78" s="6">
         <v>46234.0</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D78" s="7">
+        <v>50</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D78" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F78" s="7">
+        <v>73</v>
+      </c>
+      <c r="F78" s="8">
         <v>5580.0</v>
       </c>
-      <c r="G78" s="7">
+      <c r="G78" s="8">
         <v>2192.0</v>
       </c>
-      <c r="H78" s="7">
+      <c r="H78" s="8">
         <v>3984.0</v>
       </c>
-      <c r="I78" s="10" t="s">
-        <v>31</v>
+      <c r="I78" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="J78" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="79" ht="22.5" hidden="1" customHeight="1">
-      <c r="A79" s="19">
+      <c r="A79" s="18">
         <v>46237.0</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D79" s="7">
+        <v>50</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D79" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F79" s="7">
+        <v>13</v>
+      </c>
+      <c r="F79" s="8">
         <v>192903.0</v>
       </c>
-      <c r="G79" s="7">
+      <c r="G79" s="8">
         <v>150030.0</v>
       </c>
-      <c r="H79" s="7">
+      <c r="H79" s="8">
         <v>77501.0</v>
       </c>
-      <c r="I79" s="10" t="s">
-        <v>31</v>
+      <c r="I79" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="J79" s="12" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="80" ht="22.5" hidden="1" customHeight="1">
-      <c r="A80" s="19">
+      <c r="A80" s="18">
         <v>46237.0</v>
       </c>
       <c r="B80" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D80" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C80" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D80" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F80" s="7">
+      <c r="F80" s="8">
         <v>152062.0</v>
       </c>
-      <c r="G80" s="7">
+      <c r="G80" s="8">
         <v>112769.0</v>
       </c>
-      <c r="H80" s="7">
+      <c r="H80" s="8">
         <v>124423.0</v>
       </c>
-      <c r="I80" s="10" t="s">
-        <v>31</v>
+      <c r="I80" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="J80" s="12" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="81" ht="22.5" hidden="1" customHeight="1">
-      <c r="A81" s="19">
+      <c r="A81" s="18">
         <v>46237.0</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C81" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C81" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D81" s="7">
+      <c r="D81" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F81" s="7">
+        <v>32</v>
+      </c>
+      <c r="F81" s="8">
         <v>153692.0</v>
       </c>
-      <c r="G81" s="7">
+      <c r="G81" s="8">
         <v>136980.0</v>
       </c>
-      <c r="H81" s="7">
+      <c r="H81" s="8">
         <v>63920.0</v>
       </c>
-      <c r="I81" s="10" t="s">
-        <v>48</v>
+      <c r="I81" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="J81" s="12" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="82" ht="22.5" hidden="1" customHeight="1">
-      <c r="A82" s="19">
+      <c r="A82" s="18">
         <v>46237.0</v>
       </c>
       <c r="B82" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D82" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" s="8">
+        <v>45564.0</v>
+      </c>
+      <c r="G82" s="8">
+        <v>10456.0</v>
+      </c>
+      <c r="H82" s="8">
+        <v>40560.0</v>
+      </c>
+      <c r="I82" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" s="12"/>
+    </row>
+    <row r="83" ht="22.5" hidden="1" customHeight="1">
+      <c r="A83" s="18">
+        <v>46237.0</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D82" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F82" s="7">
-        <v>45564.0</v>
-      </c>
-      <c r="G82" s="7">
-        <v>10456.0</v>
-      </c>
-      <c r="H82" s="7">
-        <v>40560.0</v>
-      </c>
-      <c r="I82" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="12"/>
-    </row>
-    <row r="83" ht="22.5" hidden="1" customHeight="1">
-      <c r="A83" s="19">
-        <v>46237.0</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D83" s="7">
+      <c r="C83" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F83" s="7">
+        <v>32</v>
+      </c>
+      <c r="F83" s="8">
         <v>93517.0</v>
       </c>
-      <c r="G83" s="7">
+      <c r="G83" s="8">
         <v>18622.0</v>
       </c>
-      <c r="H83" s="7">
+      <c r="H83" s="8">
         <v>48804.0</v>
       </c>
-      <c r="I83" s="10" t="s">
-        <v>24</v>
+      <c r="I83" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J83" s="12" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
-      <c r="A84" s="9">
+      <c r="A84" s="6">
         <v>46238.0</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D84" s="7">
+      <c r="C84" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D84" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F84" s="7">
+        <v>73</v>
+      </c>
+      <c r="F84" s="8">
         <v>43200.0</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G84" s="8">
         <v>5340.0</v>
       </c>
-      <c r="H84" s="7">
+      <c r="H84" s="8">
         <v>40890.0</v>
       </c>
-      <c r="I84" s="10" t="s">
-        <v>17</v>
+      <c r="I84" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J84" s="12"/>
     </row>
     <row r="85" ht="22.5" customHeight="1">
-      <c r="A85" s="9">
+      <c r="A85" s="6">
         <v>46238.0</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D85" s="7">
+      <c r="C85" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D85" s="8">
         <v>152384.0</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F85" s="7">
+        <v>47</v>
+      </c>
+      <c r="F85" s="8">
         <v>25350.0</v>
       </c>
-      <c r="G85" s="7">
+      <c r="G85" s="8">
         <v>6240.0</v>
       </c>
-      <c r="H85" s="7">
+      <c r="H85" s="8">
         <v>30750.0</v>
       </c>
-      <c r="I85" s="10" t="s">
-        <v>24</v>
+      <c r="I85" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J85" s="12"/>
     </row>
     <row r="86" ht="22.5" customHeight="1">
-      <c r="A86" s="9">
+      <c r="A86" s="6">
         <v>46238.0</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C86" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D86" s="7">
+      <c r="C86" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D86" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F86" s="7">
+        <v>45</v>
+      </c>
+      <c r="F86" s="8">
         <v>5040.0</v>
       </c>
-      <c r="G86" s="7">
+      <c r="G86" s="8">
         <v>720.0</v>
       </c>
-      <c r="H86" s="7">
+      <c r="H86" s="8">
         <v>4680.0</v>
       </c>
-      <c r="I86" s="10" t="s">
-        <v>17</v>
+      <c r="I86" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J86" s="12"/>
     </row>
     <row r="87" ht="22.5" customHeight="1">
-      <c r="A87" s="9">
+      <c r="A87" s="6">
         <v>46238.0</v>
       </c>
       <c r="B87" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E87" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C87" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D87" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F87" s="7">
+      <c r="F87" s="8">
         <v>124423.0</v>
       </c>
-      <c r="G87" s="7">
+      <c r="G87" s="8">
         <v>60002.0</v>
       </c>
-      <c r="H87" s="7">
+      <c r="H87" s="8">
         <v>69217.0</v>
       </c>
-      <c r="I87" s="10" t="s">
-        <v>24</v>
+      <c r="I87" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J87" s="12" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
-      <c r="A88" s="9">
+      <c r="A88" s="6">
         <v>46239.0</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C88" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D88" s="7">
+      <c r="C88" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D88" s="8">
         <v>152384.0</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F88" s="7">
+        <v>47</v>
+      </c>
+      <c r="F88" s="8">
         <v>30750.0</v>
       </c>
-      <c r="G88" s="7">
+      <c r="G88" s="8">
         <v>9975.0</v>
       </c>
-      <c r="H88" s="7">
+      <c r="H88" s="8">
         <v>36300.0</v>
       </c>
-      <c r="I88" s="10" t="s">
-        <v>37</v>
+      <c r="I88" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="J88" s="12"/>
     </row>
     <row r="89" ht="22.5" customHeight="1">
-      <c r="A89" s="9">
+      <c r="A89" s="6">
         <v>46239.0</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D89" s="7">
+        <v>25</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D89" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F89" s="7">
+        <v>32</v>
+      </c>
+      <c r="F89" s="8">
         <v>58320.0</v>
       </c>
-      <c r="G89" s="7">
+      <c r="G89" s="8">
         <v>53468.0</v>
       </c>
-      <c r="H89" s="7">
+      <c r="H89" s="8">
         <v>12480.0</v>
       </c>
-      <c r="I89" s="10" t="s">
-        <v>24</v>
+      <c r="I89" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J89" s="12" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
-      <c r="A90" s="19">
+      <c r="A90" s="18">
         <v>46240.0</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D90" s="7">
+        <v>25</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D90" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" s="7">
+        <v>13</v>
+      </c>
+      <c r="F90" s="8">
         <v>254880.0</v>
       </c>
-      <c r="G90" s="7">
+      <c r="G90" s="8">
         <v>151786.0</v>
       </c>
-      <c r="H90" s="7">
+      <c r="H90" s="8">
         <v>27180.0</v>
       </c>
-      <c r="I90" s="10" t="s">
-        <v>26</v>
+      <c r="I90" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="J90" s="12" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
-      <c r="A91" s="19">
+      <c r="A91" s="18">
         <v>46240.0</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C91" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C91" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D91" s="7">
+      <c r="D91" s="8">
         <v>112379.0</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F91" s="7">
+        <v>33</v>
+      </c>
+      <c r="F91" s="8">
         <v>13800.0</v>
       </c>
-      <c r="G91" s="7">
+      <c r="G91" s="8">
         <v>900.0</v>
       </c>
-      <c r="H91" s="7">
+      <c r="H91" s="8">
         <v>12132.0</v>
       </c>
-      <c r="I91" s="10" t="s">
-        <v>24</v>
+      <c r="I91" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="J91" s="12"/>
     </row>
     <row r="92" ht="22.5" customHeight="1">
-      <c r="A92" s="19">
+      <c r="A92" s="18">
         <v>46240.0</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C92" s="21"/>
-      <c r="D92" s="7">
+      <c r="C92" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D92" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F92" s="7">
+        <v>45</v>
+      </c>
+      <c r="F92" s="8">
         <v>4575.0</v>
       </c>
-      <c r="G92" s="7">
+      <c r="G92" s="8">
         <v>570.0</v>
       </c>
-      <c r="H92" s="7">
+      <c r="H92" s="8">
         <v>4213.0</v>
       </c>
-      <c r="I92" s="10"/>
-      <c r="J92" s="12"/>
-    </row>
-    <row r="93">
-      <c r="I93" s="20"/>
-    </row>
-    <row r="94">
-      <c r="I94" s="20"/>
-    </row>
-    <row r="95">
-      <c r="I95" s="20"/>
-    </row>
-    <row r="96">
-      <c r="I96" s="20"/>
+      <c r="I92" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="93" ht="22.5" customHeight="1">
+      <c r="A93" s="22">
+        <v>46244.0</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D93" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F93" s="8">
+        <v>222000.0</v>
+      </c>
+      <c r="G93" s="8">
+        <v>142780.0</v>
+      </c>
+      <c r="H93" s="8">
+        <v>312480.0</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J93" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="94" ht="22.5" customHeight="1">
+      <c r="A94" s="22">
+        <v>46244.0</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D94" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="8">
+        <v>300060.0</v>
+      </c>
+      <c r="G94" s="8">
+        <v>265744.0</v>
+      </c>
+      <c r="H94" s="8">
+        <v>260696.0</v>
+      </c>
+      <c r="I94" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J94" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="95" ht="22.5" customHeight="1">
+      <c r="A95" s="22">
+        <v>46244.0</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D95" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F95" s="8">
+        <v>36240.0</v>
+      </c>
+      <c r="G95" s="8">
+        <v>10696.0</v>
+      </c>
+      <c r="H95" s="8">
+        <v>39840.0</v>
+      </c>
+      <c r="I95" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J95" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="96" ht="22.5" customHeight="1">
+      <c r="A96" s="22">
+        <v>46244.0</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D96" s="8">
+        <v>2110317.0</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F96" s="8">
+        <v>21690.0</v>
+      </c>
+      <c r="G96" s="8">
+        <v>13530.0</v>
+      </c>
+      <c r="H96" s="8">
+        <v>26280.0</v>
+      </c>
+      <c r="I96" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J96" s="12"/>
     </row>
     <row r="97">
       <c r="I97" s="20"/>
@@ -6462,13 +6591,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I92">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I96">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I93:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I97:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A92">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A96">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -6531,1613 +6660,1646 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="9">
+      <c r="A2" s="6">
         <v>46224.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="7">
+        <v>12</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="8">
         <v>2110402.0</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="8">
+        <v>333.0</v>
+      </c>
+      <c r="G2" s="8">
+        <v>6480.0</v>
+      </c>
+      <c r="H2" s="8">
+        <v>3712.0</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7">
-        <v>333.0</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="J2" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" hidden="1" customHeight="1">
+      <c r="A3" s="6">
+        <v>46224.0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="8">
+        <v>2114158.0</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="8">
+        <v>60.0</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1000.0</v>
+      </c>
+      <c r="H3" s="8">
+        <v>60.0</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
+      <c r="A4" s="6">
+        <v>46225.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="8">
+        <v>10501.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="8">
+        <v>415093.0</v>
+      </c>
+      <c r="G4" s="8">
+        <v>115920.0</v>
+      </c>
+      <c r="H4" s="8">
+        <v>543038.0</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
+      <c r="A5" s="6">
+        <v>46225.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="8">
+        <v>112379.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="8">
+        <v>3000.0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>29400.0</v>
+      </c>
+      <c r="H5" s="8">
+        <v>3000.0</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="6">
+        <v>46225.0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="8">
+        <v>112268.0</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="8">
+        <v>3000.0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>12300.0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>3300.0</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="6">
+        <v>46225.0</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="8">
+        <v>132357.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1560.0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1560.0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>4560.0</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="6">
+        <v>46225.0</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="8">
+        <v>2152388.0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="8">
+        <v>720.0</v>
+      </c>
+      <c r="G8" s="8">
+        <v>11160.0</v>
+      </c>
+      <c r="H8" s="8">
+        <v>5940.0</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
+      <c r="A9" s="6">
+        <v>46225.0</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="8">
+        <v>3712.0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>46723.0</v>
+      </c>
+      <c r="H9" s="8">
+        <v>213.0</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
+      <c r="A10" s="6">
+        <v>46226.0</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="8">
+        <v>73001.0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="8">
+        <v>73787.0</v>
+      </c>
+      <c r="G10" s="8">
+        <v>72000.0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>109487.0</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="6">
+        <v>46226.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="8">
+        <v>112268.0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="8">
+        <v>3300.0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>1800.0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>3300.0</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="12"/>
+    </row>
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
+      <c r="A12" s="6">
+        <v>46226.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="8">
+        <v>112379.0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="8">
+        <v>4200.0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>7500.0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>3900.0</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="12"/>
+    </row>
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
+      <c r="A13" s="6">
+        <v>46226.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="8">
+        <v>379471.0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>392580.0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>357186.0</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
+      <c r="A14" s="6">
+        <v>46227.0</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="8">
+        <v>72001.0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="8">
+        <v>21905.0</v>
+      </c>
+      <c r="G14" s="8">
+        <v>47670.0</v>
+      </c>
+      <c r="H14" s="8">
+        <v>38000.0</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="6">
+        <v>46227.0</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="8">
+        <v>2110327.0</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8">
+        <v>69120.0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>57600.0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>40320.0</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
+      <c r="A16" s="6">
+        <v>46227.0</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="8">
+        <v>112379.0</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="8">
+        <v>3900.0</v>
+      </c>
+      <c r="G16" s="8">
+        <v>102600.0</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1500.0</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" ht="22.5" hidden="1" customHeight="1">
+      <c r="A17" s="6">
+        <v>46227.0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="8">
+        <v>2152388.0</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="8">
+        <v>720.0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>9720.0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>2580.0</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="12"/>
+    </row>
+    <row r="18" ht="22.5" hidden="1" customHeight="1">
+      <c r="A18" s="6">
+        <v>46227.0</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="8">
+        <v>112268.0</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="8">
+        <v>3300.0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>30600.0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>600.0</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
+      <c r="A19" s="6">
+        <v>46230.0</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="8">
+        <v>2410401.0</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="8">
+        <v>136538.0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>34080.0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>213000.0</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
+      <c r="A20" s="6">
+        <v>46231.0</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="8">
+        <v>591750.0</v>
+      </c>
+      <c r="G20" s="8">
+        <v>239760.0</v>
+      </c>
+      <c r="H20" s="8">
+        <v>577207.0</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
+      <c r="A21" s="6">
+        <v>46231.0</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="8">
+        <v>10601.0</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="8">
+        <v>1230.0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>8626.0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>1958.0</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" hidden="1" customHeight="1">
+      <c r="A22" s="6">
+        <v>46231.0</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="8">
+        <v>2152388.0</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="8">
+        <v>4320.0</v>
+      </c>
+      <c r="G22" s="8">
+        <v>2700.0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>3420.0</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="12"/>
+    </row>
+    <row r="23" ht="22.5" hidden="1" customHeight="1">
+      <c r="A23" s="6">
+        <v>46231.0</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="8">
+        <v>114357.0</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="8">
+        <v>240.0</v>
+      </c>
+      <c r="G23" s="8">
+        <v>52320.0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>240.0</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="12"/>
+    </row>
+    <row r="24" ht="22.5" hidden="1" customHeight="1">
+      <c r="A24" s="6">
+        <v>46232.0</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="8">
+        <v>10501.0</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="8">
+        <v>19663.0</v>
+      </c>
+      <c r="G24" s="8">
+        <v>49540.0</v>
+      </c>
+      <c r="H24" s="8">
+        <v>29632.0</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="12"/>
+    </row>
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
+      <c r="A25" s="6">
+        <v>46232.0</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="8">
+        <v>112268.0</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="8">
+        <v>5700.0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>34800.0</v>
+      </c>
+      <c r="H25" s="8">
+        <v>5100.0</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
+      <c r="A26" s="6">
+        <v>46232.0</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="8">
+        <v>2110317.0</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="8">
+        <v>720.0</v>
+      </c>
+      <c r="G26" s="8">
+        <v>7920.0</v>
+      </c>
+      <c r="H26" s="8">
+        <v>720.0</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="12"/>
+    </row>
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
+      <c r="A27" s="6">
+        <v>46232.0</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="8">
+        <v>2114357.0</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="8">
+        <v>432.0</v>
+      </c>
+      <c r="G27" s="8">
+        <v>576.0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>432.0</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="12"/>
+    </row>
+    <row r="28" ht="22.5" hidden="1" customHeight="1">
+      <c r="A28" s="6">
+        <v>46232.0</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="8">
+        <v>10501.0</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="8">
+        <v>219540.0</v>
+      </c>
+      <c r="G28" s="8">
+        <v>272160.0</v>
+      </c>
+      <c r="H28" s="8">
+        <v>16698.0</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="12"/>
+    </row>
+    <row r="29" ht="22.5" hidden="1" customHeight="1">
+      <c r="A29" s="6">
+        <v>46233.0</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="8">
+        <v>112268.0</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="8">
+        <v>5100.0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>3300.0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>4800.0</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J29" s="12"/>
+    </row>
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
+      <c r="A30" s="6">
+        <v>46233.0</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="8">
+        <v>114357.0</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="8">
+        <v>240.0</v>
+      </c>
+      <c r="G30" s="8">
+        <v>7800.0</v>
+      </c>
+      <c r="H30" s="8">
+        <v>1560.0</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="12"/>
+    </row>
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="6">
+        <v>46233.0</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="8">
+        <v>10601.0</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" s="8">
+        <v>7717.0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>10080.0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>12867.0</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
+      <c r="A32" s="6">
+        <v>46234.0</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="8">
+        <v>79110.0</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="8">
+        <v>48000.0</v>
+      </c>
+      <c r="G32" s="8">
+        <v>24600.0</v>
+      </c>
+      <c r="H32" s="8">
+        <v>36300.0</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
+      <c r="A33" s="6">
+        <v>46234.0</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="8">
+        <v>10501.0</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="8">
+        <v>95574.0</v>
+      </c>
+      <c r="G33" s="8">
+        <v>78469.0</v>
+      </c>
+      <c r="H33" s="8">
+        <v>142801.0</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
+      <c r="A34" s="6">
+        <v>46234.0</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" s="8">
+        <v>73001.0</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34" s="8">
+        <v>73367.0</v>
+      </c>
+      <c r="G34" s="8">
+        <v>94608.0</v>
+      </c>
+      <c r="H34" s="8">
+        <v>39150.0</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="12"/>
+    </row>
+    <row r="35" ht="22.5" hidden="1" customHeight="1">
+      <c r="A35" s="6">
+        <v>46234.0</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="14"/>
+      <c r="D35" s="8">
+        <v>112357.0</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35" s="8">
+        <v>840.0</v>
+      </c>
+      <c r="G35" s="8">
+        <v>5160.0</v>
+      </c>
+      <c r="H35" s="8">
+        <v>480.0</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="12"/>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="A36" s="18">
+        <v>46237.0</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="8">
+        <v>10601.0</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" s="8">
+        <v>17934.0</v>
+      </c>
+      <c r="G36" s="8">
+        <v>64980.0</v>
+      </c>
+      <c r="H36" s="8">
+        <v>21714.0</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" customHeight="1">
+      <c r="A37" s="18">
+        <v>46237.0</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="14"/>
+      <c r="D37" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="8">
+        <v>194520.0</v>
+      </c>
+      <c r="G37" s="8">
+        <v>84060.0</v>
+      </c>
+      <c r="H37" s="8">
+        <v>122840.0</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" s="12"/>
+    </row>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="18">
+        <v>46237.0</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="14"/>
+      <c r="D38" s="8">
+        <v>114379.0</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="8">
+        <v>52200.0</v>
+      </c>
+      <c r="G38" s="8">
+        <v>16200.0</v>
+      </c>
+      <c r="H38" s="8">
+        <v>7500.0</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J38" s="12"/>
+    </row>
+    <row r="39" ht="22.5" customHeight="1">
+      <c r="A39" s="18">
+        <v>46237.0</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="14"/>
+      <c r="D39" s="8">
+        <v>2110317.0</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="8">
+        <v>6450.0</v>
+      </c>
+      <c r="G39" s="8">
+        <v>16920.0</v>
+      </c>
+      <c r="H39" s="8">
         <v>6480.0</v>
       </c>
-      <c r="H2" s="7">
-        <v>3712.0</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="9">
-        <v>46224.0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="7">
-        <v>2114158.0</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="7">
-        <v>60.0</v>
-      </c>
-      <c r="G3" s="7">
-        <v>1000.0</v>
-      </c>
-      <c r="H3" s="7">
-        <v>60.0</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="I39" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" s="12"/>
+    </row>
+    <row r="40" ht="22.5" customHeight="1">
+      <c r="A40" s="18">
+        <v>46237.0</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="8">
+        <v>2010102.0</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="8">
+        <v>1398.0</v>
+      </c>
+      <c r="G40" s="8">
+        <v>1320.0</v>
+      </c>
+      <c r="H40" s="8">
+        <v>438.0</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" s="12"/>
+    </row>
+    <row r="41" ht="22.5" customHeight="1">
+      <c r="A41" s="6">
+        <v>46238.0</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="14"/>
+      <c r="D41" s="8">
+        <v>2152388.0</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" s="8">
+        <v>2460.0</v>
+      </c>
+      <c r="G41" s="8">
+        <v>17640.0</v>
+      </c>
+      <c r="H41" s="8">
+        <v>3240.0</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" s="12"/>
+    </row>
+    <row r="42" ht="22.5" customHeight="1">
+      <c r="A42" s="6">
+        <v>46238.0</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="14"/>
+      <c r="D42" s="8">
+        <v>112268.0</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="7">
+      <c r="F42" s="8">
+        <v>3600.0</v>
+      </c>
+      <c r="G42" s="8">
+        <v>1500.0</v>
+      </c>
+      <c r="H42" s="8">
+        <v>3900.0</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" s="12"/>
+    </row>
+    <row r="43" ht="22.5" customHeight="1">
+      <c r="A43" s="6">
+        <v>46238.0</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="14"/>
+      <c r="D43" s="8">
+        <v>114379.0</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="8">
+        <v>7500.0</v>
+      </c>
+      <c r="G43" s="8">
+        <v>54900.0</v>
+      </c>
+      <c r="H43" s="8">
+        <v>8400.0</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" s="12"/>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="6">
+        <v>46238.0</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="14"/>
+      <c r="D44" s="8">
+        <v>114357.0</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" s="8">
+        <v>240.0</v>
+      </c>
+      <c r="G44" s="8">
+        <v>7680.0</v>
+      </c>
+      <c r="H44" s="8">
+        <v>360.0</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" s="12"/>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="6">
+        <v>46239.0</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="14"/>
+      <c r="D45" s="8">
+        <v>10601.0</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F45" s="8">
+        <v>1115.0</v>
+      </c>
+      <c r="G45" s="8">
+        <v>5267.0</v>
+      </c>
+      <c r="H45" s="8">
+        <v>1590.0</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="A46" s="6">
+        <v>46239.0</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="14"/>
+      <c r="D46" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" s="8">
+        <v>114240.0</v>
+      </c>
+      <c r="G46" s="8">
+        <v>79680.0</v>
+      </c>
+      <c r="H46" s="8">
+        <v>191130.0</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="12"/>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="A47" s="6">
+        <v>46239.0</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="14"/>
+      <c r="D47" s="8">
+        <v>2112207.0</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" s="8">
+        <v>1800.0</v>
+      </c>
+      <c r="G47" s="8">
+        <v>1800.0</v>
+      </c>
+      <c r="H47" s="8">
+        <v>1980.0</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J47" s="12"/>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="6">
+        <v>46239.0</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" s="8">
+        <v>112268.0</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" s="8">
+        <v>3900.0</v>
+      </c>
+      <c r="G48" s="8">
+        <v>34200.0</v>
+      </c>
+      <c r="H48" s="8">
+        <v>1200.0</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J48" s="12"/>
+    </row>
+    <row r="49" ht="22.5" customHeight="1">
+      <c r="A49" s="6">
+        <v>46239.0</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" s="8">
+        <v>112357.0</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F49" s="8">
+        <v>600.0</v>
+      </c>
+      <c r="G49" s="8">
+        <v>8400.0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>600.0</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" s="12"/>
+    </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="6">
+        <v>46239.0</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="14"/>
+      <c r="D50" s="8">
+        <v>114268.0</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F50" s="8">
+        <v>2700.0</v>
+      </c>
+      <c r="G50" s="8">
+        <v>5700.0</v>
+      </c>
+      <c r="H50" s="8">
+        <v>300.0</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J50" s="12"/>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="6">
+        <v>46239.0</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="14"/>
+      <c r="D51" s="8">
         <v>10501.0</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="7">
-        <v>415093.0</v>
-      </c>
-      <c r="G4" s="7">
-        <v>115920.0</v>
-      </c>
-      <c r="H4" s="7">
-        <v>543038.0</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="7">
+      <c r="E51" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="8">
+        <v>68651.0</v>
+      </c>
+      <c r="G51" s="8">
+        <v>64050.0</v>
+      </c>
+      <c r="H51" s="8">
+        <v>13421.0</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="6">
+        <v>46239.0</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" s="14"/>
+      <c r="D52" s="8">
+        <v>72003.0</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F52" s="8">
+        <v>1391.0</v>
+      </c>
+      <c r="G52" s="8">
+        <v>3885.0</v>
+      </c>
+      <c r="H52" s="8">
+        <v>2407.0</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" s="12"/>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="6">
+        <v>46239.0</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="14"/>
+      <c r="D53" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" s="8">
+        <v>2974.0</v>
+      </c>
+      <c r="G53" s="8">
+        <v>1200.0</v>
+      </c>
+      <c r="H53" s="8">
+        <v>3317.0</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="18">
+        <v>46240.0</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="14"/>
+      <c r="D54" s="8">
         <v>112379.0</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="7">
-        <v>3000.0</v>
-      </c>
-      <c r="G5" s="7">
-        <v>29400.0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>3000.0</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="7">
-        <v>112268.0</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="7">
-        <v>3000.0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>12300.0</v>
-      </c>
-      <c r="H6" s="7">
-        <v>3300.0</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="7">
-        <v>132357.0</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1560.0</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1560.0</v>
-      </c>
-      <c r="H7" s="7">
-        <v>4560.0</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="7">
-        <v>2152388.0</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="7">
-        <v>720.0</v>
-      </c>
-      <c r="G8" s="7">
-        <v>11160.0</v>
-      </c>
-      <c r="H8" s="7">
-        <v>5940.0</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="9">
-        <v>46225.0</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="7">
-        <v>3712.0</v>
-      </c>
-      <c r="G9" s="7">
-        <v>46723.0</v>
-      </c>
-      <c r="H9" s="7">
-        <v>213.0</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="7">
+      <c r="E54" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="8">
+        <v>3600.0</v>
+      </c>
+      <c r="G54" s="8">
+        <v>26100.0</v>
+      </c>
+      <c r="H54" s="8">
+        <v>6900.0</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J54" s="12"/>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="18">
+        <v>46240.0</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="14"/>
+      <c r="D55" s="8">
         <v>73001.0</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="7">
-        <v>73787.0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>72000.0</v>
-      </c>
-      <c r="H10" s="7">
-        <v>109487.0</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="7">
-        <v>112268.0</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="7">
-        <v>3300.0</v>
-      </c>
-      <c r="G11" s="7">
-        <v>1800.0</v>
-      </c>
-      <c r="H11" s="7">
-        <v>3300.0</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="12"/>
-    </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="7">
+      <c r="E55" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55" s="8">
+        <v>2415.0</v>
+      </c>
+      <c r="G55" s="8">
+        <v>26490.0</v>
+      </c>
+      <c r="H55" s="8">
+        <v>2415.0</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" s="12"/>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="A56" s="18">
+        <v>46240.0</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="14"/>
+      <c r="D56" s="8">
+        <v>112357.0</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F56" s="8">
+        <v>600.0</v>
+      </c>
+      <c r="G56" s="8">
+        <v>3960.0</v>
+      </c>
+      <c r="H56" s="8">
+        <v>600.0</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J56" s="12"/>
+    </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="18">
+        <v>46240.0</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="14"/>
+      <c r="D57" s="8">
+        <v>114379.0</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F57" s="8">
+        <v>2400.0</v>
+      </c>
+      <c r="G57" s="8">
+        <v>15000.0</v>
+      </c>
+      <c r="H57" s="8">
+        <v>300.0</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J57" s="12"/>
+    </row>
+    <row r="58" ht="22.5" customHeight="1">
+      <c r="A58" s="18">
+        <v>46244.0</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="14"/>
+      <c r="D58" s="8">
         <v>112379.0</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="7">
-        <v>4200.0</v>
-      </c>
-      <c r="G12" s="7">
-        <v>7500.0</v>
-      </c>
-      <c r="H12" s="7">
-        <v>3900.0</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="9">
-        <v>46226.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="7">
-        <v>379471.0</v>
-      </c>
-      <c r="G13" s="7">
-        <v>392580.0</v>
-      </c>
-      <c r="H13" s="7">
-        <v>357186.0</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="9">
-        <v>46227.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="7">
-        <v>72001.0</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="7">
-        <v>21905.0</v>
-      </c>
-      <c r="G14" s="7">
-        <v>47670.0</v>
-      </c>
-      <c r="H14" s="7">
-        <v>38000.0</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="9">
-        <v>46227.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="7">
-        <v>2110327.0</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="7">
-        <v>69120.0</v>
-      </c>
-      <c r="G15" s="7">
-        <v>57600.0</v>
-      </c>
-      <c r="H15" s="7">
-        <v>40320.0</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="9">
-        <v>46227.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="7">
-        <v>112379.0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="7">
-        <v>3900.0</v>
-      </c>
-      <c r="G16" s="7">
-        <v>102600.0</v>
-      </c>
-      <c r="H16" s="7">
-        <v>1500.0</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="9">
-        <v>46227.0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="7">
-        <v>2152388.0</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="7">
-        <v>720.0</v>
-      </c>
-      <c r="G17" s="7">
-        <v>9720.0</v>
-      </c>
-      <c r="H17" s="7">
-        <v>2580.0</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="12"/>
-    </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="9">
-        <v>46227.0</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="7">
-        <v>112268.0</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="7">
-        <v>3300.0</v>
-      </c>
-      <c r="G18" s="7">
-        <v>30600.0</v>
-      </c>
-      <c r="H18" s="7">
-        <v>600.0</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="9">
-        <v>46230.0</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="7">
-        <v>2410401.0</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" s="7">
-        <v>136538.0</v>
-      </c>
-      <c r="G19" s="7">
-        <v>34080.0</v>
-      </c>
-      <c r="H19" s="7">
-        <v>213000.0</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="9">
-        <v>46231.0</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="7">
-        <v>591750.0</v>
-      </c>
-      <c r="G20" s="7">
-        <v>239760.0</v>
-      </c>
-      <c r="H20" s="7">
-        <v>577207.0</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="9">
-        <v>46231.0</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="7">
-        <v>10601.0</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="7">
-        <v>1230.0</v>
-      </c>
-      <c r="G21" s="7">
-        <v>8626.0</v>
-      </c>
-      <c r="H21" s="7">
-        <v>1958.0</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="9">
-        <v>46231.0</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="7">
-        <v>2152388.0</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="7">
-        <v>4320.0</v>
-      </c>
-      <c r="G22" s="7">
-        <v>2700.0</v>
-      </c>
-      <c r="H22" s="7">
-        <v>3420.0</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="12"/>
-    </row>
-    <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="9">
-        <v>46231.0</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="7">
-        <v>114357.0</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F23" s="7">
-        <v>240.0</v>
-      </c>
-      <c r="G23" s="7">
-        <v>52320.0</v>
-      </c>
-      <c r="H23" s="7">
-        <v>240.0</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" s="12"/>
-    </row>
-    <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="9">
-        <v>46232.0</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="7">
-        <v>10501.0</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F24" s="7">
-        <v>19663.0</v>
-      </c>
-      <c r="G24" s="7">
-        <v>49540.0</v>
-      </c>
-      <c r="H24" s="7">
-        <v>29632.0</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="12"/>
-    </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="9">
-        <v>46232.0</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="7">
-        <v>112268.0</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" s="7">
-        <v>5700.0</v>
-      </c>
-      <c r="G25" s="7">
-        <v>34800.0</v>
-      </c>
-      <c r="H25" s="7">
+      <c r="E58" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F58" s="8">
+        <v>4800.0</v>
+      </c>
+      <c r="G58" s="8">
+        <v>41100.0</v>
+      </c>
+      <c r="H58" s="8">
         <v>5100.0</v>
       </c>
-      <c r="I25" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="12"/>
-    </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="9">
-        <v>46232.0</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="7">
-        <v>2110317.0</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" s="7">
-        <v>720.0</v>
-      </c>
-      <c r="G26" s="7">
-        <v>7920.0</v>
-      </c>
-      <c r="H26" s="7">
-        <v>720.0</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J26" s="12"/>
-    </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="9">
-        <v>46232.0</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="7">
-        <v>2114357.0</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="7">
-        <v>432.0</v>
-      </c>
-      <c r="G27" s="7">
-        <v>576.0</v>
-      </c>
-      <c r="H27" s="7">
-        <v>432.0</v>
-      </c>
-      <c r="I27" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J27" s="12"/>
-    </row>
-    <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="9">
-        <v>46232.0</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="7">
-        <v>10501.0</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="7">
-        <v>219540.0</v>
-      </c>
-      <c r="G28" s="7">
-        <v>272160.0</v>
-      </c>
-      <c r="H28" s="7">
-        <v>16698.0</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J28" s="12"/>
-    </row>
-    <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="9">
-        <v>46233.0</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="7">
-        <v>112268.0</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" s="7">
-        <v>5100.0</v>
-      </c>
-      <c r="G29" s="7">
-        <v>3300.0</v>
-      </c>
-      <c r="H29" s="7">
-        <v>4800.0</v>
-      </c>
-      <c r="I29" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="12"/>
-    </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="9">
-        <v>46233.0</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="7">
-        <v>114357.0</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F30" s="7">
-        <v>240.0</v>
-      </c>
-      <c r="G30" s="7">
-        <v>7800.0</v>
-      </c>
-      <c r="H30" s="7">
-        <v>1560.0</v>
-      </c>
-      <c r="I30" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J30" s="12"/>
-    </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="9">
-        <v>46233.0</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="7">
-        <v>10601.0</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F31" s="7">
-        <v>7717.0</v>
-      </c>
-      <c r="G31" s="7">
-        <v>10080.0</v>
-      </c>
-      <c r="H31" s="7">
-        <v>12867.0</v>
-      </c>
-      <c r="I31" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="9">
-        <v>46234.0</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="7">
-        <v>79110.0</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F32" s="7">
-        <v>48000.0</v>
-      </c>
-      <c r="G32" s="7">
-        <v>24600.0</v>
-      </c>
-      <c r="H32" s="7">
-        <v>36300.0</v>
-      </c>
-      <c r="I32" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="9">
-        <v>46234.0</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="7">
-        <v>10501.0</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F33" s="7">
-        <v>95574.0</v>
-      </c>
-      <c r="G33" s="7">
-        <v>78469.0</v>
-      </c>
-      <c r="H33" s="7">
-        <v>142801.0</v>
-      </c>
-      <c r="I33" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="9">
-        <v>46234.0</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="7">
-        <v>73001.0</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F34" s="7">
-        <v>73367.0</v>
-      </c>
-      <c r="G34" s="7">
-        <v>94608.0</v>
-      </c>
-      <c r="H34" s="7">
-        <v>39150.0</v>
-      </c>
-      <c r="I34" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="12"/>
-    </row>
-    <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="9">
-        <v>46234.0</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="7">
-        <v>112357.0</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F35" s="7">
-        <v>840.0</v>
-      </c>
-      <c r="G35" s="7">
-        <v>5160.0</v>
-      </c>
-      <c r="H35" s="7">
-        <v>480.0</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J35" s="12"/>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="19">
-        <v>46237.0</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="7">
-        <v>10601.0</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F36" s="7">
-        <v>17934.0</v>
-      </c>
-      <c r="G36" s="7">
-        <v>64980.0</v>
-      </c>
-      <c r="H36" s="7">
-        <v>21714.0</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="19">
-        <v>46237.0</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="7">
-        <v>194520.0</v>
-      </c>
-      <c r="G37" s="7">
-        <v>84060.0</v>
-      </c>
-      <c r="H37" s="7">
-        <v>122840.0</v>
-      </c>
-      <c r="I37" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="12"/>
-    </row>
-    <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="19">
-        <v>46237.0</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="7">
-        <v>114379.0</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F38" s="7">
-        <v>52200.0</v>
-      </c>
-      <c r="G38" s="7">
-        <v>16200.0</v>
-      </c>
-      <c r="H38" s="7">
-        <v>7500.0</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" s="12"/>
-    </row>
-    <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="19">
-        <v>46237.0</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="16"/>
-      <c r="D39" s="7">
-        <v>2110317.0</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F39" s="7">
-        <v>6450.0</v>
-      </c>
-      <c r="G39" s="7">
-        <v>16920.0</v>
-      </c>
-      <c r="H39" s="7">
-        <v>6480.0</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="12"/>
-    </row>
-    <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="19">
-        <v>46237.0</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" s="16"/>
-      <c r="D40" s="7">
-        <v>2010102.0</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="7">
-        <v>1398.0</v>
-      </c>
-      <c r="G40" s="7">
-        <v>1320.0</v>
-      </c>
-      <c r="H40" s="7">
-        <v>438.0</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="12"/>
-    </row>
-    <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="7">
-        <v>2152388.0</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" s="7">
-        <v>2460.0</v>
-      </c>
-      <c r="G41" s="7">
-        <v>17640.0</v>
-      </c>
-      <c r="H41" s="7">
-        <v>3240.0</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" s="12"/>
-    </row>
-    <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="7">
-        <v>112268.0</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F42" s="7">
-        <v>3600.0</v>
-      </c>
-      <c r="G42" s="7">
-        <v>1500.0</v>
-      </c>
-      <c r="H42" s="7">
-        <v>3900.0</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="12"/>
-    </row>
-    <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="7">
-        <v>114379.0</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F43" s="7">
-        <v>7500.0</v>
-      </c>
-      <c r="G43" s="7">
-        <v>54900.0</v>
-      </c>
-      <c r="H43" s="7">
-        <v>8400.0</v>
-      </c>
-      <c r="I43" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J43" s="12"/>
-    </row>
-    <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="9">
-        <v>46238.0</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="7">
-        <v>114357.0</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F44" s="7">
-        <v>240.0</v>
-      </c>
-      <c r="G44" s="7">
-        <v>7680.0</v>
-      </c>
-      <c r="H44" s="7">
-        <v>360.0</v>
-      </c>
-      <c r="I44" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J44" s="12"/>
-    </row>
-    <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="9">
-        <v>46239.0</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C45" s="16"/>
-      <c r="D45" s="7">
-        <v>10601.0</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F45" s="7">
-        <v>1115.0</v>
-      </c>
-      <c r="G45" s="7">
-        <v>5267.0</v>
-      </c>
-      <c r="H45" s="7">
-        <v>1590.0</v>
-      </c>
-      <c r="I45" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="9">
-        <v>46239.0</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E46" s="5" t="s">
+      <c r="I58" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F46" s="7">
-        <v>114240.0</v>
-      </c>
-      <c r="G46" s="7">
-        <v>79680.0</v>
-      </c>
-      <c r="H46" s="7">
-        <v>191130.0</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="12"/>
-    </row>
-    <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="9">
-        <v>46239.0</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" s="16"/>
-      <c r="D47" s="7">
-        <v>2112207.0</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F47" s="7">
-        <v>1800.0</v>
-      </c>
-      <c r="G47" s="7">
-        <v>1800.0</v>
-      </c>
-      <c r="H47" s="7">
-        <v>1980.0</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J47" s="12"/>
-    </row>
-    <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="9">
-        <v>46239.0</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C48" s="16"/>
-      <c r="D48" s="7">
-        <v>112268.0</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F48" s="7">
-        <v>3900.0</v>
-      </c>
-      <c r="G48" s="7">
-        <v>34200.0</v>
-      </c>
-      <c r="H48" s="7">
-        <v>1200.0</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J48" s="12"/>
-    </row>
-    <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="9">
-        <v>46239.0</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="16"/>
-      <c r="D49" s="7">
-        <v>112357.0</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F49" s="7">
-        <v>600.0</v>
-      </c>
-      <c r="G49" s="7">
-        <v>8400.0</v>
-      </c>
-      <c r="H49" s="7">
-        <v>600.0</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J49" s="12"/>
-    </row>
-    <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="9">
-        <v>46239.0</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="7">
-        <v>114268.0</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F50" s="7">
-        <v>2700.0</v>
-      </c>
-      <c r="G50" s="7">
-        <v>5700.0</v>
-      </c>
-      <c r="H50" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J50" s="12"/>
-    </row>
-    <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="9">
-        <v>46239.0</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51" s="16"/>
-      <c r="D51" s="7">
-        <v>10501.0</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F51" s="7">
-        <v>68651.0</v>
-      </c>
-      <c r="G51" s="7">
-        <v>64050.0</v>
-      </c>
-      <c r="H51" s="7">
-        <v>13421.0</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="9">
-        <v>46239.0</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="7">
-        <v>72003.0</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F52" s="7">
-        <v>1391.0</v>
-      </c>
-      <c r="G52" s="7">
-        <v>3885.0</v>
-      </c>
-      <c r="H52" s="7">
-        <v>2407.0</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="12"/>
-    </row>
-    <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="9">
-        <v>46239.0</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C53" s="16"/>
-      <c r="D53" s="7">
-        <v>2110402.0</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F53" s="7">
-        <v>2974.0</v>
-      </c>
-      <c r="G53" s="7">
-        <v>1200.0</v>
-      </c>
-      <c r="H53" s="7">
-        <v>3317.0</v>
-      </c>
-      <c r="I53" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="19">
-        <v>46240.0</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="7">
-        <v>112379.0</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F54" s="7">
-        <v>3600.0</v>
-      </c>
-      <c r="G54" s="7">
-        <v>26100.0</v>
-      </c>
-      <c r="H54" s="7">
-        <v>6900.0</v>
-      </c>
-      <c r="I54" s="15"/>
-      <c r="J54" s="12"/>
-    </row>
-    <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="19">
-        <v>46240.0</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="16"/>
-      <c r="D55" s="7">
-        <v>73001.0</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F55" s="7">
-        <v>2415.0</v>
-      </c>
-      <c r="G55" s="7">
-        <v>26490.0</v>
-      </c>
-      <c r="H55" s="7">
-        <v>2415.0</v>
-      </c>
-      <c r="I55" s="15"/>
-      <c r="J55" s="12"/>
-    </row>
-    <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="19">
-        <v>46240.0</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C56" s="16"/>
-      <c r="D56" s="7">
-        <v>112357.0</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F56" s="7">
-        <v>600.0</v>
-      </c>
-      <c r="G56" s="7">
-        <v>3960.0</v>
-      </c>
-      <c r="H56" s="7">
-        <v>600.0</v>
-      </c>
-      <c r="I56" s="15"/>
-      <c r="J56" s="12"/>
-    </row>
-    <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="19">
-        <v>46240.0</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C57" s="16"/>
-      <c r="D57" s="7">
-        <v>114379.0</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F57" s="7">
-        <v>2400.0</v>
-      </c>
-      <c r="G57" s="7">
-        <v>15000.0</v>
-      </c>
-      <c r="H57" s="7">
-        <v>300.0</v>
-      </c>
-      <c r="I57" s="15"/>
-      <c r="J57" s="12"/>
-    </row>
-    <row r="58">
-      <c r="I58" s="20"/>
+      <c r="J58" s="12"/>
     </row>
     <row r="59">
       <c r="I59" s="20"/>
@@ -10847,13 +11009,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I57">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I58">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I58:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I59:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A57">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A58">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="140">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -44,76 +44,82 @@
     <t xml:space="preserve">Otro </t>
   </si>
   <si>
+    <t>ALKA2</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>TAT BOGOTA MONTEVIDEO</t>
   </si>
   <si>
+    <t>7. Otro</t>
+  </si>
+  <si>
     <t>Daniel Castro</t>
   </si>
   <si>
-    <t>ALKA2</t>
+    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
   </si>
   <si>
     <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
-    <t>7. Otro</t>
-  </si>
-  <si>
-    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
+    <t>LANZA</t>
+  </si>
+  <si>
+    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
     <t>TAT MONTERIA</t>
   </si>
   <si>
+    <t>6. Transformación De Referencias</t>
+  </si>
+  <si>
+    <t>Pendiente Transformar Roto GT Por manipulación</t>
+  </si>
+  <si>
     <t>LUIS LOPEZ</t>
   </si>
   <si>
-    <t>LANZA</t>
-  </si>
-  <si>
-    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
+    <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
     <t>3. Falla De Rotación</t>
   </si>
   <si>
-    <t>6. Transformación De Referencias</t>
-  </si>
-  <si>
-    <t>Pendiente Transformar Roto GT Por manipulación</t>
-  </si>
-  <si>
     <t>TAT MEDELLIN</t>
   </si>
   <si>
+    <t>se equivocaron al cargar una estiba</t>
+  </si>
+  <si>
     <t>FABIO GOMEZ</t>
   </si>
   <si>
     <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
   </si>
   <si>
-    <t>HUEVO B X30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>se equivocaron al cargar una estiba</t>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
     <t>TAT CARTAGENA</t>
   </si>
   <si>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
     <t>Dilan Barraza</t>
   </si>
   <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
     <t>4. Exigencia Del Cliente (Edad)</t>
@@ -122,48 +128,42 @@
     <t>Venta FS</t>
   </si>
   <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
-  </si>
-  <si>
     <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
   </si>
   <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+  </si>
+  <si>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+  </si>
+  <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
-    <t>PALMAS</t>
-  </si>
-  <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
-  </si>
-  <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+  </si>
+  <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
-  </si>
-  <si>
     <t>TAT CALI</t>
   </si>
   <si>
@@ -176,25 +176,40 @@
     <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
+    <t>HUEVO SUCIO DE JAULA</t>
+  </si>
+  <si>
     <t>TAT CUCUTA</t>
   </si>
   <si>
     <t>ALEXANDER PEÑA</t>
   </si>
   <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
+    <t>Esta para despacho hoy</t>
+  </si>
+  <si>
     <t>Clientes FS</t>
   </si>
   <si>
-    <t>HUEVO SUCIO DE JAULA</t>
+    <t>Cola de programación</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
   </si>
   <si>
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
-  </si>
-  <si>
-    <t>Esta para despacho hoy</t>
+    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+  </si>
+  <si>
+    <t>HUEVO CX30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
   </si>
   <si>
     <t>Transformación de PET</t>
@@ -203,123 +218,108 @@
     <t>ANDRES MEJIA</t>
   </si>
   <si>
-    <t>Cola de programación</t>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
     <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
   </si>
   <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
-  </si>
-  <si>
     <t>TAT POPAYAN</t>
   </si>
   <si>
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
-    <t>HUEVO CX30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
-  </si>
-  <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
-  </si>
-  <si>
     <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
+    <t>ALKA1</t>
+  </si>
+  <si>
+    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
+  </si>
+  <si>
+    <t>HUEVO ROTO - ZF</t>
+  </si>
+  <si>
+    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
+  </si>
+  <si>
+    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
   </si>
   <si>
-    <t>ALKA1</t>
-  </si>
-  <si>
-    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
-  </si>
-  <si>
-    <t>HUEVO ROTO - ZF</t>
-  </si>
-  <si>
-    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
+  </si>
+  <si>
+    <t>Cargo en incubación</t>
   </si>
   <si>
     <t>5. Ingreso De Planta</t>
   </si>
   <si>
-    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
     <t>Se despacha par FS con producto más nuevo</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
     <t>ANDREA QUIROGA</t>
   </si>
   <si>
-    <t>Cargo en incubación</t>
-  </si>
-  <si>
     <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
     <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
+    <t>BELLAVISTA</t>
+  </si>
+  <si>
+    <t>Traslado a cedi, producto de devolución</t>
+  </si>
+  <si>
     <t>TAT PASTO</t>
   </si>
   <si>
     <t>CAROLINA VITERI</t>
   </si>
   <si>
-    <t>BELLAVISTA</t>
-  </si>
-  <si>
-    <t>Traslado a cedi, producto de devolución</t>
-  </si>
-  <si>
     <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
     <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
     <t>Pedido para villavicencio</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
     <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
   </si>
   <si>
     <t>HUEVO SUCIO ZF MARCADO</t>
   </si>
   <si>
+    <t>vehiculo con flata de capacidad / TAT cali</t>
+  </si>
+  <si>
     <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
-    <t>vehiculo con flata de capacidad / TAT cali</t>
-  </si>
-  <si>
     <t>Inventario de Asesor de Rionegro que renuncio</t>
   </si>
   <si>
@@ -423,6 +423,15 @@
   </si>
   <si>
     <t>Se envía huevo fresco a Rionegro</t>
+  </si>
+  <si>
+    <t>Clientes Fs</t>
+  </si>
+  <si>
+    <t>Se envían para Rionegro con mejor fecha</t>
+  </si>
+  <si>
+    <t>Llega de planta bellavista</t>
   </si>
 </sst>
 </file>
@@ -462,14 +471,14 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -500,58 +509,58 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -643,7 +652,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J96" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J100" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -661,7 +670,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J58" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J59" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -924,1081 +933,1081 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="8">
         <v>46204.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="7">
+        <v>359100.0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>83486.0</v>
+      </c>
+      <c r="H2" s="7">
+        <v>206140.0</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" hidden="1" customHeight="1">
+      <c r="A3" s="4">
+        <v>46205.0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="8">
+      <c r="F3" s="7">
+        <v>298282.0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>42201.0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>260675.0</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
+      <c r="A4" s="4">
+        <v>46205.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2110217.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="7">
+        <v>21120.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>11039.0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>16920.0</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
+      <c r="A5" s="4">
+        <v>46205.0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="7">
+        <v>75680.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>5640.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3134.0</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="7">
         <v>2110202.0</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="7">
+        <v>189540.0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>161685.0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>144720.0</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="8">
-        <v>359100.0</v>
-      </c>
-      <c r="G2" s="8">
-        <v>83486.0</v>
-      </c>
-      <c r="H2" s="8">
-        <v>206140.0</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="6">
-        <v>46205.0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="8">
-        <v>298282.0</v>
-      </c>
-      <c r="G3" s="8">
-        <v>42201.0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>260675.0</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="9"/>
-    </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="6">
-        <v>46205.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="J6" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="8">
-        <v>2110217.0</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="8">
-        <v>21120.0</v>
-      </c>
-      <c r="G4" s="8">
-        <v>11039.0</v>
-      </c>
-      <c r="H4" s="8">
-        <v>16920.0</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="9"/>
-    </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="6">
-        <v>46205.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="8">
-        <v>75680.0</v>
-      </c>
-      <c r="G5" s="8">
-        <v>5640.0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>3134.0</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="6">
+      <c r="C7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="7">
+        <v>20640.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>3761.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>13920.0</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="8">
-        <v>189540.0</v>
-      </c>
-      <c r="G6" s="8">
-        <v>161685.0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>144720.0</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="6">
-        <v>46206.0</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="8">
-        <v>20640.0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>3761.0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>13920.0</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="6">
-        <v>46206.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="8">
+      <c r="C8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="7">
         <v>152384.0</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>14700.0</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>6435.0</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>9600.0</v>
       </c>
-      <c r="I8" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="12"/>
+      <c r="I8" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="11"/>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="6">
+      <c r="A9" s="4">
         <v>46206.0</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="7">
+        <v>228240.0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>77306.0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>124260.0</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
+      <c r="A10" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="7">
+        <v>7830.0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>1980.0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>6030.0</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="7">
+        <v>31680.0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>5526.0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>23040.0</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
+      <c r="A12" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="7">
+        <v>51387.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>10827.0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>12170.0</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
+      <c r="A13" s="4">
+        <v>46209.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="7">
+        <v>195810.0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>93809.0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>133410.0</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
+      <c r="A14" s="4">
+        <v>46209.0</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="7">
+        <v>526002.0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>301965.0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>424588.0</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="4">
+        <v>46209.0</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="7">
+        <v>14160.0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>6692.0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>12360.0</v>
+      </c>
+      <c r="I15" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="8">
-        <v>228240.0</v>
-      </c>
-      <c r="G9" s="8">
-        <v>77306.0</v>
-      </c>
-      <c r="H9" s="8">
-        <v>124260.0</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="6">
-        <v>46206.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="8">
-        <v>2152388.0</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="8">
-        <v>7830.0</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1980.0</v>
-      </c>
-      <c r="H10" s="8">
-        <v>6030.0</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="6">
-        <v>46206.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="8">
-        <v>31680.0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>5526.0</v>
-      </c>
-      <c r="H11" s="8">
-        <v>23040.0</v>
-      </c>
-      <c r="I11" s="13" t="s">
+      <c r="J15" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
+      <c r="A16" s="4">
+        <v>46210.0</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="6">
-        <v>46206.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="8">
-        <v>51387.0</v>
-      </c>
-      <c r="G12" s="8">
-        <v>10827.0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>12170.0</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="6">
-        <v>46209.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="8">
-        <v>195810.0</v>
-      </c>
-      <c r="G13" s="8">
-        <v>93809.0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>133410.0</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="6">
-        <v>46209.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="8">
-        <v>526002.0</v>
-      </c>
-      <c r="G14" s="8">
-        <v>301965.0</v>
-      </c>
-      <c r="H14" s="8">
-        <v>424588.0</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="6">
-        <v>46209.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="8">
-        <v>14160.0</v>
-      </c>
-      <c r="G15" s="8">
-        <v>6692.0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>12360.0</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="6">
-        <v>46210.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="8">
+      <c r="F16" s="7">
         <v>149040.0</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <v>119573.0</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <v>289680.0</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="12"/>
+      <c r="I16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="11"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="6">
+      <c r="A17" s="4">
         <v>46210.0</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>2110217.0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="8">
+        <v>29</v>
+      </c>
+      <c r="F17" s="7">
         <v>22770.0</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="7">
         <v>3926.0</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <v>19770.0</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="12"/>
+      <c r="I17" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="11"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="6">
+      <c r="A18" s="4">
         <v>46210.0</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="8">
+        <v>34</v>
+      </c>
+      <c r="F18" s="7">
         <v>222021.0</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="7">
         <v>61385.0</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <v>162125.0</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="12"/>
+      <c r="I18" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="11"/>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="6">
+      <c r="A19" s="4">
         <v>46211.0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="8">
+      <c r="C19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="8">
+        <v>11</v>
+      </c>
+      <c r="F19" s="7">
         <v>495833.0</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="7">
         <v>148815.0</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>401280.0</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>72</v>
+      <c r="I19" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="6">
+      <c r="A20" s="4">
         <v>46211.0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="8">
+        <v>20</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="8">
+        <v>11</v>
+      </c>
+      <c r="F20" s="7">
         <v>139920.0</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="7">
         <v>54384.0</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="7">
         <v>74040.0</v>
       </c>
-      <c r="I20" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="12"/>
+      <c r="I20" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="11"/>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="6">
+      <c r="A21" s="4">
         <v>46211.0</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="8">
+        <v>34</v>
+      </c>
+      <c r="F21" s="7">
         <v>162125.0</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="7">
         <v>60138.0</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="7">
         <v>100687.0</v>
       </c>
-      <c r="I21" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>74</v>
+      <c r="I21" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="6">
+      <c r="A22" s="4">
         <v>46211.0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="8">
+        <v>12</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="7">
         <v>152384.0</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="7">
         <v>32850.0</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="7">
         <v>7065.0</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="7">
         <v>32700.0</v>
       </c>
-      <c r="I22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="12"/>
+      <c r="I22" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="11"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="6">
+      <c r="A23" s="4">
         <v>46211.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="8">
+        <v>26</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="7">
         <v>112271.0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" s="8">
+        <v>81</v>
+      </c>
+      <c r="F23" s="7">
         <v>16500.0</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="7">
         <v>5310.0</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="7">
         <v>18000.0</v>
       </c>
-      <c r="I23" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J23" s="12"/>
+      <c r="I23" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" s="11"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="6">
+      <c r="A24" s="4">
         <v>46212.0</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="7">
+        <v>190047.0</v>
+      </c>
+      <c r="G24" s="7">
+        <v>59822.0</v>
+      </c>
+      <c r="H24" s="7">
+        <v>248481.0</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="11"/>
+    </row>
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
+      <c r="A25" s="4">
+        <v>46212.0</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="7">
+        <v>178080.0</v>
+      </c>
+      <c r="G25" s="7">
+        <v>47784.0</v>
+      </c>
+      <c r="H25" s="7">
+        <v>203520.0</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J25" s="11"/>
+    </row>
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
+      <c r="A26" s="4">
+        <v>46212.0</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="7">
+        <v>10320.0</v>
+      </c>
+      <c r="G26" s="7">
+        <v>5869.0</v>
+      </c>
+      <c r="H26" s="7">
+        <v>13200.0</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
+      <c r="A27" s="4">
+        <v>46212.0</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="7">
+        <v>112271.0</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="7">
+        <v>18000.0</v>
+      </c>
+      <c r="G27" s="7">
+        <v>4485.0</v>
+      </c>
+      <c r="H27" s="7">
+        <v>13500.0</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" s="11"/>
+    </row>
+    <row r="28" ht="22.5" hidden="1" customHeight="1">
+      <c r="A28" s="4">
+        <v>46213.0</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="7">
+        <v>208440.0</v>
+      </c>
+      <c r="G28" s="7">
+        <v>85608.0</v>
+      </c>
+      <c r="H28" s="7">
+        <v>150833.0</v>
+      </c>
+      <c r="I28" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="8">
-        <v>190047.0</v>
-      </c>
-      <c r="G24" s="8">
-        <v>59822.0</v>
-      </c>
-      <c r="H24" s="8">
-        <v>248481.0</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J24" s="12"/>
-    </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="6">
-        <v>46212.0</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="J28" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" hidden="1" customHeight="1">
+      <c r="A29" s="4">
+        <v>46213.0</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="7">
+        <v>962820.0</v>
+      </c>
+      <c r="G29" s="7">
+        <v>80644.0</v>
+      </c>
+      <c r="H29" s="7">
+        <v>922140.0</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
+      <c r="A30" s="4">
+        <v>46213.0</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="7">
+        <v>335340.0</v>
+      </c>
+      <c r="G30" s="7">
+        <v>111433.0</v>
+      </c>
+      <c r="H30" s="7">
+        <v>381600.0</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="4">
+        <v>46213.0</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" s="7">
+        <v>316800.0</v>
+      </c>
+      <c r="G31" s="7">
+        <v>99546.0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>229680.0</v>
+      </c>
+      <c r="I31" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="8">
-        <v>178080.0</v>
-      </c>
-      <c r="G25" s="8">
-        <v>47784.0</v>
-      </c>
-      <c r="H25" s="8">
-        <v>203520.0</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J25" s="12"/>
-    </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="6">
-        <v>46212.0</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="8">
-        <v>2110402.0</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="8">
-        <v>10320.0</v>
-      </c>
-      <c r="G26" s="8">
-        <v>5869.0</v>
-      </c>
-      <c r="H26" s="8">
-        <v>13200.0</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="6">
-        <v>46212.0</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="8">
-        <v>112271.0</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="8">
-        <v>18000.0</v>
-      </c>
-      <c r="G27" s="8">
-        <v>4485.0</v>
-      </c>
-      <c r="H27" s="8">
-        <v>13500.0</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="12"/>
-    </row>
-    <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="6">
-        <v>46213.0</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="8">
-        <v>208440.0</v>
-      </c>
-      <c r="G28" s="8">
-        <v>85608.0</v>
-      </c>
-      <c r="H28" s="8">
-        <v>150833.0</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="6">
-        <v>46213.0</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="8">
-        <v>962820.0</v>
-      </c>
-      <c r="G29" s="8">
-        <v>80644.0</v>
-      </c>
-      <c r="H29" s="8">
-        <v>922140.0</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="6">
-        <v>46213.0</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="8">
-        <v>335340.0</v>
-      </c>
-      <c r="G30" s="8">
-        <v>111433.0</v>
-      </c>
-      <c r="H30" s="8">
-        <v>381600.0</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="6">
-        <v>46213.0</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="8">
-        <v>316800.0</v>
-      </c>
-      <c r="G31" s="8">
-        <v>99546.0</v>
-      </c>
-      <c r="H31" s="8">
-        <v>229680.0</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" s="12"/>
+      <c r="J31" s="11"/>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="6">
+      <c r="A32" s="4">
         <v>46213.0</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="8">
+        <v>34</v>
+      </c>
+      <c r="F32" s="7">
         <v>176850.0</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="7">
         <v>47499.0</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="7">
         <v>128971.0</v>
       </c>
-      <c r="I32" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J32" s="12"/>
+      <c r="I32" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J32" s="11"/>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="6">
+      <c r="A33" s="4">
         <v>46213.0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="8">
+        <v>70</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="8">
+        <v>11</v>
+      </c>
+      <c r="F33" s="7">
         <v>58080.0</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="7">
         <v>20865.0</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="7">
         <v>25440.0</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="12"/>
+      <c r="I33" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" s="11"/>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="6">
+      <c r="A34" s="4">
         <v>46217.0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34" s="8">
+        <v>92</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" s="8">
+        <v>34</v>
+      </c>
+      <c r="F34" s="7">
         <v>481440.0</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="7">
         <v>464517.0</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="7">
         <v>151435.0</v>
       </c>
-      <c r="I34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="12"/>
+      <c r="I34" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" s="11"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="6">
+      <c r="A35" s="4">
         <v>46217.0</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="7">
+        <v>355720.0</v>
+      </c>
+      <c r="G35" s="7">
+        <v>342811.0</v>
+      </c>
+      <c r="H35" s="7">
+        <v>302760.0</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="11"/>
+    </row>
+    <row r="36" ht="22.5" hidden="1" customHeight="1">
+      <c r="A36" s="4">
+        <v>46217.0</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="7">
+        <v>35280.0</v>
+      </c>
+      <c r="G36" s="7">
+        <v>16988.0</v>
+      </c>
+      <c r="H36" s="7">
+        <v>37926.0</v>
+      </c>
+      <c r="I36" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="8">
-        <v>355720.0</v>
-      </c>
-      <c r="G35" s="8">
-        <v>342811.0</v>
-      </c>
-      <c r="H35" s="8">
-        <v>302760.0</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="12"/>
-    </row>
-    <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="6">
-        <v>46217.0</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D36" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="8">
-        <v>35280.0</v>
-      </c>
-      <c r="G36" s="8">
-        <v>16988.0</v>
-      </c>
-      <c r="H36" s="8">
-        <v>37926.0</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" s="12" t="s">
+      <c r="J36" s="11" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2007,31 +2016,31 @@
         <v>46218.0</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="8">
+        <v>12</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" s="8">
+        <v>34</v>
+      </c>
+      <c r="F37" s="7">
         <v>272073.0</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="7">
         <v>76546.0</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="7">
         <v>275205.0</v>
       </c>
-      <c r="I37" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>96</v>
+      <c r="I37" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
@@ -2039,30 +2048,30 @@
         <v>46218.0</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" s="8">
+        <v>12</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="8">
+        <v>44</v>
+      </c>
+      <c r="F38" s="7">
         <v>37926.0</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="7">
         <v>5633.0</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="7">
         <v>25746.0</v>
       </c>
-      <c r="I38" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J38" s="12" t="s">
+      <c r="I38" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" s="11" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2071,31 +2080,31 @@
         <v>46218.0</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="8">
+      <c r="C39" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="8">
+        <v>11</v>
+      </c>
+      <c r="F39" s="7">
         <v>20640.0</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="7">
         <v>4951.0</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="7">
         <v>16320.0</v>
       </c>
-      <c r="I39" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>100</v>
+      <c r="I39" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
@@ -2103,1070 +2112,1070 @@
         <v>46218.0</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="7">
+        <v>2110317.0</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F40" s="7">
+        <v>10980.0</v>
+      </c>
+      <c r="G40" s="7">
+        <v>2379.0</v>
+      </c>
+      <c r="H40" s="7">
+        <v>13500.0</v>
+      </c>
+      <c r="I40" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" ht="22.5" hidden="1" customHeight="1">
+      <c r="A41" s="4">
+        <v>46219.0</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D40" s="8">
-        <v>2110317.0</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F40" s="8">
-        <v>10980.0</v>
-      </c>
-      <c r="G40" s="8">
-        <v>2379.0</v>
-      </c>
-      <c r="H40" s="8">
-        <v>13500.0</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J40" s="12"/>
-    </row>
-    <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="6">
-        <v>46219.0</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D41" s="8">
+      <c r="C41" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="8">
+        <v>34</v>
+      </c>
+      <c r="F41" s="7">
         <v>130320.0</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="7">
         <v>47410.0</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="7">
         <v>90480.0</v>
       </c>
-      <c r="I41" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J41" s="12" t="s">
+      <c r="I41" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J41" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="6">
+      <c r="A42" s="4">
         <v>46219.0</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F42" s="8">
+        <v>43</v>
+      </c>
+      <c r="F42" s="7">
         <v>36225.0</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="7">
         <v>11746.0</v>
       </c>
-      <c r="H42" s="8">
+      <c r="H42" s="7">
         <v>27570.0</v>
       </c>
-      <c r="I42" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" s="12"/>
+      <c r="I42" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="11"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="6">
+      <c r="A43" s="4">
         <v>46219.0</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F43" s="8">
+        <v>34</v>
+      </c>
+      <c r="F43" s="7">
         <v>152833.0</v>
       </c>
-      <c r="G43" s="8">
+      <c r="G43" s="7">
         <v>50641.0</v>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="7">
         <v>96472.0</v>
       </c>
-      <c r="I43" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J43" s="12" t="s">
+      <c r="I43" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J43" s="11" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="6">
+      <c r="A44" s="4">
         <v>46219.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="8">
+        <v>92</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F44" s="8">
+        <v>34</v>
+      </c>
+      <c r="F44" s="7">
         <v>237828.0</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="7">
         <v>173585.0</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="7">
         <v>71560.0</v>
       </c>
-      <c r="I44" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" s="12"/>
+      <c r="I44" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="11"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="6">
+      <c r="A45" s="4">
         <v>46219.0</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" s="8">
+        <v>12</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="7">
         <v>152384.0</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="7">
         <v>31125.0</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="7">
         <v>7815.0</v>
       </c>
-      <c r="H45" s="8">
+      <c r="H45" s="7">
         <v>31845.0</v>
       </c>
-      <c r="I45" s="13" t="s">
+      <c r="I45" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" hidden="1" customHeight="1">
+      <c r="A46" s="4">
+        <v>46219.0</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D46" s="7">
+        <v>2010102.0</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F46" s="7">
+        <v>25746.0</v>
+      </c>
+      <c r="G46" s="7">
+        <v>6168.0</v>
+      </c>
+      <c r="H46" s="7">
+        <v>28683.0</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" ht="22.5" hidden="1" customHeight="1">
+      <c r="A47" s="4">
+        <v>46220.0</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J45" s="12" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="6">
-        <v>46219.0</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D46" s="8">
-        <v>2010102.0</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F46" s="8">
-        <v>25746.0</v>
-      </c>
-      <c r="G46" s="8">
-        <v>6168.0</v>
-      </c>
-      <c r="H46" s="8">
-        <v>28683.0</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="6">
+      <c r="F47" s="7">
+        <v>261166.0</v>
+      </c>
+      <c r="G47" s="7">
+        <v>74573.0</v>
+      </c>
+      <c r="H47" s="7">
+        <v>221549.0</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" ht="22.5" hidden="1" customHeight="1">
+      <c r="A48" s="4">
         <v>46220.0</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D47" s="8">
-        <v>2110302.0</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F47" s="8">
-        <v>261166.0</v>
-      </c>
-      <c r="G47" s="8">
-        <v>74573.0</v>
-      </c>
-      <c r="H47" s="8">
-        <v>221549.0</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="6">
-        <v>46220.0</v>
-      </c>
       <c r="B48" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D48" s="8">
+        <v>12</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" s="7">
         <v>2110217.0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F48" s="8">
+        <v>29</v>
+      </c>
+      <c r="F48" s="7">
         <v>115289.0</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="7">
         <v>26931.0</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="7">
         <v>119584.0</v>
       </c>
-      <c r="I48" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J48" s="12"/>
+      <c r="I48" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="11"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="6">
+      <c r="A49" s="4">
         <v>46224.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="8">
+        <v>20</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" s="8">
+        <v>11</v>
+      </c>
+      <c r="F49" s="7">
         <v>398570.0</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="7">
         <v>288226.0</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="7">
         <v>287235.0</v>
       </c>
-      <c r="I49" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J49" s="12" t="s">
+      <c r="I49" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J49" s="11" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="6">
+      <c r="A50" s="4">
         <v>46224.0</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F50" s="8">
+        <v>11</v>
+      </c>
+      <c r="F50" s="7">
         <v>745107.0</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="7">
         <v>378927.0</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="7">
         <v>551645.0</v>
       </c>
-      <c r="I50" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" s="12" t="s">
+      <c r="I50" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="11" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="6">
+      <c r="A51" s="4">
         <v>46225.0</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" s="8">
+        <v>26</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F51" s="8">
+        <v>34</v>
+      </c>
+      <c r="F51" s="7">
         <v>130560.0</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="7">
         <v>52658.0</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="7">
         <v>153840.0</v>
       </c>
-      <c r="I51" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J51" s="12" t="s">
+      <c r="I51" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" s="11" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="6">
+      <c r="A52" s="4">
         <v>46225.0</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F52" s="8">
+        <v>34</v>
+      </c>
+      <c r="F52" s="7">
         <v>87447.0</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="7">
         <v>59056.0</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="7">
         <v>104365.0</v>
       </c>
-      <c r="I52" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J52" s="12"/>
+      <c r="I52" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" s="11"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="6">
+      <c r="A53" s="4">
         <v>46225.0</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D53" s="8">
+        <v>12</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D53" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" s="8">
+        <v>11</v>
+      </c>
+      <c r="F53" s="7">
         <v>25200.0</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="7">
         <v>2085.0</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="7">
         <v>25920.0</v>
       </c>
-      <c r="I53" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J53" s="12" t="s">
+      <c r="I53" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J53" s="11" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
-      <c r="A54" s="6">
+      <c r="A54" s="4">
         <v>46226.0</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C54" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="8">
+        <v>11</v>
+      </c>
+      <c r="F54" s="7">
         <v>285405.0</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="7">
         <v>203180.0</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="7">
         <v>226069.0</v>
       </c>
-      <c r="I54" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J54" s="12" t="s">
+      <c r="I54" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J54" s="11" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
-      <c r="A55" s="6">
+      <c r="A55" s="4">
         <v>46226.0</v>
       </c>
       <c r="B55" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" s="7">
+        <v>692280.0</v>
+      </c>
+      <c r="G55" s="7">
+        <v>118381.0</v>
+      </c>
+      <c r="H55" s="7">
+        <v>700200.0</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J55" s="11"/>
+    </row>
+    <row r="56" ht="22.5" hidden="1" customHeight="1">
+      <c r="A56" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" s="7">
+        <v>700200.0</v>
+      </c>
+      <c r="G56" s="7">
+        <v>112628.0</v>
+      </c>
+      <c r="H56" s="7">
+        <v>668440.0</v>
+      </c>
+      <c r="I56" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="8">
-        <v>692280.0</v>
-      </c>
-      <c r="G55" s="8">
-        <v>118381.0</v>
-      </c>
-      <c r="H55" s="8">
-        <v>700200.0</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J55" s="12"/>
-    </row>
-    <row r="56" ht="22.5" hidden="1" customHeight="1">
-      <c r="A56" s="6">
+      <c r="J56" s="11"/>
+    </row>
+    <row r="57" ht="22.5" hidden="1" customHeight="1">
+      <c r="A57" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D56" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="8">
-        <v>700200.0</v>
-      </c>
-      <c r="G56" s="8">
-        <v>112628.0</v>
-      </c>
-      <c r="H56" s="8">
-        <v>668440.0</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J56" s="12"/>
-    </row>
-    <row r="57" ht="22.5" hidden="1" customHeight="1">
-      <c r="A57" s="6">
-        <v>46227.0</v>
-      </c>
       <c r="B57" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C57" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F57" s="8">
+        <v>11</v>
+      </c>
+      <c r="F57" s="7">
         <v>226069.0</v>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="7">
         <v>193130.0</v>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="7">
         <v>326391.0</v>
       </c>
-      <c r="I57" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J57" s="12" t="s">
+      <c r="I57" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J57" s="11" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
-      <c r="A58" s="6">
+      <c r="A58" s="4">
         <v>46227.0</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="8">
+        <v>16</v>
+      </c>
+      <c r="F58" s="7">
         <v>144637.0</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G58" s="7">
         <v>64227.0</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="7">
         <v>128160.0</v>
       </c>
-      <c r="I58" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J58" s="12"/>
+      <c r="I58" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J58" s="11"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="6">
+      <c r="A59" s="4">
         <v>46227.0</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F59" s="8">
+        <v>11</v>
+      </c>
+      <c r="F59" s="7">
         <v>295359.0</v>
       </c>
-      <c r="G59" s="8">
+      <c r="G59" s="7">
         <v>126369.0</v>
       </c>
-      <c r="H59" s="8">
+      <c r="H59" s="7">
         <v>166642.0</v>
       </c>
-      <c r="I59" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" s="12" t="s">
+      <c r="I59" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="11" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="6">
+      <c r="A60" s="4">
         <v>46230.0</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="7">
         <v>2110403.0</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="7">
         <v>9960.0</v>
       </c>
-      <c r="G60" s="8">
+      <c r="G60" s="7">
         <v>6018.0</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="7">
         <v>3660.0</v>
       </c>
-      <c r="I60" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J60" s="12"/>
+      <c r="I60" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J60" s="11"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="6">
+      <c r="A61" s="4">
         <v>46230.0</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D61" s="8">
+        <v>12</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F61" s="8">
+        <v>34</v>
+      </c>
+      <c r="F61" s="7">
         <v>306720.0</v>
       </c>
-      <c r="G61" s="8">
+      <c r="G61" s="7">
         <v>164175.0</v>
       </c>
-      <c r="H61" s="8">
+      <c r="H61" s="7">
         <v>247096.0</v>
       </c>
-      <c r="I61" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61" s="12"/>
+      <c r="I61" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J61" s="11"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
-      <c r="A62" s="6">
+      <c r="A62" s="4">
         <v>46230.0</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C62" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D62" s="8">
+      <c r="C62" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="8">
+        <v>16</v>
+      </c>
+      <c r="F62" s="7">
         <v>437080.0</v>
       </c>
-      <c r="G62" s="8">
+      <c r="G62" s="7">
         <v>277785.0</v>
       </c>
-      <c r="H62" s="8">
+      <c r="H62" s="7">
         <v>353700.0</v>
       </c>
-      <c r="I62" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J62" s="12" t="s">
+      <c r="I62" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J62" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
-      <c r="A63" s="6">
+      <c r="A63" s="4">
         <v>46231.0</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D63" s="8">
+        <v>20</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" s="8">
+        <v>11</v>
+      </c>
+      <c r="F63" s="7">
         <v>165466.0</v>
       </c>
-      <c r="G63" s="8">
+      <c r="G63" s="7">
         <v>113462.0</v>
       </c>
-      <c r="H63" s="8">
+      <c r="H63" s="7">
         <v>375549.0</v>
       </c>
-      <c r="I63" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J63" s="12" t="s">
+      <c r="I63" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J63" s="11" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
-      <c r="A64" s="6">
+      <c r="A64" s="4">
         <v>46231.0</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F64" s="8">
+        <v>34</v>
+      </c>
+      <c r="F64" s="7">
         <v>238497.0</v>
       </c>
-      <c r="G64" s="8">
+      <c r="G64" s="7">
         <v>56526.0</v>
       </c>
-      <c r="H64" s="8">
+      <c r="H64" s="7">
         <v>181858.0</v>
       </c>
-      <c r="I64" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J64" s="12" t="s">
+      <c r="I64" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J64" s="11" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
-      <c r="A65" s="6">
+      <c r="A65" s="4">
         <v>46231.0</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F65" s="8">
+        <v>72</v>
+      </c>
+      <c r="F65" s="7">
         <v>8190.0</v>
       </c>
-      <c r="G65" s="8">
+      <c r="G65" s="7">
         <v>2049.0</v>
       </c>
-      <c r="H65" s="8">
+      <c r="H65" s="7">
         <v>7200.0</v>
       </c>
-      <c r="I65" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J65" s="12" t="s">
+      <c r="I65" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J65" s="11" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
-      <c r="A66" s="6">
+      <c r="A66" s="4">
         <v>46231.0</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="8">
+        <v>16</v>
+      </c>
+      <c r="F66" s="7">
         <v>146224.0</v>
       </c>
-      <c r="G66" s="8">
+      <c r="G66" s="7">
         <v>78064.0</v>
       </c>
-      <c r="H66" s="8">
+      <c r="H66" s="7">
         <v>98850.0</v>
       </c>
-      <c r="I66" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J66" s="12" t="s">
+      <c r="I66" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J66" s="11" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
-      <c r="A67" s="6">
+      <c r="A67" s="4">
         <v>46232.0</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>120</v>
       </c>
       <c r="C67" s="21"/>
-      <c r="D67" s="8">
+      <c r="D67" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E67" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67" s="7">
+        <v>14599.0</v>
+      </c>
+      <c r="G67" s="7">
+        <v>3782.0</v>
+      </c>
+      <c r="H67" s="7">
+        <v>7263.0</v>
+      </c>
+      <c r="I67" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F67" s="8">
-        <v>14599.0</v>
-      </c>
-      <c r="G67" s="8">
-        <v>3782.0</v>
-      </c>
-      <c r="H67" s="8">
-        <v>7263.0</v>
-      </c>
-      <c r="I67" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J67" s="12"/>
+      <c r="J67" s="11"/>
     </row>
     <row r="68" ht="22.5" hidden="1" customHeight="1">
-      <c r="A68" s="6">
+      <c r="A68" s="4">
         <v>46232.0</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C68" s="21"/>
-      <c r="D68" s="8">
+      <c r="D68" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F68" s="8">
+        <v>11</v>
+      </c>
+      <c r="F68" s="7">
         <v>22080.0</v>
       </c>
-      <c r="G68" s="8">
+      <c r="G68" s="7">
         <v>5686.0</v>
       </c>
-      <c r="H68" s="8">
+      <c r="H68" s="7">
         <v>36720.0</v>
       </c>
-      <c r="I68" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J68" s="12"/>
+      <c r="I68" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="11"/>
     </row>
     <row r="69" ht="22.5" hidden="1" customHeight="1">
-      <c r="A69" s="6">
+      <c r="A69" s="4">
         <v>46232.0</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C69" s="21"/>
-      <c r="D69" s="8">
+      <c r="D69" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F69" s="8">
+        <v>11</v>
+      </c>
+      <c r="F69" s="7">
         <v>353905.0</v>
       </c>
-      <c r="G69" s="8">
+      <c r="G69" s="7">
         <v>208296.0</v>
       </c>
-      <c r="H69" s="8">
+      <c r="H69" s="7">
         <v>117570.0</v>
       </c>
-      <c r="I69" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J69" s="12"/>
+      <c r="I69" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="11"/>
     </row>
     <row r="70" ht="22.5" hidden="1" customHeight="1">
-      <c r="A70" s="6">
+      <c r="A70" s="4">
         <v>46232.0</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C70" s="21"/>
-      <c r="D70" s="8">
+      <c r="D70" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F70" s="8">
+        <v>44</v>
+      </c>
+      <c r="F70" s="7">
         <v>5913.0</v>
       </c>
-      <c r="G70" s="8">
+      <c r="G70" s="7">
         <v>902.0</v>
       </c>
-      <c r="H70" s="8">
+      <c r="H70" s="7">
         <v>5893.0</v>
       </c>
-      <c r="I70" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J70" s="12"/>
+      <c r="I70" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="11"/>
     </row>
     <row r="71" ht="22.5" hidden="1" customHeight="1">
-      <c r="A71" s="6">
+      <c r="A71" s="4">
         <v>46232.0</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C71" s="21"/>
-      <c r="D71" s="8">
+      <c r="D71" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F71" s="8">
+        <v>34</v>
+      </c>
+      <c r="F71" s="7">
         <v>256613.0</v>
       </c>
-      <c r="G71" s="8">
+      <c r="G71" s="7">
         <v>86092.0</v>
       </c>
-      <c r="H71" s="8">
+      <c r="H71" s="7">
         <v>142320.0</v>
       </c>
-      <c r="I71" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J71" s="12"/>
+      <c r="I71" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="11"/>
     </row>
     <row r="72" ht="22.5" hidden="1" customHeight="1">
-      <c r="A72" s="6">
+      <c r="A72" s="4">
         <v>46232.0</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C72" s="21"/>
-      <c r="D72" s="8">
+      <c r="D72" s="7">
         <v>152384.0</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="7">
         <v>21300.0</v>
       </c>
-      <c r="G72" s="8">
+      <c r="G72" s="7">
         <v>9765.0</v>
       </c>
-      <c r="H72" s="8">
+      <c r="H72" s="7">
         <v>18690.0</v>
       </c>
-      <c r="I72" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" s="12"/>
+      <c r="I72" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="11"/>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
-      <c r="A73" s="6">
+      <c r="A73" s="4">
         <v>46232.0</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>103</v>
       </c>
       <c r="C73" s="21"/>
-      <c r="D73" s="8">
+      <c r="D73" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="8">
+        <v>11</v>
+      </c>
+      <c r="F73" s="7">
         <v>351733.0</v>
       </c>
-      <c r="G73" s="8">
+      <c r="G73" s="7">
         <v>145994.0</v>
       </c>
-      <c r="H73" s="8">
+      <c r="H73" s="7">
         <v>200114.0</v>
       </c>
-      <c r="I73" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" s="12"/>
+      <c r="I73" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="11"/>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
       <c r="A74" s="19">
         <v>46233.0</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C74" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D74" s="8">
+      <c r="C74" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D74" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F74" s="8">
+        <v>34</v>
+      </c>
+      <c r="F74" s="7">
         <v>158761.0</v>
       </c>
-      <c r="G74" s="8">
+      <c r="G74" s="7">
         <v>68908.0</v>
       </c>
-      <c r="H74" s="8">
+      <c r="H74" s="7">
         <v>183014.0</v>
       </c>
-      <c r="I74" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J74" s="12" t="s">
+      <c r="I74" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J74" s="11" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3177,120 +3186,120 @@
       <c r="B75" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C75" s="16" t="s">
+      <c r="C75" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F75" s="8">
+        <v>34</v>
+      </c>
+      <c r="F75" s="7">
         <v>117430.0</v>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="7">
         <v>57323.0</v>
       </c>
-      <c r="H75" s="8">
+      <c r="H75" s="7">
         <v>86643.0</v>
       </c>
-      <c r="I75" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J75" s="12"/>
+      <c r="I75" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J75" s="11"/>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
-      <c r="A76" s="6">
+      <c r="A76" s="4">
         <v>46234.0</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D76" s="8">
+        <v>12</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D76" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F76" s="8">
+        <v>34</v>
+      </c>
+      <c r="F76" s="7">
         <v>265693.0</v>
       </c>
-      <c r="G76" s="8">
+      <c r="G76" s="7">
         <v>83477.0</v>
       </c>
-      <c r="H76" s="8">
+      <c r="H76" s="7">
         <v>116000.0</v>
       </c>
-      <c r="I76" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J76" s="12"/>
+      <c r="I76" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" s="11"/>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
-      <c r="A77" s="6">
+      <c r="A77" s="4">
         <v>46234.0</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="7">
         <v>112357.0</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F77" s="8">
+        <v>82</v>
+      </c>
+      <c r="F77" s="7">
         <v>720.0</v>
       </c>
-      <c r="G77" s="8">
+      <c r="G77" s="7">
         <v>360.0</v>
       </c>
-      <c r="H77" s="8">
+      <c r="H77" s="7">
         <v>2040.0</v>
       </c>
-      <c r="I77" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J77" s="12" t="s">
+      <c r="I77" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="11" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
-      <c r="A78" s="6">
+      <c r="A78" s="4">
         <v>46234.0</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F78" s="8">
+        <v>72</v>
+      </c>
+      <c r="F78" s="7">
         <v>5580.0</v>
       </c>
-      <c r="G78" s="8">
+      <c r="G78" s="7">
         <v>2192.0</v>
       </c>
-      <c r="H78" s="8">
+      <c r="H78" s="7">
         <v>3984.0</v>
       </c>
-      <c r="I78" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J78" s="12" t="s">
+      <c r="I78" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J78" s="11" t="s">
         <v>125</v>
       </c>
     </row>
@@ -3301,28 +3310,28 @@
       <c r="B79" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="8">
+        <v>16</v>
+      </c>
+      <c r="F79" s="7">
         <v>192903.0</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="7">
         <v>150030.0</v>
       </c>
-      <c r="H79" s="8">
+      <c r="H79" s="7">
         <v>77501.0</v>
       </c>
-      <c r="I79" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J79" s="12" t="s">
+      <c r="I79" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J79" s="11" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3333,28 +3342,28 @@
       <c r="B80" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F80" s="8">
+        <v>34</v>
+      </c>
+      <c r="F80" s="7">
         <v>152062.0</v>
       </c>
-      <c r="G80" s="8">
+      <c r="G80" s="7">
         <v>112769.0</v>
       </c>
-      <c r="H80" s="8">
+      <c r="H80" s="7">
         <v>124423.0</v>
       </c>
-      <c r="I80" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J80" s="12" t="s">
+      <c r="I80" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J80" s="11" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3363,30 +3372,30 @@
         <v>46237.0</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C81" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C81" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F81" s="8">
+        <v>34</v>
+      </c>
+      <c r="F81" s="7">
         <v>153692.0</v>
       </c>
-      <c r="G81" s="8">
+      <c r="G81" s="7">
         <v>136980.0</v>
       </c>
-      <c r="H81" s="8">
+      <c r="H81" s="7">
         <v>63920.0</v>
       </c>
-      <c r="I81" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="J81" s="12" t="s">
+      <c r="I81" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J81" s="11" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3395,244 +3404,244 @@
         <v>46237.0</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C82" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F82" s="8">
+        <v>11</v>
+      </c>
+      <c r="F82" s="7">
         <v>45564.0</v>
       </c>
-      <c r="G82" s="8">
+      <c r="G82" s="7">
         <v>10456.0</v>
       </c>
-      <c r="H82" s="8">
+      <c r="H82" s="7">
         <v>40560.0</v>
       </c>
-      <c r="I82" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J82" s="12"/>
+      <c r="I82" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="11"/>
     </row>
     <row r="83" ht="22.5" hidden="1" customHeight="1">
       <c r="A83" s="18">
         <v>46237.0</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D83" s="8">
+        <v>20</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F83" s="8">
+        <v>34</v>
+      </c>
+      <c r="F83" s="7">
         <v>93517.0</v>
       </c>
-      <c r="G83" s="8">
+      <c r="G83" s="7">
         <v>18622.0</v>
       </c>
-      <c r="H83" s="8">
+      <c r="H83" s="7">
         <v>48804.0</v>
       </c>
-      <c r="I83" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J83" s="12" t="s">
+      <c r="I83" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J83" s="11" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
-      <c r="A84" s="6">
+      <c r="A84" s="4">
         <v>46238.0</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D84" s="8">
+        <v>12</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D84" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F84" s="8">
+        <v>72</v>
+      </c>
+      <c r="F84" s="7">
         <v>43200.0</v>
       </c>
-      <c r="G84" s="8">
+      <c r="G84" s="7">
         <v>5340.0</v>
       </c>
-      <c r="H84" s="8">
+      <c r="H84" s="7">
         <v>40890.0</v>
       </c>
-      <c r="I84" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J84" s="12"/>
+      <c r="I84" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" s="11"/>
     </row>
     <row r="85" ht="22.5" customHeight="1">
-      <c r="A85" s="6">
+      <c r="A85" s="4">
         <v>46238.0</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D85" s="8">
+        <v>12</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D85" s="7">
         <v>152384.0</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F85" s="8">
+      <c r="F85" s="7">
         <v>25350.0</v>
       </c>
-      <c r="G85" s="8">
+      <c r="G85" s="7">
         <v>6240.0</v>
       </c>
-      <c r="H85" s="8">
+      <c r="H85" s="7">
         <v>30750.0</v>
       </c>
-      <c r="I85" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J85" s="12"/>
+      <c r="I85" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J85" s="11"/>
     </row>
     <row r="86" ht="22.5" customHeight="1">
-      <c r="A86" s="6">
+      <c r="A86" s="4">
         <v>46238.0</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D86" s="8">
+        <v>12</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D86" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F86" s="8">
+        <v>43</v>
+      </c>
+      <c r="F86" s="7">
         <v>5040.0</v>
       </c>
-      <c r="G86" s="8">
+      <c r="G86" s="7">
         <v>720.0</v>
       </c>
-      <c r="H86" s="8">
+      <c r="H86" s="7">
         <v>4680.0</v>
       </c>
-      <c r="I86" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J86" s="12"/>
+      <c r="I86" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J86" s="11"/>
     </row>
     <row r="87" ht="22.5" customHeight="1">
-      <c r="A87" s="6">
+      <c r="A87" s="4">
         <v>46238.0</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F87" s="8">
+        <v>34</v>
+      </c>
+      <c r="F87" s="7">
         <v>124423.0</v>
       </c>
-      <c r="G87" s="8">
+      <c r="G87" s="7">
         <v>60002.0</v>
       </c>
-      <c r="H87" s="8">
+      <c r="H87" s="7">
         <v>69217.0</v>
       </c>
-      <c r="I87" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J87" s="12" t="s">
+      <c r="I87" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J87" s="11" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
-      <c r="A88" s="6">
+      <c r="A88" s="4">
         <v>46239.0</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D88" s="8">
+        <v>12</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D88" s="7">
         <v>152384.0</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F88" s="8">
+      <c r="F88" s="7">
         <v>30750.0</v>
       </c>
-      <c r="G88" s="8">
+      <c r="G88" s="7">
         <v>9975.0</v>
       </c>
-      <c r="H88" s="8">
+      <c r="H88" s="7">
         <v>36300.0</v>
       </c>
-      <c r="I88" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J88" s="12"/>
+      <c r="I88" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" s="11"/>
     </row>
     <row r="89" ht="22.5" customHeight="1">
-      <c r="A89" s="6">
+      <c r="A89" s="4">
         <v>46239.0</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C89" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D89" s="8">
+      <c r="C89" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D89" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F89" s="8">
+        <v>34</v>
+      </c>
+      <c r="F89" s="7">
         <v>58320.0</v>
       </c>
-      <c r="G89" s="8">
+      <c r="G89" s="7">
         <v>53468.0</v>
       </c>
-      <c r="H89" s="8">
+      <c r="H89" s="7">
         <v>12480.0</v>
       </c>
-      <c r="I89" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J89" s="12" t="s">
+      <c r="I89" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J89" s="11" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3641,30 +3650,30 @@
         <v>46240.0</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C90" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D90" s="8">
+      <c r="C90" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D90" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E90" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F90" s="7">
+        <v>254880.0</v>
+      </c>
+      <c r="G90" s="7">
+        <v>151786.0</v>
+      </c>
+      <c r="H90" s="7">
+        <v>27180.0</v>
+      </c>
+      <c r="I90" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F90" s="8">
-        <v>254880.0</v>
-      </c>
-      <c r="G90" s="8">
-        <v>151786.0</v>
-      </c>
-      <c r="H90" s="8">
-        <v>27180.0</v>
-      </c>
-      <c r="I90" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J90" s="12" t="s">
+      <c r="J90" s="11" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3673,30 +3682,30 @@
         <v>46240.0</v>
       </c>
       <c r="B91" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D91" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C91" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D91" s="8">
-        <v>112379.0</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F91" s="8">
+      <c r="F91" s="7">
         <v>13800.0</v>
       </c>
-      <c r="G91" s="8">
+      <c r="G91" s="7">
         <v>900.0</v>
       </c>
-      <c r="H91" s="8">
+      <c r="H91" s="7">
         <v>12132.0</v>
       </c>
-      <c r="I91" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J91" s="12"/>
+      <c r="I91" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J91" s="11"/>
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="18">
@@ -3705,28 +3714,28 @@
       <c r="B92" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F92" s="8">
+        <v>43</v>
+      </c>
+      <c r="F92" s="7">
         <v>4575.0</v>
       </c>
-      <c r="G92" s="8">
+      <c r="G92" s="7">
         <v>570.0</v>
       </c>
-      <c r="H92" s="8">
+      <c r="H92" s="7">
         <v>4213.0</v>
       </c>
-      <c r="I92" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J92" s="12" t="s">
+      <c r="I92" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J92" s="11" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3735,30 +3744,30 @@
         <v>46244.0</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C93" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D93" s="8">
+      <c r="C93" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D93" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F93" s="8">
+        <v>34</v>
+      </c>
+      <c r="F93" s="7">
         <v>222000.0</v>
       </c>
-      <c r="G93" s="8">
+      <c r="G93" s="7">
         <v>142780.0</v>
       </c>
-      <c r="H93" s="8">
+      <c r="H93" s="7">
         <v>312480.0</v>
       </c>
-      <c r="I93" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J93" s="12" t="s">
+      <c r="I93" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J93" s="11" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3767,30 +3776,30 @@
         <v>46244.0</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C94" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D94" s="8">
+      <c r="C94" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D94" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="8">
+        <v>16</v>
+      </c>
+      <c r="F94" s="7">
         <v>300060.0</v>
       </c>
-      <c r="G94" s="8">
+      <c r="G94" s="7">
         <v>265744.0</v>
       </c>
-      <c r="H94" s="8">
+      <c r="H94" s="7">
         <v>260696.0</v>
       </c>
-      <c r="I94" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J94" s="12" t="s">
+      <c r="I94" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J94" s="11" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3799,30 +3808,30 @@
         <v>46244.0</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C95" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D95" s="8">
+      <c r="C95" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D95" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F95" s="8">
+        <v>11</v>
+      </c>
+      <c r="F95" s="7">
         <v>36240.0</v>
       </c>
-      <c r="G95" s="8">
+      <c r="G95" s="7">
         <v>10696.0</v>
       </c>
-      <c r="H95" s="8">
+      <c r="H95" s="7">
         <v>39840.0</v>
       </c>
-      <c r="I95" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J95" s="12" t="s">
+      <c r="I95" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J95" s="11" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3831,42 +3840,156 @@
         <v>46244.0</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D96" s="8">
+        <v>12</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D96" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F96" s="8">
+        <v>72</v>
+      </c>
+      <c r="F96" s="7">
         <v>21690.0</v>
       </c>
-      <c r="G96" s="8">
+      <c r="G96" s="7">
         <v>13530.0</v>
       </c>
-      <c r="H96" s="8">
+      <c r="H96" s="7">
         <v>26280.0</v>
       </c>
-      <c r="I96" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J96" s="12"/>
-    </row>
-    <row r="97">
-      <c r="I97" s="20"/>
-    </row>
-    <row r="98">
-      <c r="I98" s="20"/>
-    </row>
-    <row r="99">
-      <c r="I99" s="20"/>
-    </row>
-    <row r="100">
-      <c r="I100" s="20"/>
+      <c r="I96" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" s="11"/>
+    </row>
+    <row r="97" ht="22.5" customHeight="1">
+      <c r="A97" s="4">
+        <v>46245.0</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97" s="7">
+        <v>112271.0</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F97" s="7">
+        <v>20100.0</v>
+      </c>
+      <c r="G97" s="7">
+        <v>6795.0</v>
+      </c>
+      <c r="H97" s="7">
+        <v>10800.0</v>
+      </c>
+      <c r="I97" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J97" s="11"/>
+    </row>
+    <row r="98" ht="22.5" customHeight="1">
+      <c r="A98" s="4">
+        <v>46245.0</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D98" s="7">
+        <v>2110402.0</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" s="7">
+        <v>39840.0</v>
+      </c>
+      <c r="G98" s="7">
+        <v>5352.0</v>
+      </c>
+      <c r="H98" s="7">
+        <v>23520.0</v>
+      </c>
+      <c r="I98" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="99" ht="22.5" customHeight="1">
+      <c r="A99" s="4">
+        <v>46245.0</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D99" s="7">
+        <v>152384.0</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F99" s="7">
+        <v>18600.0</v>
+      </c>
+      <c r="G99" s="7">
+        <v>5550.0</v>
+      </c>
+      <c r="H99" s="7">
+        <v>12900.0</v>
+      </c>
+      <c r="I99" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J99" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="100" ht="22.5" customHeight="1">
+      <c r="A100" s="4">
+        <v>46245.0</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D100" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F100" s="7">
+        <v>225620.0</v>
+      </c>
+      <c r="G100" s="7">
+        <v>74165.0</v>
+      </c>
+      <c r="H100" s="7">
+        <v>269040.0</v>
+      </c>
+      <c r="I100" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="11" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="101">
       <c r="I101" s="20"/>
@@ -6591,13 +6714,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I96">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I100">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I97:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I101:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A96">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A100">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -6660,1023 +6783,1023 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="6">
+      <c r="A2" s="4">
         <v>46224.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="8">
+        <v>10</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="8">
+        <v>11</v>
+      </c>
+      <c r="F2" s="7">
         <v>333.0</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>6480.0</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <v>3712.0</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>17</v>
+      <c r="I2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>46224.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="8">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7">
         <v>2114158.0</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="7">
+        <v>60.0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>1000.0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>60.0</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="8">
-        <v>60.0</v>
-      </c>
-      <c r="G3" s="8">
-        <v>1000.0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>60.0</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
+      <c r="A4" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="7">
+        <v>10501.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="6">
+      <c r="F4" s="7">
+        <v>415093.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>115920.0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>543038.0</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
+      <c r="A5" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="8">
-        <v>10501.0</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="8">
-        <v>415093.0</v>
-      </c>
-      <c r="G4" s="8">
-        <v>115920.0</v>
-      </c>
-      <c r="H4" s="8">
-        <v>543038.0</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="6">
+      <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>29400.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3000.0</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
+      <c r="A6" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="8">
-        <v>112379.0</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="8">
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="7">
         <v>3000.0</v>
       </c>
-      <c r="G5" s="8">
-        <v>29400.0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>3000.0</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="6">
+      <c r="G6" s="7">
+        <v>12300.0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="8">
-        <v>3000.0</v>
-      </c>
-      <c r="G6" s="8">
-        <v>12300.0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>3300.0</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="6">
+      <c r="B7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="7">
+        <v>132357.0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1560.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1560.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>4560.0</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
+      <c r="A8" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="8">
-        <v>132357.0</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1560.0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1560.0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>4560.0</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="12" t="s">
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="6">
+      <c r="F8" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>11160.0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>5940.0</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
+      <c r="A9" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="8">
-        <v>2152388.0</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="8">
-        <v>720.0</v>
-      </c>
-      <c r="G8" s="8">
-        <v>11160.0</v>
-      </c>
-      <c r="H8" s="8">
-        <v>5940.0</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="6">
-        <v>46225.0</v>
-      </c>
       <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="8">
+        <v>10</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="8">
+        <v>11</v>
+      </c>
+      <c r="F9" s="7">
         <v>3712.0</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>46723.0</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <v>213.0</v>
       </c>
-      <c r="I9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>49</v>
+      <c r="I9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="6">
+      <c r="A10" s="4">
         <v>46226.0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="8">
+        <v>18</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="7">
         <v>73001.0</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>73787.0</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>72000.0</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <v>109487.0</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="G11" s="7">
+        <v>1800.0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>3300.0</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
+      <c r="A12" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="7">
+        <v>4200.0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>7500.0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>3900.0</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
+      <c r="A13" s="4">
+        <v>46226.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="F13" s="7">
+        <v>379471.0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>392580.0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>357186.0</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="6">
-        <v>46226.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="8">
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
+      <c r="A14" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="7">
+        <v>72001.0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="7">
+        <v>21905.0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>47670.0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>38000.0</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="7">
+        <v>2110327.0</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="7">
+        <v>69120.0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>57600.0</v>
+      </c>
+      <c r="H15" s="7">
+        <v>40320.0</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
+      <c r="A16" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="7">
+        <v>112379.0</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="7">
+        <v>3900.0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>102600.0</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1500.0</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" ht="22.5" hidden="1" customHeight="1">
+      <c r="A17" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="13"/>
+      <c r="D17" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>9720.0</v>
+      </c>
+      <c r="H17" s="7">
+        <v>2580.0</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" ht="22.5" hidden="1" customHeight="1">
+      <c r="A18" s="4">
+        <v>46227.0</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="7">
         <v>112268.0</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="8">
+      <c r="E18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="7">
         <v>3300.0</v>
       </c>
-      <c r="G11" s="8">
-        <v>1800.0</v>
-      </c>
-      <c r="H11" s="8">
+      <c r="G18" s="7">
+        <v>30600.0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>600.0</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
+      <c r="A19" s="4">
+        <v>46230.0</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="7">
+        <v>2410401.0</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="7">
+        <v>136538.0</v>
+      </c>
+      <c r="G19" s="7">
+        <v>34080.0</v>
+      </c>
+      <c r="H19" s="7">
+        <v>213000.0</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
+      <c r="A20" s="4">
+        <v>46231.0</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="7">
+        <v>2110202.0</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="7">
+        <v>591750.0</v>
+      </c>
+      <c r="G20" s="7">
+        <v>239760.0</v>
+      </c>
+      <c r="H20" s="7">
+        <v>577207.0</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
+      <c r="A21" s="4">
+        <v>46231.0</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="7">
+        <v>10601.0</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1230.0</v>
+      </c>
+      <c r="G21" s="7">
+        <v>8626.0</v>
+      </c>
+      <c r="H21" s="7">
+        <v>1958.0</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" hidden="1" customHeight="1">
+      <c r="A22" s="4">
+        <v>46231.0</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="7">
+        <v>2152388.0</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="7">
+        <v>4320.0</v>
+      </c>
+      <c r="G22" s="7">
+        <v>2700.0</v>
+      </c>
+      <c r="H22" s="7">
+        <v>3420.0</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" ht="22.5" hidden="1" customHeight="1">
+      <c r="A23" s="4">
+        <v>46231.0</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="7">
+        <v>114357.0</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="7">
+        <v>240.0</v>
+      </c>
+      <c r="G23" s="7">
+        <v>52320.0</v>
+      </c>
+      <c r="H23" s="7">
+        <v>240.0</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="11"/>
+    </row>
+    <row r="24" ht="22.5" hidden="1" customHeight="1">
+      <c r="A24" s="4">
+        <v>46232.0</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="7">
+        <v>10501.0</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="7">
+        <v>19663.0</v>
+      </c>
+      <c r="G24" s="7">
+        <v>49540.0</v>
+      </c>
+      <c r="H24" s="7">
+        <v>29632.0</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="11"/>
+    </row>
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
+      <c r="A25" s="4">
+        <v>46232.0</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="7">
+        <v>5700.0</v>
+      </c>
+      <c r="G25" s="7">
+        <v>34800.0</v>
+      </c>
+      <c r="H25" s="7">
+        <v>5100.0</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="11"/>
+    </row>
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
+      <c r="A26" s="4">
+        <v>46232.0</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="7">
+        <v>2110317.0</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="G26" s="7">
+        <v>7920.0</v>
+      </c>
+      <c r="H26" s="7">
+        <v>720.0</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="11"/>
+    </row>
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
+      <c r="A27" s="4">
+        <v>46232.0</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="7">
+        <v>2114357.0</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="7">
+        <v>432.0</v>
+      </c>
+      <c r="G27" s="7">
+        <v>576.0</v>
+      </c>
+      <c r="H27" s="7">
+        <v>432.0</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="11"/>
+    </row>
+    <row r="28" ht="22.5" hidden="1" customHeight="1">
+      <c r="A28" s="4">
+        <v>46232.0</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="7">
+        <v>10501.0</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="7">
+        <v>219540.0</v>
+      </c>
+      <c r="G28" s="7">
+        <v>272160.0</v>
+      </c>
+      <c r="H28" s="7">
+        <v>16698.0</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="11"/>
+    </row>
+    <row r="29" ht="22.5" hidden="1" customHeight="1">
+      <c r="A29" s="4">
+        <v>46233.0</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="7">
+        <v>112268.0</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F29" s="7">
+        <v>5100.0</v>
+      </c>
+      <c r="G29" s="7">
         <v>3300.0</v>
       </c>
-      <c r="I11" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="12"/>
-    </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="6">
-        <v>46226.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="8">
-        <v>112379.0</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="8">
-        <v>4200.0</v>
-      </c>
-      <c r="G12" s="8">
-        <v>7500.0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>3900.0</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="6">
-        <v>46226.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="H29" s="7">
+        <v>4800.0</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" s="11"/>
+    </row>
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
+      <c r="A30" s="4">
+        <v>46233.0</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="7">
+        <v>114357.0</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="7">
+        <v>240.0</v>
+      </c>
+      <c r="G30" s="7">
+        <v>7800.0</v>
+      </c>
+      <c r="H30" s="7">
+        <v>1560.0</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J30" s="11"/>
+    </row>
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
+      <c r="A31" s="4">
+        <v>46233.0</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="7">
+        <v>10601.0</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="7">
+        <v>7717.0</v>
+      </c>
+      <c r="G31" s="7">
+        <v>10080.0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>12867.0</v>
+      </c>
+      <c r="I31" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="8">
-        <v>379471.0</v>
-      </c>
-      <c r="G13" s="8">
-        <v>392580.0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>357186.0</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="6">
-        <v>46227.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="8">
-        <v>72001.0</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="8">
-        <v>21905.0</v>
-      </c>
-      <c r="G14" s="8">
-        <v>47670.0</v>
-      </c>
-      <c r="H14" s="8">
-        <v>38000.0</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="6">
-        <v>46227.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="8">
-        <v>2110327.0</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="8">
-        <v>69120.0</v>
-      </c>
-      <c r="G15" s="8">
-        <v>57600.0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>40320.0</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="6">
-        <v>46227.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="8">
-        <v>112379.0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="8">
-        <v>3900.0</v>
-      </c>
-      <c r="G16" s="8">
-        <v>102600.0</v>
-      </c>
-      <c r="H16" s="8">
-        <v>1500.0</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="6">
-        <v>46227.0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="8">
-        <v>2152388.0</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="8">
-        <v>720.0</v>
-      </c>
-      <c r="G17" s="8">
-        <v>9720.0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>2580.0</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" s="12"/>
-    </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="6">
-        <v>46227.0</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="8">
-        <v>3300.0</v>
-      </c>
-      <c r="G18" s="8">
-        <v>30600.0</v>
-      </c>
-      <c r="H18" s="8">
-        <v>600.0</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="6">
-        <v>46230.0</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="8">
-        <v>2410401.0</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="8">
-        <v>136538.0</v>
-      </c>
-      <c r="G19" s="8">
-        <v>34080.0</v>
-      </c>
-      <c r="H19" s="8">
-        <v>213000.0</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="6">
-        <v>46231.0</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="8">
-        <v>2110202.0</v>
-      </c>
-      <c r="E20" s="5" t="s">
+      <c r="J31" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
+      <c r="A32" s="4">
+        <v>46234.0</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="7">
+        <v>79110.0</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" s="7">
+        <v>48000.0</v>
+      </c>
+      <c r="G32" s="7">
+        <v>24600.0</v>
+      </c>
+      <c r="H32" s="7">
+        <v>36300.0</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
+      <c r="A33" s="4">
+        <v>46234.0</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="13"/>
+      <c r="D33" s="7">
+        <v>10501.0</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="7">
+        <v>95574.0</v>
+      </c>
+      <c r="G33" s="7">
+        <v>78469.0</v>
+      </c>
+      <c r="H33" s="7">
+        <v>142801.0</v>
+      </c>
+      <c r="I33" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="8">
-        <v>591750.0</v>
-      </c>
-      <c r="G20" s="8">
-        <v>239760.0</v>
-      </c>
-      <c r="H20" s="8">
-        <v>577207.0</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="6">
-        <v>46231.0</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="8">
-        <v>10601.0</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="8">
-        <v>1230.0</v>
-      </c>
-      <c r="G21" s="8">
-        <v>8626.0</v>
-      </c>
-      <c r="H21" s="8">
-        <v>1958.0</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="6">
-        <v>46231.0</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="8">
-        <v>2152388.0</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" s="8">
-        <v>4320.0</v>
-      </c>
-      <c r="G22" s="8">
-        <v>2700.0</v>
-      </c>
-      <c r="H22" s="8">
-        <v>3420.0</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="12"/>
-    </row>
-    <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="6">
-        <v>46231.0</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="8">
-        <v>114357.0</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F23" s="8">
-        <v>240.0</v>
-      </c>
-      <c r="G23" s="8">
-        <v>52320.0</v>
-      </c>
-      <c r="H23" s="8">
-        <v>240.0</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="12"/>
-    </row>
-    <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="6">
-        <v>46232.0</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="8">
-        <v>10501.0</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="8">
-        <v>19663.0</v>
-      </c>
-      <c r="G24" s="8">
-        <v>49540.0</v>
-      </c>
-      <c r="H24" s="8">
-        <v>29632.0</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="12"/>
-    </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="6">
-        <v>46232.0</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="8">
-        <v>5700.0</v>
-      </c>
-      <c r="G25" s="8">
-        <v>34800.0</v>
-      </c>
-      <c r="H25" s="8">
-        <v>5100.0</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="12"/>
-    </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="6">
-        <v>46232.0</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="8">
-        <v>2110317.0</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" s="8">
-        <v>720.0</v>
-      </c>
-      <c r="G26" s="8">
-        <v>7920.0</v>
-      </c>
-      <c r="H26" s="8">
-        <v>720.0</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="12"/>
-    </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="6">
-        <v>46232.0</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="8">
-        <v>2114357.0</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="8">
-        <v>432.0</v>
-      </c>
-      <c r="G27" s="8">
-        <v>576.0</v>
-      </c>
-      <c r="H27" s="8">
-        <v>432.0</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="12"/>
-    </row>
-    <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="6">
-        <v>46232.0</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="8">
-        <v>10501.0</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="8">
-        <v>219540.0</v>
-      </c>
-      <c r="G28" s="8">
-        <v>272160.0</v>
-      </c>
-      <c r="H28" s="8">
-        <v>16698.0</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="12"/>
-    </row>
-    <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="6">
-        <v>46233.0</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="8">
-        <v>112268.0</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="8">
-        <v>5100.0</v>
-      </c>
-      <c r="G29" s="8">
-        <v>3300.0</v>
-      </c>
-      <c r="H29" s="8">
-        <v>4800.0</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J29" s="12"/>
-    </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="6">
-        <v>46233.0</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="8">
-        <v>114357.0</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" s="8">
-        <v>240.0</v>
-      </c>
-      <c r="G30" s="8">
-        <v>7800.0</v>
-      </c>
-      <c r="H30" s="8">
-        <v>1560.0</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="12"/>
-    </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="6">
-        <v>46233.0</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="8">
-        <v>10601.0</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F31" s="8">
-        <v>7717.0</v>
-      </c>
-      <c r="G31" s="8">
-        <v>10080.0</v>
-      </c>
-      <c r="H31" s="8">
-        <v>12867.0</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="6">
+      <c r="J33" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
+      <c r="A34" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="8">
-        <v>79110.0</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F32" s="8">
-        <v>48000.0</v>
-      </c>
-      <c r="G32" s="8">
-        <v>24600.0</v>
-      </c>
-      <c r="H32" s="8">
-        <v>36300.0</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="6">
-        <v>46234.0</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="8">
-        <v>10501.0</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="8">
-        <v>95574.0</v>
-      </c>
-      <c r="G33" s="8">
-        <v>78469.0</v>
-      </c>
-      <c r="H33" s="8">
-        <v>142801.0</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="6">
-        <v>46234.0</v>
-      </c>
       <c r="B34" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="8">
+        <v>18</v>
+      </c>
+      <c r="C34" s="13"/>
+      <c r="D34" s="7">
         <v>73001.0</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="7">
         <v>73367.0</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="7">
         <v>94608.0</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="7">
         <v>39150.0</v>
       </c>
-      <c r="I34" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="12"/>
+      <c r="I34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="11"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="6">
+      <c r="A35" s="4">
         <v>46234.0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="8">
+        <v>18</v>
+      </c>
+      <c r="C35" s="13"/>
+      <c r="D35" s="7">
         <v>112357.0</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F35" s="8">
+        <v>82</v>
+      </c>
+      <c r="F35" s="7">
         <v>840.0</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="7">
         <v>5160.0</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="7">
         <v>480.0</v>
       </c>
-      <c r="I35" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="12"/>
+      <c r="I35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="11"/>
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="18">
         <v>46237.0</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="8">
+        <v>18</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="7">
         <v>10601.0</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F36" s="8">
+        <v>64</v>
+      </c>
+      <c r="F36" s="7">
         <v>17934.0</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="7">
         <v>64980.0</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="7">
         <v>21714.0</v>
       </c>
-      <c r="I36" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>86</v>
+      <c r="I36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
@@ -7684,481 +7807,481 @@
         <v>46237.0</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="8">
+        <v>18</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="8">
+        <v>16</v>
+      </c>
+      <c r="F37" s="7">
         <v>194520.0</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="7">
         <v>84060.0</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="7">
         <v>122840.0</v>
       </c>
-      <c r="I37" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" s="12"/>
+      <c r="I37" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" s="11"/>
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="18">
         <v>46237.0</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="8">
+        <v>18</v>
+      </c>
+      <c r="C38" s="13"/>
+      <c r="D38" s="7">
         <v>114379.0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" s="8">
+        <v>85</v>
+      </c>
+      <c r="F38" s="7">
         <v>52200.0</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="7">
         <v>16200.0</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="7">
         <v>7500.0</v>
       </c>
-      <c r="I38" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J38" s="12"/>
+      <c r="I38" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J38" s="11"/>
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="18">
         <v>46237.0</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="8">
+        <v>18</v>
+      </c>
+      <c r="C39" s="13"/>
+      <c r="D39" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F39" s="8">
+        <v>72</v>
+      </c>
+      <c r="F39" s="7">
         <v>6450.0</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="7">
         <v>16920.0</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="7">
         <v>6480.0</v>
       </c>
-      <c r="I39" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J39" s="12"/>
+      <c r="I39" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" s="11"/>
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="18">
         <v>46237.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="8">
+        <v>18</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" s="8">
+        <v>44</v>
+      </c>
+      <c r="F40" s="7">
         <v>1398.0</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="7">
         <v>1320.0</v>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="7">
         <v>438.0</v>
       </c>
-      <c r="I40" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J40" s="12"/>
+      <c r="I40" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" s="11"/>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="6">
+      <c r="A41" s="4">
         <v>46238.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="8">
+        <v>18</v>
+      </c>
+      <c r="C41" s="13"/>
+      <c r="D41" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F41" s="8">
+        <v>43</v>
+      </c>
+      <c r="F41" s="7">
         <v>2460.0</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="7">
         <v>17640.0</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="7">
         <v>3240.0</v>
       </c>
-      <c r="I41" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J41" s="12"/>
+      <c r="I41" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="11"/>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="6">
+      <c r="A42" s="4">
         <v>46238.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="8">
+        <v>18</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="7">
         <v>112268.0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F42" s="8">
+        <v>35</v>
+      </c>
+      <c r="F42" s="7">
         <v>3600.0</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="7">
         <v>1500.0</v>
       </c>
-      <c r="H42" s="8">
+      <c r="H42" s="7">
         <v>3900.0</v>
       </c>
-      <c r="I42" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J42" s="12"/>
+      <c r="I42" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="11"/>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="6">
+      <c r="A43" s="4">
         <v>46238.0</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="14"/>
-      <c r="D43" s="8">
+        <v>18</v>
+      </c>
+      <c r="C43" s="13"/>
+      <c r="D43" s="7">
         <v>114379.0</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F43" s="8">
+        <v>85</v>
+      </c>
+      <c r="F43" s="7">
         <v>7500.0</v>
       </c>
-      <c r="G43" s="8">
+      <c r="G43" s="7">
         <v>54900.0</v>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="7">
         <v>8400.0</v>
       </c>
-      <c r="I43" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J43" s="12"/>
+      <c r="I43" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" s="11"/>
     </row>
     <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="6">
+      <c r="A44" s="4">
         <v>46238.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="14"/>
-      <c r="D44" s="8">
+        <v>18</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="7">
         <v>114357.0</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F44" s="8">
+        <v>68</v>
+      </c>
+      <c r="F44" s="7">
         <v>240.0</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="7">
         <v>7680.0</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="7">
         <v>360.0</v>
       </c>
-      <c r="I44" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" s="12"/>
+      <c r="I44" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" s="11"/>
     </row>
     <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="6">
+      <c r="A45" s="4">
         <v>46239.0</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" s="14"/>
-      <c r="D45" s="8">
+        <v>90</v>
+      </c>
+      <c r="C45" s="13"/>
+      <c r="D45" s="7">
         <v>10601.0</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F45" s="8">
+        <v>64</v>
+      </c>
+      <c r="F45" s="7">
         <v>1115.0</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="7">
         <v>5267.0</v>
       </c>
-      <c r="H45" s="8">
+      <c r="H45" s="7">
         <v>1590.0</v>
       </c>
-      <c r="I45" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>93</v>
+      <c r="I45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="6">
+      <c r="A46" s="4">
         <v>46239.0</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="14"/>
-      <c r="D46" s="8">
+        <v>18</v>
+      </c>
+      <c r="C46" s="13"/>
+      <c r="D46" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" s="8">
+        <v>34</v>
+      </c>
+      <c r="F46" s="7">
         <v>114240.0</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="7">
         <v>79680.0</v>
       </c>
-      <c r="H46" s="8">
+      <c r="H46" s="7">
         <v>191130.0</v>
       </c>
-      <c r="I46" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="12"/>
+      <c r="I46" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" s="11"/>
     </row>
     <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="6">
+      <c r="A47" s="4">
         <v>46239.0</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="14"/>
-      <c r="D47" s="8">
+        <v>18</v>
+      </c>
+      <c r="C47" s="13"/>
+      <c r="D47" s="7">
         <v>2112207.0</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="7">
         <v>1800.0</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="7">
         <v>1800.0</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="7">
         <v>1980.0</v>
       </c>
-      <c r="I47" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J47" s="12"/>
+      <c r="I47" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J47" s="11"/>
     </row>
     <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="6">
+      <c r="A48" s="4">
         <v>46239.0</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="8">
+        <v>18</v>
+      </c>
+      <c r="C48" s="13"/>
+      <c r="D48" s="7">
         <v>112268.0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F48" s="8">
+        <v>35</v>
+      </c>
+      <c r="F48" s="7">
         <v>3900.0</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="7">
         <v>34200.0</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="7">
         <v>1200.0</v>
       </c>
-      <c r="I48" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J48" s="12"/>
+      <c r="I48" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J48" s="11"/>
     </row>
     <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="6">
+      <c r="A49" s="4">
         <v>46239.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="14"/>
-      <c r="D49" s="8">
+        <v>18</v>
+      </c>
+      <c r="C49" s="13"/>
+      <c r="D49" s="7">
         <v>112357.0</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F49" s="8">
+        <v>82</v>
+      </c>
+      <c r="F49" s="7">
         <v>600.0</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="7">
         <v>8400.0</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="7">
         <v>600.0</v>
       </c>
-      <c r="I49" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J49" s="12"/>
+      <c r="I49" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J49" s="11"/>
     </row>
     <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="6">
+      <c r="A50" s="4">
         <v>46239.0</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="14"/>
-      <c r="D50" s="8">
+        <v>18</v>
+      </c>
+      <c r="C50" s="13"/>
+      <c r="D50" s="7">
         <v>114268.0</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F50" s="8">
+        <v>96</v>
+      </c>
+      <c r="F50" s="7">
         <v>2700.0</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="7">
         <v>5700.0</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="7">
         <v>300.0</v>
       </c>
-      <c r="I50" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J50" s="12"/>
+      <c r="I50" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J50" s="11"/>
     </row>
     <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="6">
+      <c r="A51" s="4">
         <v>46239.0</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" s="14"/>
-      <c r="D51" s="8">
+        <v>39</v>
+      </c>
+      <c r="C51" s="13"/>
+      <c r="D51" s="7">
         <v>10501.0</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F51" s="8">
+        <v>24</v>
+      </c>
+      <c r="F51" s="7">
         <v>68651.0</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="7">
         <v>64050.0</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="7">
         <v>13421.0</v>
       </c>
-      <c r="I51" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J51" s="12" t="s">
+      <c r="I51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="11" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="6">
+      <c r="A52" s="4">
         <v>46239.0</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C52" s="14"/>
-      <c r="D52" s="8">
+        <v>39</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="7">
         <v>72003.0</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="7">
         <v>1391.0</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="7">
         <v>3885.0</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="7">
         <v>2407.0</v>
       </c>
-      <c r="I52" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J52" s="12"/>
+      <c r="I52" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="11"/>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="6">
+      <c r="A53" s="4">
         <v>46239.0</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C53" s="14"/>
-      <c r="D53" s="8">
+        <v>39</v>
+      </c>
+      <c r="C53" s="13"/>
+      <c r="D53" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" s="8">
+        <v>11</v>
+      </c>
+      <c r="F53" s="7">
         <v>2974.0</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="7">
         <v>1200.0</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="7">
         <v>3317.0</v>
       </c>
-      <c r="I53" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>101</v>
+      <c r="I53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
@@ -8166,143 +8289,168 @@
         <v>46240.0</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="14"/>
-      <c r="D54" s="8">
+        <v>18</v>
+      </c>
+      <c r="C54" s="13"/>
+      <c r="D54" s="7">
         <v>112379.0</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F54" s="8">
+        <v>30</v>
+      </c>
+      <c r="F54" s="7">
         <v>3600.0</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="7">
         <v>26100.0</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="7">
         <v>6900.0</v>
       </c>
-      <c r="I54" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J54" s="12"/>
+      <c r="I54" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" s="11"/>
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="18">
         <v>46240.0</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" s="14"/>
-      <c r="D55" s="8">
+        <v>18</v>
+      </c>
+      <c r="C55" s="13"/>
+      <c r="D55" s="7">
         <v>73001.0</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="7">
         <v>2415.0</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="7">
         <v>26490.0</v>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="7">
         <v>2415.0</v>
       </c>
-      <c r="I55" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J55" s="12"/>
+      <c r="I55" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" s="11"/>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="18">
         <v>46240.0</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="14"/>
-      <c r="D56" s="8">
+        <v>18</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="7">
         <v>112357.0</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F56" s="8">
+        <v>82</v>
+      </c>
+      <c r="F56" s="7">
         <v>600.0</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="7">
         <v>3960.0</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="7">
         <v>600.0</v>
       </c>
-      <c r="I56" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J56" s="12"/>
+      <c r="I56" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" s="11"/>
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="18">
         <v>46240.0</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" s="14"/>
-      <c r="D57" s="8">
+        <v>18</v>
+      </c>
+      <c r="C57" s="13"/>
+      <c r="D57" s="7">
         <v>114379.0</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F57" s="8">
+        <v>85</v>
+      </c>
+      <c r="F57" s="7">
         <v>2400.0</v>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="7">
         <v>15000.0</v>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="7">
         <v>300.0</v>
       </c>
-      <c r="I57" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J57" s="12"/>
+      <c r="I57" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" s="11"/>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="18">
         <v>46244.0</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C58" s="14"/>
-      <c r="D58" s="8">
+        <v>18</v>
+      </c>
+      <c r="C58" s="13"/>
+      <c r="D58" s="7">
         <v>112379.0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F58" s="8">
+        <v>30</v>
+      </c>
+      <c r="F58" s="7">
         <v>4800.0</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G58" s="7">
         <v>41100.0</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="7">
         <v>5100.0</v>
       </c>
-      <c r="I58" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J58" s="12"/>
-    </row>
-    <row r="59">
-      <c r="I59" s="20"/>
+      <c r="I58" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" s="11"/>
+    </row>
+    <row r="59" ht="22.5" customHeight="1">
+      <c r="A59" s="4">
+        <v>46245.0</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="13"/>
+      <c r="D59" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F59" s="7">
+        <v>25574.0</v>
+      </c>
+      <c r="G59" s="7">
+        <v>75840.0</v>
+      </c>
+      <c r="H59" s="7">
+        <v>42960.0</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J59" s="11"/>
     </row>
     <row r="60">
       <c r="I60" s="20"/>
@@ -11009,13 +11157,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I58">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I59">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I59:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I60:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A58">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A59">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="142">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -47,51 +47,51 @@
     <t>ALKA2</t>
   </si>
   <si>
+    <t>TAT BOGOTA MONTEVIDEO</t>
+  </si>
+  <si>
+    <t>Daniel Castro</t>
+  </si>
+  <si>
     <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>TAT BOGOTA MONTEVIDEO</t>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
     <t>7. Otro</t>
   </si>
   <si>
-    <t>Daniel Castro</t>
-  </si>
-  <si>
     <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
   </si>
   <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
     <t>LANZA</t>
   </si>
   <si>
+    <t>TAT MONTERIA</t>
+  </si>
+  <si>
+    <t>LUIS LOPEZ</t>
+  </si>
+  <si>
     <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
-    <t>TAT MONTERIA</t>
-  </si>
-  <si>
     <t>6. Transformación De Referencias</t>
   </si>
   <si>
     <t>Pendiente Transformar Roto GT Por manipulación</t>
   </si>
   <si>
-    <t>LUIS LOPEZ</t>
+    <t>3. Falla De Rotación</t>
   </si>
   <si>
     <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
-    <t>3. Falla De Rotación</t>
-  </si>
-  <si>
     <t>TAT MEDELLIN</t>
   </si>
   <si>
@@ -101,66 +101,72 @@
     <t>FABIO GOMEZ</t>
   </si>
   <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
     <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
     <t>TAT CARTAGENA</t>
   </si>
   <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
-  </si>
-  <si>
     <t>Dilan Barraza</t>
   </si>
   <si>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+  </si>
+  <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
     <t>4. Exigencia Del Cliente (Edad)</t>
   </si>
   <si>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
+  </si>
+  <si>
     <t>Venta FS</t>
   </si>
   <si>
-    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
-  </si>
-  <si>
-    <t>PALMAS</t>
-  </si>
-  <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
-  </si>
-  <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+  </si>
+  <si>
+    <t>HUEVO PICADO ROJO</t>
   </si>
   <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+    <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
-  </si>
-  <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
-  </si>
-  <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
@@ -170,24 +176,18 @@
     <t>DIEGO ROJAS</t>
   </si>
   <si>
-    <t>HUEVO PICADO ROJO</t>
-  </si>
-  <si>
-    <t>No se carga todod por capacidad de Vehiculo</t>
-  </si>
-  <si>
     <t>HUEVO SUCIO DE JAULA</t>
   </si>
   <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
     <t>TAT CUCUTA</t>
   </si>
   <si>
     <t>ALEXANDER PEÑA</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
-  </si>
-  <si>
     <t>Esta para despacho hoy</t>
   </si>
   <si>
@@ -200,12 +200,12 @@
     <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
   </si>
   <si>
+    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+  </si>
+  <si>
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
-    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
-  </si>
-  <si>
     <t>HUEVO CX30 CARTON GRIS</t>
   </si>
   <si>
@@ -215,12 +215,12 @@
     <t>Transformación de PET</t>
   </si>
   <si>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+  </si>
+  <si>
     <t>ANDRES MEJIA</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
-  </si>
-  <si>
     <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
   </si>
   <si>
@@ -239,12 +239,12 @@
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
+    <t>ALKA1</t>
+  </si>
+  <si>
     <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
-    <t>ALKA1</t>
-  </si>
-  <si>
     <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
   </si>
   <si>
@@ -269,12 +269,12 @@
     <t>5. Ingreso De Planta</t>
   </si>
   <si>
+    <t>Se despacha par FS con producto más nuevo</t>
+  </si>
+  <si>
     <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>Se despacha par FS con producto más nuevo</t>
-  </si>
-  <si>
     <t>ANDREA QUIROGA</t>
   </si>
   <si>
@@ -290,33 +290,33 @@
     <t>Traslado a cedi, producto de devolución</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CANASTA</t>
+  </si>
+  <si>
     <t>TAT PASTO</t>
   </si>
   <si>
     <t>CAROLINA VITERI</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CANASTA</t>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
+  </si>
+  <si>
+    <t>HUEVO SUCIO ZF MARCADO</t>
   </si>
   <si>
     <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+    <t>vehiculo con flata de capacidad / TAT cali</t>
   </si>
   <si>
     <t>Pedido para villavicencio</t>
   </si>
   <si>
-    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
-  </si>
-  <si>
-    <t>HUEVO SUCIO ZF MARCADO</t>
-  </si>
-  <si>
-    <t>vehiculo con flata de capacidad / TAT cali</t>
-  </si>
-  <si>
     <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
@@ -432,6 +432,12 @@
   </si>
   <si>
     <t>Llega de planta bellavista</t>
+  </si>
+  <si>
+    <t>Jhonathan Gomez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se registraron edades antes de sacar el sugerido del dia </t>
   </si>
 </sst>
 </file>
@@ -511,17 +517,23 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -529,17 +541,11 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -652,7 +658,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J100" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J104" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -670,7 +676,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J59" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J60" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -933,28 +939,28 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="8">
+      <c r="A2" s="5">
         <v>46204.0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="F2" s="9">
         <v>359100.0</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="9">
         <v>83486.0</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="9">
         <v>206140.0</v>
       </c>
       <c r="I2" s="12" t="s">
@@ -965,185 +971,185 @@
       <c r="A3" s="4">
         <v>46205.0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="7">
+      <c r="D3" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="9">
         <v>298282.0</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="9">
         <v>42201.0</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="9">
         <v>260675.0</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="6"/>
+      <c r="I3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
       <c r="A4" s="4">
         <v>46205.0</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="9">
         <v>2110217.0</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="9">
         <v>21120.0</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="9">
         <v>11039.0</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="9">
         <v>16920.0</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="6"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
       <c r="A5" s="4">
         <v>46205.0</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="B5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="9">
         <v>75680.0</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>5640.0</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>3134.0</v>
       </c>
-      <c r="I5" s="14" t="s">
-        <v>36</v>
+      <c r="I5" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
       <c r="A6" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="E6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="9">
         <v>189540.0</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="9">
         <v>161685.0</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <v>144720.0</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>13</v>
+      <c r="I6" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
       <c r="A7" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="9">
         <v>2010102.0</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="9">
         <v>20640.0</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="9">
         <v>3761.0</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="9">
         <v>13920.0</v>
       </c>
-      <c r="I7" s="14" t="s">
-        <v>36</v>
+      <c r="I7" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
       <c r="A8" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="9">
         <v>152384.0</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="9">
         <v>14700.0</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="9">
         <v>6435.0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="9">
         <v>9600.0</v>
       </c>
-      <c r="I8" s="14" t="s">
-        <v>49</v>
+      <c r="I8" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="J8" s="11"/>
     </row>
@@ -1151,29 +1157,29 @@
       <c r="A9" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="9">
+        <v>228240.0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>77306.0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>124260.0</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D9" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="7">
-        <v>228240.0</v>
-      </c>
-      <c r="G9" s="7">
-        <v>77306.0</v>
-      </c>
-      <c r="H9" s="7">
-        <v>124260.0</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="J9" s="11"/>
     </row>
@@ -1181,29 +1187,29 @@
       <c r="A10" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="7">
+      <c r="C10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="9">
         <v>2152388.0</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="9">
         <v>7830.0</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="9">
         <v>1980.0</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="9">
         <v>6030.0</v>
       </c>
-      <c r="I10" s="14" t="s">
-        <v>21</v>
+      <c r="I10" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J10" s="15"/>
     </row>
@@ -1211,29 +1217,29 @@
       <c r="A11" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="9">
         <v>31680.0</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="9">
         <v>5526.0</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="9">
         <v>23040.0</v>
       </c>
-      <c r="I11" s="14" t="s">
-        <v>36</v>
+      <c r="I11" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>59</v>
@@ -1243,93 +1249,93 @@
       <c r="A12" s="4">
         <v>46206.0</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="D12" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="9">
         <v>51387.0</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="9">
         <v>10827.0</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="9">
         <v>12170.0</v>
       </c>
-      <c r="I12" s="14" t="s">
-        <v>36</v>
+      <c r="I12" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
       <c r="A13" s="4">
         <v>46209.0</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="D13" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="9">
         <v>195810.0</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="9">
         <v>93809.0</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="9">
         <v>133410.0</v>
       </c>
-      <c r="I13" s="14" t="s">
-        <v>36</v>
+      <c r="I13" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
       <c r="A14" s="4">
         <v>46209.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="B14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="7">
+      <c r="E14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="9">
         <v>526002.0</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="9">
         <v>301965.0</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="9">
         <v>424588.0</v>
       </c>
-      <c r="I14" s="14" t="s">
-        <v>21</v>
+      <c r="I14" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>66</v>
@@ -1339,29 +1345,29 @@
       <c r="A15" s="4">
         <v>46209.0</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="C15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="9">
         <v>2010102.0</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="9">
         <v>14160.0</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="9">
         <v>6692.0</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="9">
         <v>12360.0</v>
       </c>
-      <c r="I15" s="14" t="s">
-        <v>13</v>
+      <c r="I15" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>69</v>
@@ -1371,28 +1377,28 @@
       <c r="A16" s="4">
         <v>46210.0</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="E16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="9">
         <v>149040.0</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="9">
         <v>119573.0</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="9">
         <v>289680.0</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="13" t="s">
         <v>17</v>
       </c>
       <c r="J16" s="11"/>
@@ -1401,28 +1407,28 @@
       <c r="A17" s="4">
         <v>46210.0</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="7">
+      <c r="B17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="9">
         <v>2110217.0</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="E17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="9">
         <v>22770.0</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="9">
         <v>3926.0</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="9">
         <v>19770.0</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="13" t="s">
         <v>17</v>
       </c>
       <c r="J17" s="11"/>
@@ -1431,28 +1437,28 @@
       <c r="A18" s="4">
         <v>46210.0</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="7">
+      <c r="B18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="9">
         <v>222021.0</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="9">
         <v>61385.0</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="9">
         <v>162125.0</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="13" t="s">
         <v>17</v>
       </c>
       <c r="J18" s="11"/>
@@ -1461,29 +1467,29 @@
       <c r="A19" s="4">
         <v>46211.0</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="B19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="7">
+      <c r="E19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="9">
         <v>495833.0</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="9">
         <v>148815.0</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="9">
         <v>401280.0</v>
       </c>
-      <c r="I19" s="14" t="s">
-        <v>13</v>
+      <c r="I19" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>74</v>
@@ -1493,28 +1499,28 @@
       <c r="A20" s="4">
         <v>46211.0</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="7">
+      <c r="D20" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="7">
+      <c r="E20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="9">
         <v>139920.0</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="9">
         <v>54384.0</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="9">
         <v>74040.0</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="13" t="s">
         <v>17</v>
       </c>
       <c r="J20" s="11"/>
@@ -1523,61 +1529,61 @@
       <c r="A21" s="4">
         <v>46211.0</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="7">
+      <c r="B21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="7">
+      <c r="E21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="9">
         <v>162125.0</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="9">
         <v>60138.0</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="9">
         <v>100687.0</v>
       </c>
-      <c r="I21" s="14" t="s">
-        <v>13</v>
+      <c r="I21" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
       <c r="A22" s="4">
         <v>46211.0</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="7">
+      <c r="D22" s="9">
         <v>152384.0</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="E22" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="9">
         <v>32850.0</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="9">
         <v>7065.0</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="9">
         <v>32700.0</v>
       </c>
-      <c r="I22" s="14" t="s">
-        <v>36</v>
+      <c r="I22" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J22" s="11"/>
     </row>
@@ -1585,29 +1591,29 @@
       <c r="A23" s="4">
         <v>46211.0</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="7">
+      <c r="C23" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="9">
         <v>112271.0</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="9">
         <v>16500.0</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="9">
         <v>5310.0</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="9">
         <v>18000.0</v>
       </c>
-      <c r="I23" s="14" t="s">
-        <v>49</v>
+      <c r="I23" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="J23" s="11"/>
     </row>
@@ -1615,29 +1621,29 @@
       <c r="A24" s="4">
         <v>46212.0</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>50</v>
+      <c r="B24" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="C24" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="9">
+        <v>190047.0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>59822.0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>248481.0</v>
+      </c>
+      <c r="I24" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D24" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="7">
-        <v>190047.0</v>
-      </c>
-      <c r="G24" s="7">
-        <v>59822.0</v>
-      </c>
-      <c r="H24" s="7">
-        <v>248481.0</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="J24" s="11"/>
     </row>
@@ -1645,28 +1651,28 @@
       <c r="A25" s="4">
         <v>46212.0</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="7">
+        <v>68</v>
+      </c>
+      <c r="D25" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="9">
         <v>178080.0</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="9">
         <v>47784.0</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="9">
         <v>203520.0</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="13" t="s">
         <v>84</v>
       </c>
       <c r="J25" s="11"/>
@@ -1675,61 +1681,61 @@
       <c r="A26" s="4">
         <v>46212.0</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="7">
+        <v>68</v>
+      </c>
+      <c r="D26" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="E26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="9">
         <v>10320.0</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="9">
         <v>5869.0</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="9">
         <v>13200.0</v>
       </c>
-      <c r="I26" s="14" t="s">
-        <v>36</v>
+      <c r="I26" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
       <c r="A27" s="4">
         <v>46212.0</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="7">
+        <v>68</v>
+      </c>
+      <c r="D27" s="9">
         <v>112271.0</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="9">
         <v>18000.0</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="9">
         <v>4485.0</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="9">
         <v>13500.0</v>
       </c>
-      <c r="I27" s="14" t="s">
-        <v>25</v>
+      <c r="I27" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J27" s="11"/>
     </row>
@@ -1737,29 +1743,29 @@
       <c r="A28" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>12</v>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="9">
         <v>208440.0</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="9">
         <v>85608.0</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="9">
         <v>150833.0</v>
       </c>
-      <c r="I28" s="14" t="s">
-        <v>13</v>
+      <c r="I28" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>88</v>
@@ -1769,29 +1775,29 @@
       <c r="A29" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>12</v>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="E29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="9">
         <v>962820.0</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="9">
         <v>80644.0</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="9">
         <v>922140.0</v>
       </c>
-      <c r="I29" s="14" t="s">
-        <v>13</v>
+      <c r="I29" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>88</v>
@@ -1801,29 +1807,29 @@
       <c r="A30" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="7">
+        <v>68</v>
+      </c>
+      <c r="D30" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="7">
+      <c r="E30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="9">
         <v>335340.0</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="9">
         <v>111433.0</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="9">
         <v>381600.0</v>
       </c>
-      <c r="I30" s="14" t="s">
-        <v>36</v>
+      <c r="I30" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>89</v>
@@ -1833,29 +1839,29 @@
       <c r="A31" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="7">
+      <c r="E31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="9">
         <v>316800.0</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="9">
         <v>99546.0</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="9">
         <v>229680.0</v>
       </c>
-      <c r="I31" s="14" t="s">
-        <v>25</v>
+      <c r="I31" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J31" s="11"/>
     </row>
@@ -1863,29 +1869,29 @@
       <c r="A32" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>50</v>
+      <c r="B32" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="C32" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" s="9">
+        <v>176850.0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>47499.0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>128971.0</v>
+      </c>
+      <c r="I32" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D32" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="7">
-        <v>176850.0</v>
-      </c>
-      <c r="G32" s="7">
-        <v>47499.0</v>
-      </c>
-      <c r="H32" s="7">
-        <v>128971.0</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="J32" s="11"/>
     </row>
@@ -1893,29 +1899,29 @@
       <c r="A33" s="4">
         <v>46213.0</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="E33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="9">
         <v>58080.0</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="9">
         <v>20865.0</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="9">
         <v>25440.0</v>
       </c>
-      <c r="I33" s="14" t="s">
-        <v>25</v>
+      <c r="I33" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J33" s="11"/>
     </row>
@@ -1923,29 +1929,29 @@
       <c r="A34" s="4">
         <v>46217.0</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="10" t="s">
+      <c r="B34" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="7">
+      <c r="C34" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="7">
+      <c r="E34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="9">
         <v>481440.0</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="9">
         <v>464517.0</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="9">
         <v>151435.0</v>
       </c>
-      <c r="I34" s="14" t="s">
-        <v>25</v>
+      <c r="I34" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J34" s="11"/>
     </row>
@@ -1953,28 +1959,28 @@
       <c r="A35" s="4">
         <v>46217.0</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="E35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="9">
         <v>355720.0</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="9">
         <v>342811.0</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="9">
         <v>302760.0</v>
       </c>
-      <c r="I35" s="14" t="s">
+      <c r="I35" s="13" t="s">
         <v>17</v>
       </c>
       <c r="J35" s="11"/>
@@ -1983,125 +1989,125 @@
       <c r="A36" s="4">
         <v>46217.0</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>12</v>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="9">
         <v>2010102.0</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="7">
+      <c r="E36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="9">
         <v>35280.0</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="9">
         <v>16988.0</v>
       </c>
-      <c r="H36" s="7">
+      <c r="H36" s="9">
         <v>37926.0</v>
       </c>
-      <c r="I36" s="14" t="s">
-        <v>25</v>
+      <c r="I36" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
       <c r="A37" s="19">
         <v>46218.0</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>12</v>
+      <c r="B37" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="7">
+      <c r="E37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" s="9">
         <v>272073.0</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="9">
         <v>76546.0</v>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="9">
         <v>275205.0</v>
       </c>
-      <c r="I37" s="14" t="s">
-        <v>36</v>
+      <c r="I37" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
       <c r="A38" s="19">
         <v>46218.0</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>12</v>
+      <c r="B38" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="9">
         <v>2010102.0</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" s="7">
+      <c r="E38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="9">
         <v>37926.0</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="9">
         <v>5633.0</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38" s="9">
         <v>25746.0</v>
       </c>
-      <c r="I38" s="14" t="s">
-        <v>25</v>
+      <c r="I38" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
       <c r="A39" s="19">
         <v>46218.0</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="7">
+      <c r="E39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9">
         <v>20640.0</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="9">
         <v>4951.0</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="9">
         <v>16320.0</v>
       </c>
-      <c r="I39" s="14" t="s">
-        <v>36</v>
+      <c r="I39" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>101</v>
@@ -2111,29 +2117,29 @@
       <c r="A40" s="19">
         <v>46218.0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="9">
         <v>2110317.0</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="9">
         <v>10980.0</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="9">
         <v>2379.0</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40" s="9">
         <v>13500.0</v>
       </c>
-      <c r="I40" s="14" t="s">
-        <v>25</v>
+      <c r="I40" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J40" s="11"/>
     </row>
@@ -2141,29 +2147,29 @@
       <c r="A41" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="7">
+      <c r="E41" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41" s="9">
         <v>130320.0</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="9">
         <v>47410.0</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41" s="9">
         <v>90480.0</v>
       </c>
-      <c r="I41" s="14" t="s">
-        <v>49</v>
+      <c r="I41" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>102</v>
@@ -2173,28 +2179,28 @@
       <c r="A42" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>103</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="9">
         <v>2152388.0</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F42" s="7">
+      <c r="E42" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" s="9">
         <v>36225.0</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="9">
         <v>11746.0</v>
       </c>
-      <c r="H42" s="7">
+      <c r="H42" s="9">
         <v>27570.0</v>
       </c>
-      <c r="I42" s="14" t="s">
+      <c r="I42" s="13" t="s">
         <v>17</v>
       </c>
       <c r="J42" s="11"/>
@@ -2203,28 +2209,28 @@
       <c r="A43" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>50</v>
+      <c r="B43" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="7">
+        <v>53</v>
+      </c>
+      <c r="D43" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F43" s="7">
+      <c r="E43" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F43" s="9">
         <v>152833.0</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="9">
         <v>50641.0</v>
       </c>
-      <c r="H43" s="7">
+      <c r="H43" s="9">
         <v>96472.0</v>
       </c>
-      <c r="I43" s="14" t="s">
+      <c r="I43" s="13" t="s">
         <v>84</v>
       </c>
       <c r="J43" s="11" t="s">
@@ -2235,29 +2241,29 @@
       <c r="A44" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>92</v>
+      <c r="B44" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D44" s="7">
+        <v>94</v>
+      </c>
+      <c r="D44" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F44" s="7">
+      <c r="E44" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F44" s="9">
         <v>237828.0</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="9">
         <v>173585.0</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="9">
         <v>71560.0</v>
       </c>
-      <c r="I44" s="14" t="s">
-        <v>25</v>
+      <c r="I44" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J44" s="11"/>
     </row>
@@ -2265,29 +2271,29 @@
       <c r="A45" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>12</v>
+      <c r="B45" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="9">
         <v>152384.0</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F45" s="7">
+      <c r="E45" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" s="9">
         <v>31125.0</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="9">
         <v>7815.0</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H45" s="9">
         <v>31845.0</v>
       </c>
-      <c r="I45" s="14" t="s">
-        <v>36</v>
+      <c r="I45" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>106</v>
@@ -2297,61 +2303,61 @@
       <c r="A46" s="4">
         <v>46219.0</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>12</v>
+      <c r="B46" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="9">
         <v>2010102.0</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F46" s="7">
+      <c r="E46" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" s="9">
         <v>25746.0</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46" s="9">
         <v>6168.0</v>
       </c>
-      <c r="H46" s="7">
+      <c r="H46" s="9">
         <v>28683.0</v>
       </c>
-      <c r="I46" s="14" t="s">
-        <v>25</v>
+      <c r="I46" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
       <c r="A47" s="4">
         <v>46220.0</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>12</v>
+      <c r="B47" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F47" s="7">
+      <c r="E47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F47" s="9">
         <v>261166.0</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="9">
         <v>74573.0</v>
       </c>
-      <c r="H47" s="7">
+      <c r="H47" s="9">
         <v>221549.0</v>
       </c>
-      <c r="I47" s="14" t="s">
-        <v>36</v>
+      <c r="I47" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>107</v>
@@ -2361,29 +2367,29 @@
       <c r="A48" s="4">
         <v>46220.0</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>12</v>
+      <c r="B48" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="9">
         <v>2110217.0</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F48" s="7">
+      <c r="E48" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" s="9">
         <v>115289.0</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="9">
         <v>26931.0</v>
       </c>
-      <c r="H48" s="7">
+      <c r="H48" s="9">
         <v>119584.0</v>
       </c>
-      <c r="I48" s="14" t="s">
-        <v>25</v>
+      <c r="I48" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J48" s="11"/>
     </row>
@@ -2391,29 +2397,29 @@
       <c r="A49" s="4">
         <v>46224.0</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D49" s="7">
+      <c r="D49" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="7">
+      <c r="E49" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="9">
         <v>398570.0</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G49" s="9">
         <v>288226.0</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49" s="9">
         <v>287235.0</v>
       </c>
-      <c r="I49" s="14" t="s">
-        <v>36</v>
+      <c r="I49" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>108</v>
@@ -2423,29 +2429,29 @@
       <c r="A50" s="4">
         <v>46224.0</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>103</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="7">
+      <c r="E50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="9">
         <v>745107.0</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G50" s="9">
         <v>378927.0</v>
       </c>
-      <c r="H50" s="7">
+      <c r="H50" s="9">
         <v>551645.0</v>
       </c>
-      <c r="I50" s="14" t="s">
-        <v>13</v>
+      <c r="I50" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>109</v>
@@ -2455,29 +2461,29 @@
       <c r="A51" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D51" s="7">
+      <c r="C51" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F51" s="7">
+      <c r="E51" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F51" s="9">
         <v>130560.0</v>
       </c>
-      <c r="G51" s="7">
+      <c r="G51" s="9">
         <v>52658.0</v>
       </c>
-      <c r="H51" s="7">
+      <c r="H51" s="9">
         <v>153840.0</v>
       </c>
-      <c r="I51" s="14" t="s">
-        <v>21</v>
+      <c r="I51" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>110</v>
@@ -2487,29 +2493,29 @@
       <c r="A52" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D52" s="7">
+      <c r="B52" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F52" s="7">
+      <c r="E52" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F52" s="9">
         <v>87447.0</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G52" s="9">
         <v>59056.0</v>
       </c>
-      <c r="H52" s="7">
+      <c r="H52" s="9">
         <v>104365.0</v>
       </c>
-      <c r="I52" s="14" t="s">
-        <v>25</v>
+      <c r="I52" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J52" s="11"/>
     </row>
@@ -2517,29 +2523,29 @@
       <c r="A53" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>12</v>
+      <c r="B53" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="7">
+      <c r="E53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9">
         <v>25200.0</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G53" s="9">
         <v>2085.0</v>
       </c>
-      <c r="H53" s="7">
+      <c r="H53" s="9">
         <v>25920.0</v>
       </c>
-      <c r="I53" s="14" t="s">
-        <v>25</v>
+      <c r="I53" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>111</v>
@@ -2549,28 +2555,28 @@
       <c r="A54" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="10" t="s">
+      <c r="B54" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="7">
+      <c r="E54" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="9">
         <v>285405.0</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G54" s="9">
         <v>203180.0</v>
       </c>
-      <c r="H54" s="7">
+      <c r="H54" s="9">
         <v>226069.0</v>
       </c>
-      <c r="I54" s="14" t="s">
+      <c r="I54" s="13" t="s">
         <v>84</v>
       </c>
       <c r="J54" s="11" t="s">
@@ -2581,28 +2587,28 @@
       <c r="A55" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D55" s="7">
+      <c r="C55" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F55" s="7">
+      <c r="E55" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="9">
         <v>692280.0</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G55" s="9">
         <v>118381.0</v>
       </c>
-      <c r="H55" s="7">
+      <c r="H55" s="9">
         <v>700200.0</v>
       </c>
-      <c r="I55" s="14" t="s">
+      <c r="I55" s="13" t="s">
         <v>84</v>
       </c>
       <c r="J55" s="11"/>
@@ -2611,29 +2617,29 @@
       <c r="A56" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D56" s="7">
+      <c r="C56" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F56" s="7">
+      <c r="E56" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" s="9">
         <v>700200.0</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="9">
         <v>112628.0</v>
       </c>
-      <c r="H56" s="7">
+      <c r="H56" s="9">
         <v>668440.0</v>
       </c>
-      <c r="I56" s="14" t="s">
-        <v>25</v>
+      <c r="I56" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J56" s="11"/>
     </row>
@@ -2641,29 +2647,29 @@
       <c r="A57" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="10" t="s">
+      <c r="B57" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="7">
+      <c r="E57" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="9">
         <v>226069.0</v>
       </c>
-      <c r="G57" s="7">
+      <c r="G57" s="9">
         <v>193130.0</v>
       </c>
-      <c r="H57" s="7">
+      <c r="H57" s="9">
         <v>326391.0</v>
       </c>
-      <c r="I57" s="14" t="s">
-        <v>49</v>
+      <c r="I57" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>114</v>
@@ -2673,28 +2679,28 @@
       <c r="A58" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D58" s="7">
+      <c r="B58" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D58" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F58" s="7">
+      <c r="E58" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="9">
         <v>144637.0</v>
       </c>
-      <c r="G58" s="7">
+      <c r="G58" s="9">
         <v>64227.0</v>
       </c>
-      <c r="H58" s="7">
+      <c r="H58" s="9">
         <v>128160.0</v>
       </c>
-      <c r="I58" s="14" t="s">
+      <c r="I58" s="13" t="s">
         <v>84</v>
       </c>
       <c r="J58" s="11"/>
@@ -2703,29 +2709,29 @@
       <c r="A59" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="7">
+      <c r="E59" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="9">
         <v>295359.0</v>
       </c>
-      <c r="G59" s="7">
+      <c r="G59" s="9">
         <v>126369.0</v>
       </c>
-      <c r="H59" s="7">
+      <c r="H59" s="9">
         <v>166642.0</v>
       </c>
-      <c r="I59" s="14" t="s">
-        <v>13</v>
+      <c r="I59" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>115</v>
@@ -2735,29 +2741,29 @@
       <c r="A60" s="4">
         <v>46230.0</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="9">
         <v>2110403.0</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F60" s="9">
         <v>9960.0</v>
       </c>
-      <c r="G60" s="7">
+      <c r="G60" s="9">
         <v>6018.0</v>
       </c>
-      <c r="H60" s="7">
+      <c r="H60" s="9">
         <v>3660.0</v>
       </c>
-      <c r="I60" s="14" t="s">
-        <v>25</v>
+      <c r="I60" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J60" s="11"/>
     </row>
@@ -2765,29 +2771,29 @@
       <c r="A61" s="4">
         <v>46230.0</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>12</v>
+      <c r="B61" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F61" s="7">
+      <c r="E61" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F61" s="9">
         <v>306720.0</v>
       </c>
-      <c r="G61" s="7">
+      <c r="G61" s="9">
         <v>164175.0</v>
       </c>
-      <c r="H61" s="7">
+      <c r="H61" s="9">
         <v>247096.0</v>
       </c>
-      <c r="I61" s="14" t="s">
-        <v>25</v>
+      <c r="I61" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J61" s="11"/>
     </row>
@@ -2795,29 +2801,29 @@
       <c r="A62" s="4">
         <v>46230.0</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F62" s="7">
+      <c r="E62" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" s="9">
         <v>437080.0</v>
       </c>
-      <c r="G62" s="7">
+      <c r="G62" s="9">
         <v>277785.0</v>
       </c>
-      <c r="H62" s="7">
+      <c r="H62" s="9">
         <v>353700.0</v>
       </c>
-      <c r="I62" s="14" t="s">
-        <v>36</v>
+      <c r="I62" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>117</v>
@@ -2827,29 +2833,29 @@
       <c r="A63" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D63" s="7">
+      <c r="D63" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" s="7">
+      <c r="E63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="9">
         <v>165466.0</v>
       </c>
-      <c r="G63" s="7">
+      <c r="G63" s="9">
         <v>113462.0</v>
       </c>
-      <c r="H63" s="7">
+      <c r="H63" s="9">
         <v>375549.0</v>
       </c>
-      <c r="I63" s="14" t="s">
-        <v>36</v>
+      <c r="I63" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>118</v>
@@ -2859,29 +2865,29 @@
       <c r="A64" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C64" s="10" t="s">
+      <c r="B64" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F64" s="9">
+        <v>238497.0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>56526.0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>181858.0</v>
+      </c>
+      <c r="I64" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D64" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F64" s="7">
-        <v>238497.0</v>
-      </c>
-      <c r="G64" s="7">
-        <v>56526.0</v>
-      </c>
-      <c r="H64" s="7">
-        <v>181858.0</v>
-      </c>
-      <c r="I64" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>119</v>
@@ -2891,29 +2897,29 @@
       <c r="A65" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C65" s="10" t="s">
+      <c r="B65" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F65" s="9">
+        <v>8190.0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>2049.0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>7200.0</v>
+      </c>
+      <c r="I65" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D65" s="7">
-        <v>2110317.0</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F65" s="7">
-        <v>8190.0</v>
-      </c>
-      <c r="G65" s="7">
-        <v>2049.0</v>
-      </c>
-      <c r="H65" s="7">
-        <v>7200.0</v>
-      </c>
-      <c r="I65" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>119</v>
@@ -2923,29 +2929,29 @@
       <c r="A66" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C66" s="10" t="s">
+      <c r="B66" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D66" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" s="9">
+        <v>146224.0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>78064.0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>98850.0</v>
+      </c>
+      <c r="I66" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D66" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F66" s="7">
-        <v>146224.0</v>
-      </c>
-      <c r="G66" s="7">
-        <v>78064.0</v>
-      </c>
-      <c r="H66" s="7">
-        <v>98850.0</v>
-      </c>
-      <c r="I66" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>119</v>
@@ -2955,27 +2961,27 @@
       <c r="A67" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C67" s="21"/>
-      <c r="D67" s="7">
+      <c r="D67" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F67" s="7">
+      <c r="E67" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" s="9">
         <v>14599.0</v>
       </c>
-      <c r="G67" s="7">
+      <c r="G67" s="9">
         <v>3782.0</v>
       </c>
-      <c r="H67" s="7">
+      <c r="H67" s="9">
         <v>7263.0</v>
       </c>
-      <c r="I67" s="14" t="s">
-        <v>13</v>
+      <c r="I67" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J67" s="11"/>
     </row>
@@ -2983,27 +2989,27 @@
       <c r="A68" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C68" s="21"/>
-      <c r="D68" s="7">
+      <c r="D68" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="7">
+      <c r="E68" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="9">
         <v>22080.0</v>
       </c>
-      <c r="G68" s="7">
+      <c r="G68" s="9">
         <v>5686.0</v>
       </c>
-      <c r="H68" s="7">
+      <c r="H68" s="9">
         <v>36720.0</v>
       </c>
-      <c r="I68" s="14" t="s">
-        <v>13</v>
+      <c r="I68" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J68" s="11"/>
     </row>
@@ -3011,27 +3017,27 @@
       <c r="A69" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
+      <c r="B69" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="C69" s="21"/>
-      <c r="D69" s="7">
+      <c r="D69" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" s="7">
+      <c r="E69" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="9">
         <v>353905.0</v>
       </c>
-      <c r="G69" s="7">
+      <c r="G69" s="9">
         <v>208296.0</v>
       </c>
-      <c r="H69" s="7">
+      <c r="H69" s="9">
         <v>117570.0</v>
       </c>
-      <c r="I69" s="14" t="s">
-        <v>13</v>
+      <c r="I69" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J69" s="11"/>
     </row>
@@ -3039,27 +3045,27 @@
       <c r="A70" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>50</v>
+      <c r="B70" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="C70" s="21"/>
-      <c r="D70" s="7">
+      <c r="D70" s="9">
         <v>2010102.0</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F70" s="7">
+      <c r="E70" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F70" s="9">
         <v>5913.0</v>
       </c>
-      <c r="G70" s="7">
+      <c r="G70" s="9">
         <v>902.0</v>
       </c>
-      <c r="H70" s="7">
+      <c r="H70" s="9">
         <v>5893.0</v>
       </c>
-      <c r="I70" s="14" t="s">
-        <v>13</v>
+      <c r="I70" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J70" s="11"/>
     </row>
@@ -3067,27 +3073,27 @@
       <c r="A71" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>12</v>
+      <c r="B71" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C71" s="21"/>
-      <c r="D71" s="7">
+      <c r="D71" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F71" s="7">
+      <c r="E71" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F71" s="9">
         <v>256613.0</v>
       </c>
-      <c r="G71" s="7">
+      <c r="G71" s="9">
         <v>86092.0</v>
       </c>
-      <c r="H71" s="7">
+      <c r="H71" s="9">
         <v>142320.0</v>
       </c>
-      <c r="I71" s="14" t="s">
-        <v>13</v>
+      <c r="I71" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J71" s="11"/>
     </row>
@@ -3095,27 +3101,27 @@
       <c r="A72" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>12</v>
+      <c r="B72" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C72" s="21"/>
-      <c r="D72" s="7">
+      <c r="D72" s="9">
         <v>152384.0</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F72" s="7">
+      <c r="E72" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F72" s="9">
         <v>21300.0</v>
       </c>
-      <c r="G72" s="7">
+      <c r="G72" s="9">
         <v>9765.0</v>
       </c>
-      <c r="H72" s="7">
+      <c r="H72" s="9">
         <v>18690.0</v>
       </c>
-      <c r="I72" s="14" t="s">
-        <v>13</v>
+      <c r="I72" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J72" s="11"/>
     </row>
@@ -3123,27 +3129,27 @@
       <c r="A73" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="6" t="s">
         <v>103</v>
       </c>
       <c r="C73" s="21"/>
-      <c r="D73" s="7">
+      <c r="D73" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E73" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="7">
+      <c r="E73" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="9">
         <v>351733.0</v>
       </c>
-      <c r="G73" s="7">
+      <c r="G73" s="9">
         <v>145994.0</v>
       </c>
-      <c r="H73" s="7">
+      <c r="H73" s="9">
         <v>200114.0</v>
       </c>
-      <c r="I73" s="14" t="s">
-        <v>13</v>
+      <c r="I73" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J73" s="11"/>
     </row>
@@ -3151,28 +3157,28 @@
       <c r="A74" s="19">
         <v>46233.0</v>
       </c>
-      <c r="B74" s="5" t="s">
-        <v>55</v>
+      <c r="B74" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D74" s="7">
+        <v>57</v>
+      </c>
+      <c r="D74" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E74" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F74" s="7">
+      <c r="E74" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F74" s="9">
         <v>158761.0</v>
       </c>
-      <c r="G74" s="7">
+      <c r="G74" s="9">
         <v>68908.0</v>
       </c>
-      <c r="H74" s="7">
+      <c r="H74" s="9">
         <v>183014.0</v>
       </c>
-      <c r="I74" s="14" t="s">
+      <c r="I74" s="13" t="s">
         <v>84</v>
       </c>
       <c r="J74" s="11" t="s">
@@ -3183,29 +3189,29 @@
       <c r="A75" s="19">
         <v>46233.0</v>
       </c>
-      <c r="B75" s="5" t="s">
-        <v>50</v>
+      <c r="B75" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D75" s="7">
+        <v>53</v>
+      </c>
+      <c r="D75" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F75" s="7">
+      <c r="E75" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F75" s="9">
         <v>117430.0</v>
       </c>
-      <c r="G75" s="7">
+      <c r="G75" s="9">
         <v>57323.0</v>
       </c>
-      <c r="H75" s="7">
+      <c r="H75" s="9">
         <v>86643.0</v>
       </c>
-      <c r="I75" s="14" t="s">
-        <v>25</v>
+      <c r="I75" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J75" s="11"/>
     </row>
@@ -3213,29 +3219,29 @@
       <c r="A76" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="10" t="s">
+      <c r="B76" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D76" s="7">
+      <c r="D76" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E76" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F76" s="7">
+      <c r="E76" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F76" s="9">
         <v>265693.0</v>
       </c>
-      <c r="G76" s="7">
+      <c r="G76" s="9">
         <v>83477.0</v>
       </c>
-      <c r="H76" s="7">
+      <c r="H76" s="9">
         <v>116000.0</v>
       </c>
-      <c r="I76" s="14" t="s">
-        <v>25</v>
+      <c r="I76" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J76" s="11"/>
     </row>
@@ -3243,29 +3249,29 @@
       <c r="A77" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C77" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D77" s="9">
         <v>112357.0</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F77" s="9">
         <v>720.0</v>
       </c>
-      <c r="G77" s="7">
+      <c r="G77" s="9">
         <v>360.0</v>
       </c>
-      <c r="H77" s="7">
+      <c r="H77" s="9">
         <v>2040.0</v>
       </c>
-      <c r="I77" s="14" t="s">
-        <v>13</v>
+      <c r="I77" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J77" s="11" t="s">
         <v>124</v>
@@ -3275,29 +3281,29 @@
       <c r="A78" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B78" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C78" s="10" t="s">
+      <c r="B78" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D78" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F78" s="9">
+        <v>5580.0</v>
+      </c>
+      <c r="G78" s="9">
+        <v>2192.0</v>
+      </c>
+      <c r="H78" s="9">
+        <v>3984.0</v>
+      </c>
+      <c r="I78" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D78" s="7">
-        <v>2110317.0</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F78" s="7">
-        <v>5580.0</v>
-      </c>
-      <c r="G78" s="7">
-        <v>2192.0</v>
-      </c>
-      <c r="H78" s="7">
-        <v>3984.0</v>
-      </c>
-      <c r="I78" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>125</v>
@@ -3307,29 +3313,29 @@
       <c r="A79" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B79" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C79" s="10" t="s">
+      <c r="B79" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D79" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" s="9">
+        <v>192903.0</v>
+      </c>
+      <c r="G79" s="9">
+        <v>150030.0</v>
+      </c>
+      <c r="H79" s="9">
+        <v>77501.0</v>
+      </c>
+      <c r="I79" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D79" s="7">
-        <v>2110202.0</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F79" s="7">
-        <v>192903.0</v>
-      </c>
-      <c r="G79" s="7">
-        <v>150030.0</v>
-      </c>
-      <c r="H79" s="7">
-        <v>77501.0</v>
-      </c>
-      <c r="I79" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="J79" s="11" t="s">
         <v>126</v>
@@ -3339,29 +3345,29 @@
       <c r="A80" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C80" s="10" t="s">
+      <c r="B80" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D80" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F80" s="9">
+        <v>152062.0</v>
+      </c>
+      <c r="G80" s="9">
+        <v>112769.0</v>
+      </c>
+      <c r="H80" s="9">
+        <v>124423.0</v>
+      </c>
+      <c r="I80" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="D80" s="7">
-        <v>2110302.0</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F80" s="7">
-        <v>152062.0</v>
-      </c>
-      <c r="G80" s="7">
-        <v>112769.0</v>
-      </c>
-      <c r="H80" s="7">
-        <v>124423.0</v>
-      </c>
-      <c r="I80" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>126</v>
@@ -3371,28 +3377,28 @@
       <c r="A81" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B81" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C81" s="10" t="s">
+      <c r="B81" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D81" s="7">
+      <c r="D81" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E81" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F81" s="7">
+      <c r="E81" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F81" s="9">
         <v>153692.0</v>
       </c>
-      <c r="G81" s="7">
+      <c r="G81" s="9">
         <v>136980.0</v>
       </c>
-      <c r="H81" s="7">
+      <c r="H81" s="9">
         <v>63920.0</v>
       </c>
-      <c r="I81" s="14" t="s">
+      <c r="I81" s="13" t="s">
         <v>84</v>
       </c>
       <c r="J81" s="11" t="s">
@@ -3403,28 +3409,28 @@
       <c r="A82" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D82" s="7">
+      <c r="D82" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E82" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" s="7">
+      <c r="E82" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="9">
         <v>45564.0</v>
       </c>
-      <c r="G82" s="7">
+      <c r="G82" s="9">
         <v>10456.0</v>
       </c>
-      <c r="H82" s="7">
+      <c r="H82" s="9">
         <v>40560.0</v>
       </c>
-      <c r="I82" s="14" t="s">
+      <c r="I82" s="13" t="s">
         <v>17</v>
       </c>
       <c r="J82" s="11"/>
@@ -3433,29 +3439,29 @@
       <c r="A83" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C83" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D83" s="7">
+      <c r="D83" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E83" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F83" s="7">
+      <c r="E83" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F83" s="9">
         <v>93517.0</v>
       </c>
-      <c r="G83" s="7">
+      <c r="G83" s="9">
         <v>18622.0</v>
       </c>
-      <c r="H83" s="7">
+      <c r="H83" s="9">
         <v>48804.0</v>
       </c>
-      <c r="I83" s="14" t="s">
-        <v>36</v>
+      <c r="I83" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J83" s="11" t="s">
         <v>130</v>
@@ -3465,29 +3471,29 @@
       <c r="A84" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B84" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C84" s="10" t="s">
+      <c r="B84" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="7">
+      <c r="D84" s="9">
         <v>2110317.0</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E84" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F84" s="9">
         <v>43200.0</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G84" s="9">
         <v>5340.0</v>
       </c>
-      <c r="H84" s="7">
+      <c r="H84" s="9">
         <v>40890.0</v>
       </c>
-      <c r="I84" s="14" t="s">
-        <v>25</v>
+      <c r="I84" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J84" s="11"/>
     </row>
@@ -3495,29 +3501,29 @@
       <c r="A85" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B85" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C85" s="10" t="s">
+      <c r="B85" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D85" s="7">
+      <c r="D85" s="9">
         <v>152384.0</v>
       </c>
-      <c r="E85" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F85" s="7">
+      <c r="E85" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F85" s="9">
         <v>25350.0</v>
       </c>
-      <c r="G85" s="7">
+      <c r="G85" s="9">
         <v>6240.0</v>
       </c>
-      <c r="H85" s="7">
+      <c r="H85" s="9">
         <v>30750.0</v>
       </c>
-      <c r="I85" s="14" t="s">
-        <v>36</v>
+      <c r="I85" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J85" s="11"/>
     </row>
@@ -3525,29 +3531,29 @@
       <c r="A86" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B86" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C86" s="10" t="s">
+      <c r="B86" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D86" s="7">
+      <c r="D86" s="9">
         <v>2152388.0</v>
       </c>
-      <c r="E86" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F86" s="7">
+      <c r="E86" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F86" s="9">
         <v>5040.0</v>
       </c>
-      <c r="G86" s="7">
+      <c r="G86" s="9">
         <v>720.0</v>
       </c>
-      <c r="H86" s="7">
+      <c r="H86" s="9">
         <v>4680.0</v>
       </c>
-      <c r="I86" s="14" t="s">
-        <v>25</v>
+      <c r="I86" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J86" s="11"/>
     </row>
@@ -3555,29 +3561,29 @@
       <c r="A87" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D87" s="7">
+      <c r="B87" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D87" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E87" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F87" s="7">
+      <c r="E87" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F87" s="9">
         <v>124423.0</v>
       </c>
-      <c r="G87" s="7">
+      <c r="G87" s="9">
         <v>60002.0</v>
       </c>
-      <c r="H87" s="7">
+      <c r="H87" s="9">
         <v>69217.0</v>
       </c>
-      <c r="I87" s="14" t="s">
-        <v>36</v>
+      <c r="I87" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J87" s="11" t="s">
         <v>131</v>
@@ -3587,29 +3593,29 @@
       <c r="A88" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B88" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C88" s="10" t="s">
+      <c r="B88" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D88" s="7">
+      <c r="D88" s="9">
         <v>152384.0</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F88" s="7">
+      <c r="E88" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F88" s="9">
         <v>30750.0</v>
       </c>
-      <c r="G88" s="7">
+      <c r="G88" s="9">
         <v>9975.0</v>
       </c>
-      <c r="H88" s="7">
+      <c r="H88" s="9">
         <v>36300.0</v>
       </c>
-      <c r="I88" s="14" t="s">
-        <v>21</v>
+      <c r="I88" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J88" s="11"/>
     </row>
@@ -3617,29 +3623,29 @@
       <c r="A89" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C89" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D89" s="7">
+      <c r="D89" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F89" s="7">
+      <c r="E89" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F89" s="9">
         <v>58320.0</v>
       </c>
-      <c r="G89" s="7">
+      <c r="G89" s="9">
         <v>53468.0</v>
       </c>
-      <c r="H89" s="7">
+      <c r="H89" s="9">
         <v>12480.0</v>
       </c>
-      <c r="I89" s="14" t="s">
-        <v>36</v>
+      <c r="I89" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J89" s="11" t="s">
         <v>132</v>
@@ -3649,29 +3655,29 @@
       <c r="A90" s="18">
         <v>46240.0</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C90" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E90" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F90" s="7">
+      <c r="E90" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F90" s="9">
         <v>254880.0</v>
       </c>
-      <c r="G90" s="7">
+      <c r="G90" s="9">
         <v>151786.0</v>
       </c>
-      <c r="H90" s="7">
+      <c r="H90" s="9">
         <v>27180.0</v>
       </c>
-      <c r="I90" s="14" t="s">
-        <v>13</v>
+      <c r="I90" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>133</v>
@@ -3681,29 +3687,29 @@
       <c r="A91" s="18">
         <v>46240.0</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C91" s="10" t="s">
+      <c r="B91" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C91" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D91" s="7">
+      <c r="D91" s="9">
         <v>112379.0</v>
       </c>
-      <c r="E91" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F91" s="7">
+      <c r="E91" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91" s="9">
         <v>13800.0</v>
       </c>
-      <c r="G91" s="7">
+      <c r="G91" s="9">
         <v>900.0</v>
       </c>
-      <c r="H91" s="7">
+      <c r="H91" s="9">
         <v>12132.0</v>
       </c>
-      <c r="I91" s="14" t="s">
-        <v>36</v>
+      <c r="I91" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J91" s="11"/>
     </row>
@@ -3711,29 +3717,29 @@
       <c r="A92" s="18">
         <v>46240.0</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C92" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D92" s="7">
+      <c r="D92" s="9">
         <v>2152388.0</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F92" s="7">
+      <c r="E92" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F92" s="9">
         <v>4575.0</v>
       </c>
-      <c r="G92" s="7">
+      <c r="G92" s="9">
         <v>570.0</v>
       </c>
-      <c r="H92" s="7">
+      <c r="H92" s="9">
         <v>4213.0</v>
       </c>
-      <c r="I92" s="14" t="s">
-        <v>13</v>
+      <c r="I92" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>135</v>
@@ -3743,29 +3749,29 @@
       <c r="A93" s="22">
         <v>46244.0</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B93" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C93" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D93" s="7">
+      <c r="D93" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E93" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F93" s="7">
+      <c r="E93" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F93" s="9">
         <v>222000.0</v>
       </c>
-      <c r="G93" s="7">
+      <c r="G93" s="9">
         <v>142780.0</v>
       </c>
-      <c r="H93" s="7">
+      <c r="H93" s="9">
         <v>312480.0</v>
       </c>
-      <c r="I93" s="14" t="s">
-        <v>36</v>
+      <c r="I93" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J93" s="11" t="s">
         <v>136</v>
@@ -3775,29 +3781,29 @@
       <c r="A94" s="22">
         <v>46244.0</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C94" s="10" t="s">
+      <c r="C94" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D94" s="7">
+      <c r="D94" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E94" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F94" s="7">
+      <c r="E94" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" s="9">
         <v>300060.0</v>
       </c>
-      <c r="G94" s="7">
+      <c r="G94" s="9">
         <v>265744.0</v>
       </c>
-      <c r="H94" s="7">
+      <c r="H94" s="9">
         <v>260696.0</v>
       </c>
-      <c r="I94" s="14" t="s">
-        <v>36</v>
+      <c r="I94" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>136</v>
@@ -3807,29 +3813,29 @@
       <c r="A95" s="22">
         <v>46244.0</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C95" s="10" t="s">
+      <c r="C95" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D95" s="7">
+      <c r="D95" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E95" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" s="7">
+      <c r="E95" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="9">
         <v>36240.0</v>
       </c>
-      <c r="G95" s="7">
+      <c r="G95" s="9">
         <v>10696.0</v>
       </c>
-      <c r="H95" s="7">
+      <c r="H95" s="9">
         <v>39840.0</v>
       </c>
-      <c r="I95" s="14" t="s">
-        <v>36</v>
+      <c r="I95" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J95" s="11" t="s">
         <v>136</v>
@@ -3839,29 +3845,29 @@
       <c r="A96" s="22">
         <v>46244.0</v>
       </c>
-      <c r="B96" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C96" s="10" t="s">
+      <c r="B96" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D96" s="7">
+      <c r="D96" s="9">
         <v>2110317.0</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="E96" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F96" s="7">
+      <c r="F96" s="9">
         <v>21690.0</v>
       </c>
-      <c r="G96" s="7">
+      <c r="G96" s="9">
         <v>13530.0</v>
       </c>
-      <c r="H96" s="7">
+      <c r="H96" s="9">
         <v>26280.0</v>
       </c>
-      <c r="I96" s="14" t="s">
-        <v>21</v>
+      <c r="I96" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="J96" s="11"/>
     </row>
@@ -3869,29 +3875,29 @@
       <c r="A97" s="4">
         <v>46245.0</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C97" s="10" t="s">
+      <c r="C97" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D97" s="7">
+      <c r="D97" s="9">
         <v>112271.0</v>
       </c>
-      <c r="E97" s="5" t="s">
+      <c r="E97" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F97" s="7">
+      <c r="F97" s="9">
         <v>20100.0</v>
       </c>
-      <c r="G97" s="7">
+      <c r="G97" s="9">
         <v>6795.0</v>
       </c>
-      <c r="H97" s="7">
+      <c r="H97" s="9">
         <v>10800.0</v>
       </c>
-      <c r="I97" s="14" t="s">
-        <v>25</v>
+      <c r="I97" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="J97" s="11"/>
     </row>
@@ -3899,29 +3905,29 @@
       <c r="A98" s="4">
         <v>46245.0</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="C98" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D98" s="7">
+      <c r="D98" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F98" s="7">
+      <c r="E98" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" s="9">
         <v>39840.0</v>
       </c>
-      <c r="G98" s="7">
+      <c r="G98" s="9">
         <v>5352.0</v>
       </c>
-      <c r="H98" s="7">
+      <c r="H98" s="9">
         <v>23520.0</v>
       </c>
-      <c r="I98" s="14" t="s">
-        <v>36</v>
+      <c r="I98" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>137</v>
@@ -3931,29 +3937,29 @@
       <c r="A99" s="4">
         <v>46245.0</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C99" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D99" s="7">
+      <c r="D99" s="9">
         <v>152384.0</v>
       </c>
-      <c r="E99" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F99" s="7">
+      <c r="E99" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F99" s="9">
         <v>18600.0</v>
       </c>
-      <c r="G99" s="7">
+      <c r="G99" s="9">
         <v>5550.0</v>
       </c>
-      <c r="H99" s="7">
+      <c r="H99" s="9">
         <v>12900.0</v>
       </c>
-      <c r="I99" s="14" t="s">
-        <v>36</v>
+      <c r="I99" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>138</v>
@@ -3963,45 +3969,149 @@
       <c r="A100" s="4">
         <v>46245.0</v>
       </c>
-      <c r="B100" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C100" s="10" t="s">
+      <c r="B100" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D100" s="7">
+      <c r="D100" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E100" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F100" s="7">
+      <c r="E100" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F100" s="9">
         <v>225620.0</v>
       </c>
-      <c r="G100" s="7">
+      <c r="G100" s="9">
         <v>74165.0</v>
       </c>
-      <c r="H100" s="7">
+      <c r="H100" s="9">
         <v>269040.0</v>
       </c>
-      <c r="I100" s="14" t="s">
-        <v>13</v>
+      <c r="I100" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="101">
-      <c r="I101" s="20"/>
-    </row>
-    <row r="102">
-      <c r="I102" s="20"/>
-    </row>
-    <row r="103">
-      <c r="I103" s="20"/>
-    </row>
-    <row r="104">
-      <c r="I104" s="20"/>
+    <row r="101" ht="22.5" customHeight="1">
+      <c r="A101" s="4">
+        <v>46246.0</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D101" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="9">
+        <v>423758.0</v>
+      </c>
+      <c r="G101" s="9">
+        <v>119016.0</v>
+      </c>
+      <c r="H101" s="9">
+        <v>638764.0</v>
+      </c>
+      <c r="I101" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="102" ht="22.5" customHeight="1">
+      <c r="A102" s="4">
+        <v>46246.0</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" s="21"/>
+      <c r="D102" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F102" s="9">
+        <v>800120.0</v>
+      </c>
+      <c r="G102" s="9">
+        <v>99529.0</v>
+      </c>
+      <c r="H102" s="9">
+        <v>655250.0</v>
+      </c>
+      <c r="I102" s="13"/>
+      <c r="J102" s="11"/>
+    </row>
+    <row r="103" ht="22.5" customHeight="1">
+      <c r="A103" s="4">
+        <v>46246.0</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" s="21"/>
+      <c r="D103" s="9">
+        <v>112271.0</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F103" s="9">
+        <v>10815.0</v>
+      </c>
+      <c r="G103" s="9">
+        <v>7725.0</v>
+      </c>
+      <c r="H103" s="9">
+        <v>1935.0</v>
+      </c>
+      <c r="I103" s="13"/>
+      <c r="J103" s="11"/>
+    </row>
+    <row r="104" ht="22.5" customHeight="1">
+      <c r="A104" s="4">
+        <v>46246.0</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F104" s="9">
+        <v>12900.0</v>
+      </c>
+      <c r="G104" s="9">
+        <v>3600.0</v>
+      </c>
+      <c r="H104" s="9">
+        <v>19800.0</v>
+      </c>
+      <c r="I104" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="J104" s="11" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="105">
       <c r="I105" s="20"/>
@@ -6714,13 +6824,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I100">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I104">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I101:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I105:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A100">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A104">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -6786,87 +6896,87 @@
       <c r="A2" s="4">
         <v>46224.0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7">
+      <c r="C2" s="7"/>
+      <c r="D2" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="E2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="9">
         <v>333.0</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="9">
         <v>6480.0</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="9">
         <v>3712.0</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>13</v>
+      <c r="I2" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
       <c r="A3" s="4">
         <v>46224.0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7">
+      <c r="C3" s="7"/>
+      <c r="D3" s="9">
         <v>2114158.0</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="9">
         <v>60.0</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="9">
         <v>1000.0</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="9">
         <v>60.0</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>21</v>
+      <c r="I3" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
       <c r="A4" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="7">
+      <c r="C4" s="14"/>
+      <c r="D4" s="9">
         <v>10501.0</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="9">
+        <v>415093.0</v>
+      </c>
+      <c r="G4" s="9">
+        <v>115920.0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>543038.0</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="F4" s="7">
-        <v>415093.0</v>
-      </c>
-      <c r="G4" s="7">
-        <v>115920.0</v>
-      </c>
-      <c r="H4" s="7">
-        <v>543038.0</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>25</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>27</v>
@@ -6876,207 +6986,207 @@
       <c r="A5" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="7">
+      <c r="C5" s="14"/>
+      <c r="D5" s="9">
         <v>112379.0</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="9">
+        <v>3000.0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>29400.0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>3000.0</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="F5" s="7">
-        <v>3000.0</v>
-      </c>
-      <c r="G5" s="7">
-        <v>29400.0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>3000.0</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
       <c r="A6" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="7">
+      <c r="C6" s="14"/>
+      <c r="D6" s="9">
         <v>112268.0</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="E6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="9">
         <v>3000.0</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="9">
         <v>12300.0</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <v>3300.0</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>13</v>
+      <c r="I6" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
       <c r="A7" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="7">
+      <c r="B7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="9">
         <v>132357.0</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="9">
         <v>1560.0</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="9">
         <v>1560.0</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="9">
         <v>4560.0</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>13</v>
+      <c r="I7" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
       <c r="A8" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="7">
+      <c r="C8" s="14"/>
+      <c r="D8" s="9">
         <v>2152388.0</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="9">
         <v>720.0</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="9">
         <v>11160.0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="9">
         <v>5940.0</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>13</v>
+      <c r="I8" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
       <c r="A9" s="4">
         <v>46225.0</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="7">
+      <c r="C9" s="14"/>
+      <c r="D9" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="9">
         <v>3712.0</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="9">
         <v>46723.0</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="9">
         <v>213.0</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>13</v>
+      <c r="I9" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
       <c r="A10" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="7">
+      <c r="C10" s="14"/>
+      <c r="D10" s="9">
         <v>73001.0</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="9">
         <v>73787.0</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="9">
         <v>72000.0</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="9">
         <v>109487.0</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>13</v>
+      <c r="I10" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
       <c r="A11" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="7">
+      <c r="C11" s="14"/>
+      <c r="D11" s="9">
         <v>112268.0</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="9">
         <v>3300.0</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="9">
         <v>1800.0</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="9">
         <v>3300.0</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>21</v>
+      <c r="I11" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="11"/>
     </row>
@@ -7084,27 +7194,27 @@
       <c r="A12" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="7">
+      <c r="C12" s="14"/>
+      <c r="D12" s="9">
         <v>112379.0</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="9">
         <v>4200.0</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="9">
         <v>7500.0</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="9">
         <v>3900.0</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>21</v>
+      <c r="I12" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J12" s="11"/>
     </row>
@@ -7112,87 +7222,87 @@
       <c r="A13" s="4">
         <v>46226.0</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="7">
+      <c r="B13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="9">
         <v>379471.0</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="9">
         <v>392580.0</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="9">
         <v>357186.0</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>13</v>
+      <c r="I13" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
       <c r="A14" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="7">
+      <c r="C14" s="14"/>
+      <c r="D14" s="9">
         <v>72001.0</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="9">
         <v>21905.0</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="9">
         <v>47670.0</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="9">
         <v>38000.0</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>13</v>
+      <c r="I14" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
       <c r="A15" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="7">
+      <c r="C15" s="14"/>
+      <c r="D15" s="9">
         <v>2110327.0</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E15" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="9">
         <v>69120.0</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="9">
         <v>57600.0</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="9">
         <v>40320.0</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>13</v>
+      <c r="I15" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>58</v>
@@ -7202,27 +7312,27 @@
       <c r="A16" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="7">
+      <c r="C16" s="14"/>
+      <c r="D16" s="9">
         <v>112379.0</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="E16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="9">
         <v>3900.0</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="9">
         <v>102600.0</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="9">
         <v>1500.0</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>21</v>
+      <c r="I16" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J16" s="11"/>
     </row>
@@ -7230,27 +7340,27 @@
       <c r="A17" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="7">
+      <c r="C17" s="14"/>
+      <c r="D17" s="9">
         <v>2152388.0</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="E17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="9">
         <v>720.0</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="9">
         <v>9720.0</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="9">
         <v>2580.0</v>
       </c>
-      <c r="I17" s="9" t="s">
-        <v>21</v>
+      <c r="I17" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J17" s="11"/>
     </row>
@@ -7258,27 +7368,27 @@
       <c r="A18" s="4">
         <v>46227.0</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="7">
+      <c r="C18" s="14"/>
+      <c r="D18" s="9">
         <v>112268.0</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="E18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="9">
         <v>3300.0</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="9">
         <v>30600.0</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="9">
         <v>600.0</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>13</v>
+      <c r="I18" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>60</v>
@@ -7288,87 +7398,87 @@
       <c r="A19" s="4">
         <v>46230.0</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="7">
+      <c r="B19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="9">
         <v>2410401.0</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="9">
         <v>136538.0</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="9">
         <v>34080.0</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="9">
         <v>213000.0</v>
       </c>
-      <c r="I19" s="9" t="s">
-        <v>13</v>
+      <c r="I19" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
       <c r="A20" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="7">
+      <c r="B20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="7">
+      <c r="E20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="9">
         <v>591750.0</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="9">
         <v>239760.0</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="9">
         <v>577207.0</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>13</v>
+      <c r="I20" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
       <c r="A21" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="7">
+      <c r="B21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="9">
         <v>10601.0</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="9">
         <v>1230.0</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="9">
         <v>8626.0</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="9">
         <v>1958.0</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>13</v>
+      <c r="I21" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>65</v>
@@ -7378,27 +7488,27 @@
       <c r="A22" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="7">
+      <c r="C22" s="14"/>
+      <c r="D22" s="9">
         <v>2152388.0</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="E22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="9">
         <v>4320.0</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="9">
         <v>2700.0</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="9">
         <v>3420.0</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>13</v>
+      <c r="I22" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J22" s="11"/>
     </row>
@@ -7406,27 +7516,27 @@
       <c r="A23" s="4">
         <v>46231.0</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="7">
+      <c r="C23" s="14"/>
+      <c r="D23" s="9">
         <v>114357.0</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="E23" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="9">
         <v>240.0</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="9">
         <v>52320.0</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="9">
         <v>240.0</v>
       </c>
-      <c r="I23" s="9" t="s">
-        <v>13</v>
+      <c r="I23" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J23" s="11"/>
     </row>
@@ -7434,27 +7544,27 @@
       <c r="A24" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="7">
+      <c r="B24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="9">
         <v>10501.0</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="E24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="9">
         <v>19663.0</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="9">
         <v>49540.0</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="9">
         <v>29632.0</v>
       </c>
-      <c r="I24" s="9" t="s">
-        <v>13</v>
+      <c r="I24" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J24" s="11"/>
     </row>
@@ -7462,27 +7572,27 @@
       <c r="A25" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="7">
+      <c r="C25" s="14"/>
+      <c r="D25" s="9">
         <v>112268.0</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="9">
         <v>5700.0</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="9">
         <v>34800.0</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="9">
         <v>5100.0</v>
       </c>
-      <c r="I25" s="9" t="s">
-        <v>13</v>
+      <c r="I25" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J25" s="11"/>
     </row>
@@ -7490,27 +7600,27 @@
       <c r="A26" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="7">
+      <c r="C26" s="14"/>
+      <c r="D26" s="9">
         <v>2110317.0</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="9">
         <v>720.0</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="9">
         <v>7920.0</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="9">
         <v>720.0</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>13</v>
+      <c r="I26" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J26" s="11"/>
     </row>
@@ -7518,27 +7628,27 @@
       <c r="A27" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="7">
+      <c r="C27" s="14"/>
+      <c r="D27" s="9">
         <v>2114357.0</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="9">
         <v>432.0</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="9">
         <v>576.0</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="9">
         <v>432.0</v>
       </c>
-      <c r="I27" s="9" t="s">
-        <v>13</v>
+      <c r="I27" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J27" s="11"/>
     </row>
@@ -7546,27 +7656,27 @@
       <c r="A28" s="4">
         <v>46232.0</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="7">
+      <c r="C28" s="14"/>
+      <c r="D28" s="9">
         <v>10501.0</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E28" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="9">
         <v>219540.0</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="9">
         <v>272160.0</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="9">
         <v>16698.0</v>
       </c>
-      <c r="I28" s="9" t="s">
-        <v>13</v>
+      <c r="I28" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J28" s="11"/>
     </row>
@@ -7574,27 +7684,27 @@
       <c r="A29" s="4">
         <v>46233.0</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="7">
+      <c r="C29" s="14"/>
+      <c r="D29" s="9">
         <v>112268.0</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="E29" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="9">
         <v>5100.0</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="9">
         <v>3300.0</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="9">
         <v>4800.0</v>
       </c>
-      <c r="I29" s="9" t="s">
-        <v>36</v>
+      <c r="I29" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="J29" s="11"/>
     </row>
@@ -7602,27 +7712,27 @@
       <c r="A30" s="4">
         <v>46233.0</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="7">
+      <c r="C30" s="14"/>
+      <c r="D30" s="9">
         <v>114357.0</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F30" s="7">
+      <c r="E30" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="9">
         <v>240.0</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="9">
         <v>7800.0</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="9">
         <v>1560.0</v>
       </c>
-      <c r="I30" s="9" t="s">
-        <v>36</v>
+      <c r="I30" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="J30" s="11"/>
     </row>
@@ -7630,27 +7740,27 @@
       <c r="A31" s="4">
         <v>46233.0</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="7">
+      <c r="B31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="9">
         <v>10601.0</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="9">
         <v>7717.0</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="9">
         <v>10080.0</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="9">
         <v>12867.0</v>
       </c>
-      <c r="I31" s="9" t="s">
-        <v>13</v>
+      <c r="I31" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>77</v>
@@ -7660,27 +7770,27 @@
       <c r="A32" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="7">
+      <c r="B32" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="9">
         <v>79110.0</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="9">
         <v>48000.0</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="9">
         <v>24600.0</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="9">
         <v>36300.0</v>
       </c>
-      <c r="I32" s="9" t="s">
-        <v>25</v>
+      <c r="I32" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J32" s="16" t="s">
         <v>79</v>
@@ -7690,27 +7800,27 @@
       <c r="A33" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="7">
+      <c r="C33" s="14"/>
+      <c r="D33" s="9">
         <v>10501.0</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="E33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="9">
         <v>95574.0</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="9">
         <v>78469.0</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="9">
         <v>142801.0</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>13</v>
+      <c r="I33" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J33" s="16" t="s">
         <v>80</v>
@@ -7720,27 +7830,27 @@
       <c r="A34" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="7">
+      <c r="C34" s="14"/>
+      <c r="D34" s="9">
         <v>73001.0</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F34" s="7">
+      <c r="E34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" s="9">
         <v>73367.0</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="9">
         <v>94608.0</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="9">
         <v>39150.0</v>
       </c>
-      <c r="I34" s="9" t="s">
-        <v>13</v>
+      <c r="I34" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J34" s="11"/>
     </row>
@@ -7748,27 +7858,27 @@
       <c r="A35" s="4">
         <v>46234.0</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="7">
+      <c r="C35" s="14"/>
+      <c r="D35" s="9">
         <v>112357.0</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="9">
         <v>840.0</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="9">
         <v>5160.0</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="9">
         <v>480.0</v>
       </c>
-      <c r="I35" s="9" t="s">
-        <v>13</v>
+      <c r="I35" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J35" s="11"/>
     </row>
@@ -7776,27 +7886,27 @@
       <c r="A36" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="7">
+      <c r="C36" s="14"/>
+      <c r="D36" s="9">
         <v>10601.0</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="9">
         <v>17934.0</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="9">
         <v>64980.0</v>
       </c>
-      <c r="H36" s="7">
+      <c r="H36" s="9">
         <v>21714.0</v>
       </c>
-      <c r="I36" s="9" t="s">
-        <v>13</v>
+      <c r="I36" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>83</v>
@@ -7806,27 +7916,27 @@
       <c r="A37" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="7">
+      <c r="C37" s="14"/>
+      <c r="D37" s="9">
         <v>2110202.0</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F37" s="7">
+      <c r="E37" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="9">
         <v>194520.0</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="9">
         <v>84060.0</v>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="9">
         <v>122840.0</v>
       </c>
-      <c r="I37" s="9" t="s">
-        <v>25</v>
+      <c r="I37" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J37" s="11"/>
     </row>
@@ -7834,27 +7944,27 @@
       <c r="A38" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="7">
+      <c r="C38" s="14"/>
+      <c r="D38" s="9">
         <v>114379.0</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F38" s="7">
+      <c r="E38" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F38" s="9">
         <v>52200.0</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="9">
         <v>16200.0</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38" s="9">
         <v>7500.0</v>
       </c>
-      <c r="I38" s="9" t="s">
-        <v>36</v>
+      <c r="I38" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="J38" s="11"/>
     </row>
@@ -7862,27 +7972,27 @@
       <c r="A39" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="13"/>
-      <c r="D39" s="7">
+      <c r="C39" s="14"/>
+      <c r="D39" s="9">
         <v>2110317.0</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="9">
         <v>6450.0</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="9">
         <v>16920.0</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="9">
         <v>6480.0</v>
       </c>
-      <c r="I39" s="9" t="s">
-        <v>25</v>
+      <c r="I39" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J39" s="11"/>
     </row>
@@ -7890,27 +8000,27 @@
       <c r="A40" s="18">
         <v>46237.0</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="7">
+      <c r="C40" s="14"/>
+      <c r="D40" s="9">
         <v>2010102.0</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F40" s="7">
+      <c r="E40" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F40" s="9">
         <v>1398.0</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="9">
         <v>1320.0</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40" s="9">
         <v>438.0</v>
       </c>
-      <c r="I40" s="9" t="s">
-        <v>25</v>
+      <c r="I40" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J40" s="11"/>
     </row>
@@ -7918,26 +8028,26 @@
       <c r="A41" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="13"/>
-      <c r="D41" s="7">
+      <c r="C41" s="14"/>
+      <c r="D41" s="9">
         <v>2152388.0</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="7">
+      <c r="E41" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" s="9">
         <v>2460.0</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="9">
         <v>17640.0</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41" s="9">
         <v>3240.0</v>
       </c>
-      <c r="I41" s="9" t="s">
+      <c r="I41" s="10" t="s">
         <v>17</v>
       </c>
       <c r="J41" s="11"/>
@@ -7946,27 +8056,27 @@
       <c r="A42" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="13"/>
-      <c r="D42" s="7">
+      <c r="C42" s="14"/>
+      <c r="D42" s="9">
         <v>112268.0</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F42" s="7">
+      <c r="E42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" s="9">
         <v>3600.0</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="9">
         <v>1500.0</v>
       </c>
-      <c r="H42" s="7">
+      <c r="H42" s="9">
         <v>3900.0</v>
       </c>
-      <c r="I42" s="9" t="s">
-        <v>25</v>
+      <c r="I42" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J42" s="11"/>
     </row>
@@ -7974,27 +8084,27 @@
       <c r="A43" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="13"/>
-      <c r="D43" s="7">
+      <c r="C43" s="14"/>
+      <c r="D43" s="9">
         <v>114379.0</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F43" s="7">
+      <c r="E43" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="9">
         <v>7500.0</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="9">
         <v>54900.0</v>
       </c>
-      <c r="H43" s="7">
+      <c r="H43" s="9">
         <v>8400.0</v>
       </c>
-      <c r="I43" s="9" t="s">
-        <v>21</v>
+      <c r="I43" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J43" s="11"/>
     </row>
@@ -8002,27 +8112,27 @@
       <c r="A44" s="4">
         <v>46238.0</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="7">
+      <c r="C44" s="14"/>
+      <c r="D44" s="9">
         <v>114357.0</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F44" s="7">
+      <c r="E44" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F44" s="9">
         <v>240.0</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="9">
         <v>7680.0</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="9">
         <v>360.0</v>
       </c>
-      <c r="I44" s="9" t="s">
-        <v>21</v>
+      <c r="I44" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J44" s="11"/>
     </row>
@@ -8030,27 +8140,27 @@
       <c r="A45" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="13"/>
-      <c r="D45" s="7">
+      <c r="C45" s="14"/>
+      <c r="D45" s="9">
         <v>10601.0</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="9">
         <v>1115.0</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="9">
         <v>5267.0</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H45" s="9">
         <v>1590.0</v>
       </c>
-      <c r="I45" s="9" t="s">
-        <v>13</v>
+      <c r="I45" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>91</v>
@@ -8060,27 +8170,27 @@
       <c r="A46" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C46" s="13"/>
-      <c r="D46" s="7">
+      <c r="C46" s="14"/>
+      <c r="D46" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F46" s="7">
+      <c r="E46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46" s="9">
         <v>114240.0</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46" s="9">
         <v>79680.0</v>
       </c>
-      <c r="H46" s="7">
+      <c r="H46" s="9">
         <v>191130.0</v>
       </c>
-      <c r="I46" s="9" t="s">
-        <v>25</v>
+      <c r="I46" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J46" s="11"/>
     </row>
@@ -8088,27 +8198,27 @@
       <c r="A47" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C47" s="13"/>
-      <c r="D47" s="7">
+      <c r="C47" s="14"/>
+      <c r="D47" s="9">
         <v>2112207.0</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F47" s="7">
+      <c r="E47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" s="9">
         <v>1800.0</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="9">
         <v>1800.0</v>
       </c>
-      <c r="H47" s="7">
+      <c r="H47" s="9">
         <v>1980.0</v>
       </c>
-      <c r="I47" s="9" t="s">
-        <v>36</v>
+      <c r="I47" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="J47" s="11"/>
     </row>
@@ -8116,27 +8226,27 @@
       <c r="A48" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="7">
+      <c r="C48" s="14"/>
+      <c r="D48" s="9">
         <v>112268.0</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F48" s="7">
+      <c r="E48" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" s="9">
         <v>3900.0</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="9">
         <v>34200.0</v>
       </c>
-      <c r="H48" s="7">
+      <c r="H48" s="9">
         <v>1200.0</v>
       </c>
-      <c r="I48" s="9" t="s">
-        <v>36</v>
+      <c r="I48" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="J48" s="11"/>
     </row>
@@ -8144,27 +8254,27 @@
       <c r="A49" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="13"/>
-      <c r="D49" s="7">
+      <c r="C49" s="14"/>
+      <c r="D49" s="9">
         <v>112357.0</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="9">
         <v>600.0</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G49" s="9">
         <v>8400.0</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49" s="9">
         <v>600.0</v>
       </c>
-      <c r="I49" s="9" t="s">
-        <v>36</v>
+      <c r="I49" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="J49" s="11"/>
     </row>
@@ -8172,27 +8282,27 @@
       <c r="A50" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="13"/>
-      <c r="D50" s="7">
+      <c r="C50" s="14"/>
+      <c r="D50" s="9">
         <v>114268.0</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F50" s="7">
+      <c r="E50" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F50" s="9">
         <v>2700.0</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G50" s="9">
         <v>5700.0</v>
       </c>
-      <c r="H50" s="7">
+      <c r="H50" s="9">
         <v>300.0</v>
       </c>
-      <c r="I50" s="9" t="s">
-        <v>36</v>
+      <c r="I50" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="J50" s="11"/>
     </row>
@@ -8200,56 +8310,56 @@
       <c r="A51" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C51" s="13"/>
-      <c r="D51" s="7">
+      <c r="B51" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="14"/>
+      <c r="D51" s="9">
         <v>10501.0</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F51" s="7">
+      <c r="E51" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="9">
         <v>68651.0</v>
       </c>
-      <c r="G51" s="7">
+      <c r="G51" s="9">
         <v>64050.0</v>
       </c>
-      <c r="H51" s="7">
+      <c r="H51" s="9">
         <v>13421.0</v>
       </c>
-      <c r="I51" s="9" t="s">
-        <v>13</v>
+      <c r="I51" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="7">
+      <c r="B52" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="14"/>
+      <c r="D52" s="9">
         <v>72003.0</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F52" s="7">
+      <c r="E52" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F52" s="9">
         <v>1391.0</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G52" s="9">
         <v>3885.0</v>
       </c>
-      <c r="H52" s="7">
+      <c r="H52" s="9">
         <v>2407.0</v>
       </c>
-      <c r="I52" s="9" t="s">
+      <c r="I52" s="10" t="s">
         <v>17</v>
       </c>
       <c r="J52" s="11"/>
@@ -8258,57 +8368,57 @@
       <c r="A53" s="4">
         <v>46239.0</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C53" s="13"/>
-      <c r="D53" s="7">
+      <c r="B53" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53" s="14"/>
+      <c r="D53" s="9">
         <v>2110402.0</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="7">
+      <c r="E53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9">
         <v>2974.0</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G53" s="9">
         <v>1200.0</v>
       </c>
-      <c r="H53" s="7">
+      <c r="H53" s="9">
         <v>3317.0</v>
       </c>
-      <c r="I53" s="9" t="s">
-        <v>13</v>
+      <c r="I53" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="18">
         <v>46240.0</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="13"/>
-      <c r="D54" s="7">
+      <c r="C54" s="14"/>
+      <c r="D54" s="9">
         <v>112379.0</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F54" s="7">
+      <c r="E54" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54" s="9">
         <v>3600.0</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G54" s="9">
         <v>26100.0</v>
       </c>
-      <c r="H54" s="7">
+      <c r="H54" s="9">
         <v>6900.0</v>
       </c>
-      <c r="I54" s="9" t="s">
-        <v>21</v>
+      <c r="I54" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J54" s="11"/>
     </row>
@@ -8316,27 +8426,27 @@
       <c r="A55" s="18">
         <v>46240.0</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C55" s="13"/>
-      <c r="D55" s="7">
+      <c r="C55" s="14"/>
+      <c r="D55" s="9">
         <v>73001.0</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F55" s="7">
+      <c r="E55" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F55" s="9">
         <v>2415.0</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G55" s="9">
         <v>26490.0</v>
       </c>
-      <c r="H55" s="7">
+      <c r="H55" s="9">
         <v>2415.0</v>
       </c>
-      <c r="I55" s="9" t="s">
-        <v>21</v>
+      <c r="I55" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J55" s="11"/>
     </row>
@@ -8344,27 +8454,27 @@
       <c r="A56" s="18">
         <v>46240.0</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="7">
+      <c r="C56" s="14"/>
+      <c r="D56" s="9">
         <v>112357.0</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="9">
         <v>600.0</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="9">
         <v>3960.0</v>
       </c>
-      <c r="H56" s="7">
+      <c r="H56" s="9">
         <v>600.0</v>
       </c>
-      <c r="I56" s="9" t="s">
-        <v>21</v>
+      <c r="I56" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J56" s="11"/>
     </row>
@@ -8372,27 +8482,27 @@
       <c r="A57" s="18">
         <v>46240.0</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="13"/>
-      <c r="D57" s="7">
+      <c r="C57" s="14"/>
+      <c r="D57" s="9">
         <v>114379.0</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F57" s="7">
+      <c r="E57" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F57" s="9">
         <v>2400.0</v>
       </c>
-      <c r="G57" s="7">
+      <c r="G57" s="9">
         <v>15000.0</v>
       </c>
-      <c r="H57" s="7">
+      <c r="H57" s="9">
         <v>300.0</v>
       </c>
-      <c r="I57" s="9" t="s">
-        <v>21</v>
+      <c r="I57" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J57" s="11"/>
     </row>
@@ -8400,27 +8510,27 @@
       <c r="A58" s="18">
         <v>46244.0</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="13"/>
-      <c r="D58" s="7">
+      <c r="C58" s="14"/>
+      <c r="D58" s="9">
         <v>112379.0</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F58" s="7">
+      <c r="E58" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58" s="9">
         <v>4800.0</v>
       </c>
-      <c r="G58" s="7">
+      <c r="G58" s="9">
         <v>41100.0</v>
       </c>
-      <c r="H58" s="7">
+      <c r="H58" s="9">
         <v>5100.0</v>
       </c>
-      <c r="I58" s="9" t="s">
-        <v>21</v>
+      <c r="I58" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J58" s="11"/>
     </row>
@@ -8428,32 +8538,57 @@
       <c r="A59" s="4">
         <v>46245.0</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="13"/>
-      <c r="D59" s="7">
+      <c r="C59" s="14"/>
+      <c r="D59" s="9">
         <v>2110302.0</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F59" s="7">
+      <c r="E59" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F59" s="9">
         <v>25574.0</v>
       </c>
-      <c r="G59" s="7">
+      <c r="G59" s="9">
         <v>75840.0</v>
       </c>
-      <c r="H59" s="7">
+      <c r="H59" s="9">
         <v>42960.0</v>
       </c>
-      <c r="I59" s="9" t="s">
-        <v>25</v>
+      <c r="I59" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="J59" s="11"/>
     </row>
-    <row r="60">
-      <c r="I60" s="20"/>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="4">
+        <v>46246.0</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="14"/>
+      <c r="D60" s="9">
+        <v>114379.0</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F60" s="9">
+        <v>6900.0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>7200.0</v>
+      </c>
+      <c r="H60" s="9">
+        <v>5400.0</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J60" s="11"/>
     </row>
     <row r="61">
       <c r="I61" s="20"/>
@@ -11157,13 +11292,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I59">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I60">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I60:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I61:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A59">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A60">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="155">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -62,88 +62,115 @@
     <t>7. Otro</t>
   </si>
   <si>
+    <t>2. Error De Registro De Inventario</t>
+  </si>
+  <si>
     <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
   </si>
   <si>
-    <t>2. Error De Registro De Inventario</t>
+    <t>TAT MONTERIA</t>
   </si>
   <si>
     <t>LANZA</t>
   </si>
   <si>
-    <t>TAT MONTERIA</t>
-  </si>
-  <si>
     <t>LUIS LOPEZ</t>
   </si>
   <si>
     <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
+    <t>3. Falla De Rotación</t>
+  </si>
+  <si>
     <t>6. Transformación De Referencias</t>
   </si>
   <si>
     <t>Pendiente Transformar Roto GT Por manipulación</t>
   </si>
   <si>
-    <t>3. Falla De Rotación</t>
+    <t>TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>FABIO GOMEZ</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
   </si>
   <si>
     <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
-    <t>TAT MEDELLIN</t>
-  </si>
-  <si>
     <t>se equivocaron al cargar una estiba</t>
   </si>
   <si>
-    <t>FABIO GOMEZ</t>
+    <t>TAT CARTAGENA</t>
+  </si>
+  <si>
+    <t>Dilan Barraza</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
     <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
+    <t>4. Exigencia Del Cliente (Edad)</t>
+  </si>
+  <si>
+    <t>Venta FS</t>
+  </si>
+  <si>
     <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
   </si>
   <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
-  </si>
-  <si>
     <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
+    <t>Se dejó lote para revisión por calidad</t>
+  </si>
+  <si>
     <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
   </si>
   <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>PALMAS</t>
   </si>
   <si>
+    <t>Se envía más fresco a Rionegro</t>
+  </si>
+  <si>
     <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
-    <t>TAT CARTAGENA</t>
-  </si>
-  <si>
-    <t>Dilan Barraza</t>
-  </si>
-  <si>
     <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+  </si>
+  <si>
+    <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
     <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
-    <t>4. Exigencia Del Cliente (Edad)</t>
+    <t>TAT CALI</t>
+  </si>
+  <si>
+    <t>DIEGO ROJAS</t>
   </si>
   <si>
     <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
-    <t>Venta FS</t>
+    <t>TAT CUCUTA</t>
+  </si>
+  <si>
+    <t>ALEXANDER PEÑA</t>
   </si>
   <si>
     <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
@@ -152,46 +179,40 @@
     <t>HUEVO PICADO ROJO</t>
   </si>
   <si>
-    <t>Se dejó lote para revisión por calidad</t>
-  </si>
-  <si>
     <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>Se envía más fresco a Rionegro</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
-  </si>
-  <si>
-    <t>1. Ingreso Por Devolución</t>
-  </si>
-  <si>
-    <t>TAT CALI</t>
-  </si>
-  <si>
-    <t>DIEGO ROJAS</t>
+    <t>Clientes FS</t>
+  </si>
+  <si>
+    <t>Envío huevo fresco a Sincelejo</t>
+  </si>
+  <si>
+    <t>Transformación de PET</t>
+  </si>
+  <si>
+    <t>ANDRES MEJIA</t>
   </si>
   <si>
     <t>HUEVO SUCIO DE JAULA</t>
   </si>
   <si>
+    <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
+  </si>
+  <si>
+    <t>TAT POPAYAN</t>
+  </si>
+  <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
   </si>
   <si>
-    <t>TAT CUCUTA</t>
-  </si>
-  <si>
-    <t>ALEXANDER PEÑA</t>
+    <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
     <t>Esta para despacho hoy</t>
   </si>
   <si>
-    <t>Clientes FS</t>
+    <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
     <t>Cola de programación</t>
@@ -203,31 +224,25 @@
     <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
   </si>
   <si>
-    <t>Envío huevo fresco a Sincelejo</t>
+    <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
     <t>HUEVO CX30 CARTON GRIS</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+  </si>
+  <si>
     <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
   </si>
   <si>
-    <t>Transformación de PET</t>
-  </si>
-  <si>
     <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
-    <t>ANDRES MEJIA</t>
-  </si>
-  <si>
-    <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
-  </si>
-  <si>
-    <t>TAT POPAYAN</t>
-  </si>
-  <si>
-    <t>JONATHAN MOSQUERA</t>
+    <t>5. Ingreso De Planta</t>
+  </si>
+  <si>
+    <t>Se despacha par FS con producto más nuevo</t>
   </si>
   <si>
     <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
@@ -236,15 +251,18 @@
     <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
-    <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
+    <t>ANDREA QUIROGA</t>
+  </si>
+  <si>
+    <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
+  </si>
+  <si>
+    <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
     <t>ALKA1</t>
   </si>
   <si>
-    <t>Producto con novedades de calidad, se está bandejeando</t>
-  </si>
-  <si>
     <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
   </si>
   <si>
@@ -257,7 +275,10 @@
     <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+    <t>TAT PASTO</t>
+  </si>
+  <si>
+    <t>CAROLINA VITERI</t>
   </si>
   <si>
     <t>HUEVO L X 12 PET CAJA X 120</t>
@@ -266,37 +287,43 @@
     <t>Cargo en incubación</t>
   </si>
   <si>
-    <t>5. Ingreso De Planta</t>
-  </si>
-  <si>
-    <t>Se despacha par FS con producto más nuevo</t>
+    <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
     <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>ANDREA QUIROGA</t>
-  </si>
-  <si>
-    <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
-  </si>
-  <si>
-    <t>Se despacha producto más nuevo para Rionegro</t>
+    <t>Pedido para villavicencio</t>
+  </si>
+  <si>
+    <t>Se entrega inventario nuevo para FS</t>
+  </si>
+  <si>
+    <t>Inventario de Asesor de Rionegro que renuncio</t>
+  </si>
+  <si>
+    <t>TAT BARRANQUILLA</t>
+  </si>
+  <si>
+    <t>Jhonatan Gomez</t>
   </si>
   <si>
     <t>BELLAVISTA</t>
   </si>
   <si>
+    <t>Lote mezclado en la misma estiba</t>
+  </si>
+  <si>
     <t>Traslado a cedi, producto de devolución</t>
   </si>
   <si>
+    <t>Supera edad solicitada clientes grandes superficies</t>
+  </si>
+  <si>
     <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
-    <t>TAT PASTO</t>
-  </si>
-  <si>
-    <t>CAROLINA VITERI</t>
+    <t>Pedido para villacicencio</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
@@ -305,45 +332,18 @@
     <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
   </si>
   <si>
+    <t>Se envía huevo más fresco a Sincelejo</t>
+  </si>
+  <si>
     <t>HUEVO SUCIO ZF MARCADO</t>
   </si>
   <si>
-    <t>Asignacion a canal Tat para sugeridos de hoy</t>
+    <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
   </si>
   <si>
     <t>vehiculo con flata de capacidad / TAT cali</t>
   </si>
   <si>
-    <t>Pedido para villavicencio</t>
-  </si>
-  <si>
-    <t>Se entrega inventario nuevo para FS</t>
-  </si>
-  <si>
-    <t>Inventario de Asesor de Rionegro que renuncio</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA</t>
-  </si>
-  <si>
-    <t>Jhonatan Gomez</t>
-  </si>
-  <si>
-    <t>Lote mezclado en la misma estiba</t>
-  </si>
-  <si>
-    <t>Supera edad solicitada clientes grandes superficies</t>
-  </si>
-  <si>
-    <t>Pedido para villacicencio</t>
-  </si>
-  <si>
-    <t>Se envía huevo más fresco a Sincelejo</t>
-  </si>
-  <si>
-    <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
-  </si>
-  <si>
     <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
   </si>
   <si>
@@ -359,12 +359,24 @@
     <t>Devolucion de huevo de 12 dias en mal estado</t>
   </si>
   <si>
+    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
+  </si>
+  <si>
+    <t>vehiculo pendiente pro llegar a planta</t>
+  </si>
+  <si>
     <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
   </si>
   <si>
     <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
+    <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
+  </si>
+  <si>
+    <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
+  </si>
+  <si>
     <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
   </si>
   <si>
@@ -438,6 +450,33 @@
   </si>
   <si>
     <t xml:space="preserve">Se registraron edades antes de sacar el sugerido del dia </t>
+  </si>
+  <si>
+    <t>LLegada de planta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asignado canal TAT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yovanis Arevalo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">salida de pedido especial </t>
+  </si>
+  <si>
+    <t>novedad en lotes por calidad</t>
+  </si>
+  <si>
+    <t>Producto no recibido en Rionegro pr calidad, se va a revisar</t>
+  </si>
+  <si>
+    <t>Productoenviado a Rionegro más fresco</t>
+  </si>
+  <si>
+    <t>DIANA VITERIA</t>
+  </si>
+  <si>
+    <t>ERROR EN DIGITACION DE LAS EDAD</t>
   </si>
 </sst>
 </file>
@@ -501,7 +540,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -535,11 +574,11 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -550,11 +589,11 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -568,6 +607,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,13 +671,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Plantas-style">
+    <tableStyle count="4" pivot="0" name="Cedis-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Cedis-style">
+    <tableStyle count="4" pivot="0" name="Plantas-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -658,7 +700,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J104" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J114" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -676,7 +718,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J60" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J66" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -963,8 +1005,8 @@
       <c r="H2" s="9">
         <v>206140.0</v>
       </c>
-      <c r="I2" s="12" t="s">
-        <v>17</v>
+      <c r="I2" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
@@ -972,7 +1014,7 @@
         <v>46205.0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>20</v>
@@ -993,7 +1035,7 @@
         <v>260675.0</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J3" s="7"/>
     </row>
@@ -1002,16 +1044,16 @@
         <v>46205.0</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D4" s="9">
         <v>2110217.0</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F4" s="9">
         <v>21120.0</v>
@@ -1023,7 +1065,7 @@
         <v>16920.0</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J4" s="7"/>
     </row>
@@ -1032,16 +1074,16 @@
         <v>46205.0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D5" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F5" s="9">
         <v>75680.0</v>
@@ -1053,10 +1095,10 @@
         <v>3134.0</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>43</v>
+        <v>34</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
@@ -1064,10 +1106,10 @@
         <v>46206.0</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D6" s="9">
         <v>2110202.0</v>
@@ -1087,8 +1129,8 @@
       <c r="I6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>46</v>
+      <c r="J6" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
@@ -1096,16 +1138,16 @@
         <v>46206.0</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D7" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F7" s="9">
         <v>20640.0</v>
@@ -1117,10 +1159,10 @@
         <v>13920.0</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>49</v>
+        <v>34</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
@@ -1128,16 +1170,16 @@
         <v>46206.0</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D8" s="9">
         <v>152384.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F8" s="9">
         <v>14700.0</v>
@@ -1149,19 +1191,19 @@
         <v>9600.0</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="J8" s="12"/>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
       <c r="A9" s="4">
         <v>46206.0</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D9" s="9">
         <v>2110202.0</v>
@@ -1179,25 +1221,25 @@
         <v>124260.0</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="J9" s="12"/>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
       <c r="A10" s="4">
         <v>46206.0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D10" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F10" s="9">
         <v>7830.0</v>
@@ -1209,7 +1251,7 @@
         <v>6030.0</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="15"/>
     </row>
@@ -1218,10 +1260,10 @@
         <v>46206.0</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D11" s="9">
         <v>2110402.0</v>
@@ -1239,10 +1281,10 @@
         <v>23040.0</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>59</v>
+        <v>34</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
@@ -1250,7 +1292,7 @@
         <v>46206.0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>20</v>
@@ -1259,7 +1301,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>51387.0</v>
@@ -1271,10 +1313,10 @@
         <v>12170.0</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>63</v>
+        <v>34</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
@@ -1282,7 +1324,7 @@
         <v>46209.0</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>20</v>
@@ -1303,10 +1345,10 @@
         <v>133410.0</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>63</v>
+        <v>34</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
@@ -1314,10 +1356,10 @@
         <v>46209.0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D14" s="9">
         <v>2110402.0</v>
@@ -1335,10 +1377,10 @@
         <v>424588.0</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>66</v>
+        <v>23</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
@@ -1346,16 +1388,16 @@
         <v>46209.0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F15" s="9">
         <v>14160.0</v>
@@ -1369,8 +1411,8 @@
       <c r="I15" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="11" t="s">
-        <v>69</v>
+      <c r="J15" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
@@ -1378,16 +1420,16 @@
         <v>46210.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F16" s="9">
         <v>149040.0</v>
@@ -1399,25 +1441,25 @@
         <v>289680.0</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
       <c r="A17" s="4">
         <v>46210.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D17" s="9">
         <v>2110217.0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F17" s="9">
         <v>22770.0</v>
@@ -1429,25 +1471,25 @@
         <v>19770.0</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
       <c r="A18" s="4">
         <v>46210.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D18" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F18" s="9">
         <v>222021.0</v>
@@ -1459,19 +1501,19 @@
         <v>162125.0</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="J18" s="12"/>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
       <c r="A19" s="4">
         <v>46211.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D19" s="9">
         <v>2110402.0</v>
@@ -1491,8 +1533,8 @@
       <c r="I19" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="11" t="s">
-        <v>74</v>
+      <c r="J19" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
@@ -1500,7 +1542,7 @@
         <v>46211.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>20</v>
@@ -1521,25 +1563,25 @@
         <v>74040.0</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="J20" s="12"/>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
       <c r="A21" s="4">
         <v>46211.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D21" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F21" s="9">
         <v>162125.0</v>
@@ -1553,8 +1595,8 @@
       <c r="I21" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="11" t="s">
-        <v>76</v>
+      <c r="J21" s="12" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
@@ -1571,7 +1613,7 @@
         <v>152384.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F22" s="9">
         <v>32850.0</v>
@@ -1583,25 +1625,25 @@
         <v>32700.0</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J22" s="11"/>
+        <v>34</v>
+      </c>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
       <c r="A23" s="4">
         <v>46211.0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D23" s="9">
         <v>112271.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F23" s="9">
         <v>16500.0</v>
@@ -1613,19 +1655,19 @@
         <v>18000.0</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J23" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
       <c r="A24" s="4">
         <v>46212.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="D24" s="9">
         <v>2110202.0</v>
@@ -1643,25 +1685,25 @@
         <v>248481.0</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J24" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
       <c r="A25" s="4">
         <v>46212.0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>68</v>
+        <v>25</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="D25" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F25" s="9">
         <v>178080.0</v>
@@ -1673,19 +1715,19 @@
         <v>203520.0</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J25" s="11"/>
+        <v>75</v>
+      </c>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
       <c r="A26" s="4">
         <v>46212.0</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>68</v>
+        <v>25</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="D26" s="9">
         <v>2110402.0</v>
@@ -1703,10 +1745,10 @@
         <v>13200.0</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>85</v>
+        <v>34</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
@@ -1714,16 +1756,16 @@
         <v>46212.0</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>68</v>
+        <v>25</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="D27" s="9">
         <v>112271.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F27" s="9">
         <v>18000.0</v>
@@ -1735,9 +1777,9 @@
         <v>13500.0</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
       <c r="A28" s="4">
@@ -1746,14 +1788,14 @@
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="17" t="s">
-        <v>87</v>
+      <c r="C28" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D28" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F28" s="9">
         <v>208440.0</v>
@@ -1767,8 +1809,8 @@
       <c r="I28" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="11" t="s">
-        <v>88</v>
+      <c r="J28" s="12" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
@@ -1778,8 +1820,8 @@
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="17" t="s">
-        <v>87</v>
+      <c r="C29" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D29" s="9">
         <v>2110202.0</v>
@@ -1799,8 +1841,8 @@
       <c r="I29" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="11" t="s">
-        <v>88</v>
+      <c r="J29" s="12" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
@@ -1808,10 +1850,10 @@
         <v>46213.0</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>68</v>
+        <v>25</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="D30" s="9">
         <v>2110202.0</v>
@@ -1829,10 +1871,10 @@
         <v>381600.0</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>89</v>
+        <v>34</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
@@ -1840,16 +1882,16 @@
         <v>46213.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>71</v>
+        <v>62</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>64</v>
       </c>
       <c r="D31" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F31" s="9">
         <v>316800.0</v>
@@ -1861,25 +1903,25 @@
         <v>229680.0</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
       <c r="A32" s="4">
         <v>46213.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="D32" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F32" s="9">
         <v>176850.0</v>
@@ -1891,19 +1933,19 @@
         <v>128971.0</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J32" s="11"/>
+        <v>46</v>
+      </c>
+      <c r="J32" s="12"/>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
       <c r="A33" s="4">
         <v>46213.0</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>71</v>
+        <v>62</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>64</v>
       </c>
       <c r="D33" s="9">
         <v>2110402.0</v>
@@ -1921,25 +1963,25 @@
         <v>25440.0</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J33" s="12"/>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
       <c r="A34" s="4">
         <v>46217.0</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D34" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F34" s="9">
         <v>481440.0</v>
@@ -1951,19 +1993,19 @@
         <v>151435.0</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J34" s="12"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
       <c r="A35" s="4">
         <v>46217.0</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D35" s="9">
         <v>2110202.0</v>
@@ -1981,9 +2023,9 @@
         <v>302760.0</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
       <c r="A36" s="4">
@@ -1992,14 +2034,14 @@
       <c r="B36" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="17" t="s">
-        <v>87</v>
+      <c r="C36" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D36" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F36" s="9">
         <v>35280.0</v>
@@ -2011,10 +2053,10 @@
         <v>37926.0</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
@@ -2024,14 +2066,14 @@
       <c r="B37" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="17" t="s">
-        <v>87</v>
+      <c r="C37" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D37" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F37" s="9">
         <v>272073.0</v>
@@ -2043,10 +2085,10 @@
         <v>275205.0</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>100</v>
+        <v>34</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
@@ -2056,14 +2098,14 @@
       <c r="B38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="17" t="s">
-        <v>87</v>
+      <c r="C38" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D38" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F38" s="9">
         <v>37926.0</v>
@@ -2075,10 +2117,10 @@
         <v>25746.0</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
@@ -2086,10 +2128,10 @@
         <v>46218.0</v>
       </c>
       <c r="B39" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D39" s="9">
         <v>2110402.0</v>
@@ -2107,10 +2149,10 @@
         <v>16320.0</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>101</v>
+        <v>34</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
@@ -2118,16 +2160,16 @@
         <v>46218.0</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D40" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F40" s="9">
         <v>10980.0</v>
@@ -2139,25 +2181,25 @@
         <v>13500.0</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J40" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J40" s="12"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
       <c r="A41" s="4">
         <v>46219.0</v>
       </c>
       <c r="B41" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>26</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>28</v>
       </c>
       <c r="D41" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F41" s="9">
         <v>130320.0</v>
@@ -2169,10 +2211,10 @@
         <v>90480.0</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>102</v>
+        <v>46</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
@@ -2180,16 +2222,16 @@
         <v>46219.0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>104</v>
+        <v>96</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>97</v>
       </c>
       <c r="D42" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F42" s="9">
         <v>36225.0</v>
@@ -2201,25 +2243,25 @@
         <v>27570.0</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="J42" s="12"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
       <c r="A43" s="4">
         <v>46219.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="D43" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F43" s="9">
         <v>152833.0</v>
@@ -2231,10 +2273,10 @@
         <v>96472.0</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>105</v>
+        <v>75</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
@@ -2242,16 +2284,16 @@
         <v>46219.0</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>88</v>
       </c>
       <c r="D44" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F44" s="9">
         <v>237828.0</v>
@@ -2263,9 +2305,9 @@
         <v>71560.0</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J44" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J44" s="12"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
       <c r="A45" s="4">
@@ -2274,14 +2316,14 @@
       <c r="B45" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C45" s="17" t="s">
-        <v>87</v>
+      <c r="C45" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D45" s="9">
         <v>152384.0</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F45" s="9">
         <v>31125.0</v>
@@ -2293,10 +2335,10 @@
         <v>31845.0</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>106</v>
+        <v>34</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
@@ -2306,14 +2348,14 @@
       <c r="B46" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="17" t="s">
-        <v>87</v>
+      <c r="C46" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D46" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F46" s="9">
         <v>25746.0</v>
@@ -2325,10 +2367,10 @@
         <v>28683.0</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
@@ -2338,14 +2380,14 @@
       <c r="B47" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="17" t="s">
-        <v>87</v>
+      <c r="C47" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D47" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F47" s="9">
         <v>261166.0</v>
@@ -2357,10 +2399,10 @@
         <v>221549.0</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>107</v>
+        <v>34</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
@@ -2370,14 +2412,14 @@
       <c r="B48" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="17" t="s">
-        <v>87</v>
+      <c r="C48" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D48" s="9">
         <v>2110217.0</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F48" s="9">
         <v>115289.0</v>
@@ -2389,18 +2431,18 @@
         <v>119584.0</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J48" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J48" s="12"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
       <c r="A49" s="4">
         <v>46224.0</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D49" s="9">
@@ -2419,10 +2461,10 @@
         <v>287235.0</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>108</v>
+        <v>34</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
@@ -2430,10 +2472,10 @@
         <v>46224.0</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>104</v>
+        <v>96</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>97</v>
       </c>
       <c r="D50" s="9">
         <v>2110402.0</v>
@@ -2453,8 +2495,8 @@
       <c r="I50" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J50" s="11" t="s">
-        <v>109</v>
+      <c r="J50" s="12" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
@@ -2462,16 +2504,16 @@
         <v>46225.0</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D51" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F51" s="9">
         <v>130560.0</v>
@@ -2483,9 +2525,9 @@
         <v>153840.0</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J51" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" s="12" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2494,16 +2536,16 @@
         <v>46225.0</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D52" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F52" s="9">
         <v>87447.0</v>
@@ -2515,9 +2557,9 @@
         <v>104365.0</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J52" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J52" s="12"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
       <c r="A53" s="4">
@@ -2526,8 +2568,8 @@
       <c r="B53" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="17" t="s">
-        <v>87</v>
+      <c r="C53" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D53" s="9">
         <v>2110402.0</v>
@@ -2545,9 +2587,9 @@
         <v>25920.0</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" s="12" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2556,7 +2598,7 @@
         <v>46226.0</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>112</v>
@@ -2577,9 +2619,9 @@
         <v>226069.0</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J54" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J54" s="12" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2588,10 +2630,10 @@
         <v>46226.0</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D55" s="9">
         <v>2110202.0</v>
@@ -2609,19 +2651,19 @@
         <v>700200.0</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J55" s="11"/>
+        <v>75</v>
+      </c>
+      <c r="J55" s="12"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
       <c r="A56" s="4">
         <v>46227.0</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D56" s="9">
         <v>2110202.0</v>
@@ -2639,16 +2681,16 @@
         <v>668440.0</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J56" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J56" s="12"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
       <c r="A57" s="4">
         <v>46227.0</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>112</v>
@@ -2669,9 +2711,9 @@
         <v>326391.0</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J57" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J57" s="12" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2680,10 +2722,10 @@
         <v>46227.0</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D58" s="9">
         <v>2110202.0</v>
@@ -2701,19 +2743,19 @@
         <v>128160.0</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J58" s="11"/>
+        <v>75</v>
+      </c>
+      <c r="J58" s="12"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
       <c r="A59" s="4">
         <v>46227.0</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D59" s="9">
         <v>2110402.0</v>
@@ -2733,8 +2775,8 @@
       <c r="I59" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J59" s="11" t="s">
-        <v>115</v>
+      <c r="J59" s="12" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
@@ -2742,16 +2784,16 @@
         <v>46230.0</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D60" s="9">
         <v>2110403.0</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F60" s="9">
         <v>9960.0</v>
@@ -2763,9 +2805,9 @@
         <v>3660.0</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J60" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J60" s="12"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
       <c r="A61" s="4">
@@ -2774,14 +2816,14 @@
       <c r="B61" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C61" s="17" t="s">
-        <v>87</v>
+      <c r="C61" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D61" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F61" s="9">
         <v>306720.0</v>
@@ -2793,19 +2835,19 @@
         <v>247096.0</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J61" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J61" s="12"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
       <c r="A62" s="4">
         <v>46230.0</v>
       </c>
       <c r="B62" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D62" s="9">
         <v>2110202.0</v>
@@ -2823,10 +2865,10 @@
         <v>353700.0</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>117</v>
+        <v>34</v>
+      </c>
+      <c r="J62" s="12" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
@@ -2834,7 +2876,7 @@
         <v>46231.0</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>20</v>
@@ -2855,10 +2897,10 @@
         <v>375549.0</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>118</v>
+        <v>34</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
@@ -2866,16 +2908,16 @@
         <v>46231.0</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D64" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F64" s="9">
         <v>238497.0</v>
@@ -2887,10 +2929,10 @@
         <v>181858.0</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>119</v>
+        <v>46</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
@@ -2898,16 +2940,16 @@
         <v>46231.0</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D65" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F65" s="9">
         <v>8190.0</v>
@@ -2919,10 +2961,10 @@
         <v>7200.0</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>119</v>
+        <v>46</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
@@ -2930,10 +2972,10 @@
         <v>46231.0</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D66" s="9">
         <v>2110202.0</v>
@@ -2951,10 +2993,10 @@
         <v>98850.0</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>119</v>
+        <v>46</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
@@ -2962,7 +3004,7 @@
         <v>46232.0</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C67" s="21"/>
       <c r="D67" s="9">
@@ -2983,14 +3025,14 @@
       <c r="I67" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J67" s="11"/>
+      <c r="J67" s="12"/>
     </row>
     <row r="68" ht="22.5" hidden="1" customHeight="1">
       <c r="A68" s="4">
         <v>46232.0</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C68" s="21"/>
       <c r="D68" s="9">
@@ -3011,14 +3053,14 @@
       <c r="I68" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J68" s="11"/>
+      <c r="J68" s="12"/>
     </row>
     <row r="69" ht="22.5" hidden="1" customHeight="1">
       <c r="A69" s="4">
         <v>46232.0</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C69" s="21"/>
       <c r="D69" s="9">
@@ -3039,21 +3081,21 @@
       <c r="I69" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J69" s="11"/>
+      <c r="J69" s="12"/>
     </row>
     <row r="70" ht="22.5" hidden="1" customHeight="1">
       <c r="A70" s="4">
         <v>46232.0</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C70" s="21"/>
       <c r="D70" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F70" s="9">
         <v>5913.0</v>
@@ -3067,7 +3109,7 @@
       <c r="I70" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J70" s="11"/>
+      <c r="J70" s="12"/>
     </row>
     <row r="71" ht="22.5" hidden="1" customHeight="1">
       <c r="A71" s="4">
@@ -3081,7 +3123,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F71" s="9">
         <v>256613.0</v>
@@ -3095,7 +3137,7 @@
       <c r="I71" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J71" s="11"/>
+      <c r="J71" s="12"/>
     </row>
     <row r="72" ht="22.5" hidden="1" customHeight="1">
       <c r="A72" s="4">
@@ -3109,7 +3151,7 @@
         <v>152384.0</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F72" s="9">
         <v>21300.0</v>
@@ -3123,14 +3165,14 @@
       <c r="I72" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J72" s="11"/>
+      <c r="J72" s="12"/>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
       <c r="A73" s="4">
         <v>46232.0</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C73" s="21"/>
       <c r="D73" s="9">
@@ -3151,23 +3193,23 @@
       <c r="I73" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J73" s="11"/>
+      <c r="J73" s="12"/>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
       <c r="A74" s="19">
         <v>46233.0</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C74" s="17" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="D74" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F74" s="9">
         <v>158761.0</v>
@@ -3179,10 +3221,10 @@
         <v>183014.0</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>121</v>
+        <v>75</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
@@ -3190,16 +3232,16 @@
         <v>46233.0</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C75" s="17" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="D75" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F75" s="9">
         <v>117430.0</v>
@@ -3211,9 +3253,9 @@
         <v>86643.0</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J75" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J75" s="12"/>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
       <c r="A76" s="4">
@@ -3223,13 +3265,13 @@
         <v>11</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D76" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F76" s="9">
         <v>265693.0</v>
@@ -3241,25 +3283,25 @@
         <v>116000.0</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J76" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J76" s="12"/>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
       <c r="A77" s="4">
         <v>46234.0</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D77" s="9">
         <v>112357.0</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F77" s="9">
         <v>720.0</v>
@@ -3273,8 +3315,8 @@
       <c r="I77" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J77" s="11" t="s">
-        <v>124</v>
+      <c r="J77" s="12" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
@@ -3282,16 +3324,16 @@
         <v>46234.0</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D78" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F78" s="9">
         <v>5580.0</v>
@@ -3303,10 +3345,10 @@
         <v>3984.0</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J78" s="11" t="s">
-        <v>125</v>
+        <v>46</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="79" ht="22.5" hidden="1" customHeight="1">
@@ -3314,10 +3356,10 @@
         <v>46237.0</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D79" s="9">
         <v>2110202.0</v>
@@ -3335,10 +3377,10 @@
         <v>77501.0</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>126</v>
+        <v>46</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="80" ht="22.5" hidden="1" customHeight="1">
@@ -3346,16 +3388,16 @@
         <v>46237.0</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D80" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F80" s="9">
         <v>152062.0</v>
@@ -3367,10 +3409,10 @@
         <v>124423.0</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>126</v>
+        <v>46</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="81" ht="22.5" hidden="1" customHeight="1">
@@ -3378,16 +3420,16 @@
         <v>46237.0</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D81" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F81" s="9">
         <v>153692.0</v>
@@ -3399,10 +3441,10 @@
         <v>63920.0</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>128</v>
+        <v>75</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="82" ht="22.5" hidden="1" customHeight="1">
@@ -3410,10 +3452,10 @@
         <v>46237.0</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D82" s="9">
         <v>2110402.0</v>
@@ -3431,16 +3473,16 @@
         <v>40560.0</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="J82" s="12"/>
     </row>
     <row r="83" ht="22.5" hidden="1" customHeight="1">
       <c r="A83" s="18">
         <v>46237.0</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>20</v>
@@ -3449,7 +3491,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F83" s="9">
         <v>93517.0</v>
@@ -3461,13 +3503,13 @@
         <v>48804.0</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="84" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="84" ht="22.5" hidden="1" customHeight="1">
       <c r="A84" s="4">
         <v>46238.0</v>
       </c>
@@ -3475,13 +3517,13 @@
         <v>11</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D84" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F84" s="9">
         <v>43200.0</v>
@@ -3493,11 +3535,11 @@
         <v>40890.0</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J84" s="11"/>
-    </row>
-    <row r="85" ht="22.5" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="J84" s="12"/>
+    </row>
+    <row r="85" ht="22.5" hidden="1" customHeight="1">
       <c r="A85" s="4">
         <v>46238.0</v>
       </c>
@@ -3505,13 +3547,13 @@
         <v>11</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D85" s="9">
         <v>152384.0</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F85" s="9">
         <v>25350.0</v>
@@ -3523,11 +3565,11 @@
         <v>30750.0</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J85" s="11"/>
-    </row>
-    <row r="86" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J85" s="12"/>
+    </row>
+    <row r="86" ht="22.5" hidden="1" customHeight="1">
       <c r="A86" s="4">
         <v>46238.0</v>
       </c>
@@ -3535,13 +3577,13 @@
         <v>11</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D86" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F86" s="9">
         <v>5040.0</v>
@@ -3553,25 +3595,25 @@
         <v>4680.0</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J86" s="11"/>
-    </row>
-    <row r="87" ht="22.5" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="J86" s="12"/>
+    </row>
+    <row r="87" ht="22.5" hidden="1" customHeight="1">
       <c r="A87" s="4">
         <v>46238.0</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D87" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F87" s="9">
         <v>124423.0</v>
@@ -3583,13 +3625,13 @@
         <v>69217.0</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="88" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="88" ht="22.5" hidden="1" customHeight="1">
       <c r="A88" s="4">
         <v>46239.0</v>
       </c>
@@ -3597,13 +3639,13 @@
         <v>11</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D88" s="9">
         <v>152384.0</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F88" s="9">
         <v>30750.0</v>
@@ -3615,25 +3657,25 @@
         <v>36300.0</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J88" s="11"/>
-    </row>
-    <row r="89" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J88" s="12"/>
+    </row>
+    <row r="89" ht="22.5" hidden="1" customHeight="1">
       <c r="A89" s="4">
         <v>46239.0</v>
       </c>
       <c r="B89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D89" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F89" s="9">
         <v>58320.0</v>
@@ -3645,21 +3687,21 @@
         <v>12480.0</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J89" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="90" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J89" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="90" ht="22.5" hidden="1" customHeight="1">
       <c r="A90" s="18">
         <v>46240.0</v>
       </c>
       <c r="B90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D90" s="9">
         <v>2110202.0</v>
@@ -3679,25 +3721,25 @@
       <c r="I90" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J90" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="91" ht="22.5" customHeight="1">
+      <c r="J90" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="91" ht="22.5" hidden="1" customHeight="1">
       <c r="A91" s="18">
         <v>46240.0</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D91" s="9">
         <v>112379.0</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F91" s="9">
         <v>13800.0</v>
@@ -3709,25 +3751,25 @@
         <v>12132.0</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J91" s="11"/>
-    </row>
-    <row r="92" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J91" s="12"/>
+    </row>
+    <row r="92" ht="22.5" hidden="1" customHeight="1">
       <c r="A92" s="18">
         <v>46240.0</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D92" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F92" s="9">
         <v>4575.0</v>
@@ -3741,25 +3783,25 @@
       <c r="I92" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J92" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="93" ht="22.5" customHeight="1">
+      <c r="J92" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="93" ht="22.5" hidden="1" customHeight="1">
       <c r="A93" s="22">
         <v>46244.0</v>
       </c>
       <c r="B93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D93" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F93" s="9">
         <v>222000.0</v>
@@ -3771,21 +3813,21 @@
         <v>312480.0</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J93" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="94" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J93" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="94" ht="22.5" hidden="1" customHeight="1">
       <c r="A94" s="22">
         <v>46244.0</v>
       </c>
       <c r="B94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D94" s="9">
         <v>2110202.0</v>
@@ -3803,21 +3845,21 @@
         <v>260696.0</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J94" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="95" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J94" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="95" ht="22.5" hidden="1" customHeight="1">
       <c r="A95" s="22">
         <v>46244.0</v>
       </c>
       <c r="B95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D95" s="9">
         <v>2110402.0</v>
@@ -3835,13 +3877,13 @@
         <v>39840.0</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J95" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="96" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J95" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="96" ht="22.5" hidden="1" customHeight="1">
       <c r="A96" s="22">
         <v>46244.0</v>
       </c>
@@ -3849,13 +3891,13 @@
         <v>11</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D96" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F96" s="9">
         <v>21690.0</v>
@@ -3867,25 +3909,25 @@
         <v>26280.0</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J96" s="11"/>
-    </row>
-    <row r="97" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J96" s="12"/>
+    </row>
+    <row r="97" ht="22.5" hidden="1" customHeight="1">
       <c r="A97" s="4">
         <v>46245.0</v>
       </c>
       <c r="B97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C97" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D97" s="9">
         <v>112271.0</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F97" s="9">
         <v>20100.0</v>
@@ -3897,19 +3939,19 @@
         <v>10800.0</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J97" s="11"/>
-    </row>
-    <row r="98" ht="22.5" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="J97" s="12"/>
+    </row>
+    <row r="98" ht="22.5" hidden="1" customHeight="1">
       <c r="A98" s="4">
         <v>46245.0</v>
       </c>
       <c r="B98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D98" s="9">
         <v>2110402.0</v>
@@ -3927,27 +3969,27 @@
         <v>23520.0</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J98" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="99" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J98" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="99" ht="22.5" hidden="1" customHeight="1">
       <c r="A99" s="4">
         <v>46245.0</v>
       </c>
       <c r="B99" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D99" s="9">
         <v>152384.0</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F99" s="9">
         <v>18600.0</v>
@@ -3959,13 +4001,13 @@
         <v>12900.0</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J99" s="11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="100" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J99" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" ht="22.5" hidden="1" customHeight="1">
       <c r="A100" s="4">
         <v>46245.0</v>
       </c>
@@ -3973,13 +4015,13 @@
         <v>11</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D100" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F100" s="9">
         <v>225620.0</v>
@@ -3993,8 +4035,8 @@
       <c r="I100" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J100" s="11" t="s">
-        <v>139</v>
+      <c r="J100" s="12" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="101" ht="22.5" customHeight="1">
@@ -4002,10 +4044,10 @@
         <v>46246.0</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D101" s="9">
         <v>2110402.0</v>
@@ -4023,10 +4065,10 @@
         <v>638764.0</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" s="11" t="s">
-        <v>141</v>
+        <v>16</v>
+      </c>
+      <c r="J101" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="102" ht="22.5" customHeight="1">
@@ -4036,7 +4078,9 @@
       <c r="B102" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C102" s="21"/>
+      <c r="C102" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="D102" s="9">
         <v>2110202.0</v>
       </c>
@@ -4052,8 +4096,12 @@
       <c r="H102" s="9">
         <v>655250.0</v>
       </c>
-      <c r="I102" s="13"/>
-      <c r="J102" s="11"/>
+      <c r="I102" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J102" s="12" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="4">
@@ -4062,12 +4110,14 @@
       <c r="B103" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C103" s="21"/>
+      <c r="C103" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="D103" s="9">
         <v>112271.0</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F103" s="9">
         <v>10815.0</v>
@@ -4078,24 +4128,28 @@
       <c r="H103" s="9">
         <v>1935.0</v>
       </c>
-      <c r="I103" s="13"/>
-      <c r="J103" s="11"/>
+      <c r="I103" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J103" s="12" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="4">
         <v>46246.0</v>
       </c>
       <c r="B104" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D104" s="9">
         <v>152384.0</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F104" s="9">
         <v>12900.0</v>
@@ -4107,41 +4161,289 @@
         <v>19800.0</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J104" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="I105" s="20"/>
-    </row>
-    <row r="106">
-      <c r="I106" s="20"/>
-    </row>
-    <row r="107">
-      <c r="I107" s="20"/>
-    </row>
-    <row r="108">
-      <c r="I108" s="20"/>
-    </row>
-    <row r="109">
-      <c r="I109" s="20"/>
-    </row>
-    <row r="110">
-      <c r="I110" s="20"/>
-    </row>
-    <row r="111">
-      <c r="I111" s="20"/>
-    </row>
-    <row r="112">
-      <c r="I112" s="20"/>
-    </row>
-    <row r="113">
-      <c r="I113" s="20"/>
-    </row>
-    <row r="114">
-      <c r="I114" s="20"/>
+        <v>34</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="105" ht="22.5" customHeight="1">
+      <c r="A105" s="4">
+        <v>46247.0</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D105" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F105" s="9">
+        <v>193026.0</v>
+      </c>
+      <c r="G105" s="9">
+        <v>2970.0</v>
+      </c>
+      <c r="H105" s="9">
+        <v>63824.0</v>
+      </c>
+      <c r="I105" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J105" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="106" ht="22.5" customHeight="1">
+      <c r="A106" s="4">
+        <v>46247.0</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C106" s="21"/>
+      <c r="D106" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106" s="9">
+        <v>245520.0</v>
+      </c>
+      <c r="G106" s="9">
+        <v>149087.0</v>
+      </c>
+      <c r="H106" s="9">
+        <v>230580.0</v>
+      </c>
+      <c r="I106" s="13"/>
+      <c r="J106" s="12"/>
+    </row>
+    <row r="107" ht="22.5" customHeight="1">
+      <c r="A107" s="4">
+        <v>46247.0</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C107" s="21"/>
+      <c r="D107" s="9">
+        <v>2110217.0</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F107" s="9">
+        <v>21120.0</v>
+      </c>
+      <c r="G107" s="9">
+        <v>11430.0</v>
+      </c>
+      <c r="H107" s="9">
+        <v>17280.0</v>
+      </c>
+      <c r="I107" s="13"/>
+      <c r="J107" s="12"/>
+    </row>
+    <row r="108" ht="22.5" customHeight="1">
+      <c r="A108" s="4">
+        <v>46247.0</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108" s="21"/>
+      <c r="D108" s="9">
+        <v>112271.0</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F108" s="9">
+        <v>16500.0</v>
+      </c>
+      <c r="G108" s="9">
+        <v>3552.0</v>
+      </c>
+      <c r="H108" s="9">
+        <v>12600.0</v>
+      </c>
+      <c r="I108" s="13"/>
+      <c r="J108" s="12"/>
+    </row>
+    <row r="109" ht="22.5" customHeight="1">
+      <c r="A109" s="4">
+        <v>46248.0</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" s="21"/>
+      <c r="D109" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F109" s="9">
+        <v>793976.0</v>
+      </c>
+      <c r="G109" s="9">
+        <v>90730.0</v>
+      </c>
+      <c r="H109" s="9">
+        <v>584490.0</v>
+      </c>
+      <c r="I109" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J109" s="12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="110" ht="22.5" customHeight="1">
+      <c r="A110" s="4">
+        <v>46248.0</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D110" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F110" s="9">
+        <v>289920.0</v>
+      </c>
+      <c r="G110" s="9">
+        <v>47417.0</v>
+      </c>
+      <c r="H110" s="9">
+        <v>247440.0</v>
+      </c>
+      <c r="I110" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J110" s="12"/>
+    </row>
+    <row r="111" ht="22.5" customHeight="1">
+      <c r="A111" s="4">
+        <v>46248.0</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D111" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F111" s="9">
+        <v>230580.0</v>
+      </c>
+      <c r="G111" s="9">
+        <v>142342.0</v>
+      </c>
+      <c r="H111" s="9">
+        <v>298620.0</v>
+      </c>
+      <c r="I111" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J111" s="12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="112" ht="22.5" customHeight="1">
+      <c r="A112" s="4">
+        <v>46248.0</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D112" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F112" s="9">
+        <v>13200.0</v>
+      </c>
+      <c r="G112" s="9">
+        <v>6075.0</v>
+      </c>
+      <c r="H112" s="9">
+        <v>7200.0</v>
+      </c>
+      <c r="I112" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J112" s="12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="113" ht="22.5" customHeight="1">
+      <c r="A113" s="4">
+        <v>46248.0</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D113" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F113" s="9">
+        <v>9900.0</v>
+      </c>
+      <c r="G113" s="9">
+        <v>1800.0</v>
+      </c>
+      <c r="H113" s="9">
+        <v>8100.0</v>
+      </c>
+      <c r="I113" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J113" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="114" ht="22.5" customHeight="1">
+      <c r="A114" s="23"/>
+      <c r="B114" s="21"/>
+      <c r="C114" s="21"/>
+      <c r="D114" s="21"/>
+      <c r="E114" s="21"/>
+      <c r="F114" s="21"/>
+      <c r="G114" s="21"/>
+      <c r="H114" s="21"/>
+      <c r="I114" s="13"/>
+      <c r="J114" s="12"/>
     </row>
     <row r="115">
       <c r="I115" s="20"/>
@@ -6824,13 +7126,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I104">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I114">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I105:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I115:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A104">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A114">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -6918,8 +7220,8 @@
       <c r="I2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="11" t="s">
-        <v>16</v>
+      <c r="J2" s="12" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
@@ -6927,7 +7229,7 @@
         <v>46224.0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="9">
@@ -6946,10 +7248,10 @@
         <v>60.0</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="11" t="s">
         <v>23</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
@@ -6964,7 +7266,7 @@
         <v>10501.0</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4" s="9">
         <v>415093.0</v>
@@ -6976,10 +7278,10 @@
         <v>543038.0</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
@@ -6994,7 +7296,7 @@
         <v>112379.0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F5" s="9">
         <v>3000.0</v>
@@ -7008,8 +7310,8 @@
       <c r="I5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>30</v>
+      <c r="J5" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
@@ -7017,14 +7319,14 @@
         <v>46225.0</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="9">
         <v>112268.0</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F6" s="9">
         <v>3000.0</v>
@@ -7038,8 +7340,8 @@
       <c r="I6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>33</v>
+      <c r="J6" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
@@ -7047,14 +7349,14 @@
         <v>46225.0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="9">
         <v>132357.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F7" s="9">
         <v>1560.0</v>
@@ -7068,8 +7370,8 @@
       <c r="I7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>38</v>
+      <c r="J7" s="12" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
@@ -7077,14 +7379,14 @@
         <v>46225.0</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F8" s="9">
         <v>720.0</v>
@@ -7098,8 +7400,8 @@
       <c r="I8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="11" t="s">
-        <v>42</v>
+      <c r="J8" s="12" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
@@ -7128,8 +7430,8 @@
       <c r="I9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="11" t="s">
-        <v>44</v>
+      <c r="J9" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
@@ -7137,14 +7439,14 @@
         <v>46226.0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="9">
         <v>73001.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F10" s="9">
         <v>73787.0</v>
@@ -7158,8 +7460,8 @@
       <c r="I10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="11" t="s">
-        <v>47</v>
+      <c r="J10" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
@@ -7167,14 +7469,14 @@
         <v>46226.0</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="9">
         <v>112268.0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F11" s="9">
         <v>3300.0</v>
@@ -7186,23 +7488,23 @@
         <v>3300.0</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
       <c r="A12" s="4">
         <v>46226.0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="9">
         <v>112379.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>4200.0</v>
@@ -7214,16 +7516,16 @@
         <v>3900.0</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
       <c r="A13" s="4">
         <v>46226.0</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="9">
@@ -7244,8 +7546,8 @@
       <c r="I13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="11" t="s">
-        <v>47</v>
+      <c r="J13" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
@@ -7253,14 +7555,14 @@
         <v>46227.0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="9">
         <v>72001.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F14" s="9">
         <v>21905.0</v>
@@ -7274,8 +7576,8 @@
       <c r="I14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="11" t="s">
-        <v>47</v>
+      <c r="J14" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
@@ -7283,14 +7585,14 @@
         <v>46227.0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="9">
         <v>2110327.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F15" s="9">
         <v>69120.0</v>
@@ -7304,8 +7606,8 @@
       <c r="I15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="11" t="s">
-        <v>58</v>
+      <c r="J15" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
@@ -7313,14 +7615,14 @@
         <v>46227.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="9">
         <v>112379.0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F16" s="9">
         <v>3900.0</v>
@@ -7332,23 +7634,23 @@
         <v>1500.0</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
       <c r="A17" s="4">
         <v>46227.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F17" s="9">
         <v>720.0</v>
@@ -7360,23 +7662,23 @@
         <v>2580.0</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
       <c r="A18" s="4">
         <v>46227.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="9">
         <v>112268.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F18" s="9">
         <v>3300.0</v>
@@ -7390,8 +7692,8 @@
       <c r="I18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="11" t="s">
-        <v>60</v>
+      <c r="J18" s="12" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
@@ -7399,14 +7701,14 @@
         <v>46230.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="9">
         <v>2410401.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F19" s="9">
         <v>136538.0</v>
@@ -7420,8 +7722,8 @@
       <c r="I19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="11" t="s">
-        <v>62</v>
+      <c r="J19" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
@@ -7429,7 +7731,7 @@
         <v>46231.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="9">
@@ -7450,8 +7752,8 @@
       <c r="I20" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="11" t="s">
-        <v>62</v>
+      <c r="J20" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
@@ -7459,14 +7761,14 @@
         <v>46231.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="9">
         <v>10601.0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F21" s="9">
         <v>1230.0</v>
@@ -7480,8 +7782,8 @@
       <c r="I21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="11" t="s">
-        <v>65</v>
+      <c r="J21" s="12" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
@@ -7489,14 +7791,14 @@
         <v>46231.0</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F22" s="9">
         <v>4320.0</v>
@@ -7510,21 +7812,21 @@
       <c r="I22" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="11"/>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
       <c r="A23" s="4">
         <v>46231.0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="9">
         <v>114357.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F23" s="9">
         <v>240.0</v>
@@ -7538,21 +7840,21 @@
       <c r="I23" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="11"/>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
       <c r="A24" s="4">
         <v>46232.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="9">
         <v>10501.0</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F24" s="9">
         <v>19663.0</v>
@@ -7566,21 +7868,21 @@
       <c r="I24" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="11"/>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
       <c r="A25" s="4">
         <v>46232.0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="9">
         <v>112268.0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F25" s="9">
         <v>5700.0</v>
@@ -7594,21 +7896,21 @@
       <c r="I25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J25" s="11"/>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
       <c r="A26" s="4">
         <v>46232.0</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F26" s="9">
         <v>720.0</v>
@@ -7622,21 +7924,21 @@
       <c r="I26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J26" s="11"/>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
       <c r="A27" s="4">
         <v>46232.0</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="9">
         <v>2114357.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F27" s="9">
         <v>432.0</v>
@@ -7650,7 +7952,7 @@
       <c r="I27" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J27" s="11"/>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
       <c r="A28" s="4">
@@ -7664,7 +7966,7 @@
         <v>10501.0</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F28" s="9">
         <v>219540.0</v>
@@ -7678,21 +7980,21 @@
       <c r="I28" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="11"/>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
       <c r="A29" s="4">
         <v>46233.0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="9">
         <v>112268.0</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F29" s="9">
         <v>5100.0</v>
@@ -7704,23 +8006,23 @@
         <v>4800.0</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J29" s="11"/>
+        <v>34</v>
+      </c>
+      <c r="J29" s="12"/>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
       <c r="A30" s="4">
         <v>46233.0</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="9">
         <v>114357.0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F30" s="9">
         <v>240.0</v>
@@ -7732,23 +8034,23 @@
         <v>1560.0</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" s="11"/>
+        <v>34</v>
+      </c>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
       <c r="A31" s="4">
         <v>46233.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="9">
         <v>10601.0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F31" s="9">
         <v>7717.0</v>
@@ -7762,8 +8064,8 @@
       <c r="I31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J31" s="11" t="s">
-        <v>77</v>
+      <c r="J31" s="12" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
@@ -7771,14 +8073,14 @@
         <v>46234.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="9">
         <v>79110.0</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F32" s="9">
         <v>48000.0</v>
@@ -7790,10 +8092,10 @@
         <v>36300.0</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>79</v>
+        <v>22</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
@@ -7808,7 +8110,7 @@
         <v>10501.0</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F33" s="9">
         <v>95574.0</v>
@@ -7822,8 +8124,8 @@
       <c r="I33" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J33" s="16" t="s">
-        <v>80</v>
+      <c r="J33" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
@@ -7831,14 +8133,14 @@
         <v>46234.0</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="9">
         <v>73001.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F34" s="9">
         <v>73367.0</v>
@@ -7852,21 +8154,21 @@
       <c r="I34" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J34" s="11"/>
+      <c r="J34" s="12"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
       <c r="A35" s="4">
         <v>46234.0</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="9">
         <v>112357.0</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F35" s="9">
         <v>840.0</v>
@@ -7880,21 +8182,21 @@
       <c r="I35" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J35" s="11"/>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
+      <c r="J35" s="12"/>
+    </row>
+    <row r="36" ht="22.5" hidden="1" customHeight="1">
       <c r="A36" s="18">
         <v>46237.0</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="9">
         <v>10601.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F36" s="9">
         <v>17934.0</v>
@@ -7908,16 +8210,16 @@
       <c r="I36" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J36" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="37" ht="22.5" customHeight="1">
+      <c r="J36" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" hidden="1" customHeight="1">
       <c r="A37" s="18">
         <v>46237.0</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="9">
@@ -7936,23 +8238,23 @@
         <v>122840.0</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J37" s="11"/>
-    </row>
-    <row r="38" ht="22.5" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="J37" s="12"/>
+    </row>
+    <row r="38" ht="22.5" hidden="1" customHeight="1">
       <c r="A38" s="18">
         <v>46237.0</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="9">
         <v>114379.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F38" s="9">
         <v>52200.0</v>
@@ -7964,23 +8266,23 @@
         <v>7500.0</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J38" s="11"/>
-    </row>
-    <row r="39" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J38" s="12"/>
+    </row>
+    <row r="39" ht="22.5" hidden="1" customHeight="1">
       <c r="A39" s="18">
         <v>46237.0</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C39" s="14"/>
       <c r="D39" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F39" s="9">
         <v>6450.0</v>
@@ -7992,23 +8294,23 @@
         <v>6480.0</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" s="11"/>
-    </row>
-    <row r="40" ht="22.5" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="J39" s="12"/>
+    </row>
+    <row r="40" ht="22.5" hidden="1" customHeight="1">
       <c r="A40" s="18">
         <v>46237.0</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F40" s="9">
         <v>1398.0</v>
@@ -8020,23 +8322,23 @@
         <v>438.0</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J40" s="11"/>
-    </row>
-    <row r="41" ht="22.5" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="J40" s="12"/>
+    </row>
+    <row r="41" ht="22.5" hidden="1" customHeight="1">
       <c r="A41" s="4">
         <v>46238.0</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C41" s="14"/>
       <c r="D41" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F41" s="9">
         <v>2460.0</v>
@@ -8048,23 +8350,23 @@
         <v>3240.0</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="11"/>
-    </row>
-    <row r="42" ht="22.5" customHeight="1">
+        <v>16</v>
+      </c>
+      <c r="J41" s="12"/>
+    </row>
+    <row r="42" ht="22.5" hidden="1" customHeight="1">
       <c r="A42" s="4">
         <v>46238.0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="9">
         <v>112268.0</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F42" s="9">
         <v>3600.0</v>
@@ -8076,23 +8378,23 @@
         <v>3900.0</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J42" s="11"/>
-    </row>
-    <row r="43" ht="22.5" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="J42" s="12"/>
+    </row>
+    <row r="43" ht="22.5" hidden="1" customHeight="1">
       <c r="A43" s="4">
         <v>46238.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="9">
         <v>114379.0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F43" s="9">
         <v>7500.0</v>
@@ -8104,23 +8406,23 @@
         <v>8400.0</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J43" s="11"/>
-    </row>
-    <row r="44" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J43" s="12"/>
+    </row>
+    <row r="44" ht="22.5" hidden="1" customHeight="1">
       <c r="A44" s="4">
         <v>46238.0</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="9">
         <v>114357.0</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F44" s="9">
         <v>240.0</v>
@@ -8132,23 +8434,23 @@
         <v>360.0</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" s="11"/>
-    </row>
-    <row r="45" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J44" s="12"/>
+    </row>
+    <row r="45" ht="22.5" hidden="1" customHeight="1">
       <c r="A45" s="4">
         <v>46239.0</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="9">
         <v>10601.0</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F45" s="9">
         <v>1115.0</v>
@@ -8162,23 +8464,23 @@
       <c r="I45" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J45" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" customHeight="1">
+      <c r="J45" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" hidden="1" customHeight="1">
       <c r="A46" s="4">
         <v>46239.0</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F46" s="9">
         <v>114240.0</v>
@@ -8190,23 +8492,23 @@
         <v>191130.0</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J46" s="11"/>
-    </row>
-    <row r="47" ht="22.5" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="J46" s="12"/>
+    </row>
+    <row r="47" ht="22.5" hidden="1" customHeight="1">
       <c r="A47" s="4">
         <v>46239.0</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="9">
         <v>2112207.0</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="F47" s="9">
         <v>1800.0</v>
@@ -8218,23 +8520,23 @@
         <v>1980.0</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J47" s="11"/>
-    </row>
-    <row r="48" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J47" s="12"/>
+    </row>
+    <row r="48" ht="22.5" hidden="1" customHeight="1">
       <c r="A48" s="4">
         <v>46239.0</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="9">
         <v>112268.0</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F48" s="9">
         <v>3900.0</v>
@@ -8246,23 +8548,23 @@
         <v>1200.0</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J48" s="11"/>
-    </row>
-    <row r="49" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J48" s="12"/>
+    </row>
+    <row r="49" ht="22.5" hidden="1" customHeight="1">
       <c r="A49" s="4">
         <v>46239.0</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="9">
         <v>112357.0</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F49" s="9">
         <v>600.0</v>
@@ -8274,23 +8576,23 @@
         <v>600.0</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J49" s="11"/>
-    </row>
-    <row r="50" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J49" s="12"/>
+    </row>
+    <row r="50" ht="22.5" hidden="1" customHeight="1">
       <c r="A50" s="4">
         <v>46239.0</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="9">
         <v>114268.0</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F50" s="9">
         <v>2700.0</v>
@@ -8302,23 +8604,23 @@
         <v>300.0</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J50" s="11"/>
-    </row>
-    <row r="51" ht="22.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="J50" s="12"/>
+    </row>
+    <row r="51" ht="22.5" hidden="1" customHeight="1">
       <c r="A51" s="4">
         <v>46239.0</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C51" s="14"/>
       <c r="D51" s="9">
         <v>10501.0</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F51" s="9">
         <v>68651.0</v>
@@ -8332,23 +8634,23 @@
       <c r="I51" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J51" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52" ht="22.5" customHeight="1">
+      <c r="J51" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" hidden="1" customHeight="1">
       <c r="A52" s="4">
         <v>46239.0</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C52" s="14"/>
       <c r="D52" s="9">
         <v>72003.0</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F52" s="9">
         <v>1391.0</v>
@@ -8360,16 +8662,16 @@
         <v>2407.0</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="11"/>
-    </row>
-    <row r="53" ht="22.5" customHeight="1">
+        <v>16</v>
+      </c>
+      <c r="J52" s="12"/>
+    </row>
+    <row r="53" ht="22.5" hidden="1" customHeight="1">
       <c r="A53" s="4">
         <v>46239.0</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C53" s="14"/>
       <c r="D53" s="9">
@@ -8390,8 +8692,8 @@
       <c r="I53" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J53" s="11" t="s">
-        <v>99</v>
+      <c r="J53" s="12" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
@@ -8399,14 +8701,14 @@
         <v>46240.0</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C54" s="14"/>
       <c r="D54" s="9">
         <v>112379.0</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F54" s="9">
         <v>3600.0</v>
@@ -8418,23 +8720,23 @@
         <v>6900.0</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J54" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="J54" s="12"/>
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="18">
         <v>46240.0</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="9">
         <v>73001.0</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F55" s="9">
         <v>2415.0</v>
@@ -8446,23 +8748,23 @@
         <v>2415.0</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J55" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="J55" s="12"/>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="18">
         <v>46240.0</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C56" s="14"/>
       <c r="D56" s="9">
         <v>112357.0</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F56" s="9">
         <v>600.0</v>
@@ -8474,23 +8776,23 @@
         <v>600.0</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J56" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="J56" s="12"/>
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="18">
         <v>46240.0</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="9">
         <v>114379.0</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F57" s="9">
         <v>2400.0</v>
@@ -8502,23 +8804,23 @@
         <v>300.0</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J57" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="J57" s="12"/>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="18">
         <v>46244.0</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="9">
         <v>112379.0</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F58" s="9">
         <v>4800.0</v>
@@ -8530,23 +8832,23 @@
         <v>5100.0</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="J58" s="12"/>
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="4">
         <v>46245.0</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C59" s="14"/>
       <c r="D59" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F59" s="9">
         <v>25574.0</v>
@@ -8558,23 +8860,23 @@
         <v>42960.0</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J59" s="11"/>
+        <v>22</v>
+      </c>
+      <c r="J59" s="12"/>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="4">
         <v>46246.0</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="9">
         <v>114379.0</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F60" s="9">
         <v>6900.0</v>
@@ -8586,27 +8888,177 @@
         <v>5400.0</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J60" s="11"/>
-    </row>
-    <row r="61">
-      <c r="I61" s="20"/>
-    </row>
-    <row r="62">
-      <c r="I62" s="20"/>
-    </row>
-    <row r="63">
-      <c r="I63" s="20"/>
-    </row>
-    <row r="64">
-      <c r="I64" s="20"/>
-    </row>
-    <row r="65">
-      <c r="I65" s="20"/>
-    </row>
-    <row r="66">
-      <c r="I66" s="20"/>
+        <v>23</v>
+      </c>
+      <c r="J60" s="12"/>
+    </row>
+    <row r="61" ht="22.5" customHeight="1">
+      <c r="A61" s="4">
+        <v>46247.0</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="14"/>
+      <c r="D61" s="9">
+        <v>112379.0</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" s="9">
+        <v>20100.0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>6000.0</v>
+      </c>
+      <c r="H61" s="9">
+        <v>20100.0</v>
+      </c>
+      <c r="I61" s="10"/>
+      <c r="J61" s="12"/>
+    </row>
+    <row r="62" ht="22.5" customHeight="1">
+      <c r="A62" s="4">
+        <v>46247.0</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="14"/>
+      <c r="D62" s="9">
+        <v>112268.0</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F62" s="9">
+        <v>8400.0</v>
+      </c>
+      <c r="G62" s="9">
+        <v>3600.0</v>
+      </c>
+      <c r="H62" s="9">
+        <v>8400.0</v>
+      </c>
+      <c r="I62" s="10"/>
+      <c r="J62" s="12"/>
+    </row>
+    <row r="63" ht="22.5" customHeight="1">
+      <c r="A63" s="4">
+        <v>46247.0</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="14"/>
+      <c r="D63" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" s="9">
+        <v>61250.0</v>
+      </c>
+      <c r="G63" s="9">
+        <v>23760.0</v>
+      </c>
+      <c r="H63" s="9">
+        <v>76033.0</v>
+      </c>
+      <c r="I63" s="10"/>
+      <c r="J63" s="12"/>
+    </row>
+    <row r="64" ht="22.5" customHeight="1">
+      <c r="A64" s="4">
+        <v>46247.0</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="14"/>
+      <c r="D64" s="9">
+        <v>13358.0</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F64" s="9">
+        <v>73728.0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>183168.0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>73440.0</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65" ht="22.5" customHeight="1">
+      <c r="A65" s="4">
+        <v>46248.0</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" s="14"/>
+      <c r="D65" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F65" s="9">
+        <v>285596.0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>288000.0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>72480.0</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" ht="22.5" customHeight="1">
+      <c r="A66" s="4">
+        <v>46248.0</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" s="14"/>
+      <c r="D66" s="9">
+        <v>73001.0</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F66" s="9">
+        <v>31772.0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>74720.0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>28820.0</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="67">
       <c r="I67" s="20"/>
@@ -11292,13 +11744,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I60">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I66">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I61:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I67:I960">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A60">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A66">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="160">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -44,12 +44,12 @@
     <t xml:space="preserve">Otro </t>
   </si>
   <si>
+    <t>ALKA2</t>
+  </si>
+  <si>
     <t>TAT BOGOTA MONTEVIDEO</t>
   </si>
   <si>
-    <t>ALKA2</t>
-  </si>
-  <si>
     <t>Daniel Castro</t>
   </si>
   <si>
@@ -62,12 +62,12 @@
     <t>7. Otro</t>
   </si>
   <si>
+    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
+  </si>
+  <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
-    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
-  </si>
-  <si>
     <t>TAT MONTERIA</t>
   </si>
   <si>
@@ -80,12 +80,12 @@
     <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
+    <t>3. Falla De Rotación</t>
+  </si>
+  <si>
     <t>6. Transformación De Referencias</t>
   </si>
   <si>
-    <t>3. Falla De Rotación</t>
-  </si>
-  <si>
     <t>Pendiente Transformar Roto GT Por manipulación</t>
   </si>
   <si>
@@ -125,45 +125,45 @@
     <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
+  </si>
+  <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
+    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
   </si>
   <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
-    <t>PALMAS</t>
-  </si>
-  <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
-  </si>
-  <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
     <t>TAT CALI</t>
   </si>
   <si>
     <t>DIEGO ROJAS</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
     <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
@@ -176,18 +176,27 @@
     <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
   </si>
   <si>
+    <t>HUEVO PICADO ROJO</t>
+  </si>
+  <si>
+    <t>No se carga todod por capacidad de Vehiculo</t>
+  </si>
+  <si>
     <t>Clientes FS</t>
   </si>
   <si>
-    <t>HUEVO PICADO ROJO</t>
-  </si>
-  <si>
-    <t>No se carga todod por capacidad de Vehiculo</t>
-  </si>
-  <si>
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
+    <t>HUEVO SUCIO DE JAULA</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
+    <t>Esta para despacho hoy</t>
+  </si>
+  <si>
     <t>Transformación de PET</t>
   </si>
   <si>
@@ -203,46 +212,43 @@
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
-    <t>HUEVO SUCIO DE JAULA</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
-  </si>
-  <si>
-    <t>Esta para despacho hoy</t>
+    <t>Cola de programación</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
   </si>
   <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
+    <t>HUEVO CX30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
+  </si>
+  <si>
     <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
-    <t>Cola de programación</t>
-  </si>
-  <si>
     <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
   </si>
   <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
     <t>5. Ingreso De Planta</t>
   </si>
   <si>
-    <t>HUEVO CX30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
-  </si>
-  <si>
     <t>Se despacha par FS con producto más nuevo</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
     <t>ANDREA QUIROGA</t>
@@ -251,13 +257,19 @@
     <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
-  </si>
-  <si>
     <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
+    <t>ALKA1</t>
+  </si>
+  <si>
+    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
+  </si>
+  <si>
+    <t>HUEVO ROTO - ZF</t>
+  </si>
+  <si>
+    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
   </si>
   <si>
     <t>TAT PASTO</t>
@@ -266,33 +278,27 @@
     <t>CAROLINA VITERI</t>
   </si>
   <si>
-    <t>ALKA1</t>
+    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
   </si>
   <si>
     <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
-    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
-  </si>
-  <si>
-    <t>HUEVO ROTO - ZF</t>
-  </si>
-  <si>
     <t>Pedido para villavicencio</t>
   </si>
   <si>
-    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
-  </si>
-  <si>
-    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
+    <t>Cargo en incubación</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
     <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
     <t>Inventario de Asesor de Rionegro que renuncio</t>
   </si>
   <si>
@@ -302,25 +308,25 @@
     <t>Jhonatan Gomez</t>
   </si>
   <si>
-    <t>Cargo en incubación</t>
-  </si>
-  <si>
     <t>Lote mezclado en la misma estiba</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
     <t>Supera edad solicitada clientes grandes superficies</t>
   </si>
   <si>
+    <t>BELLAVISTA</t>
+  </si>
+  <si>
     <t>Pedido para villacicencio</t>
   </si>
   <si>
+    <t>Traslado a cedi, producto de devolución</t>
+  </si>
+  <si>
     <t>Se envía huevo más fresco a Sincelejo</t>
   </si>
   <si>
-    <t>BELLAVISTA</t>
+    <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
     <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
@@ -332,27 +338,33 @@
     <t>SalIO en sugeridos de hoy 22/07/2026</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
     <t>Yovanis Arevalo</t>
   </si>
   <si>
     <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
   </si>
   <si>
+    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
+  </si>
+  <si>
+    <t>HUEVO SUCIO ZF MARCADO</t>
+  </si>
+  <si>
+    <t>vehiculo con flata de capacidad / TAT cali</t>
+  </si>
+  <si>
     <t>Devolucion de huevo de 12 dias en mal estado</t>
   </si>
   <si>
-    <t>Traslado a cedi, producto de devolución</t>
-  </si>
-  <si>
     <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
   </si>
   <si>
     <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CANASTA</t>
-  </si>
-  <si>
     <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
   </si>
   <si>
@@ -362,19 +374,19 @@
     <t>Producto que queda de clientes de preventa - TAT, que el cliente no recibe</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
     <t>TAT VILLAVICENCIO</t>
   </si>
   <si>
-    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
-  </si>
-  <si>
-    <t>HUEVO SUCIO ZF MARCADO</t>
-  </si>
-  <si>
-    <t>vehiculo con flata de capacidad / TAT cali</t>
+    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
+  </si>
+  <si>
+    <t>vehiculo pendiente pro llegar a planta</t>
+  </si>
+  <si>
+    <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
+  </si>
+  <si>
+    <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
   </si>
   <si>
     <t xml:space="preserve">En la estiba llegan lotes en la parte de abajo </t>
@@ -404,21 +416,9 @@
     <t>ANDRES MEJA</t>
   </si>
   <si>
-    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
-  </si>
-  <si>
     <t>Se envía lotemás nuevo a Sincelejo</t>
   </si>
   <si>
-    <t>vehiculo pendiente pro llegar a planta</t>
-  </si>
-  <si>
-    <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
-  </si>
-  <si>
-    <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
-  </si>
-  <si>
     <t>Se envía huevo más fresco para clientes FS</t>
   </si>
   <si>
@@ -479,10 +479,19 @@
     <t>ERROR EN DIGITACION DE LAS EDAD</t>
   </si>
   <si>
+    <t>Pedidos para FD más fresco</t>
+  </si>
+  <si>
     <t>Padidos para FS con mayor frescura</t>
   </si>
   <si>
     <t>Pendiente Transformacion a suelto</t>
+  </si>
+  <si>
+    <t>se registra mal el dia de ayer el lote de 2 dias</t>
+  </si>
+  <si>
+    <t>Devolucion Blindar</t>
   </si>
 </sst>
 </file>
@@ -560,10 +569,10 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -580,11 +589,11 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -598,11 +607,11 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -703,7 +712,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J116" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J122" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -984,11 +993,11 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>46204.0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>12</v>
@@ -1008,12 +1017,12 @@
       <c r="H2" s="9">
         <v>206140.0</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>16</v>
+      <c r="I2" s="12" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>46205.0</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -1038,12 +1047,12 @@
         <v>260675.0</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J3" s="7"/>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>46205.0</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1068,12 +1077,12 @@
         <v>16920.0</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="7"/>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>46205.0</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -1100,12 +1109,12 @@
       <c r="I5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>46206.0</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -1132,12 +1141,12 @@
       <c r="I6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>37</v>
+      <c r="J6" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>46206.0</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1150,7 +1159,7 @@
         <v>2010102.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F7" s="9">
         <v>20640.0</v>
@@ -1164,12 +1173,12 @@
       <c r="I7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>41</v>
+      <c r="J7" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>46206.0</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -1182,7 +1191,7 @@
         <v>152384.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" s="9">
         <v>14700.0</v>
@@ -1196,17 +1205,17 @@
       <c r="I8" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="12"/>
+      <c r="J8" s="11"/>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>46206.0</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="9">
         <v>2110202.0</v>
@@ -1226,10 +1235,10 @@
       <c r="I9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J9" s="12"/>
+      <c r="J9" s="11"/>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>46206.0</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1242,7 +1251,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F10" s="9">
         <v>7830.0</v>
@@ -1254,12 +1263,12 @@
         <v>6030.0</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="15"/>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>46206.0</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1286,12 +1295,12 @@
       <c r="I11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>54</v>
+      <c r="J11" s="11" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>46206.0</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -1318,12 +1327,12 @@
       <c r="I12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="11" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>46209.0</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -1350,12 +1359,12 @@
       <c r="I13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="11" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>46209.0</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -1380,27 +1389,27 @@
         <v>424588.0</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>58</v>
+        <v>23</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>46209.0</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D15" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F15" s="9">
         <v>14160.0</v>
@@ -1414,19 +1423,19 @@
       <c r="I15" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>60</v>
+      <c r="J15" s="11" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <v>46210.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D16" s="9">
         <v>2110302.0</v>
@@ -1444,19 +1453,19 @@
         <v>289680.0</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J16" s="11"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>46210.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="9">
         <v>2110217.0</v>
@@ -1474,19 +1483,19 @@
         <v>19770.0</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J17" s="11"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <v>46210.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="9">
         <v>2110302.0</v>
@@ -1504,12 +1513,12 @@
         <v>162125.0</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J18" s="11"/>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <v>46211.0</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -1536,12 +1545,12 @@
       <c r="I19" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="12" t="s">
-        <v>66</v>
+      <c r="J19" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="5">
+      <c r="A20" s="4">
         <v>46211.0</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -1566,19 +1575,19 @@
         <v>74040.0</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J20" s="11"/>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <v>46211.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D21" s="9">
         <v>2110302.0</v>
@@ -1598,16 +1607,16 @@
       <c r="I21" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="12" t="s">
-        <v>67</v>
+      <c r="J21" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <v>46211.0</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>12</v>
@@ -1616,7 +1625,7 @@
         <v>152384.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F22" s="9">
         <v>32850.0</v>
@@ -1630,23 +1639,23 @@
       <c r="I22" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="12"/>
+      <c r="J22" s="11"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <v>46211.0</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D23" s="9">
         <v>112271.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F23" s="9">
         <v>16500.0</v>
@@ -1660,17 +1669,17 @@
       <c r="I23" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J23" s="12"/>
+      <c r="J23" s="11"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="5">
+      <c r="A24" s="4">
         <v>46212.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D24" s="9">
         <v>2110202.0</v>
@@ -1690,17 +1699,17 @@
       <c r="I24" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J24" s="12"/>
+      <c r="J24" s="11"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <v>46212.0</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D25" s="9">
         <v>2110302.0</v>
@@ -1718,19 +1727,19 @@
         <v>203520.0</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="J25" s="12"/>
+        <v>75</v>
+      </c>
+      <c r="J25" s="11"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="5">
+      <c r="A26" s="4">
         <v>46212.0</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D26" s="9">
         <v>2110402.0</v>
@@ -1750,25 +1759,25 @@
       <c r="I26" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J26" s="12" t="s">
-        <v>75</v>
+      <c r="J26" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="5">
+      <c r="A27" s="4">
         <v>46212.0</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D27" s="9">
         <v>112271.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F27" s="9">
         <v>18000.0</v>
@@ -1780,19 +1789,19 @@
         <v>13500.0</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J27" s="11"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="5">
+      <c r="A28" s="4">
         <v>46213.0</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D28" s="9">
         <v>2110302.0</v>
@@ -1812,19 +1821,19 @@
       <c r="I28" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="12" t="s">
-        <v>78</v>
+      <c r="J28" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="5">
+      <c r="A29" s="4">
         <v>46213.0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D29" s="9">
         <v>2110202.0</v>
@@ -1844,19 +1853,19 @@
       <c r="I29" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="12" t="s">
-        <v>78</v>
+      <c r="J29" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="5">
+      <c r="A30" s="4">
         <v>46213.0</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D30" s="9">
         <v>2110202.0</v>
@@ -1876,19 +1885,19 @@
       <c r="I30" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J30" s="12" t="s">
-        <v>80</v>
+      <c r="J30" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="5">
+      <c r="A31" s="4">
         <v>46213.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D31" s="9">
         <v>2110302.0</v>
@@ -1906,19 +1915,19 @@
         <v>229680.0</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J31" s="11"/>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="5">
+      <c r="A32" s="4">
         <v>46213.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D32" s="9">
         <v>2110302.0</v>
@@ -1938,17 +1947,17 @@
       <c r="I32" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J32" s="12"/>
+      <c r="J32" s="11"/>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="5">
+      <c r="A33" s="4">
         <v>46213.0</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D33" s="9">
         <v>2110402.0</v>
@@ -1966,19 +1975,19 @@
         <v>25440.0</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J33" s="11"/>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="5">
+      <c r="A34" s="4">
         <v>46217.0</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D34" s="9">
         <v>2110302.0</v>
@@ -1996,12 +2005,12 @@
         <v>151435.0</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J34" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J34" s="11"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="5">
+      <c r="A35" s="4">
         <v>46217.0</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -2026,25 +2035,25 @@
         <v>302760.0</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J35" s="11"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="5">
+      <c r="A36" s="4">
         <v>46217.0</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D36" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F36" s="9">
         <v>35280.0</v>
@@ -2056,21 +2065,21 @@
         <v>37926.0</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>85</v>
+        <v>22</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
-      <c r="A37" s="17">
+      <c r="A37" s="18">
         <v>46218.0</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D37" s="9">
         <v>2110302.0</v>
@@ -2090,25 +2099,25 @@
       <c r="I37" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J37" s="12" t="s">
-        <v>88</v>
+      <c r="J37" s="11" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
-      <c r="A38" s="17">
+      <c r="A38" s="18">
         <v>46218.0</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D38" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F38" s="9">
         <v>37926.0</v>
@@ -2120,14 +2129,14 @@
         <v>25746.0</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>85</v>
+        <v>22</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
-      <c r="A39" s="17">
+      <c r="A39" s="18">
         <v>46218.0</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -2154,12 +2163,12 @@
       <c r="I39" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J39" s="12" t="s">
-        <v>91</v>
+      <c r="J39" s="11" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
-      <c r="A40" s="17">
+      <c r="A40" s="18">
         <v>46218.0</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -2172,7 +2181,7 @@
         <v>2110317.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F40" s="9">
         <v>10980.0</v>
@@ -2184,12 +2193,12 @@
         <v>13500.0</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J40" s="11"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="5">
+      <c r="A41" s="4">
         <v>46219.0</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -2216,25 +2225,25 @@
       <c r="I41" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J41" s="12" t="s">
-        <v>93</v>
+      <c r="J41" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="5">
+      <c r="A42" s="4">
         <v>46219.0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D42" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F42" s="9">
         <v>36225.0</v>
@@ -2246,19 +2255,19 @@
         <v>27570.0</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J42" s="11"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="5">
+      <c r="A43" s="4">
         <v>46219.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D43" s="9">
         <v>2110302.0</v>
@@ -2276,21 +2285,21 @@
         <v>96472.0</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>97</v>
+        <v>75</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="5">
+      <c r="A44" s="4">
         <v>46219.0</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D44" s="9">
         <v>2110302.0</v>
@@ -2308,25 +2317,25 @@
         <v>71560.0</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J44" s="11"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="5">
+      <c r="A45" s="4">
         <v>46219.0</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D45" s="9">
         <v>152384.0</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F45" s="9">
         <v>31125.0</v>
@@ -2340,25 +2349,25 @@
       <c r="I45" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J45" s="12" t="s">
+      <c r="J45" s="11" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="5">
+      <c r="A46" s="4">
         <v>46219.0</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D46" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F46" s="9">
         <v>25746.0</v>
@@ -2370,21 +2379,21 @@
         <v>28683.0</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" s="12" t="s">
-        <v>85</v>
+        <v>22</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="5">
+      <c r="A47" s="4">
         <v>46220.0</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D47" s="9">
         <v>2110302.0</v>
@@ -2404,19 +2413,19 @@
       <c r="I47" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J47" s="12" t="s">
-        <v>100</v>
+      <c r="J47" s="11" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="5">
+      <c r="A48" s="4">
         <v>46220.0</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D48" s="9">
         <v>2110217.0</v>
@@ -2434,12 +2443,12 @@
         <v>119584.0</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J48" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J48" s="11"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="5">
+      <c r="A49" s="4">
         <v>46224.0</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -2466,19 +2475,19 @@
       <c r="I49" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J49" s="12" t="s">
-        <v>101</v>
+      <c r="J49" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="5">
+      <c r="A50" s="4">
         <v>46224.0</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D50" s="9">
         <v>2110402.0</v>
@@ -2498,19 +2507,19 @@
       <c r="I50" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J50" s="12" t="s">
-        <v>103</v>
+      <c r="J50" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="5">
+      <c r="A51" s="4">
         <v>46225.0</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D51" s="9">
         <v>2110302.0</v>
@@ -2528,21 +2537,21 @@
         <v>153840.0</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>104</v>
+        <v>23</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="5">
+      <c r="A52" s="4">
         <v>46225.0</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D52" s="9">
         <v>2110302.0</v>
@@ -2560,19 +2569,19 @@
         <v>104365.0</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J52" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J52" s="11"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="5">
+      <c r="A53" s="4">
         <v>46225.0</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D53" s="9">
         <v>2110402.0</v>
@@ -2590,21 +2599,21 @@
         <v>25920.0</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>105</v>
+        <v>22</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
-      <c r="A54" s="5">
+      <c r="A54" s="4">
         <v>46226.0</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D54" s="9">
         <v>2110402.0</v>
@@ -2622,21 +2631,21 @@
         <v>226069.0</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>107</v>
+        <v>75</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
-      <c r="A55" s="5">
+      <c r="A55" s="4">
         <v>46226.0</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D55" s="9">
         <v>2110202.0</v>
@@ -2654,19 +2663,19 @@
         <v>700200.0</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="J55" s="12"/>
+        <v>75</v>
+      </c>
+      <c r="J55" s="11"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
-      <c r="A56" s="5">
+      <c r="A56" s="4">
         <v>46227.0</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D56" s="9">
         <v>2110202.0</v>
@@ -2684,19 +2693,19 @@
         <v>668440.0</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J56" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J56" s="11"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
-      <c r="A57" s="5">
+      <c r="A57" s="4">
         <v>46227.0</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D57" s="9">
         <v>2110402.0</v>
@@ -2716,19 +2725,19 @@
       <c r="I57" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J57" s="12" t="s">
-        <v>108</v>
+      <c r="J57" s="11" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
-      <c r="A58" s="5">
+      <c r="A58" s="4">
         <v>46227.0</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D58" s="9">
         <v>2110202.0</v>
@@ -2746,19 +2755,19 @@
         <v>128160.0</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="J58" s="12"/>
+        <v>75</v>
+      </c>
+      <c r="J58" s="11"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="5">
+      <c r="A59" s="4">
         <v>46227.0</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D59" s="9">
         <v>2110402.0</v>
@@ -2778,25 +2787,25 @@
       <c r="I59" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J59" s="12" t="s">
-        <v>110</v>
+      <c r="J59" s="11" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="5">
+      <c r="A60" s="4">
         <v>46230.0</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D60" s="9">
         <v>2110403.0</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F60" s="9">
         <v>9960.0</v>
@@ -2808,19 +2817,19 @@
         <v>3660.0</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J60" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J60" s="11"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="5">
+      <c r="A61" s="4">
         <v>46230.0</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D61" s="9">
         <v>2110302.0</v>
@@ -2838,12 +2847,12 @@
         <v>247096.0</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J61" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J61" s="11"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
-      <c r="A62" s="5">
+      <c r="A62" s="4">
         <v>46230.0</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -2870,12 +2879,12 @@
       <c r="I62" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J62" s="12" t="s">
-        <v>113</v>
+      <c r="J62" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
-      <c r="A63" s="5">
+      <c r="A63" s="4">
         <v>46231.0</v>
       </c>
       <c r="B63" s="6" t="s">
@@ -2902,19 +2911,19 @@
       <c r="I63" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J63" s="12" t="s">
-        <v>114</v>
+      <c r="J63" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
-      <c r="A64" s="5">
+      <c r="A64" s="4">
         <v>46231.0</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D64" s="9">
         <v>2110302.0</v>
@@ -2934,25 +2943,25 @@
       <c r="I64" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J64" s="12" t="s">
-        <v>115</v>
+      <c r="J64" s="11" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
-      <c r="A65" s="5">
+      <c r="A65" s="4">
         <v>46231.0</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D65" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F65" s="9">
         <v>8190.0</v>
@@ -2966,19 +2975,19 @@
       <c r="I65" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J65" s="12" t="s">
-        <v>115</v>
+      <c r="J65" s="11" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
-      <c r="A66" s="5">
+      <c r="A66" s="4">
         <v>46231.0</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D66" s="9">
         <v>2110202.0</v>
@@ -2998,16 +3007,16 @@
       <c r="I66" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J66" s="12" t="s">
-        <v>115</v>
+      <c r="J66" s="11" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
-      <c r="A67" s="5">
+      <c r="A67" s="4">
         <v>46232.0</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C67" s="20"/>
       <c r="D67" s="9">
@@ -3028,10 +3037,10 @@
       <c r="I67" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J67" s="12"/>
+      <c r="J67" s="11"/>
     </row>
     <row r="68" ht="22.5" hidden="1" customHeight="1">
-      <c r="A68" s="5">
+      <c r="A68" s="4">
         <v>46232.0</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -3056,10 +3065,10 @@
       <c r="I68" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J68" s="12"/>
+      <c r="J68" s="11"/>
     </row>
     <row r="69" ht="22.5" hidden="1" customHeight="1">
-      <c r="A69" s="5">
+      <c r="A69" s="4">
         <v>46232.0</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -3084,21 +3093,21 @@
       <c r="I69" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J69" s="12"/>
+      <c r="J69" s="11"/>
     </row>
     <row r="70" ht="22.5" hidden="1" customHeight="1">
-      <c r="A70" s="5">
+      <c r="A70" s="4">
         <v>46232.0</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F70" s="9">
         <v>5913.0</v>
@@ -3112,14 +3121,14 @@
       <c r="I70" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J70" s="12"/>
+      <c r="J70" s="11"/>
     </row>
     <row r="71" ht="22.5" hidden="1" customHeight="1">
-      <c r="A71" s="5">
+      <c r="A71" s="4">
         <v>46232.0</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="9">
@@ -3140,21 +3149,21 @@
       <c r="I71" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J71" s="12"/>
+      <c r="J71" s="11"/>
     </row>
     <row r="72" ht="22.5" hidden="1" customHeight="1">
-      <c r="A72" s="5">
+      <c r="A72" s="4">
         <v>46232.0</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C72" s="20"/>
       <c r="D72" s="9">
         <v>152384.0</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F72" s="9">
         <v>21300.0</v>
@@ -3168,14 +3177,14 @@
       <c r="I72" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J72" s="12"/>
+      <c r="J72" s="11"/>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
-      <c r="A73" s="5">
+      <c r="A73" s="4">
         <v>46232.0</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C73" s="20"/>
       <c r="D73" s="9">
@@ -3196,10 +3205,10 @@
       <c r="I73" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J73" s="12"/>
+      <c r="J73" s="11"/>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
-      <c r="A74" s="17">
+      <c r="A74" s="18">
         <v>46233.0</v>
       </c>
       <c r="B74" s="6" t="s">
@@ -3224,21 +3233,21 @@
         <v>183014.0</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="J74" s="12" t="s">
-        <v>121</v>
+        <v>75</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
-      <c r="A75" s="17">
+      <c r="A75" s="18">
         <v>46233.0</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D75" s="9">
         <v>2110302.0</v>
@@ -3256,19 +3265,19 @@
         <v>86643.0</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J75" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J75" s="11"/>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
-      <c r="A76" s="5">
+      <c r="A76" s="4">
         <v>46234.0</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D76" s="9">
         <v>2110302.0</v>
@@ -3286,25 +3295,25 @@
         <v>116000.0</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J76" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J76" s="11"/>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
-      <c r="A77" s="5">
+      <c r="A77" s="4">
         <v>46234.0</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D77" s="9">
         <v>112357.0</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F77" s="9">
         <v>720.0</v>
@@ -3318,25 +3327,25 @@
       <c r="I77" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J77" s="12" t="s">
-        <v>124</v>
+      <c r="J77" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
-      <c r="A78" s="5">
+      <c r="A78" s="4">
         <v>46234.0</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D78" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F78" s="9">
         <v>5580.0</v>
@@ -3350,8 +3359,8 @@
       <c r="I78" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J78" s="12" t="s">
-        <v>125</v>
+      <c r="J78" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="79" ht="22.5" hidden="1" customHeight="1">
@@ -3359,10 +3368,10 @@
         <v>46237.0</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D79" s="9">
         <v>2110202.0</v>
@@ -3382,8 +3391,8 @@
       <c r="I79" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J79" s="12" t="s">
-        <v>126</v>
+      <c r="J79" s="11" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="80" ht="22.5" hidden="1" customHeight="1">
@@ -3391,10 +3400,10 @@
         <v>46237.0</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D80" s="9">
         <v>2110302.0</v>
@@ -3414,8 +3423,8 @@
       <c r="I80" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J80" s="12" t="s">
-        <v>126</v>
+      <c r="J80" s="11" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="81" ht="22.5" hidden="1" customHeight="1">
@@ -3426,7 +3435,7 @@
         <v>51</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D81" s="9">
         <v>2110302.0</v>
@@ -3444,10 +3453,10 @@
         <v>63920.0</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="J81" s="12" t="s">
-        <v>128</v>
+        <v>75</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="82" ht="22.5" hidden="1" customHeight="1">
@@ -3458,7 +3467,7 @@
         <v>25</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D82" s="9">
         <v>2110402.0</v>
@@ -3476,9 +3485,9 @@
         <v>40560.0</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J82" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J82" s="11"/>
     </row>
     <row r="83" ht="22.5" hidden="1" customHeight="1">
       <c r="A83" s="19">
@@ -3508,25 +3517,25 @@
       <c r="I83" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J83" s="12" t="s">
-        <v>131</v>
+      <c r="J83" s="11" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="84" ht="22.5" hidden="1" customHeight="1">
-      <c r="A84" s="5">
+      <c r="A84" s="4">
         <v>46238.0</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D84" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F84" s="9">
         <v>43200.0</v>
@@ -3538,25 +3547,25 @@
         <v>40890.0</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J84" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J84" s="11"/>
     </row>
     <row r="85" ht="22.5" hidden="1" customHeight="1">
-      <c r="A85" s="5">
+      <c r="A85" s="4">
         <v>46238.0</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D85" s="9">
         <v>152384.0</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F85" s="9">
         <v>25350.0</v>
@@ -3570,23 +3579,23 @@
       <c r="I85" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J85" s="12"/>
+      <c r="J85" s="11"/>
     </row>
     <row r="86" ht="22.5" hidden="1" customHeight="1">
-      <c r="A86" s="5">
+      <c r="A86" s="4">
         <v>46238.0</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D86" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F86" s="9">
         <v>5040.0</v>
@@ -3598,19 +3607,19 @@
         <v>4680.0</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J86" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J86" s="11"/>
     </row>
     <row r="87" ht="22.5" hidden="1" customHeight="1">
-      <c r="A87" s="5">
+      <c r="A87" s="4">
         <v>46238.0</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D87" s="9">
         <v>2110302.0</v>
@@ -3630,25 +3639,25 @@
       <c r="I87" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J87" s="12" t="s">
+      <c r="J87" s="11" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="88" ht="22.5" hidden="1" customHeight="1">
-      <c r="A88" s="5">
+      <c r="A88" s="4">
         <v>46239.0</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D88" s="9">
         <v>152384.0</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F88" s="9">
         <v>30750.0</v>
@@ -3660,12 +3669,12 @@
         <v>36300.0</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J88" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J88" s="11"/>
     </row>
     <row r="89" ht="22.5" hidden="1" customHeight="1">
-      <c r="A89" s="5">
+      <c r="A89" s="4">
         <v>46239.0</v>
       </c>
       <c r="B89" s="6" t="s">
@@ -3692,7 +3701,7 @@
       <c r="I89" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J89" s="12" t="s">
+      <c r="J89" s="11" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3724,7 +3733,7 @@
       <c r="I90" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J90" s="12" t="s">
+      <c r="J90" s="11" t="s">
         <v>137</v>
       </c>
     </row>
@@ -3756,23 +3765,23 @@
       <c r="I91" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J91" s="12"/>
+      <c r="J91" s="11"/>
     </row>
     <row r="92" ht="22.5" hidden="1" customHeight="1">
       <c r="A92" s="19">
         <v>46240.0</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D92" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F92" s="9">
         <v>4575.0</v>
@@ -3786,7 +3795,7 @@
       <c r="I92" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J92" s="12" t="s">
+      <c r="J92" s="11" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3818,7 +3827,7 @@
       <c r="I93" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J93" s="12" t="s">
+      <c r="J93" s="11" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3850,7 +3859,7 @@
       <c r="I94" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J94" s="12" t="s">
+      <c r="J94" s="11" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3882,7 +3891,7 @@
       <c r="I95" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J95" s="12" t="s">
+      <c r="J95" s="11" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3891,16 +3900,16 @@
         <v>46244.0</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D96" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F96" s="9">
         <v>21690.0</v>
@@ -3912,12 +3921,12 @@
         <v>26280.0</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J96" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J96" s="11"/>
     </row>
     <row r="97" ht="22.5" hidden="1" customHeight="1">
-      <c r="A97" s="5">
+      <c r="A97" s="4">
         <v>46245.0</v>
       </c>
       <c r="B97" s="6" t="s">
@@ -3930,7 +3939,7 @@
         <v>112271.0</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F97" s="9">
         <v>20100.0</v>
@@ -3942,12 +3951,12 @@
         <v>10800.0</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J97" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J97" s="11"/>
     </row>
     <row r="98" ht="22.5" hidden="1" customHeight="1">
-      <c r="A98" s="5">
+      <c r="A98" s="4">
         <v>46245.0</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -3974,12 +3983,12 @@
       <c r="I98" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J98" s="12" t="s">
+      <c r="J98" s="11" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="99" ht="22.5" hidden="1" customHeight="1">
-      <c r="A99" s="5">
+      <c r="A99" s="4">
         <v>46245.0</v>
       </c>
       <c r="B99" s="6" t="s">
@@ -3992,7 +4001,7 @@
         <v>152384.0</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F99" s="9">
         <v>18600.0</v>
@@ -4006,19 +4015,19 @@
       <c r="I99" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J99" s="12" t="s">
+      <c r="J99" s="11" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="100" ht="22.5" hidden="1" customHeight="1">
-      <c r="A100" s="5">
+      <c r="A100" s="4">
         <v>46245.0</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D100" s="9">
         <v>2110302.0</v>
@@ -4038,16 +4047,16 @@
       <c r="I100" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J100" s="12" t="s">
+      <c r="J100" s="11" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="101" ht="22.5" customHeight="1">
-      <c r="A101" s="5">
+    <row r="101" ht="22.5" hidden="1" customHeight="1">
+      <c r="A101" s="4">
         <v>46246.0</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>144</v>
@@ -4068,21 +4077,21 @@
         <v>638764.0</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J101" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="11" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="102" ht="22.5" customHeight="1">
-      <c r="A102" s="5">
+    <row r="102" ht="22.5" hidden="1" customHeight="1">
+      <c r="A102" s="4">
         <v>46246.0</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D102" s="9">
         <v>2110202.0</v>
@@ -4102,25 +4111,25 @@
       <c r="I102" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J102" s="12" t="s">
+      <c r="J102" s="11" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="103" ht="22.5" customHeight="1">
-      <c r="A103" s="5">
+    <row r="103" ht="22.5" hidden="1" customHeight="1">
+      <c r="A103" s="4">
         <v>46246.0</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D103" s="9">
         <v>112271.0</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F103" s="9">
         <v>10815.0</v>
@@ -4132,14 +4141,14 @@
         <v>1935.0</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J103" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J103" s="11" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="104" ht="22.5" customHeight="1">
-      <c r="A104" s="5">
+    <row r="104" ht="22.5" hidden="1" customHeight="1">
+      <c r="A104" s="4">
         <v>46246.0</v>
       </c>
       <c r="B104" s="6" t="s">
@@ -4152,7 +4161,7 @@
         <v>152384.0</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F104" s="9">
         <v>12900.0</v>
@@ -4166,12 +4175,12 @@
       <c r="I104" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J104" s="12" t="s">
+      <c r="J104" s="11" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="105" ht="22.5" customHeight="1">
-      <c r="A105" s="5">
+    <row r="105" ht="22.5" hidden="1" customHeight="1">
+      <c r="A105" s="4">
         <v>46247.0</v>
       </c>
       <c r="B105" s="6" t="s">
@@ -4198,12 +4207,12 @@
       <c r="I105" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J105" s="12" t="s">
+      <c r="J105" s="11" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="106" ht="22.5" customHeight="1">
-      <c r="A106" s="5">
+    <row r="106" ht="22.5" hidden="1" customHeight="1">
+      <c r="A106" s="4">
         <v>46247.0</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -4230,10 +4239,10 @@
       <c r="I106" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J106" s="12"/>
-    </row>
-    <row r="107" ht="22.5" customHeight="1">
-      <c r="A107" s="5">
+      <c r="J106" s="11"/>
+    </row>
+    <row r="107" ht="22.5" hidden="1" customHeight="1">
+      <c r="A107" s="4">
         <v>46247.0</v>
       </c>
       <c r="B107" s="6" t="s">
@@ -4258,12 +4267,12 @@
         <v>17280.0</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J107" s="12"/>
-    </row>
-    <row r="108" ht="22.5" customHeight="1">
-      <c r="A108" s="5">
+        <v>22</v>
+      </c>
+      <c r="J107" s="11"/>
+    </row>
+    <row r="108" ht="22.5" hidden="1" customHeight="1">
+      <c r="A108" s="4">
         <v>46247.0</v>
       </c>
       <c r="B108" s="6" t="s">
@@ -4276,7 +4285,7 @@
         <v>112271.0</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F108" s="9">
         <v>16500.0</v>
@@ -4290,16 +4299,18 @@
       <c r="I108" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J108" s="12"/>
-    </row>
-    <row r="109" ht="22.5" customHeight="1">
-      <c r="A109" s="5">
+      <c r="J108" s="11"/>
+    </row>
+    <row r="109" ht="22.5" hidden="1" customHeight="1">
+      <c r="A109" s="4">
         <v>46248.0</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C109" s="20"/>
+        <v>11</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="D109" s="9">
         <v>2110202.0</v>
       </c>
@@ -4318,12 +4329,12 @@
       <c r="I109" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J109" s="12" t="s">
+      <c r="J109" s="11" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="110" ht="22.5" customHeight="1">
-      <c r="A110" s="5">
+    <row r="110" ht="22.5" hidden="1" customHeight="1">
+      <c r="A110" s="4">
         <v>46248.0</v>
       </c>
       <c r="B110" s="6" t="s">
@@ -4348,12 +4359,12 @@
         <v>247440.0</v>
       </c>
       <c r="I110" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J110" s="12"/>
-    </row>
-    <row r="111" ht="22.5" customHeight="1">
-      <c r="A111" s="5">
+        <v>22</v>
+      </c>
+      <c r="J110" s="11"/>
+    </row>
+    <row r="111" ht="22.5" hidden="1" customHeight="1">
+      <c r="A111" s="4">
         <v>46248.0</v>
       </c>
       <c r="B111" s="6" t="s">
@@ -4380,12 +4391,12 @@
       <c r="I111" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J111" s="12" t="s">
+      <c r="J111" s="11" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="112" ht="22.5" customHeight="1">
-      <c r="A112" s="5">
+    <row r="112" ht="22.5" hidden="1" customHeight="1">
+      <c r="A112" s="4">
         <v>46248.0</v>
       </c>
       <c r="B112" s="6" t="s">
@@ -4398,7 +4409,7 @@
         <v>152384.0</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F112" s="9">
         <v>13200.0</v>
@@ -4412,16 +4423,16 @@
       <c r="I112" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J112" s="12" t="s">
+      <c r="J112" s="11" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="113" ht="22.5" customHeight="1">
-      <c r="A113" s="5">
+    <row r="113" ht="22.5" hidden="1" customHeight="1">
+      <c r="A113" s="4">
         <v>46248.0</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>153</v>
@@ -4430,7 +4441,7 @@
         <v>152384.0</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F113" s="9">
         <v>9900.0</v>
@@ -4442,21 +4453,21 @@
         <v>8100.0</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J113" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J113" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="114" ht="22.5" customHeight="1">
-      <c r="A114" s="5">
+      <c r="A114" s="4">
         <v>46252.0</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D114" s="9">
         <v>2110302.0</v>
@@ -4473,18 +4484,22 @@
       <c r="H114" s="9">
         <v>68640.0</v>
       </c>
-      <c r="I114" s="13"/>
-      <c r="J114" s="12"/>
+      <c r="I114" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J114" s="11" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="115" ht="22.5" customHeight="1">
-      <c r="A115" s="5">
+      <c r="A115" s="4">
         <v>46252.0</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D115" s="9">
         <v>2110402.0</v>
@@ -4504,25 +4519,25 @@
       <c r="I115" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J115" s="12" t="s">
-        <v>155</v>
+      <c r="J115" s="11" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="116" ht="22.5" customHeight="1">
-      <c r="A116" s="5">
+      <c r="A116" s="4">
         <v>46252.0</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D116" s="9">
         <v>152384.0</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F116" s="9">
         <v>21585.0</v>
@@ -4536,27 +4551,195 @@
       <c r="I116" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J116" s="12" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="I117" s="21"/>
-    </row>
-    <row r="118">
-      <c r="I118" s="21"/>
-    </row>
-    <row r="119">
-      <c r="I119" s="21"/>
-    </row>
-    <row r="120">
-      <c r="I120" s="21"/>
-    </row>
-    <row r="121">
-      <c r="I121" s="21"/>
-    </row>
-    <row r="122">
-      <c r="I122" s="21"/>
+      <c r="J116" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="117" ht="22.5" customHeight="1">
+      <c r="A117" s="4">
+        <v>46253.0</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D117" s="9">
+        <v>2110202.0</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F117" s="9">
+        <v>179640.0</v>
+      </c>
+      <c r="G117" s="9">
+        <v>160928.0</v>
+      </c>
+      <c r="H117" s="9">
+        <v>39060.0</v>
+      </c>
+      <c r="I117" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J117" s="11"/>
+    </row>
+    <row r="118" ht="22.5" customHeight="1">
+      <c r="A118" s="4">
+        <v>46253.0</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D118" s="9">
+        <v>2110402.0</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="9">
+        <v>26880.0</v>
+      </c>
+      <c r="G118" s="9">
+        <v>4990.0</v>
+      </c>
+      <c r="H118" s="9">
+        <v>25680.0</v>
+      </c>
+      <c r="I118" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J118" s="11"/>
+    </row>
+    <row r="119" ht="22.5" customHeight="1">
+      <c r="A119" s="4">
+        <v>46253.0</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D119" s="9">
+        <v>152384.0</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F119" s="9">
+        <v>14230.0</v>
+      </c>
+      <c r="G119" s="9">
+        <v>3645.0</v>
+      </c>
+      <c r="H119" s="9">
+        <v>13200.0</v>
+      </c>
+      <c r="I119" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J119" s="11"/>
+    </row>
+    <row r="120" ht="22.5" customHeight="1">
+      <c r="A120" s="4">
+        <v>46253.0</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D120" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F120" s="9">
+        <v>26677.0</v>
+      </c>
+      <c r="G120" s="9">
+        <v>6105.0</v>
+      </c>
+      <c r="H120" s="9">
+        <v>11790.0</v>
+      </c>
+      <c r="I120" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J120" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="121" ht="22.5" customHeight="1">
+      <c r="A121" s="4">
+        <v>46253.0</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D121" s="9">
+        <v>2110317.0</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F121" s="9">
+        <v>22500.0</v>
+      </c>
+      <c r="G121" s="9">
+        <v>5807.0</v>
+      </c>
+      <c r="H121" s="9">
+        <v>18300.0</v>
+      </c>
+      <c r="I121" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="J121" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="122" ht="22.5" customHeight="1">
+      <c r="A122" s="4">
+        <v>46253.0</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D122" s="9">
+        <v>112271.0</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F122" s="9">
+        <v>16500.0</v>
+      </c>
+      <c r="G122" s="9">
+        <v>5820.0</v>
+      </c>
+      <c r="H122" s="9">
+        <v>8100.0</v>
+      </c>
+      <c r="I122" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J122" s="11" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="123">
       <c r="I123" s="21"/>
@@ -7215,13 +7398,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I116">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I122">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I117:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I123:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A116">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A122">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -7284,11 +7467,11 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>46224.0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="9">
@@ -7309,12 +7492,12 @@
       <c r="I2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>17</v>
+      <c r="J2" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>46224.0</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -7337,18 +7520,18 @@
         <v>60.0</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>46225.0</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="9">
@@ -7367,18 +7550,18 @@
         <v>543038.0</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>46225.0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="9">
@@ -7399,12 +7582,12 @@
       <c r="I5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>46225.0</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -7415,7 +7598,7 @@
         <v>112268.0</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" s="9">
         <v>3000.0</v>
@@ -7429,23 +7612,23 @@
       <c r="I6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="9">
         <v>132357.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" s="9">
         <v>1560.0</v>
@@ -7459,12 +7642,12 @@
       <c r="I7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>45</v>
+      <c r="J7" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>46225.0</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -7475,7 +7658,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F8" s="9">
         <v>720.0</v>
@@ -7489,16 +7672,16 @@
       <c r="I8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>46225.0</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="9">
@@ -7519,12 +7702,12 @@
       <c r="I9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>46226.0</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -7535,7 +7718,7 @@
         <v>73001.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F10" s="9">
         <v>73787.0</v>
@@ -7549,12 +7732,12 @@
       <c r="I10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>56</v>
+      <c r="J10" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>46226.0</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -7565,7 +7748,7 @@
         <v>112268.0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" s="9">
         <v>3300.0</v>
@@ -7577,12 +7760,12 @@
         <v>3300.0</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J11" s="11"/>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>46226.0</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -7605,16 +7788,16 @@
         <v>3900.0</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J12" s="11"/>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>46226.0</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="9">
@@ -7635,12 +7818,12 @@
       <c r="I13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>56</v>
+      <c r="J13" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>46227.0</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -7651,7 +7834,7 @@
         <v>72001.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F14" s="9">
         <v>21905.0</v>
@@ -7665,12 +7848,12 @@
       <c r="I14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>56</v>
+      <c r="J14" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>46227.0</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -7681,7 +7864,7 @@
         <v>2110327.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F15" s="9">
         <v>69120.0</v>
@@ -7695,12 +7878,12 @@
       <c r="I15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>65</v>
+      <c r="J15" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <v>46227.0</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -7723,12 +7906,12 @@
         <v>1500.0</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J16" s="11"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>46227.0</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -7739,7 +7922,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F17" s="9">
         <v>720.0</v>
@@ -7751,12 +7934,12 @@
         <v>2580.0</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J17" s="11"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <v>46227.0</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -7767,7 +7950,7 @@
         <v>112268.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F18" s="9">
         <v>3300.0</v>
@@ -7781,23 +7964,23 @@
       <c r="I18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="12" t="s">
-        <v>68</v>
+      <c r="J18" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <v>46230.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="9">
         <v>2410401.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F19" s="9">
         <v>136538.0</v>
@@ -7811,16 +7994,16 @@
       <c r="I19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="12" t="s">
-        <v>71</v>
+      <c r="J19" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="5">
+      <c r="A20" s="4">
         <v>46231.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="9">
@@ -7841,23 +8024,23 @@
       <c r="I20" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="12" t="s">
-        <v>71</v>
+      <c r="J20" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <v>46231.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="9">
         <v>10601.0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F21" s="9">
         <v>1230.0</v>
@@ -7871,12 +8054,12 @@
       <c r="I21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="12" t="s">
-        <v>74</v>
+      <c r="J21" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <v>46231.0</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -7887,7 +8070,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F22" s="9">
         <v>4320.0</v>
@@ -7901,10 +8084,10 @@
       <c r="I22" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="12"/>
+      <c r="J22" s="11"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <v>46231.0</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -7915,7 +8098,7 @@
         <v>114357.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F23" s="9">
         <v>240.0</v>
@@ -7929,14 +8112,14 @@
       <c r="I23" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="12"/>
+      <c r="J23" s="11"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="5">
+      <c r="A24" s="4">
         <v>46232.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="9">
@@ -7957,10 +8140,10 @@
       <c r="I24" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="12"/>
+      <c r="J24" s="11"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <v>46232.0</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -7971,7 +8154,7 @@
         <v>112268.0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F25" s="9">
         <v>5700.0</v>
@@ -7985,10 +8168,10 @@
       <c r="I25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="11"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="5">
+      <c r="A26" s="4">
         <v>46232.0</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -7999,7 +8182,7 @@
         <v>2110317.0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F26" s="9">
         <v>720.0</v>
@@ -8013,10 +8196,10 @@
       <c r="I26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J26" s="12"/>
+      <c r="J26" s="11"/>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="5">
+      <c r="A27" s="4">
         <v>46232.0</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -8027,7 +8210,7 @@
         <v>2114357.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F27" s="9">
         <v>432.0</v>
@@ -8041,14 +8224,14 @@
       <c r="I27" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J27" s="12"/>
+      <c r="J27" s="11"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="5">
+      <c r="A28" s="4">
         <v>46232.0</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="9">
@@ -8069,10 +8252,10 @@
       <c r="I28" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="12"/>
+      <c r="J28" s="11"/>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="5">
+      <c r="A29" s="4">
         <v>46233.0</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -8083,7 +8266,7 @@
         <v>112268.0</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F29" s="9">
         <v>5100.0</v>
@@ -8097,10 +8280,10 @@
       <c r="I29" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J29" s="12"/>
+      <c r="J29" s="11"/>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="5">
+      <c r="A30" s="4">
         <v>46233.0</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -8111,7 +8294,7 @@
         <v>114357.0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F30" s="9">
         <v>240.0</v>
@@ -8125,21 +8308,21 @@
       <c r="I30" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J30" s="12"/>
+      <c r="J30" s="11"/>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="5">
+      <c r="A31" s="4">
         <v>46233.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="9">
         <v>10601.0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F31" s="9">
         <v>7717.0</v>
@@ -8153,23 +8336,23 @@
       <c r="I31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J31" s="12" t="s">
-        <v>86</v>
+      <c r="J31" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="5">
+      <c r="A32" s="4">
         <v>46234.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="9">
         <v>79110.0</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F32" s="9">
         <v>48000.0</v>
@@ -8181,18 +8364,18 @@
         <v>36300.0</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>89</v>
+        <v>22</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="5">
+      <c r="A33" s="4">
         <v>46234.0</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="9">
@@ -8213,12 +8396,12 @@
       <c r="I33" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J33" s="18" t="s">
-        <v>90</v>
+      <c r="J33" s="17" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="5">
+      <c r="A34" s="4">
         <v>46234.0</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -8229,7 +8412,7 @@
         <v>73001.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F34" s="9">
         <v>73367.0</v>
@@ -8243,10 +8426,10 @@
       <c r="I34" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J34" s="12"/>
+      <c r="J34" s="11"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="5">
+      <c r="A35" s="4">
         <v>46234.0</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -8257,7 +8440,7 @@
         <v>112357.0</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F35" s="9">
         <v>840.0</v>
@@ -8271,7 +8454,7 @@
       <c r="I35" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J35" s="12"/>
+      <c r="J35" s="11"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
       <c r="A36" s="19">
@@ -8285,7 +8468,7 @@
         <v>10601.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F36" s="9">
         <v>17934.0</v>
@@ -8299,8 +8482,8 @@
       <c r="I36" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J36" s="12" t="s">
-        <v>96</v>
+      <c r="J36" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
@@ -8327,9 +8510,9 @@
         <v>122840.0</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J37" s="11"/>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
       <c r="A38" s="19">
@@ -8343,7 +8526,7 @@
         <v>114379.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F38" s="9">
         <v>52200.0</v>
@@ -8357,7 +8540,7 @@
       <c r="I38" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J38" s="12"/>
+      <c r="J38" s="11"/>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
       <c r="A39" s="19">
@@ -8371,7 +8554,7 @@
         <v>2110317.0</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F39" s="9">
         <v>6450.0</v>
@@ -8383,9 +8566,9 @@
         <v>6480.0</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J39" s="11"/>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
       <c r="A40" s="19">
@@ -8399,7 +8582,7 @@
         <v>2010102.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F40" s="9">
         <v>1398.0</v>
@@ -8411,12 +8594,12 @@
         <v>438.0</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J40" s="11"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="5">
+      <c r="A41" s="4">
         <v>46238.0</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -8427,7 +8610,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F41" s="9">
         <v>2460.0</v>
@@ -8439,12 +8622,12 @@
         <v>3240.0</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J41" s="11"/>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="5">
+      <c r="A42" s="4">
         <v>46238.0</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -8455,7 +8638,7 @@
         <v>112268.0</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F42" s="9">
         <v>3600.0</v>
@@ -8467,12 +8650,12 @@
         <v>3900.0</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J42" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J42" s="11"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="5">
+      <c r="A43" s="4">
         <v>46238.0</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -8483,7 +8666,7 @@
         <v>114379.0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F43" s="9">
         <v>7500.0</v>
@@ -8495,12 +8678,12 @@
         <v>8400.0</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J43" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J43" s="11"/>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="5">
+      <c r="A44" s="4">
         <v>46238.0</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -8511,7 +8694,7 @@
         <v>114357.0</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F44" s="9">
         <v>240.0</v>
@@ -8523,23 +8706,23 @@
         <v>360.0</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="J44" s="11"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="5">
+      <c r="A45" s="4">
         <v>46239.0</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="9">
         <v>10601.0</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F45" s="9">
         <v>1115.0</v>
@@ -8553,12 +8736,12 @@
       <c r="I45" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J45" s="12" t="s">
-        <v>109</v>
+      <c r="J45" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="5">
+      <c r="A46" s="4">
         <v>46239.0</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -8581,12 +8764,12 @@
         <v>191130.0</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" s="12"/>
+        <v>22</v>
+      </c>
+      <c r="J46" s="11"/>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="5">
+      <c r="A47" s="4">
         <v>46239.0</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -8597,7 +8780,7 @@
         <v>2112207.0</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F47" s="9">
         <v>1800.0</v>
@@ -8611,10 +8794,10 @@
       <c r="I47" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J47" s="12"/>
+      <c r="J47" s="11"/>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="5">
+      <c r="A48" s="4">
         <v>46239.0</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -8625,7 +8808,7 @@
         <v>112268.0</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F48" s="9">
         <v>3900.0</v>
@@ -8639,10 +8822,10 @@
       <c r="I48" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J48" s="12"/>
+      <c r="J48" s="11"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="5">
+      <c r="A49" s="4">
         <v>46239.0</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -8653,7 +8836,7 @@
         <v>112357.0</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F49" s="9">
         <v>600.0</v>
@@ -8667,10 +8850,10 @@
       <c r="I49" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J49" s="12"/>
+      <c r="J49" s="11"/>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="5">
+      <c r="A50" s="4">
         <v>46239.0</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -8681,7 +8864,7 @@
         <v>114268.0</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F50" s="9">
         <v>2700.0</v>
@@ -8695,14 +8878,14 @@
       <c r="I50" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J50" s="12"/>
+      <c r="J50" s="11"/>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="5">
+      <c r="A51" s="4">
         <v>46239.0</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C51" s="14"/>
       <c r="D51" s="9">
@@ -8723,23 +8906,23 @@
       <c r="I51" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J51" s="12" t="s">
-        <v>118</v>
+      <c r="J51" s="11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="5">
+      <c r="A52" s="4">
         <v>46239.0</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C52" s="14"/>
       <c r="D52" s="9">
         <v>72003.0</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F52" s="9">
         <v>1391.0</v>
@@ -8751,16 +8934,16 @@
         <v>2407.0</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J52" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="J52" s="11"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="5">
+      <c r="A53" s="4">
         <v>46239.0</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C53" s="14"/>
       <c r="D53" s="9">
@@ -8781,11 +8964,11 @@
       <c r="I53" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J53" s="12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="54" ht="22.5" customHeight="1">
+      <c r="J53" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" hidden="1" customHeight="1">
       <c r="A54" s="19">
         <v>46240.0</v>
       </c>
@@ -8809,11 +8992,11 @@
         <v>6900.0</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J54" s="12"/>
-    </row>
-    <row r="55" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J54" s="11"/>
+    </row>
+    <row r="55" ht="22.5" hidden="1" customHeight="1">
       <c r="A55" s="19">
         <v>46240.0</v>
       </c>
@@ -8825,7 +9008,7 @@
         <v>73001.0</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F55" s="9">
         <v>2415.0</v>
@@ -8837,11 +9020,11 @@
         <v>2415.0</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J55" s="12"/>
-    </row>
-    <row r="56" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J55" s="11"/>
+    </row>
+    <row r="56" ht="22.5" hidden="1" customHeight="1">
       <c r="A56" s="19">
         <v>46240.0</v>
       </c>
@@ -8853,7 +9036,7 @@
         <v>112357.0</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F56" s="9">
         <v>600.0</v>
@@ -8865,11 +9048,11 @@
         <v>600.0</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J56" s="12"/>
-    </row>
-    <row r="57" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J56" s="11"/>
+    </row>
+    <row r="57" ht="22.5" hidden="1" customHeight="1">
       <c r="A57" s="19">
         <v>46240.0</v>
       </c>
@@ -8881,7 +9064,7 @@
         <v>114379.0</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F57" s="9">
         <v>2400.0</v>
@@ -8893,11 +9076,11 @@
         <v>300.0</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J57" s="12"/>
-    </row>
-    <row r="58" ht="22.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="J57" s="11"/>
+    </row>
+    <row r="58" ht="22.5" hidden="1" customHeight="1">
       <c r="A58" s="19">
         <v>46244.0</v>
       </c>
@@ -8921,12 +9104,12 @@
         <v>5100.0</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" s="12"/>
-    </row>
-    <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="5">
+        <v>23</v>
+      </c>
+      <c r="J58" s="11"/>
+    </row>
+    <row r="59" ht="22.5" hidden="1" customHeight="1">
+      <c r="A59" s="4">
         <v>46245.0</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -8949,12 +9132,12 @@
         <v>42960.0</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J59" s="12"/>
-    </row>
-    <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" s="5">
+        <v>22</v>
+      </c>
+      <c r="J59" s="11"/>
+    </row>
+    <row r="60" ht="22.5" hidden="1" customHeight="1">
+      <c r="A60" s="4">
         <v>46246.0</v>
       </c>
       <c r="B60" s="6" t="s">
@@ -8965,7 +9148,7 @@
         <v>114379.0</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F60" s="9">
         <v>6900.0</v>
@@ -8977,16 +9160,16 @@
         <v>5400.0</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J60" s="12"/>
-    </row>
-    <row r="61" ht="22.5" customHeight="1">
-      <c r="A61" s="5">
+        <v>23</v>
+      </c>
+      <c r="J60" s="11"/>
+    </row>
+    <row r="61" ht="22.5" hidden="1" customHeight="1">
+      <c r="A61" s="4">
         <v>46247.0</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="9">
@@ -9004,22 +9187,24 @@
       <c r="H61" s="9">
         <v>20100.0</v>
       </c>
-      <c r="I61" s="10"/>
-      <c r="J61" s="12"/>
-    </row>
-    <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="5">
+      <c r="I61" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" s="11"/>
+    </row>
+    <row r="62" ht="22.5" hidden="1" customHeight="1">
+      <c r="A62" s="4">
         <v>46247.0</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="9">
         <v>112268.0</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F62" s="9">
         <v>8400.0</v>
@@ -9030,15 +9215,17 @@
       <c r="H62" s="9">
         <v>8400.0</v>
       </c>
-      <c r="I62" s="10"/>
-      <c r="J62" s="12"/>
-    </row>
-    <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="5">
+      <c r="I62" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J62" s="11"/>
+    </row>
+    <row r="63" ht="22.5" hidden="1" customHeight="1">
+      <c r="A63" s="4">
         <v>46247.0</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="9">
@@ -9056,22 +9243,24 @@
       <c r="H63" s="9">
         <v>76033.0</v>
       </c>
-      <c r="I63" s="10"/>
-      <c r="J63" s="12"/>
-    </row>
-    <row r="64" ht="22.5" customHeight="1">
-      <c r="A64" s="5">
+      <c r="I63" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J63" s="11"/>
+    </row>
+    <row r="64" ht="22.5" hidden="1" customHeight="1">
+      <c r="A64" s="4">
         <v>46247.0</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="9">
         <v>13358.0</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F64" s="9">
         <v>73728.0</v>
@@ -9085,16 +9274,16 @@
       <c r="I64" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J64" s="12" t="s">
-        <v>132</v>
+      <c r="J64" s="11" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
-      <c r="A65" s="5">
+      <c r="A65" s="4">
         <v>46248.0</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="9">
@@ -9115,23 +9304,23 @@
       <c r="I65" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J65" s="12" t="s">
-        <v>133</v>
+      <c r="J65" s="11" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
-      <c r="A66" s="5">
+      <c r="A66" s="4">
         <v>46248.0</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="9">
         <v>73001.0</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F66" s="9">
         <v>31772.0</v>
@@ -9145,8 +9334,8 @@
       <c r="I66" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J66" s="12" t="s">
-        <v>134</v>
+      <c r="J66" s="11" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="67">
@@ -11824,19 +12013,13 @@
     </row>
     <row r="958">
       <c r="I958" s="21"/>
-    </row>
-    <row r="959">
-      <c r="I959" s="21"/>
-    </row>
-    <row r="960">
-      <c r="I960" s="21"/>
     </row>
   </sheetData>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="I2:I66">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I67:I960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I67:I958">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A66">

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="188">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -44,22 +44,40 @@
     <t xml:space="preserve">Otro </t>
   </si>
   <si>
+    <t>ALKA2</t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>7. Otro</t>
+  </si>
+  <si>
+    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
+  </si>
+  <si>
     <t>TAT BOGOTA MONTEVIDEO</t>
   </si>
   <si>
     <t>Daniel Castro</t>
   </si>
   <si>
+    <t>LANZA</t>
+  </si>
+  <si>
     <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>ALKA2</t>
+    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+    <t>6. Transformación De Referencias</t>
+  </si>
+  <si>
+    <t>Pendiente Transformar Roto GT Por manipulación</t>
   </si>
   <si>
     <t>TAT MONTERIA</t>
@@ -68,16 +86,10 @@
     <t>LUIS LOPEZ</t>
   </si>
   <si>
-    <t>7. Otro</t>
-  </si>
-  <si>
-    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
-  </si>
-  <si>
     <t>3. Falla De Rotación</t>
   </si>
   <si>
-    <t>LANZA</t>
+    <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
     <t>TAT MEDELLIN</t>
@@ -86,114 +98,105 @@
     <t>FABIO GOMEZ</t>
   </si>
   <si>
-    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
+    <t>se equivocaron al cargar una estiba</t>
   </si>
   <si>
     <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
   </si>
   <si>
-    <t>6. Transformación De Referencias</t>
-  </si>
-  <si>
-    <t>Pendiente Transformar Roto GT Por manipulación</t>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
     <t>TAT CARTAGENA</t>
   </si>
   <si>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
     <t>Dilan Barraza</t>
   </si>
   <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO B X30 CARTON GRIS</t>
-  </si>
-  <si>
     <t>4. Exigencia Del Cliente (Edad)</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
+  </si>
+  <si>
     <t>Venta FS</t>
   </si>
   <si>
-    <t>se equivocaron al cargar una estiba</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
+    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
+  </si>
+  <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
-  </si>
-  <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+  </si>
+  <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
-    <t>PALMAS</t>
-  </si>
-  <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
-  </si>
-  <si>
     <t>TAT CALI</t>
   </si>
   <si>
+    <t>HUEVO PICADO ROJO</t>
+  </si>
+  <si>
     <t>DIEGO ROJAS</t>
   </si>
   <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+    <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
     <t>TAT CUCUTA</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
     <t>ALEXANDER PEÑA</t>
   </si>
   <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
-  </si>
-  <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
-  </si>
-  <si>
     <t>Clientes FS</t>
   </si>
   <si>
-    <t>HUEVO PICADO ROJO</t>
-  </si>
-  <si>
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
-    <t>No se carga todod por capacidad de Vehiculo</t>
-  </si>
-  <si>
     <t>Transformación de PET</t>
   </si>
   <si>
     <t>ANDRES MEJIA</t>
   </si>
   <si>
+    <t>HUEVO SUCIO DE JAULA</t>
+  </si>
+  <si>
     <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
   </si>
   <si>
@@ -203,9 +206,6 @@
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
-    <t>HUEVO SUCIO DE JAULA</t>
-  </si>
-  <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
   </si>
   <si>
@@ -221,109 +221,127 @@
     <t>Cola de programación</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+  </si>
+  <si>
     <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
   </si>
   <si>
     <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
+    <t>5. Ingreso De Planta</t>
+  </si>
+  <si>
+    <t>Se despacha par FS con producto más nuevo</t>
   </si>
   <si>
     <t>HUEVO CX30 CARTON GRIS</t>
   </si>
   <si>
-    <t>5. Ingreso De Planta</t>
-  </si>
-  <si>
     <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
   </si>
   <si>
-    <t>Se despacha par FS con producto más nuevo</t>
+    <t>ANDREA QUIROGA</t>
+  </si>
+  <si>
+    <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
   </si>
   <si>
     <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
-    <t>ANDREA QUIROGA</t>
-  </si>
-  <si>
-    <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
-  </si>
-  <si>
     <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
+    <t>TAT PASTO</t>
+  </si>
+  <si>
+    <t>CAROLINA VITERI</t>
+  </si>
+  <si>
     <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
   </si>
   <si>
     <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
-    <t>TAT PASTO</t>
-  </si>
-  <si>
-    <t>CAROLINA VITERI</t>
+    <t>Asignacion a canal Tat para sugeridos de hoy</t>
+  </si>
+  <si>
+    <t>Pedido para villavicencio</t>
+  </si>
+  <si>
+    <t>Se entrega inventario nuevo para FS</t>
+  </si>
+  <si>
+    <t>Inventario de Asesor de Rionegro que renuncio</t>
   </si>
   <si>
     <t>ALKA1</t>
   </si>
   <si>
-    <t>Asignacion a canal Tat para sugeridos de hoy</t>
+    <t>TAT BARRANQUILLA</t>
+  </si>
+  <si>
+    <t>Jhonatan Gomez</t>
   </si>
   <si>
     <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
   </si>
   <si>
+    <t>Lote mezclado en la misma estiba</t>
+  </si>
+  <si>
     <t>HUEVO ROTO - ZF</t>
   </si>
   <si>
-    <t>Pedido para villavicencio</t>
-  </si>
-  <si>
     <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
   </si>
   <si>
+    <t>Supera edad solicitada clientes grandes superficies</t>
+  </si>
+  <si>
     <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
   </si>
   <si>
-    <t>Se entrega inventario nuevo para FS</t>
+    <t>Pedido para villacicencio</t>
   </si>
   <si>
     <t>HUEVO L X 12 PET CAJA X 120</t>
   </si>
   <si>
-    <t>Inventario de Asesor de Rionegro que renuncio</t>
-  </si>
-  <si>
-    <t>TAT BARRANQUILLA</t>
-  </si>
-  <si>
-    <t>Jhonatan Gomez</t>
+    <t>Se envía huevo más fresco a Sincelejo</t>
+  </si>
+  <si>
+    <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
   </si>
   <si>
     <t>Cargo en incubación</t>
   </si>
   <si>
-    <t>Lote mezclado en la misma estiba</t>
+    <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
   </si>
   <si>
     <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>Supera edad solicitada clientes grandes superficies</t>
-  </si>
-  <si>
-    <t>Pedido para villacicencio</t>
-  </si>
-  <si>
-    <t>Se envía huevo más fresco a Sincelejo</t>
-  </si>
-  <si>
-    <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
-  </si>
-  <si>
-    <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
+    <t>SalIO en sugeridos de hoy 22/07/2026</t>
+  </si>
+  <si>
+    <t>Yovanis Arevalo</t>
+  </si>
+  <si>
+    <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
+  </si>
+  <si>
+    <t>Devolucion de huevo de 12 dias en mal estado</t>
+  </si>
+  <si>
+    <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
+  </si>
+  <si>
+    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
     <t>BELLAVISTA</t>
@@ -332,19 +350,16 @@
     <t>Traslado a cedi, producto de devolución</t>
   </si>
   <si>
-    <t>SalIO en sugeridos de hoy 22/07/2026</t>
-  </si>
-  <si>
-    <t>Yovanis Arevalo</t>
+    <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
-    <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
-  </si>
-  <si>
-    <t>Devolucion de huevo de 12 dias en mal estado</t>
+    <t>Se envía producto a Sincelejo con menor edad</t>
+  </si>
+  <si>
+    <t>Producto que queda de clientes de preventa - TAT, que el cliente no recibe</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
@@ -353,97 +368,82 @@
     <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
   </si>
   <si>
-    <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
+    <t>TAT VILLAVICENCIO</t>
   </si>
   <si>
     <t>HUEVO SUCIO ZF MARCADO</t>
   </si>
   <si>
-    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
-  </si>
-  <si>
     <t>vehiculo con flata de capacidad / TAT cali</t>
   </si>
   <si>
-    <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
-  </si>
-  <si>
-    <t>Se envía producto a Sincelejo con menor edad</t>
-  </si>
-  <si>
-    <t>Producto que queda de clientes de preventa - TAT, que el cliente no recibe</t>
-  </si>
-  <si>
-    <t>TAT VILLAVICENCIO</t>
+    <t xml:space="preserve">En la estiba llegan lotes en la parte de abajo </t>
+  </si>
+  <si>
+    <t>TAT BUCARAMANGA</t>
+  </si>
+  <si>
+    <t>SHIRLEY ARIZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No salio la totalidad  de la mercancia y se roto el de 5 dias </t>
   </si>
   <si>
     <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
   </si>
   <si>
+    <t>Producto queda en CEDI por calidad</t>
+  </si>
+  <si>
     <t>vehiculo pendiente pro llegar a planta</t>
   </si>
   <si>
-    <t xml:space="preserve">En la estiba llegan lotes en la parte de abajo </t>
-  </si>
-  <si>
     <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
   </si>
   <si>
+    <t>Producto devuelto clientes TAT</t>
+  </si>
+  <si>
     <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
   </si>
   <si>
-    <t>TAT BUCARAMANGA</t>
-  </si>
-  <si>
-    <t>SHIRLEY ARIZA</t>
-  </si>
-  <si>
     <t>no salio el dia progrmado por falta de flota, se corre despacho para el dia siguiente en la tarde</t>
   </si>
   <si>
-    <t xml:space="preserve">No salio la totalidad  de la mercancia y se roto el de 5 dias </t>
+    <t xml:space="preserve">ALEXANDER PEÑA </t>
   </si>
   <si>
     <t>anularon pedidos y por orden de planeacion se autorizo soltar para enviar a medellin</t>
   </si>
   <si>
-    <t>Producto queda en CEDI por calidad</t>
-  </si>
-  <si>
-    <t>Producto devuelto clientes TAT</t>
+    <t>Llegaron canastas combinados llegaron en la parte de abajo</t>
   </si>
   <si>
     <t>Clasificación entrego una caja de más y no fue posible rotarla en cliente olimpica.</t>
   </si>
   <si>
-    <t xml:space="preserve">ALEXANDER PEÑA </t>
+    <t>ANDRES MEJA</t>
   </si>
   <si>
     <t>NO SE PUEDE BAJAR DE LA ESTANTERIA POR DAÑO DE PANTOGRAFOS</t>
   </si>
   <si>
-    <t>Llegaron canastas combinados llegaron en la parte de abajo</t>
-  </si>
-  <si>
-    <t>ANDRES MEJA</t>
+    <t>Se envía lotemás nuevo a Sincelejo</t>
   </si>
   <si>
     <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
-  </si>
-  <si>
-    <t>Se envía lotemás nuevo a Sincelejo</t>
   </si>
   <si>
     <t xml:space="preserve"> estaba programado para despacho a tat cali, planeación quito el pedido y se nos notificó que se debía dar rotación inmediatamente.
 En simultáneo, se cargó la mula y se desencadenaron las 18.000 unidades de 112379 para despachar para Medellín. En esta acción nos percatamos solo cuando la mula ya estaba en un 70 % cargada que se nos estaban quedando 21.525 de la referencia L canastas (2110302) con fecha de producción 19/08/2026.</t>
   </si>
   <si>
+    <t>Se envía huevo más fresco para clientes FS</t>
+  </si>
+  <si>
     <t>REPOSICION SIN SOLTAR</t>
   </si>
   <si>
-    <t>Se envía huevo más fresco para clientes FS</t>
-  </si>
-  <si>
     <t>Producto enviado a Rionegro y para FS más fresco</t>
   </si>
   <si>
@@ -565,6 +565,18 @@
   </si>
   <si>
     <t>Producto para revisión por calidad</t>
+  </si>
+  <si>
+    <t>TAT SANTA MARTA</t>
+  </si>
+  <si>
+    <t>LEONARDO MEDINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JONATHAN MOSQUERA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIO GOMEZ </t>
   </si>
 </sst>
 </file>
@@ -604,14 +616,14 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -642,63 +654,63 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -759,13 +771,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Cedis-style">
+    <tableStyle count="4" pivot="0" name="Plantas-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Plantas-style">
+    <tableStyle count="4" pivot="0" name="Cedis-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -788,7 +800,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J139" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J143" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -806,7 +818,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J76" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J78" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -1069,20 +1081,20 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="10">
         <v>46204.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="D2" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F2" s="7">
         <v>359100.0</v>
@@ -1093,25 +1105,25 @@
       <c r="H2" s="7">
         <v>206140.0</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>14</v>
+      <c r="I2" s="12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="8">
+      <c r="A3" s="4">
         <v>46205.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="D3" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" s="7">
         <v>298282.0</v>
@@ -1123,25 +1135,25 @@
         <v>260675.0</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="10"/>
+        <v>24</v>
+      </c>
+      <c r="J3" s="6"/>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="8">
+      <c r="A4" s="4">
         <v>46205.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D4" s="7">
         <v>2110217.0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F4" s="7">
         <v>21120.0</v>
@@ -1153,25 +1165,25 @@
         <v>16920.0</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="10"/>
+        <v>19</v>
+      </c>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="8">
+      <c r="A5" s="4">
         <v>46205.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="D5" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F5" s="7">
         <v>75680.0</v>
@@ -1183,27 +1195,27 @@
         <v>3134.0</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="8">
+      <c r="A6" s="4">
         <v>46206.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D6" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F6" s="7">
         <v>189540.0</v>
@@ -1215,27 +1227,27 @@
         <v>144720.0</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>36</v>
+        <v>12</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="8">
+      <c r="A7" s="4">
         <v>46206.0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D7" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F7" s="7">
         <v>20640.0</v>
@@ -1247,27 +1259,27 @@
         <v>13920.0</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="8">
+      <c r="A8" s="4">
         <v>46206.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D8" s="7">
         <v>152384.0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F8" s="7">
         <v>14700.0</v>
@@ -1279,25 +1291,25 @@
         <v>9600.0</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="12"/>
+        <v>49</v>
+      </c>
+      <c r="J8" s="9"/>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="8">
+      <c r="A9" s="4">
         <v>46206.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D9" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F9" s="7">
         <v>228240.0</v>
@@ -1309,25 +1321,25 @@
         <v>124260.0</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="12"/>
+        <v>49</v>
+      </c>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="8">
+      <c r="A10" s="4">
         <v>46206.0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="D10" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F10" s="7">
         <v>7830.0</v>
@@ -1339,25 +1351,25 @@
         <v>6030.0</v>
       </c>
       <c r="I10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
+      <c r="A11" s="4">
+        <v>46206.0</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="8">
-        <v>46206.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>23</v>
+      <c r="C11" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D11" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F11" s="7">
         <v>31680.0</v>
@@ -1369,27 +1381,27 @@
         <v>23040.0</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>54</v>
+        <v>35</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="8">
+      <c r="A12" s="4">
         <v>46206.0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="D12" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F12" s="7">
         <v>51387.0</v>
@@ -1401,27 +1413,27 @@
         <v>12170.0</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>56</v>
+        <v>35</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="8">
+      <c r="A13" s="4">
         <v>46209.0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="D13" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F13" s="7">
         <v>195810.0</v>
@@ -1433,27 +1445,27 @@
         <v>133410.0</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>56</v>
+        <v>35</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="8">
+      <c r="A14" s="4">
         <v>46209.0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="D14" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F14" s="7">
         <v>526002.0</v>
@@ -1465,27 +1477,27 @@
         <v>424588.0</v>
       </c>
       <c r="I14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
+      <c r="A15" s="4">
+        <v>46209.0</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="8">
-        <v>46209.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D15" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F15" s="7">
         <v>14160.0</v>
@@ -1497,27 +1509,27 @@
         <v>12360.0</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>60</v>
+        <v>12</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="8">
+      <c r="A16" s="4">
         <v>46210.0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="6" t="s">
         <v>62</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="D16" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F16" s="7">
         <v>149040.0</v>
@@ -1529,25 +1541,25 @@
         <v>289680.0</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="12"/>
+        <v>19</v>
+      </c>
+      <c r="J16" s="9"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="8">
+      <c r="A17" s="4">
         <v>46210.0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D17" s="7">
         <v>2110217.0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F17" s="7">
         <v>22770.0</v>
@@ -1559,25 +1571,25 @@
         <v>19770.0</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="12"/>
+        <v>19</v>
+      </c>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="8">
+      <c r="A18" s="4">
         <v>46210.0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D18" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F18" s="7">
         <v>222021.0</v>
@@ -1589,25 +1601,25 @@
         <v>162125.0</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" s="12"/>
+        <v>19</v>
+      </c>
+      <c r="J18" s="9"/>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="8">
+      <c r="A19" s="4">
         <v>46211.0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="D19" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F19" s="7">
         <v>495833.0</v>
@@ -1619,27 +1631,27 @@
         <v>401280.0</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="8">
+      <c r="A20" s="4">
         <v>46211.0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="D20" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F20" s="7">
         <v>139920.0</v>
@@ -1651,25 +1663,25 @@
         <v>74040.0</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="12"/>
+        <v>19</v>
+      </c>
+      <c r="J20" s="9"/>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="8">
+      <c r="A21" s="4">
         <v>46211.0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D21" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F21" s="7">
         <v>162125.0</v>
@@ -1681,27 +1693,27 @@
         <v>100687.0</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="8">
+      <c r="A22" s="4">
         <v>46211.0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="D22" s="7">
         <v>152384.0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F22" s="7">
         <v>32850.0</v>
@@ -1713,25 +1725,25 @@
         <v>32700.0</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="12"/>
+        <v>35</v>
+      </c>
+      <c r="J22" s="9"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="8">
+      <c r="A23" s="4">
         <v>46211.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D23" s="7">
         <v>112271.0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F23" s="7">
         <v>16500.0</v>
@@ -1743,25 +1755,25 @@
         <v>18000.0</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J23" s="12"/>
+        <v>49</v>
+      </c>
+      <c r="J23" s="9"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="8">
+      <c r="A24" s="4">
         <v>46212.0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D24" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F24" s="7">
         <v>190047.0</v>
@@ -1773,16 +1785,16 @@
         <v>248481.0</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J24" s="12"/>
+        <v>49</v>
+      </c>
+      <c r="J24" s="9"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="8">
+      <c r="A25" s="4">
         <v>46212.0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>59</v>
@@ -1791,7 +1803,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F25" s="7">
         <v>178080.0</v>
@@ -1803,16 +1815,16 @@
         <v>203520.0</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J25" s="12"/>
+        <v>72</v>
+      </c>
+      <c r="J25" s="9"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="8">
+      <c r="A26" s="4">
         <v>46212.0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>59</v>
@@ -1821,7 +1833,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F26" s="7">
         <v>10320.0</v>
@@ -1833,18 +1845,18 @@
         <v>13200.0</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>75</v>
+        <v>35</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="8">
+      <c r="A27" s="4">
         <v>46212.0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>59</v>
@@ -1853,7 +1865,7 @@
         <v>112271.0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F27" s="7">
         <v>18000.0</v>
@@ -1865,25 +1877,25 @@
         <v>13500.0</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J27" s="9"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="8">
+      <c r="A28" s="4">
         <v>46213.0</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D28" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F28" s="7">
         <v>208440.0</v>
@@ -1895,27 +1907,27 @@
         <v>150833.0</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>78</v>
+        <v>12</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="8">
+      <c r="A29" s="4">
         <v>46213.0</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D29" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F29" s="7">
         <v>962820.0</v>
@@ -1927,18 +1939,18 @@
         <v>922140.0</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" s="12" t="s">
-        <v>78</v>
+        <v>12</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="8">
+      <c r="A30" s="4">
         <v>46213.0</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>59</v>
@@ -1947,7 +1959,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F30" s="7">
         <v>335340.0</v>
@@ -1959,27 +1971,27 @@
         <v>381600.0</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J30" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="8">
+      <c r="A31" s="4">
         <v>46213.0</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D31" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F31" s="7">
         <v>316800.0</v>
@@ -1991,25 +2003,25 @@
         <v>229680.0</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J31" s="9"/>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="8">
+      <c r="A32" s="4">
         <v>46213.0</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D32" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F32" s="7">
         <v>176850.0</v>
@@ -2021,25 +2033,25 @@
         <v>128971.0</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J32" s="12"/>
+        <v>49</v>
+      </c>
+      <c r="J32" s="9"/>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="8">
+      <c r="A33" s="4">
         <v>46213.0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D33" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F33" s="7">
         <v>58080.0</v>
@@ -2051,25 +2063,25 @@
         <v>25440.0</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J33" s="9"/>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="8">
+      <c r="A34" s="4">
         <v>46217.0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="D34" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F34" s="7">
         <v>481440.0</v>
@@ -2081,25 +2093,25 @@
         <v>151435.0</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J34" s="9"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="8">
+      <c r="A35" s="4">
         <v>46217.0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D35" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F35" s="7">
         <v>355720.0</v>
@@ -2111,25 +2123,25 @@
         <v>302760.0</v>
       </c>
       <c r="I35" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="9"/>
+    </row>
+    <row r="36" ht="22.5" hidden="1" customHeight="1">
+      <c r="A36" s="4">
+        <v>46217.0</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J35" s="12"/>
-    </row>
-    <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="8">
-        <v>46217.0</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="C36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D36" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F36" s="7">
         <v>35280.0</v>
@@ -2141,10 +2153,10 @@
         <v>37926.0</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>85</v>
+        <v>24</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
@@ -2152,16 +2164,16 @@
         <v>46218.0</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D37" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F37" s="7">
         <v>272073.0</v>
@@ -2173,10 +2185,10 @@
         <v>275205.0</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>88</v>
+        <v>35</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
@@ -2184,16 +2196,16 @@
         <v>46218.0</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D38" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F38" s="7">
         <v>37926.0</v>
@@ -2205,10 +2217,10 @@
         <v>25746.0</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>85</v>
+        <v>24</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
@@ -2216,16 +2228,16 @@
         <v>46218.0</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D39" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F39" s="7">
         <v>20640.0</v>
@@ -2237,10 +2249,10 @@
         <v>16320.0</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>91</v>
+        <v>35</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
@@ -2248,16 +2260,16 @@
         <v>46218.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D40" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F40" s="7">
         <v>10980.0</v>
@@ -2269,25 +2281,25 @@
         <v>13500.0</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J40" s="9"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="8">
+      <c r="A41" s="4">
         <v>46219.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D41" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F41" s="7">
         <v>130320.0</v>
@@ -2299,27 +2311,27 @@
         <v>90480.0</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>93</v>
+        <v>49</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="8">
+      <c r="A42" s="4">
         <v>46219.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D42" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F42" s="7">
         <v>36225.0</v>
@@ -2331,25 +2343,25 @@
         <v>27570.0</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J42" s="12"/>
+        <v>19</v>
+      </c>
+      <c r="J42" s="9"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="8">
+      <c r="A43" s="4">
         <v>46219.0</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D43" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F43" s="7">
         <v>152833.0</v>
@@ -2361,27 +2373,27 @@
         <v>96472.0</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>97</v>
+        <v>72</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="8">
+      <c r="A44" s="4">
         <v>46219.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D44" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F44" s="7">
         <v>237828.0</v>
@@ -2393,25 +2405,25 @@
         <v>71560.0</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J44" s="9"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="8">
+      <c r="A45" s="4">
         <v>46219.0</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D45" s="7">
         <v>152384.0</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F45" s="7">
         <v>31125.0</v>
@@ -2423,27 +2435,27 @@
         <v>31845.0</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>99</v>
+        <v>35</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="8">
+      <c r="A46" s="4">
         <v>46219.0</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D46" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F46" s="7">
         <v>25746.0</v>
@@ -2455,27 +2467,27 @@
         <v>28683.0</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="12" t="s">
-        <v>85</v>
+        <v>24</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="8">
+      <c r="A47" s="4">
         <v>46220.0</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D47" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F47" s="7">
         <v>261166.0</v>
@@ -2487,27 +2499,27 @@
         <v>221549.0</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="8">
+      <c r="A48" s="4">
         <v>46220.0</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D48" s="7">
         <v>2110217.0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F48" s="7">
         <v>115289.0</v>
@@ -2519,25 +2531,25 @@
         <v>119584.0</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J48" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J48" s="9"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="8">
+      <c r="A49" s="4">
         <v>46224.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D49" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F49" s="7">
         <v>398570.0</v>
@@ -2549,27 +2561,27 @@
         <v>287235.0</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>101</v>
+        <v>35</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="8">
+      <c r="A50" s="4">
         <v>46224.0</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D50" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F50" s="7">
         <v>745107.0</v>
@@ -2581,27 +2593,27 @@
         <v>551645.0</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>102</v>
+        <v>12</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="8">
+      <c r="A51" s="4">
         <v>46225.0</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D51" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F51" s="7">
         <v>130560.0</v>
@@ -2613,27 +2625,27 @@
         <v>153840.0</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>103</v>
+        <v>20</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="8">
+      <c r="A52" s="4">
         <v>46225.0</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D52" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F52" s="7">
         <v>87447.0</v>
@@ -2645,25 +2657,25 @@
         <v>104365.0</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J52" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J52" s="9"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="8">
+      <c r="A53" s="4">
         <v>46225.0</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D53" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F53" s="7">
         <v>25200.0</v>
@@ -2675,27 +2687,27 @@
         <v>25920.0</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>106</v>
+        <v>24</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
-      <c r="A54" s="8">
+      <c r="A54" s="4">
         <v>46226.0</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>107</v>
+        <v>31</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>105</v>
       </c>
       <c r="D54" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F54" s="7">
         <v>285405.0</v>
@@ -2707,27 +2719,27 @@
         <v>226069.0</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>109</v>
+        <v>72</v>
+      </c>
+      <c r="J54" s="9" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
-      <c r="A55" s="8">
+      <c r="A55" s="4">
         <v>46226.0</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C55" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D55" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F55" s="7">
         <v>692280.0</v>
@@ -2739,25 +2751,25 @@
         <v>700200.0</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J55" s="12"/>
+        <v>72</v>
+      </c>
+      <c r="J55" s="9"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
-      <c r="A56" s="8">
+      <c r="A56" s="4">
         <v>46227.0</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D56" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F56" s="7">
         <v>700200.0</v>
@@ -2769,25 +2781,25 @@
         <v>668440.0</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J56" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J56" s="9"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
-      <c r="A57" s="8">
+      <c r="A57" s="4">
         <v>46227.0</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>107</v>
+        <v>31</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>105</v>
       </c>
       <c r="D57" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F57" s="7">
         <v>226069.0</v>
@@ -2799,27 +2811,27 @@
         <v>326391.0</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J57" s="12" t="s">
-        <v>110</v>
+        <v>49</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
-      <c r="A58" s="8">
+      <c r="A58" s="4">
         <v>46227.0</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D58" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F58" s="7">
         <v>144637.0</v>
@@ -2831,25 +2843,25 @@
         <v>128160.0</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J58" s="12"/>
+        <v>72</v>
+      </c>
+      <c r="J58" s="9"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="8">
+      <c r="A59" s="4">
         <v>46227.0</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>95</v>
+        <v>89</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>90</v>
       </c>
       <c r="D59" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F59" s="7">
         <v>295359.0</v>
@@ -2861,27 +2873,27 @@
         <v>166642.0</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>113</v>
+        <v>12</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="8">
+      <c r="A60" s="4">
         <v>46230.0</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>95</v>
+        <v>89</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>90</v>
       </c>
       <c r="D60" s="7">
         <v>2110403.0</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F60" s="7">
         <v>9960.0</v>
@@ -2893,25 +2905,25 @@
         <v>3660.0</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J60" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J60" s="9"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="8">
+      <c r="A61" s="4">
         <v>46230.0</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D61" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F61" s="7">
         <v>306720.0</v>
@@ -2923,25 +2935,25 @@
         <v>247096.0</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J61" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J61" s="9"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
-      <c r="A62" s="8">
+      <c r="A62" s="4">
         <v>46230.0</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D62" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F62" s="7">
         <v>437080.0</v>
@@ -2953,27 +2965,27 @@
         <v>353700.0</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J62" s="12" t="s">
-        <v>117</v>
+        <v>35</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
-      <c r="A63" s="8">
+      <c r="A63" s="4">
         <v>46231.0</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="D63" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F63" s="7">
         <v>165466.0</v>
@@ -2985,27 +2997,27 @@
         <v>375549.0</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>118</v>
+        <v>35</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
-      <c r="A64" s="8">
+      <c r="A64" s="4">
         <v>46231.0</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D64" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F64" s="7">
         <v>238497.0</v>
@@ -3017,27 +3029,27 @@
         <v>181858.0</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J64" s="12" t="s">
-        <v>119</v>
+        <v>49</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
-      <c r="A65" s="8">
+      <c r="A65" s="4">
         <v>46231.0</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D65" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F65" s="7">
         <v>8190.0</v>
@@ -3049,27 +3061,27 @@
         <v>7200.0</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J65" s="12" t="s">
-        <v>119</v>
+        <v>49</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
-      <c r="A66" s="8">
+      <c r="A66" s="4">
         <v>46231.0</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D66" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F66" s="7">
         <v>146224.0</v>
@@ -3081,25 +3093,25 @@
         <v>98850.0</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J66" s="12" t="s">
-        <v>119</v>
+        <v>49</v>
+      </c>
+      <c r="J66" s="9" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
-      <c r="A67" s="8">
+      <c r="A67" s="4">
         <v>46232.0</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C67" s="20"/>
       <c r="D67" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F67" s="7">
         <v>14599.0</v>
@@ -3111,23 +3123,23 @@
         <v>7263.0</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="J67" s="9"/>
     </row>
     <row r="68" ht="22.5" hidden="1" customHeight="1">
-      <c r="A68" s="8">
+      <c r="A68" s="4">
         <v>46232.0</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C68" s="20"/>
       <c r="D68" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F68" s="7">
         <v>22080.0</v>
@@ -3139,23 +3151,23 @@
         <v>36720.0</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="J68" s="9"/>
     </row>
     <row r="69" ht="22.5" hidden="1" customHeight="1">
-      <c r="A69" s="8">
+      <c r="A69" s="4">
         <v>46232.0</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C69" s="20"/>
       <c r="D69" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F69" s="7">
         <v>353905.0</v>
@@ -3167,23 +3179,23 @@
         <v>117570.0</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J69" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="J69" s="9"/>
     </row>
     <row r="70" ht="22.5" hidden="1" customHeight="1">
-      <c r="A70" s="8">
+      <c r="A70" s="4">
         <v>46232.0</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F70" s="7">
         <v>5913.0</v>
@@ -3195,23 +3207,23 @@
         <v>5893.0</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="J70" s="9"/>
     </row>
     <row r="71" ht="22.5" hidden="1" customHeight="1">
-      <c r="A71" s="8">
+      <c r="A71" s="4">
         <v>46232.0</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F71" s="7">
         <v>256613.0</v>
@@ -3223,23 +3235,23 @@
         <v>142320.0</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="J71" s="9"/>
     </row>
     <row r="72" ht="22.5" hidden="1" customHeight="1">
-      <c r="A72" s="8">
+      <c r="A72" s="4">
         <v>46232.0</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C72" s="20"/>
       <c r="D72" s="7">
         <v>152384.0</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F72" s="7">
         <v>21300.0</v>
@@ -3251,23 +3263,23 @@
         <v>18690.0</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="J72" s="9"/>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
-      <c r="A73" s="8">
+      <c r="A73" s="4">
         <v>46232.0</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C73" s="20"/>
       <c r="D73" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F73" s="7">
         <v>351733.0</v>
@@ -3279,25 +3291,25 @@
         <v>200114.0</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J73" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="J73" s="9"/>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
       <c r="A74" s="17">
         <v>46233.0</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D74" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F74" s="7">
         <v>158761.0</v>
@@ -3309,10 +3321,10 @@
         <v>183014.0</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J74" s="12" t="s">
-        <v>123</v>
+        <v>72</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
@@ -3320,16 +3332,16 @@
         <v>46233.0</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D75" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F75" s="7">
         <v>117430.0</v>
@@ -3341,25 +3353,25 @@
         <v>86643.0</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J75" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J75" s="9"/>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
-      <c r="A76" s="8">
+      <c r="A76" s="4">
         <v>46234.0</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D76" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F76" s="7">
         <v>265693.0</v>
@@ -3371,25 +3383,25 @@
         <v>116000.0</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J76" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J76" s="9"/>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
-      <c r="A77" s="8">
+      <c r="A77" s="4">
         <v>46234.0</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>127</v>
+        <v>122</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>123</v>
       </c>
       <c r="D77" s="7">
         <v>112357.0</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F77" s="7">
         <v>720.0</v>
@@ -3401,27 +3413,27 @@
         <v>2040.0</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J77" s="12" t="s">
-        <v>129</v>
+        <v>12</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
-      <c r="A78" s="8">
+      <c r="A78" s="4">
         <v>46234.0</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D78" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F78" s="7">
         <v>5580.0</v>
@@ -3433,10 +3445,10 @@
         <v>3984.0</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J78" s="12" t="s">
-        <v>131</v>
+        <v>49</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="79" ht="22.5" hidden="1" customHeight="1">
@@ -3444,16 +3456,16 @@
         <v>46237.0</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D79" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F79" s="7">
         <v>192903.0</v>
@@ -3465,10 +3477,10 @@
         <v>77501.0</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J79" s="12" t="s">
-        <v>132</v>
+        <v>49</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="80" ht="22.5" hidden="1" customHeight="1">
@@ -3476,16 +3488,16 @@
         <v>46237.0</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D80" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F80" s="7">
         <v>152062.0</v>
@@ -3497,10 +3509,10 @@
         <v>124423.0</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J80" s="12" t="s">
-        <v>132</v>
+        <v>49</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="81" ht="22.5" hidden="1" customHeight="1">
@@ -3508,16 +3520,16 @@
         <v>46237.0</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>134</v>
+        <v>54</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="D81" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F81" s="7">
         <v>153692.0</v>
@@ -3529,10 +3541,10 @@
         <v>63920.0</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J81" s="12" t="s">
-        <v>136</v>
+        <v>72</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="82" ht="22.5" hidden="1" customHeight="1">
@@ -3540,16 +3552,16 @@
         <v>46237.0</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>137</v>
+        <v>26</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>136</v>
       </c>
       <c r="D82" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F82" s="7">
         <v>45564.0</v>
@@ -3561,25 +3573,25 @@
         <v>40560.0</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J82" s="12"/>
+        <v>19</v>
+      </c>
+      <c r="J82" s="9"/>
     </row>
     <row r="83" ht="22.5" hidden="1" customHeight="1">
       <c r="A83" s="19">
         <v>46237.0</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="D83" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F83" s="7">
         <v>93517.0</v>
@@ -3591,27 +3603,27 @@
         <v>48804.0</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J83" s="12" t="s">
-        <v>139</v>
+        <v>35</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="84" ht="22.5" hidden="1" customHeight="1">
-      <c r="A84" s="8">
+      <c r="A84" s="4">
         <v>46238.0</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D84" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F84" s="7">
         <v>43200.0</v>
@@ -3623,25 +3635,25 @@
         <v>40890.0</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J84" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J84" s="9"/>
     </row>
     <row r="85" ht="22.5" hidden="1" customHeight="1">
-      <c r="A85" s="8">
+      <c r="A85" s="4">
         <v>46238.0</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D85" s="7">
         <v>152384.0</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F85" s="7">
         <v>25350.0</v>
@@ -3653,25 +3665,25 @@
         <v>30750.0</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J85" s="12"/>
+        <v>35</v>
+      </c>
+      <c r="J85" s="9"/>
     </row>
     <row r="86" ht="22.5" hidden="1" customHeight="1">
-      <c r="A86" s="8">
+      <c r="A86" s="4">
         <v>46238.0</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D86" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F86" s="7">
         <v>5040.0</v>
@@ -3683,25 +3695,25 @@
         <v>4680.0</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J86" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J86" s="9"/>
     </row>
     <row r="87" ht="22.5" hidden="1" customHeight="1">
-      <c r="A87" s="8">
+      <c r="A87" s="4">
         <v>46238.0</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D87" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F87" s="7">
         <v>124423.0</v>
@@ -3713,27 +3725,27 @@
         <v>69217.0</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J87" s="12" t="s">
-        <v>142</v>
+        <v>35</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="88" ht="22.5" hidden="1" customHeight="1">
-      <c r="A88" s="8">
+      <c r="A88" s="4">
         <v>46239.0</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D88" s="7">
         <v>152384.0</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F88" s="7">
         <v>30750.0</v>
@@ -3745,25 +3757,25 @@
         <v>36300.0</v>
       </c>
       <c r="I88" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J88" s="9"/>
+    </row>
+    <row r="89" ht="22.5" hidden="1" customHeight="1">
+      <c r="A89" s="4">
+        <v>46239.0</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J88" s="12"/>
-    </row>
-    <row r="89" ht="22.5" hidden="1" customHeight="1">
-      <c r="A89" s="8">
-        <v>46239.0</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>23</v>
+      <c r="C89" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D89" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F89" s="7">
         <v>58320.0</v>
@@ -3775,9 +3787,9 @@
         <v>12480.0</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J89" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J89" s="9" t="s">
         <v>143</v>
       </c>
     </row>
@@ -3786,16 +3798,16 @@
         <v>46240.0</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D90" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F90" s="7">
         <v>254880.0</v>
@@ -3807,9 +3819,9 @@
         <v>27180.0</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J90" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J90" s="9" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3818,16 +3830,16 @@
         <v>46240.0</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C91" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="11" t="s">
         <v>145</v>
       </c>
       <c r="D91" s="7">
         <v>112379.0</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F91" s="7">
         <v>13800.0</v>
@@ -3839,25 +3851,25 @@
         <v>12132.0</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J91" s="12"/>
+        <v>35</v>
+      </c>
+      <c r="J91" s="9"/>
     </row>
     <row r="92" ht="22.5" hidden="1" customHeight="1">
       <c r="A92" s="19">
         <v>46240.0</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>127</v>
+        <v>122</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>123</v>
       </c>
       <c r="D92" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F92" s="7">
         <v>4575.0</v>
@@ -3869,9 +3881,9 @@
         <v>4213.0</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J92" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J92" s="9" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3880,16 +3892,16 @@
         <v>46244.0</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D93" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F93" s="7">
         <v>222000.0</v>
@@ -3901,9 +3913,9 @@
         <v>312480.0</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J93" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J93" s="9" t="s">
         <v>147</v>
       </c>
     </row>
@@ -3912,16 +3924,16 @@
         <v>46244.0</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D94" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F94" s="7">
         <v>300060.0</v>
@@ -3933,9 +3945,9 @@
         <v>260696.0</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J94" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J94" s="9" t="s">
         <v>147</v>
       </c>
     </row>
@@ -3944,16 +3956,16 @@
         <v>46244.0</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D95" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F95" s="7">
         <v>36240.0</v>
@@ -3965,9 +3977,9 @@
         <v>39840.0</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J95" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J95" s="9" t="s">
         <v>147</v>
       </c>
     </row>
@@ -3976,16 +3988,16 @@
         <v>46244.0</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D96" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F96" s="7">
         <v>21690.0</v>
@@ -3997,25 +4009,25 @@
         <v>26280.0</v>
       </c>
       <c r="I96" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J96" s="9"/>
+    </row>
+    <row r="97" ht="22.5" hidden="1" customHeight="1">
+      <c r="A97" s="4">
+        <v>46245.0</v>
+      </c>
+      <c r="B97" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J96" s="12"/>
-    </row>
-    <row r="97" ht="22.5" hidden="1" customHeight="1">
-      <c r="A97" s="8">
-        <v>46245.0</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>23</v>
+      <c r="C97" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D97" s="7">
         <v>112271.0</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F97" s="7">
         <v>20100.0</v>
@@ -4027,25 +4039,25 @@
         <v>10800.0</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J97" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J97" s="9"/>
     </row>
     <row r="98" ht="22.5" hidden="1" customHeight="1">
-      <c r="A98" s="8">
+      <c r="A98" s="4">
         <v>46245.0</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D98" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F98" s="7">
         <v>39840.0</v>
@@ -4057,27 +4069,27 @@
         <v>23520.0</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J98" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J98" s="9" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="99" ht="22.5" hidden="1" customHeight="1">
-      <c r="A99" s="8">
+      <c r="A99" s="4">
         <v>46245.0</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D99" s="7">
         <v>152384.0</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F99" s="7">
         <v>18600.0</v>
@@ -4089,27 +4101,27 @@
         <v>12900.0</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J99" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J99" s="9" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="100" ht="22.5" hidden="1" customHeight="1">
-      <c r="A100" s="8">
+      <c r="A100" s="4">
         <v>46245.0</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D100" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F100" s="7">
         <v>225620.0</v>
@@ -4121,27 +4133,27 @@
         <v>269040.0</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J100" s="9" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="101" ht="22.5" hidden="1" customHeight="1">
-      <c r="A101" s="8">
+      <c r="A101" s="4">
         <v>46246.0</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C101" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C101" s="11" t="s">
         <v>151</v>
       </c>
       <c r="D101" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F101" s="7">
         <v>423758.0</v>
@@ -4153,27 +4165,27 @@
         <v>638764.0</v>
       </c>
       <c r="I101" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" s="9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" ht="22.5" hidden="1" customHeight="1">
+      <c r="A102" s="4">
+        <v>46246.0</v>
+      </c>
+      <c r="B102" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J101" s="12" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="102" ht="22.5" hidden="1" customHeight="1">
-      <c r="A102" s="8">
-        <v>46246.0</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>77</v>
+      <c r="C102" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D102" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F102" s="7">
         <v>800120.0</v>
@@ -4185,27 +4197,27 @@
         <v>655250.0</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J102" s="9" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="103" ht="22.5" hidden="1" customHeight="1">
-      <c r="A103" s="8">
+      <c r="A103" s="4">
         <v>46246.0</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D103" s="7">
         <v>112271.0</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F103" s="7">
         <v>10815.0</v>
@@ -4217,27 +4229,27 @@
         <v>1935.0</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J103" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J103" s="9" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="104" ht="22.5" hidden="1" customHeight="1">
-      <c r="A104" s="8">
+      <c r="A104" s="4">
         <v>46246.0</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D104" s="7">
         <v>152384.0</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F104" s="7">
         <v>12900.0</v>
@@ -4249,18 +4261,18 @@
         <v>19800.0</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J104" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J104" s="9" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="105" ht="22.5" hidden="1" customHeight="1">
-      <c r="A105" s="8">
+      <c r="A105" s="4">
         <v>46247.0</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>155</v>
@@ -4269,7 +4281,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F105" s="7">
         <v>193026.0</v>
@@ -4281,27 +4293,27 @@
         <v>63824.0</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J105" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J105" s="9" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="106" ht="22.5" hidden="1" customHeight="1">
-      <c r="A106" s="8">
+      <c r="A106" s="4">
         <v>46247.0</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D106" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F106" s="7">
         <v>245520.0</v>
@@ -4313,25 +4325,25 @@
         <v>230580.0</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J106" s="12"/>
+        <v>35</v>
+      </c>
+      <c r="J106" s="9"/>
     </row>
     <row r="107" ht="22.5" hidden="1" customHeight="1">
-      <c r="A107" s="8">
+      <c r="A107" s="4">
         <v>46247.0</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D107" s="7">
         <v>2110217.0</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F107" s="7">
         <v>21120.0</v>
@@ -4343,25 +4355,25 @@
         <v>17280.0</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J107" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J107" s="9"/>
     </row>
     <row r="108" ht="22.5" hidden="1" customHeight="1">
-      <c r="A108" s="8">
+      <c r="A108" s="4">
         <v>46247.0</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D108" s="7">
         <v>112271.0</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F108" s="7">
         <v>16500.0</v>
@@ -4373,25 +4385,25 @@
         <v>12600.0</v>
       </c>
       <c r="I108" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J108" s="12"/>
+        <v>35</v>
+      </c>
+      <c r="J108" s="9"/>
     </row>
     <row r="109" ht="22.5" hidden="1" customHeight="1">
-      <c r="A109" s="8">
+      <c r="A109" s="4">
         <v>46248.0</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D109" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F109" s="7">
         <v>793976.0</v>
@@ -4403,27 +4415,27 @@
         <v>584490.0</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J109" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J109" s="9" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="110" ht="22.5" hidden="1" customHeight="1">
-      <c r="A110" s="8">
+      <c r="A110" s="4">
         <v>46248.0</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D110" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F110" s="7">
         <v>289920.0</v>
@@ -4435,25 +4447,25 @@
         <v>247440.0</v>
       </c>
       <c r="I110" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J110" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J110" s="9"/>
     </row>
     <row r="111" ht="22.5" hidden="1" customHeight="1">
-      <c r="A111" s="8">
+      <c r="A111" s="4">
         <v>46248.0</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D111" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F111" s="7">
         <v>230580.0</v>
@@ -4465,27 +4477,27 @@
         <v>298620.0</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J111" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J111" s="9" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="112" ht="22.5" hidden="1" customHeight="1">
-      <c r="A112" s="8">
+      <c r="A112" s="4">
         <v>46248.0</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="D112" s="7">
         <v>152384.0</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F112" s="7">
         <v>13200.0</v>
@@ -4497,27 +4509,27 @@
         <v>7200.0</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J112" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J112" s="9" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="113" ht="22.5" hidden="1" customHeight="1">
-      <c r="A113" s="8">
+      <c r="A113" s="4">
         <v>46248.0</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C113" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C113" s="11" t="s">
         <v>160</v>
       </c>
       <c r="D113" s="7">
         <v>152384.0</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F113" s="7">
         <v>9900.0</v>
@@ -4529,27 +4541,27 @@
         <v>8100.0</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J113" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J113" s="9" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="114" ht="22.5" hidden="1" customHeight="1">
-      <c r="A114" s="8">
+      <c r="A114" s="4">
         <v>46252.0</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C114" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D114" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F114" s="7">
         <v>184290.0</v>
@@ -4561,27 +4573,27 @@
         <v>68640.0</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J114" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J114" s="9" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="115" ht="22.5" hidden="1" customHeight="1">
-      <c r="A115" s="8">
+      <c r="A115" s="4">
         <v>46252.0</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C115" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C115" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D115" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F115" s="7">
         <v>26880.0</v>
@@ -4593,27 +4605,27 @@
         <v>26880.0</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J115" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J115" s="9" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="116" ht="22.5" hidden="1" customHeight="1">
-      <c r="A116" s="8">
+      <c r="A116" s="4">
         <v>46252.0</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D116" s="7">
         <v>152384.0</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F116" s="7">
         <v>21585.0</v>
@@ -4625,27 +4637,27 @@
         <v>12900.0</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J116" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J116" s="9" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="117" ht="22.5" hidden="1" customHeight="1">
-      <c r="A117" s="8">
+      <c r="A117" s="4">
         <v>46253.0</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C117" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C117" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D117" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F117" s="7">
         <v>179640.0</v>
@@ -4656,26 +4668,26 @@
       <c r="H117" s="7">
         <v>39060.0</v>
       </c>
-      <c r="I117" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J117" s="12"/>
+      <c r="I117" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J117" s="9"/>
     </row>
     <row r="118" ht="22.5" hidden="1" customHeight="1">
-      <c r="A118" s="8">
+      <c r="A118" s="4">
         <v>46253.0</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C118" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C118" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D118" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F118" s="7">
         <v>26880.0</v>
@@ -4686,26 +4698,26 @@
       <c r="H118" s="7">
         <v>25680.0</v>
       </c>
-      <c r="I118" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J118" s="12"/>
+      <c r="I118" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J118" s="9"/>
     </row>
     <row r="119" ht="22.5" hidden="1" customHeight="1">
-      <c r="A119" s="8">
+      <c r="A119" s="4">
         <v>46253.0</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C119" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C119" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D119" s="7">
         <v>152384.0</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F119" s="7">
         <v>14230.0</v>
@@ -4716,26 +4728,26 @@
       <c r="H119" s="7">
         <v>13200.0</v>
       </c>
-      <c r="I119" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J119" s="12"/>
+      <c r="I119" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J119" s="9"/>
     </row>
     <row r="120" ht="22.5" hidden="1" customHeight="1">
-      <c r="A120" s="8">
+      <c r="A120" s="4">
         <v>46253.0</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>107</v>
+        <v>31</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>105</v>
       </c>
       <c r="D120" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F120" s="7">
         <v>26677.0</v>
@@ -4746,28 +4758,28 @@
       <c r="H120" s="7">
         <v>11790.0</v>
       </c>
-      <c r="I120" s="9" t="s">
+      <c r="I120" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J120" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="121" ht="22.5" hidden="1" customHeight="1">
+      <c r="A121" s="4">
+        <v>46253.0</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J120" s="12" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="121" ht="22.5" hidden="1" customHeight="1">
-      <c r="A121" s="8">
-        <v>46253.0</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>77</v>
+      <c r="C121" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D121" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F121" s="7">
         <v>22500.0</v>
@@ -4778,28 +4790,28 @@
       <c r="H121" s="7">
         <v>18300.0</v>
       </c>
-      <c r="I121" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J121" s="12" t="s">
+      <c r="I121" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J121" s="9" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="122" ht="22.5" hidden="1" customHeight="1">
-      <c r="A122" s="8">
+      <c r="A122" s="4">
         <v>46253.0</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D122" s="7">
         <v>112271.0</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F122" s="7">
         <v>16500.0</v>
@@ -4810,28 +4822,28 @@
       <c r="H122" s="7">
         <v>8100.0</v>
       </c>
-      <c r="I122" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="J122" s="12" t="s">
+      <c r="I122" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J122" s="9" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="123" ht="22.5" hidden="1" customHeight="1">
-      <c r="A123" s="8">
+      <c r="A123" s="4">
         <v>46254.0</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C123" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C123" s="11" t="s">
         <v>151</v>
       </c>
       <c r="D123" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F123" s="7">
         <v>21915.0</v>
@@ -4843,27 +4855,27 @@
         <v>14235.0</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J123" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J123" s="9" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="124" ht="22.5" hidden="1" customHeight="1">
-      <c r="A124" s="8">
+      <c r="A124" s="4">
         <v>46254.0</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D124" s="7">
         <v>2112207.0</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F124" s="7">
         <v>10125.0</v>
@@ -4875,25 +4887,25 @@
         <v>8565.0</v>
       </c>
       <c r="I124" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J124" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J124" s="9"/>
     </row>
     <row r="125" ht="22.5" hidden="1" customHeight="1">
-      <c r="A125" s="8">
+      <c r="A125" s="4">
         <v>46254.0</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C125" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C125" s="11" t="s">
         <v>168</v>
       </c>
       <c r="D125" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F125" s="7">
         <v>6380.0</v>
@@ -4905,27 +4917,27 @@
         <v>1980.0</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J125" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J125" s="9" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="126" ht="22.5" customHeight="1">
-      <c r="A126" s="8">
+      <c r="A126" s="4">
         <v>46255.0</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="D126" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F126" s="7">
         <v>28200.0</v>
@@ -4937,25 +4949,25 @@
         <v>51080.0</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J126" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J126" s="9"/>
     </row>
     <row r="127" ht="22.5" customHeight="1">
-      <c r="A127" s="8">
+      <c r="A127" s="4">
         <v>46255.0</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C127" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" s="11" t="s">
         <v>170</v>
       </c>
       <c r="D127" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F127" s="7">
         <v>23760.0</v>
@@ -4967,27 +4979,27 @@
         <v>17760.0</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J127" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J127" s="9" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="128" ht="22.5" customHeight="1">
-      <c r="A128" s="8">
+      <c r="A128" s="4">
         <v>46255.0</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C128" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C128" s="11" t="s">
         <v>172</v>
       </c>
       <c r="D128" s="7">
         <v>112268.0</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F128" s="7">
         <v>3300.0</v>
@@ -4999,27 +5011,27 @@
         <v>5400.0</v>
       </c>
       <c r="I128" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J128" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J128" s="9" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="129" ht="22.5" customHeight="1">
-      <c r="A129" s="8">
+      <c r="A129" s="4">
         <v>46255.0</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="C129" s="11" t="s">
         <v>175</v>
       </c>
       <c r="D129" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F129" s="7">
         <v>2130.0</v>
@@ -5031,9 +5043,9 @@
         <v>1230.0</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J129" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J129" s="9" t="s">
         <v>176</v>
       </c>
     </row>
@@ -5042,16 +5054,16 @@
         <v>46258.0</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C130" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C130" s="11" t="s">
         <v>177</v>
       </c>
       <c r="D130" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F130" s="7">
         <v>341120.0</v>
@@ -5063,9 +5075,9 @@
         <v>545850.0</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J130" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J130" s="9" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5074,16 +5086,16 @@
         <v>46258.0</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D131" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F131" s="7">
         <v>11520.0</v>
@@ -5095,25 +5107,25 @@
         <v>11880.0</v>
       </c>
       <c r="I131" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J131" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="J131" s="9"/>
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="19">
         <v>46258.0</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C132" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C132" s="11" t="s">
         <v>177</v>
       </c>
       <c r="D132" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F132" s="7">
         <v>35520.0</v>
@@ -5125,27 +5137,27 @@
         <v>18000.0</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J132" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J132" s="9" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="133" ht="22.5" customHeight="1">
-      <c r="A133" s="8">
+      <c r="A133" s="4">
         <v>46259.0</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D133" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F133" s="7">
         <v>64620.0</v>
@@ -5157,25 +5169,25 @@
         <v>47685.0</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J133" s="12"/>
+        <v>72</v>
+      </c>
+      <c r="J133" s="9"/>
     </row>
     <row r="134" ht="22.5" customHeight="1">
-      <c r="A134" s="8">
+      <c r="A134" s="4">
         <v>46259.0</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C134" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C134" s="11" t="s">
         <v>177</v>
       </c>
       <c r="D134" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F134" s="7">
         <v>18000.0</v>
@@ -5187,27 +5199,27 @@
         <v>11510.0</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J134" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J134" s="9" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="135" ht="22.5" customHeight="1">
-      <c r="A135" s="8">
+      <c r="A135" s="4">
         <v>46259.0</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="D135" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F135" s="7">
         <v>48540.0</v>
@@ -5219,27 +5231,27 @@
         <v>105048.0</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J135" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J135" s="9" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="136" ht="22.5" customHeight="1">
-      <c r="A136" s="8">
+      <c r="A136" s="4">
         <v>46260.0</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C136" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" s="11" t="s">
         <v>177</v>
       </c>
       <c r="D136" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F136" s="7">
         <v>194198.0</v>
@@ -5251,27 +5263,27 @@
         <v>140840.0</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J136" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J136" s="9" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="137" ht="22.5" customHeight="1">
-      <c r="A137" s="8">
+      <c r="A137" s="4">
         <v>46260.0</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C137" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C137" s="11" t="s">
         <v>177</v>
       </c>
       <c r="D137" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F137" s="7">
         <v>11510.0</v>
@@ -5283,27 +5295,27 @@
         <v>10398.0</v>
       </c>
       <c r="I137" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J137" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J137" s="9" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="138" ht="22.5" customHeight="1">
-      <c r="A138" s="8">
+      <c r="A138" s="4">
         <v>46260.0</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C138" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="D138" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F138" s="7">
         <v>47685.0</v>
@@ -5315,27 +5327,27 @@
         <v>107298.0</v>
       </c>
       <c r="I138" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J138" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J138" s="9" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="139" ht="22.5" customHeight="1">
-      <c r="A139" s="8">
+      <c r="A139" s="4">
         <v>46260.0</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C139" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C139" s="11" t="s">
         <v>177</v>
       </c>
       <c r="D139" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F139" s="7">
         <v>30600.0</v>
@@ -5347,23 +5359,129 @@
         <v>33440.0</v>
       </c>
       <c r="I139" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J139" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J139" s="9" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="140">
-      <c r="I140" s="23"/>
-    </row>
-    <row r="141">
-      <c r="I141" s="23"/>
-    </row>
-    <row r="142">
-      <c r="I142" s="23"/>
-    </row>
-    <row r="143">
-      <c r="I143" s="23"/>
+    <row r="140" ht="22.5" customHeight="1">
+      <c r="A140" s="19">
+        <v>46261.0</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C140" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D140" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F140" s="7">
+        <v>38640.0</v>
+      </c>
+      <c r="G140" s="7">
+        <v>8420.0</v>
+      </c>
+      <c r="H140" s="7">
+        <v>22800.0</v>
+      </c>
+      <c r="I140" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J140" s="9"/>
+    </row>
+    <row r="141" ht="22.5" customHeight="1">
+      <c r="A141" s="19">
+        <v>46261.0</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C141" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D141" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F141" s="7">
+        <v>365280.0</v>
+      </c>
+      <c r="G141" s="7">
+        <v>93252.0</v>
+      </c>
+      <c r="H141" s="7">
+        <v>283680.0</v>
+      </c>
+      <c r="I141" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J141" s="9"/>
+    </row>
+    <row r="142" ht="22.5" customHeight="1">
+      <c r="A142" s="19">
+        <v>46261.0</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D142" s="7">
+        <v>2110302.0</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F142" s="7">
+        <v>192000.0</v>
+      </c>
+      <c r="G142" s="7">
+        <v>46072.0</v>
+      </c>
+      <c r="H142" s="7">
+        <v>91680.0</v>
+      </c>
+      <c r="I142" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J142" s="9"/>
+    </row>
+    <row r="143" ht="22.5" customHeight="1">
+      <c r="A143" s="19">
+        <v>46261.0</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C143" s="20"/>
+      <c r="D143" s="7">
+        <v>2110317.0</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F143" s="7">
+        <v>10260.0</v>
+      </c>
+      <c r="G143" s="7">
+        <v>2543.0</v>
+      </c>
+      <c r="H143" s="7">
+        <v>7860.0</v>
+      </c>
+      <c r="I143" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J143" s="9"/>
     </row>
     <row r="144">
       <c r="I144" s="23"/>
@@ -7959,13 +8077,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I139">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I143">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I140:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I144:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A139">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A143">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -8028,18 +8146,18 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="8">
+      <c r="A2" s="4">
         <v>46224.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="10"/>
+        <v>10</v>
+      </c>
+      <c r="C2" s="6"/>
       <c r="D2" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F2" s="7">
         <v>333.0</v>
@@ -8050,26 +8168,26 @@
       <c r="H2" s="7">
         <v>3712.0</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>19</v>
+      <c r="I2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="8">
+      <c r="A3" s="4">
         <v>46224.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="C3" s="6"/>
       <c r="D3" s="7">
         <v>2114158.0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F3" s="7">
         <v>60.0</v>
@@ -8080,26 +8198,26 @@
       <c r="H3" s="7">
         <v>60.0</v>
       </c>
-      <c r="I3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>27</v>
+      <c r="I3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="8">
+      <c r="A4" s="4">
         <v>46225.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="7">
         <v>10501.0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F4" s="7">
         <v>415093.0</v>
@@ -8110,26 +8228,26 @@
       <c r="H4" s="7">
         <v>543038.0</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>34</v>
+      <c r="I4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="8">
+      <c r="A5" s="4">
         <v>46225.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="7">
         <v>112379.0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F5" s="7">
         <v>3000.0</v>
@@ -8140,26 +8258,26 @@
       <c r="H5" s="7">
         <v>3000.0</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>37</v>
+      <c r="I5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="8">
+      <c r="A6" s="4">
         <v>46225.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="7">
         <v>112268.0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F6" s="7">
         <v>3000.0</v>
@@ -8170,26 +8288,26 @@
       <c r="H6" s="7">
         <v>3300.0</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>41</v>
+      <c r="I6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="8">
+      <c r="A7" s="4">
         <v>46225.0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="7">
         <v>132357.0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F7" s="7">
         <v>1560.0</v>
@@ -8200,26 +8318,26 @@
       <c r="H7" s="7">
         <v>4560.0</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>48</v>
+      <c r="I7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="8">
+      <c r="A8" s="4">
         <v>46225.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F8" s="7">
         <v>720.0</v>
@@ -8230,26 +8348,26 @@
       <c r="H8" s="7">
         <v>5940.0</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>52</v>
+      <c r="I8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="8">
+      <c r="A9" s="4">
         <v>46225.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F9" s="7">
         <v>3712.0</v>
@@ -8260,26 +8378,26 @@
       <c r="H9" s="7">
         <v>213.0</v>
       </c>
-      <c r="I9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>53</v>
+      <c r="I9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="8">
+      <c r="A10" s="4">
         <v>46226.0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="7">
         <v>73001.0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F10" s="7">
         <v>73787.0</v>
@@ -8290,26 +8408,26 @@
       <c r="H10" s="7">
         <v>109487.0</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>57</v>
+      <c r="I10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="8">
+      <c r="A11" s="4">
         <v>46226.0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="7">
         <v>112268.0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F11" s="7">
         <v>3300.0</v>
@@ -8320,24 +8438,24 @@
       <c r="H11" s="7">
         <v>3300.0</v>
       </c>
-      <c r="I11" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" s="12"/>
+      <c r="I11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="8">
+      <c r="A12" s="4">
         <v>46226.0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="7">
         <v>112379.0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F12" s="7">
         <v>4200.0</v>
@@ -8348,24 +8466,24 @@
       <c r="H12" s="7">
         <v>3900.0</v>
       </c>
-      <c r="I12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="12"/>
+      <c r="I12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="9"/>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="8">
+      <c r="A13" s="4">
         <v>46226.0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F13" s="7">
         <v>379471.0</v>
@@ -8376,26 +8494,26 @@
       <c r="H13" s="7">
         <v>357186.0</v>
       </c>
-      <c r="I13" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>57</v>
+      <c r="I13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="8">
+      <c r="A14" s="4">
         <v>46227.0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="7">
         <v>72001.0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F14" s="7">
         <v>21905.0</v>
@@ -8406,19 +8524,19 @@
       <c r="H14" s="7">
         <v>38000.0</v>
       </c>
-      <c r="I14" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>57</v>
+      <c r="I14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="8">
+      <c r="A15" s="4">
         <v>46227.0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="7">
@@ -8436,26 +8554,26 @@
       <c r="H15" s="7">
         <v>40320.0</v>
       </c>
-      <c r="I15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="12" t="s">
+      <c r="I15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="8">
+      <c r="A16" s="4">
         <v>46227.0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="7">
         <v>112379.0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F16" s="7">
         <v>3900.0</v>
@@ -8466,24 +8584,24 @@
       <c r="H16" s="7">
         <v>1500.0</v>
       </c>
-      <c r="I16" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="12"/>
+      <c r="I16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="9"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="8">
+      <c r="A17" s="4">
         <v>46227.0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F17" s="7">
         <v>720.0</v>
@@ -8494,24 +8612,24 @@
       <c r="H17" s="7">
         <v>2580.0</v>
       </c>
-      <c r="I17" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="12"/>
+      <c r="I17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="8">
+      <c r="A18" s="4">
         <v>46227.0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="7">
         <v>112268.0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F18" s="7">
         <v>3300.0</v>
@@ -8522,26 +8640,26 @@
       <c r="H18" s="7">
         <v>600.0</v>
       </c>
-      <c r="I18" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="12" t="s">
+      <c r="I18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="8">
+      <c r="A19" s="4">
         <v>46230.0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="7">
         <v>2410401.0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" s="7">
         <v>136538.0</v>
@@ -8552,26 +8670,26 @@
       <c r="H19" s="7">
         <v>213000.0</v>
       </c>
-      <c r="I19" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>70</v>
+      <c r="I19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="8">
+      <c r="A20" s="4">
         <v>46231.0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F20" s="7">
         <v>591750.0</v>
@@ -8582,26 +8700,26 @@
       <c r="H20" s="7">
         <v>577207.0</v>
       </c>
-      <c r="I20" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>70</v>
+      <c r="I20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="8">
+      <c r="A21" s="4">
         <v>46231.0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="7">
         <v>10601.0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F21" s="7">
         <v>1230.0</v>
@@ -8612,26 +8730,26 @@
       <c r="H21" s="7">
         <v>1958.0</v>
       </c>
-      <c r="I21" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>74</v>
+      <c r="I21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="8">
+      <c r="A22" s="4">
         <v>46231.0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F22" s="7">
         <v>4320.0</v>
@@ -8642,24 +8760,24 @@
       <c r="H22" s="7">
         <v>3420.0</v>
       </c>
-      <c r="I22" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="12"/>
+      <c r="I22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="9"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="8">
+      <c r="A23" s="4">
         <v>46231.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="7">
         <v>114357.0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F23" s="7">
         <v>240.0</v>
@@ -8670,24 +8788,24 @@
       <c r="H23" s="7">
         <v>240.0</v>
       </c>
-      <c r="I23" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="12"/>
+      <c r="I23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="9"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="8">
+      <c r="A24" s="4">
         <v>46232.0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="7">
         <v>10501.0</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F24" s="7">
         <v>19663.0</v>
@@ -8698,24 +8816,24 @@
       <c r="H24" s="7">
         <v>29632.0</v>
       </c>
-      <c r="I24" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="12"/>
+      <c r="I24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" s="9"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="8">
+      <c r="A25" s="4">
         <v>46232.0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="7">
         <v>112268.0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F25" s="7">
         <v>5700.0</v>
@@ -8726,24 +8844,24 @@
       <c r="H25" s="7">
         <v>5100.0</v>
       </c>
-      <c r="I25" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" s="12"/>
+      <c r="I25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25" s="9"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="8">
+      <c r="A26" s="4">
         <v>46232.0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F26" s="7">
         <v>720.0</v>
@@ -8754,24 +8872,24 @@
       <c r="H26" s="7">
         <v>720.0</v>
       </c>
-      <c r="I26" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="12"/>
+      <c r="I26" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="9"/>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="8">
+      <c r="A27" s="4">
         <v>46232.0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="7">
         <v>2114357.0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F27" s="7">
         <v>432.0</v>
@@ -8782,24 +8900,24 @@
       <c r="H27" s="7">
         <v>432.0</v>
       </c>
-      <c r="I27" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="12"/>
+      <c r="I27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="9"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="8">
+      <c r="A28" s="4">
         <v>46232.0</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="7">
         <v>10501.0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F28" s="7">
         <v>219540.0</v>
@@ -8810,24 +8928,24 @@
       <c r="H28" s="7">
         <v>16698.0</v>
       </c>
-      <c r="I28" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="12"/>
+      <c r="I28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28" s="9"/>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="8">
+      <c r="A29" s="4">
         <v>46233.0</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="7">
         <v>112268.0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F29" s="7">
         <v>5100.0</v>
@@ -8838,24 +8956,24 @@
       <c r="H29" s="7">
         <v>4800.0</v>
       </c>
-      <c r="I29" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J29" s="12"/>
+      <c r="I29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="9"/>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="8">
+      <c r="A30" s="4">
         <v>46233.0</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="7">
         <v>114357.0</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F30" s="7">
         <v>240.0</v>
@@ -8866,24 +8984,24 @@
       <c r="H30" s="7">
         <v>1560.0</v>
       </c>
-      <c r="I30" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J30" s="12"/>
+      <c r="I30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="8">
+      <c r="A31" s="4">
         <v>46233.0</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="7">
         <v>10601.0</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F31" s="7">
         <v>7717.0</v>
@@ -8894,26 +9012,26 @@
       <c r="H31" s="7">
         <v>12867.0</v>
       </c>
-      <c r="I31" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>86</v>
+      <c r="I31" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="8">
+      <c r="A32" s="4">
         <v>46234.0</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="7">
         <v>79110.0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F32" s="7">
         <v>48000.0</v>
@@ -8924,26 +9042,26 @@
       <c r="H32" s="7">
         <v>36300.0</v>
       </c>
-      <c r="I32" s="11" t="s">
-        <v>20</v>
+      <c r="I32" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="8">
+      <c r="A33" s="4">
         <v>46234.0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="7">
         <v>10501.0</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F33" s="7">
         <v>95574.0</v>
@@ -8954,26 +9072,26 @@
       <c r="H33" s="7">
         <v>142801.0</v>
       </c>
-      <c r="I33" s="11" t="s">
-        <v>18</v>
+      <c r="I33" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="8">
+      <c r="A34" s="4">
         <v>46234.0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="7">
         <v>73001.0</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F34" s="7">
         <v>73367.0</v>
@@ -8984,24 +9102,24 @@
       <c r="H34" s="7">
         <v>39150.0</v>
       </c>
-      <c r="I34" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="12"/>
+      <c r="I34" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J34" s="9"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="8">
+      <c r="A35" s="4">
         <v>46234.0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="7">
         <v>112357.0</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F35" s="7">
         <v>840.0</v>
@@ -9012,24 +9130,24 @@
       <c r="H35" s="7">
         <v>480.0</v>
       </c>
-      <c r="I35" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="12"/>
+      <c r="I35" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J35" s="9"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
       <c r="A36" s="19">
         <v>46237.0</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="7">
         <v>10601.0</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F36" s="7">
         <v>17934.0</v>
@@ -9040,11 +9158,11 @@
       <c r="H36" s="7">
         <v>21714.0</v>
       </c>
-      <c r="I36" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>96</v>
+      <c r="I36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
@@ -9052,14 +9170,14 @@
         <v>46237.0</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F37" s="7">
         <v>194520.0</v>
@@ -9070,24 +9188,24 @@
       <c r="H37" s="7">
         <v>122840.0</v>
       </c>
-      <c r="I37" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="12"/>
+      <c r="I37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="9"/>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
       <c r="A38" s="19">
         <v>46237.0</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="7">
         <v>114379.0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F38" s="7">
         <v>52200.0</v>
@@ -9098,24 +9216,24 @@
       <c r="H38" s="7">
         <v>7500.0</v>
       </c>
-      <c r="I38" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J38" s="12"/>
+      <c r="I38" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J38" s="9"/>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
       <c r="A39" s="19">
         <v>46237.0</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C39" s="14"/>
       <c r="D39" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F39" s="7">
         <v>6450.0</v>
@@ -9126,24 +9244,24 @@
       <c r="H39" s="7">
         <v>6480.0</v>
       </c>
-      <c r="I39" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="12"/>
+      <c r="I39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" s="9"/>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
       <c r="A40" s="19">
         <v>46237.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F40" s="7">
         <v>1398.0</v>
@@ -9154,24 +9272,24 @@
       <c r="H40" s="7">
         <v>438.0</v>
       </c>
-      <c r="I40" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="12"/>
+      <c r="I40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" s="9"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="8">
+      <c r="A41" s="4">
         <v>46238.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C41" s="14"/>
       <c r="D41" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F41" s="7">
         <v>2460.0</v>
@@ -9182,24 +9300,24 @@
       <c r="H41" s="7">
         <v>3240.0</v>
       </c>
-      <c r="I41" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J41" s="12"/>
+      <c r="I41" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="9"/>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="8">
+      <c r="A42" s="4">
         <v>46238.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="7">
         <v>112268.0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F42" s="7">
         <v>3600.0</v>
@@ -9210,24 +9328,24 @@
       <c r="H42" s="7">
         <v>3900.0</v>
       </c>
-      <c r="I42" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" s="12"/>
+      <c r="I42" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" s="9"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="8">
+      <c r="A43" s="4">
         <v>46238.0</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="7">
         <v>114379.0</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F43" s="7">
         <v>7500.0</v>
@@ -9238,24 +9356,24 @@
       <c r="H43" s="7">
         <v>8400.0</v>
       </c>
-      <c r="I43" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J43" s="12"/>
+      <c r="I43" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="9"/>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="8">
+      <c r="A44" s="4">
         <v>46238.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="7">
         <v>114357.0</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F44" s="7">
         <v>240.0</v>
@@ -9266,24 +9384,24 @@
       <c r="H44" s="7">
         <v>360.0</v>
       </c>
-      <c r="I44" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J44" s="12"/>
+      <c r="I44" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="9"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="8">
+      <c r="A45" s="4">
         <v>46239.0</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="7">
         <v>10601.0</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F45" s="7">
         <v>1115.0</v>
@@ -9294,26 +9412,26 @@
       <c r="H45" s="7">
         <v>1590.0</v>
       </c>
-      <c r="I45" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="12" t="s">
-        <v>105</v>
+      <c r="I45" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="8">
+      <c r="A46" s="4">
         <v>46239.0</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F46" s="7">
         <v>114240.0</v>
@@ -9324,24 +9442,24 @@
       <c r="H46" s="7">
         <v>191130.0</v>
       </c>
-      <c r="I46" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="12"/>
+      <c r="I46" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" s="9"/>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="8">
+      <c r="A47" s="4">
         <v>46239.0</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="7">
         <v>2112207.0</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F47" s="7">
         <v>1800.0</v>
@@ -9352,24 +9470,24 @@
       <c r="H47" s="7">
         <v>1980.0</v>
       </c>
-      <c r="I47" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J47" s="12"/>
+      <c r="I47" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J47" s="9"/>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="8">
+      <c r="A48" s="4">
         <v>46239.0</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="7">
         <v>112268.0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F48" s="7">
         <v>3900.0</v>
@@ -9380,24 +9498,24 @@
       <c r="H48" s="7">
         <v>1200.0</v>
       </c>
-      <c r="I48" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J48" s="12"/>
+      <c r="I48" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J48" s="9"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="8">
+      <c r="A49" s="4">
         <v>46239.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="7">
         <v>112357.0</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F49" s="7">
         <v>600.0</v>
@@ -9408,24 +9526,24 @@
       <c r="H49" s="7">
         <v>600.0</v>
       </c>
-      <c r="I49" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J49" s="12"/>
+      <c r="I49" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J49" s="9"/>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="8">
+      <c r="A50" s="4">
         <v>46239.0</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="7">
         <v>114268.0</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F50" s="7">
         <v>2700.0</v>
@@ -9436,24 +9554,24 @@
       <c r="H50" s="7">
         <v>300.0</v>
       </c>
-      <c r="I50" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J50" s="12"/>
+      <c r="I50" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J50" s="9"/>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="8">
+      <c r="A51" s="4">
         <v>46239.0</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C51" s="14"/>
       <c r="D51" s="7">
         <v>10501.0</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F51" s="7">
         <v>68651.0</v>
@@ -9464,26 +9582,26 @@
       <c r="H51" s="7">
         <v>13421.0</v>
       </c>
-      <c r="I51" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>112</v>
+      <c r="I51" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="8">
+      <c r="A52" s="4">
         <v>46239.0</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C52" s="14"/>
       <c r="D52" s="7">
         <v>72003.0</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F52" s="7">
         <v>1391.0</v>
@@ -9494,24 +9612,24 @@
       <c r="H52" s="7">
         <v>2407.0</v>
       </c>
-      <c r="I52" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J52" s="12"/>
+      <c r="I52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J52" s="9"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="8">
+      <c r="A53" s="4">
         <v>46239.0</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C53" s="14"/>
       <c r="D53" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F53" s="7">
         <v>2974.0</v>
@@ -9522,11 +9640,11 @@
       <c r="H53" s="7">
         <v>3317.0</v>
       </c>
-      <c r="I53" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>116</v>
+      <c r="I53" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
@@ -9534,14 +9652,14 @@
         <v>46240.0</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C54" s="14"/>
       <c r="D54" s="7">
         <v>112379.0</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F54" s="7">
         <v>3600.0</v>
@@ -9552,24 +9670,24 @@
       <c r="H54" s="7">
         <v>6900.0</v>
       </c>
-      <c r="I54" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J54" s="12"/>
+      <c r="I54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" s="9"/>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
       <c r="A55" s="19">
         <v>46240.0</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="7">
         <v>73001.0</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F55" s="7">
         <v>2415.0</v>
@@ -9580,24 +9698,24 @@
       <c r="H55" s="7">
         <v>2415.0</v>
       </c>
-      <c r="I55" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J55" s="12"/>
+      <c r="I55" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="9"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
       <c r="A56" s="19">
         <v>46240.0</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C56" s="14"/>
       <c r="D56" s="7">
         <v>112357.0</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F56" s="7">
         <v>600.0</v>
@@ -9608,24 +9726,24 @@
       <c r="H56" s="7">
         <v>600.0</v>
       </c>
-      <c r="I56" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J56" s="12"/>
+      <c r="I56" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" s="9"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
       <c r="A57" s="19">
         <v>46240.0</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="7">
         <v>114379.0</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F57" s="7">
         <v>2400.0</v>
@@ -9636,24 +9754,24 @@
       <c r="H57" s="7">
         <v>300.0</v>
       </c>
-      <c r="I57" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J57" s="12"/>
+      <c r="I57" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="9"/>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
       <c r="A58" s="19">
         <v>46244.0</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="7">
         <v>112379.0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F58" s="7">
         <v>4800.0</v>
@@ -9664,24 +9782,24 @@
       <c r="H58" s="7">
         <v>5100.0</v>
       </c>
-      <c r="I58" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J58" s="12"/>
+      <c r="I58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="9"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="8">
+      <c r="A59" s="4">
         <v>46245.0</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C59" s="14"/>
       <c r="D59" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F59" s="7">
         <v>25574.0</v>
@@ -9692,24 +9810,24 @@
       <c r="H59" s="7">
         <v>42960.0</v>
       </c>
-      <c r="I59" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J59" s="12"/>
+      <c r="I59" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J59" s="9"/>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="8">
+      <c r="A60" s="4">
         <v>46246.0</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="7">
         <v>114379.0</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F60" s="7">
         <v>6900.0</v>
@@ -9720,24 +9838,24 @@
       <c r="H60" s="7">
         <v>5400.0</v>
       </c>
-      <c r="I60" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J60" s="12"/>
+      <c r="I60" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="9"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="8">
+      <c r="A61" s="4">
         <v>46247.0</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="7">
         <v>112379.0</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F61" s="7">
         <v>20100.0</v>
@@ -9748,24 +9866,24 @@
       <c r="H61" s="7">
         <v>20100.0</v>
       </c>
-      <c r="I61" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="12"/>
+      <c r="I61" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J61" s="9"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
-      <c r="A62" s="8">
+      <c r="A62" s="4">
         <v>46247.0</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="7">
         <v>112268.0</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F62" s="7">
         <v>8400.0</v>
@@ -9776,24 +9894,24 @@
       <c r="H62" s="7">
         <v>8400.0</v>
       </c>
-      <c r="I62" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="12"/>
+      <c r="I62" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J62" s="9"/>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
-      <c r="A63" s="8">
+      <c r="A63" s="4">
         <v>46247.0</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F63" s="7">
         <v>61250.0</v>
@@ -9804,24 +9922,24 @@
       <c r="H63" s="7">
         <v>76033.0</v>
       </c>
-      <c r="I63" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J63" s="12"/>
+      <c r="I63" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J63" s="9"/>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
-      <c r="A64" s="8">
+      <c r="A64" s="4">
         <v>46247.0</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="7">
         <v>13358.0</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F64" s="7">
         <v>73728.0</v>
@@ -9832,26 +9950,26 @@
       <c r="H64" s="7">
         <v>73440.0</v>
       </c>
-      <c r="I64" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J64" s="12" t="s">
-        <v>122</v>
+      <c r="I64" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="65" ht="19.5" hidden="1" customHeight="1">
-      <c r="A65" s="8">
+      <c r="A65" s="4">
         <v>46248.0</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F65" s="7">
         <v>285596.0</v>
@@ -9862,26 +9980,26 @@
       <c r="H65" s="7">
         <v>72480.0</v>
       </c>
-      <c r="I65" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J65" s="12" t="s">
-        <v>124</v>
+      <c r="I65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="66" ht="19.5" hidden="1" customHeight="1">
-      <c r="A66" s="8">
+      <c r="A66" s="4">
         <v>46248.0</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="7">
         <v>73001.0</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F66" s="7">
         <v>31772.0</v>
@@ -9892,26 +10010,26 @@
       <c r="H66" s="7">
         <v>28820.0</v>
       </c>
-      <c r="I66" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="12" t="s">
-        <v>125</v>
+      <c r="I66" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J66" s="9" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="67" ht="19.5" hidden="1" customHeight="1">
-      <c r="A67" s="8">
+      <c r="A67" s="4">
         <v>46254.0</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="7">
         <v>10601.0</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F67" s="7">
         <v>73085.0</v>
@@ -9922,26 +10040,26 @@
       <c r="H67" s="7">
         <v>78125.0</v>
       </c>
-      <c r="I67" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="12" t="s">
-        <v>128</v>
+      <c r="I67" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="68" ht="19.5" hidden="1" customHeight="1">
-      <c r="A68" s="8">
+      <c r="A68" s="4">
         <v>46254.0</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C68" s="14"/>
       <c r="D68" s="7">
         <v>112379.0</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F68" s="7">
         <v>18000.0</v>
@@ -9952,26 +10070,26 @@
       <c r="H68" s="7">
         <v>18000.0</v>
       </c>
-      <c r="I68" s="11" t="s">
-        <v>18</v>
+      <c r="I68" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="J68" s="21" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="69" ht="19.5" hidden="1" customHeight="1">
-      <c r="A69" s="8">
+      <c r="A69" s="4">
         <v>46254.0</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C69" s="14"/>
       <c r="D69" s="7">
         <v>114357.0</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F69" s="7">
         <v>120.0</v>
@@ -9982,26 +10100,26 @@
       <c r="H69" s="7">
         <v>120.0</v>
       </c>
-      <c r="I69" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J69" s="12" t="s">
-        <v>133</v>
+      <c r="I69" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="70" ht="19.5" hidden="1" customHeight="1">
-      <c r="A70" s="8">
+      <c r="A70" s="4">
         <v>46254.0</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="7">
         <v>10601.0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F70" s="7">
         <v>5700.0</v>
@@ -10012,26 +10130,26 @@
       <c r="H70" s="7">
         <v>9270.0</v>
       </c>
-      <c r="I70" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="12" t="s">
-        <v>135</v>
+      <c r="I70" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="71" ht="19.5" hidden="1" customHeight="1">
-      <c r="A71" s="8">
+      <c r="A71" s="4">
         <v>46254.0</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C71" s="14"/>
       <c r="D71" s="7">
         <v>114268.0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F71" s="7">
         <v>2700.0</v>
@@ -10042,26 +10160,26 @@
       <c r="H71" s="7">
         <v>5700.0</v>
       </c>
-      <c r="I71" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="12" t="s">
-        <v>135</v>
+      <c r="I71" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="72" ht="19.5" hidden="1" customHeight="1">
-      <c r="A72" s="8">
+      <c r="A72" s="4">
         <v>46254.0</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C72" s="14"/>
       <c r="D72" s="7">
         <v>2114379.0</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F72" s="7">
         <v>2340.0</v>
@@ -10072,26 +10190,26 @@
       <c r="H72" s="7">
         <v>2340.0</v>
       </c>
-      <c r="I72" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="12" t="s">
-        <v>135</v>
+      <c r="I72" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
-      <c r="A73" s="8">
+      <c r="A73" s="4">
         <v>46255.0</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C73" s="14"/>
       <c r="D73" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F73" s="7">
         <v>88073.0</v>
@@ -10102,26 +10220,26 @@
       <c r="H73" s="7">
         <v>23165.0</v>
       </c>
-      <c r="I73" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J73" s="12" t="s">
+      <c r="I73" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J73" s="9" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
-      <c r="A74" s="8">
+      <c r="A74" s="4">
         <v>46255.0</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="7">
         <v>2110202.0</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F74" s="7">
         <v>72060.0</v>
@@ -10132,26 +10250,26 @@
       <c r="H74" s="7">
         <v>133320.0</v>
       </c>
-      <c r="I74" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" s="12" t="s">
-        <v>135</v>
+      <c r="I74" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
-      <c r="A75" s="8">
+      <c r="A75" s="4">
         <v>46255.0</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C75" s="14"/>
       <c r="D75" s="7">
         <v>152384.0</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F75" s="7">
         <v>6600.0</v>
@@ -10162,11 +10280,11 @@
       <c r="H75" s="7">
         <v>1200.0</v>
       </c>
-      <c r="I75" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J75" s="12" t="s">
-        <v>135</v>
+      <c r="I75" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
@@ -10174,14 +10292,14 @@
         <v>46256.0</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C76" s="14"/>
       <c r="D76" s="7">
         <v>13358.0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F76" s="7">
         <v>288.0</v>
@@ -10192,18 +10310,68 @@
       <c r="H76" s="7">
         <v>288.0</v>
       </c>
-      <c r="I76" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J76" s="12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="I77" s="23"/>
-    </row>
-    <row r="78">
-      <c r="I78" s="23"/>
+      <c r="I76" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J76" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77" ht="22.5" customHeight="1">
+      <c r="A77" s="22">
+        <v>46261.0</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="14"/>
+      <c r="D77" s="7">
+        <v>10601.0</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F77" s="7">
+        <v>16770.0</v>
+      </c>
+      <c r="G77" s="7">
+        <v>20160.0</v>
+      </c>
+      <c r="H77" s="7">
+        <v>2670.0</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="9"/>
+    </row>
+    <row r="78" ht="22.5" customHeight="1">
+      <c r="A78" s="22">
+        <v>46261.0</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="14"/>
+      <c r="D78" s="7">
+        <v>114379.0</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F78" s="7">
+        <v>3600.0</v>
+      </c>
+      <c r="G78" s="7">
+        <v>1500.0</v>
+      </c>
+      <c r="H78" s="7">
+        <v>3600.0</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J78" s="9"/>
     </row>
     <row r="79">
       <c r="I79" s="23"/>
@@ -12847,13 +13015,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I76">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I78">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I77:I958">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I79:I958">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A76">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A78">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="199">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -56,6 +56,9 @@
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
+    <t>ALKA2</t>
+  </si>
+  <si>
     <t>TAT MONTERIA</t>
   </si>
   <si>
@@ -95,6 +98,15 @@
     <t>7. Otro</t>
   </si>
   <si>
+    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
+  </si>
+  <si>
+    <t>LANZA</t>
+  </si>
+  <si>
+    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
+  </si>
+  <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
@@ -107,9 +119,15 @@
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
+    <t>6. Transformación De Referencias</t>
+  </si>
+  <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
+    <t>Pendiente Transformar Roto GT Por manipulación</t>
+  </si>
+  <si>
     <t>TAT CALI</t>
   </si>
   <si>
@@ -125,18 +143,42 @@
     <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
-    <t>6. Transformación De Referencias</t>
+    <t>HUEVO B X30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>se equivocaron al cargar una estiba</t>
   </si>
   <si>
     <t>Clientes FS</t>
   </si>
   <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
+  </si>
+  <si>
+    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+  </si>
+  <si>
     <t>Transformación de PET</t>
   </si>
   <si>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+  </si>
+  <si>
     <t>ANDRES MEJIA</t>
   </si>
   <si>
@@ -146,85 +188,88 @@
     <t>TAT POPAYAN</t>
   </si>
   <si>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
+  </si>
+  <si>
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+  </si>
+  <si>
+    <t>HUEVO PICADO ROJO</t>
+  </si>
+  <si>
+    <t>No se carga todod por capacidad de Vehiculo</t>
+  </si>
+  <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
-    <t>ALKA2</t>
+    <t>HUEVO SUCIO DE JAULA</t>
   </si>
   <si>
     <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
-    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
-  </si>
-  <si>
-    <t>LANZA</t>
-  </si>
-  <si>
-    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
+    <t>Esta para despacho hoy</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
   </si>
   <si>
-    <t>Pendiente Transformar Roto GT Por manipulación</t>
-  </si>
-  <si>
-    <t>HUEVO B X30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>se equivocaron al cargar una estiba</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+    <t>Cola de programación</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+  </si>
+  <si>
+    <t>HUEVO CX30 CARTON GRIS</t>
   </si>
   <si>
     <t>5. Ingreso De Planta</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
-  </si>
-  <si>
-    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
     <t>Se despacha par FS con producto más nuevo</t>
   </si>
   <si>
-    <t>PALMAS</t>
-  </si>
-  <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
-  </si>
-  <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
-  </si>
-  <si>
     <t>ANDREA QUIROGA</t>
   </si>
   <si>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
+  </si>
+  <si>
     <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
   </si>
   <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
-  </si>
-  <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
     <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
-    <t>HUEVO PICADO ROJO</t>
-  </si>
-  <si>
-    <t>No se carga todod por capacidad de Vehiculo</t>
+    <t>ALKA1</t>
+  </si>
+  <si>
+    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
+  </si>
+  <si>
+    <t>HUEVO ROTO - ZF</t>
+  </si>
+  <si>
+    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
   </si>
   <si>
     <t>TAT PASTO</t>
@@ -233,42 +278,27 @@
     <t>CAROLINA VITERI</t>
   </si>
   <si>
-    <t>HUEVO SUCIO DE JAULA</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
-  </si>
-  <si>
-    <t>Esta para despacho hoy</t>
+    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
   </si>
   <si>
     <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
+    <t>Cargo en incubación</t>
+  </si>
+  <si>
     <t>Pedido para villavicencio</t>
   </si>
   <si>
-    <t>Cola de programación</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
     <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
-  </si>
-  <si>
-    <t>HUEVO CX30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
-  </si>
-  <si>
     <t>Inventario de Asesor de Rionegro que renuncio</t>
   </si>
   <si>
@@ -278,175 +308,97 @@
     <t>Jhonatan Gomez</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+    <t>BELLAVISTA</t>
   </si>
   <si>
     <t>Lote mezclado en la misma estiba</t>
   </si>
   <si>
+    <t>Traslado a cedi, producto de devolución</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CANASTA</t>
+  </si>
+  <si>
     <t>Supera edad solicitada clientes grandes superficies</t>
   </si>
   <si>
     <t>Pedido para villacicencio</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
+    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
   </si>
   <si>
     <t>Se envía huevo más fresco a Sincelejo</t>
   </si>
   <si>
+    <t>HUEVO SUCIO ZF MARCADO</t>
+  </si>
+  <si>
     <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
   </si>
   <si>
+    <t>vehiculo con flata de capacidad / TAT cali</t>
+  </si>
+  <si>
     <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
   </si>
   <si>
-    <t>ALKA1</t>
-  </si>
-  <si>
     <t>SalIO en sugeridos de hoy 22/07/2026</t>
   </si>
   <si>
     <t>Yovanis Arevalo</t>
   </si>
   <si>
-    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
-  </si>
-  <si>
     <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
   </si>
   <si>
-    <t>HUEVO ROTO - ZF</t>
-  </si>
-  <si>
-    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
-  </si>
-  <si>
-    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
-  </si>
-  <si>
     <t>Devolucion de huevo de 12 dias en mal estado</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
     <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
   </si>
   <si>
-    <t>Cargo en incubación</t>
-  </si>
-  <si>
     <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
     <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
   </si>
   <si>
+    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
+  </si>
+  <si>
     <t>Se envía producto a Sincelejo con menor edad</t>
   </si>
   <si>
+    <t>vehiculo pendiente pro llegar a planta</t>
+  </si>
+  <si>
+    <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
+  </si>
+  <si>
     <t>Producto que queda de clientes de preventa - TAT, que el cliente no recibe</t>
   </si>
   <si>
+    <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
+  </si>
+  <si>
+    <t>no salio el dia progrmado por falta de flota, se corre despacho para el dia siguiente en la tarde</t>
+  </si>
+  <si>
     <t>TAT VILLAVICENCIO</t>
   </si>
   <si>
-    <t>BELLAVISTA</t>
-  </si>
-  <si>
-    <t>Traslado a cedi, producto de devolución</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CANASTA</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En la estiba llegan lotes en la parte de abajo </t>
-  </si>
-  <si>
-    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
-  </si>
-  <si>
-    <t>HUEVO SUCIO ZF MARCADO</t>
-  </si>
-  <si>
-    <t>TAT BUCARAMANGA</t>
-  </si>
-  <si>
-    <t>SHIRLEY ARIZA</t>
-  </si>
-  <si>
-    <t>vehiculo con flata de capacidad / TAT cali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No salio la totalidad  de la mercancia y se roto el de 5 dias </t>
-  </si>
-  <si>
-    <t>Producto queda en CEDI por calidad</t>
-  </si>
-  <si>
-    <t>Producto devuelto clientes TAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALEXANDER PEÑA </t>
-  </si>
-  <si>
-    <t>Llegaron canastas combinados llegaron en la parte de abajo</t>
-  </si>
-  <si>
-    <t>ANDRES MEJA</t>
-  </si>
-  <si>
-    <t>Se envía lotemás nuevo a Sincelejo</t>
-  </si>
-  <si>
-    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
-  </si>
-  <si>
-    <t>vehiculo pendiente pro llegar a planta</t>
-  </si>
-  <si>
-    <t>Se envía huevo más fresco para clientes FS</t>
-  </si>
-  <si>
-    <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
-  </si>
-  <si>
-    <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
-  </si>
-  <si>
-    <t>Producto enviado a Rionegro y para FS más fresco</t>
-  </si>
-  <si>
-    <t>no salio el dia progrmado por falta de flota, se corre despacho para el dia siguiente en la tarde</t>
-  </si>
-  <si>
-    <t>Identificación producto averiado en el momento de la entrega del TAT, se bandejea</t>
-  </si>
-  <si>
     <t>anularon pedidos y por orden de planeacion se autorizo soltar para enviar a medellin</t>
   </si>
   <si>
-    <t>yOVANIS AREVALO</t>
-  </si>
-  <si>
     <t>Clasificación entrego una caja de más y no fue posible rotarla en cliente olimpica.</t>
   </si>
   <si>
-    <t xml:space="preserve">DEV CLIENTE MAS POR MENOS </t>
-  </si>
-  <si>
     <t>NO SE PUEDE BAJAR DE LA ESTANTERIA POR DAÑO DE PANTOGRAFOS</t>
-  </si>
-  <si>
-    <t>Se envía huevo fresco a Rionegro</t>
   </si>
   <si>
     <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
@@ -456,9 +408,63 @@
 En simultáneo, se cargó la mula y se desencadenaron las 18.000 unidades de 112379 para despachar para Medellín. En esta acción nos percatamos solo cuando la mula ya estaba en un 70 % cargada que se nos estaban quedando 21.525 de la referencia L canastas (2110302) con fecha de producción 19/08/2026.</t>
   </si>
   <si>
+    <t xml:space="preserve">En la estiba llegan lotes en la parte de abajo </t>
+  </si>
+  <si>
     <t>REPOSICION SIN SOLTAR</t>
   </si>
   <si>
+    <t>TAT BUCARAMANGA</t>
+  </si>
+  <si>
+    <t>SHIRLEY ARIZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No salio la totalidad  de la mercancia y se roto el de 5 dias </t>
+  </si>
+  <si>
+    <t>Producto queda en CEDI por calidad</t>
+  </si>
+  <si>
+    <t>Producto devuelto clientes TAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDER PEÑA </t>
+  </si>
+  <si>
+    <t>Llegaron canastas combinados llegaron en la parte de abajo</t>
+  </si>
+  <si>
+    <t>ANDRES MEJA</t>
+  </si>
+  <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE AMARRADO</t>
+  </si>
+  <si>
+    <t>Se envía lotemás nuevo a Sincelejo</t>
+  </si>
+  <si>
+    <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
+  </si>
+  <si>
+    <t>Se envía huevo más fresco para clientes FS</t>
+  </si>
+  <si>
+    <t>Producto enviado a Rionegro y para FS más fresco</t>
+  </si>
+  <si>
+    <t>Identificación producto averiado en el momento de la entrega del TAT, se bandejea</t>
+  </si>
+  <si>
+    <t>yOVANIS AREVALO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEV CLIENTE MAS POR MENOS </t>
+  </si>
+  <si>
+    <t>Se envía huevo fresco a Rionegro</t>
+  </si>
+  <si>
     <t>Clientes Fs</t>
   </si>
   <si>
@@ -480,18 +486,12 @@
     <t xml:space="preserve">Asignado canal TAT </t>
   </si>
   <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE AMARRADO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yovanis Arevalo </t>
   </si>
   <si>
     <t xml:space="preserve">salida de pedido especial </t>
   </si>
   <si>
-    <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
-  </si>
-  <si>
     <t>novedad en lotes por calidad</t>
   </si>
   <si>
@@ -604,6 +604,12 @@
   </si>
   <si>
     <t>PARA ENTREGA CLIENTE FS</t>
+  </si>
+  <si>
+    <t>PENDIENTE TRANSFORMACION</t>
+  </si>
+  <si>
+    <t>HOY SE TERMINA DE ENTREGAR AYER SOLICITARON 13.294 UNIDADES</t>
   </si>
 </sst>
 </file>
@@ -692,11 +698,11 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -708,24 +714,24 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -827,7 +833,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J151" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J154" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -845,7 +851,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J88" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J89" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -1132,25 +1138,25 @@
       <c r="H2" s="7">
         <v>206140.0</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>46205.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" s="7">
         <v>298282.0</v>
@@ -1162,25 +1168,25 @@
         <v>260675.0</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>46205.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="7">
         <v>2110217.0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="7">
         <v>21120.0</v>
@@ -1197,20 +1203,20 @@
       <c r="J4" s="11"/>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>46205.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="7">
         <v>75680.0</v>
@@ -1222,21 +1228,21 @@
         <v>3134.0</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>46206.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="7">
         <v>2110202.0</v>
@@ -1254,27 +1260,27 @@
         <v>144720.0</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>46206.0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7" s="7">
         <v>20640.0</v>
@@ -1286,27 +1292,27 @@
         <v>13920.0</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>46206.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="7">
         <v>152384.0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F8" s="7">
         <v>14700.0</v>
@@ -1318,19 +1324,19 @@
         <v>9600.0</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J8" s="12"/>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>46206.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D9" s="7">
         <v>2110202.0</v>
@@ -1348,25 +1354,25 @@
         <v>124260.0</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J9" s="12"/>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>46206.0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D10" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F10" s="7">
         <v>7830.0</v>
@@ -1378,25 +1384,25 @@
         <v>6030.0</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="13"/>
+        <v>35</v>
+      </c>
+      <c r="J10" s="15"/>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>46206.0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" s="7">
         <v>31680.0</v>
@@ -1408,27 +1414,27 @@
         <v>23040.0</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>46206.0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" s="7">
         <v>51387.0</v>
@@ -1440,27 +1446,27 @@
         <v>12170.0</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>46209.0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" s="7">
         <v>195810.0</v>
@@ -1472,27 +1478,27 @@
         <v>133410.0</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>46209.0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" s="7">
         <v>526002.0</v>
@@ -1504,27 +1510,27 @@
         <v>424588.0</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>46209.0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D15" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F15" s="7">
         <v>14160.0</v>
@@ -1536,27 +1542,27 @@
         <v>12360.0</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>46210.0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D16" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16" s="7">
         <v>149040.0</v>
@@ -1573,20 +1579,20 @@
       <c r="J16" s="12"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>46210.0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D17" s="7">
         <v>2110217.0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17" s="7">
         <v>22770.0</v>
@@ -1603,20 +1609,20 @@
       <c r="J17" s="12"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>46210.0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D18" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18" s="7">
         <v>222021.0</v>
@@ -1633,20 +1639,20 @@
       <c r="J18" s="12"/>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="9">
+      <c r="A19" s="8">
         <v>46211.0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" s="7">
         <v>495833.0</v>
@@ -1658,27 +1664,27 @@
         <v>401280.0</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="9">
+      <c r="A20" s="8">
         <v>46211.0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" s="7">
         <v>139920.0</v>
@@ -1695,20 +1701,20 @@
       <c r="J20" s="12"/>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="9">
+      <c r="A21" s="8">
         <v>46211.0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D21" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" s="7">
         <v>162125.0</v>
@@ -1720,14 +1726,14 @@
         <v>100687.0</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="9">
+      <c r="A22" s="8">
         <v>46211.0</v>
       </c>
       <c r="B22" s="5" t="s">
@@ -1740,7 +1746,7 @@
         <v>152384.0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F22" s="7">
         <v>32850.0</v>
@@ -1752,25 +1758,25 @@
         <v>32700.0</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J22" s="12"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="9">
+      <c r="A23" s="8">
         <v>46211.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D23" s="7">
         <v>112271.0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F23" s="7">
         <v>16500.0</v>
@@ -1782,19 +1788,19 @@
         <v>18000.0</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J23" s="12"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="9">
+      <c r="A24" s="8">
         <v>46212.0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D24" s="7">
         <v>2110202.0</v>
@@ -1812,25 +1818,25 @@
         <v>248481.0</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J24" s="12"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="9">
+      <c r="A25" s="8">
         <v>46212.0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D25" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25" s="7">
         <v>178080.0</v>
@@ -1842,25 +1848,25 @@
         <v>203520.0</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="J25" s="12"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="9">
+      <c r="A26" s="8">
         <v>46212.0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D26" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F26" s="7">
         <v>10320.0</v>
@@ -1872,27 +1878,27 @@
         <v>13200.0</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="9">
+      <c r="A27" s="8">
         <v>46212.0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D27" s="7">
         <v>112271.0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F27" s="7">
         <v>18000.0</v>
@@ -1904,25 +1910,25 @@
         <v>13500.0</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" s="12"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="9">
+      <c r="A28" s="8">
         <v>46213.0</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D28" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" s="7">
         <v>208440.0</v>
@@ -1934,21 +1940,21 @@
         <v>150833.0</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="9">
+      <c r="A29" s="8">
         <v>46213.0</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D29" s="7">
         <v>2110202.0</v>
@@ -1966,21 +1972,21 @@
         <v>922140.0</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="9">
+      <c r="A30" s="8">
         <v>46213.0</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D30" s="7">
         <v>2110202.0</v>
@@ -1998,27 +2004,27 @@
         <v>381600.0</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="9">
+      <c r="A31" s="8">
         <v>46213.0</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D31" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31" s="7">
         <v>316800.0</v>
@@ -2030,25 +2036,25 @@
         <v>229680.0</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J31" s="12"/>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="9">
+      <c r="A32" s="8">
         <v>46213.0</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D32" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F32" s="7">
         <v>176850.0</v>
@@ -2060,25 +2066,25 @@
         <v>128971.0</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J32" s="12"/>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="9">
+      <c r="A33" s="8">
         <v>46213.0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D33" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F33" s="7">
         <v>58080.0</v>
@@ -2090,25 +2096,25 @@
         <v>25440.0</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J33" s="12"/>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="9">
+      <c r="A34" s="8">
         <v>46217.0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D34" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F34" s="7">
         <v>481440.0</v>
@@ -2120,19 +2126,19 @@
         <v>151435.0</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J34" s="12"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="9">
+      <c r="A35" s="8">
         <v>46217.0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D35" s="7">
         <v>2110202.0</v>
@@ -2155,20 +2161,20 @@
       <c r="J35" s="12"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="9">
+      <c r="A36" s="8">
         <v>46217.0</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D36" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F36" s="7">
         <v>35280.0</v>
@@ -2180,27 +2186,27 @@
         <v>37926.0</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
-      <c r="A37" s="17">
+      <c r="A37" s="19">
         <v>46218.0</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D37" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F37" s="7">
         <v>272073.0</v>
@@ -2212,27 +2218,27 @@
         <v>275205.0</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
-      <c r="A38" s="17">
+      <c r="A38" s="19">
         <v>46218.0</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D38" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F38" s="7">
         <v>37926.0</v>
@@ -2244,27 +2250,27 @@
         <v>25746.0</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
-      <c r="A39" s="17">
+      <c r="A39" s="19">
         <v>46218.0</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D39" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F39" s="7">
         <v>20640.0</v>
@@ -2276,27 +2282,27 @@
         <v>16320.0</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
-      <c r="A40" s="17">
+      <c r="A40" s="19">
         <v>46218.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D40" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F40" s="7">
         <v>10980.0</v>
@@ -2308,25 +2314,25 @@
         <v>13500.0</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J40" s="12"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="9">
+      <c r="A41" s="8">
         <v>46219.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F41" s="7">
         <v>130320.0</v>
@@ -2338,27 +2344,27 @@
         <v>90480.0</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="9">
+      <c r="A42" s="8">
         <v>46219.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D42" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F42" s="7">
         <v>36225.0</v>
@@ -2375,20 +2381,20 @@
       <c r="J42" s="12"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="9">
+      <c r="A43" s="8">
         <v>46219.0</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D43" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F43" s="7">
         <v>152833.0</v>
@@ -2400,27 +2406,27 @@
         <v>96472.0</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="9">
+      <c r="A44" s="8">
         <v>46219.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D44" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F44" s="7">
         <v>237828.0</v>
@@ -2432,25 +2438,25 @@
         <v>71560.0</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J44" s="12"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="9">
+      <c r="A45" s="8">
         <v>46219.0</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D45" s="7">
         <v>152384.0</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F45" s="7">
         <v>31125.0</v>
@@ -2462,27 +2468,27 @@
         <v>31845.0</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="9">
+      <c r="A46" s="8">
         <v>46219.0</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D46" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F46" s="7">
         <v>25746.0</v>
@@ -2494,27 +2500,27 @@
         <v>28683.0</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="9">
+      <c r="A47" s="8">
         <v>46220.0</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D47" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F47" s="7">
         <v>261166.0</v>
@@ -2526,27 +2532,27 @@
         <v>221549.0</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="9">
+      <c r="A48" s="8">
         <v>46220.0</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D48" s="7">
         <v>2110217.0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F48" s="7">
         <v>115289.0</v>
@@ -2558,25 +2564,25 @@
         <v>119584.0</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J48" s="12"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="9">
+      <c r="A49" s="8">
         <v>46224.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D49" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F49" s="7">
         <v>398570.0</v>
@@ -2588,27 +2594,27 @@
         <v>287235.0</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="9">
+      <c r="A50" s="8">
         <v>46224.0</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D50" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F50" s="7">
         <v>745107.0</v>
@@ -2620,27 +2626,27 @@
         <v>551645.0</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="9">
+      <c r="A51" s="8">
         <v>46225.0</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D51" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F51" s="7">
         <v>130560.0</v>
@@ -2652,27 +2658,27 @@
         <v>153840.0</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="9">
+      <c r="A52" s="8">
         <v>46225.0</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D52" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F52" s="7">
         <v>87447.0</v>
@@ -2684,25 +2690,25 @@
         <v>104365.0</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J52" s="12"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="9">
+      <c r="A53" s="8">
         <v>46225.0</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D53" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F53" s="7">
         <v>25200.0</v>
@@ -2714,27 +2720,27 @@
         <v>25920.0</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
-      <c r="A54" s="9">
+      <c r="A54" s="8">
         <v>46226.0</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D54" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F54" s="7">
         <v>285405.0</v>
@@ -2746,21 +2752,21 @@
         <v>226069.0</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
-      <c r="A55" s="9">
+      <c r="A55" s="8">
         <v>46226.0</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D55" s="7">
         <v>2110202.0</v>
@@ -2778,19 +2784,19 @@
         <v>700200.0</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="J55" s="12"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
-      <c r="A56" s="9">
+      <c r="A56" s="8">
         <v>46227.0</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D56" s="7">
         <v>2110202.0</v>
@@ -2808,25 +2814,25 @@
         <v>668440.0</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J56" s="12"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
-      <c r="A57" s="9">
+      <c r="A57" s="8">
         <v>46227.0</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D57" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F57" s="7">
         <v>226069.0</v>
@@ -2838,21 +2844,21 @@
         <v>326391.0</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
-      <c r="A58" s="9">
+      <c r="A58" s="8">
         <v>46227.0</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D58" s="7">
         <v>2110202.0</v>
@@ -2870,25 +2876,25 @@
         <v>128160.0</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="J58" s="12"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="9">
+      <c r="A59" s="8">
         <v>46227.0</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D59" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F59" s="7">
         <v>295359.0</v>
@@ -2900,27 +2906,27 @@
         <v>166642.0</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="9">
+      <c r="A60" s="8">
         <v>46230.0</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D60" s="7">
         <v>2110403.0</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F60" s="7">
         <v>9960.0</v>
@@ -2932,25 +2938,25 @@
         <v>3660.0</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J60" s="12"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="9">
+      <c r="A61" s="8">
         <v>46230.0</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D61" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F61" s="7">
         <v>306720.0</v>
@@ -2962,19 +2968,19 @@
         <v>247096.0</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J61" s="12"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
-      <c r="A62" s="9">
+      <c r="A62" s="8">
         <v>46230.0</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D62" s="7">
         <v>2110202.0</v>
@@ -2992,27 +2998,27 @@
         <v>353700.0</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
-      <c r="A63" s="9">
+      <c r="A63" s="8">
         <v>46231.0</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D63" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F63" s="7">
         <v>165466.0</v>
@@ -3024,27 +3030,27 @@
         <v>375549.0</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
-      <c r="A64" s="9">
+      <c r="A64" s="8">
         <v>46231.0</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D64" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F64" s="7">
         <v>238497.0</v>
@@ -3056,27 +3062,27 @@
         <v>181858.0</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
-      <c r="A65" s="9">
+      <c r="A65" s="8">
         <v>46231.0</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D65" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F65" s="7">
         <v>8190.0</v>
@@ -3088,21 +3094,21 @@
         <v>7200.0</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
-      <c r="A66" s="9">
+      <c r="A66" s="8">
         <v>46231.0</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D66" s="7">
         <v>2110202.0</v>
@@ -3120,18 +3126,18 @@
         <v>98850.0</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
-      <c r="A67" s="9">
+      <c r="A67" s="8">
         <v>46232.0</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C67" s="20"/>
       <c r="D67" s="7">
@@ -3150,23 +3156,23 @@
         <v>7263.0</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J67" s="12"/>
     </row>
     <row r="68" ht="22.5" hidden="1" customHeight="1">
-      <c r="A68" s="9">
+      <c r="A68" s="8">
         <v>46232.0</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C68" s="20"/>
       <c r="D68" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F68" s="7">
         <v>22080.0</v>
@@ -3178,23 +3184,23 @@
         <v>36720.0</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J68" s="12"/>
     </row>
     <row r="69" ht="22.5" hidden="1" customHeight="1">
-      <c r="A69" s="9">
+      <c r="A69" s="8">
         <v>46232.0</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C69" s="20"/>
       <c r="D69" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F69" s="7">
         <v>353905.0</v>
@@ -3206,23 +3212,23 @@
         <v>117570.0</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J69" s="12"/>
     </row>
     <row r="70" ht="22.5" hidden="1" customHeight="1">
-      <c r="A70" s="9">
+      <c r="A70" s="8">
         <v>46232.0</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="7">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F70" s="7">
         <v>5913.0</v>
@@ -3234,12 +3240,12 @@
         <v>5893.0</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J70" s="12"/>
     </row>
     <row r="71" ht="22.5" hidden="1" customHeight="1">
-      <c r="A71" s="9">
+      <c r="A71" s="8">
         <v>46232.0</v>
       </c>
       <c r="B71" s="5" t="s">
@@ -3250,7 +3256,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F71" s="7">
         <v>256613.0</v>
@@ -3262,12 +3268,12 @@
         <v>142320.0</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J71" s="12"/>
     </row>
     <row r="72" ht="22.5" hidden="1" customHeight="1">
-      <c r="A72" s="9">
+      <c r="A72" s="8">
         <v>46232.0</v>
       </c>
       <c r="B72" s="5" t="s">
@@ -3278,7 +3284,7 @@
         <v>152384.0</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F72" s="7">
         <v>21300.0</v>
@@ -3290,23 +3296,23 @@
         <v>18690.0</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J72" s="12"/>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
-      <c r="A73" s="9">
+      <c r="A73" s="8">
         <v>46232.0</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C73" s="20"/>
       <c r="D73" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F73" s="7">
         <v>351733.0</v>
@@ -3318,25 +3324,25 @@
         <v>200114.0</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J73" s="12"/>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
-      <c r="A74" s="17">
+      <c r="A74" s="19">
         <v>46233.0</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D74" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F74" s="7">
         <v>158761.0</v>
@@ -3348,27 +3354,27 @@
         <v>183014.0</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
-      <c r="A75" s="17">
+      <c r="A75" s="19">
         <v>46233.0</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D75" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F75" s="7">
         <v>117430.0</v>
@@ -3380,25 +3386,25 @@
         <v>86643.0</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J75" s="12"/>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
-      <c r="A76" s="9">
+      <c r="A76" s="8">
         <v>46234.0</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D76" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F76" s="7">
         <v>265693.0</v>
@@ -3410,25 +3416,25 @@
         <v>116000.0</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J76" s="12"/>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
-      <c r="A77" s="9">
+      <c r="A77" s="8">
         <v>46234.0</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D77" s="7">
         <v>112357.0</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F77" s="7">
         <v>720.0</v>
@@ -3440,27 +3446,27 @@
         <v>2040.0</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
-      <c r="A78" s="9">
+      <c r="A78" s="8">
         <v>46234.0</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D78" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F78" s="7">
         <v>5580.0</v>
@@ -3472,21 +3478,21 @@
         <v>3984.0</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" ht="22.5" hidden="1" customHeight="1">
-      <c r="A79" s="19">
+      <c r="A79" s="18">
         <v>46237.0</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D79" s="7">
         <v>2110202.0</v>
@@ -3504,27 +3510,27 @@
         <v>77501.0</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="80" ht="22.5" hidden="1" customHeight="1">
-      <c r="A80" s="19">
+      <c r="A80" s="18">
         <v>46237.0</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D80" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F80" s="7">
         <v>152062.0</v>
@@ -3536,27 +3542,27 @@
         <v>124423.0</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J80" s="12" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81" ht="22.5" hidden="1" customHeight="1">
-      <c r="A81" s="19">
+      <c r="A81" s="18">
         <v>46237.0</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D81" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F81" s="7">
         <v>153692.0</v>
@@ -3568,27 +3574,27 @@
         <v>63920.0</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" ht="22.5" hidden="1" customHeight="1">
-      <c r="A82" s="19">
+      <c r="A82" s="18">
         <v>46237.0</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D82" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" s="7">
         <v>45564.0</v>
@@ -3605,20 +3611,20 @@
       <c r="J82" s="12"/>
     </row>
     <row r="83" ht="22.5" hidden="1" customHeight="1">
-      <c r="A83" s="19">
+      <c r="A83" s="18">
         <v>46237.0</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D83" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F83" s="7">
         <v>93517.0</v>
@@ -3630,27 +3636,27 @@
         <v>48804.0</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" ht="22.5" hidden="1" customHeight="1">
-      <c r="A84" s="9">
+      <c r="A84" s="8">
         <v>46238.0</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D84" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F84" s="7">
         <v>43200.0</v>
@@ -3662,25 +3668,25 @@
         <v>40890.0</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J84" s="12"/>
     </row>
     <row r="85" ht="22.5" hidden="1" customHeight="1">
-      <c r="A85" s="9">
+      <c r="A85" s="8">
         <v>46238.0</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D85" s="7">
         <v>152384.0</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F85" s="7">
         <v>25350.0</v>
@@ -3692,25 +3698,25 @@
         <v>30750.0</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J85" s="12"/>
     </row>
     <row r="86" ht="22.5" hidden="1" customHeight="1">
-      <c r="A86" s="9">
+      <c r="A86" s="8">
         <v>46238.0</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D86" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F86" s="7">
         <v>5040.0</v>
@@ -3722,25 +3728,25 @@
         <v>4680.0</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J86" s="12"/>
     </row>
     <row r="87" ht="22.5" hidden="1" customHeight="1">
-      <c r="A87" s="9">
+      <c r="A87" s="8">
         <v>46238.0</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D87" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F87" s="7">
         <v>124423.0</v>
@@ -3752,27 +3758,27 @@
         <v>69217.0</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="88" ht="22.5" hidden="1" customHeight="1">
-      <c r="A88" s="9">
+      <c r="A88" s="8">
         <v>46239.0</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D88" s="7">
         <v>152384.0</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F88" s="7">
         <v>30750.0</v>
@@ -3784,25 +3790,25 @@
         <v>36300.0</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J88" s="12"/>
     </row>
     <row r="89" ht="22.5" hidden="1" customHeight="1">
-      <c r="A89" s="9">
+      <c r="A89" s="8">
         <v>46239.0</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D89" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F89" s="7">
         <v>58320.0</v>
@@ -3814,21 +3820,21 @@
         <v>12480.0</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="90" ht="22.5" hidden="1" customHeight="1">
-      <c r="A90" s="19">
+      <c r="A90" s="18">
         <v>46240.0</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D90" s="7">
         <v>2110202.0</v>
@@ -3846,27 +3852,27 @@
         <v>27180.0</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" ht="22.5" hidden="1" customHeight="1">
-      <c r="A91" s="19">
+      <c r="A91" s="18">
         <v>46240.0</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D91" s="7">
         <v>112379.0</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F91" s="7">
         <v>13800.0</v>
@@ -3878,25 +3884,25 @@
         <v>12132.0</v>
       </c>
       <c r="I91" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J91" s="12"/>
     </row>
     <row r="92" ht="22.5" hidden="1" customHeight="1">
-      <c r="A92" s="19">
+      <c r="A92" s="18">
         <v>46240.0</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D92" s="7">
         <v>2152388.0</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F92" s="7">
         <v>4575.0</v>
@@ -3908,10 +3914,10 @@
         <v>4213.0</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="93" ht="22.5" hidden="1" customHeight="1">
@@ -3919,16 +3925,16 @@
         <v>46244.0</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D93" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F93" s="7">
         <v>222000.0</v>
@@ -3940,10 +3946,10 @@
         <v>312480.0</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="94" ht="22.5" hidden="1" customHeight="1">
@@ -3951,10 +3957,10 @@
         <v>46244.0</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D94" s="7">
         <v>2110202.0</v>
@@ -3972,10 +3978,10 @@
         <v>260696.0</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="95" ht="22.5" hidden="1" customHeight="1">
@@ -3983,16 +3989,16 @@
         <v>46244.0</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D95" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F95" s="7">
         <v>36240.0</v>
@@ -4004,10 +4010,10 @@
         <v>39840.0</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="96" ht="22.5" hidden="1" customHeight="1">
@@ -4018,13 +4024,13 @@
         <v>10</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D96" s="7">
         <v>2110317.0</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F96" s="7">
         <v>21690.0</v>
@@ -4036,25 +4042,25 @@
         <v>26280.0</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J96" s="12"/>
     </row>
     <row r="97" ht="22.5" hidden="1" customHeight="1">
-      <c r="A97" s="9">
+      <c r="A97" s="8">
         <v>46245.0</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D97" s="7">
         <v>112271.0</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F97" s="7">
         <v>20100.0</v>
@@ -4066,25 +4072,25 @@
         <v>10800.0</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J97" s="12"/>
     </row>
     <row r="98" ht="22.5" hidden="1" customHeight="1">
-      <c r="A98" s="9">
+      <c r="A98" s="8">
         <v>46245.0</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D98" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F98" s="7">
         <v>39840.0</v>
@@ -4096,27 +4102,27 @@
         <v>23520.0</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="99" ht="22.5" hidden="1" customHeight="1">
-      <c r="A99" s="9">
+      <c r="A99" s="8">
         <v>46245.0</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D99" s="7">
         <v>152384.0</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F99" s="7">
         <v>18600.0</v>
@@ -4128,27 +4134,27 @@
         <v>12900.0</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="100" ht="22.5" hidden="1" customHeight="1">
-      <c r="A100" s="9">
+      <c r="A100" s="8">
         <v>46245.0</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D100" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F100" s="7">
         <v>225620.0</v>
@@ -4160,27 +4166,27 @@
         <v>269040.0</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="101" ht="22.5" hidden="1" customHeight="1">
-      <c r="A101" s="9">
+      <c r="A101" s="8">
         <v>46246.0</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D101" s="7">
         <v>2110402.0</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F101" s="7">
         <v>423758.0</v>
@@ -4195,18 +4201,18 @@
         <v>13</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="102" ht="22.5" hidden="1" customHeight="1">
-      <c r="A102" s="9">
+      <c r="A102" s="8">
         <v>46246.0</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D102" s="7">
         <v>2110202.0</v>
@@ -4224,27 +4230,27 @@
         <v>655250.0</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="103" ht="22.5" hidden="1" customHeight="1">
-      <c r="A103" s="9">
+      <c r="A103" s="8">
         <v>46246.0</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D103" s="7">
         <v>112271.0</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F103" s="7">
         <v>10815.0</v>
@@ -4256,27 +4262,27 @@
         <v>1935.0</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="104" ht="22.5" hidden="1" customHeight="1">
-      <c r="A104" s="9">
+      <c r="A104" s="8">
         <v>46246.0</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D104" s="7">
         <v>152384.0</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F104" s="7">
         <v>12900.0</v>
@@ -4288,27 +4294,27 @@
         <v>19800.0</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="105" ht="22.5" hidden="1" customHeight="1">
-      <c r="A105" s="9">
+      <c r="A105" s="8">
         <v>46247.0</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D105" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F105" s="7">
         <v>193026.0</v>
@@ -4320,21 +4326,21 @@
         <v>63824.0</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="106" ht="22.5" hidden="1" customHeight="1">
-      <c r="A106" s="9">
+      <c r="A106" s="8">
         <v>46247.0</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D106" s="7">
         <v>2110202.0</v>
@@ -4352,25 +4358,25 @@
         <v>230580.0</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J106" s="12"/>
     </row>
     <row r="107" ht="22.5" hidden="1" customHeight="1">
-      <c r="A107" s="9">
+      <c r="A107" s="8">
         <v>46247.0</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D107" s="7">
         <v>2110217.0</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F107" s="7">
         <v>21120.0</v>
@@ -4382,25 +4388,25 @@
         <v>17280.0</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J107" s="12"/>
     </row>
     <row r="108" ht="22.5" hidden="1" customHeight="1">
-      <c r="A108" s="9">
+      <c r="A108" s="8">
         <v>46247.0</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D108" s="7">
         <v>112271.0</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F108" s="7">
         <v>16500.0</v>
@@ -4412,19 +4418,19 @@
         <v>12600.0</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J108" s="12"/>
     </row>
     <row r="109" ht="22.5" hidden="1" customHeight="1">
-      <c r="A109" s="9">
+      <c r="A109" s="8">
         <v>46248.0</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D109" s="7">
         <v>2110202.0</v>
@@ -4442,27 +4448,27 @@
         <v>584490.0</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J109" s="12" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="110" ht="22.5" hidden="1" customHeight="1">
-      <c r="A110" s="9">
+      <c r="A110" s="8">
         <v>46248.0</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D110" s="7">
         <v>2110302.0</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F110" s="7">
         <v>289920.0</v>
@@ -4474,19 +4480,19 @@
         <v>247440.0</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J110" s="12"/>
     </row>
     <row r="111" ht="22.5" hidden="1" customHeight="1">
-      <c r="A111" s="9">
+      <c r="A111" s="8">
         <v>46248.0</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D111" s="7">
         <v>2110202.0</v>
@@ -4504,27 +4510,27 @@
         <v>298620.0</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J111" s="12" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="112" ht="22.5" hidden="1" customHeight="1">
-      <c r="A112" s="9">
+      <c r="A112" s="8">
         <v>46248.0</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D112" s="7">
         <v>152384.0</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F112" s="7">
         <v>13200.0</v>
@@ -4536,18 +4542,18 @@
         <v>7200.0</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J112" s="12" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="113" ht="22.5" hidden="1" customHeight="1">
-      <c r="A113" s="9">
+      <c r="A113" s="8">
         <v>46248.0</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>162</v>
@@ -4556,7 +4562,7 @@
         <v>152384.0</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F113" s="7">
         <v>9900.0</v>
@@ -4575,20 +4581,20 @@
       </c>
     </row>
     <row r="114" ht="22.5" hidden="1" customHeight="1">
-      <c r="A114" s="9">
+      <c r="A114" s="8">
         <v>46252.0</v>
